--- a/data_fetching/Entsoe/Wind_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Wind_Production_Historical.xlsx
@@ -31,568 +31,568 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>03.09.20261</t>
-  </si>
-  <si>
-    <t>03.09.20262</t>
-  </si>
-  <si>
-    <t>03.09.20263</t>
-  </si>
-  <si>
-    <t>03.09.20264</t>
-  </si>
-  <si>
-    <t>03.09.20265</t>
-  </si>
-  <si>
-    <t>03.09.20266</t>
-  </si>
-  <si>
-    <t>03.09.20267</t>
-  </si>
-  <si>
-    <t>03.09.20268</t>
-  </si>
-  <si>
-    <t>03.09.20269</t>
-  </si>
-  <si>
-    <t>03.09.202610</t>
-  </si>
-  <si>
-    <t>03.09.202611</t>
-  </si>
-  <si>
-    <t>03.09.202612</t>
-  </si>
-  <si>
-    <t>03.09.202613</t>
-  </si>
-  <si>
-    <t>03.09.202614</t>
-  </si>
-  <si>
-    <t>03.09.202615</t>
-  </si>
-  <si>
-    <t>03.09.202616</t>
-  </si>
-  <si>
-    <t>03.09.202617</t>
-  </si>
-  <si>
-    <t>03.09.202618</t>
-  </si>
-  <si>
-    <t>03.09.202619</t>
-  </si>
-  <si>
-    <t>03.09.202620</t>
-  </si>
-  <si>
-    <t>03.09.202621</t>
-  </si>
-  <si>
-    <t>03.09.202622</t>
-  </si>
-  <si>
-    <t>03.09.202623</t>
-  </si>
-  <si>
-    <t>03.09.202624</t>
-  </si>
-  <si>
-    <t>03.09.202625</t>
-  </si>
-  <si>
-    <t>03.09.202626</t>
-  </si>
-  <si>
-    <t>03.09.202627</t>
-  </si>
-  <si>
-    <t>03.09.202628</t>
-  </si>
-  <si>
-    <t>03.09.202629</t>
-  </si>
-  <si>
-    <t>03.09.202630</t>
-  </si>
-  <si>
-    <t>03.09.202631</t>
-  </si>
-  <si>
-    <t>03.09.202632</t>
-  </si>
-  <si>
-    <t>03.09.202633</t>
-  </si>
-  <si>
-    <t>03.09.202634</t>
-  </si>
-  <si>
-    <t>03.09.202635</t>
-  </si>
-  <si>
-    <t>03.09.202636</t>
-  </si>
-  <si>
-    <t>03.09.202637</t>
-  </si>
-  <si>
-    <t>03.09.202638</t>
-  </si>
-  <si>
-    <t>03.09.202639</t>
-  </si>
-  <si>
-    <t>03.09.202640</t>
-  </si>
-  <si>
-    <t>03.09.202641</t>
-  </si>
-  <si>
-    <t>03.09.202642</t>
-  </si>
-  <si>
-    <t>03.09.202643</t>
-  </si>
-  <si>
-    <t>03.09.202644</t>
-  </si>
-  <si>
-    <t>03.09.202645</t>
-  </si>
-  <si>
-    <t>03.09.202646</t>
-  </si>
-  <si>
-    <t>03.09.202647</t>
-  </si>
-  <si>
-    <t>03.09.202648</t>
-  </si>
-  <si>
-    <t>03.09.202649</t>
-  </si>
-  <si>
-    <t>03.09.202650</t>
-  </si>
-  <si>
-    <t>03.09.202651</t>
-  </si>
-  <si>
-    <t>03.09.202652</t>
-  </si>
-  <si>
-    <t>03.09.202653</t>
-  </si>
-  <si>
-    <t>03.09.202654</t>
-  </si>
-  <si>
-    <t>03.09.202655</t>
-  </si>
-  <si>
-    <t>03.09.202656</t>
-  </si>
-  <si>
-    <t>03.09.202657</t>
-  </si>
-  <si>
-    <t>03.09.202658</t>
-  </si>
-  <si>
-    <t>03.09.202659</t>
-  </si>
-  <si>
-    <t>03.09.202660</t>
-  </si>
-  <si>
-    <t>03.09.202661</t>
-  </si>
-  <si>
-    <t>03.09.202662</t>
-  </si>
-  <si>
-    <t>03.09.202663</t>
-  </si>
-  <si>
-    <t>03.09.202664</t>
-  </si>
-  <si>
-    <t>03.09.202665</t>
-  </si>
-  <si>
-    <t>03.09.202666</t>
-  </si>
-  <si>
-    <t>03.09.202667</t>
-  </si>
-  <si>
-    <t>03.09.202668</t>
-  </si>
-  <si>
-    <t>03.09.202669</t>
-  </si>
-  <si>
-    <t>03.09.202670</t>
-  </si>
-  <si>
-    <t>03.09.202671</t>
-  </si>
-  <si>
-    <t>03.09.202672</t>
-  </si>
-  <si>
-    <t>03.09.202673</t>
-  </si>
-  <si>
-    <t>03.09.202674</t>
-  </si>
-  <si>
-    <t>03.09.202675</t>
-  </si>
-  <si>
-    <t>03.09.202676</t>
-  </si>
-  <si>
-    <t>03.09.202677</t>
-  </si>
-  <si>
-    <t>03.09.202678</t>
-  </si>
-  <si>
-    <t>03.09.202679</t>
-  </si>
-  <si>
-    <t>03.09.202680</t>
-  </si>
-  <si>
-    <t>03.09.202681</t>
-  </si>
-  <si>
-    <t>03.09.202682</t>
-  </si>
-  <si>
-    <t>03.09.202683</t>
-  </si>
-  <si>
-    <t>03.09.202684</t>
-  </si>
-  <si>
-    <t>03.09.202685</t>
-  </si>
-  <si>
-    <t>03.09.202686</t>
-  </si>
-  <si>
-    <t>03.09.202687</t>
-  </si>
-  <si>
-    <t>03.09.202688</t>
-  </si>
-  <si>
-    <t>03.09.202689</t>
-  </si>
-  <si>
-    <t>03.09.202690</t>
-  </si>
-  <si>
-    <t>03.09.202691</t>
-  </si>
-  <si>
-    <t>03.09.202692</t>
-  </si>
-  <si>
-    <t>03.09.202693</t>
-  </si>
-  <si>
-    <t>03.09.202694</t>
-  </si>
-  <si>
-    <t>03.09.202695</t>
-  </si>
-  <si>
-    <t>03.09.202696</t>
-  </si>
-  <si>
-    <t>04.09.20261</t>
-  </si>
-  <si>
-    <t>04.09.20262</t>
-  </si>
-  <si>
-    <t>04.09.20263</t>
-  </si>
-  <si>
-    <t>04.09.20264</t>
-  </si>
-  <si>
-    <t>04.09.20265</t>
-  </si>
-  <si>
-    <t>04.09.20266</t>
-  </si>
-  <si>
-    <t>04.09.20267</t>
-  </si>
-  <si>
-    <t>04.09.20268</t>
-  </si>
-  <si>
-    <t>04.09.20269</t>
-  </si>
-  <si>
-    <t>04.09.202610</t>
-  </si>
-  <si>
-    <t>04.09.202611</t>
-  </si>
-  <si>
-    <t>04.09.202612</t>
-  </si>
-  <si>
-    <t>04.09.202613</t>
-  </si>
-  <si>
-    <t>04.09.202614</t>
-  </si>
-  <si>
-    <t>04.09.202615</t>
-  </si>
-  <si>
-    <t>04.09.202616</t>
-  </si>
-  <si>
-    <t>04.09.202617</t>
-  </si>
-  <si>
-    <t>04.09.202618</t>
-  </si>
-  <si>
-    <t>04.09.202619</t>
-  </si>
-  <si>
-    <t>04.09.202620</t>
-  </si>
-  <si>
-    <t>04.09.202621</t>
-  </si>
-  <si>
-    <t>04.09.202622</t>
-  </si>
-  <si>
-    <t>04.09.202623</t>
-  </si>
-  <si>
-    <t>04.09.202624</t>
-  </si>
-  <si>
-    <t>04.09.202625</t>
-  </si>
-  <si>
-    <t>04.09.202626</t>
-  </si>
-  <si>
-    <t>04.09.202627</t>
-  </si>
-  <si>
-    <t>04.09.202628</t>
-  </si>
-  <si>
-    <t>04.09.202629</t>
-  </si>
-  <si>
-    <t>04.09.202630</t>
-  </si>
-  <si>
-    <t>04.09.202631</t>
-  </si>
-  <si>
-    <t>04.09.202632</t>
-  </si>
-  <si>
-    <t>04.09.202633</t>
-  </si>
-  <si>
-    <t>04.09.202634</t>
-  </si>
-  <si>
-    <t>04.09.202635</t>
-  </si>
-  <si>
-    <t>04.09.202636</t>
-  </si>
-  <si>
-    <t>04.09.202637</t>
-  </si>
-  <si>
-    <t>04.09.202638</t>
-  </si>
-  <si>
-    <t>04.09.202639</t>
-  </si>
-  <si>
-    <t>04.09.202640</t>
-  </si>
-  <si>
-    <t>04.09.202641</t>
-  </si>
-  <si>
-    <t>04.09.202642</t>
-  </si>
-  <si>
-    <t>04.09.202643</t>
-  </si>
-  <si>
-    <t>04.09.202644</t>
-  </si>
-  <si>
-    <t>04.09.202645</t>
-  </si>
-  <si>
-    <t>04.09.202646</t>
-  </si>
-  <si>
-    <t>04.09.202647</t>
-  </si>
-  <si>
-    <t>04.09.202648</t>
-  </si>
-  <si>
-    <t>04.09.202649</t>
-  </si>
-  <si>
-    <t>04.09.202650</t>
-  </si>
-  <si>
-    <t>04.09.202651</t>
-  </si>
-  <si>
-    <t>04.09.202652</t>
-  </si>
-  <si>
-    <t>04.09.202653</t>
-  </si>
-  <si>
-    <t>04.09.202654</t>
-  </si>
-  <si>
-    <t>04.09.202655</t>
-  </si>
-  <si>
-    <t>04.09.202656</t>
-  </si>
-  <si>
-    <t>04.09.202657</t>
-  </si>
-  <si>
-    <t>04.09.202658</t>
-  </si>
-  <si>
-    <t>04.09.202659</t>
-  </si>
-  <si>
-    <t>04.09.202660</t>
-  </si>
-  <si>
-    <t>04.09.202661</t>
-  </si>
-  <si>
-    <t>04.09.202662</t>
-  </si>
-  <si>
-    <t>04.09.202663</t>
-  </si>
-  <si>
-    <t>04.09.202664</t>
-  </si>
-  <si>
-    <t>04.09.202665</t>
-  </si>
-  <si>
-    <t>04.09.202666</t>
-  </si>
-  <si>
-    <t>04.09.202667</t>
-  </si>
-  <si>
-    <t>04.09.202668</t>
-  </si>
-  <si>
-    <t>04.09.202669</t>
-  </si>
-  <si>
-    <t>04.09.202670</t>
-  </si>
-  <si>
-    <t>04.09.202671</t>
-  </si>
-  <si>
-    <t>04.09.202672</t>
-  </si>
-  <si>
-    <t>04.09.202673</t>
-  </si>
-  <si>
-    <t>04.09.202674</t>
-  </si>
-  <si>
-    <t>04.09.202675</t>
-  </si>
-  <si>
-    <t>04.09.202676</t>
-  </si>
-  <si>
-    <t>04.09.202677</t>
-  </si>
-  <si>
-    <t>04.09.202678</t>
-  </si>
-  <si>
-    <t>04.09.202679</t>
-  </si>
-  <si>
-    <t>04.09.202680</t>
-  </si>
-  <si>
-    <t>04.09.202681</t>
-  </si>
-  <si>
-    <t>04.09.202682</t>
-  </si>
-  <si>
-    <t>04.09.202683</t>
-  </si>
-  <si>
-    <t>04.09.202684</t>
-  </si>
-  <si>
-    <t>04.09.202685</t>
-  </si>
-  <si>
-    <t>04.09.202686</t>
-  </si>
-  <si>
-    <t>04.09.202687</t>
-  </si>
-  <si>
-    <t>04.09.202688</t>
-  </si>
-  <si>
-    <t>04.09.202689</t>
-  </si>
-  <si>
-    <t>04.09.202690</t>
-  </si>
-  <si>
-    <t>04.09.202691</t>
-  </si>
-  <si>
-    <t>04.09.202692</t>
+    <t>12.09.20261</t>
+  </si>
+  <si>
+    <t>12.09.20262</t>
+  </si>
+  <si>
+    <t>12.09.20263</t>
+  </si>
+  <si>
+    <t>12.09.20264</t>
+  </si>
+  <si>
+    <t>12.09.20265</t>
+  </si>
+  <si>
+    <t>12.09.20266</t>
+  </si>
+  <si>
+    <t>12.09.20267</t>
+  </si>
+  <si>
+    <t>12.09.20268</t>
+  </si>
+  <si>
+    <t>12.09.20269</t>
+  </si>
+  <si>
+    <t>12.09.202610</t>
+  </si>
+  <si>
+    <t>12.09.202611</t>
+  </si>
+  <si>
+    <t>12.09.202612</t>
+  </si>
+  <si>
+    <t>12.09.202613</t>
+  </si>
+  <si>
+    <t>12.09.202614</t>
+  </si>
+  <si>
+    <t>12.09.202615</t>
+  </si>
+  <si>
+    <t>12.09.202616</t>
+  </si>
+  <si>
+    <t>12.09.202617</t>
+  </si>
+  <si>
+    <t>12.09.202618</t>
+  </si>
+  <si>
+    <t>12.09.202619</t>
+  </si>
+  <si>
+    <t>12.09.202620</t>
+  </si>
+  <si>
+    <t>12.09.202621</t>
+  </si>
+  <si>
+    <t>12.09.202622</t>
+  </si>
+  <si>
+    <t>12.09.202623</t>
+  </si>
+  <si>
+    <t>12.09.202624</t>
+  </si>
+  <si>
+    <t>12.09.202625</t>
+  </si>
+  <si>
+    <t>12.09.202626</t>
+  </si>
+  <si>
+    <t>12.09.202627</t>
+  </si>
+  <si>
+    <t>12.09.202628</t>
+  </si>
+  <si>
+    <t>12.09.202629</t>
+  </si>
+  <si>
+    <t>12.09.202630</t>
+  </si>
+  <si>
+    <t>12.09.202631</t>
+  </si>
+  <si>
+    <t>12.09.202632</t>
+  </si>
+  <si>
+    <t>12.09.202633</t>
+  </si>
+  <si>
+    <t>12.09.202634</t>
+  </si>
+  <si>
+    <t>12.09.202635</t>
+  </si>
+  <si>
+    <t>12.09.202636</t>
+  </si>
+  <si>
+    <t>12.09.202637</t>
+  </si>
+  <si>
+    <t>12.09.202638</t>
+  </si>
+  <si>
+    <t>12.09.202639</t>
+  </si>
+  <si>
+    <t>12.09.202640</t>
+  </si>
+  <si>
+    <t>12.09.202641</t>
+  </si>
+  <si>
+    <t>12.09.202642</t>
+  </si>
+  <si>
+    <t>12.09.202643</t>
+  </si>
+  <si>
+    <t>12.09.202644</t>
+  </si>
+  <si>
+    <t>12.09.202645</t>
+  </si>
+  <si>
+    <t>12.09.202646</t>
+  </si>
+  <si>
+    <t>12.09.202647</t>
+  </si>
+  <si>
+    <t>12.09.202648</t>
+  </si>
+  <si>
+    <t>12.09.202649</t>
+  </si>
+  <si>
+    <t>12.09.202650</t>
+  </si>
+  <si>
+    <t>12.09.202651</t>
+  </si>
+  <si>
+    <t>12.09.202652</t>
+  </si>
+  <si>
+    <t>12.09.202653</t>
+  </si>
+  <si>
+    <t>12.09.202654</t>
+  </si>
+  <si>
+    <t>12.09.202655</t>
+  </si>
+  <si>
+    <t>12.09.202656</t>
+  </si>
+  <si>
+    <t>12.09.202657</t>
+  </si>
+  <si>
+    <t>12.09.202658</t>
+  </si>
+  <si>
+    <t>12.09.202659</t>
+  </si>
+  <si>
+    <t>12.09.202660</t>
+  </si>
+  <si>
+    <t>12.09.202661</t>
+  </si>
+  <si>
+    <t>12.09.202662</t>
+  </si>
+  <si>
+    <t>12.09.202663</t>
+  </si>
+  <si>
+    <t>12.09.202664</t>
+  </si>
+  <si>
+    <t>12.09.202665</t>
+  </si>
+  <si>
+    <t>12.09.202666</t>
+  </si>
+  <si>
+    <t>12.09.202667</t>
+  </si>
+  <si>
+    <t>12.09.202668</t>
+  </si>
+  <si>
+    <t>12.09.202669</t>
+  </si>
+  <si>
+    <t>12.09.202670</t>
+  </si>
+  <si>
+    <t>12.09.202671</t>
+  </si>
+  <si>
+    <t>12.09.202672</t>
+  </si>
+  <si>
+    <t>12.09.202673</t>
+  </si>
+  <si>
+    <t>12.09.202674</t>
+  </si>
+  <si>
+    <t>12.09.202675</t>
+  </si>
+  <si>
+    <t>12.09.202676</t>
+  </si>
+  <si>
+    <t>12.09.202677</t>
+  </si>
+  <si>
+    <t>12.09.202678</t>
+  </si>
+  <si>
+    <t>12.09.202679</t>
+  </si>
+  <si>
+    <t>12.09.202680</t>
+  </si>
+  <si>
+    <t>12.09.202681</t>
+  </si>
+  <si>
+    <t>12.09.202682</t>
+  </si>
+  <si>
+    <t>12.09.202683</t>
+  </si>
+  <si>
+    <t>12.09.202684</t>
+  </si>
+  <si>
+    <t>12.09.202685</t>
+  </si>
+  <si>
+    <t>12.09.202686</t>
+  </si>
+  <si>
+    <t>12.09.202687</t>
+  </si>
+  <si>
+    <t>12.09.202688</t>
+  </si>
+  <si>
+    <t>12.09.202689</t>
+  </si>
+  <si>
+    <t>12.09.202690</t>
+  </si>
+  <si>
+    <t>12.09.202691</t>
+  </si>
+  <si>
+    <t>12.09.202692</t>
+  </si>
+  <si>
+    <t>12.09.202693</t>
+  </si>
+  <si>
+    <t>12.09.202694</t>
+  </si>
+  <si>
+    <t>12.09.202695</t>
+  </si>
+  <si>
+    <t>12.09.202696</t>
+  </si>
+  <si>
+    <t>13.09.20261</t>
+  </si>
+  <si>
+    <t>13.09.20262</t>
+  </si>
+  <si>
+    <t>13.09.20263</t>
+  </si>
+  <si>
+    <t>13.09.20264</t>
+  </si>
+  <si>
+    <t>13.09.20265</t>
+  </si>
+  <si>
+    <t>13.09.20266</t>
+  </si>
+  <si>
+    <t>13.09.20267</t>
+  </si>
+  <si>
+    <t>13.09.20268</t>
+  </si>
+  <si>
+    <t>13.09.20269</t>
+  </si>
+  <si>
+    <t>13.09.202610</t>
+  </si>
+  <si>
+    <t>13.09.202611</t>
+  </si>
+  <si>
+    <t>13.09.202612</t>
+  </si>
+  <si>
+    <t>13.09.202613</t>
+  </si>
+  <si>
+    <t>13.09.202614</t>
+  </si>
+  <si>
+    <t>13.09.202615</t>
+  </si>
+  <si>
+    <t>13.09.202616</t>
+  </si>
+  <si>
+    <t>13.09.202617</t>
+  </si>
+  <si>
+    <t>13.09.202618</t>
+  </si>
+  <si>
+    <t>13.09.202619</t>
+  </si>
+  <si>
+    <t>13.09.202620</t>
+  </si>
+  <si>
+    <t>13.09.202621</t>
+  </si>
+  <si>
+    <t>13.09.202622</t>
+  </si>
+  <si>
+    <t>13.09.202623</t>
+  </si>
+  <si>
+    <t>13.09.202624</t>
+  </si>
+  <si>
+    <t>13.09.202625</t>
+  </si>
+  <si>
+    <t>13.09.202626</t>
+  </si>
+  <si>
+    <t>13.09.202627</t>
+  </si>
+  <si>
+    <t>13.09.202628</t>
+  </si>
+  <si>
+    <t>13.09.202629</t>
+  </si>
+  <si>
+    <t>13.09.202630</t>
+  </si>
+  <si>
+    <t>13.09.202631</t>
+  </si>
+  <si>
+    <t>13.09.202632</t>
+  </si>
+  <si>
+    <t>13.09.202633</t>
+  </si>
+  <si>
+    <t>13.09.202634</t>
+  </si>
+  <si>
+    <t>13.09.202635</t>
+  </si>
+  <si>
+    <t>13.09.202636</t>
+  </si>
+  <si>
+    <t>13.09.202637</t>
+  </si>
+  <si>
+    <t>13.09.202638</t>
+  </si>
+  <si>
+    <t>13.09.202639</t>
+  </si>
+  <si>
+    <t>13.09.202640</t>
+  </si>
+  <si>
+    <t>13.09.202641</t>
+  </si>
+  <si>
+    <t>13.09.202642</t>
+  </si>
+  <si>
+    <t>13.09.202643</t>
+  </si>
+  <si>
+    <t>13.09.202644</t>
+  </si>
+  <si>
+    <t>13.09.202645</t>
+  </si>
+  <si>
+    <t>13.09.202646</t>
+  </si>
+  <si>
+    <t>13.09.202647</t>
+  </si>
+  <si>
+    <t>13.09.202648</t>
+  </si>
+  <si>
+    <t>13.09.202649</t>
+  </si>
+  <si>
+    <t>13.09.202650</t>
+  </si>
+  <si>
+    <t>13.09.202651</t>
+  </si>
+  <si>
+    <t>13.09.202652</t>
+  </si>
+  <si>
+    <t>13.09.202653</t>
+  </si>
+  <si>
+    <t>13.09.202654</t>
+  </si>
+  <si>
+    <t>13.09.202655</t>
+  </si>
+  <si>
+    <t>13.09.202656</t>
+  </si>
+  <si>
+    <t>13.09.202657</t>
+  </si>
+  <si>
+    <t>13.09.202658</t>
+  </si>
+  <si>
+    <t>13.09.202659</t>
+  </si>
+  <si>
+    <t>13.09.202660</t>
+  </si>
+  <si>
+    <t>13.09.202661</t>
+  </si>
+  <si>
+    <t>13.09.202662</t>
+  </si>
+  <si>
+    <t>13.09.202663</t>
+  </si>
+  <si>
+    <t>13.09.202664</t>
+  </si>
+  <si>
+    <t>13.09.202665</t>
+  </si>
+  <si>
+    <t>13.09.202666</t>
+  </si>
+  <si>
+    <t>13.09.202667</t>
+  </si>
+  <si>
+    <t>13.09.202668</t>
+  </si>
+  <si>
+    <t>13.09.202669</t>
+  </si>
+  <si>
+    <t>13.09.202670</t>
+  </si>
+  <si>
+    <t>13.09.202671</t>
+  </si>
+  <si>
+    <t>13.09.202672</t>
+  </si>
+  <si>
+    <t>13.09.202673</t>
+  </si>
+  <si>
+    <t>13.09.202674</t>
+  </si>
+  <si>
+    <t>13.09.202675</t>
+  </si>
+  <si>
+    <t>13.09.202676</t>
+  </si>
+  <si>
+    <t>13.09.202677</t>
+  </si>
+  <si>
+    <t>13.09.202678</t>
+  </si>
+  <si>
+    <t>13.09.202679</t>
+  </si>
+  <si>
+    <t>13.09.202680</t>
+  </si>
+  <si>
+    <t>13.09.202681</t>
+  </si>
+  <si>
+    <t>13.09.202682</t>
+  </si>
+  <si>
+    <t>13.09.202683</t>
+  </si>
+  <si>
+    <t>13.09.202684</t>
+  </si>
+  <si>
+    <t>13.09.202685</t>
+  </si>
+  <si>
+    <t>13.09.202686</t>
+  </si>
+  <si>
+    <t>13.09.202687</t>
+  </si>
+  <si>
+    <t>13.09.202688</t>
+  </si>
+  <si>
+    <t>13.09.202689</t>
+  </si>
+  <si>
+    <t>13.09.202690</t>
+  </si>
+  <si>
+    <t>13.09.202691</t>
+  </si>
+  <si>
+    <t>13.09.202692</t>
   </si>
 </sst>
 </file>
@@ -976,13 +976,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46268</v>
+        <v>46277</v>
       </c>
       <c r="B2">
-        <v>169.715</v>
+        <v>976.338</v>
       </c>
       <c r="C2">
-        <v>24</v>
+        <v>955</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -993,13 +993,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46268.01041666666</v>
+        <v>46277.01041666666</v>
       </c>
       <c r="B3">
-        <v>170.188</v>
+        <v>962.371</v>
       </c>
       <c r="C3">
-        <v>22</v>
+        <v>946</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1010,13 +1010,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46268.02083333334</v>
+        <v>46277.02083333334</v>
       </c>
       <c r="B4">
-        <v>171.236</v>
+        <v>947.331</v>
       </c>
       <c r="C4">
-        <v>28</v>
+        <v>969</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1027,13 +1027,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46268.03125</v>
+        <v>46277.03125</v>
       </c>
       <c r="B5">
-        <v>174.232</v>
+        <v>931.304</v>
       </c>
       <c r="C5">
-        <v>30</v>
+        <v>933</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1044,13 +1044,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46268.04166666666</v>
+        <v>46277.04166666666</v>
       </c>
       <c r="B6">
-        <v>183.179</v>
+        <v>906.643</v>
       </c>
       <c r="C6">
-        <v>29</v>
+        <v>864</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1061,13 +1061,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46268.05208333334</v>
+        <v>46277.05208333334</v>
       </c>
       <c r="B7">
-        <v>187.518</v>
+        <v>884.224</v>
       </c>
       <c r="C7">
-        <v>51</v>
+        <v>800</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1078,13 +1078,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46268.0625</v>
+        <v>46277.0625</v>
       </c>
       <c r="B8">
-        <v>191.611</v>
+        <v>861.6</v>
       </c>
       <c r="C8">
-        <v>88</v>
+        <v>769</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1095,13 +1095,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46268.07291666666</v>
+        <v>46277.07291666666</v>
       </c>
       <c r="B9">
-        <v>195.495</v>
+        <v>831.872</v>
       </c>
       <c r="C9">
-        <v>114</v>
+        <v>780</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1112,13 +1112,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46268.08333333334</v>
+        <v>46277.08333333334</v>
       </c>
       <c r="B10">
-        <v>207.055</v>
+        <v>792.924</v>
       </c>
       <c r="C10">
-        <v>138</v>
+        <v>782</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1129,13 +1129,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46268.09375</v>
+        <v>46277.09375</v>
       </c>
       <c r="B11">
-        <v>209.614</v>
+        <v>794.097</v>
       </c>
       <c r="C11">
-        <v>148</v>
+        <v>758</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1146,13 +1146,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46268.10416666666</v>
+        <v>46277.10416666666</v>
       </c>
       <c r="B12">
-        <v>224.733</v>
+        <v>783.398</v>
       </c>
       <c r="C12">
-        <v>164</v>
+        <v>762</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1163,13 +1163,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46268.11458333334</v>
+        <v>46277.11458333334</v>
       </c>
       <c r="B13">
-        <v>229.284</v>
+        <v>762.989</v>
       </c>
       <c r="C13">
-        <v>179</v>
+        <v>736</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1180,13 +1180,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46268.125</v>
+        <v>46277.125</v>
       </c>
       <c r="B14">
-        <v>236.845</v>
+        <v>720.136</v>
       </c>
       <c r="C14">
-        <v>183</v>
+        <v>722</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1197,13 +1197,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46268.13541666666</v>
+        <v>46277.13541666666</v>
       </c>
       <c r="B15">
-        <v>238.425</v>
+        <v>713.913</v>
       </c>
       <c r="C15">
-        <v>212</v>
+        <v>696</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1214,13 +1214,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46268.14583333334</v>
+        <v>46277.14583333334</v>
       </c>
       <c r="B16">
-        <v>254.797</v>
+        <v>705.192</v>
       </c>
       <c r="C16">
-        <v>215</v>
+        <v>670</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1231,13 +1231,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46268.15625</v>
+        <v>46277.15625</v>
       </c>
       <c r="B17">
-        <v>266.351</v>
+        <v>697.6950000000001</v>
       </c>
       <c r="C17">
-        <v>209</v>
+        <v>657</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1248,13 +1248,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46268.16666666666</v>
+        <v>46277.16666666666</v>
       </c>
       <c r="B18">
-        <v>289.974</v>
+        <v>694.407</v>
       </c>
       <c r="C18">
-        <v>225</v>
+        <v>681</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1265,13 +1265,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46268.17708333334</v>
+        <v>46277.17708333334</v>
       </c>
       <c r="B19">
-        <v>282.745</v>
+        <v>672.323</v>
       </c>
       <c r="C19">
-        <v>285</v>
+        <v>690</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1282,13 +1282,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46268.1875</v>
+        <v>46277.1875</v>
       </c>
       <c r="B20">
-        <v>314.563</v>
+        <v>694.735</v>
       </c>
       <c r="C20">
-        <v>346</v>
+        <v>669</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1299,13 +1299,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46268.19791666666</v>
+        <v>46277.19791666666</v>
       </c>
       <c r="B21">
-        <v>323.067</v>
+        <v>692.41</v>
       </c>
       <c r="C21">
-        <v>348</v>
+        <v>706</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1316,13 +1316,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46268.20833333334</v>
+        <v>46277.20833333334</v>
       </c>
       <c r="B22">
-        <v>317.929</v>
+        <v>677.401</v>
       </c>
       <c r="C22">
-        <v>355</v>
+        <v>727</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1333,13 +1333,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46268.21875</v>
+        <v>46277.21875</v>
       </c>
       <c r="B23">
-        <v>323.919</v>
+        <v>662.217</v>
       </c>
       <c r="C23">
-        <v>388</v>
+        <v>746</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1350,13 +1350,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46268.22916666666</v>
+        <v>46277.22916666666</v>
       </c>
       <c r="B24">
-        <v>333.638</v>
+        <v>644.783</v>
       </c>
       <c r="C24">
-        <v>418</v>
+        <v>757</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1367,13 +1367,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46268.23958333334</v>
+        <v>46277.23958333334</v>
       </c>
       <c r="B25">
-        <v>341.461</v>
+        <v>627.001</v>
       </c>
       <c r="C25">
-        <v>453</v>
+        <v>734</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1384,13 +1384,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46268.25</v>
+        <v>46277.25</v>
       </c>
       <c r="B26">
-        <v>351.96</v>
+        <v>609.0309999999999</v>
       </c>
       <c r="C26">
-        <v>495</v>
+        <v>737</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1401,13 +1401,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46268.26041666666</v>
+        <v>46277.26041666666</v>
       </c>
       <c r="B27">
-        <v>355.939</v>
+        <v>593.522</v>
       </c>
       <c r="C27">
-        <v>525</v>
+        <v>750</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1418,13 +1418,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46268.27083333334</v>
+        <v>46277.27083333334</v>
       </c>
       <c r="B28">
-        <v>363.117</v>
+        <v>560.603</v>
       </c>
       <c r="C28">
-        <v>550</v>
+        <v>755</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1435,13 +1435,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46268.28125</v>
+        <v>46277.28125</v>
       </c>
       <c r="B29">
-        <v>368.317</v>
+        <v>544.338</v>
       </c>
       <c r="C29">
-        <v>557</v>
+        <v>791</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1452,13 +1452,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46268.29166666666</v>
+        <v>46277.29166666666</v>
       </c>
       <c r="B30">
-        <v>370.631</v>
+        <v>482.865</v>
       </c>
       <c r="C30">
-        <v>553</v>
+        <v>708</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1469,13 +1469,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46268.30208333334</v>
+        <v>46277.30208333334</v>
       </c>
       <c r="B31">
-        <v>352.265</v>
+        <v>466.16</v>
       </c>
       <c r="C31">
-        <v>495</v>
+        <v>602</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1486,13 +1486,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46268.3125</v>
+        <v>46277.3125</v>
       </c>
       <c r="B32">
-        <v>332.859</v>
+        <v>441.914</v>
       </c>
       <c r="C32">
-        <v>395</v>
+        <v>454</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1503,13 +1503,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46268.32291666666</v>
+        <v>46277.32291666666</v>
       </c>
       <c r="B33">
-        <v>309.337</v>
+        <v>411.656</v>
       </c>
       <c r="C33">
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1520,13 +1520,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46268.33333333334</v>
+        <v>46277.33333333334</v>
       </c>
       <c r="B34">
-        <v>279.951</v>
+        <v>433.74</v>
       </c>
       <c r="C34">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1537,13 +1537,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46268.34375</v>
+        <v>46277.34375</v>
       </c>
       <c r="B35">
-        <v>255.62</v>
+        <v>424.464</v>
       </c>
       <c r="C35">
-        <v>310</v>
+        <v>327</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1554,13 +1554,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46268.35416666666</v>
+        <v>46277.35416666666</v>
       </c>
       <c r="B36">
-        <v>234.201</v>
+        <v>423.081</v>
       </c>
       <c r="C36">
-        <v>336</v>
+        <v>364</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1571,13 +1571,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46268.36458333334</v>
+        <v>46277.36458333334</v>
       </c>
       <c r="B37">
-        <v>220.696</v>
+        <v>414.24</v>
       </c>
       <c r="C37">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1588,13 +1588,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46268.375</v>
+        <v>46277.375</v>
       </c>
       <c r="B38">
-        <v>216.311</v>
+        <v>441.689</v>
       </c>
       <c r="C38">
-        <v>296</v>
+        <v>358</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1605,13 +1605,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46268.38541666666</v>
+        <v>46277.38541666666</v>
       </c>
       <c r="B39">
-        <v>212.098</v>
+        <v>445.054</v>
       </c>
       <c r="C39">
-        <v>288</v>
+        <v>329</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1622,13 +1622,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46268.39583333334</v>
+        <v>46277.39583333334</v>
       </c>
       <c r="B40">
-        <v>208.428</v>
+        <v>444.284</v>
       </c>
       <c r="C40">
-        <v>266</v>
+        <v>317</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1639,13 +1639,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46268.40625</v>
+        <v>46277.40625</v>
       </c>
       <c r="B41">
-        <v>204.012</v>
+        <v>445.529</v>
       </c>
       <c r="C41">
-        <v>242</v>
+        <v>308</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1656,13 +1656,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46268.41666666666</v>
+        <v>46277.41666666666</v>
       </c>
       <c r="B42">
-        <v>195.676</v>
+        <v>447.963</v>
       </c>
       <c r="C42">
-        <v>231</v>
+        <v>300</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1673,13 +1673,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46268.42708333334</v>
+        <v>46277.42708333334</v>
       </c>
       <c r="B43">
-        <v>191.717</v>
+        <v>450.384</v>
       </c>
       <c r="C43">
-        <v>227</v>
+        <v>298</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1690,13 +1690,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46268.4375</v>
+        <v>46277.4375</v>
       </c>
       <c r="B44">
-        <v>186.356</v>
+        <v>452.278</v>
       </c>
       <c r="C44">
-        <v>219</v>
+        <v>295</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1707,13 +1707,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46268.44791666666</v>
+        <v>46277.44791666666</v>
       </c>
       <c r="B45">
-        <v>181.589</v>
+        <v>454.126</v>
       </c>
       <c r="C45">
-        <v>201</v>
+        <v>295</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1724,13 +1724,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46268.45833333334</v>
+        <v>46277.45833333334</v>
       </c>
       <c r="B46">
-        <v>175.829</v>
+        <v>455.896</v>
       </c>
       <c r="C46">
-        <v>189</v>
+        <v>286</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1741,13 +1741,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46268.46875</v>
+        <v>46277.46875</v>
       </c>
       <c r="B47">
-        <v>172.629</v>
+        <v>459.926</v>
       </c>
       <c r="C47">
-        <v>173</v>
+        <v>277</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1758,13 +1758,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46268.47916666666</v>
+        <v>46277.47916666666</v>
       </c>
       <c r="B48">
-        <v>170.233</v>
+        <v>461.398</v>
       </c>
       <c r="C48">
-        <v>174</v>
+        <v>256</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1775,13 +1775,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46268.48958333334</v>
+        <v>46277.48958333334</v>
       </c>
       <c r="B49">
-        <v>167.758</v>
+        <v>463.044</v>
       </c>
       <c r="C49">
-        <v>175</v>
+        <v>237</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1792,13 +1792,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46268.5</v>
+        <v>46277.5</v>
       </c>
       <c r="B50">
-        <v>166.718</v>
+        <v>466.208</v>
       </c>
       <c r="C50">
-        <v>172</v>
+        <v>231</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1809,13 +1809,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46268.51041666666</v>
+        <v>46277.51041666666</v>
       </c>
       <c r="B51">
-        <v>166.39</v>
+        <v>470.793</v>
       </c>
       <c r="C51">
-        <v>163</v>
+        <v>228</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1826,13 +1826,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46268.52083333334</v>
+        <v>46277.52083333334</v>
       </c>
       <c r="B52">
-        <v>167.443</v>
+        <v>474.866</v>
       </c>
       <c r="C52">
-        <v>153</v>
+        <v>240</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1843,13 +1843,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46268.53125</v>
+        <v>46277.53125</v>
       </c>
       <c r="B53">
-        <v>168.111</v>
+        <v>479.194</v>
       </c>
       <c r="C53">
-        <v>160</v>
+        <v>261</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1860,13 +1860,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46268.54166666666</v>
+        <v>46277.54166666666</v>
       </c>
       <c r="B54">
-        <v>171.344</v>
+        <v>464.609</v>
       </c>
       <c r="C54">
-        <v>164</v>
+        <v>280</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1877,13 +1877,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46268.55208333334</v>
+        <v>46277.55208333334</v>
       </c>
       <c r="B55">
-        <v>175.182</v>
+        <v>472.028</v>
       </c>
       <c r="C55">
-        <v>174</v>
+        <v>306</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1894,13 +1894,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46268.5625</v>
+        <v>46277.5625</v>
       </c>
       <c r="B56">
-        <v>179.846</v>
+        <v>480.067</v>
       </c>
       <c r="C56">
-        <v>170</v>
+        <v>356</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1911,13 +1911,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46268.57291666666</v>
+        <v>46277.57291666666</v>
       </c>
       <c r="B57">
-        <v>183.532</v>
+        <v>488.099</v>
       </c>
       <c r="C57">
-        <v>187</v>
+        <v>408</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1928,13 +1928,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46268.58333333334</v>
+        <v>46277.58333333334</v>
       </c>
       <c r="B58">
-        <v>190.385</v>
+        <v>519.029</v>
       </c>
       <c r="C58">
-        <v>186</v>
+        <v>463</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1945,13 +1945,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46268.59375</v>
+        <v>46277.59375</v>
       </c>
       <c r="B59">
-        <v>193.615</v>
+        <v>526.537</v>
       </c>
       <c r="C59">
-        <v>175</v>
+        <v>504</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1962,13 +1962,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46268.60416666666</v>
+        <v>46277.60416666666</v>
       </c>
       <c r="B60">
-        <v>195.65</v>
+        <v>534.707</v>
       </c>
       <c r="C60">
-        <v>182</v>
+        <v>546</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1979,13 +1979,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46268.61458333334</v>
+        <v>46277.61458333334</v>
       </c>
       <c r="B61">
-        <v>197.691</v>
+        <v>541.771</v>
       </c>
       <c r="C61">
-        <v>211</v>
+        <v>587</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -1996,13 +1996,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46268.625</v>
+        <v>46277.625</v>
       </c>
       <c r="B62">
-        <v>197.641</v>
+        <v>559.03</v>
       </c>
       <c r="C62">
-        <v>205</v>
+        <v>620</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2013,13 +2013,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46268.63541666666</v>
+        <v>46277.63541666666</v>
       </c>
       <c r="B63">
-        <v>198.827</v>
+        <v>571.045</v>
       </c>
       <c r="C63">
-        <v>187</v>
+        <v>626</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2030,13 +2030,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46268.64583333334</v>
+        <v>46277.64583333334</v>
       </c>
       <c r="B64">
-        <v>200.357</v>
+        <v>582.9829999999999</v>
       </c>
       <c r="C64">
-        <v>183</v>
+        <v>627</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2047,13 +2047,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46268.65625</v>
+        <v>46277.65625</v>
       </c>
       <c r="B65">
-        <v>202.669</v>
+        <v>595.256</v>
       </c>
       <c r="C65">
-        <v>174</v>
+        <v>617</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2064,13 +2064,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46268.66666666666</v>
+        <v>46277.66666666666</v>
       </c>
       <c r="B66">
-        <v>201.679</v>
+        <v>581.901</v>
       </c>
       <c r="C66">
-        <v>176</v>
+        <v>606</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2081,13 +2081,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46268.67708333334</v>
+        <v>46277.67708333334</v>
       </c>
       <c r="B67">
-        <v>200.218</v>
+        <v>597.71</v>
       </c>
       <c r="C67">
-        <v>183</v>
+        <v>615</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2098,13 +2098,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46268.6875</v>
+        <v>46277.6875</v>
       </c>
       <c r="B68">
-        <v>198.474</v>
+        <v>614.783</v>
       </c>
       <c r="C68">
-        <v>179</v>
+        <v>614</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2115,13 +2115,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46268.69791666666</v>
+        <v>46277.69791666666</v>
       </c>
       <c r="B69">
-        <v>196.991</v>
+        <v>630.447</v>
       </c>
       <c r="C69">
-        <v>176</v>
+        <v>637</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2132,13 +2132,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46268.70833333334</v>
+        <v>46277.70833333334</v>
       </c>
       <c r="B70">
-        <v>187.628</v>
+        <v>576.638</v>
       </c>
       <c r="C70">
-        <v>169</v>
+        <v>645</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2149,13 +2149,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46268.71875</v>
+        <v>46277.71875</v>
       </c>
       <c r="B71">
-        <v>194.202</v>
+        <v>588.716</v>
       </c>
       <c r="C71">
-        <v>150</v>
+        <v>672</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2166,13 +2166,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46268.72916666666</v>
+        <v>46277.72916666666</v>
       </c>
       <c r="B72">
-        <v>184.089</v>
+        <v>602.871</v>
       </c>
       <c r="C72">
-        <v>140</v>
+        <v>708</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2183,13 +2183,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46268.73958333334</v>
+        <v>46277.73958333334</v>
       </c>
       <c r="B73">
-        <v>182.38</v>
+        <v>615.58</v>
       </c>
       <c r="C73">
-        <v>123</v>
+        <v>680</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2200,13 +2200,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46268.75</v>
+        <v>46277.75</v>
       </c>
       <c r="B74">
-        <v>166.654</v>
+        <v>636.797</v>
       </c>
       <c r="C74">
-        <v>103</v>
+        <v>632</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2217,13 +2217,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46268.76041666666</v>
+        <v>46277.76041666666</v>
       </c>
       <c r="B75">
-        <v>167.62</v>
+        <v>653.421</v>
       </c>
       <c r="C75">
-        <v>109</v>
+        <v>638</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2234,13 +2234,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46268.77083333334</v>
+        <v>46277.77083333334</v>
       </c>
       <c r="B76">
-        <v>168.63</v>
+        <v>672.348</v>
       </c>
       <c r="C76">
-        <v>90</v>
+        <v>626</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2251,13 +2251,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46268.78125</v>
+        <v>46277.78125</v>
       </c>
       <c r="B77">
-        <v>169.987</v>
+        <v>689.702</v>
       </c>
       <c r="C77">
-        <v>76</v>
+        <v>645</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2268,13 +2268,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46268.79166666666</v>
+        <v>46277.79166666666</v>
       </c>
       <c r="B78">
-        <v>176.839</v>
+        <v>733.97</v>
       </c>
       <c r="C78">
-        <v>72</v>
+        <v>641</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2285,13 +2285,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46268.80208333334</v>
+        <v>46277.80208333334</v>
       </c>
       <c r="B79">
-        <v>177.11</v>
+        <v>731.551</v>
       </c>
       <c r="C79">
-        <v>58</v>
+        <v>642</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2302,13 +2302,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46268.8125</v>
+        <v>46277.8125</v>
       </c>
       <c r="B80">
-        <v>177.754</v>
+        <v>728.426</v>
       </c>
       <c r="C80">
-        <v>50</v>
+        <v>634</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2319,13 +2319,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46268.82291666666</v>
+        <v>46277.82291666666</v>
       </c>
       <c r="B81">
-        <v>179.208</v>
+        <v>728.742</v>
       </c>
       <c r="C81">
-        <v>49</v>
+        <v>637</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2336,13 +2336,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46268.83333333334</v>
+        <v>46277.83333333334</v>
       </c>
       <c r="B82">
-        <v>176.599</v>
+        <v>725.105</v>
       </c>
       <c r="C82">
-        <v>53</v>
+        <v>599</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2353,13 +2353,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46268.84375</v>
+        <v>46277.84375</v>
       </c>
       <c r="B83">
-        <v>174.578</v>
+        <v>724.8339999999999</v>
       </c>
       <c r="C83">
-        <v>47</v>
+        <v>550</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2370,13 +2370,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46268.85416666666</v>
+        <v>46277.85416666666</v>
       </c>
       <c r="B84">
-        <v>172.014</v>
+        <v>720.427</v>
       </c>
       <c r="C84">
-        <v>40</v>
+        <v>540</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2387,13 +2387,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46268.86458333334</v>
+        <v>46277.86458333334</v>
       </c>
       <c r="B85">
-        <v>169.897</v>
+        <v>721.627</v>
       </c>
       <c r="C85">
-        <v>32</v>
+        <v>584</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2404,13 +2404,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46268.875</v>
+        <v>46277.875</v>
       </c>
       <c r="B86">
-        <v>165.991</v>
+        <v>717.417</v>
       </c>
       <c r="C86">
-        <v>15</v>
+        <v>654</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2421,13 +2421,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46268.88541666666</v>
+        <v>46277.88541666666</v>
       </c>
       <c r="B87">
-        <v>167.239</v>
+        <v>726.653</v>
       </c>
       <c r="C87">
-        <v>13</v>
+        <v>693</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2438,13 +2438,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46268.89583333334</v>
+        <v>46277.89583333334</v>
       </c>
       <c r="B88">
-        <v>170.348</v>
+        <v>739.777</v>
       </c>
       <c r="C88">
-        <v>11</v>
+        <v>760</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2455,13 +2455,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46268.90625</v>
+        <v>46277.90625</v>
       </c>
       <c r="B89">
-        <v>172.335</v>
+        <v>751.842</v>
       </c>
       <c r="C89">
-        <v>10</v>
+        <v>811</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2472,13 +2472,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46268.91666666666</v>
+        <v>46277.91666666666</v>
       </c>
       <c r="B90">
-        <v>180.869</v>
+        <v>773.76</v>
       </c>
       <c r="C90">
-        <v>17</v>
+        <v>848</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2489,13 +2489,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46268.92708333334</v>
+        <v>46277.92708333334</v>
       </c>
       <c r="B91">
-        <v>181.452</v>
+        <v>798.829</v>
       </c>
       <c r="C91">
-        <v>114</v>
+        <v>826</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2506,13 +2506,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46268.9375</v>
+        <v>46277.9375</v>
       </c>
       <c r="B92">
-        <v>182.049</v>
+        <v>827.573</v>
       </c>
       <c r="C92">
-        <v>141</v>
+        <v>820</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2523,13 +2523,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46268.94791666666</v>
+        <v>46277.94791666666</v>
       </c>
       <c r="B93">
-        <v>182.361</v>
+        <v>855.373</v>
       </c>
       <c r="C93">
-        <v>144</v>
+        <v>841</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2540,13 +2540,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46268.95833333334</v>
+        <v>46277.95833333334</v>
       </c>
       <c r="B94">
-        <v>174.028</v>
+        <v>944.289</v>
       </c>
       <c r="C94">
-        <v>146</v>
+        <v>898</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2557,13 +2557,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46268.96875</v>
+        <v>46277.96875</v>
       </c>
       <c r="B95">
-        <v>171.8</v>
+        <v>972.974</v>
       </c>
       <c r="C95">
-        <v>141</v>
+        <v>938</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2574,13 +2574,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46268.97916666666</v>
+        <v>46277.97916666666</v>
       </c>
       <c r="B96">
-        <v>172.562</v>
+        <v>1002.955</v>
       </c>
       <c r="C96">
-        <v>118</v>
+        <v>1024</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2591,13 +2591,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46268.98958333334</v>
+        <v>46277.98958333334</v>
       </c>
       <c r="B97">
-        <v>166.418</v>
+        <v>1041.637</v>
       </c>
       <c r="C97">
-        <v>94</v>
+        <v>1060</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2608,13 +2608,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46269</v>
+        <v>46278</v>
       </c>
       <c r="B98">
-        <v>177.573</v>
+        <v>1082.132</v>
       </c>
       <c r="C98">
-        <v>74</v>
+        <v>1076</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2625,13 +2625,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46269.01041666666</v>
+        <v>46278.01041666666</v>
       </c>
       <c r="B99">
-        <v>172.29</v>
+        <v>1143.352</v>
       </c>
       <c r="C99">
-        <v>61</v>
+        <v>1083</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2642,13 +2642,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46269.02083333334</v>
+        <v>46278.02083333334</v>
       </c>
       <c r="B100">
-        <v>162.283</v>
+        <v>1191.495</v>
       </c>
       <c r="C100">
-        <v>45</v>
+        <v>1110</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2659,13 +2659,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46269.03125</v>
+        <v>46278.03125</v>
       </c>
       <c r="B101">
-        <v>156.43</v>
+        <v>1257.255</v>
       </c>
       <c r="C101">
-        <v>34</v>
+        <v>1220</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2676,13 +2676,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46269.04166666666</v>
+        <v>46278.04166666666</v>
       </c>
       <c r="B102">
-        <v>144.313</v>
+        <v>1260.135</v>
       </c>
       <c r="C102">
-        <v>22</v>
+        <v>1349</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2693,13 +2693,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46269.05208333334</v>
+        <v>46278.05208333334</v>
       </c>
       <c r="B103">
-        <v>135.558</v>
+        <v>1299.366</v>
       </c>
       <c r="C103">
-        <v>22</v>
+        <v>1490</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2710,13 +2710,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46269.0625</v>
+        <v>46278.0625</v>
       </c>
       <c r="B104">
-        <v>131.185</v>
+        <v>1341.428</v>
       </c>
       <c r="C104">
-        <v>25</v>
+        <v>1574</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2727,13 +2727,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46269.07291666666</v>
+        <v>46278.07291666666</v>
       </c>
       <c r="B105">
-        <v>126.733</v>
+        <v>1372.732</v>
       </c>
       <c r="C105">
-        <v>40</v>
+        <v>1587</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2744,13 +2744,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46269.08333333334</v>
+        <v>46278.08333333334</v>
       </c>
       <c r="B106">
-        <v>131.235</v>
+        <v>1407.986</v>
       </c>
       <c r="C106">
-        <v>48</v>
+        <v>1572</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2761,13 +2761,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46269.09375</v>
+        <v>46278.09375</v>
       </c>
       <c r="B107">
-        <v>128.687</v>
+        <v>1429.29</v>
       </c>
       <c r="C107">
-        <v>34</v>
+        <v>1615</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2778,13 +2778,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46269.10416666666</v>
+        <v>46278.10416666666</v>
       </c>
       <c r="B108">
-        <v>126.361</v>
+        <v>1437.35</v>
       </c>
       <c r="C108">
-        <v>27</v>
+        <v>1635</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2795,13 +2795,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46269.11458333334</v>
+        <v>46278.11458333334</v>
       </c>
       <c r="B109">
-        <v>125.147</v>
+        <v>1456.504</v>
       </c>
       <c r="C109">
-        <v>18</v>
+        <v>1625</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2812,13 +2812,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46269.125</v>
+        <v>46278.125</v>
       </c>
       <c r="B110">
-        <v>129.272</v>
+        <v>1473.847</v>
       </c>
       <c r="C110">
-        <v>23</v>
+        <v>1579</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2829,13 +2829,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46269.13541666666</v>
+        <v>46278.13541666666</v>
       </c>
       <c r="B111">
-        <v>129.064</v>
+        <v>1461.335</v>
       </c>
       <c r="C111">
-        <v>26</v>
+        <v>1534</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2846,13 +2846,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46269.14583333334</v>
+        <v>46278.14583333334</v>
       </c>
       <c r="B112">
-        <v>118.502</v>
+        <v>1456.789</v>
       </c>
       <c r="C112">
-        <v>15</v>
+        <v>1501</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2863,13 +2863,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46269.15625</v>
+        <v>46278.15625</v>
       </c>
       <c r="B113">
-        <v>119.618</v>
+        <v>1455.575</v>
       </c>
       <c r="C113">
-        <v>17</v>
+        <v>1516</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2880,13 +2880,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46269.16666666666</v>
+        <v>46278.16666666666</v>
       </c>
       <c r="B114">
-        <v>112.846</v>
+        <v>1421.12</v>
       </c>
       <c r="C114">
-        <v>21</v>
+        <v>1533</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2897,13 +2897,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46269.17708333334</v>
+        <v>46278.17708333334</v>
       </c>
       <c r="B115">
-        <v>120.1</v>
+        <v>1411.242</v>
       </c>
       <c r="C115">
-        <v>23</v>
+        <v>1551</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2914,13 +2914,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46269.1875</v>
+        <v>46278.1875</v>
       </c>
       <c r="B116">
-        <v>118.942</v>
+        <v>1395.263</v>
       </c>
       <c r="C116">
-        <v>31</v>
+        <v>1523</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2931,13 +2931,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46269.19791666666</v>
+        <v>46278.19791666666</v>
       </c>
       <c r="B117">
-        <v>116.596</v>
+        <v>1386.174</v>
       </c>
       <c r="C117">
-        <v>45</v>
+        <v>1443</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2948,13 +2948,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46269.20833333334</v>
+        <v>46278.20833333334</v>
       </c>
       <c r="B118">
-        <v>117.78</v>
+        <v>1383.316</v>
       </c>
       <c r="C118">
-        <v>42</v>
+        <v>1411</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2965,13 +2965,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46269.21875</v>
+        <v>46278.21875</v>
       </c>
       <c r="B119">
-        <v>113.379</v>
+        <v>1380.241</v>
       </c>
       <c r="C119">
-        <v>45</v>
+        <v>1429</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2982,13 +2982,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46269.22916666666</v>
+        <v>46278.22916666666</v>
       </c>
       <c r="B120">
-        <v>108.661</v>
+        <v>1374.575</v>
       </c>
       <c r="C120">
-        <v>52</v>
+        <v>1414</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -2999,13 +2999,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46269.23958333334</v>
+        <v>46278.23958333334</v>
       </c>
       <c r="B121">
-        <v>104.269</v>
+        <v>1379.222</v>
       </c>
       <c r="C121">
-        <v>61</v>
+        <v>1465</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3016,13 +3016,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46269.25</v>
+        <v>46278.25</v>
       </c>
       <c r="B122">
-        <v>94.523</v>
+        <v>1356.256</v>
       </c>
       <c r="C122">
-        <v>63</v>
+        <v>1487</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3033,13 +3033,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46269.26041666666</v>
+        <v>46278.26041666666</v>
       </c>
       <c r="B123">
-        <v>92.51600000000001</v>
+        <v>1354.258</v>
       </c>
       <c r="C123">
-        <v>52</v>
+        <v>1511</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3050,13 +3050,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46269.27083333334</v>
+        <v>46278.27083333334</v>
       </c>
       <c r="B124">
-        <v>91.985</v>
+        <v>1330.87</v>
       </c>
       <c r="C124">
-        <v>47</v>
+        <v>1554</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3067,13 +3067,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46269.28125</v>
+        <v>46278.28125</v>
       </c>
       <c r="B125">
-        <v>90.164</v>
+        <v>1318.589</v>
       </c>
       <c r="C125">
-        <v>45</v>
+        <v>1580</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3084,13 +3084,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46269.29166666666</v>
+        <v>46278.29166666666</v>
       </c>
       <c r="B126">
-        <v>96.399</v>
+        <v>1319.6</v>
       </c>
       <c r="C126">
-        <v>43</v>
+        <v>1571</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3101,13 +3101,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46269.30208333334</v>
+        <v>46278.30208333334</v>
       </c>
       <c r="B127">
-        <v>99.09999999999999</v>
+        <v>1308.95</v>
       </c>
       <c r="C127">
-        <v>37</v>
+        <v>1562</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3118,13 +3118,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46269.3125</v>
+        <v>46278.3125</v>
       </c>
       <c r="B128">
-        <v>91.349</v>
+        <v>1315.474</v>
       </c>
       <c r="C128">
-        <v>20</v>
+        <v>1564</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3135,13 +3135,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46269.32291666666</v>
+        <v>46278.32291666666</v>
       </c>
       <c r="B129">
-        <v>91.312</v>
+        <v>1301.813</v>
       </c>
       <c r="C129">
-        <v>14</v>
+        <v>1621</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3152,13 +3152,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46269.33333333334</v>
+        <v>46278.33333333334</v>
       </c>
       <c r="B130">
-        <v>104.049</v>
+        <v>1291.528</v>
       </c>
       <c r="C130">
-        <v>11</v>
+        <v>1579</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3169,13 +3169,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46269.34375</v>
+        <v>46278.34375</v>
       </c>
       <c r="B131">
-        <v>103.108</v>
+        <v>1293.452</v>
       </c>
       <c r="C131">
-        <v>1</v>
+        <v>1554</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3186,13 +3186,10 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46269.35416666666</v>
+        <v>46278.35416666666</v>
       </c>
       <c r="B132">
-        <v>102.311</v>
-      </c>
-      <c r="C132">
-        <v>0</v>
+        <v>1286.128</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3203,13 +3200,10 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46269.36458333334</v>
+        <v>46278.36458333334</v>
       </c>
       <c r="B133">
-        <v>100.549</v>
-      </c>
-      <c r="C133">
-        <v>0</v>
+        <v>1283.178</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3220,13 +3214,10 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46269.375</v>
+        <v>46278.375</v>
       </c>
       <c r="B134">
-        <v>100.752</v>
-      </c>
-      <c r="C134">
-        <v>0</v>
+        <v>1315.717</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3237,13 +3228,10 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46269.38541666666</v>
+        <v>46278.38541666666</v>
       </c>
       <c r="B135">
-        <v>101.581</v>
-      </c>
-      <c r="C135">
-        <v>0</v>
+        <v>1310.433</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3254,13 +3242,10 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46269.39583333334</v>
+        <v>46278.39583333334</v>
       </c>
       <c r="B136">
-        <v>102.282</v>
-      </c>
-      <c r="C136">
-        <v>0</v>
+        <v>1314.982</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3271,13 +3256,10 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46269.40625</v>
+        <v>46278.40625</v>
       </c>
       <c r="B137">
-        <v>102.813</v>
-      </c>
-      <c r="C137">
-        <v>0</v>
+        <v>1320.026</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3288,13 +3270,10 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46269.41666666666</v>
+        <v>46278.41666666666</v>
       </c>
       <c r="B138">
-        <v>101.048</v>
-      </c>
-      <c r="C138">
-        <v>0</v>
+        <v>1389.296</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3305,13 +3284,10 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46269.42708333334</v>
+        <v>46278.42708333334</v>
       </c>
       <c r="B139">
-        <v>103.606</v>
-      </c>
-      <c r="C139">
-        <v>0</v>
+        <v>1388.653</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3322,13 +3298,10 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46269.4375</v>
+        <v>46278.4375</v>
       </c>
       <c r="B140">
-        <v>106.81</v>
-      </c>
-      <c r="C140">
-        <v>0</v>
+        <v>1387.403</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3339,13 +3312,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46269.44791666666</v>
+        <v>46278.44791666666</v>
       </c>
       <c r="B141">
-        <v>109.875</v>
-      </c>
-      <c r="C141">
-        <v>6</v>
+        <v>1384.574</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3356,13 +3326,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46269.45833333334</v>
+        <v>46278.45833333334</v>
       </c>
       <c r="B142">
-        <v>113.642</v>
-      </c>
-      <c r="C142">
-        <v>9</v>
+        <v>1414.001</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3373,13 +3340,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46269.46875</v>
+        <v>46278.46875</v>
       </c>
       <c r="B143">
-        <v>119.571</v>
-      </c>
-      <c r="C143">
-        <v>26</v>
+        <v>1399.882</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3390,10 +3354,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46269.47916666666</v>
+        <v>46278.47916666666</v>
       </c>
       <c r="B144">
-        <v>125.654</v>
+        <v>1385.85</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3404,10 +3368,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46269.48958333334</v>
+        <v>46278.48958333334</v>
       </c>
       <c r="B145">
-        <v>131.345</v>
+        <v>1371.337</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3418,10 +3382,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46269.5</v>
+        <v>46278.5</v>
       </c>
       <c r="B146">
-        <v>139.944</v>
+        <v>1295.262</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3432,10 +3396,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46269.51041666666</v>
+        <v>46278.51041666666</v>
       </c>
       <c r="B147">
-        <v>147.358</v>
+        <v>1275.362</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3446,10 +3410,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46269.52083333334</v>
+        <v>46278.52083333334</v>
       </c>
       <c r="B148">
-        <v>155.268</v>
+        <v>1255.889</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3460,10 +3424,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46269.53125</v>
+        <v>46278.53125</v>
       </c>
       <c r="B149">
-        <v>163.676</v>
+        <v>1234.858</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3474,10 +3438,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46269.54166666666</v>
+        <v>46278.54166666666</v>
       </c>
       <c r="B150">
-        <v>173.134</v>
+        <v>1203.179</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3488,10 +3452,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46269.55208333334</v>
+        <v>46278.55208333334</v>
       </c>
       <c r="B151">
-        <v>180.053</v>
+        <v>1188.576</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3502,10 +3466,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46269.5625</v>
+        <v>46278.5625</v>
       </c>
       <c r="B152">
-        <v>187.611</v>
+        <v>1172.532</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3516,10 +3480,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46269.57291666666</v>
+        <v>46278.57291666666</v>
       </c>
       <c r="B153">
-        <v>195.344</v>
+        <v>1157.572</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3530,10 +3494,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46269.58333333334</v>
+        <v>46278.58333333334</v>
       </c>
       <c r="B154">
-        <v>209.702</v>
+        <v>1027.842</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3544,10 +3508,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46269.59375</v>
+        <v>46278.59375</v>
       </c>
       <c r="B155">
-        <v>216.826</v>
+        <v>1009.383</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3558,10 +3522,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46269.60416666666</v>
+        <v>46278.60416666666</v>
       </c>
       <c r="B156">
-        <v>225.029</v>
+        <v>990.6799999999999</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3572,10 +3536,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46269.61458333334</v>
+        <v>46278.61458333334</v>
       </c>
       <c r="B157">
-        <v>233.312</v>
+        <v>973.548</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3586,10 +3550,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46269.625</v>
+        <v>46278.625</v>
       </c>
       <c r="B158">
-        <v>221.3</v>
+        <v>935.727</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3600,10 +3564,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46269.63541666666</v>
+        <v>46278.63541666666</v>
       </c>
       <c r="B159">
-        <v>226.323</v>
+        <v>913.913</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3614,10 +3578,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46269.64583333334</v>
+        <v>46278.64583333334</v>
       </c>
       <c r="B160">
-        <v>232.152</v>
+        <v>893.477</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3628,10 +3592,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46269.65625</v>
+        <v>46278.65625</v>
       </c>
       <c r="B161">
-        <v>238.068</v>
+        <v>870.798</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3642,10 +3606,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46269.66666666666</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="B162">
-        <v>245.109</v>
+        <v>844.655</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -3656,10 +3620,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46269.67708333334</v>
+        <v>46278.67708333334</v>
       </c>
       <c r="B163">
-        <v>247.26</v>
+        <v>828.869</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -3670,10 +3634,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46269.6875</v>
+        <v>46278.6875</v>
       </c>
       <c r="B164">
-        <v>248.325</v>
+        <v>812.37</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -3684,10 +3648,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46269.69791666666</v>
+        <v>46278.69791666666</v>
       </c>
       <c r="B165">
-        <v>248.465</v>
+        <v>797.398</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -3698,10 +3662,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46269.70833333334</v>
+        <v>46278.70833333334</v>
       </c>
       <c r="B166">
-        <v>229.332</v>
+        <v>814.52</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -3712,10 +3676,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46269.71875</v>
+        <v>46278.71875</v>
       </c>
       <c r="B167">
-        <v>229.944</v>
+        <v>793.128</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -3726,10 +3690,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46269.72916666666</v>
+        <v>46278.72916666666</v>
       </c>
       <c r="B168">
-        <v>232.055</v>
+        <v>773.705</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -3740,10 +3704,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46269.73958333334</v>
+        <v>46278.73958333334</v>
       </c>
       <c r="B169">
-        <v>233.663</v>
+        <v>753.728</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -3754,10 +3718,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46269.75</v>
+        <v>46278.75</v>
       </c>
       <c r="B170">
-        <v>217.665</v>
+        <v>697.6900000000001</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -3768,10 +3732,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46269.76041666666</v>
+        <v>46278.76041666666</v>
       </c>
       <c r="B171">
-        <v>222.889</v>
+        <v>698.513</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -3782,10 +3746,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46269.77083333334</v>
+        <v>46278.77083333334</v>
       </c>
       <c r="B172">
-        <v>230.394</v>
+        <v>700.638</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -3796,10 +3760,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46269.78125</v>
+        <v>46278.78125</v>
       </c>
       <c r="B173">
-        <v>241.271</v>
+        <v>702.925</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -3810,10 +3774,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46269.79166666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="B174">
-        <v>265.716</v>
+        <v>709.741</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -3824,10 +3788,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46269.80208333334</v>
+        <v>46278.80208333334</v>
       </c>
       <c r="B175">
-        <v>281.786</v>
+        <v>721.796</v>
       </c>
       <c r="D175">
         <v>78</v>
@@ -3838,10 +3802,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46269.8125</v>
+        <v>46278.8125</v>
       </c>
       <c r="B176">
-        <v>299.201</v>
+        <v>732.838</v>
       </c>
       <c r="D176">
         <v>79</v>
@@ -3852,10 +3816,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46269.82291666666</v>
+        <v>46278.82291666666</v>
       </c>
       <c r="B177">
-        <v>317.365</v>
+        <v>745.074</v>
       </c>
       <c r="D177">
         <v>80</v>
@@ -3866,10 +3830,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46269.83333333334</v>
+        <v>46278.83333333334</v>
       </c>
       <c r="B178">
-        <v>351.929</v>
+        <v>773.1420000000001</v>
       </c>
       <c r="D178">
         <v>81</v>
@@ -3880,10 +3844,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46269.84375</v>
+        <v>46278.84375</v>
       </c>
       <c r="B179">
-        <v>363.251</v>
+        <v>794.522</v>
       </c>
       <c r="D179">
         <v>82</v>
@@ -3894,10 +3858,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46269.85416666666</v>
+        <v>46278.85416666666</v>
       </c>
       <c r="B180">
-        <v>375.35</v>
+        <v>817.8869999999999</v>
       </c>
       <c r="D180">
         <v>83</v>
@@ -3908,10 +3872,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46269.86458333334</v>
+        <v>46278.86458333334</v>
       </c>
       <c r="B181">
-        <v>388.224</v>
+        <v>838.121</v>
       </c>
       <c r="D181">
         <v>84</v>
@@ -3922,10 +3886,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46269.875</v>
+        <v>46278.875</v>
       </c>
       <c r="B182">
-        <v>401.236</v>
+        <v>918.673</v>
       </c>
       <c r="D182">
         <v>85</v>
@@ -3936,10 +3900,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46269.88541666666</v>
+        <v>46278.88541666666</v>
       </c>
       <c r="B183">
-        <v>411.585</v>
+        <v>950.28</v>
       </c>
       <c r="D183">
         <v>86</v>
@@ -3950,10 +3914,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46269.89583333334</v>
+        <v>46278.89583333334</v>
       </c>
       <c r="B184">
-        <v>422.299</v>
+        <v>981.497</v>
       </c>
       <c r="D184">
         <v>87</v>
@@ -3964,10 +3928,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46269.90625</v>
+        <v>46278.90625</v>
       </c>
       <c r="B185">
-        <v>431.896</v>
+        <v>1014.72</v>
       </c>
       <c r="D185">
         <v>88</v>
@@ -3978,10 +3942,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46269.91666666666</v>
+        <v>46278.91666666666</v>
       </c>
       <c r="B186">
-        <v>476.749</v>
+        <v>1053.564</v>
       </c>
       <c r="D186">
         <v>89</v>
@@ -3992,10 +3956,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46269.92708333334</v>
+        <v>46278.92708333334</v>
       </c>
       <c r="B187">
-        <v>484.721</v>
+        <v>1086.228</v>
       </c>
       <c r="D187">
         <v>90</v>
@@ -4006,10 +3970,10 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46269.9375</v>
+        <v>46278.9375</v>
       </c>
       <c r="B188">
-        <v>491.889</v>
+        <v>1121.841</v>
       </c>
       <c r="D188">
         <v>91</v>
@@ -4020,10 +3984,10 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46269.94791666666</v>
+        <v>46278.94791666666</v>
       </c>
       <c r="B189">
-        <v>500.485</v>
+        <v>1155.289</v>
       </c>
       <c r="D189">
         <v>92</v>

--- a/data_fetching/Entsoe/Wind_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Wind_Production_Historical.xlsx
@@ -31,856 +31,856 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>18.09.20261</t>
-  </si>
-  <si>
-    <t>18.09.20262</t>
-  </si>
-  <si>
-    <t>18.09.20263</t>
-  </si>
-  <si>
-    <t>18.09.20264</t>
-  </si>
-  <si>
-    <t>18.09.20265</t>
-  </si>
-  <si>
-    <t>18.09.20266</t>
-  </si>
-  <si>
-    <t>18.09.20267</t>
-  </si>
-  <si>
-    <t>18.09.20268</t>
-  </si>
-  <si>
-    <t>18.09.20269</t>
-  </si>
-  <si>
-    <t>18.09.202610</t>
-  </si>
-  <si>
-    <t>18.09.202611</t>
-  </si>
-  <si>
-    <t>18.09.202612</t>
-  </si>
-  <si>
-    <t>18.09.202613</t>
-  </si>
-  <si>
-    <t>18.09.202614</t>
-  </si>
-  <si>
-    <t>18.09.202615</t>
-  </si>
-  <si>
-    <t>18.09.202616</t>
-  </si>
-  <si>
-    <t>18.09.202617</t>
-  </si>
-  <si>
-    <t>18.09.202618</t>
-  </si>
-  <si>
-    <t>18.09.202619</t>
-  </si>
-  <si>
-    <t>18.09.202620</t>
-  </si>
-  <si>
-    <t>18.09.202621</t>
-  </si>
-  <si>
-    <t>18.09.202622</t>
-  </si>
-  <si>
-    <t>18.09.202623</t>
-  </si>
-  <si>
-    <t>18.09.202624</t>
-  </si>
-  <si>
-    <t>18.09.202625</t>
-  </si>
-  <si>
-    <t>18.09.202626</t>
-  </si>
-  <si>
-    <t>18.09.202627</t>
-  </si>
-  <si>
-    <t>18.09.202628</t>
-  </si>
-  <si>
-    <t>18.09.202629</t>
-  </si>
-  <si>
-    <t>18.09.202630</t>
-  </si>
-  <si>
-    <t>18.09.202631</t>
-  </si>
-  <si>
-    <t>18.09.202632</t>
-  </si>
-  <si>
-    <t>18.09.202633</t>
-  </si>
-  <si>
-    <t>18.09.202634</t>
-  </si>
-  <si>
-    <t>18.09.202635</t>
-  </si>
-  <si>
-    <t>18.09.202636</t>
-  </si>
-  <si>
-    <t>18.09.202637</t>
-  </si>
-  <si>
-    <t>18.09.202638</t>
-  </si>
-  <si>
-    <t>18.09.202639</t>
-  </si>
-  <si>
-    <t>18.09.202640</t>
-  </si>
-  <si>
-    <t>18.09.202641</t>
-  </si>
-  <si>
-    <t>18.09.202642</t>
-  </si>
-  <si>
-    <t>18.09.202643</t>
-  </si>
-  <si>
-    <t>18.09.202644</t>
-  </si>
-  <si>
-    <t>18.09.202645</t>
-  </si>
-  <si>
-    <t>18.09.202646</t>
-  </si>
-  <si>
-    <t>18.09.202647</t>
-  </si>
-  <si>
-    <t>18.09.202648</t>
-  </si>
-  <si>
-    <t>18.09.202649</t>
-  </si>
-  <si>
-    <t>18.09.202650</t>
-  </si>
-  <si>
-    <t>18.09.202651</t>
-  </si>
-  <si>
-    <t>18.09.202652</t>
-  </si>
-  <si>
-    <t>18.09.202653</t>
-  </si>
-  <si>
-    <t>18.09.202654</t>
-  </si>
-  <si>
-    <t>18.09.202655</t>
-  </si>
-  <si>
-    <t>18.09.202656</t>
-  </si>
-  <si>
-    <t>18.09.202657</t>
-  </si>
-  <si>
-    <t>18.09.202658</t>
-  </si>
-  <si>
-    <t>18.09.202659</t>
-  </si>
-  <si>
-    <t>18.09.202660</t>
-  </si>
-  <si>
-    <t>18.09.202661</t>
-  </si>
-  <si>
-    <t>18.09.202662</t>
-  </si>
-  <si>
-    <t>18.09.202663</t>
-  </si>
-  <si>
-    <t>18.09.202664</t>
-  </si>
-  <si>
-    <t>18.09.202665</t>
-  </si>
-  <si>
-    <t>18.09.202666</t>
-  </si>
-  <si>
-    <t>18.09.202667</t>
-  </si>
-  <si>
-    <t>18.09.202668</t>
-  </si>
-  <si>
-    <t>18.09.202669</t>
-  </si>
-  <si>
-    <t>18.09.202670</t>
-  </si>
-  <si>
-    <t>18.09.202671</t>
-  </si>
-  <si>
-    <t>18.09.202672</t>
-  </si>
-  <si>
-    <t>18.09.202673</t>
-  </si>
-  <si>
-    <t>18.09.202674</t>
-  </si>
-  <si>
-    <t>18.09.202675</t>
-  </si>
-  <si>
-    <t>18.09.202676</t>
-  </si>
-  <si>
-    <t>18.09.202677</t>
-  </si>
-  <si>
-    <t>18.09.202678</t>
-  </si>
-  <si>
-    <t>18.09.202679</t>
-  </si>
-  <si>
-    <t>18.09.202680</t>
-  </si>
-  <si>
-    <t>18.09.202681</t>
-  </si>
-  <si>
-    <t>18.09.202682</t>
-  </si>
-  <si>
-    <t>18.09.202683</t>
-  </si>
-  <si>
-    <t>18.09.202684</t>
-  </si>
-  <si>
-    <t>18.09.202685</t>
-  </si>
-  <si>
-    <t>18.09.202686</t>
-  </si>
-  <si>
-    <t>18.09.202687</t>
-  </si>
-  <si>
-    <t>18.09.202688</t>
-  </si>
-  <si>
-    <t>18.09.202689</t>
-  </si>
-  <si>
-    <t>18.09.202690</t>
-  </si>
-  <si>
-    <t>18.09.202691</t>
-  </si>
-  <si>
-    <t>18.09.202692</t>
-  </si>
-  <si>
-    <t>18.09.202693</t>
-  </si>
-  <si>
-    <t>18.09.202694</t>
-  </si>
-  <si>
-    <t>18.09.202695</t>
-  </si>
-  <si>
-    <t>18.09.202696</t>
-  </si>
-  <si>
-    <t>19.09.20261</t>
-  </si>
-  <si>
-    <t>19.09.20262</t>
-  </si>
-  <si>
-    <t>19.09.20263</t>
-  </si>
-  <si>
-    <t>19.09.20264</t>
-  </si>
-  <si>
-    <t>19.09.20265</t>
-  </si>
-  <si>
-    <t>19.09.20266</t>
-  </si>
-  <si>
-    <t>19.09.20267</t>
-  </si>
-  <si>
-    <t>19.09.20268</t>
-  </si>
-  <si>
-    <t>19.09.20269</t>
-  </si>
-  <si>
-    <t>19.09.202610</t>
-  </si>
-  <si>
-    <t>19.09.202611</t>
-  </si>
-  <si>
-    <t>19.09.202612</t>
-  </si>
-  <si>
-    <t>19.09.202613</t>
-  </si>
-  <si>
-    <t>19.09.202614</t>
-  </si>
-  <si>
-    <t>19.09.202615</t>
-  </si>
-  <si>
-    <t>19.09.202616</t>
-  </si>
-  <si>
-    <t>19.09.202617</t>
-  </si>
-  <si>
-    <t>19.09.202618</t>
-  </si>
-  <si>
-    <t>19.09.202619</t>
-  </si>
-  <si>
-    <t>19.09.202620</t>
-  </si>
-  <si>
-    <t>19.09.202621</t>
-  </si>
-  <si>
-    <t>19.09.202622</t>
-  </si>
-  <si>
-    <t>19.09.202623</t>
-  </si>
-  <si>
-    <t>19.09.202624</t>
-  </si>
-  <si>
-    <t>19.09.202625</t>
-  </si>
-  <si>
-    <t>19.09.202626</t>
-  </si>
-  <si>
-    <t>19.09.202627</t>
-  </si>
-  <si>
-    <t>19.09.202628</t>
-  </si>
-  <si>
-    <t>19.09.202629</t>
-  </si>
-  <si>
-    <t>19.09.202630</t>
-  </si>
-  <si>
-    <t>19.09.202631</t>
-  </si>
-  <si>
-    <t>19.09.202632</t>
-  </si>
-  <si>
-    <t>19.09.202633</t>
-  </si>
-  <si>
-    <t>19.09.202634</t>
-  </si>
-  <si>
-    <t>19.09.202635</t>
-  </si>
-  <si>
-    <t>19.09.202636</t>
-  </si>
-  <si>
-    <t>19.09.202637</t>
-  </si>
-  <si>
-    <t>19.09.202638</t>
-  </si>
-  <si>
-    <t>19.09.202639</t>
-  </si>
-  <si>
-    <t>19.09.202640</t>
-  </si>
-  <si>
-    <t>19.09.202641</t>
-  </si>
-  <si>
-    <t>19.09.202642</t>
-  </si>
-  <si>
-    <t>19.09.202643</t>
-  </si>
-  <si>
-    <t>19.09.202644</t>
-  </si>
-  <si>
-    <t>19.09.202645</t>
-  </si>
-  <si>
-    <t>19.09.202646</t>
-  </si>
-  <si>
-    <t>19.09.202647</t>
-  </si>
-  <si>
-    <t>19.09.202648</t>
-  </si>
-  <si>
-    <t>19.09.202649</t>
-  </si>
-  <si>
-    <t>19.09.202650</t>
-  </si>
-  <si>
-    <t>19.09.202651</t>
-  </si>
-  <si>
-    <t>19.09.202652</t>
-  </si>
-  <si>
-    <t>19.09.202653</t>
-  </si>
-  <si>
-    <t>19.09.202654</t>
-  </si>
-  <si>
-    <t>19.09.202655</t>
-  </si>
-  <si>
-    <t>19.09.202656</t>
-  </si>
-  <si>
-    <t>19.09.202657</t>
-  </si>
-  <si>
-    <t>19.09.202658</t>
-  </si>
-  <si>
-    <t>19.09.202659</t>
-  </si>
-  <si>
-    <t>19.09.202660</t>
-  </si>
-  <si>
-    <t>19.09.202661</t>
-  </si>
-  <si>
-    <t>19.09.202662</t>
-  </si>
-  <si>
-    <t>19.09.202663</t>
-  </si>
-  <si>
-    <t>19.09.202664</t>
-  </si>
-  <si>
-    <t>19.09.202665</t>
-  </si>
-  <si>
-    <t>19.09.202666</t>
-  </si>
-  <si>
-    <t>19.09.202667</t>
-  </si>
-  <si>
-    <t>19.09.202668</t>
-  </si>
-  <si>
-    <t>19.09.202669</t>
-  </si>
-  <si>
-    <t>19.09.202670</t>
-  </si>
-  <si>
-    <t>19.09.202671</t>
-  </si>
-  <si>
-    <t>19.09.202672</t>
-  </si>
-  <si>
-    <t>19.09.202673</t>
-  </si>
-  <si>
-    <t>19.09.202674</t>
-  </si>
-  <si>
-    <t>19.09.202675</t>
-  </si>
-  <si>
-    <t>19.09.202676</t>
-  </si>
-  <si>
-    <t>19.09.202677</t>
-  </si>
-  <si>
-    <t>19.09.202678</t>
-  </si>
-  <si>
-    <t>19.09.202679</t>
-  </si>
-  <si>
-    <t>19.09.202680</t>
-  </si>
-  <si>
-    <t>19.09.202681</t>
-  </si>
-  <si>
-    <t>19.09.202682</t>
-  </si>
-  <si>
-    <t>19.09.202683</t>
-  </si>
-  <si>
-    <t>19.09.202684</t>
-  </si>
-  <si>
-    <t>19.09.202685</t>
-  </si>
-  <si>
-    <t>19.09.202686</t>
-  </si>
-  <si>
-    <t>19.09.202687</t>
-  </si>
-  <si>
-    <t>19.09.202688</t>
-  </si>
-  <si>
-    <t>19.09.202689</t>
-  </si>
-  <si>
-    <t>19.09.202690</t>
-  </si>
-  <si>
-    <t>19.09.202691</t>
-  </si>
-  <si>
-    <t>19.09.202692</t>
-  </si>
-  <si>
-    <t>19.09.202693</t>
-  </si>
-  <si>
-    <t>19.09.202694</t>
-  </si>
-  <si>
-    <t>19.09.202695</t>
-  </si>
-  <si>
-    <t>19.09.202696</t>
-  </si>
-  <si>
-    <t>20.09.20261</t>
-  </si>
-  <si>
-    <t>20.09.20262</t>
-  </si>
-  <si>
-    <t>20.09.20263</t>
-  </si>
-  <si>
-    <t>20.09.20264</t>
-  </si>
-  <si>
-    <t>20.09.20265</t>
-  </si>
-  <si>
-    <t>20.09.20266</t>
-  </si>
-  <si>
-    <t>20.09.20267</t>
-  </si>
-  <si>
-    <t>20.09.20268</t>
-  </si>
-  <si>
-    <t>20.09.20269</t>
-  </si>
-  <si>
-    <t>20.09.202610</t>
-  </si>
-  <si>
-    <t>20.09.202611</t>
-  </si>
-  <si>
-    <t>20.09.202612</t>
-  </si>
-  <si>
-    <t>20.09.202613</t>
-  </si>
-  <si>
-    <t>20.09.202614</t>
-  </si>
-  <si>
-    <t>20.09.202615</t>
-  </si>
-  <si>
-    <t>20.09.202616</t>
-  </si>
-  <si>
-    <t>20.09.202617</t>
-  </si>
-  <si>
-    <t>20.09.202618</t>
-  </si>
-  <si>
-    <t>20.09.202619</t>
-  </si>
-  <si>
-    <t>20.09.202620</t>
-  </si>
-  <si>
-    <t>20.09.202621</t>
-  </si>
-  <si>
-    <t>20.09.202622</t>
-  </si>
-  <si>
-    <t>20.09.202623</t>
-  </si>
-  <si>
-    <t>20.09.202624</t>
-  </si>
-  <si>
-    <t>20.09.202625</t>
-  </si>
-  <si>
-    <t>20.09.202626</t>
-  </si>
-  <si>
-    <t>20.09.202627</t>
-  </si>
-  <si>
-    <t>20.09.202628</t>
-  </si>
-  <si>
-    <t>20.09.202629</t>
-  </si>
-  <si>
-    <t>20.09.202630</t>
-  </si>
-  <si>
-    <t>20.09.202631</t>
-  </si>
-  <si>
-    <t>20.09.202632</t>
-  </si>
-  <si>
-    <t>20.09.202633</t>
-  </si>
-  <si>
-    <t>20.09.202634</t>
-  </si>
-  <si>
-    <t>20.09.202635</t>
-  </si>
-  <si>
-    <t>20.09.202636</t>
-  </si>
-  <si>
-    <t>20.09.202637</t>
-  </si>
-  <si>
-    <t>20.09.202638</t>
-  </si>
-  <si>
-    <t>20.09.202639</t>
-  </si>
-  <si>
-    <t>20.09.202640</t>
-  </si>
-  <si>
-    <t>20.09.202641</t>
-  </si>
-  <si>
-    <t>20.09.202642</t>
-  </si>
-  <si>
-    <t>20.09.202643</t>
-  </si>
-  <si>
-    <t>20.09.202644</t>
-  </si>
-  <si>
-    <t>20.09.202645</t>
-  </si>
-  <si>
-    <t>20.09.202646</t>
-  </si>
-  <si>
-    <t>20.09.202647</t>
-  </si>
-  <si>
-    <t>20.09.202648</t>
-  </si>
-  <si>
-    <t>20.09.202649</t>
-  </si>
-  <si>
-    <t>20.09.202650</t>
-  </si>
-  <si>
-    <t>20.09.202651</t>
-  </si>
-  <si>
-    <t>20.09.202652</t>
-  </si>
-  <si>
-    <t>20.09.202653</t>
-  </si>
-  <si>
-    <t>20.09.202654</t>
-  </si>
-  <si>
-    <t>20.09.202655</t>
-  </si>
-  <si>
-    <t>20.09.202656</t>
-  </si>
-  <si>
-    <t>20.09.202657</t>
-  </si>
-  <si>
-    <t>20.09.202658</t>
-  </si>
-  <si>
-    <t>20.09.202659</t>
-  </si>
-  <si>
-    <t>20.09.202660</t>
-  </si>
-  <si>
-    <t>20.09.202661</t>
-  </si>
-  <si>
-    <t>20.09.202662</t>
-  </si>
-  <si>
-    <t>20.09.202663</t>
-  </si>
-  <si>
-    <t>20.09.202664</t>
-  </si>
-  <si>
-    <t>20.09.202665</t>
-  </si>
-  <si>
-    <t>20.09.202666</t>
-  </si>
-  <si>
-    <t>20.09.202667</t>
-  </si>
-  <si>
-    <t>20.09.202668</t>
-  </si>
-  <si>
-    <t>20.09.202669</t>
-  </si>
-  <si>
-    <t>20.09.202670</t>
-  </si>
-  <si>
-    <t>20.09.202671</t>
-  </si>
-  <si>
-    <t>20.09.202672</t>
-  </si>
-  <si>
-    <t>20.09.202673</t>
-  </si>
-  <si>
-    <t>20.09.202674</t>
-  </si>
-  <si>
-    <t>20.09.202675</t>
-  </si>
-  <si>
-    <t>20.09.202676</t>
-  </si>
-  <si>
-    <t>20.09.202677</t>
-  </si>
-  <si>
-    <t>20.09.202678</t>
-  </si>
-  <si>
-    <t>20.09.202679</t>
-  </si>
-  <si>
-    <t>20.09.202680</t>
-  </si>
-  <si>
-    <t>20.09.202681</t>
-  </si>
-  <si>
-    <t>20.09.202682</t>
-  </si>
-  <si>
-    <t>20.09.202683</t>
-  </si>
-  <si>
-    <t>20.09.202684</t>
-  </si>
-  <si>
-    <t>20.09.202685</t>
-  </si>
-  <si>
-    <t>20.09.202686</t>
-  </si>
-  <si>
-    <t>20.09.202687</t>
-  </si>
-  <si>
-    <t>20.09.202688</t>
-  </si>
-  <si>
-    <t>20.09.202689</t>
-  </si>
-  <si>
-    <t>20.09.202690</t>
-  </si>
-  <si>
-    <t>20.09.202691</t>
-  </si>
-  <si>
-    <t>20.09.202692</t>
+    <t>28.09.20261</t>
+  </si>
+  <si>
+    <t>28.09.20262</t>
+  </si>
+  <si>
+    <t>28.09.20263</t>
+  </si>
+  <si>
+    <t>28.09.20264</t>
+  </si>
+  <si>
+    <t>28.09.20265</t>
+  </si>
+  <si>
+    <t>28.09.20266</t>
+  </si>
+  <si>
+    <t>28.09.20267</t>
+  </si>
+  <si>
+    <t>28.09.20268</t>
+  </si>
+  <si>
+    <t>28.09.20269</t>
+  </si>
+  <si>
+    <t>28.09.202610</t>
+  </si>
+  <si>
+    <t>28.09.202611</t>
+  </si>
+  <si>
+    <t>28.09.202612</t>
+  </si>
+  <si>
+    <t>28.09.202613</t>
+  </si>
+  <si>
+    <t>28.09.202614</t>
+  </si>
+  <si>
+    <t>28.09.202615</t>
+  </si>
+  <si>
+    <t>28.09.202616</t>
+  </si>
+  <si>
+    <t>28.09.202617</t>
+  </si>
+  <si>
+    <t>28.09.202618</t>
+  </si>
+  <si>
+    <t>28.09.202619</t>
+  </si>
+  <si>
+    <t>28.09.202620</t>
+  </si>
+  <si>
+    <t>28.09.202621</t>
+  </si>
+  <si>
+    <t>28.09.202622</t>
+  </si>
+  <si>
+    <t>28.09.202623</t>
+  </si>
+  <si>
+    <t>28.09.202624</t>
+  </si>
+  <si>
+    <t>28.09.202625</t>
+  </si>
+  <si>
+    <t>28.09.202626</t>
+  </si>
+  <si>
+    <t>28.09.202627</t>
+  </si>
+  <si>
+    <t>28.09.202628</t>
+  </si>
+  <si>
+    <t>28.09.202629</t>
+  </si>
+  <si>
+    <t>28.09.202630</t>
+  </si>
+  <si>
+    <t>28.09.202631</t>
+  </si>
+  <si>
+    <t>28.09.202632</t>
+  </si>
+  <si>
+    <t>28.09.202633</t>
+  </si>
+  <si>
+    <t>28.09.202634</t>
+  </si>
+  <si>
+    <t>28.09.202635</t>
+  </si>
+  <si>
+    <t>28.09.202636</t>
+  </si>
+  <si>
+    <t>28.09.202637</t>
+  </si>
+  <si>
+    <t>28.09.202638</t>
+  </si>
+  <si>
+    <t>28.09.202639</t>
+  </si>
+  <si>
+    <t>28.09.202640</t>
+  </si>
+  <si>
+    <t>28.09.202641</t>
+  </si>
+  <si>
+    <t>28.09.202642</t>
+  </si>
+  <si>
+    <t>28.09.202643</t>
+  </si>
+  <si>
+    <t>28.09.202644</t>
+  </si>
+  <si>
+    <t>28.09.202645</t>
+  </si>
+  <si>
+    <t>28.09.202646</t>
+  </si>
+  <si>
+    <t>28.09.202647</t>
+  </si>
+  <si>
+    <t>28.09.202648</t>
+  </si>
+  <si>
+    <t>28.09.202649</t>
+  </si>
+  <si>
+    <t>28.09.202650</t>
+  </si>
+  <si>
+    <t>28.09.202651</t>
+  </si>
+  <si>
+    <t>28.09.202652</t>
+  </si>
+  <si>
+    <t>28.09.202653</t>
+  </si>
+  <si>
+    <t>28.09.202654</t>
+  </si>
+  <si>
+    <t>28.09.202655</t>
+  </si>
+  <si>
+    <t>28.09.202656</t>
+  </si>
+  <si>
+    <t>28.09.202657</t>
+  </si>
+  <si>
+    <t>28.09.202658</t>
+  </si>
+  <si>
+    <t>28.09.202659</t>
+  </si>
+  <si>
+    <t>28.09.202660</t>
+  </si>
+  <si>
+    <t>28.09.202661</t>
+  </si>
+  <si>
+    <t>28.09.202662</t>
+  </si>
+  <si>
+    <t>28.09.202663</t>
+  </si>
+  <si>
+    <t>28.09.202664</t>
+  </si>
+  <si>
+    <t>28.09.202665</t>
+  </si>
+  <si>
+    <t>28.09.202666</t>
+  </si>
+  <si>
+    <t>28.09.202667</t>
+  </si>
+  <si>
+    <t>28.09.202668</t>
+  </si>
+  <si>
+    <t>28.09.202669</t>
+  </si>
+  <si>
+    <t>28.09.202670</t>
+  </si>
+  <si>
+    <t>28.09.202671</t>
+  </si>
+  <si>
+    <t>28.09.202672</t>
+  </si>
+  <si>
+    <t>28.09.202673</t>
+  </si>
+  <si>
+    <t>28.09.202674</t>
+  </si>
+  <si>
+    <t>28.09.202675</t>
+  </si>
+  <si>
+    <t>28.09.202676</t>
+  </si>
+  <si>
+    <t>28.09.202677</t>
+  </si>
+  <si>
+    <t>28.09.202678</t>
+  </si>
+  <si>
+    <t>28.09.202679</t>
+  </si>
+  <si>
+    <t>28.09.202680</t>
+  </si>
+  <si>
+    <t>28.09.202681</t>
+  </si>
+  <si>
+    <t>28.09.202682</t>
+  </si>
+  <si>
+    <t>28.09.202683</t>
+  </si>
+  <si>
+    <t>28.09.202684</t>
+  </si>
+  <si>
+    <t>28.09.202685</t>
+  </si>
+  <si>
+    <t>28.09.202686</t>
+  </si>
+  <si>
+    <t>28.09.202687</t>
+  </si>
+  <si>
+    <t>28.09.202688</t>
+  </si>
+  <si>
+    <t>28.09.202689</t>
+  </si>
+  <si>
+    <t>28.09.202690</t>
+  </si>
+  <si>
+    <t>28.09.202691</t>
+  </si>
+  <si>
+    <t>28.09.202692</t>
+  </si>
+  <si>
+    <t>28.09.202693</t>
+  </si>
+  <si>
+    <t>28.09.202694</t>
+  </si>
+  <si>
+    <t>28.09.202695</t>
+  </si>
+  <si>
+    <t>28.09.202696</t>
+  </si>
+  <si>
+    <t>29.09.20261</t>
+  </si>
+  <si>
+    <t>29.09.20262</t>
+  </si>
+  <si>
+    <t>29.09.20263</t>
+  </si>
+  <si>
+    <t>29.09.20264</t>
+  </si>
+  <si>
+    <t>29.09.20265</t>
+  </si>
+  <si>
+    <t>29.09.20266</t>
+  </si>
+  <si>
+    <t>29.09.20267</t>
+  </si>
+  <si>
+    <t>29.09.20268</t>
+  </si>
+  <si>
+    <t>29.09.20269</t>
+  </si>
+  <si>
+    <t>29.09.202610</t>
+  </si>
+  <si>
+    <t>29.09.202611</t>
+  </si>
+  <si>
+    <t>29.09.202612</t>
+  </si>
+  <si>
+    <t>29.09.202613</t>
+  </si>
+  <si>
+    <t>29.09.202614</t>
+  </si>
+  <si>
+    <t>29.09.202615</t>
+  </si>
+  <si>
+    <t>29.09.202616</t>
+  </si>
+  <si>
+    <t>29.09.202617</t>
+  </si>
+  <si>
+    <t>29.09.202618</t>
+  </si>
+  <si>
+    <t>29.09.202619</t>
+  </si>
+  <si>
+    <t>29.09.202620</t>
+  </si>
+  <si>
+    <t>29.09.202621</t>
+  </si>
+  <si>
+    <t>29.09.202622</t>
+  </si>
+  <si>
+    <t>29.09.202623</t>
+  </si>
+  <si>
+    <t>29.09.202624</t>
+  </si>
+  <si>
+    <t>29.09.202625</t>
+  </si>
+  <si>
+    <t>29.09.202626</t>
+  </si>
+  <si>
+    <t>29.09.202627</t>
+  </si>
+  <si>
+    <t>29.09.202628</t>
+  </si>
+  <si>
+    <t>29.09.202629</t>
+  </si>
+  <si>
+    <t>29.09.202630</t>
+  </si>
+  <si>
+    <t>29.09.202631</t>
+  </si>
+  <si>
+    <t>29.09.202632</t>
+  </si>
+  <si>
+    <t>29.09.202633</t>
+  </si>
+  <si>
+    <t>29.09.202634</t>
+  </si>
+  <si>
+    <t>29.09.202635</t>
+  </si>
+  <si>
+    <t>29.09.202636</t>
+  </si>
+  <si>
+    <t>29.09.202637</t>
+  </si>
+  <si>
+    <t>29.09.202638</t>
+  </si>
+  <si>
+    <t>29.09.202639</t>
+  </si>
+  <si>
+    <t>29.09.202640</t>
+  </si>
+  <si>
+    <t>29.09.202641</t>
+  </si>
+  <si>
+    <t>29.09.202642</t>
+  </si>
+  <si>
+    <t>29.09.202643</t>
+  </si>
+  <si>
+    <t>29.09.202644</t>
+  </si>
+  <si>
+    <t>29.09.202645</t>
+  </si>
+  <si>
+    <t>29.09.202646</t>
+  </si>
+  <si>
+    <t>29.09.202647</t>
+  </si>
+  <si>
+    <t>29.09.202648</t>
+  </si>
+  <si>
+    <t>29.09.202649</t>
+  </si>
+  <si>
+    <t>29.09.202650</t>
+  </si>
+  <si>
+    <t>29.09.202651</t>
+  </si>
+  <si>
+    <t>29.09.202652</t>
+  </si>
+  <si>
+    <t>29.09.202653</t>
+  </si>
+  <si>
+    <t>29.09.202654</t>
+  </si>
+  <si>
+    <t>29.09.202655</t>
+  </si>
+  <si>
+    <t>29.09.202656</t>
+  </si>
+  <si>
+    <t>29.09.202657</t>
+  </si>
+  <si>
+    <t>29.09.202658</t>
+  </si>
+  <si>
+    <t>29.09.202659</t>
+  </si>
+  <si>
+    <t>29.09.202660</t>
+  </si>
+  <si>
+    <t>29.09.202661</t>
+  </si>
+  <si>
+    <t>29.09.202662</t>
+  </si>
+  <si>
+    <t>29.09.202663</t>
+  </si>
+  <si>
+    <t>29.09.202664</t>
+  </si>
+  <si>
+    <t>29.09.202665</t>
+  </si>
+  <si>
+    <t>29.09.202666</t>
+  </si>
+  <si>
+    <t>29.09.202667</t>
+  </si>
+  <si>
+    <t>29.09.202668</t>
+  </si>
+  <si>
+    <t>29.09.202669</t>
+  </si>
+  <si>
+    <t>29.09.202670</t>
+  </si>
+  <si>
+    <t>29.09.202671</t>
+  </si>
+  <si>
+    <t>29.09.202672</t>
+  </si>
+  <si>
+    <t>29.09.202673</t>
+  </si>
+  <si>
+    <t>29.09.202674</t>
+  </si>
+  <si>
+    <t>29.09.202675</t>
+  </si>
+  <si>
+    <t>29.09.202676</t>
+  </si>
+  <si>
+    <t>29.09.202677</t>
+  </si>
+  <si>
+    <t>29.09.202678</t>
+  </si>
+  <si>
+    <t>29.09.202679</t>
+  </si>
+  <si>
+    <t>29.09.202680</t>
+  </si>
+  <si>
+    <t>29.09.202681</t>
+  </si>
+  <si>
+    <t>29.09.202682</t>
+  </si>
+  <si>
+    <t>29.09.202683</t>
+  </si>
+  <si>
+    <t>29.09.202684</t>
+  </si>
+  <si>
+    <t>29.09.202685</t>
+  </si>
+  <si>
+    <t>29.09.202686</t>
+  </si>
+  <si>
+    <t>29.09.202687</t>
+  </si>
+  <si>
+    <t>29.09.202688</t>
+  </si>
+  <si>
+    <t>29.09.202689</t>
+  </si>
+  <si>
+    <t>29.09.202690</t>
+  </si>
+  <si>
+    <t>29.09.202691</t>
+  </si>
+  <si>
+    <t>29.09.202692</t>
+  </si>
+  <si>
+    <t>29.09.202693</t>
+  </si>
+  <si>
+    <t>29.09.202694</t>
+  </si>
+  <si>
+    <t>29.09.202695</t>
+  </si>
+  <si>
+    <t>29.09.202696</t>
+  </si>
+  <si>
+    <t>30.09.20261</t>
+  </si>
+  <si>
+    <t>30.09.20262</t>
+  </si>
+  <si>
+    <t>30.09.20263</t>
+  </si>
+  <si>
+    <t>30.09.20264</t>
+  </si>
+  <si>
+    <t>30.09.20265</t>
+  </si>
+  <si>
+    <t>30.09.20266</t>
+  </si>
+  <si>
+    <t>30.09.20267</t>
+  </si>
+  <si>
+    <t>30.09.20268</t>
+  </si>
+  <si>
+    <t>30.09.20269</t>
+  </si>
+  <si>
+    <t>30.09.202610</t>
+  </si>
+  <si>
+    <t>30.09.202611</t>
+  </si>
+  <si>
+    <t>30.09.202612</t>
+  </si>
+  <si>
+    <t>30.09.202613</t>
+  </si>
+  <si>
+    <t>30.09.202614</t>
+  </si>
+  <si>
+    <t>30.09.202615</t>
+  </si>
+  <si>
+    <t>30.09.202616</t>
+  </si>
+  <si>
+    <t>30.09.202617</t>
+  </si>
+  <si>
+    <t>30.09.202618</t>
+  </si>
+  <si>
+    <t>30.09.202619</t>
+  </si>
+  <si>
+    <t>30.09.202620</t>
+  </si>
+  <si>
+    <t>30.09.202621</t>
+  </si>
+  <si>
+    <t>30.09.202622</t>
+  </si>
+  <si>
+    <t>30.09.202623</t>
+  </si>
+  <si>
+    <t>30.09.202624</t>
+  </si>
+  <si>
+    <t>30.09.202625</t>
+  </si>
+  <si>
+    <t>30.09.202626</t>
+  </si>
+  <si>
+    <t>30.09.202627</t>
+  </si>
+  <si>
+    <t>30.09.202628</t>
+  </si>
+  <si>
+    <t>30.09.202629</t>
+  </si>
+  <si>
+    <t>30.09.202630</t>
+  </si>
+  <si>
+    <t>30.09.202631</t>
+  </si>
+  <si>
+    <t>30.09.202632</t>
+  </si>
+  <si>
+    <t>30.09.202633</t>
+  </si>
+  <si>
+    <t>30.09.202634</t>
+  </si>
+  <si>
+    <t>30.09.202635</t>
+  </si>
+  <si>
+    <t>30.09.202636</t>
+  </si>
+  <si>
+    <t>30.09.202637</t>
+  </si>
+  <si>
+    <t>30.09.202638</t>
+  </si>
+  <si>
+    <t>30.09.202639</t>
+  </si>
+  <si>
+    <t>30.09.202640</t>
+  </si>
+  <si>
+    <t>30.09.202641</t>
+  </si>
+  <si>
+    <t>30.09.202642</t>
+  </si>
+  <si>
+    <t>30.09.202643</t>
+  </si>
+  <si>
+    <t>30.09.202644</t>
+  </si>
+  <si>
+    <t>30.09.202645</t>
+  </si>
+  <si>
+    <t>30.09.202646</t>
+  </si>
+  <si>
+    <t>30.09.202647</t>
+  </si>
+  <si>
+    <t>30.09.202648</t>
+  </si>
+  <si>
+    <t>30.09.202649</t>
+  </si>
+  <si>
+    <t>30.09.202650</t>
+  </si>
+  <si>
+    <t>30.09.202651</t>
+  </si>
+  <si>
+    <t>30.09.202652</t>
+  </si>
+  <si>
+    <t>30.09.202653</t>
+  </si>
+  <si>
+    <t>30.09.202654</t>
+  </si>
+  <si>
+    <t>30.09.202655</t>
+  </si>
+  <si>
+    <t>30.09.202656</t>
+  </si>
+  <si>
+    <t>30.09.202657</t>
+  </si>
+  <si>
+    <t>30.09.202658</t>
+  </si>
+  <si>
+    <t>30.09.202659</t>
+  </si>
+  <si>
+    <t>30.09.202660</t>
+  </si>
+  <si>
+    <t>30.09.202661</t>
+  </si>
+  <si>
+    <t>30.09.202662</t>
+  </si>
+  <si>
+    <t>30.09.202663</t>
+  </si>
+  <si>
+    <t>30.09.202664</t>
+  </si>
+  <si>
+    <t>30.09.202665</t>
+  </si>
+  <si>
+    <t>30.09.202666</t>
+  </si>
+  <si>
+    <t>30.09.202667</t>
+  </si>
+  <si>
+    <t>30.09.202668</t>
+  </si>
+  <si>
+    <t>30.09.202669</t>
+  </si>
+  <si>
+    <t>30.09.202670</t>
+  </si>
+  <si>
+    <t>30.09.202671</t>
+  </si>
+  <si>
+    <t>30.09.202672</t>
+  </si>
+  <si>
+    <t>30.09.202673</t>
+  </si>
+  <si>
+    <t>30.09.202674</t>
+  </si>
+  <si>
+    <t>30.09.202675</t>
+  </si>
+  <si>
+    <t>30.09.202676</t>
+  </si>
+  <si>
+    <t>30.09.202677</t>
+  </si>
+  <si>
+    <t>30.09.202678</t>
+  </si>
+  <si>
+    <t>30.09.202679</t>
+  </si>
+  <si>
+    <t>30.09.202680</t>
+  </si>
+  <si>
+    <t>30.09.202681</t>
+  </si>
+  <si>
+    <t>30.09.202682</t>
+  </si>
+  <si>
+    <t>30.09.202683</t>
+  </si>
+  <si>
+    <t>30.09.202684</t>
+  </si>
+  <si>
+    <t>30.09.202685</t>
+  </si>
+  <si>
+    <t>30.09.202686</t>
+  </si>
+  <si>
+    <t>30.09.202687</t>
+  </si>
+  <si>
+    <t>30.09.202688</t>
+  </si>
+  <si>
+    <t>30.09.202689</t>
+  </si>
+  <si>
+    <t>30.09.202690</t>
+  </si>
+  <si>
+    <t>30.09.202691</t>
+  </si>
+  <si>
+    <t>30.09.202692</t>
   </si>
 </sst>
 </file>
@@ -1264,13 +1264,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46283</v>
+        <v>46293</v>
       </c>
       <c r="B2">
-        <v>618.601</v>
+        <v>2346.124</v>
       </c>
       <c r="C2">
-        <v>850</v>
+        <v>2461</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1281,13 +1281,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46283.01041666666</v>
+        <v>46293.01041666666</v>
       </c>
       <c r="B3">
-        <v>599.314</v>
+        <v>2361.247</v>
       </c>
       <c r="C3">
-        <v>799</v>
+        <v>2454</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1298,13 +1298,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46283.02083333334</v>
+        <v>46293.02083333334</v>
       </c>
       <c r="B4">
-        <v>580.867</v>
+        <v>2369.208</v>
       </c>
       <c r="C4">
-        <v>761</v>
+        <v>2427</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1315,13 +1315,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46283.03125</v>
+        <v>46293.03125</v>
       </c>
       <c r="B5">
-        <v>562.787</v>
+        <v>2377.751</v>
       </c>
       <c r="C5">
-        <v>690</v>
+        <v>2401</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1332,13 +1332,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46283.04166666666</v>
+        <v>46293.04166666666</v>
       </c>
       <c r="B6">
-        <v>512.5410000000001</v>
+        <v>2385.78</v>
       </c>
       <c r="C6">
-        <v>636</v>
+        <v>2391</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1349,13 +1349,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46283.05208333334</v>
+        <v>46293.05208333334</v>
       </c>
       <c r="B7">
-        <v>497.734</v>
+        <v>2393.076</v>
       </c>
       <c r="C7">
-        <v>592</v>
+        <v>2378</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1366,13 +1366,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46283.0625</v>
+        <v>46293.0625</v>
       </c>
       <c r="B8">
-        <v>487.199</v>
+        <v>2399.48</v>
       </c>
       <c r="C8">
-        <v>556</v>
+        <v>2354</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1383,13 +1383,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46283.07291666666</v>
+        <v>46293.07291666666</v>
       </c>
       <c r="B9">
-        <v>469.97</v>
+        <v>2404.964</v>
       </c>
       <c r="C9">
-        <v>536</v>
+        <v>2339</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1400,13 +1400,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46283.08333333334</v>
+        <v>46293.08333333334</v>
       </c>
       <c r="B10">
-        <v>431.401</v>
+        <v>2381.61</v>
       </c>
       <c r="C10">
-        <v>516</v>
+        <v>2343</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1417,13 +1417,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46283.09375</v>
+        <v>46293.09375</v>
       </c>
       <c r="B11">
-        <v>409.884</v>
+        <v>2389.247</v>
       </c>
       <c r="C11">
-        <v>473</v>
+        <v>2359</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1434,13 +1434,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46283.10416666666</v>
+        <v>46293.10416666666</v>
       </c>
       <c r="B12">
-        <v>387.977</v>
+        <v>2398.018</v>
       </c>
       <c r="C12">
-        <v>435</v>
+        <v>2391</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1451,13 +1451,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46283.11458333334</v>
+        <v>46293.11458333334</v>
       </c>
       <c r="B13">
-        <v>373.16</v>
+        <v>2409.091</v>
       </c>
       <c r="C13">
-        <v>399</v>
+        <v>2434</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1468,13 +1468,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46283.125</v>
+        <v>46293.125</v>
       </c>
       <c r="B14">
-        <v>346.589</v>
+        <v>2444.987</v>
       </c>
       <c r="C14">
-        <v>361</v>
+        <v>2473</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1485,13 +1485,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46283.13541666666</v>
+        <v>46293.13541666666</v>
       </c>
       <c r="B15">
-        <v>332.338</v>
+        <v>2462.688</v>
       </c>
       <c r="C15">
-        <v>325</v>
+        <v>2536</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1502,13 +1502,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46283.14583333334</v>
+        <v>46293.14583333334</v>
       </c>
       <c r="B16">
-        <v>318.156</v>
+        <v>2479.475</v>
       </c>
       <c r="C16">
-        <v>295</v>
+        <v>2592</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1519,13 +1519,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46283.15625</v>
+        <v>46293.15625</v>
       </c>
       <c r="B17">
-        <v>303.706</v>
+        <v>2493.099</v>
       </c>
       <c r="C17">
-        <v>259</v>
+        <v>2676</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1536,13 +1536,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46283.16666666666</v>
+        <v>46293.16666666666</v>
       </c>
       <c r="B18">
-        <v>284.167</v>
+        <v>2556.007</v>
       </c>
       <c r="C18">
-        <v>234</v>
+        <v>2720</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1553,13 +1553,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46283.17708333334</v>
+        <v>46293.17708333334</v>
       </c>
       <c r="B19">
-        <v>271.479</v>
+        <v>2576.981</v>
       </c>
       <c r="C19">
-        <v>196</v>
+        <v>2724</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1570,13 +1570,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46283.1875</v>
+        <v>46293.1875</v>
       </c>
       <c r="B20">
-        <v>257.365</v>
+        <v>2594.365</v>
       </c>
       <c r="C20">
-        <v>167</v>
+        <v>2715</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1587,13 +1587,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46283.19791666666</v>
+        <v>46293.19791666666</v>
       </c>
       <c r="B21">
-        <v>246.023</v>
+        <v>2597.555</v>
       </c>
       <c r="C21">
-        <v>150</v>
+        <v>2724</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1604,13 +1604,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46283.20833333334</v>
+        <v>46293.20833333334</v>
       </c>
       <c r="B22">
-        <v>217.855</v>
+        <v>2635.506</v>
       </c>
       <c r="C22">
-        <v>131</v>
+        <v>2755</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1621,13 +1621,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46283.21875</v>
+        <v>46293.21875</v>
       </c>
       <c r="B23">
-        <v>206.371</v>
+        <v>2668.431</v>
       </c>
       <c r="C23">
-        <v>103</v>
+        <v>2796</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1638,13 +1638,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46283.22916666666</v>
+        <v>46293.22916666666</v>
       </c>
       <c r="B24">
-        <v>196.169</v>
+        <v>2685.35</v>
       </c>
       <c r="C24">
-        <v>75</v>
+        <v>2830</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1655,13 +1655,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46283.23958333334</v>
+        <v>46293.23958333334</v>
       </c>
       <c r="B25">
-        <v>185.19</v>
+        <v>2703.877</v>
       </c>
       <c r="C25">
-        <v>48</v>
+        <v>2840</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1672,13 +1672,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46283.25</v>
+        <v>46293.25</v>
       </c>
       <c r="B26">
-        <v>171.223</v>
+        <v>2714.64</v>
       </c>
       <c r="C26">
-        <v>31</v>
+        <v>2789</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1689,13 +1689,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46283.26041666666</v>
+        <v>46293.26041666666</v>
       </c>
       <c r="B27">
-        <v>169.573</v>
+        <v>2729.64</v>
       </c>
       <c r="C27">
-        <v>22</v>
+        <v>2783</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1706,13 +1706,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46283.27083333334</v>
+        <v>46293.27083333334</v>
       </c>
       <c r="B28">
-        <v>160.092</v>
+        <v>2747.072</v>
       </c>
       <c r="C28">
-        <v>17</v>
+        <v>2781</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1723,13 +1723,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46283.28125</v>
+        <v>46293.28125</v>
       </c>
       <c r="B29">
-        <v>158.022</v>
+        <v>2761.302</v>
       </c>
       <c r="C29">
-        <v>17</v>
+        <v>2802</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1740,13 +1740,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46283.29166666666</v>
+        <v>46293.29166666666</v>
       </c>
       <c r="B30">
-        <v>160.344</v>
+        <v>2757.058</v>
       </c>
       <c r="C30">
-        <v>13</v>
+        <v>2817</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1757,13 +1757,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46283.30208333334</v>
+        <v>46293.30208333334</v>
       </c>
       <c r="B31">
-        <v>154.678</v>
+        <v>2756.889</v>
       </c>
       <c r="C31">
-        <v>8</v>
+        <v>2800</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1774,13 +1774,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46283.3125</v>
+        <v>46293.3125</v>
       </c>
       <c r="B32">
-        <v>149.956</v>
+        <v>2734.836</v>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>2796</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1791,13 +1791,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46283.32291666666</v>
+        <v>46293.32291666666</v>
       </c>
       <c r="B33">
-        <v>146.924</v>
+        <v>2727.038</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1808,13 +1808,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46283.33333333334</v>
+        <v>46293.33333333334</v>
       </c>
       <c r="B34">
-        <v>155.155</v>
+        <v>2676.012</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>2816</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1825,13 +1825,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46283.34375</v>
+        <v>46293.34375</v>
       </c>
       <c r="B35">
-        <v>149.545</v>
+        <v>2684.167</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>2841</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1842,13 +1842,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46283.35416666666</v>
+        <v>46293.35416666666</v>
       </c>
       <c r="B36">
-        <v>142.418</v>
+        <v>2690.789</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>2823</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1859,13 +1859,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46283.36458333334</v>
+        <v>46293.36458333334</v>
       </c>
       <c r="B37">
-        <v>136.767</v>
+        <v>2705.945</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>2810</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1876,13 +1876,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46283.375</v>
+        <v>46293.375</v>
       </c>
       <c r="B38">
-        <v>121.629</v>
+        <v>2777.212</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>2777</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1893,13 +1893,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46283.38541666666</v>
+        <v>46293.38541666666</v>
       </c>
       <c r="B39">
-        <v>126.044</v>
+        <v>2776.146</v>
       </c>
       <c r="C39">
-        <v>3</v>
+        <v>2769</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1910,13 +1910,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46283.39583333334</v>
+        <v>46293.39583333334</v>
       </c>
       <c r="B40">
-        <v>130.753</v>
+        <v>2786.4</v>
       </c>
       <c r="C40">
-        <v>6</v>
+        <v>2765</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1927,13 +1927,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46283.40625</v>
+        <v>46293.40625</v>
       </c>
       <c r="B41">
-        <v>135.795</v>
+        <v>2792.238</v>
       </c>
       <c r="C41">
-        <v>18</v>
+        <v>2772</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1944,13 +1944,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46283.41666666666</v>
+        <v>46293.41666666666</v>
       </c>
       <c r="B42">
-        <v>147.548</v>
+        <v>2761.51</v>
       </c>
       <c r="C42">
-        <v>30</v>
+        <v>2749</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1961,13 +1961,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46283.42708333334</v>
+        <v>46293.42708333334</v>
       </c>
       <c r="B43">
-        <v>153.511</v>
+        <v>2759.5</v>
       </c>
       <c r="C43">
-        <v>55</v>
+        <v>2734</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1978,13 +1978,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46283.4375</v>
+        <v>46293.4375</v>
       </c>
       <c r="B44">
-        <v>160.134</v>
+        <v>2726.974</v>
       </c>
       <c r="C44">
-        <v>90</v>
+        <v>2704</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1995,13 +1995,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46283.44791666666</v>
+        <v>46293.44791666666</v>
       </c>
       <c r="B45">
-        <v>166.188</v>
+        <v>2725.834</v>
       </c>
       <c r="C45">
-        <v>118</v>
+        <v>2715</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -2012,13 +2012,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46283.45833333334</v>
+        <v>46293.45833333334</v>
       </c>
       <c r="B46">
-        <v>184.307</v>
+        <v>2718.09</v>
       </c>
       <c r="C46">
-        <v>121</v>
+        <v>2745</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -2029,13 +2029,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46283.46875</v>
+        <v>46293.46875</v>
       </c>
       <c r="B47">
-        <v>188.589</v>
+        <v>2718.281</v>
       </c>
       <c r="C47">
-        <v>122</v>
+        <v>2752</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -2046,13 +2046,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46283.47916666666</v>
+        <v>46293.47916666666</v>
       </c>
       <c r="B48">
-        <v>193.36</v>
+        <v>2718.64</v>
       </c>
       <c r="C48">
-        <v>128</v>
+        <v>2759</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -2063,13 +2063,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46283.48958333334</v>
+        <v>46293.48958333334</v>
       </c>
       <c r="B49">
-        <v>196.816</v>
+        <v>2718.581</v>
       </c>
       <c r="C49">
-        <v>119</v>
+        <v>2772</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -2080,13 +2080,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46283.5</v>
+        <v>46293.5</v>
       </c>
       <c r="B50">
-        <v>206.122</v>
+        <v>2702.696</v>
       </c>
       <c r="C50">
-        <v>123</v>
+        <v>2810</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -2097,13 +2097,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46283.51041666666</v>
+        <v>46293.51041666666</v>
       </c>
       <c r="B51">
-        <v>209.198</v>
+        <v>2700.833</v>
       </c>
       <c r="C51">
-        <v>121</v>
+        <v>2833</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -2114,13 +2114,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46283.52083333334</v>
+        <v>46293.52083333334</v>
       </c>
       <c r="B52">
-        <v>211.707</v>
+        <v>2697.819</v>
       </c>
       <c r="C52">
-        <v>136</v>
+        <v>2888</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -2131,13 +2131,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46283.53125</v>
+        <v>46293.53125</v>
       </c>
       <c r="B53">
-        <v>214.337</v>
+        <v>2694.988</v>
       </c>
       <c r="C53">
-        <v>141</v>
+        <v>2903</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -2148,13 +2148,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46283.54166666666</v>
+        <v>46293.54166666666</v>
       </c>
       <c r="B54">
-        <v>212.487</v>
+        <v>2713.609</v>
       </c>
       <c r="C54">
-        <v>157</v>
+        <v>2796</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -2165,13 +2165,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46283.55208333334</v>
+        <v>46293.55208333334</v>
       </c>
       <c r="B55">
-        <v>216.797</v>
+        <v>2706.586</v>
       </c>
       <c r="C55">
-        <v>163</v>
+        <v>2799</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -2182,13 +2182,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46283.5625</v>
+        <v>46293.5625</v>
       </c>
       <c r="B56">
-        <v>221.003</v>
+        <v>2697.059</v>
       </c>
       <c r="C56">
-        <v>171</v>
+        <v>2778</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -2199,13 +2199,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46283.57291666666</v>
+        <v>46293.57291666666</v>
       </c>
       <c r="B57">
-        <v>226.776</v>
+        <v>2689.266</v>
       </c>
       <c r="C57">
-        <v>172</v>
+        <v>2820</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -2216,13 +2216,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46283.58333333334</v>
+        <v>46293.58333333334</v>
       </c>
       <c r="B58">
-        <v>232.609</v>
+        <v>2701.975</v>
       </c>
       <c r="C58">
-        <v>172</v>
+        <v>2851</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -2233,13 +2233,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46283.59375</v>
+        <v>46293.59375</v>
       </c>
       <c r="B59">
-        <v>239.287</v>
+        <v>2696.477</v>
       </c>
       <c r="C59">
-        <v>179</v>
+        <v>2844</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -2250,13 +2250,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46283.60416666666</v>
+        <v>46293.60416666666</v>
       </c>
       <c r="B60">
-        <v>246.266</v>
+        <v>2690.843</v>
       </c>
       <c r="C60">
-        <v>189</v>
+        <v>2831</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -2267,13 +2267,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46283.61458333334</v>
+        <v>46293.61458333334</v>
       </c>
       <c r="B61">
-        <v>253.348</v>
+        <v>2685.6</v>
       </c>
       <c r="C61">
-        <v>210</v>
+        <v>2864</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2284,13 +2284,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46283.625</v>
+        <v>46293.625</v>
       </c>
       <c r="B62">
-        <v>262.609</v>
+        <v>2708.146</v>
       </c>
       <c r="C62">
-        <v>223</v>
+        <v>2896</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2301,13 +2301,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46283.63541666666</v>
+        <v>46293.63541666666</v>
       </c>
       <c r="B63">
-        <v>273.92</v>
+        <v>2701.454</v>
       </c>
       <c r="C63">
-        <v>225</v>
+        <v>2898</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2318,13 +2318,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46283.64583333334</v>
+        <v>46293.64583333334</v>
       </c>
       <c r="B64">
-        <v>284.545</v>
+        <v>2693.491</v>
       </c>
       <c r="C64">
-        <v>231</v>
+        <v>2712</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2335,13 +2335,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46283.65625</v>
+        <v>46293.65625</v>
       </c>
       <c r="B65">
-        <v>296.127</v>
+        <v>2718.439</v>
       </c>
       <c r="C65">
-        <v>245</v>
+        <v>2761</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2352,13 +2352,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46283.66666666666</v>
+        <v>46293.66666666666</v>
       </c>
       <c r="B66">
-        <v>270.833</v>
+        <v>2704.841</v>
       </c>
       <c r="C66">
-        <v>254</v>
+        <v>2785</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2369,13 +2369,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46283.67708333334</v>
+        <v>46293.67708333334</v>
       </c>
       <c r="B67">
-        <v>286.171</v>
+        <v>2684.783</v>
       </c>
       <c r="C67">
-        <v>286</v>
+        <v>2816</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2386,13 +2386,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46283.6875</v>
+        <v>46293.6875</v>
       </c>
       <c r="B68">
-        <v>301.043</v>
+        <v>2666.7</v>
       </c>
       <c r="C68">
-        <v>338</v>
+        <v>2854</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2403,13 +2403,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46283.69791666666</v>
+        <v>46293.69791666666</v>
       </c>
       <c r="B69">
-        <v>316.753</v>
+        <v>2647.864</v>
       </c>
       <c r="C69">
-        <v>378</v>
+        <v>2880</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2420,13 +2420,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46283.70833333334</v>
+        <v>46293.70833333334</v>
       </c>
       <c r="B70">
-        <v>335.171</v>
+        <v>2615.433</v>
       </c>
       <c r="C70">
-        <v>373</v>
+        <v>2882</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2437,13 +2437,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46283.71875</v>
+        <v>46293.71875</v>
       </c>
       <c r="B71">
-        <v>367.131</v>
+        <v>2587.227</v>
       </c>
       <c r="C71">
-        <v>383</v>
+        <v>2847</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2454,13 +2454,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46283.72916666666</v>
+        <v>46293.72916666666</v>
       </c>
       <c r="B72">
-        <v>398.191</v>
+        <v>2562.646</v>
       </c>
       <c r="C72">
-        <v>430</v>
+        <v>2811</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2471,13 +2471,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46283.73958333334</v>
+        <v>46293.73958333334</v>
       </c>
       <c r="B73">
-        <v>433.236</v>
+        <v>2539.611</v>
       </c>
       <c r="C73">
-        <v>497</v>
+        <v>2779</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2488,13 +2488,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46283.75</v>
+        <v>46293.75</v>
       </c>
       <c r="B74">
-        <v>515.484</v>
+        <v>2500.577</v>
       </c>
       <c r="C74">
-        <v>566</v>
+        <v>2735</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2505,13 +2505,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46283.76041666666</v>
+        <v>46293.76041666666</v>
       </c>
       <c r="B75">
-        <v>556.051</v>
+        <v>2485.077</v>
       </c>
       <c r="C75">
-        <v>617</v>
+        <v>2729</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2522,13 +2522,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46283.77083333334</v>
+        <v>46293.77083333334</v>
       </c>
       <c r="B76">
-        <v>596.11</v>
+        <v>2470.963</v>
       </c>
       <c r="C76">
-        <v>676</v>
+        <v>2729</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2539,13 +2539,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46283.78125</v>
+        <v>46293.78125</v>
       </c>
       <c r="B77">
-        <v>639.5549999999999</v>
+        <v>2456.171</v>
       </c>
       <c r="C77">
-        <v>776</v>
+        <v>2758</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2556,13 +2556,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46283.79166666666</v>
+        <v>46293.79166666666</v>
       </c>
       <c r="B78">
-        <v>681.9109999999999</v>
+        <v>2361.467</v>
       </c>
       <c r="C78">
-        <v>867</v>
+        <v>2773</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2573,13 +2573,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46283.80208333334</v>
+        <v>46293.80208333334</v>
       </c>
       <c r="B79">
-        <v>707.999</v>
+        <v>2363.098</v>
       </c>
       <c r="C79">
-        <v>917</v>
+        <v>2773</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2590,13 +2590,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46283.8125</v>
+        <v>46293.8125</v>
       </c>
       <c r="B80">
-        <v>734.85</v>
+        <v>2362.729</v>
       </c>
       <c r="C80">
-        <v>980</v>
+        <v>2770</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2607,13 +2607,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46283.82291666666</v>
+        <v>46293.82291666666</v>
       </c>
       <c r="B81">
-        <v>760.822</v>
+        <v>2359.502</v>
       </c>
       <c r="C81">
-        <v>1042</v>
+        <v>2770</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2624,13 +2624,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46283.83333333334</v>
+        <v>46293.83333333334</v>
       </c>
       <c r="B82">
-        <v>784.926</v>
+        <v>2356.586</v>
       </c>
       <c r="C82">
-        <v>1069</v>
+        <v>2767</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2641,13 +2641,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46283.84375</v>
+        <v>46293.84375</v>
       </c>
       <c r="B83">
-        <v>792.636</v>
+        <v>2356.482</v>
       </c>
       <c r="C83">
-        <v>1098</v>
+        <v>2730</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2658,13 +2658,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46283.85416666666</v>
+        <v>46293.85416666666</v>
       </c>
       <c r="B84">
-        <v>802.188</v>
+        <v>2358.279</v>
       </c>
       <c r="C84">
-        <v>1073</v>
+        <v>2728</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2675,13 +2675,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46283.86458333334</v>
+        <v>46293.86458333334</v>
       </c>
       <c r="B85">
-        <v>810.912</v>
+        <v>2360.677</v>
       </c>
       <c r="C85">
-        <v>1058</v>
+        <v>2717</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2692,13 +2692,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46283.875</v>
+        <v>46293.875</v>
       </c>
       <c r="B86">
-        <v>814.213</v>
+        <v>2373.896</v>
       </c>
       <c r="C86">
-        <v>1043</v>
+        <v>2770</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2709,13 +2709,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46283.88541666666</v>
+        <v>46293.88541666666</v>
       </c>
       <c r="B87">
-        <v>811.756</v>
+        <v>2384.568</v>
       </c>
       <c r="C87">
-        <v>1042</v>
+        <v>2780</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2726,13 +2726,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46283.89583333334</v>
+        <v>46293.89583333334</v>
       </c>
       <c r="B88">
-        <v>807.973</v>
+        <v>2395.224</v>
       </c>
       <c r="C88">
-        <v>1033</v>
+        <v>2779</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2743,13 +2743,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46283.90625</v>
+        <v>46293.90625</v>
       </c>
       <c r="B89">
-        <v>803.651</v>
+        <v>2405.737</v>
       </c>
       <c r="C89">
-        <v>1010</v>
+        <v>2770</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2760,13 +2760,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46283.91666666666</v>
+        <v>46293.91666666666</v>
       </c>
       <c r="B90">
-        <v>790.898</v>
+        <v>2491.638</v>
       </c>
       <c r="C90">
-        <v>969</v>
+        <v>2756</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2777,13 +2777,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46283.92708333334</v>
+        <v>46293.92708333334</v>
       </c>
       <c r="B91">
-        <v>773.873</v>
+        <v>2500.552</v>
       </c>
       <c r="C91">
-        <v>930</v>
+        <v>2760</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2794,13 +2794,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46283.9375</v>
+        <v>46293.9375</v>
       </c>
       <c r="B92">
-        <v>756.288</v>
+        <v>2508.862</v>
       </c>
       <c r="C92">
-        <v>871</v>
+        <v>2746</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2811,13 +2811,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46283.94791666666</v>
+        <v>46293.94791666666</v>
       </c>
       <c r="B93">
-        <v>738.434</v>
+        <v>2517.125</v>
       </c>
       <c r="C93">
-        <v>813</v>
+        <v>2745</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2828,13 +2828,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46283.95833333334</v>
+        <v>46293.95833333334</v>
       </c>
       <c r="B94">
-        <v>672.793</v>
+        <v>2464.976</v>
       </c>
       <c r="C94">
-        <v>645</v>
+        <v>2732</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2845,13 +2845,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46283.96875</v>
+        <v>46293.96875</v>
       </c>
       <c r="B95">
-        <v>650.5410000000001</v>
+        <v>2461.993</v>
       </c>
       <c r="C95">
-        <v>613</v>
+        <v>2708</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2862,13 +2862,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46283.97916666666</v>
+        <v>46293.97916666666</v>
       </c>
       <c r="B96">
-        <v>622.1130000000001</v>
+        <v>2473.593</v>
       </c>
       <c r="C96">
-        <v>580</v>
+        <v>2681</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2879,13 +2879,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46283.98958333334</v>
+        <v>46293.98958333334</v>
       </c>
       <c r="B97">
-        <v>604.654</v>
+        <v>2472.181</v>
       </c>
       <c r="C97">
-        <v>533</v>
+        <v>2656</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2896,13 +2896,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46284</v>
+        <v>46294</v>
       </c>
       <c r="B98">
-        <v>576.516</v>
+        <v>2442.655</v>
       </c>
       <c r="C98">
-        <v>487</v>
+        <v>2614</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2913,13 +2913,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46284.01041666666</v>
+        <v>46294.01041666666</v>
       </c>
       <c r="B99">
-        <v>548.1079999999999</v>
+        <v>2439.735</v>
       </c>
       <c r="C99">
-        <v>460</v>
+        <v>2624</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2930,13 +2930,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46284.02083333334</v>
+        <v>46294.02083333334</v>
       </c>
       <c r="B100">
-        <v>517.86</v>
+        <v>2439.55</v>
       </c>
       <c r="C100">
-        <v>435</v>
+        <v>2624</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2947,13 +2947,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46284.03125</v>
+        <v>46294.03125</v>
       </c>
       <c r="B101">
-        <v>492.327</v>
+        <v>2439.624</v>
       </c>
       <c r="C101">
-        <v>422</v>
+        <v>2612</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2964,13 +2964,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46284.04166666666</v>
+        <v>46294.04166666666</v>
       </c>
       <c r="B102">
-        <v>428.388</v>
+        <v>2419.278</v>
       </c>
       <c r="C102">
-        <v>417</v>
+        <v>2591</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2981,13 +2981,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46284.05208333334</v>
+        <v>46294.05208333334</v>
       </c>
       <c r="B103">
-        <v>406.157</v>
+        <v>2411.935</v>
       </c>
       <c r="C103">
-        <v>385</v>
+        <v>2582</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2998,13 +2998,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46284.0625</v>
+        <v>46294.0625</v>
       </c>
       <c r="B104">
-        <v>387.744</v>
+        <v>2408.29</v>
       </c>
       <c r="C104">
-        <v>349</v>
+        <v>2577</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -3015,13 +3015,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46284.07291666666</v>
+        <v>46294.07291666666</v>
       </c>
       <c r="B105">
-        <v>366.11</v>
+        <v>2401.668</v>
       </c>
       <c r="C105">
-        <v>320</v>
+        <v>2574</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -3032,13 +3032,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46284.08333333334</v>
+        <v>46294.08333333334</v>
       </c>
       <c r="B106">
-        <v>321.818</v>
+        <v>2409.885</v>
       </c>
       <c r="C106">
-        <v>288</v>
+        <v>2564</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -3049,13 +3049,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46284.09375</v>
+        <v>46294.09375</v>
       </c>
       <c r="B107">
-        <v>306.349</v>
+        <v>2412.824</v>
       </c>
       <c r="C107">
-        <v>266</v>
+        <v>2564</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -3066,13 +3066,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46284.10416666666</v>
+        <v>46294.10416666666</v>
       </c>
       <c r="B108">
-        <v>287.285</v>
+        <v>2407.774</v>
       </c>
       <c r="C108">
-        <v>247</v>
+        <v>2552</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -3083,13 +3083,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46284.11458333334</v>
+        <v>46294.11458333334</v>
       </c>
       <c r="B109">
-        <v>272.693</v>
+        <v>2404</v>
       </c>
       <c r="C109">
-        <v>232</v>
+        <v>2530</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -3100,13 +3100,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46284.125</v>
+        <v>46294.125</v>
       </c>
       <c r="B110">
-        <v>258.567</v>
+        <v>2405.241</v>
       </c>
       <c r="C110">
-        <v>210</v>
+        <v>2510</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -3117,13 +3117,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46284.13541666666</v>
+        <v>46294.13541666666</v>
       </c>
       <c r="B111">
-        <v>243.592</v>
+        <v>2406.122</v>
       </c>
       <c r="C111">
-        <v>205</v>
+        <v>2504</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -3134,13 +3134,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46284.14583333334</v>
+        <v>46294.14583333334</v>
       </c>
       <c r="B112">
-        <v>233.779</v>
+        <v>2405.022</v>
       </c>
       <c r="C112">
-        <v>190</v>
+        <v>2511</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -3151,13 +3151,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46284.15625</v>
+        <v>46294.15625</v>
       </c>
       <c r="B113">
-        <v>219.414</v>
+        <v>2400.487</v>
       </c>
       <c r="C113">
-        <v>167</v>
+        <v>2533</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -3168,13 +3168,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46284.16666666666</v>
+        <v>46294.16666666666</v>
       </c>
       <c r="B114">
-        <v>193.155</v>
+        <v>2395.105</v>
       </c>
       <c r="C114">
-        <v>149</v>
+        <v>2549</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -3185,13 +3185,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46284.17708333334</v>
+        <v>46294.17708333334</v>
       </c>
       <c r="B115">
-        <v>184.069</v>
+        <v>2394.428</v>
       </c>
       <c r="C115">
-        <v>141</v>
+        <v>2551</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -3202,13 +3202,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46284.1875</v>
+        <v>46294.1875</v>
       </c>
       <c r="B116">
-        <v>172.771</v>
+        <v>2394.335</v>
       </c>
       <c r="C116">
-        <v>123</v>
+        <v>2550</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -3219,13 +3219,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46284.19791666666</v>
+        <v>46294.19791666666</v>
       </c>
       <c r="B117">
-        <v>160.048</v>
+        <v>2394.09</v>
       </c>
       <c r="C117">
-        <v>109</v>
+        <v>2529</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -3236,13 +3236,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46284.20833333334</v>
+        <v>46294.20833333334</v>
       </c>
       <c r="B118">
-        <v>158.317</v>
+        <v>2385.102</v>
       </c>
       <c r="C118">
-        <v>93</v>
+        <v>2528</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -3253,13 +3253,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46284.21875</v>
+        <v>46294.21875</v>
       </c>
       <c r="B119">
-        <v>148.676</v>
+        <v>2386.559</v>
       </c>
       <c r="C119">
-        <v>74</v>
+        <v>2523</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -3270,13 +3270,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46284.22916666666</v>
+        <v>46294.22916666666</v>
       </c>
       <c r="B120">
-        <v>141.248</v>
+        <v>2378.056</v>
       </c>
       <c r="C120">
-        <v>62</v>
+        <v>2523</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3287,13 +3287,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46284.23958333334</v>
+        <v>46294.23958333334</v>
       </c>
       <c r="B121">
-        <v>133.931</v>
+        <v>2375.854</v>
       </c>
       <c r="C121">
-        <v>50</v>
+        <v>2524</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3304,13 +3304,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46284.25</v>
+        <v>46294.25</v>
       </c>
       <c r="B122">
-        <v>121.804</v>
+        <v>2369.829</v>
       </c>
       <c r="C122">
-        <v>40</v>
+        <v>2524</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3321,13 +3321,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46284.26041666666</v>
+        <v>46294.26041666666</v>
       </c>
       <c r="B123">
-        <v>116.812</v>
+        <v>2366.452</v>
       </c>
       <c r="C123">
-        <v>29</v>
+        <v>2521</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3338,13 +3338,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46284.27083333334</v>
+        <v>46294.27083333334</v>
       </c>
       <c r="B124">
-        <v>113.341</v>
+        <v>2360.137</v>
       </c>
       <c r="C124">
-        <v>23</v>
+        <v>2520</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3355,13 +3355,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46284.28125</v>
+        <v>46294.28125</v>
       </c>
       <c r="B125">
-        <v>109.816</v>
+        <v>2357.493</v>
       </c>
       <c r="C125">
-        <v>10</v>
+        <v>2506</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3372,13 +3372,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46284.29166666666</v>
+        <v>46294.29166666666</v>
       </c>
       <c r="B126">
-        <v>122.359</v>
+        <v>2331.379</v>
       </c>
       <c r="C126">
-        <v>0</v>
+        <v>2473</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3389,13 +3389,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46284.30208333334</v>
+        <v>46294.30208333334</v>
       </c>
       <c r="B127">
-        <v>121.165</v>
+        <v>2322.227</v>
       </c>
       <c r="C127">
-        <v>0</v>
+        <v>2426</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3406,13 +3406,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46284.3125</v>
+        <v>46294.3125</v>
       </c>
       <c r="B128">
-        <v>120.932</v>
+        <v>2304.08</v>
       </c>
       <c r="C128">
-        <v>0</v>
+        <v>2361</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3423,13 +3423,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46284.32291666666</v>
+        <v>46294.32291666666</v>
       </c>
       <c r="B129">
-        <v>116.341</v>
+        <v>2292.625</v>
       </c>
       <c r="C129">
-        <v>0</v>
+        <v>2309</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3440,13 +3440,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46284.33333333334</v>
+        <v>46294.33333333334</v>
       </c>
       <c r="B130">
-        <v>116.475</v>
+        <v>2242.579</v>
       </c>
       <c r="C130">
-        <v>0</v>
+        <v>2264</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3457,13 +3457,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46284.34375</v>
+        <v>46294.34375</v>
       </c>
       <c r="B131">
-        <v>112.438</v>
+        <v>2238.581</v>
       </c>
       <c r="C131">
-        <v>0</v>
+        <v>2225</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3474,13 +3474,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46284.35416666666</v>
+        <v>46294.35416666666</v>
       </c>
       <c r="B132">
-        <v>113.156</v>
+        <v>2236.717</v>
       </c>
       <c r="C132">
-        <v>0</v>
+        <v>2166</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3491,13 +3491,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46284.36458333334</v>
+        <v>46294.36458333334</v>
       </c>
       <c r="B133">
-        <v>113.166</v>
+        <v>2229.567</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>2086</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3508,13 +3508,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46284.375</v>
+        <v>46294.375</v>
       </c>
       <c r="B134">
-        <v>121.655</v>
+        <v>2201.31</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>1976</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3525,13 +3525,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46284.38541666666</v>
+        <v>46294.38541666666</v>
       </c>
       <c r="B135">
-        <v>127.045</v>
+        <v>2130.513</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>1880</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3542,13 +3542,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46284.39583333334</v>
+        <v>46294.39583333334</v>
       </c>
       <c r="B136">
-        <v>128.563</v>
+        <v>2111.605</v>
       </c>
       <c r="C136">
-        <v>0</v>
+        <v>1826</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3559,13 +3559,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46284.40625</v>
+        <v>46294.40625</v>
       </c>
       <c r="B137">
-        <v>130.529</v>
+        <v>2089.304</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>1725</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3576,13 +3576,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46284.41666666666</v>
+        <v>46294.41666666666</v>
       </c>
       <c r="B138">
-        <v>132.031</v>
+        <v>2094.843</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>1705</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3593,13 +3593,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46284.42708333334</v>
+        <v>46294.42708333334</v>
       </c>
       <c r="B139">
-        <v>135.61</v>
+        <v>2080.947</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>1711</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3610,13 +3610,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46284.4375</v>
+        <v>46294.4375</v>
       </c>
       <c r="B140">
-        <v>139.136</v>
+        <v>2069.12</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>1771</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3627,13 +3627,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46284.44791666666</v>
+        <v>46294.44791666666</v>
       </c>
       <c r="B141">
-        <v>142.291</v>
+        <v>2059.574</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>1819</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3644,13 +3644,13 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46284.45833333334</v>
+        <v>46294.45833333334</v>
       </c>
       <c r="B142">
-        <v>139.521</v>
+        <v>2054.852</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>1840</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3661,13 +3661,13 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46284.46875</v>
+        <v>46294.46875</v>
       </c>
       <c r="B143">
-        <v>141.178</v>
+        <v>2060.312</v>
       </c>
       <c r="C143">
-        <v>0</v>
+        <v>1877</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3678,13 +3678,13 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46284.47916666666</v>
+        <v>46294.47916666666</v>
       </c>
       <c r="B144">
-        <v>143.126</v>
+        <v>2066.534</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>1941</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3695,13 +3695,13 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46284.48958333334</v>
+        <v>46294.48958333334</v>
       </c>
       <c r="B145">
-        <v>144.802</v>
+        <v>2071.323</v>
       </c>
       <c r="C145">
-        <v>0</v>
+        <v>1932</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3712,13 +3712,13 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46284.5</v>
+        <v>46294.5</v>
       </c>
       <c r="B146">
-        <v>146.514</v>
+        <v>2088.161</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>1999</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3729,13 +3729,13 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46284.51041666666</v>
+        <v>46294.51041666666</v>
       </c>
       <c r="B147">
-        <v>148.215</v>
+        <v>2091.646</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>2040</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3746,13 +3746,13 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46284.52083333334</v>
+        <v>46294.52083333334</v>
       </c>
       <c r="B148">
-        <v>149.78</v>
+        <v>2101.692</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>2065</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3763,13 +3763,13 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46284.53125</v>
+        <v>46294.53125</v>
       </c>
       <c r="B149">
-        <v>151.267</v>
+        <v>2108.731</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>2082</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3780,13 +3780,13 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46284.54166666666</v>
+        <v>46294.54166666666</v>
       </c>
       <c r="B150">
-        <v>151.62</v>
+        <v>2115.188</v>
       </c>
       <c r="C150">
-        <v>4</v>
+        <v>2069</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3797,13 +3797,13 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46284.55208333334</v>
+        <v>46294.55208333334</v>
       </c>
       <c r="B151">
-        <v>155.277</v>
+        <v>2114.097</v>
       </c>
       <c r="C151">
-        <v>14</v>
+        <v>2097</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3814,13 +3814,13 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46284.5625</v>
+        <v>46294.5625</v>
       </c>
       <c r="B152">
-        <v>159.655</v>
+        <v>2113.548</v>
       </c>
       <c r="C152">
-        <v>18</v>
+        <v>2116</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3831,13 +3831,13 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46284.57291666666</v>
+        <v>46294.57291666666</v>
       </c>
       <c r="B153">
-        <v>163.72</v>
+        <v>2112.258</v>
       </c>
       <c r="C153">
-        <v>38</v>
+        <v>2124</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3848,13 +3848,13 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46284.58333333334</v>
+        <v>46294.58333333334</v>
       </c>
       <c r="B154">
-        <v>173.393</v>
+        <v>2112.887</v>
       </c>
       <c r="C154">
-        <v>63</v>
+        <v>2093</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3865,13 +3865,13 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46284.59375</v>
+        <v>46294.59375</v>
       </c>
       <c r="B155">
-        <v>179.252</v>
+        <v>2107.854</v>
       </c>
       <c r="C155">
-        <v>78</v>
+        <v>1999</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3882,13 +3882,13 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46284.60416666666</v>
+        <v>46294.60416666666</v>
       </c>
       <c r="B156">
-        <v>184.217</v>
+        <v>2100.948</v>
       </c>
       <c r="C156">
-        <v>96</v>
+        <v>1947</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3899,13 +3899,13 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46284.61458333334</v>
+        <v>46294.61458333334</v>
       </c>
       <c r="B157">
-        <v>189.542</v>
+        <v>2094.578</v>
       </c>
       <c r="C157">
-        <v>126</v>
+        <v>1902</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3916,13 +3916,13 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46284.625</v>
+        <v>46294.625</v>
       </c>
       <c r="B158">
-        <v>194.142</v>
+        <v>1979.194</v>
       </c>
       <c r="C158">
-        <v>150</v>
+        <v>1922</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3933,13 +3933,13 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46284.63541666666</v>
+        <v>46294.63541666666</v>
       </c>
       <c r="B159">
-        <v>199.125</v>
+        <v>1953.875</v>
       </c>
       <c r="C159">
-        <v>187</v>
+        <v>1957</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3950,13 +3950,13 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46284.64583333334</v>
+        <v>46294.64583333334</v>
       </c>
       <c r="B160">
-        <v>203.939</v>
+        <v>1928.175</v>
       </c>
       <c r="C160">
-        <v>243</v>
+        <v>1923</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3967,13 +3967,13 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46284.65625</v>
+        <v>46294.65625</v>
       </c>
       <c r="B161">
-        <v>207.994</v>
+        <v>1902.75</v>
       </c>
       <c r="C161">
-        <v>272</v>
+        <v>1822</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3984,13 +3984,13 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46284.66666666666</v>
+        <v>46294.66666666666</v>
       </c>
       <c r="B162">
-        <v>211.494</v>
+        <v>1891.055</v>
       </c>
       <c r="C162">
-        <v>304</v>
+        <v>1634</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -4001,13 +4001,13 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46284.67708333334</v>
+        <v>46294.67708333334</v>
       </c>
       <c r="B163">
-        <v>217.355</v>
+        <v>1834.846</v>
       </c>
       <c r="C163">
-        <v>311</v>
+        <v>1535</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -4018,13 +4018,13 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46284.6875</v>
+        <v>46294.6875</v>
       </c>
       <c r="B164">
-        <v>222.347</v>
+        <v>1778.335</v>
       </c>
       <c r="C164">
-        <v>296</v>
+        <v>1364</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -4035,13 +4035,13 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46284.69791666666</v>
+        <v>46294.69791666666</v>
       </c>
       <c r="B165">
-        <v>227.444</v>
+        <v>1724.477</v>
       </c>
       <c r="C165">
-        <v>291</v>
+        <v>1209</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -4052,13 +4052,13 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46284.70833333334</v>
+        <v>46294.70833333334</v>
       </c>
       <c r="B166">
-        <v>206.534</v>
+        <v>1705.142</v>
       </c>
       <c r="C166">
-        <v>293</v>
+        <v>1112</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -4069,13 +4069,13 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46284.71875</v>
+        <v>46294.71875</v>
       </c>
       <c r="B167">
-        <v>214.822</v>
+        <v>1675.82</v>
       </c>
       <c r="C167">
-        <v>277</v>
+        <v>1127</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -4086,13 +4086,13 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46284.72916666666</v>
+        <v>46294.72916666666</v>
       </c>
       <c r="B168">
-        <v>223.191</v>
+        <v>1649.761</v>
       </c>
       <c r="C168">
-        <v>262</v>
+        <v>1143</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -4103,13 +4103,13 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46284.73958333334</v>
+        <v>46294.73958333334</v>
       </c>
       <c r="B169">
-        <v>232.423</v>
+        <v>1625.342</v>
       </c>
       <c r="C169">
-        <v>254</v>
+        <v>1141</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -4120,13 +4120,13 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46284.75</v>
+        <v>46294.75</v>
       </c>
       <c r="B170">
-        <v>255.939</v>
+        <v>1578.937</v>
       </c>
       <c r="C170">
-        <v>271</v>
+        <v>1159</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -4137,13 +4137,13 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46284.76041666666</v>
+        <v>46294.76041666666</v>
       </c>
       <c r="B171">
-        <v>267.597</v>
+        <v>1559.375</v>
       </c>
       <c r="C171">
-        <v>287</v>
+        <v>1194</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -4154,13 +4154,13 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46284.77083333334</v>
+        <v>46294.77083333334</v>
       </c>
       <c r="B172">
-        <v>278.714</v>
+        <v>1540.581</v>
       </c>
       <c r="C172">
-        <v>309</v>
+        <v>1251</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -4171,13 +4171,13 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46284.78125</v>
+        <v>46294.78125</v>
       </c>
       <c r="B173">
-        <v>291.104</v>
+        <v>1523.97</v>
       </c>
       <c r="C173">
-        <v>320</v>
+        <v>1322</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -4188,13 +4188,13 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46284.79166666666</v>
+        <v>46294.79166666666</v>
       </c>
       <c r="B174">
-        <v>300.776</v>
+        <v>1530.774</v>
       </c>
       <c r="C174">
-        <v>332</v>
+        <v>1394</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -4205,13 +4205,13 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46284.80208333334</v>
+        <v>46294.80208333334</v>
       </c>
       <c r="B175">
-        <v>304.849</v>
+        <v>1540.839</v>
       </c>
       <c r="C175">
-        <v>348</v>
+        <v>1494</v>
       </c>
       <c r="D175">
         <v>78</v>
@@ -4222,13 +4222,13 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46284.8125</v>
+        <v>46294.8125</v>
       </c>
       <c r="B176">
-        <v>309.139</v>
+        <v>1550.608</v>
       </c>
       <c r="C176">
-        <v>363</v>
+        <v>1569</v>
       </c>
       <c r="D176">
         <v>79</v>
@@ -4239,13 +4239,13 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46284.82291666666</v>
+        <v>46294.82291666666</v>
       </c>
       <c r="B177">
-        <v>313.214</v>
+        <v>1560.332</v>
       </c>
       <c r="C177">
-        <v>375</v>
+        <v>1673</v>
       </c>
       <c r="D177">
         <v>80</v>
@@ -4256,13 +4256,13 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46284.83333333334</v>
+        <v>46294.83333333334</v>
       </c>
       <c r="B178">
-        <v>347.977</v>
+        <v>1579.783</v>
       </c>
       <c r="C178">
-        <v>363</v>
+        <v>1754</v>
       </c>
       <c r="D178">
         <v>81</v>
@@ -4273,13 +4273,13 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46284.84375</v>
+        <v>46294.84375</v>
       </c>
       <c r="B179">
-        <v>344.787</v>
+        <v>1604.135</v>
       </c>
       <c r="C179">
-        <v>350</v>
+        <v>1811</v>
       </c>
       <c r="D179">
         <v>82</v>
@@ -4290,13 +4290,13 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46284.85416666666</v>
+        <v>46294.85416666666</v>
       </c>
       <c r="B180">
-        <v>341.156</v>
+        <v>1628.061</v>
       </c>
       <c r="C180">
-        <v>341</v>
+        <v>1855</v>
       </c>
       <c r="D180">
         <v>83</v>
@@ -4307,13 +4307,13 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46284.86458333334</v>
+        <v>46294.86458333334</v>
       </c>
       <c r="B181">
-        <v>338.552</v>
+        <v>1650.98</v>
       </c>
       <c r="C181">
-        <v>307</v>
+        <v>1898</v>
       </c>
       <c r="D181">
         <v>84</v>
@@ -4324,13 +4324,13 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46284.875</v>
+        <v>46294.875</v>
       </c>
       <c r="B182">
-        <v>299.158</v>
+        <v>1667.843</v>
       </c>
       <c r="C182">
-        <v>277</v>
+        <v>1962</v>
       </c>
       <c r="D182">
         <v>85</v>
@@ -4341,13 +4341,13 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46284.88541666666</v>
+        <v>46294.88541666666</v>
       </c>
       <c r="B183">
-        <v>291.112</v>
+        <v>1711.247</v>
       </c>
       <c r="C183">
-        <v>252</v>
+        <v>2049</v>
       </c>
       <c r="D183">
         <v>86</v>
@@ -4358,13 +4358,13 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46284.89583333334</v>
+        <v>46294.89583333334</v>
       </c>
       <c r="B184">
-        <v>282.979</v>
+        <v>1753.316</v>
       </c>
       <c r="C184">
-        <v>245</v>
+        <v>2120</v>
       </c>
       <c r="D184">
         <v>87</v>
@@ -4375,13 +4375,13 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46284.90625</v>
+        <v>46294.90625</v>
       </c>
       <c r="B185">
-        <v>274.406</v>
+        <v>1797.201</v>
       </c>
       <c r="C185">
-        <v>239</v>
+        <v>2180</v>
       </c>
       <c r="D185">
         <v>88</v>
@@ -4392,13 +4392,13 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46284.91666666666</v>
+        <v>46294.91666666666</v>
       </c>
       <c r="B186">
-        <v>260.272</v>
+        <v>1843.622</v>
       </c>
       <c r="C186">
-        <v>223</v>
+        <v>2263</v>
       </c>
       <c r="D186">
         <v>89</v>
@@ -4409,13 +4409,13 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46284.92708333334</v>
+        <v>46294.92708333334</v>
       </c>
       <c r="B187">
-        <v>246.843</v>
+        <v>1876.165</v>
       </c>
       <c r="C187">
-        <v>204</v>
+        <v>2335</v>
       </c>
       <c r="D187">
         <v>90</v>
@@ -4426,13 +4426,13 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46284.9375</v>
+        <v>46294.9375</v>
       </c>
       <c r="B188">
-        <v>231.092</v>
+        <v>1911.282</v>
       </c>
       <c r="C188">
-        <v>178</v>
+        <v>2391</v>
       </c>
       <c r="D188">
         <v>91</v>
@@ -4443,13 +4443,13 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46284.94791666666</v>
+        <v>46294.94791666666</v>
       </c>
       <c r="B189">
-        <v>217.87</v>
+        <v>1946.201</v>
       </c>
       <c r="C189">
-        <v>159</v>
+        <v>2446</v>
       </c>
       <c r="D189">
         <v>92</v>
@@ -4460,13 +4460,13 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46284.95833333334</v>
+        <v>46294.95833333334</v>
       </c>
       <c r="B190">
-        <v>208.595</v>
+        <v>2140.719</v>
       </c>
       <c r="C190">
-        <v>136</v>
+        <v>2443</v>
       </c>
       <c r="D190">
         <v>93</v>
@@ -4477,13 +4477,13 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46284.96875</v>
+        <v>46294.96875</v>
       </c>
       <c r="B191">
-        <v>198.044</v>
+        <v>2168.914</v>
       </c>
       <c r="C191">
-        <v>98</v>
+        <v>2442</v>
       </c>
       <c r="D191">
         <v>94</v>
@@ -4494,13 +4494,13 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46284.97916666666</v>
+        <v>46294.97916666666</v>
       </c>
       <c r="B192">
-        <v>186.12</v>
+        <v>2189.252</v>
       </c>
       <c r="C192">
-        <v>68</v>
+        <v>2412</v>
       </c>
       <c r="D192">
         <v>95</v>
@@ -4511,13 +4511,13 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46284.98958333334</v>
+        <v>46294.98958333334</v>
       </c>
       <c r="B193">
-        <v>177.525</v>
+        <v>2206.647</v>
       </c>
       <c r="C193">
-        <v>44</v>
+        <v>2351</v>
       </c>
       <c r="D193">
         <v>96</v>
@@ -4528,13 +4528,13 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="2">
-        <v>46285</v>
+        <v>46295</v>
       </c>
       <c r="B194">
-        <v>136.157</v>
+        <v>2172.625</v>
       </c>
       <c r="C194">
-        <v>23</v>
+        <v>2329</v>
       </c>
       <c r="D194">
         <v>1</v>
@@ -4545,13 +4545,13 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="2">
-        <v>46285.01041666666</v>
+        <v>46295.01041666666</v>
       </c>
       <c r="B195">
-        <v>129.864</v>
+        <v>2181.188</v>
       </c>
       <c r="C195">
-        <v>15</v>
+        <v>2344</v>
       </c>
       <c r="D195">
         <v>2</v>
@@ -4562,13 +4562,13 @@
     </row>
     <row r="196" spans="1:5">
       <c r="A196" s="2">
-        <v>46285.02083333334</v>
+        <v>46295.02083333334</v>
       </c>
       <c r="B196">
-        <v>123.973</v>
+        <v>2185.609</v>
       </c>
       <c r="C196">
-        <v>6</v>
+        <v>2321</v>
       </c>
       <c r="D196">
         <v>3</v>
@@ -4579,13 +4579,13 @@
     </row>
     <row r="197" spans="1:5">
       <c r="A197" s="2">
-        <v>46285.03125</v>
+        <v>46295.03125</v>
       </c>
       <c r="B197">
-        <v>118.956</v>
+        <v>2184.25</v>
       </c>
       <c r="C197">
-        <v>10</v>
+        <v>2285</v>
       </c>
       <c r="D197">
         <v>4</v>
@@ -4596,13 +4596,13 @@
     </row>
     <row r="198" spans="1:5">
       <c r="A198" s="2">
-        <v>46285.04166666666</v>
+        <v>46295.04166666666</v>
       </c>
       <c r="B198">
-        <v>112.728</v>
+        <v>2163.034</v>
       </c>
       <c r="C198">
-        <v>11</v>
+        <v>2237</v>
       </c>
       <c r="D198">
         <v>5</v>
@@ -4613,13 +4613,13 @@
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="2">
-        <v>46285.05208333334</v>
+        <v>46295.05208333334</v>
       </c>
       <c r="B199">
-        <v>110.881</v>
+        <v>2147.183</v>
       </c>
       <c r="C199">
-        <v>7</v>
+        <v>2183</v>
       </c>
       <c r="D199">
         <v>6</v>
@@ -4630,13 +4630,13 @@
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="2">
-        <v>46285.0625</v>
+        <v>46295.0625</v>
       </c>
       <c r="B200">
-        <v>110.116</v>
+        <v>2141.824</v>
       </c>
       <c r="C200">
-        <v>11</v>
+        <v>2129</v>
       </c>
       <c r="D200">
         <v>7</v>
@@ -4647,13 +4647,13 @@
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="2">
-        <v>46285.07291666666</v>
+        <v>46295.07291666666</v>
       </c>
       <c r="B201">
-        <v>108.268</v>
+        <v>2139.716</v>
       </c>
       <c r="C201">
-        <v>8</v>
+        <v>2102</v>
       </c>
       <c r="D201">
         <v>8</v>
@@ -4664,13 +4664,13 @@
     </row>
     <row r="202" spans="1:5">
       <c r="A202" s="2">
-        <v>46285.08333333334</v>
+        <v>46295.08333333334</v>
       </c>
       <c r="B202">
-        <v>115.442</v>
+        <v>2113.373</v>
       </c>
       <c r="C202">
-        <v>5</v>
+        <v>2092</v>
       </c>
       <c r="D202">
         <v>9</v>
@@ -4681,13 +4681,13 @@
     </row>
     <row r="203" spans="1:5">
       <c r="A203" s="2">
-        <v>46285.09375</v>
+        <v>46295.09375</v>
       </c>
       <c r="B203">
-        <v>114.648</v>
+        <v>2099.738</v>
       </c>
       <c r="C203">
-        <v>3</v>
+        <v>2077</v>
       </c>
       <c r="D203">
         <v>10</v>
@@ -4698,13 +4698,13 @@
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="2">
-        <v>46285.10416666666</v>
+        <v>46295.10416666666</v>
       </c>
       <c r="B204">
-        <v>114.395</v>
+        <v>2083.369</v>
       </c>
       <c r="C204">
-        <v>14</v>
+        <v>2069</v>
       </c>
       <c r="D204">
         <v>11</v>
@@ -4715,13 +4715,13 @@
     </row>
     <row r="205" spans="1:5">
       <c r="A205" s="2">
-        <v>46285.11458333334</v>
+        <v>46295.11458333334</v>
       </c>
       <c r="B205">
-        <v>113.536</v>
+        <v>2076.811</v>
       </c>
       <c r="C205">
-        <v>26</v>
+        <v>2045</v>
       </c>
       <c r="D205">
         <v>12</v>
@@ -4732,13 +4732,13 @@
     </row>
     <row r="206" spans="1:5">
       <c r="A206" s="2">
-        <v>46285.125</v>
+        <v>46295.125</v>
       </c>
       <c r="B206">
-        <v>115.019</v>
+        <v>2070.715</v>
       </c>
       <c r="C206">
-        <v>44</v>
+        <v>2012</v>
       </c>
       <c r="D206">
         <v>13</v>
@@ -4749,13 +4749,13 @@
     </row>
     <row r="207" spans="1:5">
       <c r="A207" s="2">
-        <v>46285.13541666666</v>
+        <v>46295.13541666666</v>
       </c>
       <c r="B207">
-        <v>115.215</v>
+        <v>2056.833</v>
       </c>
       <c r="C207">
-        <v>69</v>
+        <v>1973</v>
       </c>
       <c r="D207">
         <v>14</v>
@@ -4766,13 +4766,13 @@
     </row>
     <row r="208" spans="1:5">
       <c r="A208" s="2">
-        <v>46285.14583333334</v>
+        <v>46295.14583333334</v>
       </c>
       <c r="B208">
-        <v>115.141</v>
+        <v>2041.448</v>
       </c>
       <c r="C208">
-        <v>86</v>
+        <v>1929</v>
       </c>
       <c r="D208">
         <v>15</v>
@@ -4783,13 +4783,13 @@
     </row>
     <row r="209" spans="1:5">
       <c r="A209" s="2">
-        <v>46285.15625</v>
+        <v>46295.15625</v>
       </c>
       <c r="B209">
-        <v>115.653</v>
+        <v>2018.034</v>
       </c>
       <c r="C209">
-        <v>102</v>
+        <v>1875</v>
       </c>
       <c r="D209">
         <v>16</v>
@@ -4800,13 +4800,13 @@
     </row>
     <row r="210" spans="1:5">
       <c r="A210" s="2">
-        <v>46285.16666666666</v>
+        <v>46295.16666666666</v>
       </c>
       <c r="B210">
-        <v>112.199</v>
+        <v>1947.389</v>
       </c>
       <c r="C210">
-        <v>130</v>
+        <v>1853</v>
       </c>
       <c r="D210">
         <v>17</v>
@@ -4817,13 +4817,13 @@
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="2">
-        <v>46285.17708333334</v>
+        <v>46295.17708333334</v>
       </c>
       <c r="B211">
-        <v>111.285</v>
+        <v>1932.167</v>
       </c>
       <c r="C211">
-        <v>118</v>
+        <v>1852</v>
       </c>
       <c r="D211">
         <v>18</v>
@@ -4834,13 +4834,13 @@
     </row>
     <row r="212" spans="1:5">
       <c r="A212" s="2">
-        <v>46285.1875</v>
+        <v>46295.1875</v>
       </c>
       <c r="B212">
-        <v>110.193</v>
+        <v>1915.482</v>
       </c>
       <c r="C212">
-        <v>110</v>
+        <v>1876</v>
       </c>
       <c r="D212">
         <v>19</v>
@@ -4851,13 +4851,13 @@
     </row>
     <row r="213" spans="1:5">
       <c r="A213" s="2">
-        <v>46285.19791666666</v>
+        <v>46295.19791666666</v>
       </c>
       <c r="B213">
-        <v>109.56</v>
+        <v>1894.516</v>
       </c>
       <c r="C213">
-        <v>107</v>
+        <v>1903</v>
       </c>
       <c r="D213">
         <v>20</v>
@@ -4868,13 +4868,13 @@
     </row>
     <row r="214" spans="1:5">
       <c r="A214" s="2">
-        <v>46285.20833333334</v>
+        <v>46295.20833333334</v>
       </c>
       <c r="B214">
-        <v>108.32</v>
+        <v>1891.997</v>
       </c>
       <c r="C214">
-        <v>122</v>
+        <v>1876</v>
       </c>
       <c r="D214">
         <v>21</v>
@@ -4885,13 +4885,13 @@
     </row>
     <row r="215" spans="1:5">
       <c r="A215" s="2">
-        <v>46285.21875</v>
+        <v>46295.21875</v>
       </c>
       <c r="B215">
-        <v>107.529</v>
+        <v>1874.084</v>
       </c>
       <c r="C215">
-        <v>119</v>
+        <v>1853</v>
       </c>
       <c r="D215">
         <v>22</v>
@@ -4902,13 +4902,13 @@
     </row>
     <row r="216" spans="1:5">
       <c r="A216" s="2">
-        <v>46285.22916666666</v>
+        <v>46295.22916666666</v>
       </c>
       <c r="B216">
-        <v>105.641</v>
+        <v>1867.64</v>
       </c>
       <c r="C216">
-        <v>102</v>
+        <v>1824</v>
       </c>
       <c r="D216">
         <v>23</v>
@@ -4919,13 +4919,13 @@
     </row>
     <row r="217" spans="1:5">
       <c r="A217" s="2">
-        <v>46285.23958333334</v>
+        <v>46295.23958333334</v>
       </c>
       <c r="B217">
-        <v>103.73</v>
+        <v>1865.213</v>
       </c>
       <c r="C217">
-        <v>87</v>
+        <v>1808</v>
       </c>
       <c r="D217">
         <v>24</v>
@@ -4936,13 +4936,13 @@
     </row>
     <row r="218" spans="1:5">
       <c r="A218" s="2">
-        <v>46285.25</v>
+        <v>46295.25</v>
       </c>
       <c r="B218">
-        <v>106.586</v>
+        <v>1860.216</v>
       </c>
       <c r="C218">
-        <v>72</v>
+        <v>1796</v>
       </c>
       <c r="D218">
         <v>25</v>
@@ -4953,13 +4953,13 @@
     </row>
     <row r="219" spans="1:5">
       <c r="A219" s="2">
-        <v>46285.26041666666</v>
+        <v>46295.26041666666</v>
       </c>
       <c r="B219">
-        <v>103.854</v>
+        <v>1847.021</v>
       </c>
       <c r="C219">
-        <v>60</v>
+        <v>1773</v>
       </c>
       <c r="D219">
         <v>26</v>
@@ -4970,13 +4970,13 @@
     </row>
     <row r="220" spans="1:5">
       <c r="A220" s="2">
-        <v>46285.27083333334</v>
+        <v>46295.27083333334</v>
       </c>
       <c r="B220">
-        <v>101.672</v>
+        <v>1856.64</v>
       </c>
       <c r="C220">
-        <v>50</v>
+        <v>1747</v>
       </c>
       <c r="D220">
         <v>27</v>
@@ -4987,13 +4987,13 @@
     </row>
     <row r="221" spans="1:5">
       <c r="A221" s="2">
-        <v>46285.28125</v>
+        <v>46295.28125</v>
       </c>
       <c r="B221">
-        <v>88.843</v>
+        <v>1840.933</v>
       </c>
       <c r="C221">
-        <v>41</v>
+        <v>1697</v>
       </c>
       <c r="D221">
         <v>28</v>
@@ -5004,13 +5004,13 @@
     </row>
     <row r="222" spans="1:5">
       <c r="A222" s="2">
-        <v>46285.29166666666</v>
+        <v>46295.29166666666</v>
       </c>
       <c r="B222">
-        <v>101.673</v>
+        <v>1836.052</v>
       </c>
       <c r="C222">
-        <v>29</v>
+        <v>1602</v>
       </c>
       <c r="D222">
         <v>29</v>
@@ -5021,13 +5021,13 @@
     </row>
     <row r="223" spans="1:5">
       <c r="A223" s="2">
-        <v>46285.30208333334</v>
+        <v>46295.30208333334</v>
       </c>
       <c r="B223">
-        <v>91.491</v>
+        <v>1803.743</v>
       </c>
       <c r="C223">
-        <v>21</v>
+        <v>1490</v>
       </c>
       <c r="D223">
         <v>30</v>
@@ -5038,13 +5038,13 @@
     </row>
     <row r="224" spans="1:5">
       <c r="A224" s="2">
-        <v>46285.3125</v>
+        <v>46295.3125</v>
       </c>
       <c r="B224">
-        <v>90.738</v>
+        <v>1757.275</v>
       </c>
       <c r="C224">
-        <v>18</v>
+        <v>1318</v>
       </c>
       <c r="D224">
         <v>31</v>
@@ -5055,13 +5055,13 @@
     </row>
     <row r="225" spans="1:5">
       <c r="A225" s="2">
-        <v>46285.32291666666</v>
+        <v>46295.32291666666</v>
       </c>
       <c r="B225">
-        <v>90.499</v>
+        <v>1711.197</v>
       </c>
       <c r="C225">
-        <v>8</v>
+        <v>1159</v>
       </c>
       <c r="D225">
         <v>32</v>
@@ -5072,13 +5072,13 @@
     </row>
     <row r="226" spans="1:5">
       <c r="A226" s="2">
-        <v>46285.33333333334</v>
+        <v>46295.33333333334</v>
       </c>
       <c r="B226">
-        <v>90.29300000000001</v>
+        <v>1602.262</v>
       </c>
       <c r="C226">
-        <v>0</v>
+        <v>1015</v>
       </c>
       <c r="D226">
         <v>33</v>
@@ -5089,10 +5089,13 @@
     </row>
     <row r="227" spans="1:5">
       <c r="A227" s="2">
-        <v>46285.34375</v>
+        <v>46295.34375</v>
       </c>
       <c r="B227">
-        <v>90.854</v>
+        <v>1563.826</v>
+      </c>
+      <c r="C227">
+        <v>1017</v>
       </c>
       <c r="D227">
         <v>34</v>
@@ -5103,10 +5106,13 @@
     </row>
     <row r="228" spans="1:5">
       <c r="A228" s="2">
-        <v>46285.35416666666</v>
+        <v>46295.35416666666</v>
       </c>
       <c r="B228">
-        <v>86.83199999999999</v>
+        <v>1539.275</v>
+      </c>
+      <c r="C228">
+        <v>976</v>
       </c>
       <c r="D228">
         <v>35</v>
@@ -5117,10 +5123,13 @@
     </row>
     <row r="229" spans="1:5">
       <c r="A229" s="2">
-        <v>46285.36458333334</v>
+        <v>46295.36458333334</v>
       </c>
       <c r="B229">
-        <v>84.92400000000001</v>
+        <v>1520.451</v>
+      </c>
+      <c r="C229">
+        <v>961</v>
       </c>
       <c r="D229">
         <v>36</v>
@@ -5131,10 +5140,13 @@
     </row>
     <row r="230" spans="1:5">
       <c r="A230" s="2">
-        <v>46285.375</v>
+        <v>46295.375</v>
       </c>
       <c r="B230">
-        <v>84.988</v>
+        <v>1606.825</v>
+      </c>
+      <c r="C230">
+        <v>980</v>
       </c>
       <c r="D230">
         <v>37</v>
@@ -5145,10 +5157,13 @@
     </row>
     <row r="231" spans="1:5">
       <c r="A231" s="2">
-        <v>46285.38541666666</v>
+        <v>46295.38541666666</v>
       </c>
       <c r="B231">
-        <v>84.952</v>
+        <v>1605.192</v>
+      </c>
+      <c r="C231">
+        <v>1087</v>
       </c>
       <c r="D231">
         <v>38</v>
@@ -5159,10 +5174,13 @@
     </row>
     <row r="232" spans="1:5">
       <c r="A232" s="2">
-        <v>46285.39583333334</v>
+        <v>46295.39583333334</v>
       </c>
       <c r="B232">
-        <v>84.91800000000001</v>
+        <v>1617.596</v>
+      </c>
+      <c r="C232">
+        <v>1232</v>
       </c>
       <c r="D232">
         <v>39</v>
@@ -5173,10 +5191,10 @@
     </row>
     <row r="233" spans="1:5">
       <c r="A233" s="2">
-        <v>46285.40625</v>
+        <v>46295.40625</v>
       </c>
       <c r="B233">
-        <v>83.822</v>
+        <v>1633.477</v>
       </c>
       <c r="D233">
         <v>40</v>
@@ -5187,10 +5205,10 @@
     </row>
     <row r="234" spans="1:5">
       <c r="A234" s="2">
-        <v>46285.41666666666</v>
+        <v>46295.41666666666</v>
       </c>
       <c r="B234">
-        <v>89.163</v>
+        <v>1668.897</v>
       </c>
       <c r="D234">
         <v>41</v>
@@ -5201,10 +5219,10 @@
     </row>
     <row r="235" spans="1:5">
       <c r="A235" s="2">
-        <v>46285.42708333334</v>
+        <v>46295.42708333334</v>
       </c>
       <c r="B235">
-        <v>89.744</v>
+        <v>1701.437</v>
       </c>
       <c r="D235">
         <v>42</v>
@@ -5215,10 +5233,10 @@
     </row>
     <row r="236" spans="1:5">
       <c r="A236" s="2">
-        <v>46285.4375</v>
+        <v>46295.4375</v>
       </c>
       <c r="B236">
-        <v>90.88800000000001</v>
+        <v>1735.653</v>
       </c>
       <c r="D236">
         <v>43</v>
@@ -5229,10 +5247,10 @@
     </row>
     <row r="237" spans="1:5">
       <c r="A237" s="2">
-        <v>46285.44791666666</v>
+        <v>46295.44791666666</v>
       </c>
       <c r="B237">
-        <v>91.866</v>
+        <v>1767.671</v>
       </c>
       <c r="D237">
         <v>44</v>
@@ -5243,10 +5261,10 @@
     </row>
     <row r="238" spans="1:5">
       <c r="A238" s="2">
-        <v>46285.45833333334</v>
+        <v>46295.45833333334</v>
       </c>
       <c r="B238">
-        <v>87.265</v>
+        <v>1789.801</v>
       </c>
       <c r="D238">
         <v>45</v>
@@ -5257,10 +5275,10 @@
     </row>
     <row r="239" spans="1:5">
       <c r="A239" s="2">
-        <v>46285.46875</v>
+        <v>46295.46875</v>
       </c>
       <c r="B239">
-        <v>88.42700000000001</v>
+        <v>1791.689</v>
       </c>
       <c r="D239">
         <v>46</v>
@@ -5271,10 +5289,10 @@
     </row>
     <row r="240" spans="1:5">
       <c r="A240" s="2">
-        <v>46285.47916666666</v>
+        <v>46295.47916666666</v>
       </c>
       <c r="B240">
-        <v>89.553</v>
+        <v>1792.339</v>
       </c>
       <c r="D240">
         <v>47</v>
@@ -5285,10 +5303,10 @@
     </row>
     <row r="241" spans="1:5">
       <c r="A241" s="2">
-        <v>46285.48958333334</v>
+        <v>46295.48958333334</v>
       </c>
       <c r="B241">
-        <v>90.792</v>
+        <v>1794.777</v>
       </c>
       <c r="D241">
         <v>48</v>
@@ -5299,10 +5317,10 @@
     </row>
     <row r="242" spans="1:5">
       <c r="A242" s="2">
-        <v>46285.5</v>
+        <v>46295.5</v>
       </c>
       <c r="B242">
-        <v>92.863</v>
+        <v>1801.897</v>
       </c>
       <c r="D242">
         <v>49</v>
@@ -5313,10 +5331,10 @@
     </row>
     <row r="243" spans="1:5">
       <c r="A243" s="2">
-        <v>46285.51041666666</v>
+        <v>46295.51041666666</v>
       </c>
       <c r="B243">
-        <v>94.08499999999999</v>
+        <v>1791.921</v>
       </c>
       <c r="D243">
         <v>50</v>
@@ -5327,10 +5345,10 @@
     </row>
     <row r="244" spans="1:5">
       <c r="A244" s="2">
-        <v>46285.52083333334</v>
+        <v>46295.52083333334</v>
       </c>
       <c r="B244">
-        <v>95.732</v>
+        <v>1779.033</v>
       </c>
       <c r="D244">
         <v>51</v>
@@ -5341,10 +5359,10 @@
     </row>
     <row r="245" spans="1:5">
       <c r="A245" s="2">
-        <v>46285.53125</v>
+        <v>46295.53125</v>
       </c>
       <c r="B245">
-        <v>98.173</v>
+        <v>1762.108</v>
       </c>
       <c r="D245">
         <v>52</v>
@@ -5355,10 +5373,10 @@
     </row>
     <row r="246" spans="1:5">
       <c r="A246" s="2">
-        <v>46285.54166666666</v>
+        <v>46295.54166666666</v>
       </c>
       <c r="B246">
-        <v>99.09</v>
+        <v>1734.363</v>
       </c>
       <c r="D246">
         <v>53</v>
@@ -5369,10 +5387,10 @@
     </row>
     <row r="247" spans="1:5">
       <c r="A247" s="2">
-        <v>46285.55208333334</v>
+        <v>46295.55208333334</v>
       </c>
       <c r="B247">
-        <v>101.799</v>
+        <v>1722.668</v>
       </c>
       <c r="D247">
         <v>54</v>
@@ -5383,10 +5401,10 @@
     </row>
     <row r="248" spans="1:5">
       <c r="A248" s="2">
-        <v>46285.5625</v>
+        <v>46295.5625</v>
       </c>
       <c r="B248">
-        <v>104.625</v>
+        <v>1711.41</v>
       </c>
       <c r="D248">
         <v>55</v>
@@ -5397,10 +5415,10 @@
     </row>
     <row r="249" spans="1:5">
       <c r="A249" s="2">
-        <v>46285.57291666666</v>
+        <v>46295.57291666666</v>
       </c>
       <c r="B249">
-        <v>107.715</v>
+        <v>1700.932</v>
       </c>
       <c r="D249">
         <v>56</v>
@@ -5411,10 +5429,10 @@
     </row>
     <row r="250" spans="1:5">
       <c r="A250" s="2">
-        <v>46285.58333333334</v>
+        <v>46295.58333333334</v>
       </c>
       <c r="B250">
-        <v>113.95</v>
+        <v>1695.419</v>
       </c>
       <c r="D250">
         <v>57</v>
@@ -5425,10 +5443,10 @@
     </row>
     <row r="251" spans="1:5">
       <c r="A251" s="2">
-        <v>46285.59375</v>
+        <v>46295.59375</v>
       </c>
       <c r="B251">
-        <v>117.698</v>
+        <v>1686.035</v>
       </c>
       <c r="D251">
         <v>58</v>
@@ -5439,10 +5457,10 @@
     </row>
     <row r="252" spans="1:5">
       <c r="A252" s="2">
-        <v>46285.60416666666</v>
+        <v>46295.60416666666</v>
       </c>
       <c r="B252">
-        <v>121.817</v>
+        <v>1675.828</v>
       </c>
       <c r="D252">
         <v>59</v>
@@ -5453,10 +5471,10 @@
     </row>
     <row r="253" spans="1:5">
       <c r="A253" s="2">
-        <v>46285.61458333334</v>
+        <v>46295.61458333334</v>
       </c>
       <c r="B253">
-        <v>125.69</v>
+        <v>1666.704</v>
       </c>
       <c r="D253">
         <v>60</v>
@@ -5467,10 +5485,10 @@
     </row>
     <row r="254" spans="1:5">
       <c r="A254" s="2">
-        <v>46285.625</v>
+        <v>46295.625</v>
       </c>
       <c r="B254">
-        <v>131.411</v>
+        <v>1632.653</v>
       </c>
       <c r="D254">
         <v>61</v>
@@ -5481,10 +5499,10 @@
     </row>
     <row r="255" spans="1:5">
       <c r="A255" s="2">
-        <v>46285.63541666666</v>
+        <v>46295.63541666666</v>
       </c>
       <c r="B255">
-        <v>136.357</v>
+        <v>1612.646</v>
       </c>
       <c r="D255">
         <v>62</v>
@@ -5495,10 +5513,10 @@
     </row>
     <row r="256" spans="1:5">
       <c r="A256" s="2">
-        <v>46285.64583333334</v>
+        <v>46295.64583333334</v>
       </c>
       <c r="B256">
-        <v>143.974</v>
+        <v>1592.616</v>
       </c>
       <c r="D256">
         <v>63</v>
@@ -5509,10 +5527,10 @@
     </row>
     <row r="257" spans="1:5">
       <c r="A257" s="2">
-        <v>46285.65625</v>
+        <v>46295.65625</v>
       </c>
       <c r="B257">
-        <v>149.552</v>
+        <v>1571.786</v>
       </c>
       <c r="D257">
         <v>64</v>
@@ -5523,10 +5541,10 @@
     </row>
     <row r="258" spans="1:5">
       <c r="A258" s="2">
-        <v>46285.66666666666</v>
+        <v>46295.66666666666</v>
       </c>
       <c r="B258">
-        <v>152.923</v>
+        <v>1521.933</v>
       </c>
       <c r="D258">
         <v>65</v>
@@ -5537,10 +5555,10 @@
     </row>
     <row r="259" spans="1:5">
       <c r="A259" s="2">
-        <v>46285.67708333334</v>
+        <v>46295.67708333334</v>
       </c>
       <c r="B259">
-        <v>157.947</v>
+        <v>1475.39</v>
       </c>
       <c r="D259">
         <v>66</v>
@@ -5551,10 +5569,10 @@
     </row>
     <row r="260" spans="1:5">
       <c r="A260" s="2">
-        <v>46285.6875</v>
+        <v>46295.6875</v>
       </c>
       <c r="B260">
-        <v>163.08</v>
+        <v>1425.059</v>
       </c>
       <c r="D260">
         <v>67</v>
@@ -5565,10 +5583,10 @@
     </row>
     <row r="261" spans="1:5">
       <c r="A261" s="2">
-        <v>46285.69791666666</v>
+        <v>46295.69791666666</v>
       </c>
       <c r="B261">
-        <v>168.567</v>
+        <v>1375.403</v>
       </c>
       <c r="D261">
         <v>68</v>
@@ -5579,10 +5597,10 @@
     </row>
     <row r="262" spans="1:5">
       <c r="A262" s="2">
-        <v>46285.70833333334</v>
+        <v>46295.70833333334</v>
       </c>
       <c r="B262">
-        <v>154.486</v>
+        <v>1250.616</v>
       </c>
       <c r="D262">
         <v>69</v>
@@ -5593,10 +5611,10 @@
     </row>
     <row r="263" spans="1:5">
       <c r="A263" s="2">
-        <v>46285.71875</v>
+        <v>46295.71875</v>
       </c>
       <c r="B263">
-        <v>163.704</v>
+        <v>1218.031</v>
       </c>
       <c r="D263">
         <v>70</v>
@@ -5607,10 +5625,10 @@
     </row>
     <row r="264" spans="1:5">
       <c r="A264" s="2">
-        <v>46285.72916666666</v>
+        <v>46295.72916666666</v>
       </c>
       <c r="B264">
-        <v>173.41</v>
+        <v>1187.421</v>
       </c>
       <c r="D264">
         <v>71</v>
@@ -5621,10 +5639,10 @@
     </row>
     <row r="265" spans="1:5">
       <c r="A265" s="2">
-        <v>46285.73958333334</v>
+        <v>46295.73958333334</v>
       </c>
       <c r="B265">
-        <v>183.218</v>
+        <v>1161.974</v>
       </c>
       <c r="D265">
         <v>72</v>
@@ -5635,10 +5653,10 @@
     </row>
     <row r="266" spans="1:5">
       <c r="A266" s="2">
-        <v>46285.75</v>
+        <v>46295.75</v>
       </c>
       <c r="B266">
-        <v>199.834</v>
+        <v>1141.301</v>
       </c>
       <c r="D266">
         <v>73</v>
@@ -5649,10 +5667,10 @@
     </row>
     <row r="267" spans="1:5">
       <c r="A267" s="2">
-        <v>46285.76041666666</v>
+        <v>46295.76041666666</v>
       </c>
       <c r="B267">
-        <v>216.272</v>
+        <v>1138.113</v>
       </c>
       <c r="D267">
         <v>74</v>
@@ -5663,10 +5681,10 @@
     </row>
     <row r="268" spans="1:5">
       <c r="A268" s="2">
-        <v>46285.77083333334</v>
+        <v>46295.77083333334</v>
       </c>
       <c r="B268">
-        <v>232.127</v>
+        <v>1135.339</v>
       </c>
       <c r="D268">
         <v>75</v>
@@ -5677,10 +5695,10 @@
     </row>
     <row r="269" spans="1:5">
       <c r="A269" s="2">
-        <v>46285.78125</v>
+        <v>46295.78125</v>
       </c>
       <c r="B269">
-        <v>248.853</v>
+        <v>1129.314</v>
       </c>
       <c r="D269">
         <v>76</v>
@@ -5691,10 +5709,10 @@
     </row>
     <row r="270" spans="1:5">
       <c r="A270" s="2">
-        <v>46285.79166666666</v>
+        <v>46295.79166666666</v>
       </c>
       <c r="B270">
-        <v>270.62</v>
+        <v>1127.232</v>
       </c>
       <c r="D270">
         <v>77</v>
@@ -5705,10 +5723,10 @@
     </row>
     <row r="271" spans="1:5">
       <c r="A271" s="2">
-        <v>46285.80208333334</v>
+        <v>46295.80208333334</v>
       </c>
       <c r="B271">
-        <v>286.998</v>
+        <v>1135.236</v>
       </c>
       <c r="D271">
         <v>78</v>
@@ -5719,10 +5737,10 @@
     </row>
     <row r="272" spans="1:5">
       <c r="A272" s="2">
-        <v>46285.8125</v>
+        <v>46295.8125</v>
       </c>
       <c r="B272">
-        <v>302.263</v>
+        <v>1144.96</v>
       </c>
       <c r="D272">
         <v>79</v>
@@ -5733,10 +5751,10 @@
     </row>
     <row r="273" spans="1:5">
       <c r="A273" s="2">
-        <v>46285.82291666666</v>
+        <v>46295.82291666666</v>
       </c>
       <c r="B273">
-        <v>318.743</v>
+        <v>1154.996</v>
       </c>
       <c r="D273">
         <v>80</v>
@@ -5747,10 +5765,10 @@
     </row>
     <row r="274" spans="1:5">
       <c r="A274" s="2">
-        <v>46285.83333333334</v>
+        <v>46295.83333333334</v>
       </c>
       <c r="B274">
-        <v>338.755</v>
+        <v>1172.885</v>
       </c>
       <c r="D274">
         <v>81</v>
@@ -5761,10 +5779,10 @@
     </row>
     <row r="275" spans="1:5">
       <c r="A275" s="2">
-        <v>46285.84375</v>
+        <v>46295.84375</v>
       </c>
       <c r="B275">
-        <v>352.943</v>
+        <v>1182.145</v>
       </c>
       <c r="D275">
         <v>82</v>
@@ -5775,10 +5793,10 @@
     </row>
     <row r="276" spans="1:5">
       <c r="A276" s="2">
-        <v>46285.85416666666</v>
+        <v>46295.85416666666</v>
       </c>
       <c r="B276">
-        <v>369.06</v>
+        <v>1191.908</v>
       </c>
       <c r="D276">
         <v>83</v>
@@ -5789,10 +5807,10 @@
     </row>
     <row r="277" spans="1:5">
       <c r="A277" s="2">
-        <v>46285.86458333334</v>
+        <v>46295.86458333334</v>
       </c>
       <c r="B277">
-        <v>384.092</v>
+        <v>1201.264</v>
       </c>
       <c r="D277">
         <v>84</v>
@@ -5803,10 +5821,10 @@
     </row>
     <row r="278" spans="1:5">
       <c r="A278" s="2">
-        <v>46285.875</v>
+        <v>46295.875</v>
       </c>
       <c r="B278">
-        <v>397.976</v>
+        <v>1339.527</v>
       </c>
       <c r="D278">
         <v>85</v>
@@ -5817,10 +5835,10 @@
     </row>
     <row r="279" spans="1:5">
       <c r="A279" s="2">
-        <v>46285.88541666666</v>
+        <v>46295.88541666666</v>
       </c>
       <c r="B279">
-        <v>408.71</v>
+        <v>1367.562</v>
       </c>
       <c r="D279">
         <v>86</v>
@@ -5831,10 +5849,10 @@
     </row>
     <row r="280" spans="1:5">
       <c r="A280" s="2">
-        <v>46285.89583333334</v>
+        <v>46295.89583333334</v>
       </c>
       <c r="B280">
-        <v>419.024</v>
+        <v>1391.827</v>
       </c>
       <c r="D280">
         <v>87</v>
@@ -5845,10 +5863,10 @@
     </row>
     <row r="281" spans="1:5">
       <c r="A281" s="2">
-        <v>46285.90625</v>
+        <v>46295.90625</v>
       </c>
       <c r="B281">
-        <v>429.858</v>
+        <v>1415.457</v>
       </c>
       <c r="D281">
         <v>88</v>
@@ -5859,10 +5877,10 @@
     </row>
     <row r="282" spans="1:5">
       <c r="A282" s="2">
-        <v>46285.91666666666</v>
+        <v>46295.91666666666</v>
       </c>
       <c r="B282">
-        <v>437.478</v>
+        <v>1454.113</v>
       </c>
       <c r="D282">
         <v>89</v>
@@ -5873,10 +5891,10 @@
     </row>
     <row r="283" spans="1:5">
       <c r="A283" s="2">
-        <v>46285.92708333334</v>
+        <v>46295.92708333334</v>
       </c>
       <c r="B283">
-        <v>447.255</v>
+        <v>1491.151</v>
       </c>
       <c r="D283">
         <v>90</v>
@@ -5887,10 +5905,10 @@
     </row>
     <row r="284" spans="1:5">
       <c r="A284" s="2">
-        <v>46285.9375</v>
+        <v>46295.9375</v>
       </c>
       <c r="B284">
-        <v>457.858</v>
+        <v>1528.111</v>
       </c>
       <c r="D284">
         <v>91</v>
@@ -5901,10 +5919,10 @@
     </row>
     <row r="285" spans="1:5">
       <c r="A285" s="2">
-        <v>46285.94791666666</v>
+        <v>46295.94791666666</v>
       </c>
       <c r="B285">
-        <v>466.386</v>
+        <v>1560.86</v>
       </c>
       <c r="D285">
         <v>92</v>

--- a/data_fetching/Entsoe/Wind_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Wind_Production_Historical.xlsx
@@ -31,856 +31,856 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>28.09.20261</t>
-  </si>
-  <si>
-    <t>28.09.20262</t>
-  </si>
-  <si>
-    <t>28.09.20263</t>
-  </si>
-  <si>
-    <t>28.09.20264</t>
-  </si>
-  <si>
-    <t>28.09.20265</t>
-  </si>
-  <si>
-    <t>28.09.20266</t>
-  </si>
-  <si>
-    <t>28.09.20267</t>
-  </si>
-  <si>
-    <t>28.09.20268</t>
-  </si>
-  <si>
-    <t>28.09.20269</t>
-  </si>
-  <si>
-    <t>28.09.202610</t>
-  </si>
-  <si>
-    <t>28.09.202611</t>
-  </si>
-  <si>
-    <t>28.09.202612</t>
-  </si>
-  <si>
-    <t>28.09.202613</t>
-  </si>
-  <si>
-    <t>28.09.202614</t>
-  </si>
-  <si>
-    <t>28.09.202615</t>
-  </si>
-  <si>
-    <t>28.09.202616</t>
-  </si>
-  <si>
-    <t>28.09.202617</t>
-  </si>
-  <si>
-    <t>28.09.202618</t>
-  </si>
-  <si>
-    <t>28.09.202619</t>
-  </si>
-  <si>
-    <t>28.09.202620</t>
-  </si>
-  <si>
-    <t>28.09.202621</t>
-  </si>
-  <si>
-    <t>28.09.202622</t>
-  </si>
-  <si>
-    <t>28.09.202623</t>
-  </si>
-  <si>
-    <t>28.09.202624</t>
-  </si>
-  <si>
-    <t>28.09.202625</t>
-  </si>
-  <si>
-    <t>28.09.202626</t>
-  </si>
-  <si>
-    <t>28.09.202627</t>
-  </si>
-  <si>
-    <t>28.09.202628</t>
-  </si>
-  <si>
-    <t>28.09.202629</t>
-  </si>
-  <si>
-    <t>28.09.202630</t>
-  </si>
-  <si>
-    <t>28.09.202631</t>
-  </si>
-  <si>
-    <t>28.09.202632</t>
-  </si>
-  <si>
-    <t>28.09.202633</t>
-  </si>
-  <si>
-    <t>28.09.202634</t>
-  </si>
-  <si>
-    <t>28.09.202635</t>
-  </si>
-  <si>
-    <t>28.09.202636</t>
-  </si>
-  <si>
-    <t>28.09.202637</t>
-  </si>
-  <si>
-    <t>28.09.202638</t>
-  </si>
-  <si>
-    <t>28.09.202639</t>
-  </si>
-  <si>
-    <t>28.09.202640</t>
-  </si>
-  <si>
-    <t>28.09.202641</t>
-  </si>
-  <si>
-    <t>28.09.202642</t>
-  </si>
-  <si>
-    <t>28.09.202643</t>
-  </si>
-  <si>
-    <t>28.09.202644</t>
-  </si>
-  <si>
-    <t>28.09.202645</t>
-  </si>
-  <si>
-    <t>28.09.202646</t>
-  </si>
-  <si>
-    <t>28.09.202647</t>
-  </si>
-  <si>
-    <t>28.09.202648</t>
-  </si>
-  <si>
-    <t>28.09.202649</t>
-  </si>
-  <si>
-    <t>28.09.202650</t>
-  </si>
-  <si>
-    <t>28.09.202651</t>
-  </si>
-  <si>
-    <t>28.09.202652</t>
-  </si>
-  <si>
-    <t>28.09.202653</t>
-  </si>
-  <si>
-    <t>28.09.202654</t>
-  </si>
-  <si>
-    <t>28.09.202655</t>
-  </si>
-  <si>
-    <t>28.09.202656</t>
-  </si>
-  <si>
-    <t>28.09.202657</t>
-  </si>
-  <si>
-    <t>28.09.202658</t>
-  </si>
-  <si>
-    <t>28.09.202659</t>
-  </si>
-  <si>
-    <t>28.09.202660</t>
-  </si>
-  <si>
-    <t>28.09.202661</t>
-  </si>
-  <si>
-    <t>28.09.202662</t>
-  </si>
-  <si>
-    <t>28.09.202663</t>
-  </si>
-  <si>
-    <t>28.09.202664</t>
-  </si>
-  <si>
-    <t>28.09.202665</t>
-  </si>
-  <si>
-    <t>28.09.202666</t>
-  </si>
-  <si>
-    <t>28.09.202667</t>
-  </si>
-  <si>
-    <t>28.09.202668</t>
-  </si>
-  <si>
-    <t>28.09.202669</t>
-  </si>
-  <si>
-    <t>28.09.202670</t>
-  </si>
-  <si>
-    <t>28.09.202671</t>
-  </si>
-  <si>
-    <t>28.09.202672</t>
-  </si>
-  <si>
-    <t>28.09.202673</t>
-  </si>
-  <si>
-    <t>28.09.202674</t>
-  </si>
-  <si>
-    <t>28.09.202675</t>
-  </si>
-  <si>
-    <t>28.09.202676</t>
-  </si>
-  <si>
-    <t>28.09.202677</t>
-  </si>
-  <si>
-    <t>28.09.202678</t>
-  </si>
-  <si>
-    <t>28.09.202679</t>
-  </si>
-  <si>
-    <t>28.09.202680</t>
-  </si>
-  <si>
-    <t>28.09.202681</t>
-  </si>
-  <si>
-    <t>28.09.202682</t>
-  </si>
-  <si>
-    <t>28.09.202683</t>
-  </si>
-  <si>
-    <t>28.09.202684</t>
-  </si>
-  <si>
-    <t>28.09.202685</t>
-  </si>
-  <si>
-    <t>28.09.202686</t>
-  </si>
-  <si>
-    <t>28.09.202687</t>
-  </si>
-  <si>
-    <t>28.09.202688</t>
-  </si>
-  <si>
-    <t>28.09.202689</t>
-  </si>
-  <si>
-    <t>28.09.202690</t>
-  </si>
-  <si>
-    <t>28.09.202691</t>
-  </si>
-  <si>
-    <t>28.09.202692</t>
-  </si>
-  <si>
-    <t>28.09.202693</t>
-  </si>
-  <si>
-    <t>28.09.202694</t>
-  </si>
-  <si>
-    <t>28.09.202695</t>
-  </si>
-  <si>
-    <t>28.09.202696</t>
-  </si>
-  <si>
-    <t>29.09.20261</t>
-  </si>
-  <si>
-    <t>29.09.20262</t>
-  </si>
-  <si>
-    <t>29.09.20263</t>
-  </si>
-  <si>
-    <t>29.09.20264</t>
-  </si>
-  <si>
-    <t>29.09.20265</t>
-  </si>
-  <si>
-    <t>29.09.20266</t>
-  </si>
-  <si>
-    <t>29.09.20267</t>
-  </si>
-  <si>
-    <t>29.09.20268</t>
-  </si>
-  <si>
-    <t>29.09.20269</t>
-  </si>
-  <si>
-    <t>29.09.202610</t>
-  </si>
-  <si>
-    <t>29.09.202611</t>
-  </si>
-  <si>
-    <t>29.09.202612</t>
-  </si>
-  <si>
-    <t>29.09.202613</t>
-  </si>
-  <si>
-    <t>29.09.202614</t>
-  </si>
-  <si>
-    <t>29.09.202615</t>
-  </si>
-  <si>
-    <t>29.09.202616</t>
-  </si>
-  <si>
-    <t>29.09.202617</t>
-  </si>
-  <si>
-    <t>29.09.202618</t>
-  </si>
-  <si>
-    <t>29.09.202619</t>
-  </si>
-  <si>
-    <t>29.09.202620</t>
-  </si>
-  <si>
-    <t>29.09.202621</t>
-  </si>
-  <si>
-    <t>29.09.202622</t>
-  </si>
-  <si>
-    <t>29.09.202623</t>
-  </si>
-  <si>
-    <t>29.09.202624</t>
-  </si>
-  <si>
-    <t>29.09.202625</t>
-  </si>
-  <si>
-    <t>29.09.202626</t>
-  </si>
-  <si>
-    <t>29.09.202627</t>
-  </si>
-  <si>
-    <t>29.09.202628</t>
-  </si>
-  <si>
-    <t>29.09.202629</t>
-  </si>
-  <si>
-    <t>29.09.202630</t>
-  </si>
-  <si>
-    <t>29.09.202631</t>
-  </si>
-  <si>
-    <t>29.09.202632</t>
-  </si>
-  <si>
-    <t>29.09.202633</t>
-  </si>
-  <si>
-    <t>29.09.202634</t>
-  </si>
-  <si>
-    <t>29.09.202635</t>
-  </si>
-  <si>
-    <t>29.09.202636</t>
-  </si>
-  <si>
-    <t>29.09.202637</t>
-  </si>
-  <si>
-    <t>29.09.202638</t>
-  </si>
-  <si>
-    <t>29.09.202639</t>
-  </si>
-  <si>
-    <t>29.09.202640</t>
-  </si>
-  <si>
-    <t>29.09.202641</t>
-  </si>
-  <si>
-    <t>29.09.202642</t>
-  </si>
-  <si>
-    <t>29.09.202643</t>
-  </si>
-  <si>
-    <t>29.09.202644</t>
-  </si>
-  <si>
-    <t>29.09.202645</t>
-  </si>
-  <si>
-    <t>29.09.202646</t>
-  </si>
-  <si>
-    <t>29.09.202647</t>
-  </si>
-  <si>
-    <t>29.09.202648</t>
-  </si>
-  <si>
-    <t>29.09.202649</t>
-  </si>
-  <si>
-    <t>29.09.202650</t>
-  </si>
-  <si>
-    <t>29.09.202651</t>
-  </si>
-  <si>
-    <t>29.09.202652</t>
-  </si>
-  <si>
-    <t>29.09.202653</t>
-  </si>
-  <si>
-    <t>29.09.202654</t>
-  </si>
-  <si>
-    <t>29.09.202655</t>
-  </si>
-  <si>
-    <t>29.09.202656</t>
-  </si>
-  <si>
-    <t>29.09.202657</t>
-  </si>
-  <si>
-    <t>29.09.202658</t>
-  </si>
-  <si>
-    <t>29.09.202659</t>
-  </si>
-  <si>
-    <t>29.09.202660</t>
-  </si>
-  <si>
-    <t>29.09.202661</t>
-  </si>
-  <si>
-    <t>29.09.202662</t>
-  </si>
-  <si>
-    <t>29.09.202663</t>
-  </si>
-  <si>
-    <t>29.09.202664</t>
-  </si>
-  <si>
-    <t>29.09.202665</t>
-  </si>
-  <si>
-    <t>29.09.202666</t>
-  </si>
-  <si>
-    <t>29.09.202667</t>
-  </si>
-  <si>
-    <t>29.09.202668</t>
-  </si>
-  <si>
-    <t>29.09.202669</t>
-  </si>
-  <si>
-    <t>29.09.202670</t>
-  </si>
-  <si>
-    <t>29.09.202671</t>
-  </si>
-  <si>
-    <t>29.09.202672</t>
-  </si>
-  <si>
-    <t>29.09.202673</t>
-  </si>
-  <si>
-    <t>29.09.202674</t>
-  </si>
-  <si>
-    <t>29.09.202675</t>
-  </si>
-  <si>
-    <t>29.09.202676</t>
-  </si>
-  <si>
-    <t>29.09.202677</t>
-  </si>
-  <si>
-    <t>29.09.202678</t>
-  </si>
-  <si>
-    <t>29.09.202679</t>
-  </si>
-  <si>
-    <t>29.09.202680</t>
-  </si>
-  <si>
-    <t>29.09.202681</t>
-  </si>
-  <si>
-    <t>29.09.202682</t>
-  </si>
-  <si>
-    <t>29.09.202683</t>
-  </si>
-  <si>
-    <t>29.09.202684</t>
-  </si>
-  <si>
-    <t>29.09.202685</t>
-  </si>
-  <si>
-    <t>29.09.202686</t>
-  </si>
-  <si>
-    <t>29.09.202687</t>
-  </si>
-  <si>
-    <t>29.09.202688</t>
-  </si>
-  <si>
-    <t>29.09.202689</t>
-  </si>
-  <si>
-    <t>29.09.202690</t>
-  </si>
-  <si>
-    <t>29.09.202691</t>
-  </si>
-  <si>
-    <t>29.09.202692</t>
-  </si>
-  <si>
-    <t>29.09.202693</t>
-  </si>
-  <si>
-    <t>29.09.202694</t>
-  </si>
-  <si>
-    <t>29.09.202695</t>
-  </si>
-  <si>
-    <t>29.09.202696</t>
-  </si>
-  <si>
-    <t>30.09.20261</t>
-  </si>
-  <si>
-    <t>30.09.20262</t>
-  </si>
-  <si>
-    <t>30.09.20263</t>
-  </si>
-  <si>
-    <t>30.09.20264</t>
-  </si>
-  <si>
-    <t>30.09.20265</t>
-  </si>
-  <si>
-    <t>30.09.20266</t>
-  </si>
-  <si>
-    <t>30.09.20267</t>
-  </si>
-  <si>
-    <t>30.09.20268</t>
-  </si>
-  <si>
-    <t>30.09.20269</t>
-  </si>
-  <si>
-    <t>30.09.202610</t>
-  </si>
-  <si>
-    <t>30.09.202611</t>
-  </si>
-  <si>
-    <t>30.09.202612</t>
-  </si>
-  <si>
-    <t>30.09.202613</t>
-  </si>
-  <si>
-    <t>30.09.202614</t>
-  </si>
-  <si>
-    <t>30.09.202615</t>
-  </si>
-  <si>
-    <t>30.09.202616</t>
-  </si>
-  <si>
-    <t>30.09.202617</t>
-  </si>
-  <si>
-    <t>30.09.202618</t>
-  </si>
-  <si>
-    <t>30.09.202619</t>
-  </si>
-  <si>
-    <t>30.09.202620</t>
-  </si>
-  <si>
-    <t>30.09.202621</t>
-  </si>
-  <si>
-    <t>30.09.202622</t>
-  </si>
-  <si>
-    <t>30.09.202623</t>
-  </si>
-  <si>
-    <t>30.09.202624</t>
-  </si>
-  <si>
-    <t>30.09.202625</t>
-  </si>
-  <si>
-    <t>30.09.202626</t>
-  </si>
-  <si>
-    <t>30.09.202627</t>
-  </si>
-  <si>
-    <t>30.09.202628</t>
-  </si>
-  <si>
-    <t>30.09.202629</t>
-  </si>
-  <si>
-    <t>30.09.202630</t>
-  </si>
-  <si>
-    <t>30.09.202631</t>
-  </si>
-  <si>
-    <t>30.09.202632</t>
-  </si>
-  <si>
-    <t>30.09.202633</t>
-  </si>
-  <si>
-    <t>30.09.202634</t>
-  </si>
-  <si>
-    <t>30.09.202635</t>
-  </si>
-  <si>
-    <t>30.09.202636</t>
-  </si>
-  <si>
-    <t>30.09.202637</t>
-  </si>
-  <si>
-    <t>30.09.202638</t>
-  </si>
-  <si>
-    <t>30.09.202639</t>
-  </si>
-  <si>
-    <t>30.09.202640</t>
-  </si>
-  <si>
-    <t>30.09.202641</t>
-  </si>
-  <si>
-    <t>30.09.202642</t>
-  </si>
-  <si>
-    <t>30.09.202643</t>
-  </si>
-  <si>
-    <t>30.09.202644</t>
-  </si>
-  <si>
-    <t>30.09.202645</t>
-  </si>
-  <si>
-    <t>30.09.202646</t>
-  </si>
-  <si>
-    <t>30.09.202647</t>
-  </si>
-  <si>
-    <t>30.09.202648</t>
-  </si>
-  <si>
-    <t>30.09.202649</t>
-  </si>
-  <si>
-    <t>30.09.202650</t>
-  </si>
-  <si>
-    <t>30.09.202651</t>
-  </si>
-  <si>
-    <t>30.09.202652</t>
-  </si>
-  <si>
-    <t>30.09.202653</t>
-  </si>
-  <si>
-    <t>30.09.202654</t>
-  </si>
-  <si>
-    <t>30.09.202655</t>
-  </si>
-  <si>
-    <t>30.09.202656</t>
-  </si>
-  <si>
-    <t>30.09.202657</t>
-  </si>
-  <si>
-    <t>30.09.202658</t>
-  </si>
-  <si>
-    <t>30.09.202659</t>
-  </si>
-  <si>
-    <t>30.09.202660</t>
-  </si>
-  <si>
-    <t>30.09.202661</t>
-  </si>
-  <si>
-    <t>30.09.202662</t>
-  </si>
-  <si>
-    <t>30.09.202663</t>
-  </si>
-  <si>
-    <t>30.09.202664</t>
-  </si>
-  <si>
-    <t>30.09.202665</t>
-  </si>
-  <si>
-    <t>30.09.202666</t>
-  </si>
-  <si>
-    <t>30.09.202667</t>
-  </si>
-  <si>
-    <t>30.09.202668</t>
-  </si>
-  <si>
-    <t>30.09.202669</t>
-  </si>
-  <si>
-    <t>30.09.202670</t>
-  </si>
-  <si>
-    <t>30.09.202671</t>
-  </si>
-  <si>
-    <t>30.09.202672</t>
-  </si>
-  <si>
-    <t>30.09.202673</t>
-  </si>
-  <si>
-    <t>30.09.202674</t>
-  </si>
-  <si>
-    <t>30.09.202675</t>
-  </si>
-  <si>
-    <t>30.09.202676</t>
-  </si>
-  <si>
-    <t>30.09.202677</t>
-  </si>
-  <si>
-    <t>30.09.202678</t>
-  </si>
-  <si>
-    <t>30.09.202679</t>
-  </si>
-  <si>
-    <t>30.09.202680</t>
-  </si>
-  <si>
-    <t>30.09.202681</t>
-  </si>
-  <si>
-    <t>30.09.202682</t>
-  </si>
-  <si>
-    <t>30.09.202683</t>
-  </si>
-  <si>
-    <t>30.09.202684</t>
-  </si>
-  <si>
-    <t>30.09.202685</t>
-  </si>
-  <si>
-    <t>30.09.202686</t>
-  </si>
-  <si>
-    <t>30.09.202687</t>
-  </si>
-  <si>
-    <t>30.09.202688</t>
-  </si>
-  <si>
-    <t>30.09.202689</t>
-  </si>
-  <si>
-    <t>30.09.202690</t>
-  </si>
-  <si>
-    <t>30.09.202691</t>
-  </si>
-  <si>
-    <t>30.09.202692</t>
+    <t>01.10.20261</t>
+  </si>
+  <si>
+    <t>01.10.20262</t>
+  </si>
+  <si>
+    <t>01.10.20263</t>
+  </si>
+  <si>
+    <t>01.10.20264</t>
+  </si>
+  <si>
+    <t>01.10.20265</t>
+  </si>
+  <si>
+    <t>01.10.20266</t>
+  </si>
+  <si>
+    <t>01.10.20267</t>
+  </si>
+  <si>
+    <t>01.10.20268</t>
+  </si>
+  <si>
+    <t>01.10.20269</t>
+  </si>
+  <si>
+    <t>01.10.202610</t>
+  </si>
+  <si>
+    <t>01.10.202611</t>
+  </si>
+  <si>
+    <t>01.10.202612</t>
+  </si>
+  <si>
+    <t>01.10.202613</t>
+  </si>
+  <si>
+    <t>01.10.202614</t>
+  </si>
+  <si>
+    <t>01.10.202615</t>
+  </si>
+  <si>
+    <t>01.10.202616</t>
+  </si>
+  <si>
+    <t>01.10.202617</t>
+  </si>
+  <si>
+    <t>01.10.202618</t>
+  </si>
+  <si>
+    <t>01.10.202619</t>
+  </si>
+  <si>
+    <t>01.10.202620</t>
+  </si>
+  <si>
+    <t>01.10.202621</t>
+  </si>
+  <si>
+    <t>01.10.202622</t>
+  </si>
+  <si>
+    <t>01.10.202623</t>
+  </si>
+  <si>
+    <t>01.10.202624</t>
+  </si>
+  <si>
+    <t>01.10.202625</t>
+  </si>
+  <si>
+    <t>01.10.202626</t>
+  </si>
+  <si>
+    <t>01.10.202627</t>
+  </si>
+  <si>
+    <t>01.10.202628</t>
+  </si>
+  <si>
+    <t>01.10.202629</t>
+  </si>
+  <si>
+    <t>01.10.202630</t>
+  </si>
+  <si>
+    <t>01.10.202631</t>
+  </si>
+  <si>
+    <t>01.10.202632</t>
+  </si>
+  <si>
+    <t>01.10.202633</t>
+  </si>
+  <si>
+    <t>01.10.202634</t>
+  </si>
+  <si>
+    <t>01.10.202635</t>
+  </si>
+  <si>
+    <t>01.10.202636</t>
+  </si>
+  <si>
+    <t>01.10.202637</t>
+  </si>
+  <si>
+    <t>01.10.202638</t>
+  </si>
+  <si>
+    <t>01.10.202639</t>
+  </si>
+  <si>
+    <t>01.10.202640</t>
+  </si>
+  <si>
+    <t>01.10.202641</t>
+  </si>
+  <si>
+    <t>01.10.202642</t>
+  </si>
+  <si>
+    <t>01.10.202643</t>
+  </si>
+  <si>
+    <t>01.10.202644</t>
+  </si>
+  <si>
+    <t>01.10.202645</t>
+  </si>
+  <si>
+    <t>01.10.202646</t>
+  </si>
+  <si>
+    <t>01.10.202647</t>
+  </si>
+  <si>
+    <t>01.10.202648</t>
+  </si>
+  <si>
+    <t>01.10.202649</t>
+  </si>
+  <si>
+    <t>01.10.202650</t>
+  </si>
+  <si>
+    <t>01.10.202651</t>
+  </si>
+  <si>
+    <t>01.10.202652</t>
+  </si>
+  <si>
+    <t>01.10.202653</t>
+  </si>
+  <si>
+    <t>01.10.202654</t>
+  </si>
+  <si>
+    <t>01.10.202655</t>
+  </si>
+  <si>
+    <t>01.10.202656</t>
+  </si>
+  <si>
+    <t>01.10.202657</t>
+  </si>
+  <si>
+    <t>01.10.202658</t>
+  </si>
+  <si>
+    <t>01.10.202659</t>
+  </si>
+  <si>
+    <t>01.10.202660</t>
+  </si>
+  <si>
+    <t>01.10.202661</t>
+  </si>
+  <si>
+    <t>01.10.202662</t>
+  </si>
+  <si>
+    <t>01.10.202663</t>
+  </si>
+  <si>
+    <t>01.10.202664</t>
+  </si>
+  <si>
+    <t>01.10.202665</t>
+  </si>
+  <si>
+    <t>01.10.202666</t>
+  </si>
+  <si>
+    <t>01.10.202667</t>
+  </si>
+  <si>
+    <t>01.10.202668</t>
+  </si>
+  <si>
+    <t>01.10.202669</t>
+  </si>
+  <si>
+    <t>01.10.202670</t>
+  </si>
+  <si>
+    <t>01.10.202671</t>
+  </si>
+  <si>
+    <t>01.10.202672</t>
+  </si>
+  <si>
+    <t>01.10.202673</t>
+  </si>
+  <si>
+    <t>01.10.202674</t>
+  </si>
+  <si>
+    <t>01.10.202675</t>
+  </si>
+  <si>
+    <t>01.10.202676</t>
+  </si>
+  <si>
+    <t>01.10.202677</t>
+  </si>
+  <si>
+    <t>01.10.202678</t>
+  </si>
+  <si>
+    <t>01.10.202679</t>
+  </si>
+  <si>
+    <t>01.10.202680</t>
+  </si>
+  <si>
+    <t>01.10.202681</t>
+  </si>
+  <si>
+    <t>01.10.202682</t>
+  </si>
+  <si>
+    <t>01.10.202683</t>
+  </si>
+  <si>
+    <t>01.10.202684</t>
+  </si>
+  <si>
+    <t>01.10.202685</t>
+  </si>
+  <si>
+    <t>01.10.202686</t>
+  </si>
+  <si>
+    <t>01.10.202687</t>
+  </si>
+  <si>
+    <t>01.10.202688</t>
+  </si>
+  <si>
+    <t>01.10.202689</t>
+  </si>
+  <si>
+    <t>01.10.202690</t>
+  </si>
+  <si>
+    <t>01.10.202691</t>
+  </si>
+  <si>
+    <t>01.10.202692</t>
+  </si>
+  <si>
+    <t>01.10.202693</t>
+  </si>
+  <si>
+    <t>01.10.202694</t>
+  </si>
+  <si>
+    <t>01.10.202695</t>
+  </si>
+  <si>
+    <t>01.10.202696</t>
+  </si>
+  <si>
+    <t>02.10.20261</t>
+  </si>
+  <si>
+    <t>02.10.20262</t>
+  </si>
+  <si>
+    <t>02.10.20263</t>
+  </si>
+  <si>
+    <t>02.10.20264</t>
+  </si>
+  <si>
+    <t>02.10.20265</t>
+  </si>
+  <si>
+    <t>02.10.20266</t>
+  </si>
+  <si>
+    <t>02.10.20267</t>
+  </si>
+  <si>
+    <t>02.10.20268</t>
+  </si>
+  <si>
+    <t>02.10.20269</t>
+  </si>
+  <si>
+    <t>02.10.202610</t>
+  </si>
+  <si>
+    <t>02.10.202611</t>
+  </si>
+  <si>
+    <t>02.10.202612</t>
+  </si>
+  <si>
+    <t>02.10.202613</t>
+  </si>
+  <si>
+    <t>02.10.202614</t>
+  </si>
+  <si>
+    <t>02.10.202615</t>
+  </si>
+  <si>
+    <t>02.10.202616</t>
+  </si>
+  <si>
+    <t>02.10.202617</t>
+  </si>
+  <si>
+    <t>02.10.202618</t>
+  </si>
+  <si>
+    <t>02.10.202619</t>
+  </si>
+  <si>
+    <t>02.10.202620</t>
+  </si>
+  <si>
+    <t>02.10.202621</t>
+  </si>
+  <si>
+    <t>02.10.202622</t>
+  </si>
+  <si>
+    <t>02.10.202623</t>
+  </si>
+  <si>
+    <t>02.10.202624</t>
+  </si>
+  <si>
+    <t>02.10.202625</t>
+  </si>
+  <si>
+    <t>02.10.202626</t>
+  </si>
+  <si>
+    <t>02.10.202627</t>
+  </si>
+  <si>
+    <t>02.10.202628</t>
+  </si>
+  <si>
+    <t>02.10.202629</t>
+  </si>
+  <si>
+    <t>02.10.202630</t>
+  </si>
+  <si>
+    <t>02.10.202631</t>
+  </si>
+  <si>
+    <t>02.10.202632</t>
+  </si>
+  <si>
+    <t>02.10.202633</t>
+  </si>
+  <si>
+    <t>02.10.202634</t>
+  </si>
+  <si>
+    <t>02.10.202635</t>
+  </si>
+  <si>
+    <t>02.10.202636</t>
+  </si>
+  <si>
+    <t>02.10.202637</t>
+  </si>
+  <si>
+    <t>02.10.202638</t>
+  </si>
+  <si>
+    <t>02.10.202639</t>
+  </si>
+  <si>
+    <t>02.10.202640</t>
+  </si>
+  <si>
+    <t>02.10.202641</t>
+  </si>
+  <si>
+    <t>02.10.202642</t>
+  </si>
+  <si>
+    <t>02.10.202643</t>
+  </si>
+  <si>
+    <t>02.10.202644</t>
+  </si>
+  <si>
+    <t>02.10.202645</t>
+  </si>
+  <si>
+    <t>02.10.202646</t>
+  </si>
+  <si>
+    <t>02.10.202647</t>
+  </si>
+  <si>
+    <t>02.10.202648</t>
+  </si>
+  <si>
+    <t>02.10.202649</t>
+  </si>
+  <si>
+    <t>02.10.202650</t>
+  </si>
+  <si>
+    <t>02.10.202651</t>
+  </si>
+  <si>
+    <t>02.10.202652</t>
+  </si>
+  <si>
+    <t>02.10.202653</t>
+  </si>
+  <si>
+    <t>02.10.202654</t>
+  </si>
+  <si>
+    <t>02.10.202655</t>
+  </si>
+  <si>
+    <t>02.10.202656</t>
+  </si>
+  <si>
+    <t>02.10.202657</t>
+  </si>
+  <si>
+    <t>02.10.202658</t>
+  </si>
+  <si>
+    <t>02.10.202659</t>
+  </si>
+  <si>
+    <t>02.10.202660</t>
+  </si>
+  <si>
+    <t>02.10.202661</t>
+  </si>
+  <si>
+    <t>02.10.202662</t>
+  </si>
+  <si>
+    <t>02.10.202663</t>
+  </si>
+  <si>
+    <t>02.10.202664</t>
+  </si>
+  <si>
+    <t>02.10.202665</t>
+  </si>
+  <si>
+    <t>02.10.202666</t>
+  </si>
+  <si>
+    <t>02.10.202667</t>
+  </si>
+  <si>
+    <t>02.10.202668</t>
+  </si>
+  <si>
+    <t>02.10.202669</t>
+  </si>
+  <si>
+    <t>02.10.202670</t>
+  </si>
+  <si>
+    <t>02.10.202671</t>
+  </si>
+  <si>
+    <t>02.10.202672</t>
+  </si>
+  <si>
+    <t>02.10.202673</t>
+  </si>
+  <si>
+    <t>02.10.202674</t>
+  </si>
+  <si>
+    <t>02.10.202675</t>
+  </si>
+  <si>
+    <t>02.10.202676</t>
+  </si>
+  <si>
+    <t>02.10.202677</t>
+  </si>
+  <si>
+    <t>02.10.202678</t>
+  </si>
+  <si>
+    <t>02.10.202679</t>
+  </si>
+  <si>
+    <t>02.10.202680</t>
+  </si>
+  <si>
+    <t>02.10.202681</t>
+  </si>
+  <si>
+    <t>02.10.202682</t>
+  </si>
+  <si>
+    <t>02.10.202683</t>
+  </si>
+  <si>
+    <t>02.10.202684</t>
+  </si>
+  <si>
+    <t>02.10.202685</t>
+  </si>
+  <si>
+    <t>02.10.202686</t>
+  </si>
+  <si>
+    <t>02.10.202687</t>
+  </si>
+  <si>
+    <t>02.10.202688</t>
+  </si>
+  <si>
+    <t>02.10.202689</t>
+  </si>
+  <si>
+    <t>02.10.202690</t>
+  </si>
+  <si>
+    <t>02.10.202691</t>
+  </si>
+  <si>
+    <t>02.10.202692</t>
+  </si>
+  <si>
+    <t>02.10.202693</t>
+  </si>
+  <si>
+    <t>02.10.202694</t>
+  </si>
+  <si>
+    <t>02.10.202695</t>
+  </si>
+  <si>
+    <t>02.10.202696</t>
+  </si>
+  <si>
+    <t>03.10.20261</t>
+  </si>
+  <si>
+    <t>03.10.20262</t>
+  </si>
+  <si>
+    <t>03.10.20263</t>
+  </si>
+  <si>
+    <t>03.10.20264</t>
+  </si>
+  <si>
+    <t>03.10.20265</t>
+  </si>
+  <si>
+    <t>03.10.20266</t>
+  </si>
+  <si>
+    <t>03.10.20267</t>
+  </si>
+  <si>
+    <t>03.10.20268</t>
+  </si>
+  <si>
+    <t>03.10.20269</t>
+  </si>
+  <si>
+    <t>03.10.202610</t>
+  </si>
+  <si>
+    <t>03.10.202611</t>
+  </si>
+  <si>
+    <t>03.10.202612</t>
+  </si>
+  <si>
+    <t>03.10.202613</t>
+  </si>
+  <si>
+    <t>03.10.202614</t>
+  </si>
+  <si>
+    <t>03.10.202615</t>
+  </si>
+  <si>
+    <t>03.10.202616</t>
+  </si>
+  <si>
+    <t>03.10.202617</t>
+  </si>
+  <si>
+    <t>03.10.202618</t>
+  </si>
+  <si>
+    <t>03.10.202619</t>
+  </si>
+  <si>
+    <t>03.10.202620</t>
+  </si>
+  <si>
+    <t>03.10.202621</t>
+  </si>
+  <si>
+    <t>03.10.202622</t>
+  </si>
+  <si>
+    <t>03.10.202623</t>
+  </si>
+  <si>
+    <t>03.10.202624</t>
+  </si>
+  <si>
+    <t>03.10.202625</t>
+  </si>
+  <si>
+    <t>03.10.202626</t>
+  </si>
+  <si>
+    <t>03.10.202627</t>
+  </si>
+  <si>
+    <t>03.10.202628</t>
+  </si>
+  <si>
+    <t>03.10.202629</t>
+  </si>
+  <si>
+    <t>03.10.202630</t>
+  </si>
+  <si>
+    <t>03.10.202631</t>
+  </si>
+  <si>
+    <t>03.10.202632</t>
+  </si>
+  <si>
+    <t>03.10.202633</t>
+  </si>
+  <si>
+    <t>03.10.202634</t>
+  </si>
+  <si>
+    <t>03.10.202635</t>
+  </si>
+  <si>
+    <t>03.10.202636</t>
+  </si>
+  <si>
+    <t>03.10.202637</t>
+  </si>
+  <si>
+    <t>03.10.202638</t>
+  </si>
+  <si>
+    <t>03.10.202639</t>
+  </si>
+  <si>
+    <t>03.10.202640</t>
+  </si>
+  <si>
+    <t>03.10.202641</t>
+  </si>
+  <si>
+    <t>03.10.202642</t>
+  </si>
+  <si>
+    <t>03.10.202643</t>
+  </si>
+  <si>
+    <t>03.10.202644</t>
+  </si>
+  <si>
+    <t>03.10.202645</t>
+  </si>
+  <si>
+    <t>03.10.202646</t>
+  </si>
+  <si>
+    <t>03.10.202647</t>
+  </si>
+  <si>
+    <t>03.10.202648</t>
+  </si>
+  <si>
+    <t>03.10.202649</t>
+  </si>
+  <si>
+    <t>03.10.202650</t>
+  </si>
+  <si>
+    <t>03.10.202651</t>
+  </si>
+  <si>
+    <t>03.10.202652</t>
+  </si>
+  <si>
+    <t>03.10.202653</t>
+  </si>
+  <si>
+    <t>03.10.202654</t>
+  </si>
+  <si>
+    <t>03.10.202655</t>
+  </si>
+  <si>
+    <t>03.10.202656</t>
+  </si>
+  <si>
+    <t>03.10.202657</t>
+  </si>
+  <si>
+    <t>03.10.202658</t>
+  </si>
+  <si>
+    <t>03.10.202659</t>
+  </si>
+  <si>
+    <t>03.10.202660</t>
+  </si>
+  <si>
+    <t>03.10.202661</t>
+  </si>
+  <si>
+    <t>03.10.202662</t>
+  </si>
+  <si>
+    <t>03.10.202663</t>
+  </si>
+  <si>
+    <t>03.10.202664</t>
+  </si>
+  <si>
+    <t>03.10.202665</t>
+  </si>
+  <si>
+    <t>03.10.202666</t>
+  </si>
+  <si>
+    <t>03.10.202667</t>
+  </si>
+  <si>
+    <t>03.10.202668</t>
+  </si>
+  <si>
+    <t>03.10.202669</t>
+  </si>
+  <si>
+    <t>03.10.202670</t>
+  </si>
+  <si>
+    <t>03.10.202671</t>
+  </si>
+  <si>
+    <t>03.10.202672</t>
+  </si>
+  <si>
+    <t>03.10.202673</t>
+  </si>
+  <si>
+    <t>03.10.202674</t>
+  </si>
+  <si>
+    <t>03.10.202675</t>
+  </si>
+  <si>
+    <t>03.10.202676</t>
+  </si>
+  <si>
+    <t>03.10.202677</t>
+  </si>
+  <si>
+    <t>03.10.202678</t>
+  </si>
+  <si>
+    <t>03.10.202679</t>
+  </si>
+  <si>
+    <t>03.10.202680</t>
+  </si>
+  <si>
+    <t>03.10.202681</t>
+  </si>
+  <si>
+    <t>03.10.202682</t>
+  </si>
+  <si>
+    <t>03.10.202683</t>
+  </si>
+  <si>
+    <t>03.10.202684</t>
+  </si>
+  <si>
+    <t>03.10.202685</t>
+  </si>
+  <si>
+    <t>03.10.202686</t>
+  </si>
+  <si>
+    <t>03.10.202687</t>
+  </si>
+  <si>
+    <t>03.10.202688</t>
+  </si>
+  <si>
+    <t>03.10.202689</t>
+  </si>
+  <si>
+    <t>03.10.202690</t>
+  </si>
+  <si>
+    <t>03.10.202691</t>
+  </si>
+  <si>
+    <t>03.10.202692</t>
   </si>
 </sst>
 </file>
@@ -1264,13 +1264,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46293</v>
+        <v>46296</v>
       </c>
       <c r="B2">
-        <v>2346.124</v>
+        <v>1678.274</v>
       </c>
       <c r="C2">
-        <v>2461</v>
+        <v>1839</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1281,13 +1281,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46293.01041666666</v>
+        <v>46296.01041666666</v>
       </c>
       <c r="B3">
-        <v>2361.247</v>
+        <v>1703.396</v>
       </c>
       <c r="C3">
-        <v>2454</v>
+        <v>1878</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1298,13 +1298,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46293.02083333334</v>
+        <v>46296.02083333334</v>
       </c>
       <c r="B4">
-        <v>2369.208</v>
+        <v>1724.146</v>
       </c>
       <c r="C4">
-        <v>2427</v>
+        <v>1902</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1315,13 +1315,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46293.03125</v>
+        <v>46296.03125</v>
       </c>
       <c r="B5">
-        <v>2377.751</v>
+        <v>1751.373</v>
       </c>
       <c r="C5">
-        <v>2401</v>
+        <v>1907</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1332,13 +1332,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46293.04166666666</v>
+        <v>46296.04166666666</v>
       </c>
       <c r="B6">
-        <v>2385.78</v>
+        <v>1773.456</v>
       </c>
       <c r="C6">
-        <v>2391</v>
+        <v>1929</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1349,13 +1349,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46293.05208333334</v>
+        <v>46296.05208333334</v>
       </c>
       <c r="B7">
-        <v>2393.076</v>
+        <v>1779.911</v>
       </c>
       <c r="C7">
-        <v>2378</v>
+        <v>1935</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1366,13 +1366,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46293.0625</v>
+        <v>46296.0625</v>
       </c>
       <c r="B8">
-        <v>2399.48</v>
+        <v>1785.458</v>
       </c>
       <c r="C8">
-        <v>2354</v>
+        <v>1914</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1383,13 +1383,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46293.07291666666</v>
+        <v>46296.07291666666</v>
       </c>
       <c r="B9">
-        <v>2404.964</v>
+        <v>1788.682</v>
       </c>
       <c r="C9">
-        <v>2339</v>
+        <v>1907</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1400,13 +1400,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46293.08333333334</v>
+        <v>46296.08333333334</v>
       </c>
       <c r="B10">
-        <v>2381.61</v>
+        <v>1807.223</v>
       </c>
       <c r="C10">
-        <v>2343</v>
+        <v>1885</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1417,13 +1417,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46293.09375</v>
+        <v>46296.09375</v>
       </c>
       <c r="B11">
-        <v>2389.247</v>
+        <v>1798.226</v>
       </c>
       <c r="C11">
-        <v>2359</v>
+        <v>1829</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1434,13 +1434,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46293.10416666666</v>
+        <v>46296.10416666666</v>
       </c>
       <c r="B12">
-        <v>2398.018</v>
+        <v>1790.263</v>
       </c>
       <c r="C12">
-        <v>2391</v>
+        <v>1766</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1451,13 +1451,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46293.11458333334</v>
+        <v>46296.11458333334</v>
       </c>
       <c r="B13">
-        <v>2409.091</v>
+        <v>1778.057</v>
       </c>
       <c r="C13">
-        <v>2434</v>
+        <v>1733</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1468,13 +1468,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46293.125</v>
+        <v>46296.125</v>
       </c>
       <c r="B14">
-        <v>2444.987</v>
+        <v>1769.066</v>
       </c>
       <c r="C14">
-        <v>2473</v>
+        <v>1707</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1485,13 +1485,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46293.13541666666</v>
+        <v>46296.13541666666</v>
       </c>
       <c r="B15">
-        <v>2462.688</v>
+        <v>1755.422</v>
       </c>
       <c r="C15">
-        <v>2536</v>
+        <v>1663</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1502,13 +1502,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46293.14583333334</v>
+        <v>46296.14583333334</v>
       </c>
       <c r="B16">
-        <v>2479.475</v>
+        <v>1722.393</v>
       </c>
       <c r="C16">
-        <v>2592</v>
+        <v>1604</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1519,13 +1519,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46293.15625</v>
+        <v>46296.15625</v>
       </c>
       <c r="B17">
-        <v>2493.099</v>
+        <v>1712.858</v>
       </c>
       <c r="C17">
-        <v>2676</v>
+        <v>1578</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1536,13 +1536,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46293.16666666666</v>
+        <v>46296.16666666666</v>
       </c>
       <c r="B18">
-        <v>2556.007</v>
+        <v>1699.841</v>
       </c>
       <c r="C18">
-        <v>2720</v>
+        <v>1593</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1553,13 +1553,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46293.17708333334</v>
+        <v>46296.17708333334</v>
       </c>
       <c r="B19">
-        <v>2576.981</v>
+        <v>1693.53</v>
       </c>
       <c r="C19">
-        <v>2724</v>
+        <v>1623</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1570,13 +1570,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46293.1875</v>
+        <v>46296.1875</v>
       </c>
       <c r="B20">
-        <v>2594.365</v>
+        <v>1690.354</v>
       </c>
       <c r="C20">
-        <v>2715</v>
+        <v>1657</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1587,13 +1587,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46293.19791666666</v>
+        <v>46296.19791666666</v>
       </c>
       <c r="B21">
-        <v>2597.555</v>
+        <v>1684.677</v>
       </c>
       <c r="C21">
-        <v>2724</v>
+        <v>1666</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1604,13 +1604,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46293.20833333334</v>
+        <v>46296.20833333334</v>
       </c>
       <c r="B22">
-        <v>2635.506</v>
+        <v>1673.045</v>
       </c>
       <c r="C22">
-        <v>2755</v>
+        <v>1650</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1621,13 +1621,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46293.21875</v>
+        <v>46296.21875</v>
       </c>
       <c r="B23">
-        <v>2668.431</v>
+        <v>1667.355</v>
       </c>
       <c r="C23">
-        <v>2796</v>
+        <v>1634</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1638,13 +1638,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46293.22916666666</v>
+        <v>46296.22916666666</v>
       </c>
       <c r="B24">
-        <v>2685.35</v>
+        <v>1666.063</v>
       </c>
       <c r="C24">
-        <v>2830</v>
+        <v>1632</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1655,13 +1655,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46293.23958333334</v>
+        <v>46296.23958333334</v>
       </c>
       <c r="B25">
-        <v>2703.877</v>
+        <v>1671.15</v>
       </c>
       <c r="C25">
-        <v>2840</v>
+        <v>1628</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1672,13 +1672,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46293.25</v>
+        <v>46296.25</v>
       </c>
       <c r="B26">
-        <v>2714.64</v>
+        <v>1657.133</v>
       </c>
       <c r="C26">
-        <v>2789</v>
+        <v>1620</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1689,13 +1689,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46293.26041666666</v>
+        <v>46296.26041666666</v>
       </c>
       <c r="B27">
-        <v>2729.64</v>
+        <v>1651.613</v>
       </c>
       <c r="C27">
-        <v>2783</v>
+        <v>1603</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1706,13 +1706,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46293.27083333334</v>
+        <v>46296.27083333334</v>
       </c>
       <c r="B28">
-        <v>2747.072</v>
+        <v>1650.568</v>
       </c>
       <c r="C28">
-        <v>2781</v>
+        <v>1575</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1723,13 +1723,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46293.28125</v>
+        <v>46296.28125</v>
       </c>
       <c r="B29">
-        <v>2761.302</v>
+        <v>1649.712</v>
       </c>
       <c r="C29">
-        <v>2802</v>
+        <v>1530</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1740,13 +1740,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46293.29166666666</v>
+        <v>46296.29166666666</v>
       </c>
       <c r="B30">
-        <v>2757.058</v>
+        <v>1635.703</v>
       </c>
       <c r="C30">
-        <v>2817</v>
+        <v>1466</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1757,13 +1757,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46293.30208333334</v>
+        <v>46296.30208333334</v>
       </c>
       <c r="B31">
-        <v>2756.889</v>
+        <v>1617.586</v>
       </c>
       <c r="C31">
-        <v>2800</v>
+        <v>1403</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1774,13 +1774,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46293.3125</v>
+        <v>46296.3125</v>
       </c>
       <c r="B32">
-        <v>2734.836</v>
+        <v>1595.415</v>
       </c>
       <c r="C32">
-        <v>2796</v>
+        <v>1293</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1791,13 +1791,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46293.32291666666</v>
+        <v>46296.32291666666</v>
       </c>
       <c r="B33">
-        <v>2727.038</v>
+        <v>1568.631</v>
       </c>
       <c r="C33">
-        <v>2800</v>
+        <v>1170</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1808,13 +1808,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46293.33333333334</v>
+        <v>46296.33333333334</v>
       </c>
       <c r="B34">
-        <v>2676.012</v>
+        <v>1532.782</v>
       </c>
       <c r="C34">
-        <v>2816</v>
+        <v>1045</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1825,13 +1825,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46293.34375</v>
+        <v>46296.34375</v>
       </c>
       <c r="B35">
-        <v>2684.167</v>
+        <v>1507.541</v>
       </c>
       <c r="C35">
-        <v>2841</v>
+        <v>955</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1842,13 +1842,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46293.35416666666</v>
+        <v>46296.35416666666</v>
       </c>
       <c r="B36">
-        <v>2690.789</v>
+        <v>1486.574</v>
       </c>
       <c r="C36">
-        <v>2823</v>
+        <v>895</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1859,13 +1859,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46293.36458333334</v>
+        <v>46296.36458333334</v>
       </c>
       <c r="B37">
-        <v>2705.945</v>
+        <v>1455.013</v>
       </c>
       <c r="C37">
-        <v>2810</v>
+        <v>905</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1876,13 +1876,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46293.375</v>
+        <v>46296.375</v>
       </c>
       <c r="B38">
-        <v>2777.212</v>
+        <v>1488.324</v>
       </c>
       <c r="C38">
-        <v>2777</v>
+        <v>939</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1893,13 +1893,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46293.38541666666</v>
+        <v>46296.38541666666</v>
       </c>
       <c r="B39">
-        <v>2776.146</v>
+        <v>1485.857</v>
       </c>
       <c r="C39">
-        <v>2769</v>
+        <v>1043</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1910,13 +1910,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46293.39583333334</v>
+        <v>46296.39583333334</v>
       </c>
       <c r="B40">
-        <v>2786.4</v>
+        <v>1503.142</v>
       </c>
       <c r="C40">
-        <v>2765</v>
+        <v>1223</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1927,13 +1927,10 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46293.40625</v>
+        <v>46296.40625</v>
       </c>
       <c r="B41">
-        <v>2792.238</v>
-      </c>
-      <c r="C41">
-        <v>2772</v>
+        <v>1514.136</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1944,13 +1941,10 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46293.41666666666</v>
+        <v>46296.41666666666</v>
       </c>
       <c r="B42">
-        <v>2761.51</v>
-      </c>
-      <c r="C42">
-        <v>2749</v>
+        <v>1643.661</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1961,13 +1955,10 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46293.42708333334</v>
+        <v>46296.42708333334</v>
       </c>
       <c r="B43">
-        <v>2759.5</v>
-      </c>
-      <c r="C43">
-        <v>2734</v>
+        <v>1694.287</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1978,13 +1969,10 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46293.4375</v>
+        <v>46296.4375</v>
       </c>
       <c r="B44">
-        <v>2726.974</v>
-      </c>
-      <c r="C44">
-        <v>2704</v>
+        <v>1740.061</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1995,13 +1983,10 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46293.44791666666</v>
+        <v>46296.44791666666</v>
       </c>
       <c r="B45">
-        <v>2725.834</v>
-      </c>
-      <c r="C45">
-        <v>2715</v>
+        <v>1780.383</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -2012,13 +1997,10 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46293.45833333334</v>
+        <v>46296.45833333334</v>
       </c>
       <c r="B46">
-        <v>2718.09</v>
-      </c>
-      <c r="C46">
-        <v>2745</v>
+        <v>1851.816</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -2029,13 +2011,10 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46293.46875</v>
+        <v>46296.46875</v>
       </c>
       <c r="B47">
-        <v>2718.281</v>
-      </c>
-      <c r="C47">
-        <v>2752</v>
+        <v>1879.383</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -2046,13 +2025,10 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46293.47916666666</v>
+        <v>46296.47916666666</v>
       </c>
       <c r="B48">
-        <v>2718.64</v>
-      </c>
-      <c r="C48">
-        <v>2759</v>
+        <v>1906.988</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -2063,13 +2039,10 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46293.48958333334</v>
+        <v>46296.48958333334</v>
       </c>
       <c r="B49">
-        <v>2718.581</v>
-      </c>
-      <c r="C49">
-        <v>2772</v>
+        <v>1935.521</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -2080,13 +2053,10 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46293.5</v>
+        <v>46296.5</v>
       </c>
       <c r="B50">
-        <v>2702.696</v>
-      </c>
-      <c r="C50">
-        <v>2810</v>
+        <v>1968.91</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -2097,13 +2067,10 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46293.51041666666</v>
+        <v>46296.51041666666</v>
       </c>
       <c r="B51">
-        <v>2700.833</v>
-      </c>
-      <c r="C51">
-        <v>2833</v>
+        <v>1965.115</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -2114,13 +2081,10 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46293.52083333334</v>
+        <v>46296.52083333334</v>
       </c>
       <c r="B52">
-        <v>2697.819</v>
-      </c>
-      <c r="C52">
-        <v>2888</v>
+        <v>1960.669</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -2131,13 +2095,10 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46293.53125</v>
+        <v>46296.53125</v>
       </c>
       <c r="B53">
-        <v>2694.988</v>
-      </c>
-      <c r="C53">
-        <v>2903</v>
+        <v>1954.766</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -2148,13 +2109,10 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46293.54166666666</v>
+        <v>46296.54166666666</v>
       </c>
       <c r="B54">
-        <v>2713.609</v>
-      </c>
-      <c r="C54">
-        <v>2796</v>
+        <v>1947.503</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -2165,13 +2123,10 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46293.55208333334</v>
+        <v>46296.55208333334</v>
       </c>
       <c r="B55">
-        <v>2706.586</v>
-      </c>
-      <c r="C55">
-        <v>2799</v>
+        <v>1948.46</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -2182,13 +2137,10 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46293.5625</v>
+        <v>46296.5625</v>
       </c>
       <c r="B56">
-        <v>2697.059</v>
-      </c>
-      <c r="C56">
-        <v>2778</v>
+        <v>1949.897</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -2199,13 +2151,10 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46293.57291666666</v>
+        <v>46296.57291666666</v>
       </c>
       <c r="B57">
-        <v>2689.266</v>
-      </c>
-      <c r="C57">
-        <v>2820</v>
+        <v>1949.933</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -2216,13 +2165,10 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46293.58333333334</v>
+        <v>46296.58333333334</v>
       </c>
       <c r="B58">
-        <v>2701.975</v>
-      </c>
-      <c r="C58">
-        <v>2851</v>
+        <v>1887.666</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -2233,13 +2179,10 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46293.59375</v>
+        <v>46296.59375</v>
       </c>
       <c r="B59">
-        <v>2696.477</v>
-      </c>
-      <c r="C59">
-        <v>2844</v>
+        <v>1884.363</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -2250,13 +2193,10 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46293.60416666666</v>
+        <v>46296.60416666666</v>
       </c>
       <c r="B60">
-        <v>2690.843</v>
-      </c>
-      <c r="C60">
-        <v>2831</v>
+        <v>1882.854</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -2267,13 +2207,10 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46293.61458333334</v>
+        <v>46296.61458333334</v>
       </c>
       <c r="B61">
-        <v>2685.6</v>
-      </c>
-      <c r="C61">
-        <v>2864</v>
+        <v>1881.944</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2284,13 +2221,10 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46293.625</v>
+        <v>46296.625</v>
       </c>
       <c r="B62">
-        <v>2708.146</v>
-      </c>
-      <c r="C62">
-        <v>2896</v>
+        <v>1867.84</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2301,13 +2235,10 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46293.63541666666</v>
+        <v>46296.63541666666</v>
       </c>
       <c r="B63">
-        <v>2701.454</v>
-      </c>
-      <c r="C63">
-        <v>2898</v>
+        <v>1850.808</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2318,13 +2249,10 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46293.64583333334</v>
+        <v>46296.64583333334</v>
       </c>
       <c r="B64">
-        <v>2693.491</v>
-      </c>
-      <c r="C64">
-        <v>2712</v>
+        <v>1833.121</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2335,13 +2263,10 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46293.65625</v>
+        <v>46296.65625</v>
       </c>
       <c r="B65">
-        <v>2718.439</v>
-      </c>
-      <c r="C65">
-        <v>2761</v>
+        <v>1814.512</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2352,13 +2277,10 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46293.66666666666</v>
+        <v>46296.66666666666</v>
       </c>
       <c r="B66">
-        <v>2704.841</v>
-      </c>
-      <c r="C66">
-        <v>2785</v>
+        <v>1768.116</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2369,13 +2291,10 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46293.67708333334</v>
+        <v>46296.67708333334</v>
       </c>
       <c r="B67">
-        <v>2684.783</v>
-      </c>
-      <c r="C67">
-        <v>2816</v>
+        <v>1716.381</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2386,13 +2305,10 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46293.6875</v>
+        <v>46296.6875</v>
       </c>
       <c r="B68">
-        <v>2666.7</v>
-      </c>
-      <c r="C68">
-        <v>2854</v>
+        <v>1662.02</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2403,13 +2319,10 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46293.69791666666</v>
+        <v>46296.69791666666</v>
       </c>
       <c r="B69">
-        <v>2647.864</v>
-      </c>
-      <c r="C69">
-        <v>2880</v>
+        <v>1606.042</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2420,13 +2333,10 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46293.70833333334</v>
+        <v>46296.70833333334</v>
       </c>
       <c r="B70">
-        <v>2615.433</v>
-      </c>
-      <c r="C70">
-        <v>2882</v>
+        <v>1454.495</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2437,13 +2347,10 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46293.71875</v>
+        <v>46296.71875</v>
       </c>
       <c r="B71">
-        <v>2587.227</v>
-      </c>
-      <c r="C71">
-        <v>2847</v>
+        <v>1431.521</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2454,13 +2361,10 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46293.72916666666</v>
+        <v>46296.72916666666</v>
       </c>
       <c r="B72">
-        <v>2562.646</v>
-      </c>
-      <c r="C72">
-        <v>2811</v>
+        <v>1405.618</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2471,13 +2375,10 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46293.73958333334</v>
+        <v>46296.73958333334</v>
       </c>
       <c r="B73">
-        <v>2539.611</v>
-      </c>
-      <c r="C73">
-        <v>2779</v>
+        <v>1387.977</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2488,13 +2389,10 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46293.75</v>
+        <v>46296.75</v>
       </c>
       <c r="B74">
-        <v>2500.577</v>
-      </c>
-      <c r="C74">
-        <v>2735</v>
+        <v>1384.683</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2505,13 +2403,10 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46293.76041666666</v>
+        <v>46296.76041666666</v>
       </c>
       <c r="B75">
-        <v>2485.077</v>
-      </c>
-      <c r="C75">
-        <v>2729</v>
+        <v>1408.492</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2522,13 +2417,10 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46293.77083333334</v>
+        <v>46296.77083333334</v>
       </c>
       <c r="B76">
-        <v>2470.963</v>
-      </c>
-      <c r="C76">
-        <v>2729</v>
+        <v>1431.575</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2539,13 +2431,10 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46293.78125</v>
+        <v>46296.78125</v>
       </c>
       <c r="B77">
-        <v>2456.171</v>
-      </c>
-      <c r="C77">
-        <v>2758</v>
+        <v>1455.183</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2556,13 +2445,10 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46293.79166666666</v>
+        <v>46296.79166666666</v>
       </c>
       <c r="B78">
-        <v>2361.467</v>
-      </c>
-      <c r="C78">
-        <v>2773</v>
+        <v>1500.092</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2573,13 +2459,10 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46293.80208333334</v>
+        <v>46296.80208333334</v>
       </c>
       <c r="B79">
-        <v>2363.098</v>
-      </c>
-      <c r="C79">
-        <v>2773</v>
+        <v>1536.463</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2590,13 +2473,10 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46293.8125</v>
+        <v>46296.8125</v>
       </c>
       <c r="B80">
-        <v>2362.729</v>
-      </c>
-      <c r="C80">
-        <v>2770</v>
+        <v>1570.361</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2607,13 +2487,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46293.82291666666</v>
+        <v>46296.82291666666</v>
       </c>
       <c r="B81">
-        <v>2359.502</v>
-      </c>
-      <c r="C81">
-        <v>2770</v>
+        <v>1604.135</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2624,13 +2501,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46293.83333333334</v>
+        <v>46296.83333333334</v>
       </c>
       <c r="B82">
-        <v>2356.586</v>
-      </c>
-      <c r="C82">
-        <v>2767</v>
+        <v>1752.332</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2641,13 +2515,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46293.84375</v>
+        <v>46296.84375</v>
       </c>
       <c r="B83">
-        <v>2356.482</v>
-      </c>
-      <c r="C83">
-        <v>2730</v>
+        <v>1780.827</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2658,13 +2529,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46293.85416666666</v>
+        <v>46296.85416666666</v>
       </c>
       <c r="B84">
-        <v>2358.279</v>
-      </c>
-      <c r="C84">
-        <v>2728</v>
+        <v>1807.111</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2675,13 +2543,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46293.86458333334</v>
+        <v>46296.86458333334</v>
       </c>
       <c r="B85">
-        <v>2360.677</v>
-      </c>
-      <c r="C85">
-        <v>2717</v>
+        <v>1835.884</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2692,13 +2557,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46293.875</v>
+        <v>46296.875</v>
       </c>
       <c r="B86">
-        <v>2373.896</v>
-      </c>
-      <c r="C86">
-        <v>2770</v>
+        <v>1872.539</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2709,13 +2571,10 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46293.88541666666</v>
+        <v>46296.88541666666</v>
       </c>
       <c r="B87">
-        <v>2384.568</v>
-      </c>
-      <c r="C87">
-        <v>2780</v>
+        <v>1906.901</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2726,13 +2585,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46293.89583333334</v>
+        <v>46296.89583333334</v>
       </c>
       <c r="B88">
-        <v>2395.224</v>
-      </c>
-      <c r="C88">
-        <v>2779</v>
+        <v>1938.885</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2743,13 +2599,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46293.90625</v>
+        <v>46296.90625</v>
       </c>
       <c r="B89">
-        <v>2405.737</v>
-      </c>
-      <c r="C89">
-        <v>2770</v>
+        <v>1970.223</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2760,13 +2613,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46293.91666666666</v>
+        <v>46296.91666666666</v>
       </c>
       <c r="B90">
-        <v>2491.638</v>
-      </c>
-      <c r="C90">
-        <v>2756</v>
+        <v>2005.884</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2777,13 +2627,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46293.92708333334</v>
+        <v>46296.92708333334</v>
       </c>
       <c r="B91">
-        <v>2500.552</v>
-      </c>
-      <c r="C91">
-        <v>2760</v>
+        <v>2030.121</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2794,13 +2641,10 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46293.9375</v>
+        <v>46296.9375</v>
       </c>
       <c r="B92">
-        <v>2508.862</v>
-      </c>
-      <c r="C92">
-        <v>2746</v>
+        <v>2055.298</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2811,13 +2655,10 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46293.94791666666</v>
+        <v>46296.94791666666</v>
       </c>
       <c r="B93">
-        <v>2517.125</v>
-      </c>
-      <c r="C93">
-        <v>2745</v>
+        <v>2079.918</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2828,13 +2669,10 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46293.95833333334</v>
+        <v>46296.95833333334</v>
       </c>
       <c r="B94">
-        <v>2464.976</v>
-      </c>
-      <c r="C94">
-        <v>2732</v>
+        <v>1974.346</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2845,13 +2683,10 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46293.96875</v>
+        <v>46296.96875</v>
       </c>
       <c r="B95">
-        <v>2461.993</v>
-      </c>
-      <c r="C95">
-        <v>2708</v>
+        <v>1987.017</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2862,13 +2697,10 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46293.97916666666</v>
+        <v>46296.97916666666</v>
       </c>
       <c r="B96">
-        <v>2473.593</v>
-      </c>
-      <c r="C96">
-        <v>2681</v>
+        <v>2005.331</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2879,13 +2711,10 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46293.98958333334</v>
+        <v>46296.98958333334</v>
       </c>
       <c r="B97">
-        <v>2472.181</v>
-      </c>
-      <c r="C97">
-        <v>2656</v>
+        <v>2053.493</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2896,13 +2725,10 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="B98">
-        <v>2442.655</v>
-      </c>
-      <c r="C98">
-        <v>2614</v>
+        <v>2166.343</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2913,13 +2739,10 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46294.01041666666</v>
+        <v>46297.01041666666</v>
       </c>
       <c r="B99">
-        <v>2439.735</v>
-      </c>
-      <c r="C99">
-        <v>2624</v>
+        <v>2173.917</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2930,13 +2753,10 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46294.02083333334</v>
+        <v>46297.02083333334</v>
       </c>
       <c r="B100">
-        <v>2439.55</v>
-      </c>
-      <c r="C100">
-        <v>2624</v>
+        <v>2176.448</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2947,13 +2767,10 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46294.03125</v>
+        <v>46297.03125</v>
       </c>
       <c r="B101">
-        <v>2439.624</v>
-      </c>
-      <c r="C101">
-        <v>2612</v>
+        <v>2181.03</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2964,13 +2781,10 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46294.04166666666</v>
+        <v>46297.04166666666</v>
       </c>
       <c r="B102">
-        <v>2419.278</v>
-      </c>
-      <c r="C102">
-        <v>2591</v>
+        <v>2191.031</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2981,13 +2795,10 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46294.05208333334</v>
+        <v>46297.05208333334</v>
       </c>
       <c r="B103">
-        <v>2411.935</v>
-      </c>
-      <c r="C103">
-        <v>2582</v>
+        <v>2186.818</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2998,13 +2809,10 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46294.0625</v>
+        <v>46297.0625</v>
       </c>
       <c r="B104">
-        <v>2408.29</v>
-      </c>
-      <c r="C104">
-        <v>2577</v>
+        <v>2185.927</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -3015,13 +2823,10 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46294.07291666666</v>
+        <v>46297.07291666666</v>
       </c>
       <c r="B105">
-        <v>2401.668</v>
-      </c>
-      <c r="C105">
-        <v>2574</v>
+        <v>2183.097</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -3032,13 +2837,10 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46294.08333333334</v>
+        <v>46297.08333333334</v>
       </c>
       <c r="B106">
-        <v>2409.885</v>
-      </c>
-      <c r="C106">
-        <v>2564</v>
+        <v>2191.57</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -3049,13 +2851,10 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46294.09375</v>
+        <v>46297.09375</v>
       </c>
       <c r="B107">
-        <v>2412.824</v>
-      </c>
-      <c r="C107">
-        <v>2564</v>
+        <v>2190.983</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -3066,13 +2865,10 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46294.10416666666</v>
+        <v>46297.10416666666</v>
       </c>
       <c r="B108">
-        <v>2407.774</v>
-      </c>
-      <c r="C108">
-        <v>2552</v>
+        <v>2195.916</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -3083,13 +2879,10 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46294.11458333334</v>
+        <v>46297.11458333334</v>
       </c>
       <c r="B109">
-        <v>2404</v>
-      </c>
-      <c r="C109">
-        <v>2530</v>
+        <v>2191.348</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -3100,13 +2893,10 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46294.125</v>
+        <v>46297.125</v>
       </c>
       <c r="B110">
-        <v>2405.241</v>
-      </c>
-      <c r="C110">
-        <v>2510</v>
+        <v>2188.62</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -3117,13 +2907,10 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46294.13541666666</v>
+        <v>46297.13541666666</v>
       </c>
       <c r="B111">
-        <v>2406.122</v>
-      </c>
-      <c r="C111">
-        <v>2504</v>
+        <v>2188.52</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -3134,13 +2921,10 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46294.14583333334</v>
+        <v>46297.14583333334</v>
       </c>
       <c r="B112">
-        <v>2405.022</v>
-      </c>
-      <c r="C112">
-        <v>2511</v>
+        <v>2187.128</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -3151,13 +2935,10 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46294.15625</v>
+        <v>46297.15625</v>
       </c>
       <c r="B113">
-        <v>2400.487</v>
-      </c>
-      <c r="C113">
-        <v>2533</v>
+        <v>2187.773</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -3168,13 +2949,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46294.16666666666</v>
+        <v>46297.16666666666</v>
       </c>
       <c r="B114">
-        <v>2395.105</v>
-      </c>
-      <c r="C114">
-        <v>2549</v>
+        <v>2182.637</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -3185,13 +2963,10 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46294.17708333334</v>
+        <v>46297.17708333334</v>
       </c>
       <c r="B115">
-        <v>2394.428</v>
-      </c>
-      <c r="C115">
-        <v>2551</v>
+        <v>2185.718</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -3202,13 +2977,10 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46294.1875</v>
+        <v>46297.1875</v>
       </c>
       <c r="B116">
-        <v>2394.335</v>
-      </c>
-      <c r="C116">
-        <v>2550</v>
+        <v>2184.986</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -3219,13 +2991,10 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46294.19791666666</v>
+        <v>46297.19791666666</v>
       </c>
       <c r="B117">
-        <v>2394.09</v>
-      </c>
-      <c r="C117">
-        <v>2529</v>
+        <v>2185.382</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -3236,13 +3005,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46294.20833333334</v>
+        <v>46297.20833333334</v>
       </c>
       <c r="B118">
-        <v>2385.102</v>
-      </c>
-      <c r="C118">
-        <v>2528</v>
+        <v>2249.993</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -3253,13 +3019,10 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46294.21875</v>
+        <v>46297.21875</v>
       </c>
       <c r="B119">
-        <v>2386.559</v>
-      </c>
-      <c r="C119">
-        <v>2523</v>
+        <v>2243.439</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -3270,13 +3033,10 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46294.22916666666</v>
+        <v>46297.22916666666</v>
       </c>
       <c r="B120">
-        <v>2378.056</v>
-      </c>
-      <c r="C120">
-        <v>2523</v>
+        <v>2158.308</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3287,13 +3047,10 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46294.23958333334</v>
+        <v>46297.23958333334</v>
       </c>
       <c r="B121">
-        <v>2375.854</v>
-      </c>
-      <c r="C121">
-        <v>2524</v>
+        <v>2156.736</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3304,13 +3061,10 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46294.25</v>
+        <v>46297.25</v>
       </c>
       <c r="B122">
-        <v>2369.829</v>
-      </c>
-      <c r="C122">
-        <v>2524</v>
+        <v>2123.358</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3321,13 +3075,10 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46294.26041666666</v>
+        <v>46297.26041666666</v>
       </c>
       <c r="B123">
-        <v>2366.452</v>
-      </c>
-      <c r="C123">
-        <v>2521</v>
+        <v>2122.566</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3338,13 +3089,10 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46294.27083333334</v>
+        <v>46297.27083333334</v>
       </c>
       <c r="B124">
-        <v>2360.137</v>
-      </c>
-      <c r="C124">
-        <v>2520</v>
+        <v>2100.143</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3355,13 +3103,10 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46294.28125</v>
+        <v>46297.28125</v>
       </c>
       <c r="B125">
-        <v>2357.493</v>
-      </c>
-      <c r="C125">
-        <v>2506</v>
+        <v>2104.315</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3372,13 +3117,10 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46294.29166666666</v>
+        <v>46297.29166666666</v>
       </c>
       <c r="B126">
-        <v>2331.379</v>
-      </c>
-      <c r="C126">
-        <v>2473</v>
+        <v>2125.749</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3389,13 +3131,10 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46294.30208333334</v>
+        <v>46297.30208333334</v>
       </c>
       <c r="B127">
-        <v>2322.227</v>
-      </c>
-      <c r="C127">
-        <v>2426</v>
+        <v>2091.794</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3406,13 +3145,10 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46294.3125</v>
+        <v>46297.3125</v>
       </c>
       <c r="B128">
-        <v>2304.08</v>
-      </c>
-      <c r="C128">
-        <v>2361</v>
+        <v>2047.298</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3423,13 +3159,10 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46294.32291666666</v>
+        <v>46297.32291666666</v>
       </c>
       <c r="B129">
-        <v>2292.625</v>
-      </c>
-      <c r="C129">
-        <v>2309</v>
+        <v>2012.182</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3440,13 +3173,10 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46294.33333333334</v>
+        <v>46297.33333333334</v>
       </c>
       <c r="B130">
-        <v>2242.579</v>
-      </c>
-      <c r="C130">
-        <v>2264</v>
+        <v>1909.851</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3457,13 +3187,10 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46294.34375</v>
+        <v>46297.34375</v>
       </c>
       <c r="B131">
-        <v>2238.581</v>
-      </c>
-      <c r="C131">
-        <v>2225</v>
+        <v>1886.166</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3474,13 +3201,10 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46294.35416666666</v>
+        <v>46297.35416666666</v>
       </c>
       <c r="B132">
-        <v>2236.717</v>
-      </c>
-      <c r="C132">
-        <v>2166</v>
+        <v>1875.403</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3491,13 +3215,10 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46294.36458333334</v>
+        <v>46297.36458333334</v>
       </c>
       <c r="B133">
-        <v>2229.567</v>
-      </c>
-      <c r="C133">
-        <v>2086</v>
+        <v>1855.614</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3508,13 +3229,10 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46294.375</v>
+        <v>46297.375</v>
       </c>
       <c r="B134">
-        <v>2201.31</v>
-      </c>
-      <c r="C134">
-        <v>1976</v>
+        <v>2018.482</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3525,13 +3243,10 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46294.38541666666</v>
+        <v>46297.38541666666</v>
       </c>
       <c r="B135">
-        <v>2130.513</v>
-      </c>
-      <c r="C135">
-        <v>1880</v>
+        <v>2027.749</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3542,13 +3257,10 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46294.39583333334</v>
+        <v>46297.39583333334</v>
       </c>
       <c r="B136">
-        <v>2111.605</v>
-      </c>
-      <c r="C136">
-        <v>1826</v>
+        <v>2042.092</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3559,13 +3271,10 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46294.40625</v>
+        <v>46297.40625</v>
       </c>
       <c r="B137">
-        <v>2089.304</v>
-      </c>
-      <c r="C137">
-        <v>1725</v>
+        <v>2054.338</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3576,13 +3285,10 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46294.41666666666</v>
+        <v>46297.41666666666</v>
       </c>
       <c r="B138">
-        <v>2094.843</v>
-      </c>
-      <c r="C138">
-        <v>1705</v>
+        <v>2122.165</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3593,13 +3299,10 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46294.42708333334</v>
+        <v>46297.42708333334</v>
       </c>
       <c r="B139">
-        <v>2080.947</v>
-      </c>
-      <c r="C139">
-        <v>1711</v>
+        <v>2162.192</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3610,13 +3313,10 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46294.4375</v>
+        <v>46297.4375</v>
       </c>
       <c r="B140">
-        <v>2069.12</v>
-      </c>
-      <c r="C140">
-        <v>1771</v>
+        <v>2197.602</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3627,13 +3327,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46294.44791666666</v>
+        <v>46297.44791666666</v>
       </c>
       <c r="B141">
-        <v>2059.574</v>
-      </c>
-      <c r="C141">
-        <v>1819</v>
+        <v>2236.1</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3644,13 +3341,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46294.45833333334</v>
+        <v>46297.45833333334</v>
       </c>
       <c r="B142">
-        <v>2054.852</v>
-      </c>
-      <c r="C142">
-        <v>1840</v>
+        <v>2288.189</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3661,13 +3355,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46294.46875</v>
+        <v>46297.46875</v>
       </c>
       <c r="B143">
-        <v>2060.312</v>
-      </c>
-      <c r="C143">
-        <v>1877</v>
+        <v>2309.173</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3678,13 +3369,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46294.47916666666</v>
+        <v>46297.47916666666</v>
       </c>
       <c r="B144">
-        <v>2066.534</v>
-      </c>
-      <c r="C144">
-        <v>1941</v>
+        <v>2332.053</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3695,13 +3383,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46294.48958333334</v>
+        <v>46297.48958333334</v>
       </c>
       <c r="B145">
-        <v>2071.323</v>
-      </c>
-      <c r="C145">
-        <v>1932</v>
+        <v>2350.638</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3712,13 +3397,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46294.5</v>
+        <v>46297.5</v>
       </c>
       <c r="B146">
-        <v>2088.161</v>
-      </c>
-      <c r="C146">
-        <v>1999</v>
+        <v>2364.653</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3729,13 +3411,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46294.51041666666</v>
+        <v>46297.51041666666</v>
       </c>
       <c r="B147">
-        <v>2091.646</v>
-      </c>
-      <c r="C147">
-        <v>2040</v>
+        <v>2345.255</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3746,13 +3425,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46294.52083333334</v>
+        <v>46297.52083333334</v>
       </c>
       <c r="B148">
-        <v>2101.692</v>
-      </c>
-      <c r="C148">
-        <v>2065</v>
+        <v>2319.574</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3763,13 +3439,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46294.53125</v>
+        <v>46297.53125</v>
       </c>
       <c r="B149">
-        <v>2108.731</v>
-      </c>
-      <c r="C149">
-        <v>2082</v>
+        <v>2294.546</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3780,13 +3453,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46294.54166666666</v>
+        <v>46297.54166666666</v>
       </c>
       <c r="B150">
-        <v>2115.188</v>
-      </c>
-      <c r="C150">
-        <v>2069</v>
+        <v>2261.802</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3797,13 +3467,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46294.55208333334</v>
+        <v>46297.55208333334</v>
       </c>
       <c r="B151">
-        <v>2114.097</v>
-      </c>
-      <c r="C151">
-        <v>2097</v>
+        <v>2227.574</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3814,13 +3481,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46294.5625</v>
+        <v>46297.5625</v>
       </c>
       <c r="B152">
-        <v>2113.548</v>
-      </c>
-      <c r="C152">
-        <v>2116</v>
+        <v>2196.144</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3831,13 +3495,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46294.57291666666</v>
+        <v>46297.57291666666</v>
       </c>
       <c r="B153">
-        <v>2112.258</v>
-      </c>
-      <c r="C153">
-        <v>2124</v>
+        <v>2164.117</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3848,13 +3509,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46294.58333333334</v>
+        <v>46297.58333333334</v>
       </c>
       <c r="B154">
-        <v>2112.887</v>
-      </c>
-      <c r="C154">
-        <v>2093</v>
+        <v>2106.485</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3865,13 +3523,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46294.59375</v>
+        <v>46297.59375</v>
       </c>
       <c r="B155">
-        <v>2107.854</v>
-      </c>
-      <c r="C155">
-        <v>1999</v>
+        <v>2073.657</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3882,13 +3537,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46294.60416666666</v>
+        <v>46297.60416666666</v>
       </c>
       <c r="B156">
-        <v>2100.948</v>
-      </c>
-      <c r="C156">
-        <v>1947</v>
+        <v>2042.928</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3899,13 +3551,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46294.61458333334</v>
+        <v>46297.61458333334</v>
       </c>
       <c r="B157">
-        <v>2094.578</v>
-      </c>
-      <c r="C157">
-        <v>1902</v>
+        <v>2009.888</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3916,13 +3565,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46294.625</v>
+        <v>46297.625</v>
       </c>
       <c r="B158">
-        <v>1979.194</v>
-      </c>
-      <c r="C158">
-        <v>1922</v>
+        <v>1973.029</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3933,13 +3579,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46294.63541666666</v>
+        <v>46297.63541666666</v>
       </c>
       <c r="B159">
-        <v>1953.875</v>
-      </c>
-      <c r="C159">
-        <v>1957</v>
+        <v>1935.909</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3950,13 +3593,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46294.64583333334</v>
+        <v>46297.64583333334</v>
       </c>
       <c r="B160">
-        <v>1928.175</v>
-      </c>
-      <c r="C160">
-        <v>1923</v>
+        <v>1892.277</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3967,13 +3607,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46294.65625</v>
+        <v>46297.65625</v>
       </c>
       <c r="B161">
-        <v>1902.75</v>
-      </c>
-      <c r="C161">
-        <v>1822</v>
+        <v>1857.25</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3984,13 +3621,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46294.66666666666</v>
+        <v>46297.66666666666</v>
       </c>
       <c r="B162">
-        <v>1891.055</v>
-      </c>
-      <c r="C162">
-        <v>1634</v>
+        <v>1666.541</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -4001,13 +3635,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46294.67708333334</v>
+        <v>46297.67708333334</v>
       </c>
       <c r="B163">
-        <v>1834.846</v>
-      </c>
-      <c r="C163">
-        <v>1535</v>
+        <v>1604.161</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -4018,13 +3649,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46294.6875</v>
+        <v>46297.6875</v>
       </c>
       <c r="B164">
-        <v>1778.335</v>
-      </c>
-      <c r="C164">
-        <v>1364</v>
+        <v>1537.067</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -4035,13 +3663,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46294.69791666666</v>
+        <v>46297.69791666666</v>
       </c>
       <c r="B165">
-        <v>1724.477</v>
-      </c>
-      <c r="C165">
-        <v>1209</v>
+        <v>1473.919</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -4052,13 +3677,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46294.70833333334</v>
+        <v>46297.70833333334</v>
       </c>
       <c r="B166">
-        <v>1705.142</v>
-      </c>
-      <c r="C166">
-        <v>1112</v>
+        <v>1406.197</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -4069,13 +3691,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46294.71875</v>
+        <v>46297.71875</v>
       </c>
       <c r="B167">
-        <v>1675.82</v>
-      </c>
-      <c r="C167">
-        <v>1127</v>
+        <v>1357.281</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -4086,13 +3705,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46294.72916666666</v>
+        <v>46297.72916666666</v>
       </c>
       <c r="B168">
-        <v>1649.761</v>
-      </c>
-      <c r="C168">
-        <v>1143</v>
+        <v>1309.165</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -4103,13 +3719,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46294.73958333334</v>
+        <v>46297.73958333334</v>
       </c>
       <c r="B169">
-        <v>1625.342</v>
-      </c>
-      <c r="C169">
-        <v>1141</v>
+        <v>1263.414</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -4120,13 +3733,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46294.75</v>
+        <v>46297.75</v>
       </c>
       <c r="B170">
-        <v>1578.937</v>
-      </c>
-      <c r="C170">
-        <v>1159</v>
+        <v>1193.233</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -4137,13 +3747,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46294.76041666666</v>
+        <v>46297.76041666666</v>
       </c>
       <c r="B171">
-        <v>1559.375</v>
-      </c>
-      <c r="C171">
-        <v>1194</v>
+        <v>1162.273</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -4154,13 +3761,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46294.77083333334</v>
+        <v>46297.77083333334</v>
       </c>
       <c r="B172">
-        <v>1540.581</v>
-      </c>
-      <c r="C172">
-        <v>1251</v>
+        <v>1134.598</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -4171,13 +3775,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46294.78125</v>
+        <v>46297.78125</v>
       </c>
       <c r="B173">
-        <v>1523.97</v>
-      </c>
-      <c r="C173">
-        <v>1322</v>
+        <v>1106.035</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -4188,13 +3789,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46294.79166666666</v>
+        <v>46297.79166666666</v>
       </c>
       <c r="B174">
-        <v>1530.774</v>
-      </c>
-      <c r="C174">
-        <v>1394</v>
+        <v>1099.801</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -4205,13 +3803,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46294.80208333334</v>
+        <v>46297.80208333334</v>
       </c>
       <c r="B175">
-        <v>1540.839</v>
-      </c>
-      <c r="C175">
-        <v>1494</v>
+        <v>1081.617</v>
       </c>
       <c r="D175">
         <v>78</v>
@@ -4222,13 +3817,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46294.8125</v>
+        <v>46297.8125</v>
       </c>
       <c r="B176">
-        <v>1550.608</v>
-      </c>
-      <c r="C176">
-        <v>1569</v>
+        <v>1063.499</v>
       </c>
       <c r="D176">
         <v>79</v>
@@ -4239,13 +3831,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46294.82291666666</v>
+        <v>46297.82291666666</v>
       </c>
       <c r="B177">
-        <v>1560.332</v>
-      </c>
-      <c r="C177">
-        <v>1673</v>
+        <v>1046.388</v>
       </c>
       <c r="D177">
         <v>80</v>
@@ -4256,13 +3845,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46294.83333333334</v>
+        <v>46297.83333333334</v>
       </c>
       <c r="B178">
-        <v>1579.783</v>
-      </c>
-      <c r="C178">
-        <v>1754</v>
+        <v>1032.723</v>
       </c>
       <c r="D178">
         <v>81</v>
@@ -4273,13 +3859,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46294.84375</v>
+        <v>46297.84375</v>
       </c>
       <c r="B179">
-        <v>1604.135</v>
-      </c>
-      <c r="C179">
-        <v>1811</v>
+        <v>1023.944</v>
       </c>
       <c r="D179">
         <v>82</v>
@@ -4290,13 +3873,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46294.85416666666</v>
+        <v>46297.85416666666</v>
       </c>
       <c r="B180">
-        <v>1628.061</v>
-      </c>
-      <c r="C180">
-        <v>1855</v>
+        <v>1017.785</v>
       </c>
       <c r="D180">
         <v>83</v>
@@ -4307,13 +3887,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46294.86458333334</v>
+        <v>46297.86458333334</v>
       </c>
       <c r="B181">
-        <v>1650.98</v>
-      </c>
-      <c r="C181">
-        <v>1898</v>
+        <v>1010.78</v>
       </c>
       <c r="D181">
         <v>84</v>
@@ -4324,13 +3901,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46294.875</v>
+        <v>46297.875</v>
       </c>
       <c r="B182">
-        <v>1667.843</v>
-      </c>
-      <c r="C182">
-        <v>1962</v>
+        <v>1019.926</v>
       </c>
       <c r="D182">
         <v>85</v>
@@ -4341,13 +3915,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46294.88541666666</v>
+        <v>46297.88541666666</v>
       </c>
       <c r="B183">
-        <v>1711.247</v>
-      </c>
-      <c r="C183">
-        <v>2049</v>
+        <v>1026.423</v>
       </c>
       <c r="D183">
         <v>86</v>
@@ -4358,13 +3929,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46294.89583333334</v>
+        <v>46297.89583333334</v>
       </c>
       <c r="B184">
-        <v>1753.316</v>
-      </c>
-      <c r="C184">
-        <v>2120</v>
+        <v>1035.402</v>
       </c>
       <c r="D184">
         <v>87</v>
@@ -4375,13 +3943,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46294.90625</v>
+        <v>46297.90625</v>
       </c>
       <c r="B185">
-        <v>1797.201</v>
-      </c>
-      <c r="C185">
-        <v>2180</v>
+        <v>1043.833</v>
       </c>
       <c r="D185">
         <v>88</v>
@@ -4392,13 +3957,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46294.91666666666</v>
+        <v>46297.91666666666</v>
       </c>
       <c r="B186">
-        <v>1843.622</v>
-      </c>
-      <c r="C186">
-        <v>2263</v>
+        <v>1067.226</v>
       </c>
       <c r="D186">
         <v>89</v>
@@ -4409,13 +3971,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46294.92708333334</v>
+        <v>46297.92708333334</v>
       </c>
       <c r="B187">
-        <v>1876.165</v>
-      </c>
-      <c r="C187">
-        <v>2335</v>
+        <v>1086.232</v>
       </c>
       <c r="D187">
         <v>90</v>
@@ -4426,13 +3985,10 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46294.9375</v>
+        <v>46297.9375</v>
       </c>
       <c r="B188">
-        <v>1911.282</v>
-      </c>
-      <c r="C188">
-        <v>2391</v>
+        <v>1103.643</v>
       </c>
       <c r="D188">
         <v>91</v>
@@ -4443,13 +3999,10 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46294.94791666666</v>
+        <v>46297.94791666666</v>
       </c>
       <c r="B189">
-        <v>1946.201</v>
-      </c>
-      <c r="C189">
-        <v>2446</v>
+        <v>1121.369</v>
       </c>
       <c r="D189">
         <v>92</v>
@@ -4460,13 +4013,10 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46294.95833333334</v>
+        <v>46297.95833333334</v>
       </c>
       <c r="B190">
-        <v>2140.719</v>
-      </c>
-      <c r="C190">
-        <v>2443</v>
+        <v>915.669</v>
       </c>
       <c r="D190">
         <v>93</v>
@@ -4477,13 +4027,10 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46294.96875</v>
+        <v>46297.96875</v>
       </c>
       <c r="B191">
-        <v>2168.914</v>
-      </c>
-      <c r="C191">
-        <v>2442</v>
+        <v>944.554</v>
       </c>
       <c r="D191">
         <v>94</v>
@@ -4494,13 +4041,10 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46294.97916666666</v>
+        <v>46297.97916666666</v>
       </c>
       <c r="B192">
-        <v>2189.252</v>
-      </c>
-      <c r="C192">
-        <v>2412</v>
+        <v>970.269</v>
       </c>
       <c r="D192">
         <v>95</v>
@@ -4511,13 +4055,10 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46294.98958333334</v>
+        <v>46297.98958333334</v>
       </c>
       <c r="B193">
-        <v>2206.647</v>
-      </c>
-      <c r="C193">
-        <v>2351</v>
+        <v>999.78</v>
       </c>
       <c r="D193">
         <v>96</v>
@@ -4528,13 +4069,10 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="2">
-        <v>46295</v>
+        <v>46298</v>
       </c>
       <c r="B194">
-        <v>2172.625</v>
-      </c>
-      <c r="C194">
-        <v>2329</v>
+        <v>942.974</v>
       </c>
       <c r="D194">
         <v>1</v>
@@ -4545,13 +4083,10 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="2">
-        <v>46295.01041666666</v>
+        <v>46298.01041666666</v>
       </c>
       <c r="B195">
-        <v>2181.188</v>
-      </c>
-      <c r="C195">
-        <v>2344</v>
+        <v>965.169</v>
       </c>
       <c r="D195">
         <v>2</v>
@@ -4562,13 +4097,10 @@
     </row>
     <row r="196" spans="1:5">
       <c r="A196" s="2">
-        <v>46295.02083333334</v>
+        <v>46298.02083333334</v>
       </c>
       <c r="B196">
-        <v>2185.609</v>
-      </c>
-      <c r="C196">
-        <v>2321</v>
+        <v>979.8440000000001</v>
       </c>
       <c r="D196">
         <v>3</v>
@@ -4579,13 +4111,10 @@
     </row>
     <row r="197" spans="1:5">
       <c r="A197" s="2">
-        <v>46295.03125</v>
+        <v>46298.03125</v>
       </c>
       <c r="B197">
-        <v>2184.25</v>
-      </c>
-      <c r="C197">
-        <v>2285</v>
+        <v>991.799</v>
       </c>
       <c r="D197">
         <v>4</v>
@@ -4596,13 +4125,10 @@
     </row>
     <row r="198" spans="1:5">
       <c r="A198" s="2">
-        <v>46295.04166666666</v>
+        <v>46298.04166666666</v>
       </c>
       <c r="B198">
-        <v>2163.034</v>
-      </c>
-      <c r="C198">
-        <v>2237</v>
+        <v>1009.589</v>
       </c>
       <c r="D198">
         <v>5</v>
@@ -4613,13 +4139,10 @@
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="2">
-        <v>46295.05208333334</v>
+        <v>46298.05208333334</v>
       </c>
       <c r="B199">
-        <v>2147.183</v>
-      </c>
-      <c r="C199">
-        <v>2183</v>
+        <v>1020.702</v>
       </c>
       <c r="D199">
         <v>6</v>
@@ -4630,13 +4153,10 @@
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="2">
-        <v>46295.0625</v>
+        <v>46298.0625</v>
       </c>
       <c r="B200">
-        <v>2141.824</v>
-      </c>
-      <c r="C200">
-        <v>2129</v>
+        <v>1035.901</v>
       </c>
       <c r="D200">
         <v>7</v>
@@ -4647,13 +4167,10 @@
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="2">
-        <v>46295.07291666666</v>
+        <v>46298.07291666666</v>
       </c>
       <c r="B201">
-        <v>2139.716</v>
-      </c>
-      <c r="C201">
-        <v>2102</v>
+        <v>1049.011</v>
       </c>
       <c r="D201">
         <v>8</v>
@@ -4664,13 +4181,10 @@
     </row>
     <row r="202" spans="1:5">
       <c r="A202" s="2">
-        <v>46295.08333333334</v>
+        <v>46298.08333333334</v>
       </c>
       <c r="B202">
-        <v>2113.373</v>
-      </c>
-      <c r="C202">
-        <v>2092</v>
+        <v>1065.328</v>
       </c>
       <c r="D202">
         <v>9</v>
@@ -4681,13 +4195,10 @@
     </row>
     <row r="203" spans="1:5">
       <c r="A203" s="2">
-        <v>46295.09375</v>
+        <v>46298.09375</v>
       </c>
       <c r="B203">
-        <v>2099.738</v>
-      </c>
-      <c r="C203">
-        <v>2077</v>
+        <v>1060.988</v>
       </c>
       <c r="D203">
         <v>10</v>
@@ -4698,13 +4209,10 @@
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="2">
-        <v>46295.10416666666</v>
+        <v>46298.10416666666</v>
       </c>
       <c r="B204">
-        <v>2083.369</v>
-      </c>
-      <c r="C204">
-        <v>2069</v>
+        <v>1060.102</v>
       </c>
       <c r="D204">
         <v>11</v>
@@ -4715,13 +4223,10 @@
     </row>
     <row r="205" spans="1:5">
       <c r="A205" s="2">
-        <v>46295.11458333334</v>
+        <v>46298.11458333334</v>
       </c>
       <c r="B205">
-        <v>2076.811</v>
-      </c>
-      <c r="C205">
-        <v>2045</v>
+        <v>1053.509</v>
       </c>
       <c r="D205">
         <v>12</v>
@@ -4732,13 +4237,10 @@
     </row>
     <row r="206" spans="1:5">
       <c r="A206" s="2">
-        <v>46295.125</v>
+        <v>46298.125</v>
       </c>
       <c r="B206">
-        <v>2070.715</v>
-      </c>
-      <c r="C206">
-        <v>2012</v>
+        <v>1046.845</v>
       </c>
       <c r="D206">
         <v>13</v>
@@ -4749,13 +4251,10 @@
     </row>
     <row r="207" spans="1:5">
       <c r="A207" s="2">
-        <v>46295.13541666666</v>
+        <v>46298.13541666666</v>
       </c>
       <c r="B207">
-        <v>2056.833</v>
-      </c>
-      <c r="C207">
-        <v>1973</v>
+        <v>1035.005</v>
       </c>
       <c r="D207">
         <v>14</v>
@@ -4766,13 +4265,10 @@
     </row>
     <row r="208" spans="1:5">
       <c r="A208" s="2">
-        <v>46295.14583333334</v>
+        <v>46298.14583333334</v>
       </c>
       <c r="B208">
-        <v>2041.448</v>
-      </c>
-      <c r="C208">
-        <v>1929</v>
+        <v>1017.589</v>
       </c>
       <c r="D208">
         <v>15</v>
@@ -4783,13 +4279,10 @@
     </row>
     <row r="209" spans="1:5">
       <c r="A209" s="2">
-        <v>46295.15625</v>
+        <v>46298.15625</v>
       </c>
       <c r="B209">
-        <v>2018.034</v>
-      </c>
-      <c r="C209">
-        <v>1875</v>
+        <v>1005.551</v>
       </c>
       <c r="D209">
         <v>16</v>
@@ -4800,13 +4293,10 @@
     </row>
     <row r="210" spans="1:5">
       <c r="A210" s="2">
-        <v>46295.16666666666</v>
+        <v>46298.16666666666</v>
       </c>
       <c r="B210">
-        <v>1947.389</v>
-      </c>
-      <c r="C210">
-        <v>1853</v>
+        <v>991.264</v>
       </c>
       <c r="D210">
         <v>17</v>
@@ -4817,13 +4307,10 @@
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="2">
-        <v>46295.17708333334</v>
+        <v>46298.17708333334</v>
       </c>
       <c r="B211">
-        <v>1932.167</v>
-      </c>
-      <c r="C211">
-        <v>1852</v>
+        <v>952.528</v>
       </c>
       <c r="D211">
         <v>18</v>
@@ -4834,13 +4321,10 @@
     </row>
     <row r="212" spans="1:5">
       <c r="A212" s="2">
-        <v>46295.1875</v>
+        <v>46298.1875</v>
       </c>
       <c r="B212">
-        <v>1915.482</v>
-      </c>
-      <c r="C212">
-        <v>1876</v>
+        <v>928.641</v>
       </c>
       <c r="D212">
         <v>19</v>
@@ -4851,13 +4335,10 @@
     </row>
     <row r="213" spans="1:5">
       <c r="A213" s="2">
-        <v>46295.19791666666</v>
+        <v>46298.19791666666</v>
       </c>
       <c r="B213">
-        <v>1894.516</v>
-      </c>
-      <c r="C213">
-        <v>1903</v>
+        <v>907.171</v>
       </c>
       <c r="D213">
         <v>20</v>
@@ -4868,13 +4349,10 @@
     </row>
     <row r="214" spans="1:5">
       <c r="A214" s="2">
-        <v>46295.20833333334</v>
+        <v>46298.20833333334</v>
       </c>
       <c r="B214">
-        <v>1891.997</v>
-      </c>
-      <c r="C214">
-        <v>1876</v>
+        <v>879.26</v>
       </c>
       <c r="D214">
         <v>21</v>
@@ -4885,13 +4363,10 @@
     </row>
     <row r="215" spans="1:5">
       <c r="A215" s="2">
-        <v>46295.21875</v>
+        <v>46298.21875</v>
       </c>
       <c r="B215">
-        <v>1874.084</v>
-      </c>
-      <c r="C215">
-        <v>1853</v>
+        <v>853.925</v>
       </c>
       <c r="D215">
         <v>22</v>
@@ -4902,13 +4377,10 @@
     </row>
     <row r="216" spans="1:5">
       <c r="A216" s="2">
-        <v>46295.22916666666</v>
+        <v>46298.22916666666</v>
       </c>
       <c r="B216">
-        <v>1867.64</v>
-      </c>
-      <c r="C216">
-        <v>1824</v>
+        <v>825.172</v>
       </c>
       <c r="D216">
         <v>23</v>
@@ -4919,13 +4391,10 @@
     </row>
     <row r="217" spans="1:5">
       <c r="A217" s="2">
-        <v>46295.23958333334</v>
+        <v>46298.23958333334</v>
       </c>
       <c r="B217">
-        <v>1865.213</v>
-      </c>
-      <c r="C217">
-        <v>1808</v>
+        <v>802.749</v>
       </c>
       <c r="D217">
         <v>24</v>
@@ -4936,13 +4405,10 @@
     </row>
     <row r="218" spans="1:5">
       <c r="A218" s="2">
-        <v>46295.25</v>
+        <v>46298.25</v>
       </c>
       <c r="B218">
-        <v>1860.216</v>
-      </c>
-      <c r="C218">
-        <v>1796</v>
+        <v>782.0359999999999</v>
       </c>
       <c r="D218">
         <v>25</v>
@@ -4953,13 +4419,10 @@
     </row>
     <row r="219" spans="1:5">
       <c r="A219" s="2">
-        <v>46295.26041666666</v>
+        <v>46298.26041666666</v>
       </c>
       <c r="B219">
-        <v>1847.021</v>
-      </c>
-      <c r="C219">
-        <v>1773</v>
+        <v>758.566</v>
       </c>
       <c r="D219">
         <v>26</v>
@@ -4970,13 +4433,10 @@
     </row>
     <row r="220" spans="1:5">
       <c r="A220" s="2">
-        <v>46295.27083333334</v>
+        <v>46298.27083333334</v>
       </c>
       <c r="B220">
-        <v>1856.64</v>
-      </c>
-      <c r="C220">
-        <v>1747</v>
+        <v>728.301</v>
       </c>
       <c r="D220">
         <v>27</v>
@@ -4987,13 +4447,10 @@
     </row>
     <row r="221" spans="1:5">
       <c r="A221" s="2">
-        <v>46295.28125</v>
+        <v>46298.28125</v>
       </c>
       <c r="B221">
-        <v>1840.933</v>
-      </c>
-      <c r="C221">
-        <v>1697</v>
+        <v>703.16</v>
       </c>
       <c r="D221">
         <v>28</v>
@@ -5004,13 +4461,10 @@
     </row>
     <row r="222" spans="1:5">
       <c r="A222" s="2">
-        <v>46295.29166666666</v>
+        <v>46298.29166666666</v>
       </c>
       <c r="B222">
-        <v>1836.052</v>
-      </c>
-      <c r="C222">
-        <v>1602</v>
+        <v>654.216</v>
       </c>
       <c r="D222">
         <v>29</v>
@@ -5021,13 +4475,10 @@
     </row>
     <row r="223" spans="1:5">
       <c r="A223" s="2">
-        <v>46295.30208333334</v>
+        <v>46298.30208333334</v>
       </c>
       <c r="B223">
-        <v>1803.743</v>
-      </c>
-      <c r="C223">
-        <v>1490</v>
+        <v>620.548</v>
       </c>
       <c r="D223">
         <v>30</v>
@@ -5038,13 +4489,10 @@
     </row>
     <row r="224" spans="1:5">
       <c r="A224" s="2">
-        <v>46295.3125</v>
+        <v>46298.3125</v>
       </c>
       <c r="B224">
-        <v>1757.275</v>
-      </c>
-      <c r="C224">
-        <v>1318</v>
+        <v>585.443</v>
       </c>
       <c r="D224">
         <v>31</v>
@@ -5055,13 +4503,10 @@
     </row>
     <row r="225" spans="1:5">
       <c r="A225" s="2">
-        <v>46295.32291666666</v>
+        <v>46298.32291666666</v>
       </c>
       <c r="B225">
-        <v>1711.197</v>
-      </c>
-      <c r="C225">
-        <v>1159</v>
+        <v>545.694</v>
       </c>
       <c r="D225">
         <v>32</v>
@@ -5072,13 +4517,10 @@
     </row>
     <row r="226" spans="1:5">
       <c r="A226" s="2">
-        <v>46295.33333333334</v>
+        <v>46298.33333333334</v>
       </c>
       <c r="B226">
-        <v>1602.262</v>
-      </c>
-      <c r="C226">
-        <v>1015</v>
+        <v>518.378</v>
       </c>
       <c r="D226">
         <v>33</v>
@@ -5089,13 +4531,10 @@
     </row>
     <row r="227" spans="1:5">
       <c r="A227" s="2">
-        <v>46295.34375</v>
+        <v>46298.34375</v>
       </c>
       <c r="B227">
-        <v>1563.826</v>
-      </c>
-      <c r="C227">
-        <v>1017</v>
+        <v>472.635</v>
       </c>
       <c r="D227">
         <v>34</v>
@@ -5106,13 +4545,10 @@
     </row>
     <row r="228" spans="1:5">
       <c r="A228" s="2">
-        <v>46295.35416666666</v>
+        <v>46298.35416666666</v>
       </c>
       <c r="B228">
-        <v>1539.275</v>
-      </c>
-      <c r="C228">
-        <v>976</v>
+        <v>443.653</v>
       </c>
       <c r="D228">
         <v>35</v>
@@ -5123,13 +4559,10 @@
     </row>
     <row r="229" spans="1:5">
       <c r="A229" s="2">
-        <v>46295.36458333334</v>
+        <v>46298.36458333334</v>
       </c>
       <c r="B229">
-        <v>1520.451</v>
-      </c>
-      <c r="C229">
-        <v>961</v>
+        <v>393.648</v>
       </c>
       <c r="D229">
         <v>36</v>
@@ -5140,13 +4573,10 @@
     </row>
     <row r="230" spans="1:5">
       <c r="A230" s="2">
-        <v>46295.375</v>
+        <v>46298.375</v>
       </c>
       <c r="B230">
-        <v>1606.825</v>
-      </c>
-      <c r="C230">
-        <v>980</v>
+        <v>447.66</v>
       </c>
       <c r="D230">
         <v>37</v>
@@ -5157,13 +4587,10 @@
     </row>
     <row r="231" spans="1:5">
       <c r="A231" s="2">
-        <v>46295.38541666666</v>
+        <v>46298.38541666666</v>
       </c>
       <c r="B231">
-        <v>1605.192</v>
-      </c>
-      <c r="C231">
-        <v>1087</v>
+        <v>430.364</v>
       </c>
       <c r="D231">
         <v>38</v>
@@ -5174,13 +4601,10 @@
     </row>
     <row r="232" spans="1:5">
       <c r="A232" s="2">
-        <v>46295.39583333334</v>
+        <v>46298.39583333334</v>
       </c>
       <c r="B232">
-        <v>1617.596</v>
-      </c>
-      <c r="C232">
-        <v>1232</v>
+        <v>417.057</v>
       </c>
       <c r="D232">
         <v>39</v>
@@ -5191,10 +4615,10 @@
     </row>
     <row r="233" spans="1:5">
       <c r="A233" s="2">
-        <v>46295.40625</v>
+        <v>46298.40625</v>
       </c>
       <c r="B233">
-        <v>1633.477</v>
+        <v>403.557</v>
       </c>
       <c r="D233">
         <v>40</v>
@@ -5205,10 +4629,10 @@
     </row>
     <row r="234" spans="1:5">
       <c r="A234" s="2">
-        <v>46295.41666666666</v>
+        <v>46298.41666666666</v>
       </c>
       <c r="B234">
-        <v>1668.897</v>
+        <v>392.084</v>
       </c>
       <c r="D234">
         <v>41</v>
@@ -5219,10 +4643,10 @@
     </row>
     <row r="235" spans="1:5">
       <c r="A235" s="2">
-        <v>46295.42708333334</v>
+        <v>46298.42708333334</v>
       </c>
       <c r="B235">
-        <v>1701.437</v>
+        <v>383.8</v>
       </c>
       <c r="D235">
         <v>42</v>
@@ -5233,10 +4657,10 @@
     </row>
     <row r="236" spans="1:5">
       <c r="A236" s="2">
-        <v>46295.4375</v>
+        <v>46298.4375</v>
       </c>
       <c r="B236">
-        <v>1735.653</v>
+        <v>374.776</v>
       </c>
       <c r="D236">
         <v>43</v>
@@ -5247,10 +4671,10 @@
     </row>
     <row r="237" spans="1:5">
       <c r="A237" s="2">
-        <v>46295.44791666666</v>
+        <v>46298.44791666666</v>
       </c>
       <c r="B237">
-        <v>1767.671</v>
+        <v>366.253</v>
       </c>
       <c r="D237">
         <v>44</v>
@@ -5261,10 +4685,10 @@
     </row>
     <row r="238" spans="1:5">
       <c r="A238" s="2">
-        <v>46295.45833333334</v>
+        <v>46298.45833333334</v>
       </c>
       <c r="B238">
-        <v>1789.801</v>
+        <v>363.32</v>
       </c>
       <c r="D238">
         <v>45</v>
@@ -5275,10 +4699,10 @@
     </row>
     <row r="239" spans="1:5">
       <c r="A239" s="2">
-        <v>46295.46875</v>
+        <v>46298.46875</v>
       </c>
       <c r="B239">
-        <v>1791.689</v>
+        <v>348.634</v>
       </c>
       <c r="D239">
         <v>46</v>
@@ -5289,10 +4713,10 @@
     </row>
     <row r="240" spans="1:5">
       <c r="A240" s="2">
-        <v>46295.47916666666</v>
+        <v>46298.47916666666</v>
       </c>
       <c r="B240">
-        <v>1792.339</v>
+        <v>334.558</v>
       </c>
       <c r="D240">
         <v>47</v>
@@ -5303,10 +4727,10 @@
     </row>
     <row r="241" spans="1:5">
       <c r="A241" s="2">
-        <v>46295.48958333334</v>
+        <v>46298.48958333334</v>
       </c>
       <c r="B241">
-        <v>1794.777</v>
+        <v>320.301</v>
       </c>
       <c r="D241">
         <v>48</v>
@@ -5317,10 +4741,10 @@
     </row>
     <row r="242" spans="1:5">
       <c r="A242" s="2">
-        <v>46295.5</v>
+        <v>46298.5</v>
       </c>
       <c r="B242">
-        <v>1801.897</v>
+        <v>254.887</v>
       </c>
       <c r="D242">
         <v>49</v>
@@ -5331,10 +4755,10 @@
     </row>
     <row r="243" spans="1:5">
       <c r="A243" s="2">
-        <v>46295.51041666666</v>
+        <v>46298.51041666666</v>
       </c>
       <c r="B243">
-        <v>1791.921</v>
+        <v>243.642</v>
       </c>
       <c r="D243">
         <v>50</v>
@@ -5345,10 +4769,10 @@
     </row>
     <row r="244" spans="1:5">
       <c r="A244" s="2">
-        <v>46295.52083333334</v>
+        <v>46298.52083333334</v>
       </c>
       <c r="B244">
-        <v>1779.033</v>
+        <v>231.554</v>
       </c>
       <c r="D244">
         <v>51</v>
@@ -5359,10 +4783,10 @@
     </row>
     <row r="245" spans="1:5">
       <c r="A245" s="2">
-        <v>46295.53125</v>
+        <v>46298.53125</v>
       </c>
       <c r="B245">
-        <v>1762.108</v>
+        <v>219.447</v>
       </c>
       <c r="D245">
         <v>52</v>
@@ -5373,10 +4797,10 @@
     </row>
     <row r="246" spans="1:5">
       <c r="A246" s="2">
-        <v>46295.54166666666</v>
+        <v>46298.54166666666</v>
       </c>
       <c r="B246">
-        <v>1734.363</v>
+        <v>205.56</v>
       </c>
       <c r="D246">
         <v>53</v>
@@ -5387,10 +4811,10 @@
     </row>
     <row r="247" spans="1:5">
       <c r="A247" s="2">
-        <v>46295.55208333334</v>
+        <v>46298.55208333334</v>
       </c>
       <c r="B247">
-        <v>1722.668</v>
+        <v>199.357</v>
       </c>
       <c r="D247">
         <v>54</v>
@@ -5401,10 +4825,10 @@
     </row>
     <row r="248" spans="1:5">
       <c r="A248" s="2">
-        <v>46295.5625</v>
+        <v>46298.5625</v>
       </c>
       <c r="B248">
-        <v>1711.41</v>
+        <v>193.083</v>
       </c>
       <c r="D248">
         <v>55</v>
@@ -5415,10 +4839,10 @@
     </row>
     <row r="249" spans="1:5">
       <c r="A249" s="2">
-        <v>46295.57291666666</v>
+        <v>46298.57291666666</v>
       </c>
       <c r="B249">
-        <v>1700.932</v>
+        <v>186.846</v>
       </c>
       <c r="D249">
         <v>56</v>
@@ -5429,10 +4853,10 @@
     </row>
     <row r="250" spans="1:5">
       <c r="A250" s="2">
-        <v>46295.58333333334</v>
+        <v>46298.58333333334</v>
       </c>
       <c r="B250">
-        <v>1695.419</v>
+        <v>181.712</v>
       </c>
       <c r="D250">
         <v>57</v>
@@ -5443,10 +4867,10 @@
     </row>
     <row r="251" spans="1:5">
       <c r="A251" s="2">
-        <v>46295.59375</v>
+        <v>46298.59375</v>
       </c>
       <c r="B251">
-        <v>1686.035</v>
+        <v>177.135</v>
       </c>
       <c r="D251">
         <v>58</v>
@@ -5457,10 +4881,10 @@
     </row>
     <row r="252" spans="1:5">
       <c r="A252" s="2">
-        <v>46295.60416666666</v>
+        <v>46298.60416666666</v>
       </c>
       <c r="B252">
-        <v>1675.828</v>
+        <v>171.385</v>
       </c>
       <c r="D252">
         <v>59</v>
@@ -5471,10 +4895,10 @@
     </row>
     <row r="253" spans="1:5">
       <c r="A253" s="2">
-        <v>46295.61458333334</v>
+        <v>46298.61458333334</v>
       </c>
       <c r="B253">
-        <v>1666.704</v>
+        <v>166.232</v>
       </c>
       <c r="D253">
         <v>60</v>
@@ -5485,10 +4909,10 @@
     </row>
     <row r="254" spans="1:5">
       <c r="A254" s="2">
-        <v>46295.625</v>
+        <v>46298.625</v>
       </c>
       <c r="B254">
-        <v>1632.653</v>
+        <v>147.934</v>
       </c>
       <c r="D254">
         <v>61</v>
@@ -5499,10 +4923,10 @@
     </row>
     <row r="255" spans="1:5">
       <c r="A255" s="2">
-        <v>46295.63541666666</v>
+        <v>46298.63541666666</v>
       </c>
       <c r="B255">
-        <v>1612.646</v>
+        <v>142.534</v>
       </c>
       <c r="D255">
         <v>62</v>
@@ -5513,10 +4937,10 @@
     </row>
     <row r="256" spans="1:5">
       <c r="A256" s="2">
-        <v>46295.64583333334</v>
+        <v>46298.64583333334</v>
       </c>
       <c r="B256">
-        <v>1592.616</v>
+        <v>136.829</v>
       </c>
       <c r="D256">
         <v>63</v>
@@ -5527,10 +4951,10 @@
     </row>
     <row r="257" spans="1:5">
       <c r="A257" s="2">
-        <v>46295.65625</v>
+        <v>46298.65625</v>
       </c>
       <c r="B257">
-        <v>1571.786</v>
+        <v>131.117</v>
       </c>
       <c r="D257">
         <v>64</v>
@@ -5541,10 +4965,10 @@
     </row>
     <row r="258" spans="1:5">
       <c r="A258" s="2">
-        <v>46295.66666666666</v>
+        <v>46298.66666666666</v>
       </c>
       <c r="B258">
-        <v>1521.933</v>
+        <v>123.305</v>
       </c>
       <c r="D258">
         <v>65</v>
@@ -5555,10 +4979,10 @@
     </row>
     <row r="259" spans="1:5">
       <c r="A259" s="2">
-        <v>46295.67708333334</v>
+        <v>46298.67708333334</v>
       </c>
       <c r="B259">
-        <v>1475.39</v>
+        <v>117.841</v>
       </c>
       <c r="D259">
         <v>66</v>
@@ -5569,10 +4993,10 @@
     </row>
     <row r="260" spans="1:5">
       <c r="A260" s="2">
-        <v>46295.6875</v>
+        <v>46298.6875</v>
       </c>
       <c r="B260">
-        <v>1425.059</v>
+        <v>112.669</v>
       </c>
       <c r="D260">
         <v>67</v>
@@ -5583,10 +5007,10 @@
     </row>
     <row r="261" spans="1:5">
       <c r="A261" s="2">
-        <v>46295.69791666666</v>
+        <v>46298.69791666666</v>
       </c>
       <c r="B261">
-        <v>1375.403</v>
+        <v>107.339</v>
       </c>
       <c r="D261">
         <v>68</v>
@@ -5597,10 +5021,10 @@
     </row>
     <row r="262" spans="1:5">
       <c r="A262" s="2">
-        <v>46295.70833333334</v>
+        <v>46298.70833333334</v>
       </c>
       <c r="B262">
-        <v>1250.616</v>
+        <v>106.343</v>
       </c>
       <c r="D262">
         <v>69</v>
@@ -5611,10 +5035,10 @@
     </row>
     <row r="263" spans="1:5">
       <c r="A263" s="2">
-        <v>46295.71875</v>
+        <v>46298.71875</v>
       </c>
       <c r="B263">
-        <v>1218.031</v>
+        <v>104.483</v>
       </c>
       <c r="D263">
         <v>70</v>
@@ -5625,10 +5049,10 @@
     </row>
     <row r="264" spans="1:5">
       <c r="A264" s="2">
-        <v>46295.72916666666</v>
+        <v>46298.72916666666</v>
       </c>
       <c r="B264">
-        <v>1187.421</v>
+        <v>103.26</v>
       </c>
       <c r="D264">
         <v>71</v>
@@ -5639,10 +5063,10 @@
     </row>
     <row r="265" spans="1:5">
       <c r="A265" s="2">
-        <v>46295.73958333334</v>
+        <v>46298.73958333334</v>
       </c>
       <c r="B265">
-        <v>1161.974</v>
+        <v>102.016</v>
       </c>
       <c r="D265">
         <v>72</v>
@@ -5653,10 +5077,10 @@
     </row>
     <row r="266" spans="1:5">
       <c r="A266" s="2">
-        <v>46295.75</v>
+        <v>46298.75</v>
       </c>
       <c r="B266">
-        <v>1141.301</v>
+        <v>101.053</v>
       </c>
       <c r="D266">
         <v>73</v>
@@ -5667,10 +5091,10 @@
     </row>
     <row r="267" spans="1:5">
       <c r="A267" s="2">
-        <v>46295.76041666666</v>
+        <v>46298.76041666666</v>
       </c>
       <c r="B267">
-        <v>1138.113</v>
+        <v>98.565</v>
       </c>
       <c r="D267">
         <v>74</v>
@@ -5681,10 +5105,10 @@
     </row>
     <row r="268" spans="1:5">
       <c r="A268" s="2">
-        <v>46295.77083333334</v>
+        <v>46298.77083333334</v>
       </c>
       <c r="B268">
-        <v>1135.339</v>
+        <v>96.61799999999999</v>
       </c>
       <c r="D268">
         <v>75</v>
@@ -5695,10 +5119,10 @@
     </row>
     <row r="269" spans="1:5">
       <c r="A269" s="2">
-        <v>46295.78125</v>
+        <v>46298.78125</v>
       </c>
       <c r="B269">
-        <v>1129.314</v>
+        <v>94.639</v>
       </c>
       <c r="D269">
         <v>76</v>
@@ -5709,10 +5133,10 @@
     </row>
     <row r="270" spans="1:5">
       <c r="A270" s="2">
-        <v>46295.79166666666</v>
+        <v>46298.79166666666</v>
       </c>
       <c r="B270">
-        <v>1127.232</v>
+        <v>93.69799999999999</v>
       </c>
       <c r="D270">
         <v>77</v>
@@ -5723,10 +5147,10 @@
     </row>
     <row r="271" spans="1:5">
       <c r="A271" s="2">
-        <v>46295.80208333334</v>
+        <v>46298.80208333334</v>
       </c>
       <c r="B271">
-        <v>1135.236</v>
+        <v>93.331</v>
       </c>
       <c r="D271">
         <v>78</v>
@@ -5737,10 +5161,10 @@
     </row>
     <row r="272" spans="1:5">
       <c r="A272" s="2">
-        <v>46295.8125</v>
+        <v>46298.8125</v>
       </c>
       <c r="B272">
-        <v>1144.96</v>
+        <v>92.53</v>
       </c>
       <c r="D272">
         <v>79</v>
@@ -5751,10 +5175,10 @@
     </row>
     <row r="273" spans="1:5">
       <c r="A273" s="2">
-        <v>46295.82291666666</v>
+        <v>46298.82291666666</v>
       </c>
       <c r="B273">
-        <v>1154.996</v>
+        <v>92.17400000000001</v>
       </c>
       <c r="D273">
         <v>80</v>
@@ -5765,10 +5189,10 @@
     </row>
     <row r="274" spans="1:5">
       <c r="A274" s="2">
-        <v>46295.83333333334</v>
+        <v>46298.83333333334</v>
       </c>
       <c r="B274">
-        <v>1172.885</v>
+        <v>93.95999999999999</v>
       </c>
       <c r="D274">
         <v>81</v>
@@ -5779,10 +5203,10 @@
     </row>
     <row r="275" spans="1:5">
       <c r="A275" s="2">
-        <v>46295.84375</v>
+        <v>46298.84375</v>
       </c>
       <c r="B275">
-        <v>1182.145</v>
+        <v>94.212</v>
       </c>
       <c r="D275">
         <v>82</v>
@@ -5793,10 +5217,10 @@
     </row>
     <row r="276" spans="1:5">
       <c r="A276" s="2">
-        <v>46295.85416666666</v>
+        <v>46298.85416666666</v>
       </c>
       <c r="B276">
-        <v>1191.908</v>
+        <v>95.617</v>
       </c>
       <c r="D276">
         <v>83</v>
@@ -5807,10 +5231,10 @@
     </row>
     <row r="277" spans="1:5">
       <c r="A277" s="2">
-        <v>46295.86458333334</v>
+        <v>46298.86458333334</v>
       </c>
       <c r="B277">
-        <v>1201.264</v>
+        <v>97.15900000000001</v>
       </c>
       <c r="D277">
         <v>84</v>
@@ -5821,10 +5245,10 @@
     </row>
     <row r="278" spans="1:5">
       <c r="A278" s="2">
-        <v>46295.875</v>
+        <v>46298.875</v>
       </c>
       <c r="B278">
-        <v>1339.527</v>
+        <v>98.065</v>
       </c>
       <c r="D278">
         <v>85</v>
@@ -5835,10 +5259,10 @@
     </row>
     <row r="279" spans="1:5">
       <c r="A279" s="2">
-        <v>46295.88541666666</v>
+        <v>46298.88541666666</v>
       </c>
       <c r="B279">
-        <v>1367.562</v>
+        <v>100.403</v>
       </c>
       <c r="D279">
         <v>86</v>
@@ -5849,10 +5273,10 @@
     </row>
     <row r="280" spans="1:5">
       <c r="A280" s="2">
-        <v>46295.89583333334</v>
+        <v>46298.89583333334</v>
       </c>
       <c r="B280">
-        <v>1391.827</v>
+        <v>102.086</v>
       </c>
       <c r="D280">
         <v>87</v>
@@ -5863,10 +5287,10 @@
     </row>
     <row r="281" spans="1:5">
       <c r="A281" s="2">
-        <v>46295.90625</v>
+        <v>46298.90625</v>
       </c>
       <c r="B281">
-        <v>1415.457</v>
+        <v>104.682</v>
       </c>
       <c r="D281">
         <v>88</v>
@@ -5877,10 +5301,10 @@
     </row>
     <row r="282" spans="1:5">
       <c r="A282" s="2">
-        <v>46295.91666666666</v>
+        <v>46298.91666666666</v>
       </c>
       <c r="B282">
-        <v>1454.113</v>
+        <v>115.698</v>
       </c>
       <c r="D282">
         <v>89</v>
@@ -5891,10 +5315,10 @@
     </row>
     <row r="283" spans="1:5">
       <c r="A283" s="2">
-        <v>46295.92708333334</v>
+        <v>46298.92708333334</v>
       </c>
       <c r="B283">
-        <v>1491.151</v>
+        <v>118.11</v>
       </c>
       <c r="D283">
         <v>90</v>
@@ -5905,10 +5329,10 @@
     </row>
     <row r="284" spans="1:5">
       <c r="A284" s="2">
-        <v>46295.9375</v>
+        <v>46298.9375</v>
       </c>
       <c r="B284">
-        <v>1528.111</v>
+        <v>120.912</v>
       </c>
       <c r="D284">
         <v>91</v>
@@ -5919,10 +5343,10 @@
     </row>
     <row r="285" spans="1:5">
       <c r="A285" s="2">
-        <v>46295.94791666666</v>
+        <v>46298.94791666666</v>
       </c>
       <c r="B285">
-        <v>1560.86</v>
+        <v>123.747</v>
       </c>
       <c r="D285">
         <v>92</v>

--- a/data_fetching/Entsoe/Wind_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Wind_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,582 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>01.10.20261</t>
-  </si>
-  <si>
-    <t>01.10.20262</t>
-  </si>
-  <si>
-    <t>01.10.20263</t>
-  </si>
-  <si>
-    <t>01.10.20264</t>
-  </si>
-  <si>
-    <t>01.10.20265</t>
-  </si>
-  <si>
-    <t>01.10.20266</t>
-  </si>
-  <si>
-    <t>01.10.20267</t>
-  </si>
-  <si>
-    <t>01.10.20268</t>
-  </si>
-  <si>
-    <t>01.10.20269</t>
-  </si>
-  <si>
-    <t>01.10.202610</t>
-  </si>
-  <si>
-    <t>01.10.202611</t>
-  </si>
-  <si>
-    <t>01.10.202612</t>
-  </si>
-  <si>
-    <t>01.10.202613</t>
-  </si>
-  <si>
-    <t>01.10.202614</t>
-  </si>
-  <si>
-    <t>01.10.202615</t>
-  </si>
-  <si>
-    <t>01.10.202616</t>
-  </si>
-  <si>
-    <t>01.10.202617</t>
-  </si>
-  <si>
-    <t>01.10.202618</t>
-  </si>
-  <si>
-    <t>01.10.202619</t>
-  </si>
-  <si>
-    <t>01.10.202620</t>
-  </si>
-  <si>
-    <t>01.10.202621</t>
-  </si>
-  <si>
-    <t>01.10.202622</t>
-  </si>
-  <si>
-    <t>01.10.202623</t>
-  </si>
-  <si>
-    <t>01.10.202624</t>
-  </si>
-  <si>
-    <t>01.10.202625</t>
-  </si>
-  <si>
-    <t>01.10.202626</t>
-  </si>
-  <si>
-    <t>01.10.202627</t>
-  </si>
-  <si>
-    <t>01.10.202628</t>
-  </si>
-  <si>
-    <t>01.10.202629</t>
-  </si>
-  <si>
-    <t>01.10.202630</t>
-  </si>
-  <si>
-    <t>01.10.202631</t>
-  </si>
-  <si>
-    <t>01.10.202632</t>
-  </si>
-  <si>
-    <t>01.10.202633</t>
-  </si>
-  <si>
-    <t>01.10.202634</t>
-  </si>
-  <si>
-    <t>01.10.202635</t>
-  </si>
-  <si>
-    <t>01.10.202636</t>
-  </si>
-  <si>
-    <t>01.10.202637</t>
-  </si>
-  <si>
-    <t>01.10.202638</t>
-  </si>
-  <si>
-    <t>01.10.202639</t>
-  </si>
-  <si>
-    <t>01.10.202640</t>
-  </si>
-  <si>
-    <t>01.10.202641</t>
-  </si>
-  <si>
-    <t>01.10.202642</t>
-  </si>
-  <si>
-    <t>01.10.202643</t>
-  </si>
-  <si>
-    <t>01.10.202644</t>
-  </si>
-  <si>
-    <t>01.10.202645</t>
-  </si>
-  <si>
-    <t>01.10.202646</t>
-  </si>
-  <si>
-    <t>01.10.202647</t>
-  </si>
-  <si>
-    <t>01.10.202648</t>
-  </si>
-  <si>
-    <t>01.10.202649</t>
-  </si>
-  <si>
-    <t>01.10.202650</t>
-  </si>
-  <si>
-    <t>01.10.202651</t>
-  </si>
-  <si>
-    <t>01.10.202652</t>
-  </si>
-  <si>
-    <t>01.10.202653</t>
-  </si>
-  <si>
-    <t>01.10.202654</t>
-  </si>
-  <si>
-    <t>01.10.202655</t>
-  </si>
-  <si>
-    <t>01.10.202656</t>
-  </si>
-  <si>
-    <t>01.10.202657</t>
-  </si>
-  <si>
-    <t>01.10.202658</t>
-  </si>
-  <si>
-    <t>01.10.202659</t>
-  </si>
-  <si>
-    <t>01.10.202660</t>
-  </si>
-  <si>
-    <t>01.10.202661</t>
-  </si>
-  <si>
-    <t>01.10.202662</t>
-  </si>
-  <si>
-    <t>01.10.202663</t>
-  </si>
-  <si>
-    <t>01.10.202664</t>
-  </si>
-  <si>
-    <t>01.10.202665</t>
-  </si>
-  <si>
-    <t>01.10.202666</t>
-  </si>
-  <si>
-    <t>01.10.202667</t>
-  </si>
-  <si>
-    <t>01.10.202668</t>
-  </si>
-  <si>
-    <t>01.10.202669</t>
-  </si>
-  <si>
-    <t>01.10.202670</t>
-  </si>
-  <si>
-    <t>01.10.202671</t>
-  </si>
-  <si>
-    <t>01.10.202672</t>
-  </si>
-  <si>
-    <t>01.10.202673</t>
-  </si>
-  <si>
-    <t>01.10.202674</t>
-  </si>
-  <si>
-    <t>01.10.202675</t>
-  </si>
-  <si>
-    <t>01.10.202676</t>
-  </si>
-  <si>
-    <t>01.10.202677</t>
-  </si>
-  <si>
-    <t>01.10.202678</t>
-  </si>
-  <si>
-    <t>01.10.202679</t>
-  </si>
-  <si>
-    <t>01.10.202680</t>
-  </si>
-  <si>
-    <t>01.10.202681</t>
-  </si>
-  <si>
-    <t>01.10.202682</t>
-  </si>
-  <si>
-    <t>01.10.202683</t>
-  </si>
-  <si>
-    <t>01.10.202684</t>
-  </si>
-  <si>
-    <t>01.10.202685</t>
-  </si>
-  <si>
-    <t>01.10.202686</t>
-  </si>
-  <si>
-    <t>01.10.202687</t>
-  </si>
-  <si>
-    <t>01.10.202688</t>
-  </si>
-  <si>
-    <t>01.10.202689</t>
-  </si>
-  <si>
-    <t>01.10.202690</t>
-  </si>
-  <si>
-    <t>01.10.202691</t>
-  </si>
-  <si>
-    <t>01.10.202692</t>
-  </si>
-  <si>
-    <t>01.10.202693</t>
-  </si>
-  <si>
-    <t>01.10.202694</t>
-  </si>
-  <si>
-    <t>01.10.202695</t>
-  </si>
-  <si>
-    <t>01.10.202696</t>
-  </si>
-  <si>
-    <t>02.10.20261</t>
-  </si>
-  <si>
-    <t>02.10.20262</t>
-  </si>
-  <si>
-    <t>02.10.20263</t>
-  </si>
-  <si>
-    <t>02.10.20264</t>
-  </si>
-  <si>
-    <t>02.10.20265</t>
-  </si>
-  <si>
-    <t>02.10.20266</t>
-  </si>
-  <si>
-    <t>02.10.20267</t>
-  </si>
-  <si>
-    <t>02.10.20268</t>
-  </si>
-  <si>
-    <t>02.10.20269</t>
-  </si>
-  <si>
-    <t>02.10.202610</t>
-  </si>
-  <si>
-    <t>02.10.202611</t>
-  </si>
-  <si>
-    <t>02.10.202612</t>
-  </si>
-  <si>
-    <t>02.10.202613</t>
-  </si>
-  <si>
-    <t>02.10.202614</t>
-  </si>
-  <si>
-    <t>02.10.202615</t>
-  </si>
-  <si>
-    <t>02.10.202616</t>
-  </si>
-  <si>
-    <t>02.10.202617</t>
-  </si>
-  <si>
-    <t>02.10.202618</t>
-  </si>
-  <si>
-    <t>02.10.202619</t>
-  </si>
-  <si>
-    <t>02.10.202620</t>
-  </si>
-  <si>
-    <t>02.10.202621</t>
-  </si>
-  <si>
-    <t>02.10.202622</t>
-  </si>
-  <si>
-    <t>02.10.202623</t>
-  </si>
-  <si>
-    <t>02.10.202624</t>
-  </si>
-  <si>
-    <t>02.10.202625</t>
-  </si>
-  <si>
-    <t>02.10.202626</t>
-  </si>
-  <si>
-    <t>02.10.202627</t>
-  </si>
-  <si>
-    <t>02.10.202628</t>
-  </si>
-  <si>
-    <t>02.10.202629</t>
-  </si>
-  <si>
-    <t>02.10.202630</t>
-  </si>
-  <si>
-    <t>02.10.202631</t>
-  </si>
-  <si>
-    <t>02.10.202632</t>
-  </si>
-  <si>
-    <t>02.10.202633</t>
-  </si>
-  <si>
-    <t>02.10.202634</t>
-  </si>
-  <si>
-    <t>02.10.202635</t>
-  </si>
-  <si>
-    <t>02.10.202636</t>
-  </si>
-  <si>
-    <t>02.10.202637</t>
-  </si>
-  <si>
-    <t>02.10.202638</t>
-  </si>
-  <si>
-    <t>02.10.202639</t>
-  </si>
-  <si>
-    <t>02.10.202640</t>
-  </si>
-  <si>
-    <t>02.10.202641</t>
-  </si>
-  <si>
-    <t>02.10.202642</t>
-  </si>
-  <si>
-    <t>02.10.202643</t>
-  </si>
-  <si>
-    <t>02.10.202644</t>
-  </si>
-  <si>
-    <t>02.10.202645</t>
-  </si>
-  <si>
-    <t>02.10.202646</t>
-  </si>
-  <si>
-    <t>02.10.202647</t>
-  </si>
-  <si>
-    <t>02.10.202648</t>
-  </si>
-  <si>
-    <t>02.10.202649</t>
-  </si>
-  <si>
-    <t>02.10.202650</t>
-  </si>
-  <si>
-    <t>02.10.202651</t>
-  </si>
-  <si>
-    <t>02.10.202652</t>
-  </si>
-  <si>
-    <t>02.10.202653</t>
-  </si>
-  <si>
-    <t>02.10.202654</t>
-  </si>
-  <si>
-    <t>02.10.202655</t>
-  </si>
-  <si>
-    <t>02.10.202656</t>
-  </si>
-  <si>
-    <t>02.10.202657</t>
-  </si>
-  <si>
-    <t>02.10.202658</t>
-  </si>
-  <si>
-    <t>02.10.202659</t>
-  </si>
-  <si>
-    <t>02.10.202660</t>
-  </si>
-  <si>
-    <t>02.10.202661</t>
-  </si>
-  <si>
-    <t>02.10.202662</t>
-  </si>
-  <si>
-    <t>02.10.202663</t>
-  </si>
-  <si>
-    <t>02.10.202664</t>
-  </si>
-  <si>
-    <t>02.10.202665</t>
-  </si>
-  <si>
-    <t>02.10.202666</t>
-  </si>
-  <si>
-    <t>02.10.202667</t>
-  </si>
-  <si>
-    <t>02.10.202668</t>
-  </si>
-  <si>
-    <t>02.10.202669</t>
-  </si>
-  <si>
-    <t>02.10.202670</t>
-  </si>
-  <si>
-    <t>02.10.202671</t>
-  </si>
-  <si>
-    <t>02.10.202672</t>
-  </si>
-  <si>
-    <t>02.10.202673</t>
-  </si>
-  <si>
-    <t>02.10.202674</t>
-  </si>
-  <si>
-    <t>02.10.202675</t>
-  </si>
-  <si>
-    <t>02.10.202676</t>
-  </si>
-  <si>
-    <t>02.10.202677</t>
-  </si>
-  <si>
-    <t>02.10.202678</t>
-  </si>
-  <si>
-    <t>02.10.202679</t>
-  </si>
-  <si>
-    <t>02.10.202680</t>
-  </si>
-  <si>
-    <t>02.10.202681</t>
-  </si>
-  <si>
-    <t>02.10.202682</t>
-  </si>
-  <si>
-    <t>02.10.202683</t>
-  </si>
-  <si>
-    <t>02.10.202684</t>
-  </si>
-  <si>
-    <t>02.10.202685</t>
-  </si>
-  <si>
-    <t>02.10.202686</t>
-  </si>
-  <si>
-    <t>02.10.202687</t>
-  </si>
-  <si>
-    <t>02.10.202688</t>
-  </si>
-  <si>
-    <t>02.10.202689</t>
-  </si>
-  <si>
-    <t>02.10.202690</t>
-  </si>
-  <si>
-    <t>02.10.202691</t>
-  </si>
-  <si>
-    <t>02.10.202692</t>
-  </si>
-  <si>
-    <t>02.10.202693</t>
-  </si>
-  <si>
-    <t>02.10.202694</t>
-  </si>
-  <si>
-    <t>02.10.202695</t>
-  </si>
-  <si>
-    <t>02.10.202696</t>
-  </si>
-  <si>
     <t>03.10.20261</t>
   </si>
   <si>
@@ -881,6 +305,294 @@
   </si>
   <si>
     <t>03.10.202692</t>
+  </si>
+  <si>
+    <t>03.10.202693</t>
+  </si>
+  <si>
+    <t>03.10.202694</t>
+  </si>
+  <si>
+    <t>03.10.202695</t>
+  </si>
+  <si>
+    <t>03.10.202696</t>
+  </si>
+  <si>
+    <t>04.10.20261</t>
+  </si>
+  <si>
+    <t>04.10.20262</t>
+  </si>
+  <si>
+    <t>04.10.20263</t>
+  </si>
+  <si>
+    <t>04.10.20264</t>
+  </si>
+  <si>
+    <t>04.10.20265</t>
+  </si>
+  <si>
+    <t>04.10.20266</t>
+  </si>
+  <si>
+    <t>04.10.20267</t>
+  </si>
+  <si>
+    <t>04.10.20268</t>
+  </si>
+  <si>
+    <t>04.10.20269</t>
+  </si>
+  <si>
+    <t>04.10.202610</t>
+  </si>
+  <si>
+    <t>04.10.202611</t>
+  </si>
+  <si>
+    <t>04.10.202612</t>
+  </si>
+  <si>
+    <t>04.10.202613</t>
+  </si>
+  <si>
+    <t>04.10.202614</t>
+  </si>
+  <si>
+    <t>04.10.202615</t>
+  </si>
+  <si>
+    <t>04.10.202616</t>
+  </si>
+  <si>
+    <t>04.10.202617</t>
+  </si>
+  <si>
+    <t>04.10.202618</t>
+  </si>
+  <si>
+    <t>04.10.202619</t>
+  </si>
+  <si>
+    <t>04.10.202620</t>
+  </si>
+  <si>
+    <t>04.10.202621</t>
+  </si>
+  <si>
+    <t>04.10.202622</t>
+  </si>
+  <si>
+    <t>04.10.202623</t>
+  </si>
+  <si>
+    <t>04.10.202624</t>
+  </si>
+  <si>
+    <t>04.10.202625</t>
+  </si>
+  <si>
+    <t>04.10.202626</t>
+  </si>
+  <si>
+    <t>04.10.202627</t>
+  </si>
+  <si>
+    <t>04.10.202628</t>
+  </si>
+  <si>
+    <t>04.10.202629</t>
+  </si>
+  <si>
+    <t>04.10.202630</t>
+  </si>
+  <si>
+    <t>04.10.202631</t>
+  </si>
+  <si>
+    <t>04.10.202632</t>
+  </si>
+  <si>
+    <t>04.10.202633</t>
+  </si>
+  <si>
+    <t>04.10.202634</t>
+  </si>
+  <si>
+    <t>04.10.202635</t>
+  </si>
+  <si>
+    <t>04.10.202636</t>
+  </si>
+  <si>
+    <t>04.10.202637</t>
+  </si>
+  <si>
+    <t>04.10.202638</t>
+  </si>
+  <si>
+    <t>04.10.202639</t>
+  </si>
+  <si>
+    <t>04.10.202640</t>
+  </si>
+  <si>
+    <t>04.10.202641</t>
+  </si>
+  <si>
+    <t>04.10.202642</t>
+  </si>
+  <si>
+    <t>04.10.202643</t>
+  </si>
+  <si>
+    <t>04.10.202644</t>
+  </si>
+  <si>
+    <t>04.10.202645</t>
+  </si>
+  <si>
+    <t>04.10.202646</t>
+  </si>
+  <si>
+    <t>04.10.202647</t>
+  </si>
+  <si>
+    <t>04.10.202648</t>
+  </si>
+  <si>
+    <t>04.10.202649</t>
+  </si>
+  <si>
+    <t>04.10.202650</t>
+  </si>
+  <si>
+    <t>04.10.202651</t>
+  </si>
+  <si>
+    <t>04.10.202652</t>
+  </si>
+  <si>
+    <t>04.10.202653</t>
+  </si>
+  <si>
+    <t>04.10.202654</t>
+  </si>
+  <si>
+    <t>04.10.202655</t>
+  </si>
+  <si>
+    <t>04.10.202656</t>
+  </si>
+  <si>
+    <t>04.10.202657</t>
+  </si>
+  <si>
+    <t>04.10.202658</t>
+  </si>
+  <si>
+    <t>04.10.202659</t>
+  </si>
+  <si>
+    <t>04.10.202660</t>
+  </si>
+  <si>
+    <t>04.10.202661</t>
+  </si>
+  <si>
+    <t>04.10.202662</t>
+  </si>
+  <si>
+    <t>04.10.202663</t>
+  </si>
+  <si>
+    <t>04.10.202664</t>
+  </si>
+  <si>
+    <t>04.10.202665</t>
+  </si>
+  <si>
+    <t>04.10.202666</t>
+  </si>
+  <si>
+    <t>04.10.202667</t>
+  </si>
+  <si>
+    <t>04.10.202668</t>
+  </si>
+  <si>
+    <t>04.10.202669</t>
+  </si>
+  <si>
+    <t>04.10.202670</t>
+  </si>
+  <si>
+    <t>04.10.202671</t>
+  </si>
+  <si>
+    <t>04.10.202672</t>
+  </si>
+  <si>
+    <t>04.10.202673</t>
+  </si>
+  <si>
+    <t>04.10.202674</t>
+  </si>
+  <si>
+    <t>04.10.202675</t>
+  </si>
+  <si>
+    <t>04.10.202676</t>
+  </si>
+  <si>
+    <t>04.10.202677</t>
+  </si>
+  <si>
+    <t>04.10.202678</t>
+  </si>
+  <si>
+    <t>04.10.202679</t>
+  </si>
+  <si>
+    <t>04.10.202680</t>
+  </si>
+  <si>
+    <t>04.10.202681</t>
+  </si>
+  <si>
+    <t>04.10.202682</t>
+  </si>
+  <si>
+    <t>04.10.202683</t>
+  </si>
+  <si>
+    <t>04.10.202684</t>
+  </si>
+  <si>
+    <t>04.10.202685</t>
+  </si>
+  <si>
+    <t>04.10.202686</t>
+  </si>
+  <si>
+    <t>04.10.202687</t>
+  </si>
+  <si>
+    <t>04.10.202688</t>
+  </si>
+  <si>
+    <t>04.10.202689</t>
+  </si>
+  <si>
+    <t>04.10.202690</t>
+  </si>
+  <si>
+    <t>04.10.202691</t>
+  </si>
+  <si>
+    <t>04.10.202692</t>
   </si>
 </sst>
 </file>
@@ -1242,7 +954,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E285"/>
+  <dimension ref="A1:E189"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1264,13 +976,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="B2">
-        <v>1678.274</v>
-      </c>
-      <c r="C2">
-        <v>1839</v>
+        <v>942.974</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1281,13 +990,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46296.01041666666</v>
+        <v>46298.01041666666</v>
       </c>
       <c r="B3">
-        <v>1703.396</v>
-      </c>
-      <c r="C3">
-        <v>1878</v>
+        <v>965.169</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1298,13 +1004,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46296.02083333334</v>
+        <v>46298.02083333334</v>
       </c>
       <c r="B4">
-        <v>1724.146</v>
-      </c>
-      <c r="C4">
-        <v>1902</v>
+        <v>979.8440000000001</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1315,13 +1018,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46296.03125</v>
+        <v>46298.03125</v>
       </c>
       <c r="B5">
-        <v>1751.373</v>
-      </c>
-      <c r="C5">
-        <v>1907</v>
+        <v>991.799</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1332,13 +1032,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46296.04166666666</v>
+        <v>46298.04166666666</v>
       </c>
       <c r="B6">
-        <v>1773.456</v>
-      </c>
-      <c r="C6">
-        <v>1929</v>
+        <v>1009.589</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1349,13 +1046,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46296.05208333334</v>
+        <v>46298.05208333334</v>
       </c>
       <c r="B7">
-        <v>1779.911</v>
-      </c>
-      <c r="C7">
-        <v>1935</v>
+        <v>1020.702</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1366,13 +1060,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46296.0625</v>
+        <v>46298.0625</v>
       </c>
       <c r="B8">
-        <v>1785.458</v>
-      </c>
-      <c r="C8">
-        <v>1914</v>
+        <v>1035.901</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1383,13 +1074,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46296.07291666666</v>
+        <v>46298.07291666666</v>
       </c>
       <c r="B9">
-        <v>1788.682</v>
-      </c>
-      <c r="C9">
-        <v>1907</v>
+        <v>1049.011</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1400,13 +1088,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46296.08333333334</v>
+        <v>46298.08333333334</v>
       </c>
       <c r="B10">
-        <v>1807.223</v>
-      </c>
-      <c r="C10">
-        <v>1885</v>
+        <v>1065.328</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1417,13 +1102,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46296.09375</v>
+        <v>46298.09375</v>
       </c>
       <c r="B11">
-        <v>1798.226</v>
-      </c>
-      <c r="C11">
-        <v>1829</v>
+        <v>1060.988</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1434,13 +1116,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46296.10416666666</v>
+        <v>46298.10416666666</v>
       </c>
       <c r="B12">
-        <v>1790.263</v>
-      </c>
-      <c r="C12">
-        <v>1766</v>
+        <v>1060.102</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1451,13 +1130,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46296.11458333334</v>
+        <v>46298.11458333334</v>
       </c>
       <c r="B13">
-        <v>1778.057</v>
-      </c>
-      <c r="C13">
-        <v>1733</v>
+        <v>1053.509</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1468,13 +1144,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46296.125</v>
+        <v>46298.125</v>
       </c>
       <c r="B14">
-        <v>1769.066</v>
-      </c>
-      <c r="C14">
-        <v>1707</v>
+        <v>1046.845</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1485,13 +1158,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46296.13541666666</v>
+        <v>46298.13541666666</v>
       </c>
       <c r="B15">
-        <v>1755.422</v>
-      </c>
-      <c r="C15">
-        <v>1663</v>
+        <v>1035.005</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1502,13 +1172,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46296.14583333334</v>
+        <v>46298.14583333334</v>
       </c>
       <c r="B16">
-        <v>1722.393</v>
-      </c>
-      <c r="C16">
-        <v>1604</v>
+        <v>1017.589</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1519,13 +1186,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46296.15625</v>
+        <v>46298.15625</v>
       </c>
       <c r="B17">
-        <v>1712.858</v>
-      </c>
-      <c r="C17">
-        <v>1578</v>
+        <v>1005.551</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1536,13 +1200,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46296.16666666666</v>
+        <v>46298.16666666666</v>
       </c>
       <c r="B18">
-        <v>1699.841</v>
-      </c>
-      <c r="C18">
-        <v>1593</v>
+        <v>991.264</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1553,13 +1214,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46296.17708333334</v>
+        <v>46298.17708333334</v>
       </c>
       <c r="B19">
-        <v>1693.53</v>
-      </c>
-      <c r="C19">
-        <v>1623</v>
+        <v>952.528</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1570,13 +1228,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46296.1875</v>
+        <v>46298.1875</v>
       </c>
       <c r="B20">
-        <v>1690.354</v>
-      </c>
-      <c r="C20">
-        <v>1657</v>
+        <v>928.641</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1587,13 +1242,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46296.19791666666</v>
+        <v>46298.19791666666</v>
       </c>
       <c r="B21">
-        <v>1684.677</v>
-      </c>
-      <c r="C21">
-        <v>1666</v>
+        <v>907.171</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1604,13 +1256,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46296.20833333334</v>
+        <v>46298.20833333334</v>
       </c>
       <c r="B22">
-        <v>1673.045</v>
-      </c>
-      <c r="C22">
-        <v>1650</v>
+        <v>879.26</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1621,13 +1270,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46296.21875</v>
+        <v>46298.21875</v>
       </c>
       <c r="B23">
-        <v>1667.355</v>
-      </c>
-      <c r="C23">
-        <v>1634</v>
+        <v>853.925</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1638,13 +1284,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46296.22916666666</v>
+        <v>46298.22916666666</v>
       </c>
       <c r="B24">
-        <v>1666.063</v>
-      </c>
-      <c r="C24">
-        <v>1632</v>
+        <v>825.172</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1655,13 +1298,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46296.23958333334</v>
+        <v>46298.23958333334</v>
       </c>
       <c r="B25">
-        <v>1671.15</v>
-      </c>
-      <c r="C25">
-        <v>1628</v>
+        <v>802.749</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1672,13 +1312,10 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46296.25</v>
+        <v>46298.25</v>
       </c>
       <c r="B26">
-        <v>1657.133</v>
-      </c>
-      <c r="C26">
-        <v>1620</v>
+        <v>782.0359999999999</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1689,13 +1326,10 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46296.26041666666</v>
+        <v>46298.26041666666</v>
       </c>
       <c r="B27">
-        <v>1651.613</v>
-      </c>
-      <c r="C27">
-        <v>1603</v>
+        <v>758.566</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1706,13 +1340,10 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46296.27083333334</v>
+        <v>46298.27083333334</v>
       </c>
       <c r="B28">
-        <v>1650.568</v>
-      </c>
-      <c r="C28">
-        <v>1575</v>
+        <v>728.301</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1723,13 +1354,10 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46296.28125</v>
+        <v>46298.28125</v>
       </c>
       <c r="B29">
-        <v>1649.712</v>
-      </c>
-      <c r="C29">
-        <v>1530</v>
+        <v>703.16</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1740,13 +1368,10 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46296.29166666666</v>
+        <v>46298.29166666666</v>
       </c>
       <c r="B30">
-        <v>1635.703</v>
-      </c>
-      <c r="C30">
-        <v>1466</v>
+        <v>654.216</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1757,13 +1382,10 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46296.30208333334</v>
+        <v>46298.30208333334</v>
       </c>
       <c r="B31">
-        <v>1617.586</v>
-      </c>
-      <c r="C31">
-        <v>1403</v>
+        <v>620.548</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1774,13 +1396,10 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46296.3125</v>
+        <v>46298.3125</v>
       </c>
       <c r="B32">
-        <v>1595.415</v>
-      </c>
-      <c r="C32">
-        <v>1293</v>
+        <v>585.443</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1791,13 +1410,10 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46296.32291666666</v>
+        <v>46298.32291666666</v>
       </c>
       <c r="B33">
-        <v>1568.631</v>
-      </c>
-      <c r="C33">
-        <v>1170</v>
+        <v>545.694</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1808,13 +1424,10 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46296.33333333334</v>
+        <v>46298.33333333334</v>
       </c>
       <c r="B34">
-        <v>1532.782</v>
-      </c>
-      <c r="C34">
-        <v>1045</v>
+        <v>518.378</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1825,13 +1438,10 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46296.34375</v>
+        <v>46298.34375</v>
       </c>
       <c r="B35">
-        <v>1507.541</v>
-      </c>
-      <c r="C35">
-        <v>955</v>
+        <v>472.635</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1842,13 +1452,10 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46296.35416666666</v>
+        <v>46298.35416666666</v>
       </c>
       <c r="B36">
-        <v>1486.574</v>
-      </c>
-      <c r="C36">
-        <v>895</v>
+        <v>443.653</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1859,13 +1466,10 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46296.36458333334</v>
+        <v>46298.36458333334</v>
       </c>
       <c r="B37">
-        <v>1455.013</v>
-      </c>
-      <c r="C37">
-        <v>905</v>
+        <v>393.648</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1876,13 +1480,10 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46296.375</v>
+        <v>46298.375</v>
       </c>
       <c r="B38">
-        <v>1488.324</v>
-      </c>
-      <c r="C38">
-        <v>939</v>
+        <v>447.66</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1893,13 +1494,10 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46296.38541666666</v>
+        <v>46298.38541666666</v>
       </c>
       <c r="B39">
-        <v>1485.857</v>
-      </c>
-      <c r="C39">
-        <v>1043</v>
+        <v>430.364</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1910,13 +1508,10 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46296.39583333334</v>
+        <v>46298.39583333334</v>
       </c>
       <c r="B40">
-        <v>1503.142</v>
-      </c>
-      <c r="C40">
-        <v>1223</v>
+        <v>417.057</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1927,10 +1522,10 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46296.40625</v>
+        <v>46298.40625</v>
       </c>
       <c r="B41">
-        <v>1514.136</v>
+        <v>403.557</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1941,10 +1536,10 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46296.41666666666</v>
+        <v>46298.41666666666</v>
       </c>
       <c r="B42">
-        <v>1643.661</v>
+        <v>392.084</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1955,10 +1550,10 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46296.42708333334</v>
+        <v>46298.42708333334</v>
       </c>
       <c r="B43">
-        <v>1694.287</v>
+        <v>383.8</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1969,10 +1564,10 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46296.4375</v>
+        <v>46298.4375</v>
       </c>
       <c r="B44">
-        <v>1740.061</v>
+        <v>374.776</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1983,10 +1578,10 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46296.44791666666</v>
+        <v>46298.44791666666</v>
       </c>
       <c r="B45">
-        <v>1780.383</v>
+        <v>366.253</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1997,10 +1592,10 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46296.45833333334</v>
+        <v>46298.45833333334</v>
       </c>
       <c r="B46">
-        <v>1851.816</v>
+        <v>363.32</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -2011,10 +1606,10 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46296.46875</v>
+        <v>46298.46875</v>
       </c>
       <c r="B47">
-        <v>1879.383</v>
+        <v>348.634</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -2025,10 +1620,10 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46296.47916666666</v>
+        <v>46298.47916666666</v>
       </c>
       <c r="B48">
-        <v>1906.988</v>
+        <v>334.558</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -2039,10 +1634,10 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46296.48958333334</v>
+        <v>46298.48958333334</v>
       </c>
       <c r="B49">
-        <v>1935.521</v>
+        <v>320.301</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -2053,10 +1648,10 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46296.5</v>
+        <v>46298.5</v>
       </c>
       <c r="B50">
-        <v>1968.91</v>
+        <v>254.887</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -2067,10 +1662,10 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46296.51041666666</v>
+        <v>46298.51041666666</v>
       </c>
       <c r="B51">
-        <v>1965.115</v>
+        <v>243.642</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -2081,10 +1676,10 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46296.52083333334</v>
+        <v>46298.52083333334</v>
       </c>
       <c r="B52">
-        <v>1960.669</v>
+        <v>231.554</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -2095,10 +1690,10 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46296.53125</v>
+        <v>46298.53125</v>
       </c>
       <c r="B53">
-        <v>1954.766</v>
+        <v>219.447</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -2109,10 +1704,10 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46296.54166666666</v>
+        <v>46298.54166666666</v>
       </c>
       <c r="B54">
-        <v>1947.503</v>
+        <v>205.56</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -2123,10 +1718,10 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46296.55208333334</v>
+        <v>46298.55208333334</v>
       </c>
       <c r="B55">
-        <v>1948.46</v>
+        <v>199.357</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -2137,10 +1732,10 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46296.5625</v>
+        <v>46298.5625</v>
       </c>
       <c r="B56">
-        <v>1949.897</v>
+        <v>193.083</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -2151,10 +1746,10 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46296.57291666666</v>
+        <v>46298.57291666666</v>
       </c>
       <c r="B57">
-        <v>1949.933</v>
+        <v>186.846</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -2165,10 +1760,10 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46296.58333333334</v>
+        <v>46298.58333333334</v>
       </c>
       <c r="B58">
-        <v>1887.666</v>
+        <v>181.712</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -2179,10 +1774,10 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46296.59375</v>
+        <v>46298.59375</v>
       </c>
       <c r="B59">
-        <v>1884.363</v>
+        <v>177.135</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -2193,10 +1788,10 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46296.60416666666</v>
+        <v>46298.60416666666</v>
       </c>
       <c r="B60">
-        <v>1882.854</v>
+        <v>171.385</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -2207,10 +1802,10 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46296.61458333334</v>
+        <v>46298.61458333334</v>
       </c>
       <c r="B61">
-        <v>1881.944</v>
+        <v>166.232</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2221,10 +1816,10 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46296.625</v>
+        <v>46298.625</v>
       </c>
       <c r="B62">
-        <v>1867.84</v>
+        <v>147.934</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2235,10 +1830,10 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46296.63541666666</v>
+        <v>46298.63541666666</v>
       </c>
       <c r="B63">
-        <v>1850.808</v>
+        <v>142.534</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2249,10 +1844,10 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46296.64583333334</v>
+        <v>46298.64583333334</v>
       </c>
       <c r="B64">
-        <v>1833.121</v>
+        <v>136.829</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2263,10 +1858,10 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46296.65625</v>
+        <v>46298.65625</v>
       </c>
       <c r="B65">
-        <v>1814.512</v>
+        <v>131.117</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2277,10 +1872,10 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46296.66666666666</v>
+        <v>46298.66666666666</v>
       </c>
       <c r="B66">
-        <v>1768.116</v>
+        <v>123.305</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2291,10 +1886,10 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46296.67708333334</v>
+        <v>46298.67708333334</v>
       </c>
       <c r="B67">
-        <v>1716.381</v>
+        <v>117.841</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2305,10 +1900,10 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46296.6875</v>
+        <v>46298.6875</v>
       </c>
       <c r="B68">
-        <v>1662.02</v>
+        <v>112.669</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2319,10 +1914,10 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46296.69791666666</v>
+        <v>46298.69791666666</v>
       </c>
       <c r="B69">
-        <v>1606.042</v>
+        <v>107.339</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2333,10 +1928,10 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46296.70833333334</v>
+        <v>46298.70833333334</v>
       </c>
       <c r="B70">
-        <v>1454.495</v>
+        <v>106.343</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2347,10 +1942,10 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46296.71875</v>
+        <v>46298.71875</v>
       </c>
       <c r="B71">
-        <v>1431.521</v>
+        <v>104.483</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2361,10 +1956,10 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46296.72916666666</v>
+        <v>46298.72916666666</v>
       </c>
       <c r="B72">
-        <v>1405.618</v>
+        <v>103.26</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2375,10 +1970,10 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46296.73958333334</v>
+        <v>46298.73958333334</v>
       </c>
       <c r="B73">
-        <v>1387.977</v>
+        <v>102.016</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2389,10 +1984,10 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46296.75</v>
+        <v>46298.75</v>
       </c>
       <c r="B74">
-        <v>1384.683</v>
+        <v>101.053</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2403,10 +1998,10 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46296.76041666666</v>
+        <v>46298.76041666666</v>
       </c>
       <c r="B75">
-        <v>1408.492</v>
+        <v>98.565</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2417,10 +2012,10 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46296.77083333334</v>
+        <v>46298.77083333334</v>
       </c>
       <c r="B76">
-        <v>1431.575</v>
+        <v>96.61799999999999</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2431,10 +2026,10 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46296.78125</v>
+        <v>46298.78125</v>
       </c>
       <c r="B77">
-        <v>1455.183</v>
+        <v>94.639</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2445,10 +2040,10 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46296.79166666666</v>
+        <v>46298.79166666666</v>
       </c>
       <c r="B78">
-        <v>1500.092</v>
+        <v>93.69799999999999</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2459,10 +2054,10 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46296.80208333334</v>
+        <v>46298.80208333334</v>
       </c>
       <c r="B79">
-        <v>1536.463</v>
+        <v>93.331</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2473,10 +2068,10 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46296.8125</v>
+        <v>46298.8125</v>
       </c>
       <c r="B80">
-        <v>1570.361</v>
+        <v>92.53</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2487,10 +2082,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46296.82291666666</v>
+        <v>46298.82291666666</v>
       </c>
       <c r="B81">
-        <v>1604.135</v>
+        <v>92.17400000000001</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2501,10 +2096,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46296.83333333334</v>
+        <v>46298.83333333334</v>
       </c>
       <c r="B82">
-        <v>1752.332</v>
+        <v>93.95999999999999</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2515,10 +2110,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46296.84375</v>
+        <v>46298.84375</v>
       </c>
       <c r="B83">
-        <v>1780.827</v>
+        <v>94.212</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2529,10 +2124,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46296.85416666666</v>
+        <v>46298.85416666666</v>
       </c>
       <c r="B84">
-        <v>1807.111</v>
+        <v>95.617</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2543,10 +2138,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46296.86458333334</v>
+        <v>46298.86458333334</v>
       </c>
       <c r="B85">
-        <v>1835.884</v>
+        <v>97.15900000000001</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2557,10 +2152,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46296.875</v>
+        <v>46298.875</v>
       </c>
       <c r="B86">
-        <v>1872.539</v>
+        <v>98.065</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2571,10 +2166,10 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46296.88541666666</v>
+        <v>46298.88541666666</v>
       </c>
       <c r="B87">
-        <v>1906.901</v>
+        <v>100.403</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2585,10 +2180,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46296.89583333334</v>
+        <v>46298.89583333334</v>
       </c>
       <c r="B88">
-        <v>1938.885</v>
+        <v>102.086</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2599,10 +2194,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46296.90625</v>
+        <v>46298.90625</v>
       </c>
       <c r="B89">
-        <v>1970.223</v>
+        <v>104.682</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2613,10 +2208,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46296.91666666666</v>
+        <v>46298.91666666666</v>
       </c>
       <c r="B90">
-        <v>2005.884</v>
+        <v>115.698</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2627,10 +2222,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46296.92708333334</v>
+        <v>46298.92708333334</v>
       </c>
       <c r="B91">
-        <v>2030.121</v>
+        <v>118.11</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2641,10 +2236,10 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46296.9375</v>
+        <v>46298.9375</v>
       </c>
       <c r="B92">
-        <v>2055.298</v>
+        <v>120.912</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2655,10 +2250,10 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46296.94791666666</v>
+        <v>46298.94791666666</v>
       </c>
       <c r="B93">
-        <v>2079.918</v>
+        <v>123.747</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2669,10 +2264,10 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46296.95833333334</v>
+        <v>46298.95833333334</v>
       </c>
       <c r="B94">
-        <v>1974.346</v>
+        <v>125.466</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2683,10 +2278,10 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46296.96875</v>
+        <v>46298.96875</v>
       </c>
       <c r="B95">
-        <v>1987.017</v>
+        <v>129.809</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2697,10 +2292,10 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46296.97916666666</v>
+        <v>46298.97916666666</v>
       </c>
       <c r="B96">
-        <v>2005.331</v>
+        <v>133.665</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2711,10 +2306,10 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46296.98958333334</v>
+        <v>46298.98958333334</v>
       </c>
       <c r="B97">
-        <v>2053.493</v>
+        <v>137.936</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2725,10 +2320,10 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46297</v>
+        <v>46299</v>
       </c>
       <c r="B98">
-        <v>2166.343</v>
+        <v>169.102</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2739,10 +2334,10 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46297.01041666666</v>
+        <v>46299.01041666666</v>
       </c>
       <c r="B99">
-        <v>2173.917</v>
+        <v>172.962</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2753,10 +2348,10 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46297.02083333334</v>
+        <v>46299.02083333334</v>
       </c>
       <c r="B100">
-        <v>2176.448</v>
+        <v>176.779</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2767,10 +2362,10 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46297.03125</v>
+        <v>46299.03125</v>
       </c>
       <c r="B101">
-        <v>2181.03</v>
+        <v>181.373</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2781,10 +2376,10 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46297.04166666666</v>
+        <v>46299.04166666666</v>
       </c>
       <c r="B102">
-        <v>2191.031</v>
+        <v>183.045</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2795,10 +2390,10 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46297.05208333334</v>
+        <v>46299.05208333334</v>
       </c>
       <c r="B103">
-        <v>2186.818</v>
+        <v>186.526</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2809,10 +2404,10 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46297.0625</v>
+        <v>46299.0625</v>
       </c>
       <c r="B104">
-        <v>2185.927</v>
+        <v>189.143</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2823,10 +2418,10 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46297.07291666666</v>
+        <v>46299.07291666666</v>
       </c>
       <c r="B105">
-        <v>2183.097</v>
+        <v>191.974</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2837,10 +2432,10 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46297.08333333334</v>
+        <v>46299.08333333334</v>
       </c>
       <c r="B106">
-        <v>2191.57</v>
+        <v>194.656</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2851,10 +2446,10 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46297.09375</v>
+        <v>46299.09375</v>
       </c>
       <c r="B107">
-        <v>2190.983</v>
+        <v>194.437</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2865,10 +2460,10 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46297.10416666666</v>
+        <v>46299.10416666666</v>
       </c>
       <c r="B108">
-        <v>2195.916</v>
+        <v>194.639</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2879,10 +2474,10 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46297.11458333334</v>
+        <v>46299.11458333334</v>
       </c>
       <c r="B109">
-        <v>2191.348</v>
+        <v>195.502</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2893,10 +2488,10 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46297.125</v>
+        <v>46299.125</v>
       </c>
       <c r="B110">
-        <v>2188.62</v>
+        <v>194.722</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2907,10 +2502,10 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46297.13541666666</v>
+        <v>46299.13541666666</v>
       </c>
       <c r="B111">
-        <v>2188.52</v>
+        <v>194.073</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2921,10 +2516,10 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46297.14583333334</v>
+        <v>46299.14583333334</v>
       </c>
       <c r="B112">
-        <v>2187.128</v>
+        <v>193.209</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2935,10 +2530,10 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46297.15625</v>
+        <v>46299.15625</v>
       </c>
       <c r="B113">
-        <v>2187.773</v>
+        <v>192.67</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2949,10 +2544,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46297.16666666666</v>
+        <v>46299.16666666666</v>
       </c>
       <c r="B114">
-        <v>2182.637</v>
+        <v>190.491</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2963,10 +2558,10 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46297.17708333334</v>
+        <v>46299.17708333334</v>
       </c>
       <c r="B115">
-        <v>2185.718</v>
+        <v>186.937</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2977,10 +2572,10 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46297.1875</v>
+        <v>46299.1875</v>
       </c>
       <c r="B116">
-        <v>2184.986</v>
+        <v>184.025</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2991,10 +2586,10 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46297.19791666666</v>
+        <v>46299.19791666666</v>
       </c>
       <c r="B117">
-        <v>2185.382</v>
+        <v>181.203</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -3005,10 +2600,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46297.20833333334</v>
+        <v>46299.20833333334</v>
       </c>
       <c r="B118">
-        <v>2249.993</v>
+        <v>177.087</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -3019,10 +2614,10 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46297.21875</v>
+        <v>46299.21875</v>
       </c>
       <c r="B119">
-        <v>2243.439</v>
+        <v>172.726</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -3033,10 +2628,10 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46297.22916666666</v>
+        <v>46299.22916666666</v>
       </c>
       <c r="B120">
-        <v>2158.308</v>
+        <v>168.167</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3047,10 +2642,10 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46297.23958333334</v>
+        <v>46299.23958333334</v>
       </c>
       <c r="B121">
-        <v>2156.736</v>
+        <v>164.847</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3061,10 +2656,10 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46297.25</v>
+        <v>46299.25</v>
       </c>
       <c r="B122">
-        <v>2123.358</v>
+        <v>137.285</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3075,10 +2670,10 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46297.26041666666</v>
+        <v>46299.26041666666</v>
       </c>
       <c r="B123">
-        <v>2122.566</v>
+        <v>132.868</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3089,10 +2684,10 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46297.27083333334</v>
+        <v>46299.27083333334</v>
       </c>
       <c r="B124">
-        <v>2100.143</v>
+        <v>129.569</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3103,10 +2698,10 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46297.28125</v>
+        <v>46299.28125</v>
       </c>
       <c r="B125">
-        <v>2104.315</v>
+        <v>127.252</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3117,10 +2712,10 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46297.29166666666</v>
+        <v>46299.29166666666</v>
       </c>
       <c r="B126">
-        <v>2125.749</v>
+        <v>134.654</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3131,10 +2726,10 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46297.30208333334</v>
+        <v>46299.30208333334</v>
       </c>
       <c r="B127">
-        <v>2091.794</v>
+        <v>128.085</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3145,10 +2740,10 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46297.3125</v>
+        <v>46299.3125</v>
       </c>
       <c r="B128">
-        <v>2047.298</v>
+        <v>113.875</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3159,10 +2754,10 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46297.32291666666</v>
+        <v>46299.32291666666</v>
       </c>
       <c r="B129">
-        <v>2012.182</v>
+        <v>110.375</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3173,10 +2768,10 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46297.33333333334</v>
+        <v>46299.33333333334</v>
       </c>
       <c r="B130">
-        <v>1909.851</v>
+        <v>111.843</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3187,10 +2782,10 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46297.34375</v>
+        <v>46299.34375</v>
       </c>
       <c r="B131">
-        <v>1886.166</v>
+        <v>109.408</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3201,10 +2796,10 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46297.35416666666</v>
+        <v>46299.35416666666</v>
       </c>
       <c r="B132">
-        <v>1875.403</v>
+        <v>107.066</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3215,10 +2810,10 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46297.36458333334</v>
+        <v>46299.36458333334</v>
       </c>
       <c r="B133">
-        <v>1855.614</v>
+        <v>104.867</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3229,10 +2824,10 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46297.375</v>
+        <v>46299.375</v>
       </c>
       <c r="B134">
-        <v>2018.482</v>
+        <v>106.428</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3243,10 +2838,10 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46297.38541666666</v>
+        <v>46299.38541666666</v>
       </c>
       <c r="B135">
-        <v>2027.749</v>
+        <v>105.175</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3257,10 +2852,10 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46297.39583333334</v>
+        <v>46299.39583333334</v>
       </c>
       <c r="B136">
-        <v>2042.092</v>
+        <v>102.986</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3271,10 +2866,10 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46297.40625</v>
+        <v>46299.40625</v>
       </c>
       <c r="B137">
-        <v>2054.338</v>
+        <v>101.164</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3285,10 +2880,10 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46297.41666666666</v>
+        <v>46299.41666666666</v>
       </c>
       <c r="B138">
-        <v>2122.165</v>
+        <v>100.088</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3299,10 +2894,10 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46297.42708333334</v>
+        <v>46299.42708333334</v>
       </c>
       <c r="B139">
-        <v>2162.192</v>
+        <v>99.873</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3313,10 +2908,10 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46297.4375</v>
+        <v>46299.4375</v>
       </c>
       <c r="B140">
-        <v>2197.602</v>
+        <v>99.908</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3327,10 +2922,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46297.44791666666</v>
+        <v>46299.44791666666</v>
       </c>
       <c r="B141">
-        <v>2236.1</v>
+        <v>99.911</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3341,10 +2936,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46297.45833333334</v>
+        <v>46299.45833333334</v>
       </c>
       <c r="B142">
-        <v>2288.189</v>
+        <v>100.242</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3355,10 +2950,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46297.46875</v>
+        <v>46299.46875</v>
       </c>
       <c r="B143">
-        <v>2309.173</v>
+        <v>100.902</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3369,10 +2964,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46297.47916666666</v>
+        <v>46299.47916666666</v>
       </c>
       <c r="B144">
-        <v>2332.053</v>
+        <v>101.518</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3383,10 +2978,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46297.48958333334</v>
+        <v>46299.48958333334</v>
       </c>
       <c r="B145">
-        <v>2350.638</v>
+        <v>101.869</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3397,10 +2992,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46297.5</v>
+        <v>46299.5</v>
       </c>
       <c r="B146">
-        <v>2364.653</v>
+        <v>100.307</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3411,10 +3006,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46297.51041666666</v>
+        <v>46299.51041666666</v>
       </c>
       <c r="B147">
-        <v>2345.255</v>
+        <v>100.733</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3425,10 +3020,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46297.52083333334</v>
+        <v>46299.52083333334</v>
       </c>
       <c r="B148">
-        <v>2319.574</v>
+        <v>101.39</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3439,10 +3034,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46297.53125</v>
+        <v>46299.53125</v>
       </c>
       <c r="B149">
-        <v>2294.546</v>
+        <v>101.982</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3453,10 +3048,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46297.54166666666</v>
+        <v>46299.54166666666</v>
       </c>
       <c r="B150">
-        <v>2261.802</v>
+        <v>103.727</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3467,10 +3062,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46297.55208333334</v>
+        <v>46299.55208333334</v>
       </c>
       <c r="B151">
-        <v>2227.574</v>
+        <v>105.195</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3481,10 +3076,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46297.5625</v>
+        <v>46299.5625</v>
       </c>
       <c r="B152">
-        <v>2196.144</v>
+        <v>106.561</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3495,10 +3090,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46297.57291666666</v>
+        <v>46299.57291666666</v>
       </c>
       <c r="B153">
-        <v>2164.117</v>
+        <v>107.767</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3509,10 +3104,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46297.58333333334</v>
+        <v>46299.58333333334</v>
       </c>
       <c r="B154">
-        <v>2106.485</v>
+        <v>111.741</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3523,10 +3118,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46297.59375</v>
+        <v>46299.59375</v>
       </c>
       <c r="B155">
-        <v>2073.657</v>
+        <v>111.908</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3537,10 +3132,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46297.60416666666</v>
+        <v>46299.60416666666</v>
       </c>
       <c r="B156">
-        <v>2042.928</v>
+        <v>111.951</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3551,10 +3146,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46297.61458333334</v>
+        <v>46299.61458333334</v>
       </c>
       <c r="B157">
-        <v>2009.888</v>
+        <v>112.151</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3565,10 +3160,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46297.625</v>
+        <v>46299.625</v>
       </c>
       <c r="B158">
-        <v>1973.029</v>
+        <v>109.132</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3579,10 +3174,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46297.63541666666</v>
+        <v>46299.63541666666</v>
       </c>
       <c r="B159">
-        <v>1935.909</v>
+        <v>109.598</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3593,10 +3188,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46297.64583333334</v>
+        <v>46299.64583333334</v>
       </c>
       <c r="B160">
-        <v>1892.277</v>
+        <v>109.968</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3607,10 +3202,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46297.65625</v>
+        <v>46299.65625</v>
       </c>
       <c r="B161">
-        <v>1857.25</v>
+        <v>110.053</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3621,10 +3216,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46297.66666666666</v>
+        <v>46299.66666666666</v>
       </c>
       <c r="B162">
-        <v>1666.541</v>
+        <v>121.081</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -3635,10 +3230,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46297.67708333334</v>
+        <v>46299.67708333334</v>
       </c>
       <c r="B163">
-        <v>1604.161</v>
+        <v>122.384</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -3649,10 +3244,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46297.6875</v>
+        <v>46299.6875</v>
       </c>
       <c r="B164">
-        <v>1537.067</v>
+        <v>123.342</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -3663,10 +3258,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46297.69791666666</v>
+        <v>46299.69791666666</v>
       </c>
       <c r="B165">
-        <v>1473.919</v>
+        <v>124.935</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -3677,10 +3272,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46297.70833333334</v>
+        <v>46299.70833333334</v>
       </c>
       <c r="B166">
-        <v>1406.197</v>
+        <v>121.196</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -3691,10 +3286,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46297.71875</v>
+        <v>46299.71875</v>
       </c>
       <c r="B167">
-        <v>1357.281</v>
+        <v>123.975</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -3705,10 +3300,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46297.72916666666</v>
+        <v>46299.72916666666</v>
       </c>
       <c r="B168">
-        <v>1309.165</v>
+        <v>126.537</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -3719,10 +3314,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46297.73958333334</v>
+        <v>46299.73958333334</v>
       </c>
       <c r="B169">
-        <v>1263.414</v>
+        <v>129.661</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -3733,10 +3328,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46297.75</v>
+        <v>46299.75</v>
       </c>
       <c r="B170">
-        <v>1193.233</v>
+        <v>134.331</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -3747,10 +3342,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46297.76041666666</v>
+        <v>46299.76041666666</v>
       </c>
       <c r="B171">
-        <v>1162.273</v>
+        <v>139.548</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -3761,10 +3356,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46297.77083333334</v>
+        <v>46299.77083333334</v>
       </c>
       <c r="B172">
-        <v>1134.598</v>
+        <v>143.727</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -3775,10 +3370,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46297.78125</v>
+        <v>46299.78125</v>
       </c>
       <c r="B173">
-        <v>1106.035</v>
+        <v>149.084</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -3789,10 +3384,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46297.79166666666</v>
+        <v>46299.79166666666</v>
       </c>
       <c r="B174">
-        <v>1099.801</v>
+        <v>155.615</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -3803,10 +3398,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46297.80208333334</v>
+        <v>46299.80208333334</v>
       </c>
       <c r="B175">
-        <v>1081.617</v>
+        <v>163.938</v>
       </c>
       <c r="D175">
         <v>78</v>
@@ -3817,10 +3412,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46297.8125</v>
+        <v>46299.8125</v>
       </c>
       <c r="B176">
-        <v>1063.499</v>
+        <v>173.517</v>
       </c>
       <c r="D176">
         <v>79</v>
@@ -3831,10 +3426,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46297.82291666666</v>
+        <v>46299.82291666666</v>
       </c>
       <c r="B177">
-        <v>1046.388</v>
+        <v>182.073</v>
       </c>
       <c r="D177">
         <v>80</v>
@@ -3845,10 +3440,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46297.83333333334</v>
+        <v>46299.83333333334</v>
       </c>
       <c r="B178">
-        <v>1032.723</v>
+        <v>189.413</v>
       </c>
       <c r="D178">
         <v>81</v>
@@ -3859,10 +3454,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46297.84375</v>
+        <v>46299.84375</v>
       </c>
       <c r="B179">
-        <v>1023.944</v>
+        <v>193.733</v>
       </c>
       <c r="D179">
         <v>82</v>
@@ -3873,10 +3468,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46297.85416666666</v>
+        <v>46299.85416666666</v>
       </c>
       <c r="B180">
-        <v>1017.785</v>
+        <v>199.024</v>
       </c>
       <c r="D180">
         <v>83</v>
@@ -3887,10 +3482,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46297.86458333334</v>
+        <v>46299.86458333334</v>
       </c>
       <c r="B181">
-        <v>1010.78</v>
+        <v>203.507</v>
       </c>
       <c r="D181">
         <v>84</v>
@@ -3901,10 +3496,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46297.875</v>
+        <v>46299.875</v>
       </c>
       <c r="B182">
-        <v>1019.926</v>
+        <v>204.348</v>
       </c>
       <c r="D182">
         <v>85</v>
@@ -3915,10 +3510,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46297.88541666666</v>
+        <v>46299.88541666666</v>
       </c>
       <c r="B183">
-        <v>1026.423</v>
+        <v>206.27</v>
       </c>
       <c r="D183">
         <v>86</v>
@@ -3929,10 +3524,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46297.89583333334</v>
+        <v>46299.89583333334</v>
       </c>
       <c r="B184">
-        <v>1035.402</v>
+        <v>208.311</v>
       </c>
       <c r="D184">
         <v>87</v>
@@ -3943,10 +3538,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46297.90625</v>
+        <v>46299.90625</v>
       </c>
       <c r="B185">
-        <v>1043.833</v>
+        <v>209.937</v>
       </c>
       <c r="D185">
         <v>88</v>
@@ -3957,10 +3552,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46297.91666666666</v>
+        <v>46299.91666666666</v>
       </c>
       <c r="B186">
-        <v>1067.226</v>
+        <v>212.048</v>
       </c>
       <c r="D186">
         <v>89</v>
@@ -3971,10 +3566,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46297.92708333334</v>
+        <v>46299.92708333334</v>
       </c>
       <c r="B187">
-        <v>1086.232</v>
+        <v>211.211</v>
       </c>
       <c r="D187">
         <v>90</v>
@@ -3985,10 +3580,10 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46297.9375</v>
+        <v>46299.9375</v>
       </c>
       <c r="B188">
-        <v>1103.643</v>
+        <v>210.164</v>
       </c>
       <c r="D188">
         <v>91</v>
@@ -3999,1360 +3594,16 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46297.94791666666</v>
+        <v>46299.94791666666</v>
       </c>
       <c r="B189">
-        <v>1121.369</v>
+        <v>209.406</v>
       </c>
       <c r="D189">
         <v>92</v>
       </c>
       <c r="E189" t="s">
         <v>192</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5">
-      <c r="A190" s="2">
-        <v>46297.95833333334</v>
-      </c>
-      <c r="B190">
-        <v>915.669</v>
-      </c>
-      <c r="D190">
-        <v>93</v>
-      </c>
-      <c r="E190" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5">
-      <c r="A191" s="2">
-        <v>46297.96875</v>
-      </c>
-      <c r="B191">
-        <v>944.554</v>
-      </c>
-      <c r="D191">
-        <v>94</v>
-      </c>
-      <c r="E191" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5">
-      <c r="A192" s="2">
-        <v>46297.97916666666</v>
-      </c>
-      <c r="B192">
-        <v>970.269</v>
-      </c>
-      <c r="D192">
-        <v>95</v>
-      </c>
-      <c r="E192" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5">
-      <c r="A193" s="2">
-        <v>46297.98958333334</v>
-      </c>
-      <c r="B193">
-        <v>999.78</v>
-      </c>
-      <c r="D193">
-        <v>96</v>
-      </c>
-      <c r="E193" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="194" spans="1:5">
-      <c r="A194" s="2">
-        <v>46298</v>
-      </c>
-      <c r="B194">
-        <v>942.974</v>
-      </c>
-      <c r="D194">
-        <v>1</v>
-      </c>
-      <c r="E194" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5">
-      <c r="A195" s="2">
-        <v>46298.01041666666</v>
-      </c>
-      <c r="B195">
-        <v>965.169</v>
-      </c>
-      <c r="D195">
-        <v>2</v>
-      </c>
-      <c r="E195" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="196" spans="1:5">
-      <c r="A196" s="2">
-        <v>46298.02083333334</v>
-      </c>
-      <c r="B196">
-        <v>979.8440000000001</v>
-      </c>
-      <c r="D196">
-        <v>3</v>
-      </c>
-      <c r="E196" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5">
-      <c r="A197" s="2">
-        <v>46298.03125</v>
-      </c>
-      <c r="B197">
-        <v>991.799</v>
-      </c>
-      <c r="D197">
-        <v>4</v>
-      </c>
-      <c r="E197" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="198" spans="1:5">
-      <c r="A198" s="2">
-        <v>46298.04166666666</v>
-      </c>
-      <c r="B198">
-        <v>1009.589</v>
-      </c>
-      <c r="D198">
-        <v>5</v>
-      </c>
-      <c r="E198" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5">
-      <c r="A199" s="2">
-        <v>46298.05208333334</v>
-      </c>
-      <c r="B199">
-        <v>1020.702</v>
-      </c>
-      <c r="D199">
-        <v>6</v>
-      </c>
-      <c r="E199" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5">
-      <c r="A200" s="2">
-        <v>46298.0625</v>
-      </c>
-      <c r="B200">
-        <v>1035.901</v>
-      </c>
-      <c r="D200">
-        <v>7</v>
-      </c>
-      <c r="E200" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="201" spans="1:5">
-      <c r="A201" s="2">
-        <v>46298.07291666666</v>
-      </c>
-      <c r="B201">
-        <v>1049.011</v>
-      </c>
-      <c r="D201">
-        <v>8</v>
-      </c>
-      <c r="E201" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="202" spans="1:5">
-      <c r="A202" s="2">
-        <v>46298.08333333334</v>
-      </c>
-      <c r="B202">
-        <v>1065.328</v>
-      </c>
-      <c r="D202">
-        <v>9</v>
-      </c>
-      <c r="E202" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="203" spans="1:5">
-      <c r="A203" s="2">
-        <v>46298.09375</v>
-      </c>
-      <c r="B203">
-        <v>1060.988</v>
-      </c>
-      <c r="D203">
-        <v>10</v>
-      </c>
-      <c r="E203" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="204" spans="1:5">
-      <c r="A204" s="2">
-        <v>46298.10416666666</v>
-      </c>
-      <c r="B204">
-        <v>1060.102</v>
-      </c>
-      <c r="D204">
-        <v>11</v>
-      </c>
-      <c r="E204" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="205" spans="1:5">
-      <c r="A205" s="2">
-        <v>46298.11458333334</v>
-      </c>
-      <c r="B205">
-        <v>1053.509</v>
-      </c>
-      <c r="D205">
-        <v>12</v>
-      </c>
-      <c r="E205" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="206" spans="1:5">
-      <c r="A206" s="2">
-        <v>46298.125</v>
-      </c>
-      <c r="B206">
-        <v>1046.845</v>
-      </c>
-      <c r="D206">
-        <v>13</v>
-      </c>
-      <c r="E206" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="207" spans="1:5">
-      <c r="A207" s="2">
-        <v>46298.13541666666</v>
-      </c>
-      <c r="B207">
-        <v>1035.005</v>
-      </c>
-      <c r="D207">
-        <v>14</v>
-      </c>
-      <c r="E207" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="208" spans="1:5">
-      <c r="A208" s="2">
-        <v>46298.14583333334</v>
-      </c>
-      <c r="B208">
-        <v>1017.589</v>
-      </c>
-      <c r="D208">
-        <v>15</v>
-      </c>
-      <c r="E208" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="209" spans="1:5">
-      <c r="A209" s="2">
-        <v>46298.15625</v>
-      </c>
-      <c r="B209">
-        <v>1005.551</v>
-      </c>
-      <c r="D209">
-        <v>16</v>
-      </c>
-      <c r="E209" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="210" spans="1:5">
-      <c r="A210" s="2">
-        <v>46298.16666666666</v>
-      </c>
-      <c r="B210">
-        <v>991.264</v>
-      </c>
-      <c r="D210">
-        <v>17</v>
-      </c>
-      <c r="E210" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="211" spans="1:5">
-      <c r="A211" s="2">
-        <v>46298.17708333334</v>
-      </c>
-      <c r="B211">
-        <v>952.528</v>
-      </c>
-      <c r="D211">
-        <v>18</v>
-      </c>
-      <c r="E211" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="212" spans="1:5">
-      <c r="A212" s="2">
-        <v>46298.1875</v>
-      </c>
-      <c r="B212">
-        <v>928.641</v>
-      </c>
-      <c r="D212">
-        <v>19</v>
-      </c>
-      <c r="E212" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="213" spans="1:5">
-      <c r="A213" s="2">
-        <v>46298.19791666666</v>
-      </c>
-      <c r="B213">
-        <v>907.171</v>
-      </c>
-      <c r="D213">
-        <v>20</v>
-      </c>
-      <c r="E213" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="214" spans="1:5">
-      <c r="A214" s="2">
-        <v>46298.20833333334</v>
-      </c>
-      <c r="B214">
-        <v>879.26</v>
-      </c>
-      <c r="D214">
-        <v>21</v>
-      </c>
-      <c r="E214" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="215" spans="1:5">
-      <c r="A215" s="2">
-        <v>46298.21875</v>
-      </c>
-      <c r="B215">
-        <v>853.925</v>
-      </c>
-      <c r="D215">
-        <v>22</v>
-      </c>
-      <c r="E215" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="216" spans="1:5">
-      <c r="A216" s="2">
-        <v>46298.22916666666</v>
-      </c>
-      <c r="B216">
-        <v>825.172</v>
-      </c>
-      <c r="D216">
-        <v>23</v>
-      </c>
-      <c r="E216" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="217" spans="1:5">
-      <c r="A217" s="2">
-        <v>46298.23958333334</v>
-      </c>
-      <c r="B217">
-        <v>802.749</v>
-      </c>
-      <c r="D217">
-        <v>24</v>
-      </c>
-      <c r="E217" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="218" spans="1:5">
-      <c r="A218" s="2">
-        <v>46298.25</v>
-      </c>
-      <c r="B218">
-        <v>782.0359999999999</v>
-      </c>
-      <c r="D218">
-        <v>25</v>
-      </c>
-      <c r="E218" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="219" spans="1:5">
-      <c r="A219" s="2">
-        <v>46298.26041666666</v>
-      </c>
-      <c r="B219">
-        <v>758.566</v>
-      </c>
-      <c r="D219">
-        <v>26</v>
-      </c>
-      <c r="E219" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="220" spans="1:5">
-      <c r="A220" s="2">
-        <v>46298.27083333334</v>
-      </c>
-      <c r="B220">
-        <v>728.301</v>
-      </c>
-      <c r="D220">
-        <v>27</v>
-      </c>
-      <c r="E220" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="221" spans="1:5">
-      <c r="A221" s="2">
-        <v>46298.28125</v>
-      </c>
-      <c r="B221">
-        <v>703.16</v>
-      </c>
-      <c r="D221">
-        <v>28</v>
-      </c>
-      <c r="E221" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="222" spans="1:5">
-      <c r="A222" s="2">
-        <v>46298.29166666666</v>
-      </c>
-      <c r="B222">
-        <v>654.216</v>
-      </c>
-      <c r="D222">
-        <v>29</v>
-      </c>
-      <c r="E222" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="223" spans="1:5">
-      <c r="A223" s="2">
-        <v>46298.30208333334</v>
-      </c>
-      <c r="B223">
-        <v>620.548</v>
-      </c>
-      <c r="D223">
-        <v>30</v>
-      </c>
-      <c r="E223" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="224" spans="1:5">
-      <c r="A224" s="2">
-        <v>46298.3125</v>
-      </c>
-      <c r="B224">
-        <v>585.443</v>
-      </c>
-      <c r="D224">
-        <v>31</v>
-      </c>
-      <c r="E224" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="225" spans="1:5">
-      <c r="A225" s="2">
-        <v>46298.32291666666</v>
-      </c>
-      <c r="B225">
-        <v>545.694</v>
-      </c>
-      <c r="D225">
-        <v>32</v>
-      </c>
-      <c r="E225" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="226" spans="1:5">
-      <c r="A226" s="2">
-        <v>46298.33333333334</v>
-      </c>
-      <c r="B226">
-        <v>518.378</v>
-      </c>
-      <c r="D226">
-        <v>33</v>
-      </c>
-      <c r="E226" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="227" spans="1:5">
-      <c r="A227" s="2">
-        <v>46298.34375</v>
-      </c>
-      <c r="B227">
-        <v>472.635</v>
-      </c>
-      <c r="D227">
-        <v>34</v>
-      </c>
-      <c r="E227" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="228" spans="1:5">
-      <c r="A228" s="2">
-        <v>46298.35416666666</v>
-      </c>
-      <c r="B228">
-        <v>443.653</v>
-      </c>
-      <c r="D228">
-        <v>35</v>
-      </c>
-      <c r="E228" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="229" spans="1:5">
-      <c r="A229" s="2">
-        <v>46298.36458333334</v>
-      </c>
-      <c r="B229">
-        <v>393.648</v>
-      </c>
-      <c r="D229">
-        <v>36</v>
-      </c>
-      <c r="E229" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="230" spans="1:5">
-      <c r="A230" s="2">
-        <v>46298.375</v>
-      </c>
-      <c r="B230">
-        <v>447.66</v>
-      </c>
-      <c r="D230">
-        <v>37</v>
-      </c>
-      <c r="E230" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="231" spans="1:5">
-      <c r="A231" s="2">
-        <v>46298.38541666666</v>
-      </c>
-      <c r="B231">
-        <v>430.364</v>
-      </c>
-      <c r="D231">
-        <v>38</v>
-      </c>
-      <c r="E231" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="232" spans="1:5">
-      <c r="A232" s="2">
-        <v>46298.39583333334</v>
-      </c>
-      <c r="B232">
-        <v>417.057</v>
-      </c>
-      <c r="D232">
-        <v>39</v>
-      </c>
-      <c r="E232" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="233" spans="1:5">
-      <c r="A233" s="2">
-        <v>46298.40625</v>
-      </c>
-      <c r="B233">
-        <v>403.557</v>
-      </c>
-      <c r="D233">
-        <v>40</v>
-      </c>
-      <c r="E233" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="234" spans="1:5">
-      <c r="A234" s="2">
-        <v>46298.41666666666</v>
-      </c>
-      <c r="B234">
-        <v>392.084</v>
-      </c>
-      <c r="D234">
-        <v>41</v>
-      </c>
-      <c r="E234" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="235" spans="1:5">
-      <c r="A235" s="2">
-        <v>46298.42708333334</v>
-      </c>
-      <c r="B235">
-        <v>383.8</v>
-      </c>
-      <c r="D235">
-        <v>42</v>
-      </c>
-      <c r="E235" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="236" spans="1:5">
-      <c r="A236" s="2">
-        <v>46298.4375</v>
-      </c>
-      <c r="B236">
-        <v>374.776</v>
-      </c>
-      <c r="D236">
-        <v>43</v>
-      </c>
-      <c r="E236" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="237" spans="1:5">
-      <c r="A237" s="2">
-        <v>46298.44791666666</v>
-      </c>
-      <c r="B237">
-        <v>366.253</v>
-      </c>
-      <c r="D237">
-        <v>44</v>
-      </c>
-      <c r="E237" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="238" spans="1:5">
-      <c r="A238" s="2">
-        <v>46298.45833333334</v>
-      </c>
-      <c r="B238">
-        <v>363.32</v>
-      </c>
-      <c r="D238">
-        <v>45</v>
-      </c>
-      <c r="E238" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="239" spans="1:5">
-      <c r="A239" s="2">
-        <v>46298.46875</v>
-      </c>
-      <c r="B239">
-        <v>348.634</v>
-      </c>
-      <c r="D239">
-        <v>46</v>
-      </c>
-      <c r="E239" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="240" spans="1:5">
-      <c r="A240" s="2">
-        <v>46298.47916666666</v>
-      </c>
-      <c r="B240">
-        <v>334.558</v>
-      </c>
-      <c r="D240">
-        <v>47</v>
-      </c>
-      <c r="E240" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="241" spans="1:5">
-      <c r="A241" s="2">
-        <v>46298.48958333334</v>
-      </c>
-      <c r="B241">
-        <v>320.301</v>
-      </c>
-      <c r="D241">
-        <v>48</v>
-      </c>
-      <c r="E241" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="242" spans="1:5">
-      <c r="A242" s="2">
-        <v>46298.5</v>
-      </c>
-      <c r="B242">
-        <v>254.887</v>
-      </c>
-      <c r="D242">
-        <v>49</v>
-      </c>
-      <c r="E242" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="243" spans="1:5">
-      <c r="A243" s="2">
-        <v>46298.51041666666</v>
-      </c>
-      <c r="B243">
-        <v>243.642</v>
-      </c>
-      <c r="D243">
-        <v>50</v>
-      </c>
-      <c r="E243" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="244" spans="1:5">
-      <c r="A244" s="2">
-        <v>46298.52083333334</v>
-      </c>
-      <c r="B244">
-        <v>231.554</v>
-      </c>
-      <c r="D244">
-        <v>51</v>
-      </c>
-      <c r="E244" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="245" spans="1:5">
-      <c r="A245" s="2">
-        <v>46298.53125</v>
-      </c>
-      <c r="B245">
-        <v>219.447</v>
-      </c>
-      <c r="D245">
-        <v>52</v>
-      </c>
-      <c r="E245" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="246" spans="1:5">
-      <c r="A246" s="2">
-        <v>46298.54166666666</v>
-      </c>
-      <c r="B246">
-        <v>205.56</v>
-      </c>
-      <c r="D246">
-        <v>53</v>
-      </c>
-      <c r="E246" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="247" spans="1:5">
-      <c r="A247" s="2">
-        <v>46298.55208333334</v>
-      </c>
-      <c r="B247">
-        <v>199.357</v>
-      </c>
-      <c r="D247">
-        <v>54</v>
-      </c>
-      <c r="E247" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="248" spans="1:5">
-      <c r="A248" s="2">
-        <v>46298.5625</v>
-      </c>
-      <c r="B248">
-        <v>193.083</v>
-      </c>
-      <c r="D248">
-        <v>55</v>
-      </c>
-      <c r="E248" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="249" spans="1:5">
-      <c r="A249" s="2">
-        <v>46298.57291666666</v>
-      </c>
-      <c r="B249">
-        <v>186.846</v>
-      </c>
-      <c r="D249">
-        <v>56</v>
-      </c>
-      <c r="E249" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="250" spans="1:5">
-      <c r="A250" s="2">
-        <v>46298.58333333334</v>
-      </c>
-      <c r="B250">
-        <v>181.712</v>
-      </c>
-      <c r="D250">
-        <v>57</v>
-      </c>
-      <c r="E250" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="251" spans="1:5">
-      <c r="A251" s="2">
-        <v>46298.59375</v>
-      </c>
-      <c r="B251">
-        <v>177.135</v>
-      </c>
-      <c r="D251">
-        <v>58</v>
-      </c>
-      <c r="E251" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="252" spans="1:5">
-      <c r="A252" s="2">
-        <v>46298.60416666666</v>
-      </c>
-      <c r="B252">
-        <v>171.385</v>
-      </c>
-      <c r="D252">
-        <v>59</v>
-      </c>
-      <c r="E252" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="253" spans="1:5">
-      <c r="A253" s="2">
-        <v>46298.61458333334</v>
-      </c>
-      <c r="B253">
-        <v>166.232</v>
-      </c>
-      <c r="D253">
-        <v>60</v>
-      </c>
-      <c r="E253" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="254" spans="1:5">
-      <c r="A254" s="2">
-        <v>46298.625</v>
-      </c>
-      <c r="B254">
-        <v>147.934</v>
-      </c>
-      <c r="D254">
-        <v>61</v>
-      </c>
-      <c r="E254" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="255" spans="1:5">
-      <c r="A255" s="2">
-        <v>46298.63541666666</v>
-      </c>
-      <c r="B255">
-        <v>142.534</v>
-      </c>
-      <c r="D255">
-        <v>62</v>
-      </c>
-      <c r="E255" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="256" spans="1:5">
-      <c r="A256" s="2">
-        <v>46298.64583333334</v>
-      </c>
-      <c r="B256">
-        <v>136.829</v>
-      </c>
-      <c r="D256">
-        <v>63</v>
-      </c>
-      <c r="E256" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="257" spans="1:5">
-      <c r="A257" s="2">
-        <v>46298.65625</v>
-      </c>
-      <c r="B257">
-        <v>131.117</v>
-      </c>
-      <c r="D257">
-        <v>64</v>
-      </c>
-      <c r="E257" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="258" spans="1:5">
-      <c r="A258" s="2">
-        <v>46298.66666666666</v>
-      </c>
-      <c r="B258">
-        <v>123.305</v>
-      </c>
-      <c r="D258">
-        <v>65</v>
-      </c>
-      <c r="E258" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="259" spans="1:5">
-      <c r="A259" s="2">
-        <v>46298.67708333334</v>
-      </c>
-      <c r="B259">
-        <v>117.841</v>
-      </c>
-      <c r="D259">
-        <v>66</v>
-      </c>
-      <c r="E259" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="260" spans="1:5">
-      <c r="A260" s="2">
-        <v>46298.6875</v>
-      </c>
-      <c r="B260">
-        <v>112.669</v>
-      </c>
-      <c r="D260">
-        <v>67</v>
-      </c>
-      <c r="E260" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="261" spans="1:5">
-      <c r="A261" s="2">
-        <v>46298.69791666666</v>
-      </c>
-      <c r="B261">
-        <v>107.339</v>
-      </c>
-      <c r="D261">
-        <v>68</v>
-      </c>
-      <c r="E261" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="262" spans="1:5">
-      <c r="A262" s="2">
-        <v>46298.70833333334</v>
-      </c>
-      <c r="B262">
-        <v>106.343</v>
-      </c>
-      <c r="D262">
-        <v>69</v>
-      </c>
-      <c r="E262" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="263" spans="1:5">
-      <c r="A263" s="2">
-        <v>46298.71875</v>
-      </c>
-      <c r="B263">
-        <v>104.483</v>
-      </c>
-      <c r="D263">
-        <v>70</v>
-      </c>
-      <c r="E263" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="264" spans="1:5">
-      <c r="A264" s="2">
-        <v>46298.72916666666</v>
-      </c>
-      <c r="B264">
-        <v>103.26</v>
-      </c>
-      <c r="D264">
-        <v>71</v>
-      </c>
-      <c r="E264" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="265" spans="1:5">
-      <c r="A265" s="2">
-        <v>46298.73958333334</v>
-      </c>
-      <c r="B265">
-        <v>102.016</v>
-      </c>
-      <c r="D265">
-        <v>72</v>
-      </c>
-      <c r="E265" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="266" spans="1:5">
-      <c r="A266" s="2">
-        <v>46298.75</v>
-      </c>
-      <c r="B266">
-        <v>101.053</v>
-      </c>
-      <c r="D266">
-        <v>73</v>
-      </c>
-      <c r="E266" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="267" spans="1:5">
-      <c r="A267" s="2">
-        <v>46298.76041666666</v>
-      </c>
-      <c r="B267">
-        <v>98.565</v>
-      </c>
-      <c r="D267">
-        <v>74</v>
-      </c>
-      <c r="E267" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="268" spans="1:5">
-      <c r="A268" s="2">
-        <v>46298.77083333334</v>
-      </c>
-      <c r="B268">
-        <v>96.61799999999999</v>
-      </c>
-      <c r="D268">
-        <v>75</v>
-      </c>
-      <c r="E268" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="269" spans="1:5">
-      <c r="A269" s="2">
-        <v>46298.78125</v>
-      </c>
-      <c r="B269">
-        <v>94.639</v>
-      </c>
-      <c r="D269">
-        <v>76</v>
-      </c>
-      <c r="E269" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="270" spans="1:5">
-      <c r="A270" s="2">
-        <v>46298.79166666666</v>
-      </c>
-      <c r="B270">
-        <v>93.69799999999999</v>
-      </c>
-      <c r="D270">
-        <v>77</v>
-      </c>
-      <c r="E270" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="271" spans="1:5">
-      <c r="A271" s="2">
-        <v>46298.80208333334</v>
-      </c>
-      <c r="B271">
-        <v>93.331</v>
-      </c>
-      <c r="D271">
-        <v>78</v>
-      </c>
-      <c r="E271" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="272" spans="1:5">
-      <c r="A272" s="2">
-        <v>46298.8125</v>
-      </c>
-      <c r="B272">
-        <v>92.53</v>
-      </c>
-      <c r="D272">
-        <v>79</v>
-      </c>
-      <c r="E272" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="273" spans="1:5">
-      <c r="A273" s="2">
-        <v>46298.82291666666</v>
-      </c>
-      <c r="B273">
-        <v>92.17400000000001</v>
-      </c>
-      <c r="D273">
-        <v>80</v>
-      </c>
-      <c r="E273" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="274" spans="1:5">
-      <c r="A274" s="2">
-        <v>46298.83333333334</v>
-      </c>
-      <c r="B274">
-        <v>93.95999999999999</v>
-      </c>
-      <c r="D274">
-        <v>81</v>
-      </c>
-      <c r="E274" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="275" spans="1:5">
-      <c r="A275" s="2">
-        <v>46298.84375</v>
-      </c>
-      <c r="B275">
-        <v>94.212</v>
-      </c>
-      <c r="D275">
-        <v>82</v>
-      </c>
-      <c r="E275" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="276" spans="1:5">
-      <c r="A276" s="2">
-        <v>46298.85416666666</v>
-      </c>
-      <c r="B276">
-        <v>95.617</v>
-      </c>
-      <c r="D276">
-        <v>83</v>
-      </c>
-      <c r="E276" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="277" spans="1:5">
-      <c r="A277" s="2">
-        <v>46298.86458333334</v>
-      </c>
-      <c r="B277">
-        <v>97.15900000000001</v>
-      </c>
-      <c r="D277">
-        <v>84</v>
-      </c>
-      <c r="E277" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="278" spans="1:5">
-      <c r="A278" s="2">
-        <v>46298.875</v>
-      </c>
-      <c r="B278">
-        <v>98.065</v>
-      </c>
-      <c r="D278">
-        <v>85</v>
-      </c>
-      <c r="E278" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="279" spans="1:5">
-      <c r="A279" s="2">
-        <v>46298.88541666666</v>
-      </c>
-      <c r="B279">
-        <v>100.403</v>
-      </c>
-      <c r="D279">
-        <v>86</v>
-      </c>
-      <c r="E279" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="280" spans="1:5">
-      <c r="A280" s="2">
-        <v>46298.89583333334</v>
-      </c>
-      <c r="B280">
-        <v>102.086</v>
-      </c>
-      <c r="D280">
-        <v>87</v>
-      </c>
-      <c r="E280" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="281" spans="1:5">
-      <c r="A281" s="2">
-        <v>46298.90625</v>
-      </c>
-      <c r="B281">
-        <v>104.682</v>
-      </c>
-      <c r="D281">
-        <v>88</v>
-      </c>
-      <c r="E281" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="282" spans="1:5">
-      <c r="A282" s="2">
-        <v>46298.91666666666</v>
-      </c>
-      <c r="B282">
-        <v>115.698</v>
-      </c>
-      <c r="D282">
-        <v>89</v>
-      </c>
-      <c r="E282" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="283" spans="1:5">
-      <c r="A283" s="2">
-        <v>46298.92708333334</v>
-      </c>
-      <c r="B283">
-        <v>118.11</v>
-      </c>
-      <c r="D283">
-        <v>90</v>
-      </c>
-      <c r="E283" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="284" spans="1:5">
-      <c r="A284" s="2">
-        <v>46298.9375</v>
-      </c>
-      <c r="B284">
-        <v>120.912</v>
-      </c>
-      <c r="D284">
-        <v>91</v>
-      </c>
-      <c r="E284" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="285" spans="1:5">
-      <c r="A285" s="2">
-        <v>46298.94791666666</v>
-      </c>
-      <c r="B285">
-        <v>123.747</v>
-      </c>
-      <c r="D285">
-        <v>92</v>
-      </c>
-      <c r="E285" t="s">
-        <v>288</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Wind_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Wind_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="481">
   <si>
     <t>Timestamp</t>
   </si>
@@ -593,6 +593,870 @@
   </si>
   <si>
     <t>04.10.202692</t>
+  </si>
+  <si>
+    <t>04.10.202693</t>
+  </si>
+  <si>
+    <t>04.10.202694</t>
+  </si>
+  <si>
+    <t>04.10.202695</t>
+  </si>
+  <si>
+    <t>04.10.202696</t>
+  </si>
+  <si>
+    <t>05.10.20261</t>
+  </si>
+  <si>
+    <t>05.10.20262</t>
+  </si>
+  <si>
+    <t>05.10.20263</t>
+  </si>
+  <si>
+    <t>05.10.20264</t>
+  </si>
+  <si>
+    <t>05.10.20265</t>
+  </si>
+  <si>
+    <t>05.10.20266</t>
+  </si>
+  <si>
+    <t>05.10.20267</t>
+  </si>
+  <si>
+    <t>05.10.20268</t>
+  </si>
+  <si>
+    <t>05.10.20269</t>
+  </si>
+  <si>
+    <t>05.10.202610</t>
+  </si>
+  <si>
+    <t>05.10.202611</t>
+  </si>
+  <si>
+    <t>05.10.202612</t>
+  </si>
+  <si>
+    <t>05.10.202613</t>
+  </si>
+  <si>
+    <t>05.10.202614</t>
+  </si>
+  <si>
+    <t>05.10.202615</t>
+  </si>
+  <si>
+    <t>05.10.202616</t>
+  </si>
+  <si>
+    <t>05.10.202617</t>
+  </si>
+  <si>
+    <t>05.10.202618</t>
+  </si>
+  <si>
+    <t>05.10.202619</t>
+  </si>
+  <si>
+    <t>05.10.202620</t>
+  </si>
+  <si>
+    <t>05.10.202621</t>
+  </si>
+  <si>
+    <t>05.10.202622</t>
+  </si>
+  <si>
+    <t>05.10.202623</t>
+  </si>
+  <si>
+    <t>05.10.202624</t>
+  </si>
+  <si>
+    <t>05.10.202625</t>
+  </si>
+  <si>
+    <t>05.10.202626</t>
+  </si>
+  <si>
+    <t>05.10.202627</t>
+  </si>
+  <si>
+    <t>05.10.202628</t>
+  </si>
+  <si>
+    <t>05.10.202629</t>
+  </si>
+  <si>
+    <t>05.10.202630</t>
+  </si>
+  <si>
+    <t>05.10.202631</t>
+  </si>
+  <si>
+    <t>05.10.202632</t>
+  </si>
+  <si>
+    <t>05.10.202633</t>
+  </si>
+  <si>
+    <t>05.10.202634</t>
+  </si>
+  <si>
+    <t>05.10.202635</t>
+  </si>
+  <si>
+    <t>05.10.202636</t>
+  </si>
+  <si>
+    <t>05.10.202637</t>
+  </si>
+  <si>
+    <t>05.10.202638</t>
+  </si>
+  <si>
+    <t>05.10.202639</t>
+  </si>
+  <si>
+    <t>05.10.202640</t>
+  </si>
+  <si>
+    <t>05.10.202641</t>
+  </si>
+  <si>
+    <t>05.10.202642</t>
+  </si>
+  <si>
+    <t>05.10.202643</t>
+  </si>
+  <si>
+    <t>05.10.202644</t>
+  </si>
+  <si>
+    <t>05.10.202645</t>
+  </si>
+  <si>
+    <t>05.10.202646</t>
+  </si>
+  <si>
+    <t>05.10.202647</t>
+  </si>
+  <si>
+    <t>05.10.202648</t>
+  </si>
+  <si>
+    <t>05.10.202649</t>
+  </si>
+  <si>
+    <t>05.10.202650</t>
+  </si>
+  <si>
+    <t>05.10.202651</t>
+  </si>
+  <si>
+    <t>05.10.202652</t>
+  </si>
+  <si>
+    <t>05.10.202653</t>
+  </si>
+  <si>
+    <t>05.10.202654</t>
+  </si>
+  <si>
+    <t>05.10.202655</t>
+  </si>
+  <si>
+    <t>05.10.202656</t>
+  </si>
+  <si>
+    <t>05.10.202657</t>
+  </si>
+  <si>
+    <t>05.10.202658</t>
+  </si>
+  <si>
+    <t>05.10.202659</t>
+  </si>
+  <si>
+    <t>05.10.202660</t>
+  </si>
+  <si>
+    <t>05.10.202661</t>
+  </si>
+  <si>
+    <t>05.10.202662</t>
+  </si>
+  <si>
+    <t>05.10.202663</t>
+  </si>
+  <si>
+    <t>05.10.202664</t>
+  </si>
+  <si>
+    <t>05.10.202665</t>
+  </si>
+  <si>
+    <t>05.10.202666</t>
+  </si>
+  <si>
+    <t>05.10.202667</t>
+  </si>
+  <si>
+    <t>05.10.202668</t>
+  </si>
+  <si>
+    <t>05.10.202669</t>
+  </si>
+  <si>
+    <t>05.10.202670</t>
+  </si>
+  <si>
+    <t>05.10.202671</t>
+  </si>
+  <si>
+    <t>05.10.202672</t>
+  </si>
+  <si>
+    <t>05.10.202673</t>
+  </si>
+  <si>
+    <t>05.10.202674</t>
+  </si>
+  <si>
+    <t>05.10.202675</t>
+  </si>
+  <si>
+    <t>05.10.202676</t>
+  </si>
+  <si>
+    <t>05.10.202677</t>
+  </si>
+  <si>
+    <t>05.10.202678</t>
+  </si>
+  <si>
+    <t>05.10.202679</t>
+  </si>
+  <si>
+    <t>05.10.202680</t>
+  </si>
+  <si>
+    <t>05.10.202681</t>
+  </si>
+  <si>
+    <t>05.10.202682</t>
+  </si>
+  <si>
+    <t>05.10.202683</t>
+  </si>
+  <si>
+    <t>05.10.202684</t>
+  </si>
+  <si>
+    <t>05.10.202685</t>
+  </si>
+  <si>
+    <t>05.10.202686</t>
+  </si>
+  <si>
+    <t>05.10.202687</t>
+  </si>
+  <si>
+    <t>05.10.202688</t>
+  </si>
+  <si>
+    <t>05.10.202689</t>
+  </si>
+  <si>
+    <t>05.10.202690</t>
+  </si>
+  <si>
+    <t>05.10.202691</t>
+  </si>
+  <si>
+    <t>05.10.202692</t>
+  </si>
+  <si>
+    <t>05.10.202693</t>
+  </si>
+  <si>
+    <t>05.10.202694</t>
+  </si>
+  <si>
+    <t>05.10.202695</t>
+  </si>
+  <si>
+    <t>05.10.202696</t>
+  </si>
+  <si>
+    <t>06.10.20261</t>
+  </si>
+  <si>
+    <t>06.10.20262</t>
+  </si>
+  <si>
+    <t>06.10.20263</t>
+  </si>
+  <si>
+    <t>06.10.20264</t>
+  </si>
+  <si>
+    <t>06.10.20265</t>
+  </si>
+  <si>
+    <t>06.10.20266</t>
+  </si>
+  <si>
+    <t>06.10.20267</t>
+  </si>
+  <si>
+    <t>06.10.20268</t>
+  </si>
+  <si>
+    <t>06.10.20269</t>
+  </si>
+  <si>
+    <t>06.10.202610</t>
+  </si>
+  <si>
+    <t>06.10.202611</t>
+  </si>
+  <si>
+    <t>06.10.202612</t>
+  </si>
+  <si>
+    <t>06.10.202613</t>
+  </si>
+  <si>
+    <t>06.10.202614</t>
+  </si>
+  <si>
+    <t>06.10.202615</t>
+  </si>
+  <si>
+    <t>06.10.202616</t>
+  </si>
+  <si>
+    <t>06.10.202617</t>
+  </si>
+  <si>
+    <t>06.10.202618</t>
+  </si>
+  <si>
+    <t>06.10.202619</t>
+  </si>
+  <si>
+    <t>06.10.202620</t>
+  </si>
+  <si>
+    <t>06.10.202621</t>
+  </si>
+  <si>
+    <t>06.10.202622</t>
+  </si>
+  <si>
+    <t>06.10.202623</t>
+  </si>
+  <si>
+    <t>06.10.202624</t>
+  </si>
+  <si>
+    <t>06.10.202625</t>
+  </si>
+  <si>
+    <t>06.10.202626</t>
+  </si>
+  <si>
+    <t>06.10.202627</t>
+  </si>
+  <si>
+    <t>06.10.202628</t>
+  </si>
+  <si>
+    <t>06.10.202629</t>
+  </si>
+  <si>
+    <t>06.10.202630</t>
+  </si>
+  <si>
+    <t>06.10.202631</t>
+  </si>
+  <si>
+    <t>06.10.202632</t>
+  </si>
+  <si>
+    <t>06.10.202633</t>
+  </si>
+  <si>
+    <t>06.10.202634</t>
+  </si>
+  <si>
+    <t>06.10.202635</t>
+  </si>
+  <si>
+    <t>06.10.202636</t>
+  </si>
+  <si>
+    <t>06.10.202637</t>
+  </si>
+  <si>
+    <t>06.10.202638</t>
+  </si>
+  <si>
+    <t>06.10.202639</t>
+  </si>
+  <si>
+    <t>06.10.202640</t>
+  </si>
+  <si>
+    <t>06.10.202641</t>
+  </si>
+  <si>
+    <t>06.10.202642</t>
+  </si>
+  <si>
+    <t>06.10.202643</t>
+  </si>
+  <si>
+    <t>06.10.202644</t>
+  </si>
+  <si>
+    <t>06.10.202645</t>
+  </si>
+  <si>
+    <t>06.10.202646</t>
+  </si>
+  <si>
+    <t>06.10.202647</t>
+  </si>
+  <si>
+    <t>06.10.202648</t>
+  </si>
+  <si>
+    <t>06.10.202649</t>
+  </si>
+  <si>
+    <t>06.10.202650</t>
+  </si>
+  <si>
+    <t>06.10.202651</t>
+  </si>
+  <si>
+    <t>06.10.202652</t>
+  </si>
+  <si>
+    <t>06.10.202653</t>
+  </si>
+  <si>
+    <t>06.10.202654</t>
+  </si>
+  <si>
+    <t>06.10.202655</t>
+  </si>
+  <si>
+    <t>06.10.202656</t>
+  </si>
+  <si>
+    <t>06.10.202657</t>
+  </si>
+  <si>
+    <t>06.10.202658</t>
+  </si>
+  <si>
+    <t>06.10.202659</t>
+  </si>
+  <si>
+    <t>06.10.202660</t>
+  </si>
+  <si>
+    <t>06.10.202661</t>
+  </si>
+  <si>
+    <t>06.10.202662</t>
+  </si>
+  <si>
+    <t>06.10.202663</t>
+  </si>
+  <si>
+    <t>06.10.202664</t>
+  </si>
+  <si>
+    <t>06.10.202665</t>
+  </si>
+  <si>
+    <t>06.10.202666</t>
+  </si>
+  <si>
+    <t>06.10.202667</t>
+  </si>
+  <si>
+    <t>06.10.202668</t>
+  </si>
+  <si>
+    <t>06.10.202669</t>
+  </si>
+  <si>
+    <t>06.10.202670</t>
+  </si>
+  <si>
+    <t>06.10.202671</t>
+  </si>
+  <si>
+    <t>06.10.202672</t>
+  </si>
+  <si>
+    <t>06.10.202673</t>
+  </si>
+  <si>
+    <t>06.10.202674</t>
+  </si>
+  <si>
+    <t>06.10.202675</t>
+  </si>
+  <si>
+    <t>06.10.202676</t>
+  </si>
+  <si>
+    <t>06.10.202677</t>
+  </si>
+  <si>
+    <t>06.10.202678</t>
+  </si>
+  <si>
+    <t>06.10.202679</t>
+  </si>
+  <si>
+    <t>06.10.202680</t>
+  </si>
+  <si>
+    <t>06.10.202681</t>
+  </si>
+  <si>
+    <t>06.10.202682</t>
+  </si>
+  <si>
+    <t>06.10.202683</t>
+  </si>
+  <si>
+    <t>06.10.202684</t>
+  </si>
+  <si>
+    <t>06.10.202685</t>
+  </si>
+  <si>
+    <t>06.10.202686</t>
+  </si>
+  <si>
+    <t>06.10.202687</t>
+  </si>
+  <si>
+    <t>06.10.202688</t>
+  </si>
+  <si>
+    <t>06.10.202689</t>
+  </si>
+  <si>
+    <t>06.10.202690</t>
+  </si>
+  <si>
+    <t>06.10.202691</t>
+  </si>
+  <si>
+    <t>06.10.202692</t>
+  </si>
+  <si>
+    <t>06.10.202693</t>
+  </si>
+  <si>
+    <t>06.10.202694</t>
+  </si>
+  <si>
+    <t>06.10.202695</t>
+  </si>
+  <si>
+    <t>06.10.202696</t>
+  </si>
+  <si>
+    <t>07.10.20261</t>
+  </si>
+  <si>
+    <t>07.10.20262</t>
+  </si>
+  <si>
+    <t>07.10.20263</t>
+  </si>
+  <si>
+    <t>07.10.20264</t>
+  </si>
+  <si>
+    <t>07.10.20265</t>
+  </si>
+  <si>
+    <t>07.10.20266</t>
+  </si>
+  <si>
+    <t>07.10.20267</t>
+  </si>
+  <si>
+    <t>07.10.20268</t>
+  </si>
+  <si>
+    <t>07.10.20269</t>
+  </si>
+  <si>
+    <t>07.10.202610</t>
+  </si>
+  <si>
+    <t>07.10.202611</t>
+  </si>
+  <si>
+    <t>07.10.202612</t>
+  </si>
+  <si>
+    <t>07.10.202613</t>
+  </si>
+  <si>
+    <t>07.10.202614</t>
+  </si>
+  <si>
+    <t>07.10.202615</t>
+  </si>
+  <si>
+    <t>07.10.202616</t>
+  </si>
+  <si>
+    <t>07.10.202617</t>
+  </si>
+  <si>
+    <t>07.10.202618</t>
+  </si>
+  <si>
+    <t>07.10.202619</t>
+  </si>
+  <si>
+    <t>07.10.202620</t>
+  </si>
+  <si>
+    <t>07.10.202621</t>
+  </si>
+  <si>
+    <t>07.10.202622</t>
+  </si>
+  <si>
+    <t>07.10.202623</t>
+  </si>
+  <si>
+    <t>07.10.202624</t>
+  </si>
+  <si>
+    <t>07.10.202625</t>
+  </si>
+  <si>
+    <t>07.10.202626</t>
+  </si>
+  <si>
+    <t>07.10.202627</t>
+  </si>
+  <si>
+    <t>07.10.202628</t>
+  </si>
+  <si>
+    <t>07.10.202629</t>
+  </si>
+  <si>
+    <t>07.10.202630</t>
+  </si>
+  <si>
+    <t>07.10.202631</t>
+  </si>
+  <si>
+    <t>07.10.202632</t>
+  </si>
+  <si>
+    <t>07.10.202633</t>
+  </si>
+  <si>
+    <t>07.10.202634</t>
+  </si>
+  <si>
+    <t>07.10.202635</t>
+  </si>
+  <si>
+    <t>07.10.202636</t>
+  </si>
+  <si>
+    <t>07.10.202637</t>
+  </si>
+  <si>
+    <t>07.10.202638</t>
+  </si>
+  <si>
+    <t>07.10.202639</t>
+  </si>
+  <si>
+    <t>07.10.202640</t>
+  </si>
+  <si>
+    <t>07.10.202641</t>
+  </si>
+  <si>
+    <t>07.10.202642</t>
+  </si>
+  <si>
+    <t>07.10.202643</t>
+  </si>
+  <si>
+    <t>07.10.202644</t>
+  </si>
+  <si>
+    <t>07.10.202645</t>
+  </si>
+  <si>
+    <t>07.10.202646</t>
+  </si>
+  <si>
+    <t>07.10.202647</t>
+  </si>
+  <si>
+    <t>07.10.202648</t>
+  </si>
+  <si>
+    <t>07.10.202649</t>
+  </si>
+  <si>
+    <t>07.10.202650</t>
+  </si>
+  <si>
+    <t>07.10.202651</t>
+  </si>
+  <si>
+    <t>07.10.202652</t>
+  </si>
+  <si>
+    <t>07.10.202653</t>
+  </si>
+  <si>
+    <t>07.10.202654</t>
+  </si>
+  <si>
+    <t>07.10.202655</t>
+  </si>
+  <si>
+    <t>07.10.202656</t>
+  </si>
+  <si>
+    <t>07.10.202657</t>
+  </si>
+  <si>
+    <t>07.10.202658</t>
+  </si>
+  <si>
+    <t>07.10.202659</t>
+  </si>
+  <si>
+    <t>07.10.202660</t>
+  </si>
+  <si>
+    <t>07.10.202661</t>
+  </si>
+  <si>
+    <t>07.10.202662</t>
+  </si>
+  <si>
+    <t>07.10.202663</t>
+  </si>
+  <si>
+    <t>07.10.202664</t>
+  </si>
+  <si>
+    <t>07.10.202665</t>
+  </si>
+  <si>
+    <t>07.10.202666</t>
+  </si>
+  <si>
+    <t>07.10.202667</t>
+  </si>
+  <si>
+    <t>07.10.202668</t>
+  </si>
+  <si>
+    <t>07.10.202669</t>
+  </si>
+  <si>
+    <t>07.10.202670</t>
+  </si>
+  <si>
+    <t>07.10.202671</t>
+  </si>
+  <si>
+    <t>07.10.202672</t>
+  </si>
+  <si>
+    <t>07.10.202673</t>
+  </si>
+  <si>
+    <t>07.10.202674</t>
+  </si>
+  <si>
+    <t>07.10.202675</t>
+  </si>
+  <si>
+    <t>07.10.202676</t>
+  </si>
+  <si>
+    <t>07.10.202677</t>
+  </si>
+  <si>
+    <t>07.10.202678</t>
+  </si>
+  <si>
+    <t>07.10.202679</t>
+  </si>
+  <si>
+    <t>07.10.202680</t>
+  </si>
+  <si>
+    <t>07.10.202681</t>
+  </si>
+  <si>
+    <t>07.10.202682</t>
+  </si>
+  <si>
+    <t>07.10.202683</t>
+  </si>
+  <si>
+    <t>07.10.202684</t>
+  </si>
+  <si>
+    <t>07.10.202685</t>
+  </si>
+  <si>
+    <t>07.10.202686</t>
+  </si>
+  <si>
+    <t>07.10.202687</t>
+  </si>
+  <si>
+    <t>07.10.202688</t>
+  </si>
+  <si>
+    <t>07.10.202689</t>
+  </si>
+  <si>
+    <t>07.10.202690</t>
+  </si>
+  <si>
+    <t>07.10.202691</t>
+  </si>
+  <si>
+    <t>07.10.202692</t>
   </si>
 </sst>
 </file>
@@ -954,7 +1818,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E189"/>
+  <dimension ref="A1:E477"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -981,6 +1845,9 @@
       <c r="B2">
         <v>942.974</v>
       </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
       <c r="D2">
         <v>1</v>
       </c>
@@ -995,6 +1862,9 @@
       <c r="B3">
         <v>965.169</v>
       </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
       <c r="D3">
         <v>2</v>
       </c>
@@ -1009,6 +1879,9 @@
       <c r="B4">
         <v>979.8440000000001</v>
       </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
       <c r="D4">
         <v>3</v>
       </c>
@@ -1023,6 +1896,9 @@
       <c r="B5">
         <v>991.799</v>
       </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
       <c r="D5">
         <v>4</v>
       </c>
@@ -1037,6 +1913,9 @@
       <c r="B6">
         <v>1009.589</v>
       </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
       <c r="D6">
         <v>5</v>
       </c>
@@ -1051,6 +1930,9 @@
       <c r="B7">
         <v>1020.702</v>
       </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
       <c r="D7">
         <v>6</v>
       </c>
@@ -1065,6 +1947,9 @@
       <c r="B8">
         <v>1035.901</v>
       </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
       <c r="D8">
         <v>7</v>
       </c>
@@ -1079,6 +1964,9 @@
       <c r="B9">
         <v>1049.011</v>
       </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
       <c r="D9">
         <v>8</v>
       </c>
@@ -1093,6 +1981,9 @@
       <c r="B10">
         <v>1065.328</v>
       </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
       <c r="D10">
         <v>9</v>
       </c>
@@ -1107,6 +1998,9 @@
       <c r="B11">
         <v>1060.988</v>
       </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
       <c r="D11">
         <v>10</v>
       </c>
@@ -1121,6 +2015,9 @@
       <c r="B12">
         <v>1060.102</v>
       </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
       <c r="D12">
         <v>11</v>
       </c>
@@ -1135,6 +2032,9 @@
       <c r="B13">
         <v>1053.509</v>
       </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
       <c r="D13">
         <v>12</v>
       </c>
@@ -1149,6 +2049,9 @@
       <c r="B14">
         <v>1046.845</v>
       </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
       <c r="D14">
         <v>13</v>
       </c>
@@ -1163,6 +2066,9 @@
       <c r="B15">
         <v>1035.005</v>
       </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
       <c r="D15">
         <v>14</v>
       </c>
@@ -1177,6 +2083,9 @@
       <c r="B16">
         <v>1017.589</v>
       </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
       <c r="D16">
         <v>15</v>
       </c>
@@ -1191,6 +2100,9 @@
       <c r="B17">
         <v>1005.551</v>
       </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
       <c r="D17">
         <v>16</v>
       </c>
@@ -1205,6 +2117,9 @@
       <c r="B18">
         <v>991.264</v>
       </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
       <c r="D18">
         <v>17</v>
       </c>
@@ -1219,6 +2134,9 @@
       <c r="B19">
         <v>952.528</v>
       </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
       <c r="D19">
         <v>18</v>
       </c>
@@ -1233,6 +2151,9 @@
       <c r="B20">
         <v>928.641</v>
       </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
       <c r="D20">
         <v>19</v>
       </c>
@@ -1247,6 +2168,9 @@
       <c r="B21">
         <v>907.171</v>
       </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
       <c r="D21">
         <v>20</v>
       </c>
@@ -1261,6 +2185,9 @@
       <c r="B22">
         <v>879.26</v>
       </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
       <c r="D22">
         <v>21</v>
       </c>
@@ -1275,6 +2202,9 @@
       <c r="B23">
         <v>853.925</v>
       </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
       <c r="D23">
         <v>22</v>
       </c>
@@ -1289,6 +2219,9 @@
       <c r="B24">
         <v>825.172</v>
       </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
       <c r="D24">
         <v>23</v>
       </c>
@@ -1303,6 +2236,9 @@
       <c r="B25">
         <v>802.749</v>
       </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
       <c r="D25">
         <v>24</v>
       </c>
@@ -1317,6 +2253,9 @@
       <c r="B26">
         <v>782.0359999999999</v>
       </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
       <c r="D26">
         <v>25</v>
       </c>
@@ -1331,6 +2270,9 @@
       <c r="B27">
         <v>758.566</v>
       </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
       <c r="D27">
         <v>26</v>
       </c>
@@ -1345,6 +2287,9 @@
       <c r="B28">
         <v>728.301</v>
       </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
       <c r="D28">
         <v>27</v>
       </c>
@@ -1359,6 +2304,9 @@
       <c r="B29">
         <v>703.16</v>
       </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
       <c r="D29">
         <v>28</v>
       </c>
@@ -1373,6 +2321,9 @@
       <c r="B30">
         <v>654.216</v>
       </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
       <c r="D30">
         <v>29</v>
       </c>
@@ -1387,6 +2338,9 @@
       <c r="B31">
         <v>620.548</v>
       </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
       <c r="D31">
         <v>30</v>
       </c>
@@ -1401,6 +2355,9 @@
       <c r="B32">
         <v>585.443</v>
       </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
       <c r="D32">
         <v>31</v>
       </c>
@@ -1415,6 +2372,9 @@
       <c r="B33">
         <v>545.694</v>
       </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
       <c r="D33">
         <v>32</v>
       </c>
@@ -1429,6 +2389,9 @@
       <c r="B34">
         <v>518.378</v>
       </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
       <c r="D34">
         <v>33</v>
       </c>
@@ -1443,6 +2406,9 @@
       <c r="B35">
         <v>472.635</v>
       </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
       <c r="D35">
         <v>34</v>
       </c>
@@ -1457,6 +2423,9 @@
       <c r="B36">
         <v>443.653</v>
       </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
       <c r="D36">
         <v>35</v>
       </c>
@@ -1471,6 +2440,9 @@
       <c r="B37">
         <v>393.648</v>
       </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
       <c r="D37">
         <v>36</v>
       </c>
@@ -1485,6 +2457,9 @@
       <c r="B38">
         <v>447.66</v>
       </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
       <c r="D38">
         <v>37</v>
       </c>
@@ -1499,6 +2474,9 @@
       <c r="B39">
         <v>430.364</v>
       </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
       <c r="D39">
         <v>38</v>
       </c>
@@ -1513,6 +2491,9 @@
       <c r="B40">
         <v>417.057</v>
       </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
       <c r="D40">
         <v>39</v>
       </c>
@@ -1527,6 +2508,9 @@
       <c r="B41">
         <v>403.557</v>
       </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
       <c r="D41">
         <v>40</v>
       </c>
@@ -1541,6 +2525,9 @@
       <c r="B42">
         <v>392.084</v>
       </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
       <c r="D42">
         <v>41</v>
       </c>
@@ -1555,6 +2542,9 @@
       <c r="B43">
         <v>383.8</v>
       </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
       <c r="D43">
         <v>42</v>
       </c>
@@ -1569,6 +2559,9 @@
       <c r="B44">
         <v>374.776</v>
       </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
       <c r="D44">
         <v>43</v>
       </c>
@@ -1583,6 +2576,9 @@
       <c r="B45">
         <v>366.253</v>
       </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
       <c r="D45">
         <v>44</v>
       </c>
@@ -1597,6 +2593,9 @@
       <c r="B46">
         <v>363.32</v>
       </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
       <c r="D46">
         <v>45</v>
       </c>
@@ -1611,6 +2610,9 @@
       <c r="B47">
         <v>348.634</v>
       </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
       <c r="D47">
         <v>46</v>
       </c>
@@ -1625,6 +2627,9 @@
       <c r="B48">
         <v>334.558</v>
       </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
       <c r="D48">
         <v>47</v>
       </c>
@@ -1639,6 +2644,9 @@
       <c r="B49">
         <v>320.301</v>
       </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
       <c r="D49">
         <v>48</v>
       </c>
@@ -1653,6 +2661,9 @@
       <c r="B50">
         <v>254.887</v>
       </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
       <c r="D50">
         <v>49</v>
       </c>
@@ -1667,6 +2678,9 @@
       <c r="B51">
         <v>243.642</v>
       </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
       <c r="D51">
         <v>50</v>
       </c>
@@ -1681,6 +2695,9 @@
       <c r="B52">
         <v>231.554</v>
       </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
       <c r="D52">
         <v>51</v>
       </c>
@@ -1695,6 +2712,9 @@
       <c r="B53">
         <v>219.447</v>
       </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
       <c r="D53">
         <v>52</v>
       </c>
@@ -1709,6 +2729,9 @@
       <c r="B54">
         <v>205.56</v>
       </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
       <c r="D54">
         <v>53</v>
       </c>
@@ -1723,6 +2746,9 @@
       <c r="B55">
         <v>199.357</v>
       </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
       <c r="D55">
         <v>54</v>
       </c>
@@ -1737,6 +2763,9 @@
       <c r="B56">
         <v>193.083</v>
       </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
       <c r="D56">
         <v>55</v>
       </c>
@@ -1751,6 +2780,9 @@
       <c r="B57">
         <v>186.846</v>
       </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
       <c r="D57">
         <v>56</v>
       </c>
@@ -1765,6 +2797,9 @@
       <c r="B58">
         <v>181.712</v>
       </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
       <c r="D58">
         <v>57</v>
       </c>
@@ -1779,6 +2814,9 @@
       <c r="B59">
         <v>177.135</v>
       </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
       <c r="D59">
         <v>58</v>
       </c>
@@ -1793,6 +2831,9 @@
       <c r="B60">
         <v>171.385</v>
       </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
       <c r="D60">
         <v>59</v>
       </c>
@@ -1807,6 +2848,9 @@
       <c r="B61">
         <v>166.232</v>
       </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
       <c r="D61">
         <v>60</v>
       </c>
@@ -1821,6 +2865,9 @@
       <c r="B62">
         <v>147.934</v>
       </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
       <c r="D62">
         <v>61</v>
       </c>
@@ -1835,6 +2882,9 @@
       <c r="B63">
         <v>142.534</v>
       </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
       <c r="D63">
         <v>62</v>
       </c>
@@ -1849,6 +2899,9 @@
       <c r="B64">
         <v>136.829</v>
       </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
       <c r="D64">
         <v>63</v>
       </c>
@@ -1863,6 +2916,9 @@
       <c r="B65">
         <v>131.117</v>
       </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
       <c r="D65">
         <v>64</v>
       </c>
@@ -1877,6 +2933,9 @@
       <c r="B66">
         <v>123.305</v>
       </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
       <c r="D66">
         <v>65</v>
       </c>
@@ -1891,6 +2950,9 @@
       <c r="B67">
         <v>117.841</v>
       </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
       <c r="D67">
         <v>66</v>
       </c>
@@ -1905,6 +2967,9 @@
       <c r="B68">
         <v>112.669</v>
       </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
       <c r="D68">
         <v>67</v>
       </c>
@@ -1919,6 +2984,9 @@
       <c r="B69">
         <v>107.339</v>
       </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
       <c r="D69">
         <v>68</v>
       </c>
@@ -1933,6 +3001,9 @@
       <c r="B70">
         <v>106.343</v>
       </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
       <c r="D70">
         <v>69</v>
       </c>
@@ -1947,6 +3018,9 @@
       <c r="B71">
         <v>104.483</v>
       </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
       <c r="D71">
         <v>70</v>
       </c>
@@ -1961,6 +3035,9 @@
       <c r="B72">
         <v>103.26</v>
       </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
       <c r="D72">
         <v>71</v>
       </c>
@@ -1975,6 +3052,9 @@
       <c r="B73">
         <v>102.016</v>
       </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
       <c r="D73">
         <v>72</v>
       </c>
@@ -1989,6 +3069,9 @@
       <c r="B74">
         <v>101.053</v>
       </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
       <c r="D74">
         <v>73</v>
       </c>
@@ -2003,6 +3086,9 @@
       <c r="B75">
         <v>98.565</v>
       </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
       <c r="D75">
         <v>74</v>
       </c>
@@ -2017,6 +3103,9 @@
       <c r="B76">
         <v>96.61799999999999</v>
       </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
       <c r="D76">
         <v>75</v>
       </c>
@@ -2031,6 +3120,9 @@
       <c r="B77">
         <v>94.639</v>
       </c>
+      <c r="C77">
+        <v>0</v>
+      </c>
       <c r="D77">
         <v>76</v>
       </c>
@@ -2045,6 +3137,9 @@
       <c r="B78">
         <v>93.69799999999999</v>
       </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
       <c r="D78">
         <v>77</v>
       </c>
@@ -2059,6 +3154,9 @@
       <c r="B79">
         <v>93.331</v>
       </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
       <c r="D79">
         <v>78</v>
       </c>
@@ -2073,6 +3171,9 @@
       <c r="B80">
         <v>92.53</v>
       </c>
+      <c r="C80">
+        <v>0</v>
+      </c>
       <c r="D80">
         <v>79</v>
       </c>
@@ -2087,6 +3188,9 @@
       <c r="B81">
         <v>92.17400000000001</v>
       </c>
+      <c r="C81">
+        <v>0</v>
+      </c>
       <c r="D81">
         <v>80</v>
       </c>
@@ -2101,6 +3205,9 @@
       <c r="B82">
         <v>93.95999999999999</v>
       </c>
+      <c r="C82">
+        <v>0</v>
+      </c>
       <c r="D82">
         <v>81</v>
       </c>
@@ -2115,6 +3222,9 @@
       <c r="B83">
         <v>94.212</v>
       </c>
+      <c r="C83">
+        <v>0</v>
+      </c>
       <c r="D83">
         <v>82</v>
       </c>
@@ -2129,6 +3239,9 @@
       <c r="B84">
         <v>95.617</v>
       </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
       <c r="D84">
         <v>83</v>
       </c>
@@ -2143,6 +3256,9 @@
       <c r="B85">
         <v>97.15900000000001</v>
       </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
       <c r="D85">
         <v>84</v>
       </c>
@@ -2157,6 +3273,9 @@
       <c r="B86">
         <v>98.065</v>
       </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
       <c r="D86">
         <v>85</v>
       </c>
@@ -2171,6 +3290,9 @@
       <c r="B87">
         <v>100.403</v>
       </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
       <c r="D87">
         <v>86</v>
       </c>
@@ -2185,6 +3307,9 @@
       <c r="B88">
         <v>102.086</v>
       </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
       <c r="D88">
         <v>87</v>
       </c>
@@ -2199,6 +3324,9 @@
       <c r="B89">
         <v>104.682</v>
       </c>
+      <c r="C89">
+        <v>0</v>
+      </c>
       <c r="D89">
         <v>88</v>
       </c>
@@ -2213,6 +3341,9 @@
       <c r="B90">
         <v>115.698</v>
       </c>
+      <c r="C90">
+        <v>0</v>
+      </c>
       <c r="D90">
         <v>89</v>
       </c>
@@ -2227,6 +3358,9 @@
       <c r="B91">
         <v>118.11</v>
       </c>
+      <c r="C91">
+        <v>0</v>
+      </c>
       <c r="D91">
         <v>90</v>
       </c>
@@ -2241,6 +3375,9 @@
       <c r="B92">
         <v>120.912</v>
       </c>
+      <c r="C92">
+        <v>0</v>
+      </c>
       <c r="D92">
         <v>91</v>
       </c>
@@ -2255,6 +3392,9 @@
       <c r="B93">
         <v>123.747</v>
       </c>
+      <c r="C93">
+        <v>0</v>
+      </c>
       <c r="D93">
         <v>92</v>
       </c>
@@ -2267,7 +3407,10 @@
         <v>46298.95833333334</v>
       </c>
       <c r="B94">
-        <v>125.466</v>
+        <v>141.266</v>
+      </c>
+      <c r="C94">
+        <v>0</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2281,7 +3424,10 @@
         <v>46298.96875</v>
       </c>
       <c r="B95">
-        <v>129.809</v>
+        <v>146.109</v>
+      </c>
+      <c r="C95">
+        <v>0</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2295,7 +3441,10 @@
         <v>46298.97916666666</v>
       </c>
       <c r="B96">
-        <v>133.665</v>
+        <v>149.565</v>
+      </c>
+      <c r="C96">
+        <v>0</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2309,7 +3458,10 @@
         <v>46298.98958333334</v>
       </c>
       <c r="B97">
-        <v>137.936</v>
+        <v>153.636</v>
+      </c>
+      <c r="C97">
+        <v>0</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2323,7 +3475,10 @@
         <v>46299</v>
       </c>
       <c r="B98">
-        <v>169.102</v>
+        <v>165.702</v>
+      </c>
+      <c r="C98">
+        <v>0</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2337,7 +3492,10 @@
         <v>46299.01041666666</v>
       </c>
       <c r="B99">
-        <v>172.962</v>
+        <v>169.662</v>
+      </c>
+      <c r="C99">
+        <v>0</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2351,7 +3509,10 @@
         <v>46299.02083333334</v>
       </c>
       <c r="B100">
-        <v>176.779</v>
+        <v>173.479</v>
+      </c>
+      <c r="C100">
+        <v>0</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2365,7 +3526,10 @@
         <v>46299.03125</v>
       </c>
       <c r="B101">
-        <v>181.373</v>
+        <v>179.173</v>
+      </c>
+      <c r="C101">
+        <v>0</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2379,7 +3543,10 @@
         <v>46299.04166666666</v>
       </c>
       <c r="B102">
-        <v>183.045</v>
+        <v>183.445</v>
+      </c>
+      <c r="C102">
+        <v>0</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2393,7 +3560,10 @@
         <v>46299.05208333334</v>
       </c>
       <c r="B103">
-        <v>186.526</v>
+        <v>186.926</v>
+      </c>
+      <c r="C103">
+        <v>0</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2407,7 +3577,10 @@
         <v>46299.0625</v>
       </c>
       <c r="B104">
-        <v>189.143</v>
+        <v>187.943</v>
+      </c>
+      <c r="C104">
+        <v>0</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2421,7 +3594,10 @@
         <v>46299.07291666666</v>
       </c>
       <c r="B105">
-        <v>191.974</v>
+        <v>190.974</v>
+      </c>
+      <c r="C105">
+        <v>0</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2435,7 +3611,10 @@
         <v>46299.08333333334</v>
       </c>
       <c r="B106">
-        <v>194.656</v>
+        <v>190.256</v>
+      </c>
+      <c r="C106">
+        <v>0</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2449,7 +3628,10 @@
         <v>46299.09375</v>
       </c>
       <c r="B107">
-        <v>194.437</v>
+        <v>190.037</v>
+      </c>
+      <c r="C107">
+        <v>0</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2463,7 +3645,10 @@
         <v>46299.10416666666</v>
       </c>
       <c r="B108">
-        <v>194.639</v>
+        <v>192.239</v>
+      </c>
+      <c r="C108">
+        <v>0</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2477,7 +3662,10 @@
         <v>46299.11458333334</v>
       </c>
       <c r="B109">
-        <v>195.502</v>
+        <v>193.102</v>
+      </c>
+      <c r="C109">
+        <v>0</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2491,7 +3679,10 @@
         <v>46299.125</v>
       </c>
       <c r="B110">
-        <v>194.722</v>
+        <v>190.522</v>
+      </c>
+      <c r="C110">
+        <v>0</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2505,7 +3696,10 @@
         <v>46299.13541666666</v>
       </c>
       <c r="B111">
-        <v>194.073</v>
+        <v>189.173</v>
+      </c>
+      <c r="C111">
+        <v>0</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2519,7 +3713,10 @@
         <v>46299.14583333334</v>
       </c>
       <c r="B112">
-        <v>193.209</v>
+        <v>188.209</v>
+      </c>
+      <c r="C112">
+        <v>0</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2533,7 +3730,10 @@
         <v>46299.15625</v>
       </c>
       <c r="B113">
-        <v>192.67</v>
+        <v>187.47</v>
+      </c>
+      <c r="C113">
+        <v>0</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2547,7 +3747,10 @@
         <v>46299.16666666666</v>
       </c>
       <c r="B114">
-        <v>190.491</v>
+        <v>174.791</v>
+      </c>
+      <c r="C114">
+        <v>0</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2561,7 +3764,10 @@
         <v>46299.17708333334</v>
       </c>
       <c r="B115">
-        <v>186.937</v>
+        <v>171.337</v>
+      </c>
+      <c r="C115">
+        <v>0</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2575,7 +3781,10 @@
         <v>46299.1875</v>
       </c>
       <c r="B116">
-        <v>184.025</v>
+        <v>167.225</v>
+      </c>
+      <c r="C116">
+        <v>0</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2589,7 +3798,10 @@
         <v>46299.19791666666</v>
       </c>
       <c r="B117">
-        <v>181.203</v>
+        <v>164.803</v>
+      </c>
+      <c r="C117">
+        <v>0</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2603,7 +3815,10 @@
         <v>46299.20833333334</v>
       </c>
       <c r="B118">
-        <v>177.087</v>
+        <v>160.887</v>
+      </c>
+      <c r="C118">
+        <v>0</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2617,7 +3832,10 @@
         <v>46299.21875</v>
       </c>
       <c r="B119">
-        <v>172.726</v>
+        <v>156.226</v>
+      </c>
+      <c r="C119">
+        <v>0</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2631,7 +3849,10 @@
         <v>46299.22916666666</v>
       </c>
       <c r="B120">
-        <v>168.167</v>
+        <v>150.967</v>
+      </c>
+      <c r="C120">
+        <v>0</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -2645,7 +3866,10 @@
         <v>46299.23958333334</v>
       </c>
       <c r="B121">
-        <v>164.847</v>
+        <v>147.547</v>
+      </c>
+      <c r="C121">
+        <v>0</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -2659,7 +3883,10 @@
         <v>46299.25</v>
       </c>
       <c r="B122">
-        <v>137.285</v>
+        <v>141.985</v>
+      </c>
+      <c r="C122">
+        <v>0</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -2673,7 +3900,10 @@
         <v>46299.26041666666</v>
       </c>
       <c r="B123">
-        <v>132.868</v>
+        <v>137.068</v>
+      </c>
+      <c r="C123">
+        <v>0</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -2687,7 +3917,10 @@
         <v>46299.27083333334</v>
       </c>
       <c r="B124">
-        <v>129.569</v>
+        <v>128.393</v>
+      </c>
+      <c r="C124">
+        <v>0</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -2701,7 +3934,10 @@
         <v>46299.28125</v>
       </c>
       <c r="B125">
-        <v>127.252</v>
+        <v>126.757</v>
+      </c>
+      <c r="C125">
+        <v>0</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -2715,7 +3951,10 @@
         <v>46299.29166666666</v>
       </c>
       <c r="B126">
-        <v>134.654</v>
+        <v>130.533</v>
+      </c>
+      <c r="C126">
+        <v>0</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -2729,7 +3968,10 @@
         <v>46299.30208333334</v>
       </c>
       <c r="B127">
-        <v>128.085</v>
+        <v>126.92</v>
+      </c>
+      <c r="C127">
+        <v>0</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -2743,7 +3985,10 @@
         <v>46299.3125</v>
       </c>
       <c r="B128">
-        <v>113.875</v>
+        <v>115.01</v>
+      </c>
+      <c r="C128">
+        <v>0</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -2757,7 +4002,10 @@
         <v>46299.32291666666</v>
       </c>
       <c r="B129">
-        <v>110.375</v>
+        <v>113.785</v>
+      </c>
+      <c r="C129">
+        <v>0</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -2771,7 +4019,10 @@
         <v>46299.33333333334</v>
       </c>
       <c r="B130">
-        <v>111.843</v>
+        <v>113.609</v>
+      </c>
+      <c r="C130">
+        <v>0</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -2785,7 +4036,10 @@
         <v>46299.34375</v>
       </c>
       <c r="B131">
-        <v>109.408</v>
+        <v>113.234</v>
+      </c>
+      <c r="C131">
+        <v>0</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -2799,7 +4053,10 @@
         <v>46299.35416666666</v>
       </c>
       <c r="B132">
-        <v>107.066</v>
+        <v>110.874</v>
+      </c>
+      <c r="C132">
+        <v>0</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -2813,7 +4070,10 @@
         <v>46299.36458333334</v>
       </c>
       <c r="B133">
-        <v>104.867</v>
+        <v>109.598</v>
+      </c>
+      <c r="C133">
+        <v>0</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -2827,7 +4087,10 @@
         <v>46299.375</v>
       </c>
       <c r="B134">
-        <v>106.428</v>
+        <v>117.355</v>
+      </c>
+      <c r="C134">
+        <v>0</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -2841,7 +4104,10 @@
         <v>46299.38541666666</v>
       </c>
       <c r="B135">
-        <v>105.175</v>
+        <v>116.477</v>
+      </c>
+      <c r="C135">
+        <v>0</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -2855,7 +4121,10 @@
         <v>46299.39583333334</v>
       </c>
       <c r="B136">
-        <v>102.986</v>
+        <v>114.411</v>
+      </c>
+      <c r="C136">
+        <v>0</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -2869,7 +4138,10 @@
         <v>46299.40625</v>
       </c>
       <c r="B137">
-        <v>101.164</v>
+        <v>112.604</v>
+      </c>
+      <c r="C137">
+        <v>0</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -2883,7 +4155,10 @@
         <v>46299.41666666666</v>
       </c>
       <c r="B138">
-        <v>100.088</v>
+        <v>91.504</v>
+      </c>
+      <c r="C138">
+        <v>0</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -2897,7 +4172,10 @@
         <v>46299.42708333334</v>
       </c>
       <c r="B139">
-        <v>99.873</v>
+        <v>92.392</v>
+      </c>
+      <c r="C139">
+        <v>0</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -2911,7 +4189,10 @@
         <v>46299.4375</v>
       </c>
       <c r="B140">
-        <v>99.908</v>
+        <v>90.58799999999999</v>
+      </c>
+      <c r="C140">
+        <v>0</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -2925,7 +4206,10 @@
         <v>46299.44791666666</v>
       </c>
       <c r="B141">
-        <v>99.911</v>
+        <v>90.443</v>
+      </c>
+      <c r="C141">
+        <v>0</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -2939,7 +4223,10 @@
         <v>46299.45833333334</v>
       </c>
       <c r="B142">
-        <v>100.242</v>
+        <v>87.426</v>
+      </c>
+      <c r="C142">
+        <v>0</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -2953,7 +4240,10 @@
         <v>46299.46875</v>
       </c>
       <c r="B143">
-        <v>100.902</v>
+        <v>88.04600000000001</v>
+      </c>
+      <c r="C143">
+        <v>0</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -2967,7 +4257,10 @@
         <v>46299.47916666666</v>
       </c>
       <c r="B144">
-        <v>101.518</v>
+        <v>88.678</v>
+      </c>
+      <c r="C144">
+        <v>0</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -2981,7 +4274,10 @@
         <v>46299.48958333334</v>
       </c>
       <c r="B145">
-        <v>101.869</v>
+        <v>89.85299999999999</v>
+      </c>
+      <c r="C145">
+        <v>0</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -2995,7 +4291,10 @@
         <v>46299.5</v>
       </c>
       <c r="B146">
-        <v>100.307</v>
+        <v>86.899</v>
+      </c>
+      <c r="C146">
+        <v>0</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3009,7 +4308,10 @@
         <v>46299.51041666666</v>
       </c>
       <c r="B147">
-        <v>100.733</v>
+        <v>85.657</v>
+      </c>
+      <c r="C147">
+        <v>0</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3023,7 +4325,10 @@
         <v>46299.52083333334</v>
       </c>
       <c r="B148">
-        <v>101.39</v>
+        <v>82.20999999999999</v>
+      </c>
+      <c r="C148">
+        <v>0</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3037,7 +4342,10 @@
         <v>46299.53125</v>
       </c>
       <c r="B149">
-        <v>101.982</v>
+        <v>81.642</v>
+      </c>
+      <c r="C149">
+        <v>0</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3051,7 +4359,10 @@
         <v>46299.54166666666</v>
       </c>
       <c r="B150">
-        <v>103.727</v>
+        <v>85.319</v>
+      </c>
+      <c r="C150">
+        <v>0</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3065,7 +4376,10 @@
         <v>46299.55208333334</v>
       </c>
       <c r="B151">
-        <v>105.195</v>
+        <v>86.739</v>
+      </c>
+      <c r="C151">
+        <v>0</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3079,7 +4393,10 @@
         <v>46299.5625</v>
       </c>
       <c r="B152">
-        <v>106.561</v>
+        <v>87.501</v>
+      </c>
+      <c r="C152">
+        <v>0</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3093,7 +4410,10 @@
         <v>46299.57291666666</v>
       </c>
       <c r="B153">
-        <v>107.767</v>
+        <v>88.791</v>
+      </c>
+      <c r="C153">
+        <v>0</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3107,7 +4427,10 @@
         <v>46299.58333333334</v>
       </c>
       <c r="B154">
-        <v>111.741</v>
+        <v>95.06</v>
+      </c>
+      <c r="C154">
+        <v>0</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3121,7 +4444,10 @@
         <v>46299.59375</v>
       </c>
       <c r="B155">
-        <v>111.908</v>
+        <v>93.416</v>
+      </c>
+      <c r="C155">
+        <v>0</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3135,7 +4461,10 @@
         <v>46299.60416666666</v>
       </c>
       <c r="B156">
-        <v>111.951</v>
+        <v>91.503</v>
+      </c>
+      <c r="C156">
+        <v>0</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3149,7 +4478,10 @@
         <v>46299.61458333334</v>
       </c>
       <c r="B157">
-        <v>112.151</v>
+        <v>91.592</v>
+      </c>
+      <c r="C157">
+        <v>0</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3163,7 +4495,10 @@
         <v>46299.625</v>
       </c>
       <c r="B158">
-        <v>109.132</v>
+        <v>96.72499999999999</v>
+      </c>
+      <c r="C158">
+        <v>0</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3177,7 +4512,10 @@
         <v>46299.63541666666</v>
       </c>
       <c r="B159">
-        <v>109.598</v>
+        <v>98.89</v>
+      </c>
+      <c r="C159">
+        <v>0</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3191,7 +4529,10 @@
         <v>46299.64583333334</v>
       </c>
       <c r="B160">
-        <v>109.968</v>
+        <v>99.90900000000001</v>
+      </c>
+      <c r="C160">
+        <v>0</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3205,7 +4546,10 @@
         <v>46299.65625</v>
       </c>
       <c r="B161">
-        <v>110.053</v>
+        <v>100.39</v>
+      </c>
+      <c r="C161">
+        <v>0</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3219,7 +4563,10 @@
         <v>46299.66666666666</v>
       </c>
       <c r="B162">
-        <v>121.081</v>
+        <v>112.764</v>
+      </c>
+      <c r="C162">
+        <v>0</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -3233,7 +4580,10 @@
         <v>46299.67708333334</v>
       </c>
       <c r="B163">
-        <v>122.384</v>
+        <v>114.19</v>
+      </c>
+      <c r="C163">
+        <v>0</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -3247,7 +4597,10 @@
         <v>46299.6875</v>
       </c>
       <c r="B164">
-        <v>123.342</v>
+        <v>115.103</v>
+      </c>
+      <c r="C164">
+        <v>0</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -3261,7 +4614,10 @@
         <v>46299.69791666666</v>
       </c>
       <c r="B165">
-        <v>124.935</v>
+        <v>117.017</v>
+      </c>
+      <c r="C165">
+        <v>0</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -3275,7 +4631,10 @@
         <v>46299.70833333334</v>
       </c>
       <c r="B166">
-        <v>121.196</v>
+        <v>127.428</v>
+      </c>
+      <c r="C166">
+        <v>0</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -3289,7 +4648,10 @@
         <v>46299.71875</v>
       </c>
       <c r="B167">
-        <v>123.975</v>
+        <v>128.807</v>
+      </c>
+      <c r="C167">
+        <v>0</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -3303,7 +4665,10 @@
         <v>46299.72916666666</v>
       </c>
       <c r="B168">
-        <v>126.537</v>
+        <v>131.325</v>
+      </c>
+      <c r="C168">
+        <v>0</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -3317,7 +4682,10 @@
         <v>46299.73958333334</v>
       </c>
       <c r="B169">
-        <v>129.661</v>
+        <v>142.181</v>
+      </c>
+      <c r="C169">
+        <v>0</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -3331,7 +4699,10 @@
         <v>46299.75</v>
       </c>
       <c r="B170">
-        <v>134.331</v>
+        <v>126.231</v>
+      </c>
+      <c r="C170">
+        <v>0</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -3345,7 +4716,10 @@
         <v>46299.76041666666</v>
       </c>
       <c r="B171">
-        <v>139.548</v>
+        <v>131.548</v>
+      </c>
+      <c r="C171">
+        <v>0</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -3359,7 +4733,10 @@
         <v>46299.77083333334</v>
       </c>
       <c r="B172">
-        <v>143.727</v>
+        <v>136.227</v>
+      </c>
+      <c r="C172">
+        <v>0</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -3373,7 +4750,10 @@
         <v>46299.78125</v>
       </c>
       <c r="B173">
-        <v>149.084</v>
+        <v>141.384</v>
+      </c>
+      <c r="C173">
+        <v>0</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -3387,7 +4767,10 @@
         <v>46299.79166666666</v>
       </c>
       <c r="B174">
-        <v>155.615</v>
+        <v>134.415</v>
+      </c>
+      <c r="C174">
+        <v>0</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -3401,7 +4784,10 @@
         <v>46299.80208333334</v>
       </c>
       <c r="B175">
-        <v>163.938</v>
+        <v>143.738</v>
+      </c>
+      <c r="C175">
+        <v>0</v>
       </c>
       <c r="D175">
         <v>78</v>
@@ -3415,7 +4801,10 @@
         <v>46299.8125</v>
       </c>
       <c r="B176">
-        <v>173.517</v>
+        <v>156.117</v>
+      </c>
+      <c r="C176">
+        <v>0</v>
       </c>
       <c r="D176">
         <v>79</v>
@@ -3429,7 +4818,10 @@
         <v>46299.82291666666</v>
       </c>
       <c r="B177">
-        <v>182.073</v>
+        <v>167.673</v>
+      </c>
+      <c r="C177">
+        <v>0</v>
       </c>
       <c r="D177">
         <v>80</v>
@@ -3443,7 +4835,10 @@
         <v>46299.83333333334</v>
       </c>
       <c r="B178">
-        <v>189.413</v>
+        <v>179.013</v>
+      </c>
+      <c r="C178">
+        <v>0</v>
       </c>
       <c r="D178">
         <v>81</v>
@@ -3457,7 +4852,10 @@
         <v>46299.84375</v>
       </c>
       <c r="B179">
-        <v>193.733</v>
+        <v>183.433</v>
+      </c>
+      <c r="C179">
+        <v>0</v>
       </c>
       <c r="D179">
         <v>82</v>
@@ -3471,7 +4869,10 @@
         <v>46299.85416666666</v>
       </c>
       <c r="B180">
-        <v>199.024</v>
+        <v>188.724</v>
+      </c>
+      <c r="C180">
+        <v>0</v>
       </c>
       <c r="D180">
         <v>83</v>
@@ -3485,7 +4886,10 @@
         <v>46299.86458333334</v>
       </c>
       <c r="B181">
-        <v>203.507</v>
+        <v>195.107</v>
+      </c>
+      <c r="C181">
+        <v>0</v>
       </c>
       <c r="D181">
         <v>84</v>
@@ -3499,7 +4903,10 @@
         <v>46299.875</v>
       </c>
       <c r="B182">
-        <v>204.348</v>
+        <v>201.748</v>
+      </c>
+      <c r="C182">
+        <v>0</v>
       </c>
       <c r="D182">
         <v>85</v>
@@ -3513,7 +4920,10 @@
         <v>46299.88541666666</v>
       </c>
       <c r="B183">
-        <v>206.27</v>
+        <v>203.87</v>
+      </c>
+      <c r="C183">
+        <v>0</v>
       </c>
       <c r="D183">
         <v>86</v>
@@ -3527,7 +4937,10 @@
         <v>46299.89583333334</v>
       </c>
       <c r="B184">
-        <v>208.311</v>
+        <v>201.011</v>
+      </c>
+      <c r="C184">
+        <v>0</v>
       </c>
       <c r="D184">
         <v>87</v>
@@ -3541,7 +4954,10 @@
         <v>46299.90625</v>
       </c>
       <c r="B185">
-        <v>209.937</v>
+        <v>206.437</v>
+      </c>
+      <c r="C185">
+        <v>0</v>
       </c>
       <c r="D185">
         <v>88</v>
@@ -3555,7 +4971,10 @@
         <v>46299.91666666666</v>
       </c>
       <c r="B186">
-        <v>212.048</v>
+        <v>211.048</v>
+      </c>
+      <c r="C186">
+        <v>0</v>
       </c>
       <c r="D186">
         <v>89</v>
@@ -3569,7 +4988,10 @@
         <v>46299.92708333334</v>
       </c>
       <c r="B187">
-        <v>211.211</v>
+        <v>210.311</v>
+      </c>
+      <c r="C187">
+        <v>0</v>
       </c>
       <c r="D187">
         <v>90</v>
@@ -3583,7 +5005,10 @@
         <v>46299.9375</v>
       </c>
       <c r="B188">
-        <v>210.164</v>
+        <v>209.964</v>
+      </c>
+      <c r="C188">
+        <v>0</v>
       </c>
       <c r="D188">
         <v>91</v>
@@ -3597,13 +5022,4756 @@
         <v>46299.94791666666</v>
       </c>
       <c r="B189">
-        <v>209.406</v>
+        <v>208.906</v>
+      </c>
+      <c r="C189">
+        <v>0</v>
       </c>
       <c r="D189">
         <v>92</v>
       </c>
       <c r="E189" t="s">
         <v>192</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190" s="2">
+        <v>46299.95833333334</v>
+      </c>
+      <c r="B190">
+        <v>236.746</v>
+      </c>
+      <c r="C190">
+        <v>0</v>
+      </c>
+      <c r="D190">
+        <v>93</v>
+      </c>
+      <c r="E190" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191" s="2">
+        <v>46299.96875</v>
+      </c>
+      <c r="B191">
+        <v>230.174</v>
+      </c>
+      <c r="C191">
+        <v>0</v>
+      </c>
+      <c r="D191">
+        <v>94</v>
+      </c>
+      <c r="E191" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192" s="2">
+        <v>46299.97916666666</v>
+      </c>
+      <c r="B192">
+        <v>224.488</v>
+      </c>
+      <c r="C192">
+        <v>0</v>
+      </c>
+      <c r="D192">
+        <v>95</v>
+      </c>
+      <c r="E192" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193" s="2">
+        <v>46299.98958333334</v>
+      </c>
+      <c r="B193">
+        <v>226.333</v>
+      </c>
+      <c r="C193">
+        <v>0</v>
+      </c>
+      <c r="D193">
+        <v>96</v>
+      </c>
+      <c r="E193" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B194">
+        <v>231.103</v>
+      </c>
+      <c r="C194">
+        <v>0</v>
+      </c>
+      <c r="D194">
+        <v>1</v>
+      </c>
+      <c r="E194" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" s="2">
+        <v>46300.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>233.302</v>
+      </c>
+      <c r="C195">
+        <v>0</v>
+      </c>
+      <c r="D195">
+        <v>2</v>
+      </c>
+      <c r="E195" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" s="2">
+        <v>46300.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>232.181</v>
+      </c>
+      <c r="C196">
+        <v>0</v>
+      </c>
+      <c r="D196">
+        <v>3</v>
+      </c>
+      <c r="E196" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" s="2">
+        <v>46300.03125</v>
+      </c>
+      <c r="B197">
+        <v>227.348</v>
+      </c>
+      <c r="C197">
+        <v>0</v>
+      </c>
+      <c r="D197">
+        <v>4</v>
+      </c>
+      <c r="E197" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" s="2">
+        <v>46300.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>218.595</v>
+      </c>
+      <c r="C198">
+        <v>0</v>
+      </c>
+      <c r="D198">
+        <v>5</v>
+      </c>
+      <c r="E198" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" s="2">
+        <v>46300.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>217.141</v>
+      </c>
+      <c r="C199">
+        <v>0</v>
+      </c>
+      <c r="D199">
+        <v>6</v>
+      </c>
+      <c r="E199" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" s="2">
+        <v>46300.0625</v>
+      </c>
+      <c r="B200">
+        <v>204.303</v>
+      </c>
+      <c r="C200">
+        <v>0</v>
+      </c>
+      <c r="D200">
+        <v>7</v>
+      </c>
+      <c r="E200" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" s="2">
+        <v>46300.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>197.663</v>
+      </c>
+      <c r="C201">
+        <v>0</v>
+      </c>
+      <c r="D201">
+        <v>8</v>
+      </c>
+      <c r="E201" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" s="2">
+        <v>46300.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>185.683</v>
+      </c>
+      <c r="C202">
+        <v>0</v>
+      </c>
+      <c r="D202">
+        <v>9</v>
+      </c>
+      <c r="E202" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" s="2">
+        <v>46300.09375</v>
+      </c>
+      <c r="B203">
+        <v>181.031</v>
+      </c>
+      <c r="C203">
+        <v>0</v>
+      </c>
+      <c r="D203">
+        <v>10</v>
+      </c>
+      <c r="E203" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" s="2">
+        <v>46300.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>177.01</v>
+      </c>
+      <c r="C204">
+        <v>0</v>
+      </c>
+      <c r="D204">
+        <v>11</v>
+      </c>
+      <c r="E204" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" s="2">
+        <v>46300.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>173.089</v>
+      </c>
+      <c r="C205">
+        <v>0</v>
+      </c>
+      <c r="D205">
+        <v>12</v>
+      </c>
+      <c r="E205" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" s="2">
+        <v>46300.125</v>
+      </c>
+      <c r="B206">
+        <v>170.631</v>
+      </c>
+      <c r="C206">
+        <v>0</v>
+      </c>
+      <c r="D206">
+        <v>13</v>
+      </c>
+      <c r="E206" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" s="2">
+        <v>46300.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>171.049</v>
+      </c>
+      <c r="C207">
+        <v>0</v>
+      </c>
+      <c r="D207">
+        <v>14</v>
+      </c>
+      <c r="E207" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" s="2">
+        <v>46300.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>168</v>
+      </c>
+      <c r="C208">
+        <v>0</v>
+      </c>
+      <c r="D208">
+        <v>15</v>
+      </c>
+      <c r="E208" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" s="2">
+        <v>46300.15625</v>
+      </c>
+      <c r="B209">
+        <v>162.601</v>
+      </c>
+      <c r="C209">
+        <v>0</v>
+      </c>
+      <c r="D209">
+        <v>16</v>
+      </c>
+      <c r="E209" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" s="2">
+        <v>46300.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>144.787</v>
+      </c>
+      <c r="C210">
+        <v>0</v>
+      </c>
+      <c r="D210">
+        <v>17</v>
+      </c>
+      <c r="E210" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" s="2">
+        <v>46300.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>143.652</v>
+      </c>
+      <c r="C211">
+        <v>0</v>
+      </c>
+      <c r="D211">
+        <v>18</v>
+      </c>
+      <c r="E211" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" s="2">
+        <v>46300.1875</v>
+      </c>
+      <c r="B212">
+        <v>139.989</v>
+      </c>
+      <c r="C212">
+        <v>0</v>
+      </c>
+      <c r="D212">
+        <v>19</v>
+      </c>
+      <c r="E212" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" s="2">
+        <v>46300.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>137.783</v>
+      </c>
+      <c r="C213">
+        <v>0</v>
+      </c>
+      <c r="D213">
+        <v>20</v>
+      </c>
+      <c r="E213" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" s="2">
+        <v>46300.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>125.175</v>
+      </c>
+      <c r="C214">
+        <v>0</v>
+      </c>
+      <c r="D214">
+        <v>21</v>
+      </c>
+      <c r="E214" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" s="2">
+        <v>46300.21875</v>
+      </c>
+      <c r="B215">
+        <v>124.344</v>
+      </c>
+      <c r="C215">
+        <v>0</v>
+      </c>
+      <c r="D215">
+        <v>22</v>
+      </c>
+      <c r="E215" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" s="2">
+        <v>46300.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>123.823</v>
+      </c>
+      <c r="C216">
+        <v>0</v>
+      </c>
+      <c r="D216">
+        <v>23</v>
+      </c>
+      <c r="E216" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" s="2">
+        <v>46300.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>123.281</v>
+      </c>
+      <c r="C217">
+        <v>0</v>
+      </c>
+      <c r="D217">
+        <v>24</v>
+      </c>
+      <c r="E217" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" s="2">
+        <v>46300.25</v>
+      </c>
+      <c r="B218">
+        <v>117.7</v>
+      </c>
+      <c r="C218">
+        <v>0</v>
+      </c>
+      <c r="D218">
+        <v>25</v>
+      </c>
+      <c r="E218" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" s="2">
+        <v>46300.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>115.879</v>
+      </c>
+      <c r="C219">
+        <v>0</v>
+      </c>
+      <c r="D219">
+        <v>26</v>
+      </c>
+      <c r="E219" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" s="2">
+        <v>46300.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>109.405</v>
+      </c>
+      <c r="C220">
+        <v>0</v>
+      </c>
+      <c r="D220">
+        <v>27</v>
+      </c>
+      <c r="E220" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" s="2">
+        <v>46300.28125</v>
+      </c>
+      <c r="B221">
+        <v>108.984</v>
+      </c>
+      <c r="C221">
+        <v>0</v>
+      </c>
+      <c r="D221">
+        <v>28</v>
+      </c>
+      <c r="E221" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" s="2">
+        <v>46300.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>112.785</v>
+      </c>
+      <c r="C222">
+        <v>0</v>
+      </c>
+      <c r="D222">
+        <v>29</v>
+      </c>
+      <c r="E222" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" s="2">
+        <v>46300.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>113.201</v>
+      </c>
+      <c r="C223">
+        <v>0</v>
+      </c>
+      <c r="D223">
+        <v>30</v>
+      </c>
+      <c r="E223" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" s="2">
+        <v>46300.3125</v>
+      </c>
+      <c r="B224">
+        <v>117.245</v>
+      </c>
+      <c r="C224">
+        <v>0</v>
+      </c>
+      <c r="D224">
+        <v>31</v>
+      </c>
+      <c r="E224" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225" s="2">
+        <v>46300.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>118.588</v>
+      </c>
+      <c r="C225">
+        <v>0</v>
+      </c>
+      <c r="D225">
+        <v>32</v>
+      </c>
+      <c r="E225" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226" s="2">
+        <v>46300.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>119.34</v>
+      </c>
+      <c r="C226">
+        <v>0</v>
+      </c>
+      <c r="D226">
+        <v>33</v>
+      </c>
+      <c r="E226" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227" s="2">
+        <v>46300.34375</v>
+      </c>
+      <c r="B227">
+        <v>120.455</v>
+      </c>
+      <c r="C227">
+        <v>0</v>
+      </c>
+      <c r="D227">
+        <v>34</v>
+      </c>
+      <c r="E227" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228" s="2">
+        <v>46300.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>124.364</v>
+      </c>
+      <c r="C228">
+        <v>0</v>
+      </c>
+      <c r="D228">
+        <v>35</v>
+      </c>
+      <c r="E228" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229" s="2">
+        <v>46300.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>129.171</v>
+      </c>
+      <c r="C229">
+        <v>0</v>
+      </c>
+      <c r="D229">
+        <v>36</v>
+      </c>
+      <c r="E229" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230" s="2">
+        <v>46300.375</v>
+      </c>
+      <c r="B230">
+        <v>137.581</v>
+      </c>
+      <c r="C230">
+        <v>0</v>
+      </c>
+      <c r="D230">
+        <v>37</v>
+      </c>
+      <c r="E230" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" s="2">
+        <v>46300.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>146.046</v>
+      </c>
+      <c r="C231">
+        <v>0</v>
+      </c>
+      <c r="D231">
+        <v>38</v>
+      </c>
+      <c r="E231" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" s="2">
+        <v>46300.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>146.99</v>
+      </c>
+      <c r="C232">
+        <v>0</v>
+      </c>
+      <c r="D232">
+        <v>39</v>
+      </c>
+      <c r="E232" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" s="2">
+        <v>46300.40625</v>
+      </c>
+      <c r="B233">
+        <v>141.751</v>
+      </c>
+      <c r="C233">
+        <v>0</v>
+      </c>
+      <c r="D233">
+        <v>40</v>
+      </c>
+      <c r="E233" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" s="2">
+        <v>46300.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>176.884</v>
+      </c>
+      <c r="C234">
+        <v>0</v>
+      </c>
+      <c r="D234">
+        <v>41</v>
+      </c>
+      <c r="E234" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235" s="2">
+        <v>46300.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>171.149</v>
+      </c>
+      <c r="C235">
+        <v>0</v>
+      </c>
+      <c r="D235">
+        <v>42</v>
+      </c>
+      <c r="E235" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" s="2">
+        <v>46300.4375</v>
+      </c>
+      <c r="B236">
+        <v>166.376</v>
+      </c>
+      <c r="C236">
+        <v>0</v>
+      </c>
+      <c r="D236">
+        <v>43</v>
+      </c>
+      <c r="E236" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" s="2">
+        <v>46300.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>157.329</v>
+      </c>
+      <c r="C237">
+        <v>0</v>
+      </c>
+      <c r="D237">
+        <v>44</v>
+      </c>
+      <c r="E237" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" s="2">
+        <v>46300.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>174.164</v>
+      </c>
+      <c r="C238">
+        <v>0</v>
+      </c>
+      <c r="D238">
+        <v>45</v>
+      </c>
+      <c r="E238" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239" s="2">
+        <v>46300.46875</v>
+      </c>
+      <c r="B239">
+        <v>175.264</v>
+      </c>
+      <c r="C239">
+        <v>0</v>
+      </c>
+      <c r="D239">
+        <v>46</v>
+      </c>
+      <c r="E239" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" s="2">
+        <v>46300.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>171.545</v>
+      </c>
+      <c r="C240">
+        <v>0</v>
+      </c>
+      <c r="D240">
+        <v>47</v>
+      </c>
+      <c r="E240" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" s="2">
+        <v>46300.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>172.159</v>
+      </c>
+      <c r="C241">
+        <v>0</v>
+      </c>
+      <c r="D241">
+        <v>48</v>
+      </c>
+      <c r="E241" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" s="2">
+        <v>46300.5</v>
+      </c>
+      <c r="B242">
+        <v>142.325</v>
+      </c>
+      <c r="C242">
+        <v>0</v>
+      </c>
+      <c r="D242">
+        <v>49</v>
+      </c>
+      <c r="E242" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" s="2">
+        <v>46300.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>149.906</v>
+      </c>
+      <c r="C243">
+        <v>0</v>
+      </c>
+      <c r="D243">
+        <v>50</v>
+      </c>
+      <c r="E243" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" s="2">
+        <v>46300.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>155.037</v>
+      </c>
+      <c r="C244">
+        <v>0</v>
+      </c>
+      <c r="D244">
+        <v>51</v>
+      </c>
+      <c r="E244" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" s="2">
+        <v>46300.53125</v>
+      </c>
+      <c r="B245">
+        <v>159.273</v>
+      </c>
+      <c r="C245">
+        <v>0</v>
+      </c>
+      <c r="D245">
+        <v>52</v>
+      </c>
+      <c r="E245" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" s="2">
+        <v>46300.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>152.436</v>
+      </c>
+      <c r="C246">
+        <v>0</v>
+      </c>
+      <c r="D246">
+        <v>53</v>
+      </c>
+      <c r="E246" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" s="2">
+        <v>46300.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>158.408</v>
+      </c>
+      <c r="C247">
+        <v>0</v>
+      </c>
+      <c r="D247">
+        <v>54</v>
+      </c>
+      <c r="E247" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" s="2">
+        <v>46300.5625</v>
+      </c>
+      <c r="B248">
+        <v>159.527</v>
+      </c>
+      <c r="C248">
+        <v>0</v>
+      </c>
+      <c r="D248">
+        <v>55</v>
+      </c>
+      <c r="E248" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" s="2">
+        <v>46300.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>166.833</v>
+      </c>
+      <c r="C249">
+        <v>0</v>
+      </c>
+      <c r="D249">
+        <v>56</v>
+      </c>
+      <c r="E249" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" s="2">
+        <v>46300.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>168.949</v>
+      </c>
+      <c r="C250">
+        <v>0</v>
+      </c>
+      <c r="D250">
+        <v>57</v>
+      </c>
+      <c r="E250" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251" s="2">
+        <v>46300.59375</v>
+      </c>
+      <c r="B251">
+        <v>160.937</v>
+      </c>
+      <c r="C251">
+        <v>0</v>
+      </c>
+      <c r="D251">
+        <v>58</v>
+      </c>
+      <c r="E251" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252" s="2">
+        <v>46300.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>165.015</v>
+      </c>
+      <c r="C252">
+        <v>0</v>
+      </c>
+      <c r="D252">
+        <v>59</v>
+      </c>
+      <c r="E252" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253" s="2">
+        <v>46300.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>167.807</v>
+      </c>
+      <c r="C253">
+        <v>0</v>
+      </c>
+      <c r="D253">
+        <v>60</v>
+      </c>
+      <c r="E253" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254" s="2">
+        <v>46300.625</v>
+      </c>
+      <c r="B254">
+        <v>166.518</v>
+      </c>
+      <c r="C254">
+        <v>0</v>
+      </c>
+      <c r="D254">
+        <v>61</v>
+      </c>
+      <c r="E254" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255" s="2">
+        <v>46300.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>179.118</v>
+      </c>
+      <c r="C255">
+        <v>0</v>
+      </c>
+      <c r="D255">
+        <v>62</v>
+      </c>
+      <c r="E255" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256" s="2">
+        <v>46300.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>184.702</v>
+      </c>
+      <c r="C256">
+        <v>0</v>
+      </c>
+      <c r="D256">
+        <v>63</v>
+      </c>
+      <c r="E256" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257" s="2">
+        <v>46300.65625</v>
+      </c>
+      <c r="B257">
+        <v>181.61</v>
+      </c>
+      <c r="C257">
+        <v>0</v>
+      </c>
+      <c r="D257">
+        <v>64</v>
+      </c>
+      <c r="E257" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258" s="2">
+        <v>46300.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>184.582</v>
+      </c>
+      <c r="C258">
+        <v>0</v>
+      </c>
+      <c r="D258">
+        <v>65</v>
+      </c>
+      <c r="E258" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259" s="2">
+        <v>46300.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>181.996</v>
+      </c>
+      <c r="C259">
+        <v>0</v>
+      </c>
+      <c r="D259">
+        <v>66</v>
+      </c>
+      <c r="E259" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260" s="2">
+        <v>46300.6875</v>
+      </c>
+      <c r="B260">
+        <v>201</v>
+      </c>
+      <c r="C260">
+        <v>0</v>
+      </c>
+      <c r="D260">
+        <v>67</v>
+      </c>
+      <c r="E260" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261" s="2">
+        <v>46300.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>200.913</v>
+      </c>
+      <c r="C261">
+        <v>0</v>
+      </c>
+      <c r="D261">
+        <v>68</v>
+      </c>
+      <c r="E261" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262" s="2">
+        <v>46300.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>155.486</v>
+      </c>
+      <c r="C262">
+        <v>0</v>
+      </c>
+      <c r="D262">
+        <v>69</v>
+      </c>
+      <c r="E262" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263" s="2">
+        <v>46300.71875</v>
+      </c>
+      <c r="B263">
+        <v>158.757</v>
+      </c>
+      <c r="C263">
+        <v>0</v>
+      </c>
+      <c r="D263">
+        <v>70</v>
+      </c>
+      <c r="E263" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264" s="2">
+        <v>46300.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>141.154</v>
+      </c>
+      <c r="C264">
+        <v>0</v>
+      </c>
+      <c r="D264">
+        <v>71</v>
+      </c>
+      <c r="E264" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265" s="2">
+        <v>46300.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>148.051</v>
+      </c>
+      <c r="C265">
+        <v>0</v>
+      </c>
+      <c r="D265">
+        <v>72</v>
+      </c>
+      <c r="E265" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="A266" s="2">
+        <v>46300.75</v>
+      </c>
+      <c r="B266">
+        <v>135.071</v>
+      </c>
+      <c r="C266">
+        <v>0</v>
+      </c>
+      <c r="D266">
+        <v>73</v>
+      </c>
+      <c r="E266" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267" s="2">
+        <v>46300.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>133.979</v>
+      </c>
+      <c r="C267">
+        <v>0</v>
+      </c>
+      <c r="D267">
+        <v>74</v>
+      </c>
+      <c r="E267" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268" s="2">
+        <v>46300.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>135.894</v>
+      </c>
+      <c r="C268">
+        <v>0</v>
+      </c>
+      <c r="D268">
+        <v>75</v>
+      </c>
+      <c r="E268" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269" s="2">
+        <v>46300.78125</v>
+      </c>
+      <c r="B269">
+        <v>138.049</v>
+      </c>
+      <c r="C269">
+        <v>0</v>
+      </c>
+      <c r="D269">
+        <v>76</v>
+      </c>
+      <c r="E269" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270" s="2">
+        <v>46300.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>173.86</v>
+      </c>
+      <c r="C270">
+        <v>0</v>
+      </c>
+      <c r="D270">
+        <v>77</v>
+      </c>
+      <c r="E270" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271" s="2">
+        <v>46300.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>176.87</v>
+      </c>
+      <c r="C271">
+        <v>0</v>
+      </c>
+      <c r="D271">
+        <v>78</v>
+      </c>
+      <c r="E271" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272" s="2">
+        <v>46300.8125</v>
+      </c>
+      <c r="B272">
+        <v>178.36</v>
+      </c>
+      <c r="C272">
+        <v>0</v>
+      </c>
+      <c r="D272">
+        <v>79</v>
+      </c>
+      <c r="E272" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5">
+      <c r="A273" s="2">
+        <v>46300.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>183.685</v>
+      </c>
+      <c r="C273">
+        <v>0</v>
+      </c>
+      <c r="D273">
+        <v>80</v>
+      </c>
+      <c r="E273" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5">
+      <c r="A274" s="2">
+        <v>46300.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>175.188</v>
+      </c>
+      <c r="C274">
+        <v>0</v>
+      </c>
+      <c r="D274">
+        <v>81</v>
+      </c>
+      <c r="E274" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5">
+      <c r="A275" s="2">
+        <v>46300.84375</v>
+      </c>
+      <c r="B275">
+        <v>180.229</v>
+      </c>
+      <c r="C275">
+        <v>0</v>
+      </c>
+      <c r="D275">
+        <v>82</v>
+      </c>
+      <c r="E275" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5">
+      <c r="A276" s="2">
+        <v>46300.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>178.195</v>
+      </c>
+      <c r="C276">
+        <v>0</v>
+      </c>
+      <c r="D276">
+        <v>83</v>
+      </c>
+      <c r="E276" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5">
+      <c r="A277" s="2">
+        <v>46300.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>178.939</v>
+      </c>
+      <c r="C277">
+        <v>0</v>
+      </c>
+      <c r="D277">
+        <v>84</v>
+      </c>
+      <c r="E277" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5">
+      <c r="A278" s="2">
+        <v>46300.875</v>
+      </c>
+      <c r="B278">
+        <v>177.688</v>
+      </c>
+      <c r="C278">
+        <v>0</v>
+      </c>
+      <c r="D278">
+        <v>85</v>
+      </c>
+      <c r="E278" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5">
+      <c r="A279" s="2">
+        <v>46300.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>178.552</v>
+      </c>
+      <c r="C279">
+        <v>0</v>
+      </c>
+      <c r="D279">
+        <v>86</v>
+      </c>
+      <c r="E279" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5">
+      <c r="A280" s="2">
+        <v>46300.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>174.55</v>
+      </c>
+      <c r="C280">
+        <v>0</v>
+      </c>
+      <c r="D280">
+        <v>87</v>
+      </c>
+      <c r="E280" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5">
+      <c r="A281" s="2">
+        <v>46300.90625</v>
+      </c>
+      <c r="B281">
+        <v>173.696</v>
+      </c>
+      <c r="C281">
+        <v>0</v>
+      </c>
+      <c r="D281">
+        <v>88</v>
+      </c>
+      <c r="E281" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5">
+      <c r="A282" s="2">
+        <v>46300.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>178.347</v>
+      </c>
+      <c r="C282">
+        <v>0</v>
+      </c>
+      <c r="D282">
+        <v>89</v>
+      </c>
+      <c r="E282" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5">
+      <c r="A283" s="2">
+        <v>46300.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>182.239</v>
+      </c>
+      <c r="C283">
+        <v>0</v>
+      </c>
+      <c r="D283">
+        <v>90</v>
+      </c>
+      <c r="E283" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5">
+      <c r="A284" s="2">
+        <v>46300.9375</v>
+      </c>
+      <c r="B284">
+        <v>182.684</v>
+      </c>
+      <c r="C284">
+        <v>0</v>
+      </c>
+      <c r="D284">
+        <v>91</v>
+      </c>
+      <c r="E284" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5">
+      <c r="A285" s="2">
+        <v>46300.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>177.329</v>
+      </c>
+      <c r="C285">
+        <v>0</v>
+      </c>
+      <c r="D285">
+        <v>92</v>
+      </c>
+      <c r="E285" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5">
+      <c r="A286" s="2">
+        <v>46300.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>179.607</v>
+      </c>
+      <c r="C286">
+        <v>0</v>
+      </c>
+      <c r="D286">
+        <v>93</v>
+      </c>
+      <c r="E286" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5">
+      <c r="A287" s="2">
+        <v>46300.96875</v>
+      </c>
+      <c r="B287">
+        <v>178.421</v>
+      </c>
+      <c r="C287">
+        <v>0</v>
+      </c>
+      <c r="D287">
+        <v>94</v>
+      </c>
+      <c r="E287" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5">
+      <c r="A288" s="2">
+        <v>46300.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>179.841</v>
+      </c>
+      <c r="C288">
+        <v>0</v>
+      </c>
+      <c r="D288">
+        <v>95</v>
+      </c>
+      <c r="E288" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5">
+      <c r="A289" s="2">
+        <v>46300.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>178.28</v>
+      </c>
+      <c r="C289">
+        <v>0</v>
+      </c>
+      <c r="D289">
+        <v>96</v>
+      </c>
+      <c r="E289" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B290">
+        <v>180.564</v>
+      </c>
+      <c r="C290">
+        <v>0</v>
+      </c>
+      <c r="D290">
+        <v>1</v>
+      </c>
+      <c r="E290" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291" s="2">
+        <v>46301.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>181.776</v>
+      </c>
+      <c r="C291">
+        <v>0</v>
+      </c>
+      <c r="D291">
+        <v>2</v>
+      </c>
+      <c r="E291" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292" s="2">
+        <v>46301.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>182.381</v>
+      </c>
+      <c r="C292">
+        <v>0</v>
+      </c>
+      <c r="D292">
+        <v>3</v>
+      </c>
+      <c r="E292" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" s="2">
+        <v>46301.03125</v>
+      </c>
+      <c r="B293">
+        <v>182.078</v>
+      </c>
+      <c r="C293">
+        <v>0</v>
+      </c>
+      <c r="D293">
+        <v>4</v>
+      </c>
+      <c r="E293" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294" s="2">
+        <v>46301.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>192.625</v>
+      </c>
+      <c r="C294">
+        <v>0</v>
+      </c>
+      <c r="D294">
+        <v>5</v>
+      </c>
+      <c r="E294" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295" s="2">
+        <v>46301.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>198.456</v>
+      </c>
+      <c r="C295">
+        <v>0</v>
+      </c>
+      <c r="D295">
+        <v>6</v>
+      </c>
+      <c r="E295" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296" s="2">
+        <v>46301.0625</v>
+      </c>
+      <c r="B296">
+        <v>201.071</v>
+      </c>
+      <c r="C296">
+        <v>0</v>
+      </c>
+      <c r="D296">
+        <v>7</v>
+      </c>
+      <c r="E296" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297" s="2">
+        <v>46301.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>206.948</v>
+      </c>
+      <c r="C297">
+        <v>0</v>
+      </c>
+      <c r="D297">
+        <v>8</v>
+      </c>
+      <c r="E297" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="A298" s="2">
+        <v>46301.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>209.84</v>
+      </c>
+      <c r="C298">
+        <v>0</v>
+      </c>
+      <c r="D298">
+        <v>9</v>
+      </c>
+      <c r="E298" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="A299" s="2">
+        <v>46301.09375</v>
+      </c>
+      <c r="B299">
+        <v>209.157</v>
+      </c>
+      <c r="C299">
+        <v>0</v>
+      </c>
+      <c r="D299">
+        <v>10</v>
+      </c>
+      <c r="E299" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300" s="2">
+        <v>46301.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>215.088</v>
+      </c>
+      <c r="C300">
+        <v>0</v>
+      </c>
+      <c r="D300">
+        <v>11</v>
+      </c>
+      <c r="E300" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5">
+      <c r="A301" s="2">
+        <v>46301.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>215.398</v>
+      </c>
+      <c r="C301">
+        <v>0</v>
+      </c>
+      <c r="D301">
+        <v>12</v>
+      </c>
+      <c r="E301" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5">
+      <c r="A302" s="2">
+        <v>46301.125</v>
+      </c>
+      <c r="B302">
+        <v>202.188</v>
+      </c>
+      <c r="C302">
+        <v>0</v>
+      </c>
+      <c r="D302">
+        <v>13</v>
+      </c>
+      <c r="E302" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303" s="2">
+        <v>46301.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>201.628</v>
+      </c>
+      <c r="C303">
+        <v>0</v>
+      </c>
+      <c r="D303">
+        <v>14</v>
+      </c>
+      <c r="E303" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304" s="2">
+        <v>46301.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>196.683</v>
+      </c>
+      <c r="C304">
+        <v>0</v>
+      </c>
+      <c r="D304">
+        <v>15</v>
+      </c>
+      <c r="E304" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305" s="2">
+        <v>46301.15625</v>
+      </c>
+      <c r="B305">
+        <v>194.838</v>
+      </c>
+      <c r="C305">
+        <v>0</v>
+      </c>
+      <c r="D305">
+        <v>16</v>
+      </c>
+      <c r="E305" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306" s="2">
+        <v>46301.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>197.867</v>
+      </c>
+      <c r="C306">
+        <v>0</v>
+      </c>
+      <c r="D306">
+        <v>17</v>
+      </c>
+      <c r="E306" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307" s="2">
+        <v>46301.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>201.402</v>
+      </c>
+      <c r="C307">
+        <v>0</v>
+      </c>
+      <c r="D307">
+        <v>18</v>
+      </c>
+      <c r="E307" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308" s="2">
+        <v>46301.1875</v>
+      </c>
+      <c r="B308">
+        <v>208.844</v>
+      </c>
+      <c r="C308">
+        <v>0</v>
+      </c>
+      <c r="D308">
+        <v>19</v>
+      </c>
+      <c r="E308" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309" s="2">
+        <v>46301.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>205.826</v>
+      </c>
+      <c r="C309">
+        <v>0</v>
+      </c>
+      <c r="D309">
+        <v>20</v>
+      </c>
+      <c r="E309" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310" s="2">
+        <v>46301.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>184.971</v>
+      </c>
+      <c r="C310">
+        <v>0</v>
+      </c>
+      <c r="D310">
+        <v>21</v>
+      </c>
+      <c r="E310" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" s="2">
+        <v>46301.21875</v>
+      </c>
+      <c r="B311">
+        <v>184.957</v>
+      </c>
+      <c r="C311">
+        <v>0</v>
+      </c>
+      <c r="D311">
+        <v>22</v>
+      </c>
+      <c r="E311" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" s="2">
+        <v>46301.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>180.825</v>
+      </c>
+      <c r="C312">
+        <v>0</v>
+      </c>
+      <c r="D312">
+        <v>23</v>
+      </c>
+      <c r="E312" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313" s="2">
+        <v>46301.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>178.989</v>
+      </c>
+      <c r="C313">
+        <v>0</v>
+      </c>
+      <c r="D313">
+        <v>24</v>
+      </c>
+      <c r="E313" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" s="2">
+        <v>46301.25</v>
+      </c>
+      <c r="B314">
+        <v>158.431</v>
+      </c>
+      <c r="C314">
+        <v>0</v>
+      </c>
+      <c r="D314">
+        <v>25</v>
+      </c>
+      <c r="E314" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" s="2">
+        <v>46301.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>156.239</v>
+      </c>
+      <c r="C315">
+        <v>0</v>
+      </c>
+      <c r="D315">
+        <v>26</v>
+      </c>
+      <c r="E315" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" s="2">
+        <v>46301.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>146.612</v>
+      </c>
+      <c r="C316">
+        <v>0</v>
+      </c>
+      <c r="D316">
+        <v>27</v>
+      </c>
+      <c r="E316" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317" s="2">
+        <v>46301.28125</v>
+      </c>
+      <c r="B317">
+        <v>143.428</v>
+      </c>
+      <c r="C317">
+        <v>0</v>
+      </c>
+      <c r="D317">
+        <v>28</v>
+      </c>
+      <c r="E317" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318" s="2">
+        <v>46301.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>157.228</v>
+      </c>
+      <c r="C318">
+        <v>0</v>
+      </c>
+      <c r="D318">
+        <v>29</v>
+      </c>
+      <c r="E318" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319" s="2">
+        <v>46301.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>154.134</v>
+      </c>
+      <c r="C319">
+        <v>0</v>
+      </c>
+      <c r="D319">
+        <v>30</v>
+      </c>
+      <c r="E319" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320" s="2">
+        <v>46301.3125</v>
+      </c>
+      <c r="B320">
+        <v>155.867</v>
+      </c>
+      <c r="C320">
+        <v>0</v>
+      </c>
+      <c r="D320">
+        <v>31</v>
+      </c>
+      <c r="E320" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5">
+      <c r="A321" s="2">
+        <v>46301.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>154.734</v>
+      </c>
+      <c r="C321">
+        <v>0</v>
+      </c>
+      <c r="D321">
+        <v>32</v>
+      </c>
+      <c r="E321" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5">
+      <c r="A322" s="2">
+        <v>46301.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>154.002</v>
+      </c>
+      <c r="C322">
+        <v>0</v>
+      </c>
+      <c r="D322">
+        <v>33</v>
+      </c>
+      <c r="E322" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5">
+      <c r="A323" s="2">
+        <v>46301.34375</v>
+      </c>
+      <c r="B323">
+        <v>149.122</v>
+      </c>
+      <c r="C323">
+        <v>0</v>
+      </c>
+      <c r="D323">
+        <v>34</v>
+      </c>
+      <c r="E323" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5">
+      <c r="A324" s="2">
+        <v>46301.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>146.221</v>
+      </c>
+      <c r="C324">
+        <v>0</v>
+      </c>
+      <c r="D324">
+        <v>35</v>
+      </c>
+      <c r="E324" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5">
+      <c r="A325" s="2">
+        <v>46301.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>142.532</v>
+      </c>
+      <c r="C325">
+        <v>0</v>
+      </c>
+      <c r="D325">
+        <v>36</v>
+      </c>
+      <c r="E325" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5">
+      <c r="A326" s="2">
+        <v>46301.375</v>
+      </c>
+      <c r="B326">
+        <v>154.104</v>
+      </c>
+      <c r="C326">
+        <v>56</v>
+      </c>
+      <c r="D326">
+        <v>37</v>
+      </c>
+      <c r="E326" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5">
+      <c r="A327" s="2">
+        <v>46301.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>149.289</v>
+      </c>
+      <c r="C327">
+        <v>38</v>
+      </c>
+      <c r="D327">
+        <v>38</v>
+      </c>
+      <c r="E327" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5">
+      <c r="A328" s="2">
+        <v>46301.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>148.44</v>
+      </c>
+      <c r="C328">
+        <v>24</v>
+      </c>
+      <c r="D328">
+        <v>39</v>
+      </c>
+      <c r="E328" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5">
+      <c r="A329" s="2">
+        <v>46301.40625</v>
+      </c>
+      <c r="B329">
+        <v>137.635</v>
+      </c>
+      <c r="C329">
+        <v>14</v>
+      </c>
+      <c r="D329">
+        <v>40</v>
+      </c>
+      <c r="E329" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5">
+      <c r="A330" s="2">
+        <v>46301.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>170.836</v>
+      </c>
+      <c r="C330">
+        <v>6</v>
+      </c>
+      <c r="D330">
+        <v>41</v>
+      </c>
+      <c r="E330" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5">
+      <c r="A331" s="2">
+        <v>46301.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>163.989</v>
+      </c>
+      <c r="C331">
+        <v>0</v>
+      </c>
+      <c r="D331">
+        <v>42</v>
+      </c>
+      <c r="E331" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5">
+      <c r="A332" s="2">
+        <v>46301.4375</v>
+      </c>
+      <c r="B332">
+        <v>158.391</v>
+      </c>
+      <c r="C332">
+        <v>0</v>
+      </c>
+      <c r="D332">
+        <v>43</v>
+      </c>
+      <c r="E332" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5">
+      <c r="A333" s="2">
+        <v>46301.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>150.774</v>
+      </c>
+      <c r="C333">
+        <v>0</v>
+      </c>
+      <c r="D333">
+        <v>44</v>
+      </c>
+      <c r="E333" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5">
+      <c r="A334" s="2">
+        <v>46301.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>142.406</v>
+      </c>
+      <c r="C334">
+        <v>0</v>
+      </c>
+      <c r="D334">
+        <v>45</v>
+      </c>
+      <c r="E334" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5">
+      <c r="A335" s="2">
+        <v>46301.46875</v>
+      </c>
+      <c r="B335">
+        <v>140.578</v>
+      </c>
+      <c r="C335">
+        <v>0</v>
+      </c>
+      <c r="D335">
+        <v>46</v>
+      </c>
+      <c r="E335" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5">
+      <c r="A336" s="2">
+        <v>46301.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>147.6</v>
+      </c>
+      <c r="C336">
+        <v>0</v>
+      </c>
+      <c r="D336">
+        <v>47</v>
+      </c>
+      <c r="E336" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5">
+      <c r="A337" s="2">
+        <v>46301.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>148.029</v>
+      </c>
+      <c r="C337">
+        <v>0</v>
+      </c>
+      <c r="D337">
+        <v>48</v>
+      </c>
+      <c r="E337" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5">
+      <c r="A338" s="2">
+        <v>46301.5</v>
+      </c>
+      <c r="B338">
+        <v>150.446</v>
+      </c>
+      <c r="C338">
+        <v>0</v>
+      </c>
+      <c r="D338">
+        <v>49</v>
+      </c>
+      <c r="E338" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5">
+      <c r="A339" s="2">
+        <v>46301.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>154.996</v>
+      </c>
+      <c r="C339">
+        <v>0</v>
+      </c>
+      <c r="D339">
+        <v>50</v>
+      </c>
+      <c r="E339" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5">
+      <c r="A340" s="2">
+        <v>46301.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>157.012</v>
+      </c>
+      <c r="C340">
+        <v>0</v>
+      </c>
+      <c r="D340">
+        <v>51</v>
+      </c>
+      <c r="E340" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5">
+      <c r="A341" s="2">
+        <v>46301.53125</v>
+      </c>
+      <c r="B341">
+        <v>144.659</v>
+      </c>
+      <c r="C341">
+        <v>0</v>
+      </c>
+      <c r="D341">
+        <v>52</v>
+      </c>
+      <c r="E341" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5">
+      <c r="A342" s="2">
+        <v>46301.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>120.464</v>
+      </c>
+      <c r="C342">
+        <v>0</v>
+      </c>
+      <c r="D342">
+        <v>53</v>
+      </c>
+      <c r="E342" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5">
+      <c r="A343" s="2">
+        <v>46301.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>122.817</v>
+      </c>
+      <c r="C343">
+        <v>4</v>
+      </c>
+      <c r="D343">
+        <v>54</v>
+      </c>
+      <c r="E343" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5">
+      <c r="A344" s="2">
+        <v>46301.5625</v>
+      </c>
+      <c r="B344">
+        <v>128.848</v>
+      </c>
+      <c r="C344">
+        <v>7</v>
+      </c>
+      <c r="D344">
+        <v>55</v>
+      </c>
+      <c r="E344" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5">
+      <c r="A345" s="2">
+        <v>46301.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>129.938</v>
+      </c>
+      <c r="C345">
+        <v>12</v>
+      </c>
+      <c r="D345">
+        <v>56</v>
+      </c>
+      <c r="E345" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5">
+      <c r="A346" s="2">
+        <v>46301.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>128.935</v>
+      </c>
+      <c r="C346">
+        <v>10</v>
+      </c>
+      <c r="D346">
+        <v>57</v>
+      </c>
+      <c r="E346" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5">
+      <c r="A347" s="2">
+        <v>46301.59375</v>
+      </c>
+      <c r="B347">
+        <v>130.333</v>
+      </c>
+      <c r="C347">
+        <v>11</v>
+      </c>
+      <c r="D347">
+        <v>58</v>
+      </c>
+      <c r="E347" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5">
+      <c r="A348" s="2">
+        <v>46301.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>131.521</v>
+      </c>
+      <c r="C348">
+        <v>14</v>
+      </c>
+      <c r="D348">
+        <v>59</v>
+      </c>
+      <c r="E348" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5">
+      <c r="A349" s="2">
+        <v>46301.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>132.261</v>
+      </c>
+      <c r="C349">
+        <v>16</v>
+      </c>
+      <c r="D349">
+        <v>60</v>
+      </c>
+      <c r="E349" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5">
+      <c r="A350" s="2">
+        <v>46301.625</v>
+      </c>
+      <c r="B350">
+        <v>123.094</v>
+      </c>
+      <c r="C350">
+        <v>22</v>
+      </c>
+      <c r="D350">
+        <v>61</v>
+      </c>
+      <c r="E350" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5">
+      <c r="A351" s="2">
+        <v>46301.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>123.185</v>
+      </c>
+      <c r="C351">
+        <v>26</v>
+      </c>
+      <c r="D351">
+        <v>62</v>
+      </c>
+      <c r="E351" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5">
+      <c r="A352" s="2">
+        <v>46301.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>122.965</v>
+      </c>
+      <c r="C352">
+        <v>44</v>
+      </c>
+      <c r="D352">
+        <v>63</v>
+      </c>
+      <c r="E352" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5">
+      <c r="A353" s="2">
+        <v>46301.65625</v>
+      </c>
+      <c r="B353">
+        <v>122.686</v>
+      </c>
+      <c r="C353">
+        <v>55</v>
+      </c>
+      <c r="D353">
+        <v>64</v>
+      </c>
+      <c r="E353" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5">
+      <c r="A354" s="2">
+        <v>46301.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>121.532</v>
+      </c>
+      <c r="C354">
+        <v>48</v>
+      </c>
+      <c r="D354">
+        <v>65</v>
+      </c>
+      <c r="E354" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5">
+      <c r="A355" s="2">
+        <v>46301.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>121.137</v>
+      </c>
+      <c r="C355">
+        <v>54</v>
+      </c>
+      <c r="D355">
+        <v>66</v>
+      </c>
+      <c r="E355" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5">
+      <c r="A356" s="2">
+        <v>46301.6875</v>
+      </c>
+      <c r="B356">
+        <v>128.189</v>
+      </c>
+      <c r="C356">
+        <v>53</v>
+      </c>
+      <c r="D356">
+        <v>67</v>
+      </c>
+      <c r="E356" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5">
+      <c r="A357" s="2">
+        <v>46301.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>130.212</v>
+      </c>
+      <c r="C357">
+        <v>51</v>
+      </c>
+      <c r="D357">
+        <v>68</v>
+      </c>
+      <c r="E357" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5">
+      <c r="A358" s="2">
+        <v>46301.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>104.446</v>
+      </c>
+      <c r="C358">
+        <v>66</v>
+      </c>
+      <c r="D358">
+        <v>69</v>
+      </c>
+      <c r="E358" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5">
+      <c r="A359" s="2">
+        <v>46301.71875</v>
+      </c>
+      <c r="B359">
+        <v>127.326</v>
+      </c>
+      <c r="C359">
+        <v>78</v>
+      </c>
+      <c r="D359">
+        <v>70</v>
+      </c>
+      <c r="E359" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5">
+      <c r="A360" s="2">
+        <v>46301.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>104.307</v>
+      </c>
+      <c r="C360">
+        <v>77</v>
+      </c>
+      <c r="D360">
+        <v>71</v>
+      </c>
+      <c r="E360" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5">
+      <c r="A361" s="2">
+        <v>46301.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>105.128</v>
+      </c>
+      <c r="C361">
+        <v>76</v>
+      </c>
+      <c r="D361">
+        <v>72</v>
+      </c>
+      <c r="E361" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5">
+      <c r="A362" s="2">
+        <v>46301.75</v>
+      </c>
+      <c r="B362">
+        <v>115.647</v>
+      </c>
+      <c r="C362">
+        <v>77</v>
+      </c>
+      <c r="D362">
+        <v>73</v>
+      </c>
+      <c r="E362" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5">
+      <c r="A363" s="2">
+        <v>46301.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>117.576</v>
+      </c>
+      <c r="C363">
+        <v>82</v>
+      </c>
+      <c r="D363">
+        <v>74</v>
+      </c>
+      <c r="E363" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5">
+      <c r="A364" s="2">
+        <v>46301.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>120.71</v>
+      </c>
+      <c r="C364">
+        <v>89</v>
+      </c>
+      <c r="D364">
+        <v>75</v>
+      </c>
+      <c r="E364" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5">
+      <c r="A365" s="2">
+        <v>46301.78125</v>
+      </c>
+      <c r="B365">
+        <v>129.503</v>
+      </c>
+      <c r="C365">
+        <v>92</v>
+      </c>
+      <c r="D365">
+        <v>76</v>
+      </c>
+      <c r="E365" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5">
+      <c r="A366" s="2">
+        <v>46301.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>133.601</v>
+      </c>
+      <c r="C366">
+        <v>91</v>
+      </c>
+      <c r="D366">
+        <v>77</v>
+      </c>
+      <c r="E366" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5">
+      <c r="A367" s="2">
+        <v>46301.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>135.19</v>
+      </c>
+      <c r="C367">
+        <v>95</v>
+      </c>
+      <c r="D367">
+        <v>78</v>
+      </c>
+      <c r="E367" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5">
+      <c r="A368" s="2">
+        <v>46301.8125</v>
+      </c>
+      <c r="B368">
+        <v>139.394</v>
+      </c>
+      <c r="C368">
+        <v>107</v>
+      </c>
+      <c r="D368">
+        <v>79</v>
+      </c>
+      <c r="E368" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5">
+      <c r="A369" s="2">
+        <v>46301.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>143.464</v>
+      </c>
+      <c r="C369">
+        <v>121</v>
+      </c>
+      <c r="D369">
+        <v>80</v>
+      </c>
+      <c r="E369" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5">
+      <c r="A370" s="2">
+        <v>46301.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>149.363</v>
+      </c>
+      <c r="C370">
+        <v>129</v>
+      </c>
+      <c r="D370">
+        <v>81</v>
+      </c>
+      <c r="E370" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5">
+      <c r="A371" s="2">
+        <v>46301.84375</v>
+      </c>
+      <c r="B371">
+        <v>151.302</v>
+      </c>
+      <c r="C371">
+        <v>136</v>
+      </c>
+      <c r="D371">
+        <v>82</v>
+      </c>
+      <c r="E371" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5">
+      <c r="A372" s="2">
+        <v>46301.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>153.596</v>
+      </c>
+      <c r="C372">
+        <v>149</v>
+      </c>
+      <c r="D372">
+        <v>83</v>
+      </c>
+      <c r="E372" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5">
+      <c r="A373" s="2">
+        <v>46301.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>155.861</v>
+      </c>
+      <c r="C373">
+        <v>161</v>
+      </c>
+      <c r="D373">
+        <v>84</v>
+      </c>
+      <c r="E373" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5">
+      <c r="A374" s="2">
+        <v>46301.875</v>
+      </c>
+      <c r="B374">
+        <v>149.214</v>
+      </c>
+      <c r="C374">
+        <v>161</v>
+      </c>
+      <c r="D374">
+        <v>85</v>
+      </c>
+      <c r="E374" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5">
+      <c r="A375" s="2">
+        <v>46301.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>149.304</v>
+      </c>
+      <c r="C375">
+        <v>156</v>
+      </c>
+      <c r="D375">
+        <v>86</v>
+      </c>
+      <c r="E375" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5">
+      <c r="A376" s="2">
+        <v>46301.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>150.589</v>
+      </c>
+      <c r="C376">
+        <v>157</v>
+      </c>
+      <c r="D376">
+        <v>87</v>
+      </c>
+      <c r="E376" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5">
+      <c r="A377" s="2">
+        <v>46301.90625</v>
+      </c>
+      <c r="B377">
+        <v>150.99</v>
+      </c>
+      <c r="C377">
+        <v>160</v>
+      </c>
+      <c r="D377">
+        <v>88</v>
+      </c>
+      <c r="E377" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5">
+      <c r="A378" s="2">
+        <v>46301.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>152.057</v>
+      </c>
+      <c r="C378">
+        <v>174</v>
+      </c>
+      <c r="D378">
+        <v>89</v>
+      </c>
+      <c r="E378" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5">
+      <c r="A379" s="2">
+        <v>46301.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>152.065</v>
+      </c>
+      <c r="C379">
+        <v>190</v>
+      </c>
+      <c r="D379">
+        <v>90</v>
+      </c>
+      <c r="E379" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5">
+      <c r="A380" s="2">
+        <v>46301.9375</v>
+      </c>
+      <c r="B380">
+        <v>152.311</v>
+      </c>
+      <c r="C380">
+        <v>197</v>
+      </c>
+      <c r="D380">
+        <v>91</v>
+      </c>
+      <c r="E380" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5">
+      <c r="A381" s="2">
+        <v>46301.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>152.379</v>
+      </c>
+      <c r="C381">
+        <v>197</v>
+      </c>
+      <c r="D381">
+        <v>92</v>
+      </c>
+      <c r="E381" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5">
+      <c r="A382" s="2">
+        <v>46301.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>161.959</v>
+      </c>
+      <c r="C382">
+        <v>199</v>
+      </c>
+      <c r="D382">
+        <v>93</v>
+      </c>
+      <c r="E382" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5">
+      <c r="A383" s="2">
+        <v>46301.96875</v>
+      </c>
+      <c r="B383">
+        <v>164.158</v>
+      </c>
+      <c r="C383">
+        <v>211</v>
+      </c>
+      <c r="D383">
+        <v>94</v>
+      </c>
+      <c r="E383" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5">
+      <c r="A384" s="2">
+        <v>46301.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>163.605</v>
+      </c>
+      <c r="C384">
+        <v>218</v>
+      </c>
+      <c r="D384">
+        <v>95</v>
+      </c>
+      <c r="E384" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5">
+      <c r="A385" s="2">
+        <v>46301.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>158.337</v>
+      </c>
+      <c r="C385">
+        <v>213</v>
+      </c>
+      <c r="D385">
+        <v>96</v>
+      </c>
+      <c r="E385" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5">
+      <c r="A386" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B386">
+        <v>169.802</v>
+      </c>
+      <c r="C386">
+        <v>191</v>
+      </c>
+      <c r="D386">
+        <v>1</v>
+      </c>
+      <c r="E386" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5">
+      <c r="A387" s="2">
+        <v>46302.01041666666</v>
+      </c>
+      <c r="B387">
+        <v>165.04</v>
+      </c>
+      <c r="C387">
+        <v>172</v>
+      </c>
+      <c r="D387">
+        <v>2</v>
+      </c>
+      <c r="E387" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5">
+      <c r="A388" s="2">
+        <v>46302.02083333334</v>
+      </c>
+      <c r="B388">
+        <v>162.048</v>
+      </c>
+      <c r="C388">
+        <v>163</v>
+      </c>
+      <c r="D388">
+        <v>3</v>
+      </c>
+      <c r="E388" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5">
+      <c r="A389" s="2">
+        <v>46302.03125</v>
+      </c>
+      <c r="B389">
+        <v>158.004</v>
+      </c>
+      <c r="C389">
+        <v>151</v>
+      </c>
+      <c r="D389">
+        <v>4</v>
+      </c>
+      <c r="E389" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5">
+      <c r="A390" s="2">
+        <v>46302.04166666666</v>
+      </c>
+      <c r="B390">
+        <v>144.248</v>
+      </c>
+      <c r="C390">
+        <v>128</v>
+      </c>
+      <c r="D390">
+        <v>5</v>
+      </c>
+      <c r="E390" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5">
+      <c r="A391" s="2">
+        <v>46302.05208333334</v>
+      </c>
+      <c r="B391">
+        <v>140.163</v>
+      </c>
+      <c r="C391">
+        <v>114</v>
+      </c>
+      <c r="D391">
+        <v>6</v>
+      </c>
+      <c r="E391" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5">
+      <c r="A392" s="2">
+        <v>46302.0625</v>
+      </c>
+      <c r="B392">
+        <v>136.447</v>
+      </c>
+      <c r="C392">
+        <v>101</v>
+      </c>
+      <c r="D392">
+        <v>7</v>
+      </c>
+      <c r="E392" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5">
+      <c r="A393" s="2">
+        <v>46302.07291666666</v>
+      </c>
+      <c r="B393">
+        <v>130.44</v>
+      </c>
+      <c r="C393">
+        <v>89</v>
+      </c>
+      <c r="D393">
+        <v>8</v>
+      </c>
+      <c r="E393" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5">
+      <c r="A394" s="2">
+        <v>46302.08333333334</v>
+      </c>
+      <c r="B394">
+        <v>124.046</v>
+      </c>
+      <c r="C394">
+        <v>88</v>
+      </c>
+      <c r="D394">
+        <v>9</v>
+      </c>
+      <c r="E394" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5">
+      <c r="A395" s="2">
+        <v>46302.09375</v>
+      </c>
+      <c r="B395">
+        <v>120.452</v>
+      </c>
+      <c r="C395">
+        <v>81</v>
+      </c>
+      <c r="D395">
+        <v>10</v>
+      </c>
+      <c r="E395" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5">
+      <c r="A396" s="2">
+        <v>46302.10416666666</v>
+      </c>
+      <c r="B396">
+        <v>116.627</v>
+      </c>
+      <c r="C396">
+        <v>75</v>
+      </c>
+      <c r="D396">
+        <v>11</v>
+      </c>
+      <c r="E396" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5">
+      <c r="A397" s="2">
+        <v>46302.11458333334</v>
+      </c>
+      <c r="B397">
+        <v>113.147</v>
+      </c>
+      <c r="C397">
+        <v>69</v>
+      </c>
+      <c r="D397">
+        <v>12</v>
+      </c>
+      <c r="E397" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5">
+      <c r="A398" s="2">
+        <v>46302.125</v>
+      </c>
+      <c r="B398">
+        <v>108.63</v>
+      </c>
+      <c r="C398">
+        <v>60</v>
+      </c>
+      <c r="D398">
+        <v>13</v>
+      </c>
+      <c r="E398" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5">
+      <c r="A399" s="2">
+        <v>46302.13541666666</v>
+      </c>
+      <c r="B399">
+        <v>106.823</v>
+      </c>
+      <c r="C399">
+        <v>50</v>
+      </c>
+      <c r="D399">
+        <v>14</v>
+      </c>
+      <c r="E399" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5">
+      <c r="A400" s="2">
+        <v>46302.14583333334</v>
+      </c>
+      <c r="B400">
+        <v>104.969</v>
+      </c>
+      <c r="C400">
+        <v>40</v>
+      </c>
+      <c r="D400">
+        <v>15</v>
+      </c>
+      <c r="E400" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5">
+      <c r="A401" s="2">
+        <v>46302.15625</v>
+      </c>
+      <c r="B401">
+        <v>102.639</v>
+      </c>
+      <c r="C401">
+        <v>33</v>
+      </c>
+      <c r="D401">
+        <v>16</v>
+      </c>
+      <c r="E401" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="402" spans="1:5">
+      <c r="A402" s="2">
+        <v>46302.16666666666</v>
+      </c>
+      <c r="B402">
+        <v>96.809</v>
+      </c>
+      <c r="C402">
+        <v>26</v>
+      </c>
+      <c r="D402">
+        <v>17</v>
+      </c>
+      <c r="E402" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5">
+      <c r="A403" s="2">
+        <v>46302.17708333334</v>
+      </c>
+      <c r="B403">
+        <v>95.057</v>
+      </c>
+      <c r="C403">
+        <v>18</v>
+      </c>
+      <c r="D403">
+        <v>18</v>
+      </c>
+      <c r="E403" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5">
+      <c r="A404" s="2">
+        <v>46302.1875</v>
+      </c>
+      <c r="B404">
+        <v>94.983</v>
+      </c>
+      <c r="C404">
+        <v>12</v>
+      </c>
+      <c r="D404">
+        <v>19</v>
+      </c>
+      <c r="E404" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="405" spans="1:5">
+      <c r="A405" s="2">
+        <v>46302.19791666666</v>
+      </c>
+      <c r="B405">
+        <v>93.13200000000001</v>
+      </c>
+      <c r="C405">
+        <v>8</v>
+      </c>
+      <c r="D405">
+        <v>20</v>
+      </c>
+      <c r="E405" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5">
+      <c r="A406" s="2">
+        <v>46302.20833333334</v>
+      </c>
+      <c r="B406">
+        <v>89.663</v>
+      </c>
+      <c r="C406">
+        <v>5</v>
+      </c>
+      <c r="D406">
+        <v>21</v>
+      </c>
+      <c r="E406" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="407" spans="1:5">
+      <c r="A407" s="2">
+        <v>46302.21875</v>
+      </c>
+      <c r="B407">
+        <v>88.899</v>
+      </c>
+      <c r="C407">
+        <v>2</v>
+      </c>
+      <c r="D407">
+        <v>22</v>
+      </c>
+      <c r="E407" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5">
+      <c r="A408" s="2">
+        <v>46302.22916666666</v>
+      </c>
+      <c r="B408">
+        <v>88.11799999999999</v>
+      </c>
+      <c r="C408">
+        <v>0</v>
+      </c>
+      <c r="D408">
+        <v>23</v>
+      </c>
+      <c r="E408" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="409" spans="1:5">
+      <c r="A409" s="2">
+        <v>46302.23958333334</v>
+      </c>
+      <c r="B409">
+        <v>87.56699999999999</v>
+      </c>
+      <c r="C409">
+        <v>0</v>
+      </c>
+      <c r="D409">
+        <v>24</v>
+      </c>
+      <c r="E409" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="410" spans="1:5">
+      <c r="A410" s="2">
+        <v>46302.25</v>
+      </c>
+      <c r="B410">
+        <v>90.29900000000001</v>
+      </c>
+      <c r="C410">
+        <v>0</v>
+      </c>
+      <c r="D410">
+        <v>25</v>
+      </c>
+      <c r="E410" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5">
+      <c r="A411" s="2">
+        <v>46302.26041666666</v>
+      </c>
+      <c r="B411">
+        <v>89.754</v>
+      </c>
+      <c r="C411">
+        <v>0</v>
+      </c>
+      <c r="D411">
+        <v>26</v>
+      </c>
+      <c r="E411" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5">
+      <c r="A412" s="2">
+        <v>46302.27083333334</v>
+      </c>
+      <c r="B412">
+        <v>86.81699999999999</v>
+      </c>
+      <c r="C412">
+        <v>0</v>
+      </c>
+      <c r="D412">
+        <v>27</v>
+      </c>
+      <c r="E412" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="413" spans="1:5">
+      <c r="A413" s="2">
+        <v>46302.28125</v>
+      </c>
+      <c r="B413">
+        <v>88.173</v>
+      </c>
+      <c r="C413">
+        <v>0</v>
+      </c>
+      <c r="D413">
+        <v>28</v>
+      </c>
+      <c r="E413" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="414" spans="1:5">
+      <c r="A414" s="2">
+        <v>46302.29166666666</v>
+      </c>
+      <c r="B414">
+        <v>87.30800000000001</v>
+      </c>
+      <c r="C414">
+        <v>0</v>
+      </c>
+      <c r="D414">
+        <v>29</v>
+      </c>
+      <c r="E414" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5">
+      <c r="A415" s="2">
+        <v>46302.30208333334</v>
+      </c>
+      <c r="B415">
+        <v>89.407</v>
+      </c>
+      <c r="C415">
+        <v>0</v>
+      </c>
+      <c r="D415">
+        <v>30</v>
+      </c>
+      <c r="E415" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5">
+      <c r="A416" s="2">
+        <v>46302.3125</v>
+      </c>
+      <c r="B416">
+        <v>91.73399999999999</v>
+      </c>
+      <c r="C416">
+        <v>1</v>
+      </c>
+      <c r="D416">
+        <v>31</v>
+      </c>
+      <c r="E416" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5">
+      <c r="A417" s="2">
+        <v>46302.32291666666</v>
+      </c>
+      <c r="B417">
+        <v>97.084</v>
+      </c>
+      <c r="C417">
+        <v>2</v>
+      </c>
+      <c r="D417">
+        <v>32</v>
+      </c>
+      <c r="E417" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5">
+      <c r="A418" s="2">
+        <v>46302.33333333334</v>
+      </c>
+      <c r="B418">
+        <v>119.872</v>
+      </c>
+      <c r="C418">
+        <v>3</v>
+      </c>
+      <c r="D418">
+        <v>33</v>
+      </c>
+      <c r="E418" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="419" spans="1:5">
+      <c r="A419" s="2">
+        <v>46302.34375</v>
+      </c>
+      <c r="B419">
+        <v>122.889</v>
+      </c>
+      <c r="C419">
+        <v>1</v>
+      </c>
+      <c r="D419">
+        <v>34</v>
+      </c>
+      <c r="E419" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5">
+      <c r="A420" s="2">
+        <v>46302.35416666666</v>
+      </c>
+      <c r="B420">
+        <v>125.681</v>
+      </c>
+      <c r="C420">
+        <v>0</v>
+      </c>
+      <c r="D420">
+        <v>35</v>
+      </c>
+      <c r="E420" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5">
+      <c r="A421" s="2">
+        <v>46302.36458333334</v>
+      </c>
+      <c r="B421">
+        <v>127.61</v>
+      </c>
+      <c r="C421">
+        <v>0</v>
+      </c>
+      <c r="D421">
+        <v>36</v>
+      </c>
+      <c r="E421" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5">
+      <c r="A422" s="2">
+        <v>46302.375</v>
+      </c>
+      <c r="B422">
+        <v>131.742</v>
+      </c>
+      <c r="C422">
+        <v>3</v>
+      </c>
+      <c r="D422">
+        <v>37</v>
+      </c>
+      <c r="E422" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5">
+      <c r="A423" s="2">
+        <v>46302.38541666666</v>
+      </c>
+      <c r="B423">
+        <v>134.296</v>
+      </c>
+      <c r="C423">
+        <v>6</v>
+      </c>
+      <c r="D423">
+        <v>38</v>
+      </c>
+      <c r="E423" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5">
+      <c r="A424" s="2">
+        <v>46302.39583333334</v>
+      </c>
+      <c r="B424">
+        <v>136.551</v>
+      </c>
+      <c r="C424">
+        <v>4</v>
+      </c>
+      <c r="D424">
+        <v>39</v>
+      </c>
+      <c r="E424" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5">
+      <c r="A425" s="2">
+        <v>46302.40625</v>
+      </c>
+      <c r="B425">
+        <v>135.848</v>
+      </c>
+      <c r="C425">
+        <v>7</v>
+      </c>
+      <c r="D425">
+        <v>40</v>
+      </c>
+      <c r="E425" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5">
+      <c r="A426" s="2">
+        <v>46302.41666666666</v>
+      </c>
+      <c r="B426">
+        <v>146.163</v>
+      </c>
+      <c r="D426">
+        <v>41</v>
+      </c>
+      <c r="E426" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5">
+      <c r="A427" s="2">
+        <v>46302.42708333334</v>
+      </c>
+      <c r="B427">
+        <v>148.556</v>
+      </c>
+      <c r="D427">
+        <v>42</v>
+      </c>
+      <c r="E427" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="428" spans="1:5">
+      <c r="A428" s="2">
+        <v>46302.4375</v>
+      </c>
+      <c r="B428">
+        <v>154.57</v>
+      </c>
+      <c r="D428">
+        <v>43</v>
+      </c>
+      <c r="E428" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="429" spans="1:5">
+      <c r="A429" s="2">
+        <v>46302.44791666666</v>
+      </c>
+      <c r="B429">
+        <v>160.283</v>
+      </c>
+      <c r="D429">
+        <v>44</v>
+      </c>
+      <c r="E429" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5">
+      <c r="A430" s="2">
+        <v>46302.45833333334</v>
+      </c>
+      <c r="B430">
+        <v>172.853</v>
+      </c>
+      <c r="D430">
+        <v>45</v>
+      </c>
+      <c r="E430" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5">
+      <c r="A431" s="2">
+        <v>46302.46875</v>
+      </c>
+      <c r="B431">
+        <v>181.93</v>
+      </c>
+      <c r="D431">
+        <v>46</v>
+      </c>
+      <c r="E431" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5">
+      <c r="A432" s="2">
+        <v>46302.47916666666</v>
+      </c>
+      <c r="B432">
+        <v>191.941</v>
+      </c>
+      <c r="D432">
+        <v>47</v>
+      </c>
+      <c r="E432" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5">
+      <c r="A433" s="2">
+        <v>46302.48958333334</v>
+      </c>
+      <c r="B433">
+        <v>201.514</v>
+      </c>
+      <c r="D433">
+        <v>48</v>
+      </c>
+      <c r="E433" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5">
+      <c r="A434" s="2">
+        <v>46302.5</v>
+      </c>
+      <c r="B434">
+        <v>221.255</v>
+      </c>
+      <c r="D434">
+        <v>49</v>
+      </c>
+      <c r="E434" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5">
+      <c r="A435" s="2">
+        <v>46302.51041666666</v>
+      </c>
+      <c r="B435">
+        <v>230.994</v>
+      </c>
+      <c r="D435">
+        <v>50</v>
+      </c>
+      <c r="E435" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5">
+      <c r="A436" s="2">
+        <v>46302.52083333334</v>
+      </c>
+      <c r="B436">
+        <v>239.509</v>
+      </c>
+      <c r="D436">
+        <v>51</v>
+      </c>
+      <c r="E436" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5">
+      <c r="A437" s="2">
+        <v>46302.53125</v>
+      </c>
+      <c r="B437">
+        <v>248.563</v>
+      </c>
+      <c r="D437">
+        <v>52</v>
+      </c>
+      <c r="E437" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="438" spans="1:5">
+      <c r="A438" s="2">
+        <v>46302.54166666666</v>
+      </c>
+      <c r="B438">
+        <v>266.942</v>
+      </c>
+      <c r="D438">
+        <v>53</v>
+      </c>
+      <c r="E438" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="439" spans="1:5">
+      <c r="A439" s="2">
+        <v>46302.55208333334</v>
+      </c>
+      <c r="B439">
+        <v>278.504</v>
+      </c>
+      <c r="D439">
+        <v>54</v>
+      </c>
+      <c r="E439" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="440" spans="1:5">
+      <c r="A440" s="2">
+        <v>46302.5625</v>
+      </c>
+      <c r="B440">
+        <v>289.826</v>
+      </c>
+      <c r="D440">
+        <v>55</v>
+      </c>
+      <c r="E440" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="441" spans="1:5">
+      <c r="A441" s="2">
+        <v>46302.57291666666</v>
+      </c>
+      <c r="B441">
+        <v>301.06</v>
+      </c>
+      <c r="D441">
+        <v>56</v>
+      </c>
+      <c r="E441" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="442" spans="1:5">
+      <c r="A442" s="2">
+        <v>46302.58333333334</v>
+      </c>
+      <c r="B442">
+        <v>315.053</v>
+      </c>
+      <c r="D442">
+        <v>57</v>
+      </c>
+      <c r="E442" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="443" spans="1:5">
+      <c r="A443" s="2">
+        <v>46302.59375</v>
+      </c>
+      <c r="B443">
+        <v>328.251</v>
+      </c>
+      <c r="D443">
+        <v>58</v>
+      </c>
+      <c r="E443" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="444" spans="1:5">
+      <c r="A444" s="2">
+        <v>46302.60416666666</v>
+      </c>
+      <c r="B444">
+        <v>350.83</v>
+      </c>
+      <c r="D444">
+        <v>59</v>
+      </c>
+      <c r="E444" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="445" spans="1:5">
+      <c r="A445" s="2">
+        <v>46302.61458333334</v>
+      </c>
+      <c r="B445">
+        <v>363.877</v>
+      </c>
+      <c r="D445">
+        <v>60</v>
+      </c>
+      <c r="E445" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="446" spans="1:5">
+      <c r="A446" s="2">
+        <v>46302.625</v>
+      </c>
+      <c r="B446">
+        <v>388.125</v>
+      </c>
+      <c r="D446">
+        <v>61</v>
+      </c>
+      <c r="E446" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="447" spans="1:5">
+      <c r="A447" s="2">
+        <v>46302.63541666666</v>
+      </c>
+      <c r="B447">
+        <v>408.743</v>
+      </c>
+      <c r="D447">
+        <v>62</v>
+      </c>
+      <c r="E447" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="448" spans="1:5">
+      <c r="A448" s="2">
+        <v>46302.64583333334</v>
+      </c>
+      <c r="B448">
+        <v>429.994</v>
+      </c>
+      <c r="D448">
+        <v>63</v>
+      </c>
+      <c r="E448" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="449" spans="1:5">
+      <c r="A449" s="2">
+        <v>46302.65625</v>
+      </c>
+      <c r="B449">
+        <v>449.058</v>
+      </c>
+      <c r="D449">
+        <v>64</v>
+      </c>
+      <c r="E449" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="450" spans="1:5">
+      <c r="A450" s="2">
+        <v>46302.66666666666</v>
+      </c>
+      <c r="B450">
+        <v>480.417</v>
+      </c>
+      <c r="D450">
+        <v>65</v>
+      </c>
+      <c r="E450" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="451" spans="1:5">
+      <c r="A451" s="2">
+        <v>46302.67708333334</v>
+      </c>
+      <c r="B451">
+        <v>508.274</v>
+      </c>
+      <c r="D451">
+        <v>66</v>
+      </c>
+      <c r="E451" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="452" spans="1:5">
+      <c r="A452" s="2">
+        <v>46302.6875</v>
+      </c>
+      <c r="B452">
+        <v>538.272</v>
+      </c>
+      <c r="D452">
+        <v>67</v>
+      </c>
+      <c r="E452" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="453" spans="1:5">
+      <c r="A453" s="2">
+        <v>46302.69791666666</v>
+      </c>
+      <c r="B453">
+        <v>569.506</v>
+      </c>
+      <c r="D453">
+        <v>68</v>
+      </c>
+      <c r="E453" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="454" spans="1:5">
+      <c r="A454" s="2">
+        <v>46302.70833333334</v>
+      </c>
+      <c r="B454">
+        <v>601.607</v>
+      </c>
+      <c r="D454">
+        <v>69</v>
+      </c>
+      <c r="E454" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="455" spans="1:5">
+      <c r="A455" s="2">
+        <v>46302.71875</v>
+      </c>
+      <c r="B455">
+        <v>642.779</v>
+      </c>
+      <c r="D455">
+        <v>70</v>
+      </c>
+      <c r="E455" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="456" spans="1:5">
+      <c r="A456" s="2">
+        <v>46302.72916666666</v>
+      </c>
+      <c r="B456">
+        <v>686.207</v>
+      </c>
+      <c r="D456">
+        <v>71</v>
+      </c>
+      <c r="E456" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="457" spans="1:5">
+      <c r="A457" s="2">
+        <v>46302.73958333334</v>
+      </c>
+      <c r="B457">
+        <v>730.755</v>
+      </c>
+      <c r="D457">
+        <v>72</v>
+      </c>
+      <c r="E457" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="458" spans="1:5">
+      <c r="A458" s="2">
+        <v>46302.75</v>
+      </c>
+      <c r="B458">
+        <v>779.4</v>
+      </c>
+      <c r="D458">
+        <v>73</v>
+      </c>
+      <c r="E458" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="459" spans="1:5">
+      <c r="A459" s="2">
+        <v>46302.76041666666</v>
+      </c>
+      <c r="B459">
+        <v>818.375</v>
+      </c>
+      <c r="D459">
+        <v>74</v>
+      </c>
+      <c r="E459" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="460" spans="1:5">
+      <c r="A460" s="2">
+        <v>46302.77083333334</v>
+      </c>
+      <c r="B460">
+        <v>854.72</v>
+      </c>
+      <c r="D460">
+        <v>75</v>
+      </c>
+      <c r="E460" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="461" spans="1:5">
+      <c r="A461" s="2">
+        <v>46302.78125</v>
+      </c>
+      <c r="B461">
+        <v>893.5700000000001</v>
+      </c>
+      <c r="D461">
+        <v>76</v>
+      </c>
+      <c r="E461" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="462" spans="1:5">
+      <c r="A462" s="2">
+        <v>46302.79166666666</v>
+      </c>
+      <c r="B462">
+        <v>928.504</v>
+      </c>
+      <c r="D462">
+        <v>77</v>
+      </c>
+      <c r="E462" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="463" spans="1:5">
+      <c r="A463" s="2">
+        <v>46302.80208333334</v>
+      </c>
+      <c r="B463">
+        <v>958.126</v>
+      </c>
+      <c r="D463">
+        <v>78</v>
+      </c>
+      <c r="E463" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="464" spans="1:5">
+      <c r="A464" s="2">
+        <v>46302.8125</v>
+      </c>
+      <c r="B464">
+        <v>985.085</v>
+      </c>
+      <c r="D464">
+        <v>79</v>
+      </c>
+      <c r="E464" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="465" spans="1:5">
+      <c r="A465" s="2">
+        <v>46302.82291666666</v>
+      </c>
+      <c r="B465">
+        <v>1013.073</v>
+      </c>
+      <c r="D465">
+        <v>80</v>
+      </c>
+      <c r="E465" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="466" spans="1:5">
+      <c r="A466" s="2">
+        <v>46302.83333333334</v>
+      </c>
+      <c r="B466">
+        <v>1038.149</v>
+      </c>
+      <c r="D466">
+        <v>81</v>
+      </c>
+      <c r="E466" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="467" spans="1:5">
+      <c r="A467" s="2">
+        <v>46302.84375</v>
+      </c>
+      <c r="B467">
+        <v>1058.415</v>
+      </c>
+      <c r="D467">
+        <v>82</v>
+      </c>
+      <c r="E467" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="468" spans="1:5">
+      <c r="A468" s="2">
+        <v>46302.85416666666</v>
+      </c>
+      <c r="B468">
+        <v>1079.982</v>
+      </c>
+      <c r="D468">
+        <v>83</v>
+      </c>
+      <c r="E468" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="469" spans="1:5">
+      <c r="A469" s="2">
+        <v>46302.86458333334</v>
+      </c>
+      <c r="B469">
+        <v>1100.115</v>
+      </c>
+      <c r="D469">
+        <v>84</v>
+      </c>
+      <c r="E469" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="470" spans="1:5">
+      <c r="A470" s="2">
+        <v>46302.875</v>
+      </c>
+      <c r="B470">
+        <v>1114.572</v>
+      </c>
+      <c r="D470">
+        <v>85</v>
+      </c>
+      <c r="E470" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="471" spans="1:5">
+      <c r="A471" s="2">
+        <v>46302.88541666666</v>
+      </c>
+      <c r="B471">
+        <v>1127.238</v>
+      </c>
+      <c r="D471">
+        <v>86</v>
+      </c>
+      <c r="E471" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="472" spans="1:5">
+      <c r="A472" s="2">
+        <v>46302.89583333334</v>
+      </c>
+      <c r="B472">
+        <v>1139.616</v>
+      </c>
+      <c r="D472">
+        <v>87</v>
+      </c>
+      <c r="E472" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="473" spans="1:5">
+      <c r="A473" s="2">
+        <v>46302.90625</v>
+      </c>
+      <c r="B473">
+        <v>1151.578</v>
+      </c>
+      <c r="D473">
+        <v>88</v>
+      </c>
+      <c r="E473" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="474" spans="1:5">
+      <c r="A474" s="2">
+        <v>46302.91666666666</v>
+      </c>
+      <c r="B474">
+        <v>1168.146</v>
+      </c>
+      <c r="D474">
+        <v>89</v>
+      </c>
+      <c r="E474" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="475" spans="1:5">
+      <c r="A475" s="2">
+        <v>46302.92708333334</v>
+      </c>
+      <c r="B475">
+        <v>1175.747</v>
+      </c>
+      <c r="D475">
+        <v>90</v>
+      </c>
+      <c r="E475" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="476" spans="1:5">
+      <c r="A476" s="2">
+        <v>46302.9375</v>
+      </c>
+      <c r="B476">
+        <v>1183.112</v>
+      </c>
+      <c r="D476">
+        <v>91</v>
+      </c>
+      <c r="E476" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="477" spans="1:5">
+      <c r="A477" s="2">
+        <v>46302.94791666666</v>
+      </c>
+      <c r="B477">
+        <v>1188.273</v>
+      </c>
+      <c r="D477">
+        <v>92</v>
+      </c>
+      <c r="E477" t="s">
+        <v>480</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Wind_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Wind_Production_Historical.xlsx
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>07.10.20261</t>
-  </si>
-  <si>
-    <t>07.10.20262</t>
-  </si>
-  <si>
-    <t>07.10.20263</t>
-  </si>
-  <si>
-    <t>07.10.20264</t>
-  </si>
-  <si>
-    <t>07.10.20265</t>
-  </si>
-  <si>
-    <t>07.10.20266</t>
-  </si>
-  <si>
-    <t>07.10.20267</t>
-  </si>
-  <si>
-    <t>07.10.20268</t>
-  </si>
-  <si>
-    <t>07.10.20269</t>
-  </si>
-  <si>
-    <t>07.10.202610</t>
-  </si>
-  <si>
-    <t>07.10.202611</t>
-  </si>
-  <si>
-    <t>07.10.202612</t>
-  </si>
-  <si>
-    <t>07.10.202613</t>
-  </si>
-  <si>
-    <t>07.10.202614</t>
-  </si>
-  <si>
-    <t>07.10.202615</t>
-  </si>
-  <si>
-    <t>07.10.202616</t>
-  </si>
-  <si>
-    <t>07.10.202617</t>
-  </si>
-  <si>
-    <t>07.10.202618</t>
-  </si>
-  <si>
-    <t>07.10.202619</t>
-  </si>
-  <si>
-    <t>07.10.202620</t>
-  </si>
-  <si>
-    <t>07.10.202621</t>
-  </si>
-  <si>
-    <t>07.10.202622</t>
-  </si>
-  <si>
-    <t>07.10.202623</t>
-  </si>
-  <si>
-    <t>07.10.202624</t>
-  </si>
-  <si>
-    <t>07.10.202625</t>
-  </si>
-  <si>
-    <t>07.10.202626</t>
-  </si>
-  <si>
-    <t>07.10.202627</t>
-  </si>
-  <si>
-    <t>07.10.202628</t>
-  </si>
-  <si>
-    <t>07.10.202629</t>
-  </si>
-  <si>
-    <t>07.10.202630</t>
-  </si>
-  <si>
-    <t>07.10.202631</t>
-  </si>
-  <si>
-    <t>07.10.202632</t>
-  </si>
-  <si>
-    <t>07.10.202633</t>
-  </si>
-  <si>
-    <t>07.10.202634</t>
-  </si>
-  <si>
-    <t>07.10.202635</t>
-  </si>
-  <si>
-    <t>07.10.202636</t>
-  </si>
-  <si>
-    <t>07.10.202637</t>
-  </si>
-  <si>
-    <t>07.10.202638</t>
-  </si>
-  <si>
-    <t>07.10.202639</t>
-  </si>
-  <si>
-    <t>07.10.202640</t>
-  </si>
-  <si>
-    <t>07.10.202641</t>
-  </si>
-  <si>
-    <t>07.10.202642</t>
-  </si>
-  <si>
-    <t>07.10.202643</t>
-  </si>
-  <si>
-    <t>07.10.202644</t>
-  </si>
-  <si>
-    <t>07.10.202645</t>
-  </si>
-  <si>
-    <t>07.10.202646</t>
-  </si>
-  <si>
-    <t>07.10.202647</t>
-  </si>
-  <si>
-    <t>07.10.202648</t>
-  </si>
-  <si>
-    <t>07.10.202649</t>
-  </si>
-  <si>
-    <t>07.10.202650</t>
-  </si>
-  <si>
-    <t>07.10.202651</t>
-  </si>
-  <si>
-    <t>07.10.202652</t>
-  </si>
-  <si>
-    <t>07.10.202653</t>
-  </si>
-  <si>
-    <t>07.10.202654</t>
-  </si>
-  <si>
-    <t>07.10.202655</t>
-  </si>
-  <si>
-    <t>07.10.202656</t>
-  </si>
-  <si>
-    <t>07.10.202657</t>
-  </si>
-  <si>
-    <t>07.10.202658</t>
-  </si>
-  <si>
-    <t>07.10.202659</t>
-  </si>
-  <si>
-    <t>07.10.202660</t>
-  </si>
-  <si>
-    <t>07.10.202661</t>
-  </si>
-  <si>
-    <t>07.10.202662</t>
-  </si>
-  <si>
-    <t>07.10.202663</t>
-  </si>
-  <si>
-    <t>07.10.202664</t>
-  </si>
-  <si>
-    <t>07.10.202665</t>
-  </si>
-  <si>
-    <t>07.10.202666</t>
-  </si>
-  <si>
-    <t>07.10.202667</t>
-  </si>
-  <si>
-    <t>07.10.202668</t>
-  </si>
-  <si>
-    <t>07.10.202669</t>
-  </si>
-  <si>
-    <t>07.10.202670</t>
-  </si>
-  <si>
-    <t>07.10.202671</t>
-  </si>
-  <si>
-    <t>07.10.202672</t>
-  </si>
-  <si>
-    <t>07.10.202673</t>
-  </si>
-  <si>
-    <t>07.10.202674</t>
-  </si>
-  <si>
-    <t>07.10.202675</t>
-  </si>
-  <si>
-    <t>07.10.202676</t>
-  </si>
-  <si>
-    <t>07.10.202677</t>
-  </si>
-  <si>
-    <t>07.10.202678</t>
-  </si>
-  <si>
-    <t>07.10.202679</t>
-  </si>
-  <si>
-    <t>07.10.202680</t>
-  </si>
-  <si>
-    <t>07.10.202681</t>
-  </si>
-  <si>
-    <t>07.10.202682</t>
-  </si>
-  <si>
-    <t>07.10.202683</t>
-  </si>
-  <si>
-    <t>07.10.202684</t>
-  </si>
-  <si>
-    <t>07.10.202685</t>
-  </si>
-  <si>
-    <t>07.10.202686</t>
-  </si>
-  <si>
-    <t>07.10.202687</t>
-  </si>
-  <si>
-    <t>07.10.202688</t>
-  </si>
-  <si>
-    <t>07.10.202689</t>
-  </si>
-  <si>
-    <t>07.10.202690</t>
-  </si>
-  <si>
-    <t>07.10.202691</t>
-  </si>
-  <si>
-    <t>07.10.202692</t>
-  </si>
-  <si>
-    <t>07.10.202693</t>
-  </si>
-  <si>
-    <t>07.10.202694</t>
-  </si>
-  <si>
-    <t>07.10.202695</t>
-  </si>
-  <si>
-    <t>07.10.202696</t>
-  </si>
-  <si>
     <t>08.10.20261</t>
   </si>
   <si>
@@ -593,6 +305,294 @@
   </si>
   <si>
     <t>08.10.202692</t>
+  </si>
+  <si>
+    <t>08.10.202693</t>
+  </si>
+  <si>
+    <t>08.10.202694</t>
+  </si>
+  <si>
+    <t>08.10.202695</t>
+  </si>
+  <si>
+    <t>08.10.202696</t>
+  </si>
+  <si>
+    <t>09.10.20261</t>
+  </si>
+  <si>
+    <t>09.10.20262</t>
+  </si>
+  <si>
+    <t>09.10.20263</t>
+  </si>
+  <si>
+    <t>09.10.20264</t>
+  </si>
+  <si>
+    <t>09.10.20265</t>
+  </si>
+  <si>
+    <t>09.10.20266</t>
+  </si>
+  <si>
+    <t>09.10.20267</t>
+  </si>
+  <si>
+    <t>09.10.20268</t>
+  </si>
+  <si>
+    <t>09.10.20269</t>
+  </si>
+  <si>
+    <t>09.10.202610</t>
+  </si>
+  <si>
+    <t>09.10.202611</t>
+  </si>
+  <si>
+    <t>09.10.202612</t>
+  </si>
+  <si>
+    <t>09.10.202613</t>
+  </si>
+  <si>
+    <t>09.10.202614</t>
+  </si>
+  <si>
+    <t>09.10.202615</t>
+  </si>
+  <si>
+    <t>09.10.202616</t>
+  </si>
+  <si>
+    <t>09.10.202617</t>
+  </si>
+  <si>
+    <t>09.10.202618</t>
+  </si>
+  <si>
+    <t>09.10.202619</t>
+  </si>
+  <si>
+    <t>09.10.202620</t>
+  </si>
+  <si>
+    <t>09.10.202621</t>
+  </si>
+  <si>
+    <t>09.10.202622</t>
+  </si>
+  <si>
+    <t>09.10.202623</t>
+  </si>
+  <si>
+    <t>09.10.202624</t>
+  </si>
+  <si>
+    <t>09.10.202625</t>
+  </si>
+  <si>
+    <t>09.10.202626</t>
+  </si>
+  <si>
+    <t>09.10.202627</t>
+  </si>
+  <si>
+    <t>09.10.202628</t>
+  </si>
+  <si>
+    <t>09.10.202629</t>
+  </si>
+  <si>
+    <t>09.10.202630</t>
+  </si>
+  <si>
+    <t>09.10.202631</t>
+  </si>
+  <si>
+    <t>09.10.202632</t>
+  </si>
+  <si>
+    <t>09.10.202633</t>
+  </si>
+  <si>
+    <t>09.10.202634</t>
+  </si>
+  <si>
+    <t>09.10.202635</t>
+  </si>
+  <si>
+    <t>09.10.202636</t>
+  </si>
+  <si>
+    <t>09.10.202637</t>
+  </si>
+  <si>
+    <t>09.10.202638</t>
+  </si>
+  <si>
+    <t>09.10.202639</t>
+  </si>
+  <si>
+    <t>09.10.202640</t>
+  </si>
+  <si>
+    <t>09.10.202641</t>
+  </si>
+  <si>
+    <t>09.10.202642</t>
+  </si>
+  <si>
+    <t>09.10.202643</t>
+  </si>
+  <si>
+    <t>09.10.202644</t>
+  </si>
+  <si>
+    <t>09.10.202645</t>
+  </si>
+  <si>
+    <t>09.10.202646</t>
+  </si>
+  <si>
+    <t>09.10.202647</t>
+  </si>
+  <si>
+    <t>09.10.202648</t>
+  </si>
+  <si>
+    <t>09.10.202649</t>
+  </si>
+  <si>
+    <t>09.10.202650</t>
+  </si>
+  <si>
+    <t>09.10.202651</t>
+  </si>
+  <si>
+    <t>09.10.202652</t>
+  </si>
+  <si>
+    <t>09.10.202653</t>
+  </si>
+  <si>
+    <t>09.10.202654</t>
+  </si>
+  <si>
+    <t>09.10.202655</t>
+  </si>
+  <si>
+    <t>09.10.202656</t>
+  </si>
+  <si>
+    <t>09.10.202657</t>
+  </si>
+  <si>
+    <t>09.10.202658</t>
+  </si>
+  <si>
+    <t>09.10.202659</t>
+  </si>
+  <si>
+    <t>09.10.202660</t>
+  </si>
+  <si>
+    <t>09.10.202661</t>
+  </si>
+  <si>
+    <t>09.10.202662</t>
+  </si>
+  <si>
+    <t>09.10.202663</t>
+  </si>
+  <si>
+    <t>09.10.202664</t>
+  </si>
+  <si>
+    <t>09.10.202665</t>
+  </si>
+  <si>
+    <t>09.10.202666</t>
+  </si>
+  <si>
+    <t>09.10.202667</t>
+  </si>
+  <si>
+    <t>09.10.202668</t>
+  </si>
+  <si>
+    <t>09.10.202669</t>
+  </si>
+  <si>
+    <t>09.10.202670</t>
+  </si>
+  <si>
+    <t>09.10.202671</t>
+  </si>
+  <si>
+    <t>09.10.202672</t>
+  </si>
+  <si>
+    <t>09.10.202673</t>
+  </si>
+  <si>
+    <t>09.10.202674</t>
+  </si>
+  <si>
+    <t>09.10.202675</t>
+  </si>
+  <si>
+    <t>09.10.202676</t>
+  </si>
+  <si>
+    <t>09.10.202677</t>
+  </si>
+  <si>
+    <t>09.10.202678</t>
+  </si>
+  <si>
+    <t>09.10.202679</t>
+  </si>
+  <si>
+    <t>09.10.202680</t>
+  </si>
+  <si>
+    <t>09.10.202681</t>
+  </si>
+  <si>
+    <t>09.10.202682</t>
+  </si>
+  <si>
+    <t>09.10.202683</t>
+  </si>
+  <si>
+    <t>09.10.202684</t>
+  </si>
+  <si>
+    <t>09.10.202685</t>
+  </si>
+  <si>
+    <t>09.10.202686</t>
+  </si>
+  <si>
+    <t>09.10.202687</t>
+  </si>
+  <si>
+    <t>09.10.202688</t>
+  </si>
+  <si>
+    <t>09.10.202689</t>
+  </si>
+  <si>
+    <t>09.10.202690</t>
+  </si>
+  <si>
+    <t>09.10.202691</t>
+  </si>
+  <si>
+    <t>09.10.202692</t>
   </si>
 </sst>
 </file>
@@ -976,13 +976,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B2">
-        <v>169.802</v>
+        <v>1047.446</v>
       </c>
       <c r="C2">
-        <v>191</v>
+        <v>1169</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -993,13 +993,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46302.01041666666</v>
+        <v>46303.01041666666</v>
       </c>
       <c r="B3">
-        <v>165.04</v>
+        <v>1035.081</v>
       </c>
       <c r="C3">
-        <v>172</v>
+        <v>1157</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1010,13 +1010,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46302.02083333334</v>
+        <v>46303.02083333334</v>
       </c>
       <c r="B4">
-        <v>162.048</v>
+        <v>1024.452</v>
       </c>
       <c r="C4">
-        <v>163</v>
+        <v>1130</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1027,13 +1027,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46302.03125</v>
+        <v>46303.03125</v>
       </c>
       <c r="B5">
-        <v>158.004</v>
+        <v>1002.847</v>
       </c>
       <c r="C5">
-        <v>151</v>
+        <v>1101</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1044,13 +1044,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46302.04166666666</v>
+        <v>46303.04166666666</v>
       </c>
       <c r="B6">
-        <v>144.248</v>
+        <v>985.463</v>
       </c>
       <c r="C6">
-        <v>128</v>
+        <v>1096</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1061,13 +1061,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46302.05208333334</v>
+        <v>46303.05208333334</v>
       </c>
       <c r="B7">
-        <v>140.163</v>
+        <v>976.143</v>
       </c>
       <c r="C7">
-        <v>114</v>
+        <v>1075</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1078,13 +1078,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46302.0625</v>
+        <v>46303.0625</v>
       </c>
       <c r="B8">
-        <v>136.447</v>
+        <v>962.899</v>
       </c>
       <c r="C8">
-        <v>101</v>
+        <v>1045</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1095,13 +1095,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46302.07291666666</v>
+        <v>46303.07291666666</v>
       </c>
       <c r="B9">
-        <v>130.44</v>
+        <v>956.673</v>
       </c>
       <c r="C9">
-        <v>89</v>
+        <v>1009</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1112,13 +1112,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46302.08333333334</v>
+        <v>46303.08333333334</v>
       </c>
       <c r="B10">
-        <v>124.046</v>
+        <v>944.508</v>
       </c>
       <c r="C10">
-        <v>88</v>
+        <v>947</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1129,13 +1129,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46302.09375</v>
+        <v>46303.09375</v>
       </c>
       <c r="B11">
-        <v>120.452</v>
+        <v>931.173</v>
       </c>
       <c r="C11">
-        <v>81</v>
+        <v>923</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1146,13 +1146,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46302.10416666666</v>
+        <v>46303.10416666666</v>
       </c>
       <c r="B12">
-        <v>116.627</v>
+        <v>918.982</v>
       </c>
       <c r="C12">
-        <v>75</v>
+        <v>909</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1163,13 +1163,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46302.11458333334</v>
+        <v>46303.11458333334</v>
       </c>
       <c r="B13">
-        <v>113.147</v>
+        <v>907.546</v>
       </c>
       <c r="C13">
-        <v>69</v>
+        <v>884</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1180,13 +1180,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46302.125</v>
+        <v>46303.125</v>
       </c>
       <c r="B14">
-        <v>108.63</v>
+        <v>904.596</v>
       </c>
       <c r="C14">
-        <v>60</v>
+        <v>858</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1197,13 +1197,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46302.13541666666</v>
+        <v>46303.13541666666</v>
       </c>
       <c r="B15">
-        <v>106.823</v>
+        <v>876.46</v>
       </c>
       <c r="C15">
-        <v>50</v>
+        <v>822</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1214,13 +1214,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46302.14583333334</v>
+        <v>46303.14583333334</v>
       </c>
       <c r="B16">
-        <v>104.969</v>
+        <v>866.343</v>
       </c>
       <c r="C16">
-        <v>40</v>
+        <v>804</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1231,13 +1231,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46302.15625</v>
+        <v>46303.15625</v>
       </c>
       <c r="B17">
-        <v>102.639</v>
+        <v>854.367</v>
       </c>
       <c r="C17">
-        <v>33</v>
+        <v>816</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1248,13 +1248,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46302.16666666666</v>
+        <v>46303.16666666666</v>
       </c>
       <c r="B18">
-        <v>96.809</v>
+        <v>847.986</v>
       </c>
       <c r="C18">
-        <v>26</v>
+        <v>824</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1265,13 +1265,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46302.17708333334</v>
+        <v>46303.17708333334</v>
       </c>
       <c r="B19">
-        <v>95.057</v>
+        <v>845.88</v>
       </c>
       <c r="C19">
-        <v>18</v>
+        <v>821</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1282,13 +1282,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46302.1875</v>
+        <v>46303.1875</v>
       </c>
       <c r="B20">
-        <v>94.983</v>
+        <v>845.986</v>
       </c>
       <c r="C20">
-        <v>12</v>
+        <v>820</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1299,13 +1299,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46302.19791666666</v>
+        <v>46303.19791666666</v>
       </c>
       <c r="B21">
-        <v>93.13200000000001</v>
+        <v>844.8</v>
       </c>
       <c r="C21">
-        <v>8</v>
+        <v>781</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1316,13 +1316,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46302.20833333334</v>
+        <v>46303.20833333334</v>
       </c>
       <c r="B22">
-        <v>89.663</v>
+        <v>861.654</v>
       </c>
       <c r="C22">
-        <v>5</v>
+        <v>749</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1333,13 +1333,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46302.21875</v>
+        <v>46303.21875</v>
       </c>
       <c r="B23">
-        <v>88.899</v>
+        <v>862.335</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>742</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1350,13 +1350,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46302.22916666666</v>
+        <v>46303.22916666666</v>
       </c>
       <c r="B24">
-        <v>88.11799999999999</v>
+        <v>862.64</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>748</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1367,13 +1367,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46302.23958333334</v>
+        <v>46303.23958333334</v>
       </c>
       <c r="B25">
-        <v>87.56699999999999</v>
+        <v>860.624</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>760</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1384,13 +1384,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46302.25</v>
+        <v>46303.25</v>
       </c>
       <c r="B26">
-        <v>90.29900000000001</v>
+        <v>883.251</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>776</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1401,13 +1401,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46302.26041666666</v>
+        <v>46303.26041666666</v>
       </c>
       <c r="B27">
-        <v>89.754</v>
+        <v>886.48</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>803</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1418,13 +1418,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46302.27083333334</v>
+        <v>46303.27083333334</v>
       </c>
       <c r="B28">
-        <v>86.81699999999999</v>
+        <v>870.474</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>845</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1435,13 +1435,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46302.28125</v>
+        <v>46303.28125</v>
       </c>
       <c r="B29">
-        <v>88.173</v>
+        <v>877.327</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>850</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1452,13 +1452,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46302.29166666666</v>
+        <v>46303.29166666666</v>
       </c>
       <c r="B30">
-        <v>87.30800000000001</v>
+        <v>880.114</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>845</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1469,13 +1469,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46302.30208333334</v>
+        <v>46303.30208333334</v>
       </c>
       <c r="B31">
-        <v>89.407</v>
+        <v>889.495</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>867</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1486,13 +1486,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46302.3125</v>
+        <v>46303.3125</v>
       </c>
       <c r="B32">
-        <v>91.73399999999999</v>
+        <v>898.332</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>874</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1503,13 +1503,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46302.32291666666</v>
+        <v>46303.32291666666</v>
       </c>
       <c r="B33">
-        <v>97.084</v>
+        <v>910.925</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>866</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1520,13 +1520,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46302.33333333334</v>
+        <v>46303.33333333334</v>
       </c>
       <c r="B34">
-        <v>119.872</v>
+        <v>922.4349999999999</v>
       </c>
       <c r="C34">
-        <v>3</v>
+        <v>778</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1537,13 +1537,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46302.34375</v>
+        <v>46303.34375</v>
       </c>
       <c r="B35">
-        <v>122.889</v>
+        <v>894.984</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>681</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1554,13 +1554,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46302.35416666666</v>
+        <v>46303.35416666666</v>
       </c>
       <c r="B36">
-        <v>125.681</v>
+        <v>872.3200000000001</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>648</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1571,13 +1571,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46302.36458333334</v>
+        <v>46303.36458333334</v>
       </c>
       <c r="B37">
-        <v>127.61</v>
+        <v>843.4690000000001</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>673</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1588,13 +1588,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46302.375</v>
+        <v>46303.375</v>
       </c>
       <c r="B38">
-        <v>131.742</v>
+        <v>844.643</v>
       </c>
       <c r="C38">
-        <v>3</v>
+        <v>691</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1605,13 +1605,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46302.38541666666</v>
+        <v>46303.38541666666</v>
       </c>
       <c r="B39">
-        <v>134.296</v>
+        <v>843.095</v>
       </c>
       <c r="C39">
-        <v>6</v>
+        <v>694</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1622,13 +1622,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46302.39583333334</v>
+        <v>46303.39583333334</v>
       </c>
       <c r="B40">
-        <v>136.551</v>
+        <v>848.288</v>
       </c>
       <c r="C40">
-        <v>4</v>
+        <v>712</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1639,13 +1639,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46302.40625</v>
+        <v>46303.40625</v>
       </c>
       <c r="B41">
-        <v>135.848</v>
+        <v>853.222</v>
       </c>
       <c r="C41">
-        <v>7</v>
+        <v>713</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1656,13 +1656,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46302.41666666666</v>
+        <v>46303.41666666666</v>
       </c>
       <c r="B42">
-        <v>146.163</v>
+        <v>883.179</v>
       </c>
       <c r="C42">
-        <v>14</v>
+        <v>733</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1673,13 +1673,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46302.42708333334</v>
+        <v>46303.42708333334</v>
       </c>
       <c r="B43">
-        <v>148.556</v>
+        <v>898.984</v>
       </c>
       <c r="C43">
-        <v>20</v>
+        <v>779</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1690,13 +1690,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46302.4375</v>
+        <v>46303.4375</v>
       </c>
       <c r="B44">
-        <v>154.57</v>
+        <v>916.1900000000001</v>
       </c>
       <c r="C44">
-        <v>31</v>
+        <v>818</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1707,13 +1707,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46302.44791666666</v>
+        <v>46303.44791666666</v>
       </c>
       <c r="B45">
-        <v>160.283</v>
+        <v>936.092</v>
       </c>
       <c r="C45">
-        <v>46</v>
+        <v>854</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1724,13 +1724,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46302.45833333334</v>
+        <v>46303.45833333334</v>
       </c>
       <c r="B46">
-        <v>172.853</v>
+        <v>964.549</v>
       </c>
       <c r="C46">
-        <v>53</v>
+        <v>897</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1741,13 +1741,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46302.46875</v>
+        <v>46303.46875</v>
       </c>
       <c r="B47">
-        <v>181.93</v>
+        <v>987.485</v>
       </c>
       <c r="C47">
-        <v>62</v>
+        <v>936</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1758,13 +1758,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46302.47916666666</v>
+        <v>46303.47916666666</v>
       </c>
       <c r="B48">
-        <v>191.941</v>
+        <v>1010.108</v>
       </c>
       <c r="C48">
-        <v>57</v>
+        <v>982</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1775,13 +1775,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46302.48958333334</v>
+        <v>46303.48958333334</v>
       </c>
       <c r="B49">
-        <v>201.514</v>
+        <v>1031.889</v>
       </c>
       <c r="C49">
-        <v>54</v>
+        <v>1056</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1792,13 +1792,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46302.5</v>
+        <v>46303.5</v>
       </c>
       <c r="B50">
-        <v>221.255</v>
+        <v>1066.584</v>
       </c>
       <c r="C50">
-        <v>61</v>
+        <v>1117</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1809,13 +1809,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46302.51041666666</v>
+        <v>46303.51041666666</v>
       </c>
       <c r="B51">
-        <v>230.994</v>
+        <v>1088.592</v>
       </c>
       <c r="C51">
-        <v>69</v>
+        <v>1119</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1826,13 +1826,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46302.52083333334</v>
+        <v>46303.52083333334</v>
       </c>
       <c r="B52">
-        <v>239.509</v>
+        <v>1110.292</v>
       </c>
       <c r="C52">
-        <v>75</v>
+        <v>1090</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1843,13 +1843,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46302.53125</v>
+        <v>46303.53125</v>
       </c>
       <c r="B53">
-        <v>248.563</v>
+        <v>1129.892</v>
       </c>
       <c r="C53">
-        <v>87</v>
+        <v>1093</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1860,13 +1860,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46302.54166666666</v>
+        <v>46303.54166666666</v>
       </c>
       <c r="B54">
-        <v>266.942</v>
+        <v>1161.18</v>
       </c>
       <c r="C54">
-        <v>89</v>
+        <v>1107</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1877,13 +1877,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46302.55208333334</v>
+        <v>46303.55208333334</v>
       </c>
       <c r="B55">
-        <v>278.504</v>
+        <v>1177.675</v>
       </c>
       <c r="C55">
-        <v>107</v>
+        <v>1123</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1894,13 +1894,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46302.5625</v>
+        <v>46303.5625</v>
       </c>
       <c r="B56">
-        <v>289.826</v>
+        <v>1193.139</v>
       </c>
       <c r="C56">
-        <v>121</v>
+        <v>1151</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1911,13 +1911,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46302.57291666666</v>
+        <v>46303.57291666666</v>
       </c>
       <c r="B57">
-        <v>301.06</v>
+        <v>1208.626</v>
       </c>
       <c r="C57">
-        <v>142</v>
+        <v>1164</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1928,13 +1928,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46302.58333333334</v>
+        <v>46303.58333333334</v>
       </c>
       <c r="B58">
-        <v>315.053</v>
+        <v>1249.629</v>
       </c>
       <c r="C58">
-        <v>202</v>
+        <v>1193</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1945,13 +1945,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46302.59375</v>
+        <v>46303.59375</v>
       </c>
       <c r="B59">
-        <v>328.251</v>
+        <v>1260.393</v>
       </c>
       <c r="C59">
-        <v>281</v>
+        <v>1257</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1962,13 +1962,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46302.60416666666</v>
+        <v>46303.60416666666</v>
       </c>
       <c r="B60">
-        <v>350.83</v>
+        <v>1270.003</v>
       </c>
       <c r="C60">
-        <v>346</v>
+        <v>1331</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1979,13 +1979,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46302.61458333334</v>
+        <v>46303.61458333334</v>
       </c>
       <c r="B61">
-        <v>363.877</v>
+        <v>1277.895</v>
       </c>
       <c r="C61">
-        <v>409</v>
+        <v>1400</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -1996,13 +1996,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46302.625</v>
+        <v>46303.625</v>
       </c>
       <c r="B62">
-        <v>388.125</v>
+        <v>1324.173</v>
       </c>
       <c r="C62">
-        <v>475</v>
+        <v>1491</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2013,13 +2013,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46302.63541666666</v>
+        <v>46303.63541666666</v>
       </c>
       <c r="B63">
-        <v>408.743</v>
+        <v>1337.145</v>
       </c>
       <c r="C63">
-        <v>549</v>
+        <v>1579</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2030,13 +2030,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46302.64583333334</v>
+        <v>46303.64583333334</v>
       </c>
       <c r="B64">
-        <v>429.994</v>
+        <v>1346.862</v>
       </c>
       <c r="C64">
-        <v>578</v>
+        <v>1619</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2047,13 +2047,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46302.65625</v>
+        <v>46303.65625</v>
       </c>
       <c r="B65">
-        <v>449.058</v>
+        <v>1360.183</v>
       </c>
       <c r="C65">
-        <v>624</v>
+        <v>1650</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2064,13 +2064,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46302.66666666666</v>
+        <v>46303.66666666666</v>
       </c>
       <c r="B66">
-        <v>480.417</v>
+        <v>1418.277</v>
       </c>
       <c r="C66">
-        <v>670</v>
+        <v>1678</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2081,13 +2081,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46302.67708333334</v>
+        <v>46303.67708333334</v>
       </c>
       <c r="B67">
-        <v>508.274</v>
+        <v>1441.013</v>
       </c>
       <c r="C67">
-        <v>710</v>
+        <v>1728</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2098,13 +2098,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46302.6875</v>
+        <v>46303.6875</v>
       </c>
       <c r="B68">
-        <v>538.272</v>
+        <v>1465.289</v>
       </c>
       <c r="C68">
-        <v>725</v>
+        <v>1733</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2115,13 +2115,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46302.69791666666</v>
+        <v>46303.69791666666</v>
       </c>
       <c r="B69">
-        <v>569.506</v>
+        <v>1492.584</v>
       </c>
       <c r="C69">
-        <v>720</v>
+        <v>1709</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2132,13 +2132,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46302.70833333334</v>
+        <v>46303.70833333334</v>
       </c>
       <c r="B70">
-        <v>601.607</v>
+        <v>1459.914</v>
       </c>
       <c r="C70">
-        <v>724</v>
+        <v>1685</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2149,13 +2149,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46302.71875</v>
+        <v>46303.71875</v>
       </c>
       <c r="B71">
-        <v>642.779</v>
+        <v>1515.691</v>
       </c>
       <c r="C71">
-        <v>738</v>
+        <v>1717</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2166,13 +2166,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46302.72916666666</v>
+        <v>46303.72916666666</v>
       </c>
       <c r="B72">
-        <v>686.207</v>
+        <v>1577.369</v>
       </c>
       <c r="C72">
-        <v>802</v>
+        <v>1665</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2183,13 +2183,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46302.73958333334</v>
+        <v>46303.73958333334</v>
       </c>
       <c r="B73">
-        <v>730.755</v>
+        <v>1629.899</v>
       </c>
       <c r="C73">
-        <v>876</v>
+        <v>1696</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2200,13 +2200,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46302.75</v>
+        <v>46303.75</v>
       </c>
       <c r="B74">
-        <v>779.4</v>
+        <v>1674.692</v>
       </c>
       <c r="C74">
-        <v>948</v>
+        <v>1759</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2217,13 +2217,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46302.76041666666</v>
+        <v>46303.76041666666</v>
       </c>
       <c r="B75">
-        <v>818.375</v>
+        <v>1707.773</v>
       </c>
       <c r="C75">
-        <v>1003</v>
+        <v>1874</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2234,13 +2234,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46302.77083333334</v>
+        <v>46303.77083333334</v>
       </c>
       <c r="B76">
-        <v>854.72</v>
+        <v>1738.081</v>
       </c>
       <c r="C76">
-        <v>1048</v>
+        <v>1949</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2251,13 +2251,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46302.78125</v>
+        <v>46303.78125</v>
       </c>
       <c r="B77">
-        <v>893.5700000000001</v>
+        <v>1766.908</v>
       </c>
       <c r="C77">
-        <v>1088</v>
+        <v>2008</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2268,13 +2268,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46302.79166666666</v>
+        <v>46303.79166666666</v>
       </c>
       <c r="B78">
-        <v>928.504</v>
+        <v>1793.875</v>
       </c>
       <c r="C78">
-        <v>1128</v>
+        <v>2060</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2285,13 +2285,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46302.80208333334</v>
+        <v>46303.80208333334</v>
       </c>
       <c r="B79">
-        <v>958.126</v>
+        <v>1807.205</v>
       </c>
       <c r="C79">
-        <v>1158</v>
+        <v>2083</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2302,13 +2302,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46302.8125</v>
+        <v>46303.8125</v>
       </c>
       <c r="B80">
-        <v>985.085</v>
+        <v>1820.69</v>
       </c>
       <c r="C80">
-        <v>1160</v>
+        <v>2080</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2319,13 +2319,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46302.82291666666</v>
+        <v>46303.82291666666</v>
       </c>
       <c r="B81">
-        <v>1013.073</v>
+        <v>1835.841</v>
       </c>
       <c r="C81">
-        <v>1152</v>
+        <v>2024</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2336,13 +2336,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46302.83333333334</v>
+        <v>46303.83333333334</v>
       </c>
       <c r="B82">
-        <v>1038.149</v>
+        <v>1854.683</v>
       </c>
       <c r="C82">
-        <v>1157</v>
+        <v>1977</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2353,13 +2353,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46302.84375</v>
+        <v>46303.84375</v>
       </c>
       <c r="B83">
-        <v>1058.415</v>
+        <v>1858.663</v>
       </c>
       <c r="C83">
-        <v>1177</v>
+        <v>1950</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2370,13 +2370,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46302.85416666666</v>
+        <v>46303.85416666666</v>
       </c>
       <c r="B84">
-        <v>1079.982</v>
+        <v>1857.073</v>
       </c>
       <c r="C84">
-        <v>1225</v>
+        <v>1954</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2387,13 +2387,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46302.86458333334</v>
+        <v>46303.86458333334</v>
       </c>
       <c r="B85">
-        <v>1100.115</v>
+        <v>1854.992</v>
       </c>
       <c r="C85">
-        <v>1249</v>
+        <v>1950</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2404,13 +2404,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46302.875</v>
+        <v>46303.875</v>
       </c>
       <c r="B86">
-        <v>1114.572</v>
+        <v>1847.867</v>
       </c>
       <c r="C86">
-        <v>1267</v>
+        <v>1910</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2421,13 +2421,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46302.88541666666</v>
+        <v>46303.88541666666</v>
       </c>
       <c r="B87">
-        <v>1127.238</v>
+        <v>1837.619</v>
       </c>
       <c r="C87">
-        <v>1285</v>
+        <v>1908</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2438,13 +2438,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46302.89583333334</v>
+        <v>46303.89583333334</v>
       </c>
       <c r="B88">
-        <v>1139.616</v>
+        <v>1828.412</v>
       </c>
       <c r="C88">
-        <v>1281</v>
+        <v>1896</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2455,13 +2455,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46302.90625</v>
+        <v>46303.90625</v>
       </c>
       <c r="B89">
-        <v>1151.578</v>
+        <v>1817.62</v>
       </c>
       <c r="C89">
-        <v>1285</v>
+        <v>1868</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2472,13 +2472,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46302.91666666666</v>
+        <v>46303.91666666666</v>
       </c>
       <c r="B90">
-        <v>1168.146</v>
+        <v>1814.557</v>
       </c>
       <c r="C90">
-        <v>1271</v>
+        <v>1842</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2489,13 +2489,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46302.92708333334</v>
+        <v>46303.92708333334</v>
       </c>
       <c r="B91">
-        <v>1175.747</v>
+        <v>1801.449</v>
       </c>
       <c r="C91">
-        <v>1258</v>
+        <v>1842</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2506,13 +2506,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46302.9375</v>
+        <v>46303.9375</v>
       </c>
       <c r="B92">
-        <v>1183.112</v>
+        <v>1787.655</v>
       </c>
       <c r="C92">
-        <v>1251</v>
+        <v>1844</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2523,13 +2523,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46302.94791666666</v>
+        <v>46303.94791666666</v>
       </c>
       <c r="B93">
-        <v>1188.273</v>
+        <v>1773.636</v>
       </c>
       <c r="C93">
-        <v>1259</v>
+        <v>1816</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2540,13 +2540,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46302.95833333334</v>
+        <v>46303.95833333334</v>
       </c>
       <c r="B94">
-        <v>1118.746</v>
+        <v>1716.778</v>
       </c>
       <c r="C94">
-        <v>1268</v>
+        <v>1811</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2557,13 +2557,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46302.96875</v>
+        <v>46303.96875</v>
       </c>
       <c r="B95">
-        <v>1117.454</v>
+        <v>1695.724</v>
       </c>
       <c r="C95">
-        <v>1254</v>
+        <v>1825</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2574,13 +2574,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46302.97916666666</v>
+        <v>46303.97916666666</v>
       </c>
       <c r="B96">
-        <v>1112.139</v>
+        <v>1693.342</v>
       </c>
       <c r="C96">
-        <v>1209</v>
+        <v>1818</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2591,13 +2591,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46302.98958333334</v>
+        <v>46303.98958333334</v>
       </c>
       <c r="B97">
-        <v>1112.222</v>
+        <v>1672.359</v>
       </c>
       <c r="C97">
-        <v>1187</v>
+        <v>1798</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2608,13 +2608,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B98">
-        <v>1047.446</v>
+        <v>1575.952</v>
       </c>
       <c r="C98">
-        <v>1169</v>
+        <v>1726</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2625,13 +2625,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46303.01041666666</v>
+        <v>46304.01041666666</v>
       </c>
       <c r="B99">
-        <v>1035.081</v>
+        <v>1546.481</v>
       </c>
       <c r="C99">
-        <v>1157</v>
+        <v>1650</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2642,13 +2642,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46303.02083333334</v>
+        <v>46304.02083333334</v>
       </c>
       <c r="B100">
-        <v>1024.452</v>
+        <v>1516.98</v>
       </c>
       <c r="C100">
-        <v>1130</v>
+        <v>1617</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2659,13 +2659,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46303.03125</v>
+        <v>46304.03125</v>
       </c>
       <c r="B101">
-        <v>1002.847</v>
+        <v>1489.087</v>
       </c>
       <c r="C101">
-        <v>1101</v>
+        <v>1585</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2676,13 +2676,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46303.04166666666</v>
+        <v>46304.04166666666</v>
       </c>
       <c r="B102">
-        <v>985.463</v>
+        <v>1452.621</v>
       </c>
       <c r="C102">
-        <v>1096</v>
+        <v>1536</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2693,13 +2693,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46303.05208333334</v>
+        <v>46304.05208333334</v>
       </c>
       <c r="B103">
-        <v>976.143</v>
+        <v>1415.57</v>
       </c>
       <c r="C103">
-        <v>1075</v>
+        <v>1484</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2710,13 +2710,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46303.0625</v>
+        <v>46304.0625</v>
       </c>
       <c r="B104">
-        <v>962.899</v>
+        <v>1380.673</v>
       </c>
       <c r="C104">
-        <v>1045</v>
+        <v>1415</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2727,13 +2727,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46303.07291666666</v>
+        <v>46304.07291666666</v>
       </c>
       <c r="B105">
-        <v>956.673</v>
+        <v>1350.765</v>
       </c>
       <c r="C105">
-        <v>1009</v>
+        <v>1355</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2744,13 +2744,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46303.08333333334</v>
+        <v>46304.08333333334</v>
       </c>
       <c r="B106">
-        <v>944.508</v>
+        <v>1312.84</v>
       </c>
       <c r="C106">
-        <v>947</v>
+        <v>1315</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2761,13 +2761,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46303.09375</v>
+        <v>46304.09375</v>
       </c>
       <c r="B107">
-        <v>931.173</v>
+        <v>1289.018</v>
       </c>
       <c r="C107">
-        <v>923</v>
+        <v>1268</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2778,13 +2778,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46303.10416666666</v>
+        <v>46304.10416666666</v>
       </c>
       <c r="B108">
-        <v>918.982</v>
+        <v>1266.494</v>
       </c>
       <c r="C108">
-        <v>909</v>
+        <v>1192</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2795,13 +2795,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46303.11458333334</v>
+        <v>46304.11458333334</v>
       </c>
       <c r="B109">
-        <v>907.546</v>
+        <v>1241.402</v>
       </c>
       <c r="C109">
-        <v>884</v>
+        <v>1107</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2812,13 +2812,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46303.125</v>
+        <v>46304.125</v>
       </c>
       <c r="B110">
-        <v>904.596</v>
+        <v>1205.137</v>
       </c>
       <c r="C110">
-        <v>858</v>
+        <v>1024</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2829,13 +2829,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46303.13541666666</v>
+        <v>46304.13541666666</v>
       </c>
       <c r="B111">
-        <v>876.46</v>
+        <v>1179.318</v>
       </c>
       <c r="C111">
-        <v>822</v>
+        <v>973</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2846,13 +2846,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46303.14583333334</v>
+        <v>46304.14583333334</v>
       </c>
       <c r="B112">
-        <v>866.343</v>
+        <v>1152.648</v>
       </c>
       <c r="C112">
-        <v>804</v>
+        <v>949</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2863,13 +2863,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46303.15625</v>
+        <v>46304.15625</v>
       </c>
       <c r="B113">
-        <v>854.367</v>
+        <v>1129.4</v>
       </c>
       <c r="C113">
-        <v>816</v>
+        <v>935</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2880,13 +2880,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46303.16666666666</v>
+        <v>46304.16666666666</v>
       </c>
       <c r="B114">
-        <v>847.986</v>
+        <v>1073.653</v>
       </c>
       <c r="C114">
-        <v>824</v>
+        <v>903</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2897,13 +2897,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46303.17708333334</v>
+        <v>46304.17708333334</v>
       </c>
       <c r="B115">
-        <v>845.88</v>
+        <v>1043.234</v>
       </c>
       <c r="C115">
-        <v>821</v>
+        <v>883</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2914,13 +2914,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46303.1875</v>
+        <v>46304.1875</v>
       </c>
       <c r="B116">
-        <v>845.986</v>
+        <v>1015.382</v>
       </c>
       <c r="C116">
-        <v>820</v>
+        <v>861</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2931,13 +2931,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46303.19791666666</v>
+        <v>46304.19791666666</v>
       </c>
       <c r="B117">
-        <v>844.8</v>
+        <v>987.372</v>
       </c>
       <c r="C117">
-        <v>781</v>
+        <v>809</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2948,13 +2948,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46303.20833333334</v>
+        <v>46304.20833333334</v>
       </c>
       <c r="B118">
-        <v>861.654</v>
+        <v>971.984</v>
       </c>
       <c r="C118">
-        <v>749</v>
+        <v>762</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2965,13 +2965,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46303.21875</v>
+        <v>46304.21875</v>
       </c>
       <c r="B119">
-        <v>862.335</v>
+        <v>943.127</v>
       </c>
       <c r="C119">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2982,13 +2982,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46303.22916666666</v>
+        <v>46304.22916666666</v>
       </c>
       <c r="B120">
-        <v>862.64</v>
+        <v>915.84</v>
       </c>
       <c r="C120">
-        <v>748</v>
+        <v>724</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -2999,13 +2999,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46303.23958333334</v>
+        <v>46304.23958333334</v>
       </c>
       <c r="B121">
-        <v>860.624</v>
+        <v>887.677</v>
       </c>
       <c r="C121">
-        <v>760</v>
+        <v>713</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3016,13 +3016,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46303.25</v>
+        <v>46304.25</v>
       </c>
       <c r="B122">
-        <v>883.251</v>
+        <v>813.304</v>
       </c>
       <c r="C122">
-        <v>776</v>
+        <v>718</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3033,13 +3033,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46303.26041666666</v>
+        <v>46304.26041666666</v>
       </c>
       <c r="B123">
-        <v>886.48</v>
+        <v>786.075</v>
       </c>
       <c r="C123">
-        <v>803</v>
+        <v>719</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3050,13 +3050,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46303.27083333334</v>
+        <v>46304.27083333334</v>
       </c>
       <c r="B124">
-        <v>870.474</v>
+        <v>761.053</v>
       </c>
       <c r="C124">
-        <v>845</v>
+        <v>708</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3067,13 +3067,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46303.28125</v>
+        <v>46304.28125</v>
       </c>
       <c r="B125">
-        <v>877.327</v>
+        <v>743.674</v>
       </c>
       <c r="C125">
-        <v>850</v>
+        <v>704</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3084,13 +3084,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46303.29166666666</v>
+        <v>46304.29166666666</v>
       </c>
       <c r="B126">
-        <v>880.114</v>
+        <v>695.553</v>
       </c>
       <c r="C126">
-        <v>845</v>
+        <v>708</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3101,13 +3101,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46303.30208333334</v>
+        <v>46304.30208333334</v>
       </c>
       <c r="B127">
-        <v>889.495</v>
+        <v>671.939</v>
       </c>
       <c r="C127">
-        <v>867</v>
+        <v>701</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3118,13 +3118,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46303.3125</v>
+        <v>46304.3125</v>
       </c>
       <c r="B128">
-        <v>898.332</v>
+        <v>649.144</v>
       </c>
       <c r="C128">
-        <v>874</v>
+        <v>661</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3135,13 +3135,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46303.32291666666</v>
+        <v>46304.32291666666</v>
       </c>
       <c r="B129">
-        <v>910.925</v>
+        <v>629.232</v>
       </c>
       <c r="C129">
-        <v>866</v>
+        <v>586</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3152,13 +3152,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46303.33333333334</v>
+        <v>46304.33333333334</v>
       </c>
       <c r="B130">
-        <v>922.4349999999999</v>
+        <v>620.977</v>
       </c>
       <c r="C130">
-        <v>778</v>
+        <v>510</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3169,13 +3169,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46303.34375</v>
+        <v>46304.34375</v>
       </c>
       <c r="B131">
-        <v>894.984</v>
+        <v>595.1420000000001</v>
       </c>
       <c r="C131">
-        <v>681</v>
+        <v>420</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3186,13 +3186,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46303.35416666666</v>
+        <v>46304.35416666666</v>
       </c>
       <c r="B132">
-        <v>872.3200000000001</v>
+        <v>576.188</v>
       </c>
       <c r="C132">
-        <v>648</v>
+        <v>353</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3203,13 +3203,10 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46303.36458333334</v>
+        <v>46304.36458333334</v>
       </c>
       <c r="B133">
-        <v>843.4690000000001</v>
-      </c>
-      <c r="C133">
-        <v>673</v>
+        <v>546.693</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3220,10 +3217,10 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46303.375</v>
+        <v>46304.375</v>
       </c>
       <c r="B134">
-        <v>844.643</v>
+        <v>486.069</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3234,10 +3231,10 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46303.38541666666</v>
+        <v>46304.38541666666</v>
       </c>
       <c r="B135">
-        <v>843.095</v>
+        <v>472.528</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3248,10 +3245,10 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46303.39583333334</v>
+        <v>46304.39583333334</v>
       </c>
       <c r="B136">
-        <v>848.288</v>
+        <v>448.527</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3262,10 +3259,10 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46303.40625</v>
+        <v>46304.40625</v>
       </c>
       <c r="B137">
-        <v>853.222</v>
+        <v>423.218</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3276,10 +3273,10 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46303.41666666666</v>
+        <v>46304.41666666666</v>
       </c>
       <c r="B138">
-        <v>883.179</v>
+        <v>383.017</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3290,10 +3287,10 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46303.42708333334</v>
+        <v>46304.42708333334</v>
       </c>
       <c r="B139">
-        <v>898.984</v>
+        <v>376.493</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3304,10 +3301,10 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46303.4375</v>
+        <v>46304.4375</v>
       </c>
       <c r="B140">
-        <v>916.1900000000001</v>
+        <v>371.616</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3318,10 +3315,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46303.44791666666</v>
+        <v>46304.44791666666</v>
       </c>
       <c r="B141">
-        <v>936.092</v>
+        <v>369.569</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3332,10 +3329,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46303.45833333334</v>
+        <v>46304.45833333334</v>
       </c>
       <c r="B142">
-        <v>964.549</v>
+        <v>369.212</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3346,10 +3343,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46303.46875</v>
+        <v>46304.46875</v>
       </c>
       <c r="B143">
-        <v>987.485</v>
+        <v>374.842</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3360,10 +3357,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46303.47916666666</v>
+        <v>46304.47916666666</v>
       </c>
       <c r="B144">
-        <v>1010.108</v>
+        <v>380.877</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3374,10 +3371,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46303.48958333334</v>
+        <v>46304.48958333334</v>
       </c>
       <c r="B145">
-        <v>1031.889</v>
+        <v>388.173</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3388,10 +3385,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46303.5</v>
+        <v>46304.5</v>
       </c>
       <c r="B146">
-        <v>1066.584</v>
+        <v>406.774</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3402,10 +3399,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46303.51041666666</v>
+        <v>46304.51041666666</v>
       </c>
       <c r="B147">
-        <v>1088.592</v>
+        <v>414.974</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3416,10 +3413,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46303.52083333334</v>
+        <v>46304.52083333334</v>
       </c>
       <c r="B148">
-        <v>1110.292</v>
+        <v>425.947</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3430,10 +3427,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46303.53125</v>
+        <v>46304.53125</v>
       </c>
       <c r="B149">
-        <v>1129.892</v>
+        <v>436.873</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3444,10 +3441,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46303.54166666666</v>
+        <v>46304.54166666666</v>
       </c>
       <c r="B150">
-        <v>1161.18</v>
+        <v>461.365</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3458,10 +3455,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46303.55208333334</v>
+        <v>46304.55208333334</v>
       </c>
       <c r="B151">
-        <v>1177.675</v>
+        <v>473.776</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3472,10 +3469,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46303.5625</v>
+        <v>46304.5625</v>
       </c>
       <c r="B152">
-        <v>1193.139</v>
+        <v>485.813</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3486,10 +3483,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46303.57291666666</v>
+        <v>46304.57291666666</v>
       </c>
       <c r="B153">
-        <v>1208.626</v>
+        <v>496.869</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3500,10 +3497,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46303.58333333334</v>
+        <v>46304.58333333334</v>
       </c>
       <c r="B154">
-        <v>1249.629</v>
+        <v>523.6660000000001</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3514,10 +3511,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46303.59375</v>
+        <v>46304.59375</v>
       </c>
       <c r="B155">
-        <v>1260.393</v>
+        <v>532.051</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3528,10 +3525,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46303.60416666666</v>
+        <v>46304.60416666666</v>
       </c>
       <c r="B156">
-        <v>1270.003</v>
+        <v>538.784</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3542,10 +3539,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46303.61458333334</v>
+        <v>46304.61458333334</v>
       </c>
       <c r="B157">
-        <v>1277.895</v>
+        <v>544.377</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3556,10 +3553,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46303.625</v>
+        <v>46304.625</v>
       </c>
       <c r="B158">
-        <v>1324.173</v>
+        <v>564.147</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3570,10 +3567,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46303.63541666666</v>
+        <v>46304.63541666666</v>
       </c>
       <c r="B159">
-        <v>1337.145</v>
+        <v>561.487</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3584,10 +3581,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46303.64583333334</v>
+        <v>46304.64583333334</v>
       </c>
       <c r="B160">
-        <v>1346.862</v>
+        <v>557.3339999999999</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3598,10 +3595,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46303.65625</v>
+        <v>46304.65625</v>
       </c>
       <c r="B161">
-        <v>1360.183</v>
+        <v>552.684</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3612,10 +3609,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46303.66666666666</v>
+        <v>46304.66666666666</v>
       </c>
       <c r="B162">
-        <v>1418.277</v>
+        <v>529.785</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -3626,10 +3623,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46303.67708333334</v>
+        <v>46304.67708333334</v>
       </c>
       <c r="B163">
-        <v>1441.013</v>
+        <v>523.177</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -3640,10 +3637,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46303.6875</v>
+        <v>46304.6875</v>
       </c>
       <c r="B164">
-        <v>1465.289</v>
+        <v>515.89</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -3654,10 +3651,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46303.69791666666</v>
+        <v>46304.69791666666</v>
       </c>
       <c r="B165">
-        <v>1492.584</v>
+        <v>513.3869999999999</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -3668,10 +3665,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46303.70833333334</v>
+        <v>46304.70833333334</v>
       </c>
       <c r="B166">
-        <v>1459.914</v>
+        <v>532.596</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -3682,10 +3679,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46303.71875</v>
+        <v>46304.71875</v>
       </c>
       <c r="B167">
-        <v>1515.691</v>
+        <v>538.23</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -3696,10 +3693,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46303.72916666666</v>
+        <v>46304.72916666666</v>
       </c>
       <c r="B168">
-        <v>1577.369</v>
+        <v>539.0359999999999</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -3710,10 +3707,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46303.73958333334</v>
+        <v>46304.73958333334</v>
       </c>
       <c r="B169">
-        <v>1629.899</v>
+        <v>543.472</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -3724,10 +3721,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46303.75</v>
+        <v>46304.75</v>
       </c>
       <c r="B170">
-        <v>1674.692</v>
+        <v>583.511</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -3738,10 +3735,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46303.76041666666</v>
+        <v>46304.76041666666</v>
       </c>
       <c r="B171">
-        <v>1707.773</v>
+        <v>588.927</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -3752,10 +3749,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46303.77083333334</v>
+        <v>46304.77083333334</v>
       </c>
       <c r="B172">
-        <v>1738.081</v>
+        <v>595.446</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -3766,10 +3763,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46303.78125</v>
+        <v>46304.78125</v>
       </c>
       <c r="B173">
-        <v>1766.908</v>
+        <v>604.955</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -3780,10 +3777,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46303.79166666666</v>
+        <v>46304.79166666666</v>
       </c>
       <c r="B174">
-        <v>1793.875</v>
+        <v>627.329</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -3794,10 +3791,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46303.80208333334</v>
+        <v>46304.80208333334</v>
       </c>
       <c r="B175">
-        <v>1807.205</v>
+        <v>638.783</v>
       </c>
       <c r="D175">
         <v>78</v>
@@ -3808,10 +3805,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46303.8125</v>
+        <v>46304.8125</v>
       </c>
       <c r="B176">
-        <v>1820.69</v>
+        <v>646.452</v>
       </c>
       <c r="D176">
         <v>79</v>
@@ -3822,10 +3819,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46303.82291666666</v>
+        <v>46304.82291666666</v>
       </c>
       <c r="B177">
-        <v>1835.841</v>
+        <v>648.711</v>
       </c>
       <c r="D177">
         <v>80</v>
@@ -3836,10 +3833,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46303.83333333334</v>
+        <v>46304.83333333334</v>
       </c>
       <c r="B178">
-        <v>1854.683</v>
+        <v>623.946</v>
       </c>
       <c r="D178">
         <v>81</v>
@@ -3850,10 +3847,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46303.84375</v>
+        <v>46304.84375</v>
       </c>
       <c r="B179">
-        <v>1858.663</v>
+        <v>626.621</v>
       </c>
       <c r="D179">
         <v>82</v>
@@ -3864,10 +3861,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46303.85416666666</v>
+        <v>46304.85416666666</v>
       </c>
       <c r="B180">
-        <v>1857.073</v>
+        <v>630.362</v>
       </c>
       <c r="D180">
         <v>83</v>
@@ -3878,10 +3875,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46303.86458333334</v>
+        <v>46304.86458333334</v>
       </c>
       <c r="B181">
-        <v>1854.992</v>
+        <v>636.141</v>
       </c>
       <c r="D181">
         <v>84</v>
@@ -3892,10 +3889,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46303.875</v>
+        <v>46304.875</v>
       </c>
       <c r="B182">
-        <v>1847.867</v>
+        <v>639.078</v>
       </c>
       <c r="D182">
         <v>85</v>
@@ -3906,10 +3903,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46303.88541666666</v>
+        <v>46304.88541666666</v>
       </c>
       <c r="B183">
-        <v>1837.619</v>
+        <v>651.275</v>
       </c>
       <c r="D183">
         <v>86</v>
@@ -3920,10 +3917,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46303.89583333334</v>
+        <v>46304.89583333334</v>
       </c>
       <c r="B184">
-        <v>1828.412</v>
+        <v>671.658</v>
       </c>
       <c r="D184">
         <v>87</v>
@@ -3934,10 +3931,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46303.90625</v>
+        <v>46304.90625</v>
       </c>
       <c r="B185">
-        <v>1817.62</v>
+        <v>697.634</v>
       </c>
       <c r="D185">
         <v>88</v>
@@ -3948,10 +3945,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46303.91666666666</v>
+        <v>46304.91666666666</v>
       </c>
       <c r="B186">
-        <v>1814.557</v>
+        <v>741.503</v>
       </c>
       <c r="D186">
         <v>89</v>
@@ -3962,10 +3959,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46303.92708333334</v>
+        <v>46304.92708333334</v>
       </c>
       <c r="B187">
-        <v>1801.449</v>
+        <v>765.87</v>
       </c>
       <c r="D187">
         <v>90</v>
@@ -3976,10 +3973,10 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46303.9375</v>
+        <v>46304.9375</v>
       </c>
       <c r="B188">
-        <v>1787.655</v>
+        <v>792.913</v>
       </c>
       <c r="D188">
         <v>91</v>
@@ -3990,10 +3987,10 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46303.94791666666</v>
+        <v>46304.94791666666</v>
       </c>
       <c r="B189">
-        <v>1773.636</v>
+        <v>815.336</v>
       </c>
       <c r="D189">
         <v>92</v>

--- a/data_fetching/Entsoe/Wind_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Wind_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="385">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>08.10.20261</t>
-  </si>
-  <si>
-    <t>08.10.20262</t>
-  </si>
-  <si>
-    <t>08.10.20263</t>
-  </si>
-  <si>
-    <t>08.10.20264</t>
-  </si>
-  <si>
-    <t>08.10.20265</t>
-  </si>
-  <si>
-    <t>08.10.20266</t>
-  </si>
-  <si>
-    <t>08.10.20267</t>
-  </si>
-  <si>
-    <t>08.10.20268</t>
-  </si>
-  <si>
-    <t>08.10.20269</t>
-  </si>
-  <si>
-    <t>08.10.202610</t>
-  </si>
-  <si>
-    <t>08.10.202611</t>
-  </si>
-  <si>
-    <t>08.10.202612</t>
-  </si>
-  <si>
-    <t>08.10.202613</t>
-  </si>
-  <si>
-    <t>08.10.202614</t>
-  </si>
-  <si>
-    <t>08.10.202615</t>
-  </si>
-  <si>
-    <t>08.10.202616</t>
-  </si>
-  <si>
-    <t>08.10.202617</t>
-  </si>
-  <si>
-    <t>08.10.202618</t>
-  </si>
-  <si>
-    <t>08.10.202619</t>
-  </si>
-  <si>
-    <t>08.10.202620</t>
-  </si>
-  <si>
-    <t>08.10.202621</t>
-  </si>
-  <si>
-    <t>08.10.202622</t>
-  </si>
-  <si>
-    <t>08.10.202623</t>
-  </si>
-  <si>
-    <t>08.10.202624</t>
-  </si>
-  <si>
-    <t>08.10.202625</t>
-  </si>
-  <si>
-    <t>08.10.202626</t>
-  </si>
-  <si>
-    <t>08.10.202627</t>
-  </si>
-  <si>
-    <t>08.10.202628</t>
-  </si>
-  <si>
-    <t>08.10.202629</t>
-  </si>
-  <si>
-    <t>08.10.202630</t>
-  </si>
-  <si>
-    <t>08.10.202631</t>
-  </si>
-  <si>
-    <t>08.10.202632</t>
-  </si>
-  <si>
-    <t>08.10.202633</t>
-  </si>
-  <si>
-    <t>08.10.202634</t>
-  </si>
-  <si>
-    <t>08.10.202635</t>
-  </si>
-  <si>
-    <t>08.10.202636</t>
-  </si>
-  <si>
-    <t>08.10.202637</t>
-  </si>
-  <si>
-    <t>08.10.202638</t>
-  </si>
-  <si>
-    <t>08.10.202639</t>
-  </si>
-  <si>
-    <t>08.10.202640</t>
-  </si>
-  <si>
-    <t>08.10.202641</t>
-  </si>
-  <si>
-    <t>08.10.202642</t>
-  </si>
-  <si>
-    <t>08.10.202643</t>
-  </si>
-  <si>
-    <t>08.10.202644</t>
-  </si>
-  <si>
-    <t>08.10.202645</t>
-  </si>
-  <si>
-    <t>08.10.202646</t>
-  </si>
-  <si>
-    <t>08.10.202647</t>
-  </si>
-  <si>
-    <t>08.10.202648</t>
-  </si>
-  <si>
-    <t>08.10.202649</t>
-  </si>
-  <si>
-    <t>08.10.202650</t>
-  </si>
-  <si>
-    <t>08.10.202651</t>
-  </si>
-  <si>
-    <t>08.10.202652</t>
-  </si>
-  <si>
-    <t>08.10.202653</t>
-  </si>
-  <si>
-    <t>08.10.202654</t>
-  </si>
-  <si>
-    <t>08.10.202655</t>
-  </si>
-  <si>
-    <t>08.10.202656</t>
-  </si>
-  <si>
-    <t>08.10.202657</t>
-  </si>
-  <si>
-    <t>08.10.202658</t>
-  </si>
-  <si>
-    <t>08.10.202659</t>
-  </si>
-  <si>
-    <t>08.10.202660</t>
-  </si>
-  <si>
-    <t>08.10.202661</t>
-  </si>
-  <si>
-    <t>08.10.202662</t>
-  </si>
-  <si>
-    <t>08.10.202663</t>
-  </si>
-  <si>
-    <t>08.10.202664</t>
-  </si>
-  <si>
-    <t>08.10.202665</t>
-  </si>
-  <si>
-    <t>08.10.202666</t>
-  </si>
-  <si>
-    <t>08.10.202667</t>
-  </si>
-  <si>
-    <t>08.10.202668</t>
-  </si>
-  <si>
-    <t>08.10.202669</t>
-  </si>
-  <si>
-    <t>08.10.202670</t>
-  </si>
-  <si>
-    <t>08.10.202671</t>
-  </si>
-  <si>
-    <t>08.10.202672</t>
-  </si>
-  <si>
-    <t>08.10.202673</t>
-  </si>
-  <si>
-    <t>08.10.202674</t>
-  </si>
-  <si>
-    <t>08.10.202675</t>
-  </si>
-  <si>
-    <t>08.10.202676</t>
-  </si>
-  <si>
-    <t>08.10.202677</t>
-  </si>
-  <si>
-    <t>08.10.202678</t>
-  </si>
-  <si>
-    <t>08.10.202679</t>
-  </si>
-  <si>
-    <t>08.10.202680</t>
-  </si>
-  <si>
-    <t>08.10.202681</t>
-  </si>
-  <si>
-    <t>08.10.202682</t>
-  </si>
-  <si>
-    <t>08.10.202683</t>
-  </si>
-  <si>
-    <t>08.10.202684</t>
-  </si>
-  <si>
-    <t>08.10.202685</t>
-  </si>
-  <si>
-    <t>08.10.202686</t>
-  </si>
-  <si>
-    <t>08.10.202687</t>
-  </si>
-  <si>
-    <t>08.10.202688</t>
-  </si>
-  <si>
-    <t>08.10.202689</t>
-  </si>
-  <si>
-    <t>08.10.202690</t>
-  </si>
-  <si>
-    <t>08.10.202691</t>
-  </si>
-  <si>
-    <t>08.10.202692</t>
-  </si>
-  <si>
-    <t>08.10.202693</t>
-  </si>
-  <si>
-    <t>08.10.202694</t>
-  </si>
-  <si>
-    <t>08.10.202695</t>
-  </si>
-  <si>
-    <t>08.10.202696</t>
-  </si>
-  <si>
     <t>09.10.20261</t>
   </si>
   <si>
@@ -593,6 +305,870 @@
   </si>
   <si>
     <t>09.10.202692</t>
+  </si>
+  <si>
+    <t>09.10.202693</t>
+  </si>
+  <si>
+    <t>09.10.202694</t>
+  </si>
+  <si>
+    <t>09.10.202695</t>
+  </si>
+  <si>
+    <t>09.10.202696</t>
+  </si>
+  <si>
+    <t>10.10.20261</t>
+  </si>
+  <si>
+    <t>10.10.20262</t>
+  </si>
+  <si>
+    <t>10.10.20263</t>
+  </si>
+  <si>
+    <t>10.10.20264</t>
+  </si>
+  <si>
+    <t>10.10.20265</t>
+  </si>
+  <si>
+    <t>10.10.20266</t>
+  </si>
+  <si>
+    <t>10.10.20267</t>
+  </si>
+  <si>
+    <t>10.10.20268</t>
+  </si>
+  <si>
+    <t>10.10.20269</t>
+  </si>
+  <si>
+    <t>10.10.202610</t>
+  </si>
+  <si>
+    <t>10.10.202611</t>
+  </si>
+  <si>
+    <t>10.10.202612</t>
+  </si>
+  <si>
+    <t>10.10.202613</t>
+  </si>
+  <si>
+    <t>10.10.202614</t>
+  </si>
+  <si>
+    <t>10.10.202615</t>
+  </si>
+  <si>
+    <t>10.10.202616</t>
+  </si>
+  <si>
+    <t>10.10.202617</t>
+  </si>
+  <si>
+    <t>10.10.202618</t>
+  </si>
+  <si>
+    <t>10.10.202619</t>
+  </si>
+  <si>
+    <t>10.10.202620</t>
+  </si>
+  <si>
+    <t>10.10.202621</t>
+  </si>
+  <si>
+    <t>10.10.202622</t>
+  </si>
+  <si>
+    <t>10.10.202623</t>
+  </si>
+  <si>
+    <t>10.10.202624</t>
+  </si>
+  <si>
+    <t>10.10.202625</t>
+  </si>
+  <si>
+    <t>10.10.202626</t>
+  </si>
+  <si>
+    <t>10.10.202627</t>
+  </si>
+  <si>
+    <t>10.10.202628</t>
+  </si>
+  <si>
+    <t>10.10.202629</t>
+  </si>
+  <si>
+    <t>10.10.202630</t>
+  </si>
+  <si>
+    <t>10.10.202631</t>
+  </si>
+  <si>
+    <t>10.10.202632</t>
+  </si>
+  <si>
+    <t>10.10.202633</t>
+  </si>
+  <si>
+    <t>10.10.202634</t>
+  </si>
+  <si>
+    <t>10.10.202635</t>
+  </si>
+  <si>
+    <t>10.10.202636</t>
+  </si>
+  <si>
+    <t>10.10.202637</t>
+  </si>
+  <si>
+    <t>10.10.202638</t>
+  </si>
+  <si>
+    <t>10.10.202639</t>
+  </si>
+  <si>
+    <t>10.10.202640</t>
+  </si>
+  <si>
+    <t>10.10.202641</t>
+  </si>
+  <si>
+    <t>10.10.202642</t>
+  </si>
+  <si>
+    <t>10.10.202643</t>
+  </si>
+  <si>
+    <t>10.10.202644</t>
+  </si>
+  <si>
+    <t>10.10.202645</t>
+  </si>
+  <si>
+    <t>10.10.202646</t>
+  </si>
+  <si>
+    <t>10.10.202647</t>
+  </si>
+  <si>
+    <t>10.10.202648</t>
+  </si>
+  <si>
+    <t>10.10.202649</t>
+  </si>
+  <si>
+    <t>10.10.202650</t>
+  </si>
+  <si>
+    <t>10.10.202651</t>
+  </si>
+  <si>
+    <t>10.10.202652</t>
+  </si>
+  <si>
+    <t>10.10.202653</t>
+  </si>
+  <si>
+    <t>10.10.202654</t>
+  </si>
+  <si>
+    <t>10.10.202655</t>
+  </si>
+  <si>
+    <t>10.10.202656</t>
+  </si>
+  <si>
+    <t>10.10.202657</t>
+  </si>
+  <si>
+    <t>10.10.202658</t>
+  </si>
+  <si>
+    <t>10.10.202659</t>
+  </si>
+  <si>
+    <t>10.10.202660</t>
+  </si>
+  <si>
+    <t>10.10.202661</t>
+  </si>
+  <si>
+    <t>10.10.202662</t>
+  </si>
+  <si>
+    <t>10.10.202663</t>
+  </si>
+  <si>
+    <t>10.10.202664</t>
+  </si>
+  <si>
+    <t>10.10.202665</t>
+  </si>
+  <si>
+    <t>10.10.202666</t>
+  </si>
+  <si>
+    <t>10.10.202667</t>
+  </si>
+  <si>
+    <t>10.10.202668</t>
+  </si>
+  <si>
+    <t>10.10.202669</t>
+  </si>
+  <si>
+    <t>10.10.202670</t>
+  </si>
+  <si>
+    <t>10.10.202671</t>
+  </si>
+  <si>
+    <t>10.10.202672</t>
+  </si>
+  <si>
+    <t>10.10.202673</t>
+  </si>
+  <si>
+    <t>10.10.202674</t>
+  </si>
+  <si>
+    <t>10.10.202675</t>
+  </si>
+  <si>
+    <t>10.10.202676</t>
+  </si>
+  <si>
+    <t>10.10.202677</t>
+  </si>
+  <si>
+    <t>10.10.202678</t>
+  </si>
+  <si>
+    <t>10.10.202679</t>
+  </si>
+  <si>
+    <t>10.10.202680</t>
+  </si>
+  <si>
+    <t>10.10.202681</t>
+  </si>
+  <si>
+    <t>10.10.202682</t>
+  </si>
+  <si>
+    <t>10.10.202683</t>
+  </si>
+  <si>
+    <t>10.10.202684</t>
+  </si>
+  <si>
+    <t>10.10.202685</t>
+  </si>
+  <si>
+    <t>10.10.202686</t>
+  </si>
+  <si>
+    <t>10.10.202687</t>
+  </si>
+  <si>
+    <t>10.10.202688</t>
+  </si>
+  <si>
+    <t>10.10.202689</t>
+  </si>
+  <si>
+    <t>10.10.202690</t>
+  </si>
+  <si>
+    <t>10.10.202691</t>
+  </si>
+  <si>
+    <t>10.10.202692</t>
+  </si>
+  <si>
+    <t>10.10.202693</t>
+  </si>
+  <si>
+    <t>10.10.202694</t>
+  </si>
+  <si>
+    <t>10.10.202695</t>
+  </si>
+  <si>
+    <t>10.10.202696</t>
+  </si>
+  <si>
+    <t>11.10.20261</t>
+  </si>
+  <si>
+    <t>11.10.20262</t>
+  </si>
+  <si>
+    <t>11.10.20263</t>
+  </si>
+  <si>
+    <t>11.10.20264</t>
+  </si>
+  <si>
+    <t>11.10.20265</t>
+  </si>
+  <si>
+    <t>11.10.20266</t>
+  </si>
+  <si>
+    <t>11.10.20267</t>
+  </si>
+  <si>
+    <t>11.10.20268</t>
+  </si>
+  <si>
+    <t>11.10.20269</t>
+  </si>
+  <si>
+    <t>11.10.202610</t>
+  </si>
+  <si>
+    <t>11.10.202611</t>
+  </si>
+  <si>
+    <t>11.10.202612</t>
+  </si>
+  <si>
+    <t>11.10.202613</t>
+  </si>
+  <si>
+    <t>11.10.202614</t>
+  </si>
+  <si>
+    <t>11.10.202615</t>
+  </si>
+  <si>
+    <t>11.10.202616</t>
+  </si>
+  <si>
+    <t>11.10.202617</t>
+  </si>
+  <si>
+    <t>11.10.202618</t>
+  </si>
+  <si>
+    <t>11.10.202619</t>
+  </si>
+  <si>
+    <t>11.10.202620</t>
+  </si>
+  <si>
+    <t>11.10.202621</t>
+  </si>
+  <si>
+    <t>11.10.202622</t>
+  </si>
+  <si>
+    <t>11.10.202623</t>
+  </si>
+  <si>
+    <t>11.10.202624</t>
+  </si>
+  <si>
+    <t>11.10.202625</t>
+  </si>
+  <si>
+    <t>11.10.202626</t>
+  </si>
+  <si>
+    <t>11.10.202627</t>
+  </si>
+  <si>
+    <t>11.10.202628</t>
+  </si>
+  <si>
+    <t>11.10.202629</t>
+  </si>
+  <si>
+    <t>11.10.202630</t>
+  </si>
+  <si>
+    <t>11.10.202631</t>
+  </si>
+  <si>
+    <t>11.10.202632</t>
+  </si>
+  <si>
+    <t>11.10.202633</t>
+  </si>
+  <si>
+    <t>11.10.202634</t>
+  </si>
+  <si>
+    <t>11.10.202635</t>
+  </si>
+  <si>
+    <t>11.10.202636</t>
+  </si>
+  <si>
+    <t>11.10.202637</t>
+  </si>
+  <si>
+    <t>11.10.202638</t>
+  </si>
+  <si>
+    <t>11.10.202639</t>
+  </si>
+  <si>
+    <t>11.10.202640</t>
+  </si>
+  <si>
+    <t>11.10.202641</t>
+  </si>
+  <si>
+    <t>11.10.202642</t>
+  </si>
+  <si>
+    <t>11.10.202643</t>
+  </si>
+  <si>
+    <t>11.10.202644</t>
+  </si>
+  <si>
+    <t>11.10.202645</t>
+  </si>
+  <si>
+    <t>11.10.202646</t>
+  </si>
+  <si>
+    <t>11.10.202647</t>
+  </si>
+  <si>
+    <t>11.10.202648</t>
+  </si>
+  <si>
+    <t>11.10.202649</t>
+  </si>
+  <si>
+    <t>11.10.202650</t>
+  </si>
+  <si>
+    <t>11.10.202651</t>
+  </si>
+  <si>
+    <t>11.10.202652</t>
+  </si>
+  <si>
+    <t>11.10.202653</t>
+  </si>
+  <si>
+    <t>11.10.202654</t>
+  </si>
+  <si>
+    <t>11.10.202655</t>
+  </si>
+  <si>
+    <t>11.10.202656</t>
+  </si>
+  <si>
+    <t>11.10.202657</t>
+  </si>
+  <si>
+    <t>11.10.202658</t>
+  </si>
+  <si>
+    <t>11.10.202659</t>
+  </si>
+  <si>
+    <t>11.10.202660</t>
+  </si>
+  <si>
+    <t>11.10.202661</t>
+  </si>
+  <si>
+    <t>11.10.202662</t>
+  </si>
+  <si>
+    <t>11.10.202663</t>
+  </si>
+  <si>
+    <t>11.10.202664</t>
+  </si>
+  <si>
+    <t>11.10.202665</t>
+  </si>
+  <si>
+    <t>11.10.202666</t>
+  </si>
+  <si>
+    <t>11.10.202667</t>
+  </si>
+  <si>
+    <t>11.10.202668</t>
+  </si>
+  <si>
+    <t>11.10.202669</t>
+  </si>
+  <si>
+    <t>11.10.202670</t>
+  </si>
+  <si>
+    <t>11.10.202671</t>
+  </si>
+  <si>
+    <t>11.10.202672</t>
+  </si>
+  <si>
+    <t>11.10.202673</t>
+  </si>
+  <si>
+    <t>11.10.202674</t>
+  </si>
+  <si>
+    <t>11.10.202675</t>
+  </si>
+  <si>
+    <t>11.10.202676</t>
+  </si>
+  <si>
+    <t>11.10.202677</t>
+  </si>
+  <si>
+    <t>11.10.202678</t>
+  </si>
+  <si>
+    <t>11.10.202679</t>
+  </si>
+  <si>
+    <t>11.10.202680</t>
+  </si>
+  <si>
+    <t>11.10.202681</t>
+  </si>
+  <si>
+    <t>11.10.202682</t>
+  </si>
+  <si>
+    <t>11.10.202683</t>
+  </si>
+  <si>
+    <t>11.10.202684</t>
+  </si>
+  <si>
+    <t>11.10.202685</t>
+  </si>
+  <si>
+    <t>11.10.202686</t>
+  </si>
+  <si>
+    <t>11.10.202687</t>
+  </si>
+  <si>
+    <t>11.10.202688</t>
+  </si>
+  <si>
+    <t>11.10.202689</t>
+  </si>
+  <si>
+    <t>11.10.202690</t>
+  </si>
+  <si>
+    <t>11.10.202691</t>
+  </si>
+  <si>
+    <t>11.10.202692</t>
+  </si>
+  <si>
+    <t>11.10.202693</t>
+  </si>
+  <si>
+    <t>11.10.202694</t>
+  </si>
+  <si>
+    <t>11.10.202695</t>
+  </si>
+  <si>
+    <t>11.10.202696</t>
+  </si>
+  <si>
+    <t>12.10.20261</t>
+  </si>
+  <si>
+    <t>12.10.20262</t>
+  </si>
+  <si>
+    <t>12.10.20263</t>
+  </si>
+  <si>
+    <t>12.10.20264</t>
+  </si>
+  <si>
+    <t>12.10.20265</t>
+  </si>
+  <si>
+    <t>12.10.20266</t>
+  </si>
+  <si>
+    <t>12.10.20267</t>
+  </si>
+  <si>
+    <t>12.10.20268</t>
+  </si>
+  <si>
+    <t>12.10.20269</t>
+  </si>
+  <si>
+    <t>12.10.202610</t>
+  </si>
+  <si>
+    <t>12.10.202611</t>
+  </si>
+  <si>
+    <t>12.10.202612</t>
+  </si>
+  <si>
+    <t>12.10.202613</t>
+  </si>
+  <si>
+    <t>12.10.202614</t>
+  </si>
+  <si>
+    <t>12.10.202615</t>
+  </si>
+  <si>
+    <t>12.10.202616</t>
+  </si>
+  <si>
+    <t>12.10.202617</t>
+  </si>
+  <si>
+    <t>12.10.202618</t>
+  </si>
+  <si>
+    <t>12.10.202619</t>
+  </si>
+  <si>
+    <t>12.10.202620</t>
+  </si>
+  <si>
+    <t>12.10.202621</t>
+  </si>
+  <si>
+    <t>12.10.202622</t>
+  </si>
+  <si>
+    <t>12.10.202623</t>
+  </si>
+  <si>
+    <t>12.10.202624</t>
+  </si>
+  <si>
+    <t>12.10.202625</t>
+  </si>
+  <si>
+    <t>12.10.202626</t>
+  </si>
+  <si>
+    <t>12.10.202627</t>
+  </si>
+  <si>
+    <t>12.10.202628</t>
+  </si>
+  <si>
+    <t>12.10.202629</t>
+  </si>
+  <si>
+    <t>12.10.202630</t>
+  </si>
+  <si>
+    <t>12.10.202631</t>
+  </si>
+  <si>
+    <t>12.10.202632</t>
+  </si>
+  <si>
+    <t>12.10.202633</t>
+  </si>
+  <si>
+    <t>12.10.202634</t>
+  </si>
+  <si>
+    <t>12.10.202635</t>
+  </si>
+  <si>
+    <t>12.10.202636</t>
+  </si>
+  <si>
+    <t>12.10.202637</t>
+  </si>
+  <si>
+    <t>12.10.202638</t>
+  </si>
+  <si>
+    <t>12.10.202639</t>
+  </si>
+  <si>
+    <t>12.10.202640</t>
+  </si>
+  <si>
+    <t>12.10.202641</t>
+  </si>
+  <si>
+    <t>12.10.202642</t>
+  </si>
+  <si>
+    <t>12.10.202643</t>
+  </si>
+  <si>
+    <t>12.10.202644</t>
+  </si>
+  <si>
+    <t>12.10.202645</t>
+  </si>
+  <si>
+    <t>12.10.202646</t>
+  </si>
+  <si>
+    <t>12.10.202647</t>
+  </si>
+  <si>
+    <t>12.10.202648</t>
+  </si>
+  <si>
+    <t>12.10.202649</t>
+  </si>
+  <si>
+    <t>12.10.202650</t>
+  </si>
+  <si>
+    <t>12.10.202651</t>
+  </si>
+  <si>
+    <t>12.10.202652</t>
+  </si>
+  <si>
+    <t>12.10.202653</t>
+  </si>
+  <si>
+    <t>12.10.202654</t>
+  </si>
+  <si>
+    <t>12.10.202655</t>
+  </si>
+  <si>
+    <t>12.10.202656</t>
+  </si>
+  <si>
+    <t>12.10.202657</t>
+  </si>
+  <si>
+    <t>12.10.202658</t>
+  </si>
+  <si>
+    <t>12.10.202659</t>
+  </si>
+  <si>
+    <t>12.10.202660</t>
+  </si>
+  <si>
+    <t>12.10.202661</t>
+  </si>
+  <si>
+    <t>12.10.202662</t>
+  </si>
+  <si>
+    <t>12.10.202663</t>
+  </si>
+  <si>
+    <t>12.10.202664</t>
+  </si>
+  <si>
+    <t>12.10.202665</t>
+  </si>
+  <si>
+    <t>12.10.202666</t>
+  </si>
+  <si>
+    <t>12.10.202667</t>
+  </si>
+  <si>
+    <t>12.10.202668</t>
+  </si>
+  <si>
+    <t>12.10.202669</t>
+  </si>
+  <si>
+    <t>12.10.202670</t>
+  </si>
+  <si>
+    <t>12.10.202671</t>
+  </si>
+  <si>
+    <t>12.10.202672</t>
+  </si>
+  <si>
+    <t>12.10.202673</t>
+  </si>
+  <si>
+    <t>12.10.202674</t>
+  </si>
+  <si>
+    <t>12.10.202675</t>
+  </si>
+  <si>
+    <t>12.10.202676</t>
+  </si>
+  <si>
+    <t>12.10.202677</t>
+  </si>
+  <si>
+    <t>12.10.202678</t>
+  </si>
+  <si>
+    <t>12.10.202679</t>
+  </si>
+  <si>
+    <t>12.10.202680</t>
+  </si>
+  <si>
+    <t>12.10.202681</t>
+  </si>
+  <si>
+    <t>12.10.202682</t>
+  </si>
+  <si>
+    <t>12.10.202683</t>
+  </si>
+  <si>
+    <t>12.10.202684</t>
+  </si>
+  <si>
+    <t>12.10.202685</t>
+  </si>
+  <si>
+    <t>12.10.202686</t>
+  </si>
+  <si>
+    <t>12.10.202687</t>
+  </si>
+  <si>
+    <t>12.10.202688</t>
+  </si>
+  <si>
+    <t>12.10.202689</t>
+  </si>
+  <si>
+    <t>12.10.202690</t>
+  </si>
+  <si>
+    <t>12.10.202691</t>
+  </si>
+  <si>
+    <t>12.10.202692</t>
   </si>
 </sst>
 </file>
@@ -954,7 +1530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E189"/>
+  <dimension ref="A1:E381"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -976,13 +1552,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B2">
-        <v>1047.446</v>
+        <v>1575.952</v>
       </c>
       <c r="C2">
-        <v>1169</v>
+        <v>1726</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -993,13 +1569,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46303.01041666666</v>
+        <v>46304.01041666666</v>
       </c>
       <c r="B3">
-        <v>1035.081</v>
+        <v>1546.481</v>
       </c>
       <c r="C3">
-        <v>1157</v>
+        <v>1650</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1010,13 +1586,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46303.02083333334</v>
+        <v>46304.02083333334</v>
       </c>
       <c r="B4">
-        <v>1024.452</v>
+        <v>1516.98</v>
       </c>
       <c r="C4">
-        <v>1130</v>
+        <v>1617</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1027,13 +1603,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46303.03125</v>
+        <v>46304.03125</v>
       </c>
       <c r="B5">
-        <v>1002.847</v>
+        <v>1489.087</v>
       </c>
       <c r="C5">
-        <v>1101</v>
+        <v>1585</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1044,13 +1620,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46303.04166666666</v>
+        <v>46304.04166666666</v>
       </c>
       <c r="B6">
-        <v>985.463</v>
+        <v>1452.621</v>
       </c>
       <c r="C6">
-        <v>1096</v>
+        <v>1536</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1061,13 +1637,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46303.05208333334</v>
+        <v>46304.05208333334</v>
       </c>
       <c r="B7">
-        <v>976.143</v>
+        <v>1415.57</v>
       </c>
       <c r="C7">
-        <v>1075</v>
+        <v>1484</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1078,13 +1654,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46303.0625</v>
+        <v>46304.0625</v>
       </c>
       <c r="B8">
-        <v>962.899</v>
+        <v>1380.673</v>
       </c>
       <c r="C8">
-        <v>1045</v>
+        <v>1415</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1095,13 +1671,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46303.07291666666</v>
+        <v>46304.07291666666</v>
       </c>
       <c r="B9">
-        <v>956.673</v>
+        <v>1350.765</v>
       </c>
       <c r="C9">
-        <v>1009</v>
+        <v>1355</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1112,13 +1688,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46303.08333333334</v>
+        <v>46304.08333333334</v>
       </c>
       <c r="B10">
-        <v>944.508</v>
+        <v>1312.84</v>
       </c>
       <c r="C10">
-        <v>947</v>
+        <v>1315</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1129,13 +1705,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46303.09375</v>
+        <v>46304.09375</v>
       </c>
       <c r="B11">
-        <v>931.173</v>
+        <v>1289.018</v>
       </c>
       <c r="C11">
-        <v>923</v>
+        <v>1268</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1146,13 +1722,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46303.10416666666</v>
+        <v>46304.10416666666</v>
       </c>
       <c r="B12">
-        <v>918.982</v>
+        <v>1266.494</v>
       </c>
       <c r="C12">
-        <v>909</v>
+        <v>1192</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1163,13 +1739,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46303.11458333334</v>
+        <v>46304.11458333334</v>
       </c>
       <c r="B13">
-        <v>907.546</v>
+        <v>1241.402</v>
       </c>
       <c r="C13">
-        <v>884</v>
+        <v>1107</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1180,13 +1756,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46303.125</v>
+        <v>46304.125</v>
       </c>
       <c r="B14">
-        <v>904.596</v>
+        <v>1205.137</v>
       </c>
       <c r="C14">
-        <v>858</v>
+        <v>1024</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1197,13 +1773,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46303.13541666666</v>
+        <v>46304.13541666666</v>
       </c>
       <c r="B15">
-        <v>876.46</v>
+        <v>1179.318</v>
       </c>
       <c r="C15">
-        <v>822</v>
+        <v>973</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1214,13 +1790,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46303.14583333334</v>
+        <v>46304.14583333334</v>
       </c>
       <c r="B16">
-        <v>866.343</v>
+        <v>1152.648</v>
       </c>
       <c r="C16">
-        <v>804</v>
+        <v>949</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1231,13 +1807,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46303.15625</v>
+        <v>46304.15625</v>
       </c>
       <c r="B17">
-        <v>854.367</v>
+        <v>1129.4</v>
       </c>
       <c r="C17">
-        <v>816</v>
+        <v>935</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1248,13 +1824,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46303.16666666666</v>
+        <v>46304.16666666666</v>
       </c>
       <c r="B18">
-        <v>847.986</v>
+        <v>1073.653</v>
       </c>
       <c r="C18">
-        <v>824</v>
+        <v>903</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1265,13 +1841,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46303.17708333334</v>
+        <v>46304.17708333334</v>
       </c>
       <c r="B19">
-        <v>845.88</v>
+        <v>1043.234</v>
       </c>
       <c r="C19">
-        <v>821</v>
+        <v>883</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1282,13 +1858,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46303.1875</v>
+        <v>46304.1875</v>
       </c>
       <c r="B20">
-        <v>845.986</v>
+        <v>1015.382</v>
       </c>
       <c r="C20">
-        <v>820</v>
+        <v>861</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1299,13 +1875,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46303.19791666666</v>
+        <v>46304.19791666666</v>
       </c>
       <c r="B21">
-        <v>844.8</v>
+        <v>987.372</v>
       </c>
       <c r="C21">
-        <v>781</v>
+        <v>809</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1316,13 +1892,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46303.20833333334</v>
+        <v>46304.20833333334</v>
       </c>
       <c r="B22">
-        <v>861.654</v>
+        <v>971.984</v>
       </c>
       <c r="C22">
-        <v>749</v>
+        <v>762</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1333,13 +1909,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46303.21875</v>
+        <v>46304.21875</v>
       </c>
       <c r="B23">
-        <v>862.335</v>
+        <v>943.127</v>
       </c>
       <c r="C23">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1350,13 +1926,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46303.22916666666</v>
+        <v>46304.22916666666</v>
       </c>
       <c r="B24">
-        <v>862.64</v>
+        <v>915.84</v>
       </c>
       <c r="C24">
-        <v>748</v>
+        <v>724</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1367,13 +1943,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46303.23958333334</v>
+        <v>46304.23958333334</v>
       </c>
       <c r="B25">
-        <v>860.624</v>
+        <v>887.677</v>
       </c>
       <c r="C25">
-        <v>760</v>
+        <v>713</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1384,13 +1960,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46303.25</v>
+        <v>46304.25</v>
       </c>
       <c r="B26">
-        <v>883.251</v>
+        <v>813.304</v>
       </c>
       <c r="C26">
-        <v>776</v>
+        <v>718</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1401,13 +1977,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46303.26041666666</v>
+        <v>46304.26041666666</v>
       </c>
       <c r="B27">
-        <v>886.48</v>
+        <v>786.075</v>
       </c>
       <c r="C27">
-        <v>803</v>
+        <v>719</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1418,13 +1994,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46303.27083333334</v>
+        <v>46304.27083333334</v>
       </c>
       <c r="B28">
-        <v>870.474</v>
+        <v>761.053</v>
       </c>
       <c r="C28">
-        <v>845</v>
+        <v>708</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1435,13 +2011,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46303.28125</v>
+        <v>46304.28125</v>
       </c>
       <c r="B29">
-        <v>877.327</v>
+        <v>743.674</v>
       </c>
       <c r="C29">
-        <v>850</v>
+        <v>704</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1452,13 +2028,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46303.29166666666</v>
+        <v>46304.29166666666</v>
       </c>
       <c r="B30">
-        <v>880.114</v>
+        <v>695.553</v>
       </c>
       <c r="C30">
-        <v>845</v>
+        <v>708</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1469,13 +2045,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46303.30208333334</v>
+        <v>46304.30208333334</v>
       </c>
       <c r="B31">
-        <v>889.495</v>
+        <v>671.939</v>
       </c>
       <c r="C31">
-        <v>867</v>
+        <v>701</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1486,13 +2062,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46303.3125</v>
+        <v>46304.3125</v>
       </c>
       <c r="B32">
-        <v>898.332</v>
+        <v>649.144</v>
       </c>
       <c r="C32">
-        <v>874</v>
+        <v>661</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1503,13 +2079,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46303.32291666666</v>
+        <v>46304.32291666666</v>
       </c>
       <c r="B33">
-        <v>910.925</v>
+        <v>629.232</v>
       </c>
       <c r="C33">
-        <v>866</v>
+        <v>586</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1520,13 +2096,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46303.33333333334</v>
+        <v>46304.33333333334</v>
       </c>
       <c r="B34">
-        <v>922.4349999999999</v>
+        <v>620.977</v>
       </c>
       <c r="C34">
-        <v>778</v>
+        <v>510</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1537,13 +2113,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46303.34375</v>
+        <v>46304.34375</v>
       </c>
       <c r="B35">
-        <v>894.984</v>
+        <v>595.1420000000001</v>
       </c>
       <c r="C35">
-        <v>681</v>
+        <v>420</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1554,13 +2130,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46303.35416666666</v>
+        <v>46304.35416666666</v>
       </c>
       <c r="B36">
-        <v>872.3200000000001</v>
+        <v>576.188</v>
       </c>
       <c r="C36">
-        <v>648</v>
+        <v>353</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1571,13 +2147,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46303.36458333334</v>
+        <v>46304.36458333334</v>
       </c>
       <c r="B37">
-        <v>843.4690000000001</v>
+        <v>546.693</v>
       </c>
       <c r="C37">
-        <v>673</v>
+        <v>309</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1588,13 +2164,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46303.375</v>
+        <v>46304.375</v>
       </c>
       <c r="B38">
-        <v>844.643</v>
+        <v>486.069</v>
       </c>
       <c r="C38">
-        <v>691</v>
+        <v>275</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1605,13 +2181,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46303.38541666666</v>
+        <v>46304.38541666666</v>
       </c>
       <c r="B39">
-        <v>843.095</v>
+        <v>472.528</v>
       </c>
       <c r="C39">
-        <v>694</v>
+        <v>256</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1622,13 +2198,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46303.39583333334</v>
+        <v>46304.39583333334</v>
       </c>
       <c r="B40">
-        <v>848.288</v>
+        <v>448.527</v>
       </c>
       <c r="C40">
-        <v>712</v>
+        <v>243</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1639,13 +2215,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46303.40625</v>
+        <v>46304.40625</v>
       </c>
       <c r="B41">
-        <v>853.222</v>
+        <v>423.218</v>
       </c>
       <c r="C41">
-        <v>713</v>
+        <v>248</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1656,13 +2232,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46303.41666666666</v>
+        <v>46304.41666666666</v>
       </c>
       <c r="B42">
-        <v>883.179</v>
+        <v>383.017</v>
       </c>
       <c r="C42">
-        <v>733</v>
+        <v>253</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1673,13 +2249,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46303.42708333334</v>
+        <v>46304.42708333334</v>
       </c>
       <c r="B43">
-        <v>898.984</v>
+        <v>376.493</v>
       </c>
       <c r="C43">
-        <v>779</v>
+        <v>269</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1690,13 +2266,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46303.4375</v>
+        <v>46304.4375</v>
       </c>
       <c r="B44">
-        <v>916.1900000000001</v>
+        <v>371.616</v>
       </c>
       <c r="C44">
-        <v>818</v>
+        <v>277</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1707,13 +2283,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46303.44791666666</v>
+        <v>46304.44791666666</v>
       </c>
       <c r="B45">
-        <v>936.092</v>
+        <v>369.569</v>
       </c>
       <c r="C45">
-        <v>854</v>
+        <v>287</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1724,13 +2300,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46303.45833333334</v>
+        <v>46304.45833333334</v>
       </c>
       <c r="B46">
-        <v>964.549</v>
+        <v>369.212</v>
       </c>
       <c r="C46">
-        <v>897</v>
+        <v>283</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1741,13 +2317,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46303.46875</v>
+        <v>46304.46875</v>
       </c>
       <c r="B47">
-        <v>987.485</v>
+        <v>374.842</v>
       </c>
       <c r="C47">
-        <v>936</v>
+        <v>288</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1758,13 +2334,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46303.47916666666</v>
+        <v>46304.47916666666</v>
       </c>
       <c r="B48">
-        <v>1010.108</v>
+        <v>380.877</v>
       </c>
       <c r="C48">
-        <v>982</v>
+        <v>286</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1775,13 +2351,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46303.48958333334</v>
+        <v>46304.48958333334</v>
       </c>
       <c r="B49">
-        <v>1031.889</v>
+        <v>388.173</v>
       </c>
       <c r="C49">
-        <v>1056</v>
+        <v>300</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1792,13 +2368,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46303.5</v>
+        <v>46304.5</v>
       </c>
       <c r="B50">
-        <v>1066.584</v>
+        <v>406.774</v>
       </c>
       <c r="C50">
-        <v>1117</v>
+        <v>316</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1809,13 +2385,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46303.51041666666</v>
+        <v>46304.51041666666</v>
       </c>
       <c r="B51">
-        <v>1088.592</v>
+        <v>414.974</v>
       </c>
       <c r="C51">
-        <v>1119</v>
+        <v>344</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1826,13 +2402,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46303.52083333334</v>
+        <v>46304.52083333334</v>
       </c>
       <c r="B52">
-        <v>1110.292</v>
+        <v>425.947</v>
       </c>
       <c r="C52">
-        <v>1090</v>
+        <v>344</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1843,13 +2419,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46303.53125</v>
+        <v>46304.53125</v>
       </c>
       <c r="B53">
-        <v>1129.892</v>
+        <v>436.873</v>
       </c>
       <c r="C53">
-        <v>1093</v>
+        <v>360</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1860,13 +2436,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46303.54166666666</v>
+        <v>46304.54166666666</v>
       </c>
       <c r="B54">
-        <v>1161.18</v>
+        <v>461.365</v>
       </c>
       <c r="C54">
-        <v>1107</v>
+        <v>386</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1877,13 +2453,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46303.55208333334</v>
+        <v>46304.55208333334</v>
       </c>
       <c r="B55">
-        <v>1177.675</v>
+        <v>473.776</v>
       </c>
       <c r="C55">
-        <v>1123</v>
+        <v>454</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1894,13 +2470,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46303.5625</v>
+        <v>46304.5625</v>
       </c>
       <c r="B56">
-        <v>1193.139</v>
+        <v>485.813</v>
       </c>
       <c r="C56">
-        <v>1151</v>
+        <v>519</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1911,13 +2487,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46303.57291666666</v>
+        <v>46304.57291666666</v>
       </c>
       <c r="B57">
-        <v>1208.626</v>
+        <v>496.869</v>
       </c>
       <c r="C57">
-        <v>1164</v>
+        <v>537</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1928,13 +2504,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46303.58333333334</v>
+        <v>46304.58333333334</v>
       </c>
       <c r="B58">
-        <v>1249.629</v>
+        <v>523.6660000000001</v>
       </c>
       <c r="C58">
-        <v>1193</v>
+        <v>518</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1945,13 +2521,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46303.59375</v>
+        <v>46304.59375</v>
       </c>
       <c r="B59">
-        <v>1260.393</v>
+        <v>532.051</v>
       </c>
       <c r="C59">
-        <v>1257</v>
+        <v>500</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1962,13 +2538,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46303.60416666666</v>
+        <v>46304.60416666666</v>
       </c>
       <c r="B60">
-        <v>1270.003</v>
+        <v>538.784</v>
       </c>
       <c r="C60">
-        <v>1331</v>
+        <v>439</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1979,13 +2555,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46303.61458333334</v>
+        <v>46304.61458333334</v>
       </c>
       <c r="B61">
-        <v>1277.895</v>
+        <v>544.377</v>
       </c>
       <c r="C61">
-        <v>1400</v>
+        <v>414</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -1996,13 +2572,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46303.625</v>
+        <v>46304.625</v>
       </c>
       <c r="B62">
-        <v>1324.173</v>
+        <v>564.147</v>
       </c>
       <c r="C62">
-        <v>1491</v>
+        <v>403</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2013,13 +2589,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46303.63541666666</v>
+        <v>46304.63541666666</v>
       </c>
       <c r="B63">
-        <v>1337.145</v>
+        <v>561.487</v>
       </c>
       <c r="C63">
-        <v>1579</v>
+        <v>417</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2030,13 +2606,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46303.64583333334</v>
+        <v>46304.64583333334</v>
       </c>
       <c r="B64">
-        <v>1346.862</v>
+        <v>557.3339999999999</v>
       </c>
       <c r="C64">
-        <v>1619</v>
+        <v>414</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2047,13 +2623,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46303.65625</v>
+        <v>46304.65625</v>
       </c>
       <c r="B65">
-        <v>1360.183</v>
+        <v>552.684</v>
       </c>
       <c r="C65">
-        <v>1650</v>
+        <v>404</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2064,13 +2640,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46303.66666666666</v>
+        <v>46304.66666666666</v>
       </c>
       <c r="B66">
-        <v>1418.277</v>
+        <v>529.785</v>
       </c>
       <c r="C66">
-        <v>1678</v>
+        <v>392</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2081,13 +2657,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46303.67708333334</v>
+        <v>46304.67708333334</v>
       </c>
       <c r="B67">
-        <v>1441.013</v>
+        <v>523.177</v>
       </c>
       <c r="C67">
-        <v>1728</v>
+        <v>362</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2098,13 +2674,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46303.6875</v>
+        <v>46304.6875</v>
       </c>
       <c r="B68">
-        <v>1465.289</v>
+        <v>515.89</v>
       </c>
       <c r="C68">
-        <v>1733</v>
+        <v>357</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2115,13 +2691,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46303.69791666666</v>
+        <v>46304.69791666666</v>
       </c>
       <c r="B69">
-        <v>1492.584</v>
+        <v>513.3869999999999</v>
       </c>
       <c r="C69">
-        <v>1709</v>
+        <v>359</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2132,13 +2708,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46303.70833333334</v>
+        <v>46304.70833333334</v>
       </c>
       <c r="B70">
-        <v>1459.914</v>
+        <v>532.596</v>
       </c>
       <c r="C70">
-        <v>1685</v>
+        <v>362</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2149,13 +2725,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46303.71875</v>
+        <v>46304.71875</v>
       </c>
       <c r="B71">
-        <v>1515.691</v>
+        <v>538.23</v>
       </c>
       <c r="C71">
-        <v>1717</v>
+        <v>378</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2166,13 +2742,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46303.72916666666</v>
+        <v>46304.72916666666</v>
       </c>
       <c r="B72">
-        <v>1577.369</v>
+        <v>539.0359999999999</v>
       </c>
       <c r="C72">
-        <v>1665</v>
+        <v>399</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2183,13 +2759,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46303.73958333334</v>
+        <v>46304.73958333334</v>
       </c>
       <c r="B73">
-        <v>1629.899</v>
+        <v>543.472</v>
       </c>
       <c r="C73">
-        <v>1696</v>
+        <v>407</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2200,13 +2776,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46303.75</v>
+        <v>46304.75</v>
       </c>
       <c r="B74">
-        <v>1674.692</v>
+        <v>583.511</v>
       </c>
       <c r="C74">
-        <v>1759</v>
+        <v>414</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2217,13 +2793,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46303.76041666666</v>
+        <v>46304.76041666666</v>
       </c>
       <c r="B75">
-        <v>1707.773</v>
+        <v>588.927</v>
       </c>
       <c r="C75">
-        <v>1874</v>
+        <v>428</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2234,13 +2810,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46303.77083333334</v>
+        <v>46304.77083333334</v>
       </c>
       <c r="B76">
-        <v>1738.081</v>
+        <v>595.446</v>
       </c>
       <c r="C76">
-        <v>1949</v>
+        <v>427</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2251,13 +2827,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46303.78125</v>
+        <v>46304.78125</v>
       </c>
       <c r="B77">
-        <v>1766.908</v>
+        <v>604.955</v>
       </c>
       <c r="C77">
-        <v>2008</v>
+        <v>420</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2268,13 +2844,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46303.79166666666</v>
+        <v>46304.79166666666</v>
       </c>
       <c r="B78">
-        <v>1793.875</v>
+        <v>627.329</v>
       </c>
       <c r="C78">
-        <v>2060</v>
+        <v>427</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2285,13 +2861,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46303.80208333334</v>
+        <v>46304.80208333334</v>
       </c>
       <c r="B79">
-        <v>1807.205</v>
+        <v>638.783</v>
       </c>
       <c r="C79">
-        <v>2083</v>
+        <v>407</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2302,13 +2878,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46303.8125</v>
+        <v>46304.8125</v>
       </c>
       <c r="B80">
-        <v>1820.69</v>
+        <v>646.452</v>
       </c>
       <c r="C80">
-        <v>2080</v>
+        <v>357</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2319,13 +2895,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46303.82291666666</v>
+        <v>46304.82291666666</v>
       </c>
       <c r="B81">
-        <v>1835.841</v>
+        <v>648.711</v>
       </c>
       <c r="C81">
-        <v>2024</v>
+        <v>344</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2336,13 +2912,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46303.83333333334</v>
+        <v>46304.83333333334</v>
       </c>
       <c r="B82">
-        <v>1854.683</v>
+        <v>623.946</v>
       </c>
       <c r="C82">
-        <v>1977</v>
+        <v>371</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2353,13 +2929,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46303.84375</v>
+        <v>46304.84375</v>
       </c>
       <c r="B83">
-        <v>1858.663</v>
+        <v>626.621</v>
       </c>
       <c r="C83">
-        <v>1950</v>
+        <v>390</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2370,13 +2946,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46303.85416666666</v>
+        <v>46304.85416666666</v>
       </c>
       <c r="B84">
-        <v>1857.073</v>
+        <v>630.362</v>
       </c>
       <c r="C84">
-        <v>1954</v>
+        <v>391</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2387,13 +2963,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46303.86458333334</v>
+        <v>46304.86458333334</v>
       </c>
       <c r="B85">
-        <v>1854.992</v>
+        <v>636.141</v>
       </c>
       <c r="C85">
-        <v>1950</v>
+        <v>421</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2404,13 +2980,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46303.875</v>
+        <v>46304.875</v>
       </c>
       <c r="B86">
-        <v>1847.867</v>
+        <v>639.078</v>
       </c>
       <c r="C86">
-        <v>1910</v>
+        <v>454</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2421,13 +2997,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46303.88541666666</v>
+        <v>46304.88541666666</v>
       </c>
       <c r="B87">
-        <v>1837.619</v>
+        <v>651.275</v>
       </c>
       <c r="C87">
-        <v>1908</v>
+        <v>497</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2438,13 +3014,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46303.89583333334</v>
+        <v>46304.89583333334</v>
       </c>
       <c r="B88">
-        <v>1828.412</v>
+        <v>671.658</v>
       </c>
       <c r="C88">
-        <v>1896</v>
+        <v>532</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2455,13 +3031,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46303.90625</v>
+        <v>46304.90625</v>
       </c>
       <c r="B89">
-        <v>1817.62</v>
+        <v>697.634</v>
       </c>
       <c r="C89">
-        <v>1868</v>
+        <v>590</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2472,13 +3048,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46303.91666666666</v>
+        <v>46304.91666666666</v>
       </c>
       <c r="B90">
-        <v>1814.557</v>
+        <v>741.503</v>
       </c>
       <c r="C90">
-        <v>1842</v>
+        <v>611</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2489,13 +3065,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46303.92708333334</v>
+        <v>46304.92708333334</v>
       </c>
       <c r="B91">
-        <v>1801.449</v>
+        <v>765.87</v>
       </c>
       <c r="C91">
-        <v>1842</v>
+        <v>652</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2506,13 +3082,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46303.9375</v>
+        <v>46304.9375</v>
       </c>
       <c r="B92">
-        <v>1787.655</v>
+        <v>792.913</v>
       </c>
       <c r="C92">
-        <v>1844</v>
+        <v>686</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2523,13 +3099,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46303.94791666666</v>
+        <v>46304.94791666666</v>
       </c>
       <c r="B93">
-        <v>1773.636</v>
+        <v>815.336</v>
       </c>
       <c r="C93">
-        <v>1816</v>
+        <v>690</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2540,13 +3116,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46303.95833333334</v>
+        <v>46304.95833333334</v>
       </c>
       <c r="B94">
-        <v>1716.778</v>
+        <v>727.552</v>
       </c>
       <c r="C94">
-        <v>1811</v>
+        <v>599</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2557,13 +3133,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46303.96875</v>
+        <v>46304.96875</v>
       </c>
       <c r="B95">
-        <v>1695.724</v>
+        <v>737.215</v>
       </c>
       <c r="C95">
-        <v>1825</v>
+        <v>532</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2574,13 +3150,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46303.97916666666</v>
+        <v>46304.97916666666</v>
       </c>
       <c r="B96">
-        <v>1693.342</v>
+        <v>742.616</v>
       </c>
       <c r="C96">
-        <v>1818</v>
+        <v>499</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2591,13 +3167,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46303.98958333334</v>
+        <v>46304.98958333334</v>
       </c>
       <c r="B97">
-        <v>1672.359</v>
+        <v>723.951</v>
       </c>
       <c r="C97">
-        <v>1798</v>
+        <v>475</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2608,13 +3184,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="B98">
-        <v>1575.952</v>
+        <v>665.784</v>
       </c>
       <c r="C98">
-        <v>1726</v>
+        <v>482</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2625,13 +3201,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46304.01041666666</v>
+        <v>46305.01041666666</v>
       </c>
       <c r="B99">
-        <v>1546.481</v>
+        <v>658.5650000000001</v>
       </c>
       <c r="C99">
-        <v>1650</v>
+        <v>518</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2642,13 +3218,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46304.02083333334</v>
+        <v>46305.02083333334</v>
       </c>
       <c r="B100">
-        <v>1516.98</v>
+        <v>650.309</v>
       </c>
       <c r="C100">
-        <v>1617</v>
+        <v>515</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2659,13 +3235,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46304.03125</v>
+        <v>46305.03125</v>
       </c>
       <c r="B101">
-        <v>1489.087</v>
+        <v>640.194</v>
       </c>
       <c r="C101">
-        <v>1585</v>
+        <v>530</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2676,13 +3252,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46304.04166666666</v>
+        <v>46305.04166666666</v>
       </c>
       <c r="B102">
-        <v>1452.621</v>
+        <v>643.986</v>
       </c>
       <c r="C102">
-        <v>1536</v>
+        <v>543</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2693,13 +3269,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46304.05208333334</v>
+        <v>46305.05208333334</v>
       </c>
       <c r="B103">
-        <v>1415.57</v>
+        <v>640.9059999999999</v>
       </c>
       <c r="C103">
-        <v>1484</v>
+        <v>581</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2710,13 +3286,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46304.0625</v>
+        <v>46305.0625</v>
       </c>
       <c r="B104">
-        <v>1380.673</v>
+        <v>637.146</v>
       </c>
       <c r="C104">
-        <v>1415</v>
+        <v>618</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2727,13 +3303,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46304.07291666666</v>
+        <v>46305.07291666666</v>
       </c>
       <c r="B105">
-        <v>1350.765</v>
+        <v>641.966</v>
       </c>
       <c r="C105">
-        <v>1355</v>
+        <v>649</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2744,13 +3320,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46304.08333333334</v>
+        <v>46305.08333333334</v>
       </c>
       <c r="B106">
-        <v>1312.84</v>
+        <v>658.6369999999999</v>
       </c>
       <c r="C106">
-        <v>1315</v>
+        <v>709</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2761,13 +3337,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46304.09375</v>
+        <v>46305.09375</v>
       </c>
       <c r="B107">
-        <v>1289.018</v>
+        <v>651.162</v>
       </c>
       <c r="C107">
-        <v>1268</v>
+        <v>721</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2778,13 +3354,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46304.10416666666</v>
+        <v>46305.10416666666</v>
       </c>
       <c r="B108">
-        <v>1266.494</v>
+        <v>653.806</v>
       </c>
       <c r="C108">
-        <v>1192</v>
+        <v>704</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2795,13 +3371,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46304.11458333334</v>
+        <v>46305.11458333334</v>
       </c>
       <c r="B109">
-        <v>1241.402</v>
+        <v>650.524</v>
       </c>
       <c r="C109">
-        <v>1107</v>
+        <v>670</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2812,13 +3388,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46304.125</v>
+        <v>46305.125</v>
       </c>
       <c r="B110">
-        <v>1205.137</v>
+        <v>641.252</v>
       </c>
       <c r="C110">
-        <v>1024</v>
+        <v>611</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2829,13 +3405,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46304.13541666666</v>
+        <v>46305.13541666666</v>
       </c>
       <c r="B111">
-        <v>1179.318</v>
+        <v>634.994</v>
       </c>
       <c r="C111">
-        <v>973</v>
+        <v>608</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2846,13 +3422,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46304.14583333334</v>
+        <v>46305.14583333334</v>
       </c>
       <c r="B112">
-        <v>1152.648</v>
+        <v>626.005</v>
       </c>
       <c r="C112">
-        <v>949</v>
+        <v>591</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2863,13 +3439,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46304.15625</v>
+        <v>46305.15625</v>
       </c>
       <c r="B113">
-        <v>1129.4</v>
+        <v>592.5940000000001</v>
       </c>
       <c r="C113">
-        <v>935</v>
+        <v>549</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2880,13 +3456,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46304.16666666666</v>
+        <v>46305.16666666666</v>
       </c>
       <c r="B114">
-        <v>1073.653</v>
+        <v>555.647</v>
       </c>
       <c r="C114">
-        <v>903</v>
+        <v>513</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2897,13 +3473,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46304.17708333334</v>
+        <v>46305.17708333334</v>
       </c>
       <c r="B115">
-        <v>1043.234</v>
+        <v>539.678</v>
       </c>
       <c r="C115">
-        <v>883</v>
+        <v>475</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2914,13 +3490,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46304.1875</v>
+        <v>46305.1875</v>
       </c>
       <c r="B116">
-        <v>1015.382</v>
+        <v>530.864</v>
       </c>
       <c r="C116">
-        <v>861</v>
+        <v>450</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2931,13 +3507,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46304.19791666666</v>
+        <v>46305.19791666666</v>
       </c>
       <c r="B117">
-        <v>987.372</v>
+        <v>511.427</v>
       </c>
       <c r="C117">
-        <v>809</v>
+        <v>457</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2948,13 +3524,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46304.20833333334</v>
+        <v>46305.20833333334</v>
       </c>
       <c r="B118">
-        <v>971.984</v>
+        <v>488.706</v>
       </c>
       <c r="C118">
-        <v>762</v>
+        <v>459</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2965,13 +3541,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46304.21875</v>
+        <v>46305.21875</v>
       </c>
       <c r="B119">
-        <v>943.127</v>
+        <v>465.996</v>
       </c>
       <c r="C119">
-        <v>738</v>
+        <v>481</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2982,13 +3558,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46304.22916666666</v>
+        <v>46305.22916666666</v>
       </c>
       <c r="B120">
-        <v>915.84</v>
+        <v>446.79</v>
       </c>
       <c r="C120">
-        <v>724</v>
+        <v>487</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -2999,13 +3575,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46304.23958333334</v>
+        <v>46305.23958333334</v>
       </c>
       <c r="B121">
-        <v>887.677</v>
+        <v>427.548</v>
       </c>
       <c r="C121">
-        <v>713</v>
+        <v>508</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3016,13 +3592,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46304.25</v>
+        <v>46305.25</v>
       </c>
       <c r="B122">
-        <v>813.304</v>
+        <v>376.473</v>
       </c>
       <c r="C122">
-        <v>718</v>
+        <v>534</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3033,13 +3609,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46304.26041666666</v>
+        <v>46305.26041666666</v>
       </c>
       <c r="B123">
-        <v>786.075</v>
+        <v>358.351</v>
       </c>
       <c r="C123">
-        <v>719</v>
+        <v>581</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3050,13 +3626,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46304.27083333334</v>
+        <v>46305.27083333334</v>
       </c>
       <c r="B124">
-        <v>761.053</v>
+        <v>339.88</v>
       </c>
       <c r="C124">
-        <v>708</v>
+        <v>586</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3067,13 +3643,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46304.28125</v>
+        <v>46305.28125</v>
       </c>
       <c r="B125">
-        <v>743.674</v>
+        <v>325.469</v>
       </c>
       <c r="C125">
-        <v>704</v>
+        <v>584</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3084,13 +3660,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46304.29166666666</v>
+        <v>46305.29166666666</v>
       </c>
       <c r="B126">
-        <v>695.553</v>
+        <v>287.81</v>
       </c>
       <c r="C126">
-        <v>708</v>
+        <v>554</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3101,13 +3677,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46304.30208333334</v>
+        <v>46305.30208333334</v>
       </c>
       <c r="B127">
-        <v>671.939</v>
+        <v>282.675</v>
       </c>
       <c r="C127">
-        <v>701</v>
+        <v>543</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3118,13 +3694,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46304.3125</v>
+        <v>46305.3125</v>
       </c>
       <c r="B128">
-        <v>649.144</v>
+        <v>270.014</v>
       </c>
       <c r="C128">
-        <v>661</v>
+        <v>513</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3135,13 +3711,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46304.32291666666</v>
+        <v>46305.32291666666</v>
       </c>
       <c r="B129">
-        <v>629.232</v>
+        <v>257.964</v>
       </c>
       <c r="C129">
-        <v>586</v>
+        <v>436</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3152,13 +3728,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46304.33333333334</v>
+        <v>46305.33333333334</v>
       </c>
       <c r="B130">
-        <v>620.977</v>
+        <v>239.916</v>
       </c>
       <c r="C130">
-        <v>510</v>
+        <v>338</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3169,13 +3745,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46304.34375</v>
+        <v>46305.34375</v>
       </c>
       <c r="B131">
-        <v>595.1420000000001</v>
+        <v>226.258</v>
       </c>
       <c r="C131">
-        <v>420</v>
+        <v>282</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3186,13 +3762,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46304.35416666666</v>
+        <v>46305.35416666666</v>
       </c>
       <c r="B132">
-        <v>576.188</v>
+        <v>206.014</v>
       </c>
       <c r="C132">
-        <v>353</v>
+        <v>258</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3203,10 +3779,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46304.36458333334</v>
+        <v>46305.36458333334</v>
       </c>
       <c r="B133">
-        <v>546.693</v>
+        <v>190.22</v>
+      </c>
+      <c r="C133">
+        <v>234</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3217,10 +3796,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46304.375</v>
+        <v>46305.375</v>
       </c>
       <c r="B134">
-        <v>486.069</v>
+        <v>124.899</v>
+      </c>
+      <c r="C134">
+        <v>181</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3231,10 +3813,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46304.38541666666</v>
+        <v>46305.38541666666</v>
       </c>
       <c r="B135">
-        <v>472.528</v>
+        <v>124.05</v>
+      </c>
+      <c r="C135">
+        <v>127</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3245,10 +3830,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46304.39583333334</v>
+        <v>46305.39583333334</v>
       </c>
       <c r="B136">
-        <v>448.527</v>
+        <v>120.326</v>
+      </c>
+      <c r="C136">
+        <v>89</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3259,10 +3847,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46304.40625</v>
+        <v>46305.40625</v>
       </c>
       <c r="B137">
-        <v>423.218</v>
+        <v>117.084</v>
+      </c>
+      <c r="C137">
+        <v>74</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3273,10 +3864,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46304.41666666666</v>
+        <v>46305.41666666666</v>
       </c>
       <c r="B138">
-        <v>383.017</v>
+        <v>103.455</v>
+      </c>
+      <c r="C138">
+        <v>87</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3287,10 +3881,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46304.42708333334</v>
+        <v>46305.42708333334</v>
       </c>
       <c r="B139">
-        <v>376.493</v>
+        <v>103.117</v>
+      </c>
+      <c r="C139">
+        <v>100</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3301,10 +3898,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46304.4375</v>
+        <v>46305.4375</v>
       </c>
       <c r="B140">
-        <v>371.616</v>
+        <v>103.073</v>
+      </c>
+      <c r="C140">
+        <v>80</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3315,10 +3915,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46304.44791666666</v>
+        <v>46305.44791666666</v>
       </c>
       <c r="B141">
-        <v>369.569</v>
+        <v>102.757</v>
+      </c>
+      <c r="C141">
+        <v>64</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3329,10 +3932,13 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46304.45833333334</v>
+        <v>46305.45833333334</v>
       </c>
       <c r="B142">
-        <v>369.212</v>
+        <v>98.687</v>
+      </c>
+      <c r="C142">
+        <v>46</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3343,10 +3949,13 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46304.46875</v>
+        <v>46305.46875</v>
       </c>
       <c r="B143">
-        <v>374.842</v>
+        <v>99.52800000000001</v>
+      </c>
+      <c r="C143">
+        <v>31</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3357,10 +3966,13 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46304.47916666666</v>
+        <v>46305.47916666666</v>
       </c>
       <c r="B144">
-        <v>380.877</v>
+        <v>100.224</v>
+      </c>
+      <c r="C144">
+        <v>13</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3371,10 +3983,13 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46304.48958333334</v>
+        <v>46305.48958333334</v>
       </c>
       <c r="B145">
-        <v>388.173</v>
+        <v>101.145</v>
+      </c>
+      <c r="C145">
+        <v>2</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3385,10 +4000,13 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46304.5</v>
+        <v>46305.5</v>
       </c>
       <c r="B146">
-        <v>406.774</v>
+        <v>100.396</v>
+      </c>
+      <c r="C146">
+        <v>0</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3399,10 +4017,13 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46304.51041666666</v>
+        <v>46305.51041666666</v>
       </c>
       <c r="B147">
-        <v>414.974</v>
+        <v>101.64</v>
+      </c>
+      <c r="C147">
+        <v>0</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3413,10 +4034,13 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46304.52083333334</v>
+        <v>46305.52083333334</v>
       </c>
       <c r="B148">
-        <v>425.947</v>
+        <v>103.173</v>
+      </c>
+      <c r="C148">
+        <v>5</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3427,10 +4051,13 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46304.53125</v>
+        <v>46305.53125</v>
       </c>
       <c r="B149">
-        <v>436.873</v>
+        <v>104.763</v>
+      </c>
+      <c r="C149">
+        <v>11</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3441,10 +4068,13 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46304.54166666666</v>
+        <v>46305.54166666666</v>
       </c>
       <c r="B150">
-        <v>461.365</v>
+        <v>107.481</v>
+      </c>
+      <c r="C150">
+        <v>12</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3455,10 +4085,13 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46304.55208333334</v>
+        <v>46305.55208333334</v>
       </c>
       <c r="B151">
-        <v>473.776</v>
+        <v>111.618</v>
+      </c>
+      <c r="C151">
+        <v>11</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3469,10 +4102,13 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46304.5625</v>
+        <v>46305.5625</v>
       </c>
       <c r="B152">
-        <v>485.813</v>
+        <v>115.357</v>
+      </c>
+      <c r="C152">
+        <v>8</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3483,10 +4119,13 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46304.57291666666</v>
+        <v>46305.57291666666</v>
       </c>
       <c r="B153">
-        <v>496.869</v>
+        <v>119.082</v>
+      </c>
+      <c r="C153">
+        <v>5</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3497,10 +4136,13 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46304.58333333334</v>
+        <v>46305.58333333334</v>
       </c>
       <c r="B154">
-        <v>523.6660000000001</v>
+        <v>132.59</v>
+      </c>
+      <c r="C154">
+        <v>6</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3511,10 +4153,13 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46304.59375</v>
+        <v>46305.59375</v>
       </c>
       <c r="B155">
-        <v>532.051</v>
+        <v>137.511</v>
+      </c>
+      <c r="C155">
+        <v>14</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3525,10 +4170,13 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46304.60416666666</v>
+        <v>46305.60416666666</v>
       </c>
       <c r="B156">
-        <v>538.784</v>
+        <v>142.195</v>
+      </c>
+      <c r="C156">
+        <v>26</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3539,10 +4187,13 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46304.61458333334</v>
+        <v>46305.61458333334</v>
       </c>
       <c r="B157">
-        <v>544.377</v>
+        <v>146.878</v>
+      </c>
+      <c r="C157">
+        <v>27</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3553,10 +4204,13 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46304.625</v>
+        <v>46305.625</v>
       </c>
       <c r="B158">
-        <v>564.147</v>
+        <v>169.723</v>
+      </c>
+      <c r="C158">
+        <v>37</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3567,10 +4221,13 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46304.63541666666</v>
+        <v>46305.63541666666</v>
       </c>
       <c r="B159">
-        <v>561.487</v>
+        <v>175.474</v>
+      </c>
+      <c r="C159">
+        <v>50</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3581,10 +4238,13 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46304.64583333334</v>
+        <v>46305.64583333334</v>
       </c>
       <c r="B160">
-        <v>557.3339999999999</v>
+        <v>180.363</v>
+      </c>
+      <c r="C160">
+        <v>67</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3595,10 +4255,13 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46304.65625</v>
+        <v>46305.65625</v>
       </c>
       <c r="B161">
-        <v>552.684</v>
+        <v>185.823</v>
+      </c>
+      <c r="C161">
+        <v>93</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3609,10 +4272,13 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46304.66666666666</v>
+        <v>46305.66666666666</v>
       </c>
       <c r="B162">
-        <v>529.785</v>
+        <v>214.915</v>
+      </c>
+      <c r="C162">
+        <v>116</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -3623,10 +4289,13 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46304.67708333334</v>
+        <v>46305.67708333334</v>
       </c>
       <c r="B163">
-        <v>523.177</v>
+        <v>226.677</v>
+      </c>
+      <c r="C163">
+        <v>152</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -3637,10 +4306,13 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46304.6875</v>
+        <v>46305.6875</v>
       </c>
       <c r="B164">
-        <v>515.89</v>
+        <v>234.423</v>
+      </c>
+      <c r="C164">
+        <v>181</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -3651,10 +4323,13 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46304.69791666666</v>
+        <v>46305.69791666666</v>
       </c>
       <c r="B165">
-        <v>513.3869999999999</v>
+        <v>245.7</v>
+      </c>
+      <c r="C165">
+        <v>187</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -3665,10 +4340,13 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46304.70833333334</v>
+        <v>46305.70833333334</v>
       </c>
       <c r="B166">
-        <v>532.596</v>
+        <v>284.058</v>
+      </c>
+      <c r="C166">
+        <v>192</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -3679,10 +4357,13 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46304.71875</v>
+        <v>46305.71875</v>
       </c>
       <c r="B167">
-        <v>538.23</v>
+        <v>311.147</v>
+      </c>
+      <c r="C167">
+        <v>202</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -3693,10 +4374,13 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46304.72916666666</v>
+        <v>46305.72916666666</v>
       </c>
       <c r="B168">
-        <v>539.0359999999999</v>
+        <v>316.13</v>
+      </c>
+      <c r="C168">
+        <v>221</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -3707,10 +4391,13 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46304.73958333334</v>
+        <v>46305.73958333334</v>
       </c>
       <c r="B169">
-        <v>543.472</v>
+        <v>346.316</v>
+      </c>
+      <c r="C169">
+        <v>243</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -3721,10 +4408,13 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46304.75</v>
+        <v>46305.75</v>
       </c>
       <c r="B170">
-        <v>583.511</v>
+        <v>384.681</v>
+      </c>
+      <c r="C170">
+        <v>294</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -3735,10 +4425,13 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46304.76041666666</v>
+        <v>46305.76041666666</v>
       </c>
       <c r="B171">
-        <v>588.927</v>
+        <v>413.359</v>
+      </c>
+      <c r="C171">
+        <v>323</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -3749,10 +4442,13 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46304.77083333334</v>
+        <v>46305.77083333334</v>
       </c>
       <c r="B172">
-        <v>595.446</v>
+        <v>443.556</v>
+      </c>
+      <c r="C172">
+        <v>352</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -3763,10 +4459,13 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46304.78125</v>
+        <v>46305.78125</v>
       </c>
       <c r="B173">
-        <v>604.955</v>
+        <v>473.965</v>
+      </c>
+      <c r="C173">
+        <v>393</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -3777,10 +4476,13 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46304.79166666666</v>
+        <v>46305.79166666666</v>
       </c>
       <c r="B174">
-        <v>627.329</v>
+        <v>497.932</v>
+      </c>
+      <c r="C174">
+        <v>443</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -3791,10 +4493,13 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46304.80208333334</v>
+        <v>46305.80208333334</v>
       </c>
       <c r="B175">
-        <v>638.783</v>
+        <v>523.308</v>
+      </c>
+      <c r="C175">
+        <v>479</v>
       </c>
       <c r="D175">
         <v>78</v>
@@ -3805,10 +4510,13 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46304.8125</v>
+        <v>46305.8125</v>
       </c>
       <c r="B176">
-        <v>646.452</v>
+        <v>549.244</v>
+      </c>
+      <c r="C176">
+        <v>504</v>
       </c>
       <c r="D176">
         <v>79</v>
@@ -3819,10 +4527,13 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46304.82291666666</v>
+        <v>46305.82291666666</v>
       </c>
       <c r="B177">
-        <v>648.711</v>
+        <v>575.65</v>
+      </c>
+      <c r="C177">
+        <v>532</v>
       </c>
       <c r="D177">
         <v>80</v>
@@ -3833,10 +4544,13 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46304.83333333334</v>
+        <v>46305.83333333334</v>
       </c>
       <c r="B178">
-        <v>623.946</v>
+        <v>604.275</v>
+      </c>
+      <c r="C178">
+        <v>560</v>
       </c>
       <c r="D178">
         <v>81</v>
@@ -3847,10 +4561,13 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46304.84375</v>
+        <v>46305.84375</v>
       </c>
       <c r="B179">
-        <v>626.621</v>
+        <v>619.7380000000001</v>
+      </c>
+      <c r="C179">
+        <v>563</v>
       </c>
       <c r="D179">
         <v>82</v>
@@ -3861,10 +4578,13 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46304.85416666666</v>
+        <v>46305.85416666666</v>
       </c>
       <c r="B180">
-        <v>630.362</v>
+        <v>682.353</v>
+      </c>
+      <c r="C180">
+        <v>574</v>
       </c>
       <c r="D180">
         <v>83</v>
@@ -3875,10 +4595,13 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46304.86458333334</v>
+        <v>46305.86458333334</v>
       </c>
       <c r="B181">
-        <v>636.141</v>
+        <v>698.789</v>
+      </c>
+      <c r="C181">
+        <v>559</v>
       </c>
       <c r="D181">
         <v>84</v>
@@ -3889,10 +4612,13 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46304.875</v>
+        <v>46305.875</v>
       </c>
       <c r="B182">
-        <v>639.078</v>
+        <v>708.476</v>
+      </c>
+      <c r="C182">
+        <v>538</v>
       </c>
       <c r="D182">
         <v>85</v>
@@ -3903,10 +4629,13 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46304.88541666666</v>
+        <v>46305.88541666666</v>
       </c>
       <c r="B183">
-        <v>651.275</v>
+        <v>714.796</v>
+      </c>
+      <c r="C183">
+        <v>512</v>
       </c>
       <c r="D183">
         <v>86</v>
@@ -3917,10 +4646,13 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46304.89583333334</v>
+        <v>46305.89583333334</v>
       </c>
       <c r="B184">
-        <v>671.658</v>
+        <v>723.729</v>
+      </c>
+      <c r="C184">
+        <v>501</v>
       </c>
       <c r="D184">
         <v>87</v>
@@ -3931,10 +4663,13 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46304.90625</v>
+        <v>46305.90625</v>
       </c>
       <c r="B185">
-        <v>697.634</v>
+        <v>729.989</v>
+      </c>
+      <c r="C185">
+        <v>498</v>
       </c>
       <c r="D185">
         <v>88</v>
@@ -3945,10 +4680,13 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46304.91666666666</v>
+        <v>46305.91666666666</v>
       </c>
       <c r="B186">
-        <v>741.503</v>
+        <v>739.378</v>
+      </c>
+      <c r="C186">
+        <v>504</v>
       </c>
       <c r="D186">
         <v>89</v>
@@ -3959,10 +4697,13 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46304.92708333334</v>
+        <v>46305.92708333334</v>
       </c>
       <c r="B187">
-        <v>765.87</v>
+        <v>738.853</v>
+      </c>
+      <c r="C187">
+        <v>503</v>
       </c>
       <c r="D187">
         <v>90</v>
@@ -3973,10 +4714,13 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46304.9375</v>
+        <v>46305.9375</v>
       </c>
       <c r="B188">
-        <v>792.913</v>
+        <v>737.66</v>
+      </c>
+      <c r="C188">
+        <v>507</v>
       </c>
       <c r="D188">
         <v>91</v>
@@ -3987,16 +4731,3121 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46304.94791666666</v>
+        <v>46305.94791666666</v>
       </c>
       <c r="B189">
-        <v>815.336</v>
+        <v>739.299</v>
+      </c>
+      <c r="C189">
+        <v>513</v>
       </c>
       <c r="D189">
         <v>92</v>
       </c>
       <c r="E189" t="s">
         <v>192</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190" s="2">
+        <v>46305.95833333334</v>
+      </c>
+      <c r="B190">
+        <v>651.223</v>
+      </c>
+      <c r="C190">
+        <v>519</v>
+      </c>
+      <c r="D190">
+        <v>93</v>
+      </c>
+      <c r="E190" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191" s="2">
+        <v>46305.96875</v>
+      </c>
+      <c r="B191">
+        <v>655.569</v>
+      </c>
+      <c r="C191">
+        <v>527</v>
+      </c>
+      <c r="D191">
+        <v>94</v>
+      </c>
+      <c r="E191" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192" s="2">
+        <v>46305.97916666666</v>
+      </c>
+      <c r="B192">
+        <v>653.249</v>
+      </c>
+      <c r="C192">
+        <v>540</v>
+      </c>
+      <c r="D192">
+        <v>95</v>
+      </c>
+      <c r="E192" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193" s="2">
+        <v>46305.98958333334</v>
+      </c>
+      <c r="B193">
+        <v>653.895</v>
+      </c>
+      <c r="C193">
+        <v>548</v>
+      </c>
+      <c r="D193">
+        <v>96</v>
+      </c>
+      <c r="E193" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B194">
+        <v>662.278</v>
+      </c>
+      <c r="C194">
+        <v>572</v>
+      </c>
+      <c r="D194">
+        <v>1</v>
+      </c>
+      <c r="E194" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" s="2">
+        <v>46306.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>665.633</v>
+      </c>
+      <c r="C195">
+        <v>591</v>
+      </c>
+      <c r="D195">
+        <v>2</v>
+      </c>
+      <c r="E195" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" s="2">
+        <v>46306.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>667.9450000000001</v>
+      </c>
+      <c r="C196">
+        <v>587</v>
+      </c>
+      <c r="D196">
+        <v>3</v>
+      </c>
+      <c r="E196" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" s="2">
+        <v>46306.03125</v>
+      </c>
+      <c r="B197">
+        <v>674.16</v>
+      </c>
+      <c r="C197">
+        <v>581</v>
+      </c>
+      <c r="D197">
+        <v>4</v>
+      </c>
+      <c r="E197" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" s="2">
+        <v>46306.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>706.653</v>
+      </c>
+      <c r="C198">
+        <v>603</v>
+      </c>
+      <c r="D198">
+        <v>5</v>
+      </c>
+      <c r="E198" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" s="2">
+        <v>46306.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>708.818</v>
+      </c>
+      <c r="C199">
+        <v>621</v>
+      </c>
+      <c r="D199">
+        <v>6</v>
+      </c>
+      <c r="E199" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" s="2">
+        <v>46306.0625</v>
+      </c>
+      <c r="B200">
+        <v>717.568</v>
+      </c>
+      <c r="C200">
+        <v>627</v>
+      </c>
+      <c r="D200">
+        <v>7</v>
+      </c>
+      <c r="E200" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" s="2">
+        <v>46306.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>734.832</v>
+      </c>
+      <c r="C201">
+        <v>622</v>
+      </c>
+      <c r="D201">
+        <v>8</v>
+      </c>
+      <c r="E201" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" s="2">
+        <v>46306.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>758.2140000000001</v>
+      </c>
+      <c r="C202">
+        <v>611</v>
+      </c>
+      <c r="D202">
+        <v>9</v>
+      </c>
+      <c r="E202" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" s="2">
+        <v>46306.09375</v>
+      </c>
+      <c r="B203">
+        <v>761.558</v>
+      </c>
+      <c r="C203">
+        <v>613</v>
+      </c>
+      <c r="D203">
+        <v>10</v>
+      </c>
+      <c r="E203" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" s="2">
+        <v>46306.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>765.194</v>
+      </c>
+      <c r="C204">
+        <v>620</v>
+      </c>
+      <c r="D204">
+        <v>11</v>
+      </c>
+      <c r="E204" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" s="2">
+        <v>46306.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>765.764</v>
+      </c>
+      <c r="C205">
+        <v>626</v>
+      </c>
+      <c r="D205">
+        <v>12</v>
+      </c>
+      <c r="E205" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" s="2">
+        <v>46306.125</v>
+      </c>
+      <c r="B206">
+        <v>773.215</v>
+      </c>
+      <c r="C206">
+        <v>620</v>
+      </c>
+      <c r="D206">
+        <v>13</v>
+      </c>
+      <c r="E206" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" s="2">
+        <v>46306.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>779.48</v>
+      </c>
+      <c r="C207">
+        <v>642</v>
+      </c>
+      <c r="D207">
+        <v>14</v>
+      </c>
+      <c r="E207" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" s="2">
+        <v>46306.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>786.575</v>
+      </c>
+      <c r="C208">
+        <v>643</v>
+      </c>
+      <c r="D208">
+        <v>15</v>
+      </c>
+      <c r="E208" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" s="2">
+        <v>46306.15625</v>
+      </c>
+      <c r="B209">
+        <v>787.201</v>
+      </c>
+      <c r="C209">
+        <v>646</v>
+      </c>
+      <c r="D209">
+        <v>16</v>
+      </c>
+      <c r="E209" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" s="2">
+        <v>46306.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>814.83</v>
+      </c>
+      <c r="C210">
+        <v>657</v>
+      </c>
+      <c r="D210">
+        <v>17</v>
+      </c>
+      <c r="E210" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" s="2">
+        <v>46306.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>828.806</v>
+      </c>
+      <c r="C211">
+        <v>674</v>
+      </c>
+      <c r="D211">
+        <v>18</v>
+      </c>
+      <c r="E211" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" s="2">
+        <v>46306.1875</v>
+      </c>
+      <c r="B212">
+        <v>845.1180000000001</v>
+      </c>
+      <c r="C212">
+        <v>671</v>
+      </c>
+      <c r="D212">
+        <v>19</v>
+      </c>
+      <c r="E212" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" s="2">
+        <v>46306.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>858.491</v>
+      </c>
+      <c r="C213">
+        <v>667</v>
+      </c>
+      <c r="D213">
+        <v>20</v>
+      </c>
+      <c r="E213" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" s="2">
+        <v>46306.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>881.486</v>
+      </c>
+      <c r="C214">
+        <v>676</v>
+      </c>
+      <c r="D214">
+        <v>21</v>
+      </c>
+      <c r="E214" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" s="2">
+        <v>46306.21875</v>
+      </c>
+      <c r="B215">
+        <v>892.278</v>
+      </c>
+      <c r="C215">
+        <v>686</v>
+      </c>
+      <c r="D215">
+        <v>22</v>
+      </c>
+      <c r="E215" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" s="2">
+        <v>46306.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>900.788</v>
+      </c>
+      <c r="C216">
+        <v>679</v>
+      </c>
+      <c r="D216">
+        <v>23</v>
+      </c>
+      <c r="E216" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" s="2">
+        <v>46306.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>913.038</v>
+      </c>
+      <c r="C217">
+        <v>675</v>
+      </c>
+      <c r="D217">
+        <v>24</v>
+      </c>
+      <c r="E217" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" s="2">
+        <v>46306.25</v>
+      </c>
+      <c r="B218">
+        <v>933.066</v>
+      </c>
+      <c r="C218">
+        <v>666</v>
+      </c>
+      <c r="D218">
+        <v>25</v>
+      </c>
+      <c r="E218" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" s="2">
+        <v>46306.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>941.24</v>
+      </c>
+      <c r="C219">
+        <v>658</v>
+      </c>
+      <c r="D219">
+        <v>26</v>
+      </c>
+      <c r="E219" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" s="2">
+        <v>46306.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>952.053</v>
+      </c>
+      <c r="C220">
+        <v>656</v>
+      </c>
+      <c r="D220">
+        <v>27</v>
+      </c>
+      <c r="E220" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" s="2">
+        <v>46306.28125</v>
+      </c>
+      <c r="B221">
+        <v>969.021</v>
+      </c>
+      <c r="C221">
+        <v>664</v>
+      </c>
+      <c r="D221">
+        <v>28</v>
+      </c>
+      <c r="E221" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" s="2">
+        <v>46306.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>983.631</v>
+      </c>
+      <c r="C222">
+        <v>675</v>
+      </c>
+      <c r="D222">
+        <v>29</v>
+      </c>
+      <c r="E222" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" s="2">
+        <v>46306.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>986.347</v>
+      </c>
+      <c r="C223">
+        <v>689</v>
+      </c>
+      <c r="D223">
+        <v>30</v>
+      </c>
+      <c r="E223" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" s="2">
+        <v>46306.3125</v>
+      </c>
+      <c r="B224">
+        <v>992.131</v>
+      </c>
+      <c r="C224">
+        <v>726</v>
+      </c>
+      <c r="D224">
+        <v>31</v>
+      </c>
+      <c r="E224" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225" s="2">
+        <v>46306.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>992.386</v>
+      </c>
+      <c r="C225">
+        <v>781</v>
+      </c>
+      <c r="D225">
+        <v>32</v>
+      </c>
+      <c r="E225" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226" s="2">
+        <v>46306.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>978.59</v>
+      </c>
+      <c r="C226">
+        <v>770</v>
+      </c>
+      <c r="D226">
+        <v>33</v>
+      </c>
+      <c r="E226" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227" s="2">
+        <v>46306.34375</v>
+      </c>
+      <c r="B227">
+        <v>978.702</v>
+      </c>
+      <c r="C227">
+        <v>743</v>
+      </c>
+      <c r="D227">
+        <v>34</v>
+      </c>
+      <c r="E227" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228" s="2">
+        <v>46306.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>989.15</v>
+      </c>
+      <c r="C228">
+        <v>711</v>
+      </c>
+      <c r="D228">
+        <v>35</v>
+      </c>
+      <c r="E228" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229" s="2">
+        <v>46306.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>984.609</v>
+      </c>
+      <c r="C229">
+        <v>734</v>
+      </c>
+      <c r="D229">
+        <v>36</v>
+      </c>
+      <c r="E229" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230" s="2">
+        <v>46306.375</v>
+      </c>
+      <c r="B230">
+        <v>1014.251</v>
+      </c>
+      <c r="C230">
+        <v>774</v>
+      </c>
+      <c r="D230">
+        <v>37</v>
+      </c>
+      <c r="E230" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" s="2">
+        <v>46306.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>1050.745</v>
+      </c>
+      <c r="C231">
+        <v>863</v>
+      </c>
+      <c r="D231">
+        <v>38</v>
+      </c>
+      <c r="E231" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" s="2">
+        <v>46306.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>1086.144</v>
+      </c>
+      <c r="C232">
+        <v>999</v>
+      </c>
+      <c r="D232">
+        <v>39</v>
+      </c>
+      <c r="E232" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" s="2">
+        <v>46306.40625</v>
+      </c>
+      <c r="B233">
+        <v>1118.69</v>
+      </c>
+      <c r="C233">
+        <v>1164</v>
+      </c>
+      <c r="D233">
+        <v>40</v>
+      </c>
+      <c r="E233" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" s="2">
+        <v>46306.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>1152.684</v>
+      </c>
+      <c r="C234">
+        <v>1346</v>
+      </c>
+      <c r="D234">
+        <v>41</v>
+      </c>
+      <c r="E234" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235" s="2">
+        <v>46306.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>1208.761</v>
+      </c>
+      <c r="C235">
+        <v>1514</v>
+      </c>
+      <c r="D235">
+        <v>42</v>
+      </c>
+      <c r="E235" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" s="2">
+        <v>46306.4375</v>
+      </c>
+      <c r="B236">
+        <v>1268.134</v>
+      </c>
+      <c r="C236">
+        <v>1614</v>
+      </c>
+      <c r="D236">
+        <v>43</v>
+      </c>
+      <c r="E236" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" s="2">
+        <v>46306.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>1326.226</v>
+      </c>
+      <c r="C237">
+        <v>1700</v>
+      </c>
+      <c r="D237">
+        <v>44</v>
+      </c>
+      <c r="E237" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" s="2">
+        <v>46306.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>1497.776</v>
+      </c>
+      <c r="C238">
+        <v>1773</v>
+      </c>
+      <c r="D238">
+        <v>45</v>
+      </c>
+      <c r="E238" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239" s="2">
+        <v>46306.46875</v>
+      </c>
+      <c r="B239">
+        <v>1541.019</v>
+      </c>
+      <c r="C239">
+        <v>1835</v>
+      </c>
+      <c r="D239">
+        <v>46</v>
+      </c>
+      <c r="E239" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" s="2">
+        <v>46306.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>1581.939</v>
+      </c>
+      <c r="C240">
+        <v>1833</v>
+      </c>
+      <c r="D240">
+        <v>47</v>
+      </c>
+      <c r="E240" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" s="2">
+        <v>46306.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>1621.475</v>
+      </c>
+      <c r="C241">
+        <v>1857</v>
+      </c>
+      <c r="D241">
+        <v>48</v>
+      </c>
+      <c r="E241" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" s="2">
+        <v>46306.5</v>
+      </c>
+      <c r="B242">
+        <v>1679.03</v>
+      </c>
+      <c r="C242">
+        <v>1890</v>
+      </c>
+      <c r="D242">
+        <v>49</v>
+      </c>
+      <c r="E242" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" s="2">
+        <v>46306.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>1705.103</v>
+      </c>
+      <c r="C243">
+        <v>1922</v>
+      </c>
+      <c r="D243">
+        <v>50</v>
+      </c>
+      <c r="E243" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" s="2">
+        <v>46306.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>1729.292</v>
+      </c>
+      <c r="C244">
+        <v>1939</v>
+      </c>
+      <c r="D244">
+        <v>51</v>
+      </c>
+      <c r="E244" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" s="2">
+        <v>46306.53125</v>
+      </c>
+      <c r="B245">
+        <v>1754.981</v>
+      </c>
+      <c r="C245">
+        <v>1945</v>
+      </c>
+      <c r="D245">
+        <v>52</v>
+      </c>
+      <c r="E245" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" s="2">
+        <v>46306.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>1806.974</v>
+      </c>
+      <c r="C246">
+        <v>1976</v>
+      </c>
+      <c r="D246">
+        <v>53</v>
+      </c>
+      <c r="E246" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" s="2">
+        <v>46306.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>1829.23</v>
+      </c>
+      <c r="C247">
+        <v>2039</v>
+      </c>
+      <c r="D247">
+        <v>54</v>
+      </c>
+      <c r="E247" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" s="2">
+        <v>46306.5625</v>
+      </c>
+      <c r="B248">
+        <v>1849.701</v>
+      </c>
+      <c r="C248">
+        <v>2086</v>
+      </c>
+      <c r="D248">
+        <v>55</v>
+      </c>
+      <c r="E248" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" s="2">
+        <v>46306.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>1865.871</v>
+      </c>
+      <c r="C249">
+        <v>2106</v>
+      </c>
+      <c r="D249">
+        <v>56</v>
+      </c>
+      <c r="E249" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" s="2">
+        <v>46306.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>1892.95</v>
+      </c>
+      <c r="C250">
+        <v>2148</v>
+      </c>
+      <c r="D250">
+        <v>57</v>
+      </c>
+      <c r="E250" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251" s="2">
+        <v>46306.59375</v>
+      </c>
+      <c r="B251">
+        <v>1896.695</v>
+      </c>
+      <c r="C251">
+        <v>2117</v>
+      </c>
+      <c r="D251">
+        <v>58</v>
+      </c>
+      <c r="E251" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252" s="2">
+        <v>46306.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>1897.64</v>
+      </c>
+      <c r="C252">
+        <v>2092</v>
+      </c>
+      <c r="D252">
+        <v>59</v>
+      </c>
+      <c r="E252" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253" s="2">
+        <v>46306.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>1899.213</v>
+      </c>
+      <c r="C253">
+        <v>2085</v>
+      </c>
+      <c r="D253">
+        <v>60</v>
+      </c>
+      <c r="E253" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254" s="2">
+        <v>46306.625</v>
+      </c>
+      <c r="B254">
+        <v>1913.743</v>
+      </c>
+      <c r="C254">
+        <v>2054</v>
+      </c>
+      <c r="D254">
+        <v>61</v>
+      </c>
+      <c r="E254" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255" s="2">
+        <v>46306.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>1899.866</v>
+      </c>
+      <c r="C255">
+        <v>2026</v>
+      </c>
+      <c r="D255">
+        <v>62</v>
+      </c>
+      <c r="E255" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256" s="2">
+        <v>46306.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>1885.092</v>
+      </c>
+      <c r="C256">
+        <v>1992</v>
+      </c>
+      <c r="D256">
+        <v>63</v>
+      </c>
+      <c r="E256" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257" s="2">
+        <v>46306.65625</v>
+      </c>
+      <c r="B257">
+        <v>1871.838</v>
+      </c>
+      <c r="C257">
+        <v>1979</v>
+      </c>
+      <c r="D257">
+        <v>64</v>
+      </c>
+      <c r="E257" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258" s="2">
+        <v>46306.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>1872.744</v>
+      </c>
+      <c r="C258">
+        <v>1998</v>
+      </c>
+      <c r="D258">
+        <v>65</v>
+      </c>
+      <c r="E258" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259" s="2">
+        <v>46306.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>1858.482</v>
+      </c>
+      <c r="C259">
+        <v>2047</v>
+      </c>
+      <c r="D259">
+        <v>66</v>
+      </c>
+      <c r="E259" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260" s="2">
+        <v>46306.6875</v>
+      </c>
+      <c r="B260">
+        <v>1847.646</v>
+      </c>
+      <c r="C260">
+        <v>2069</v>
+      </c>
+      <c r="D260">
+        <v>67</v>
+      </c>
+      <c r="E260" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261" s="2">
+        <v>46306.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>1838.213</v>
+      </c>
+      <c r="C261">
+        <v>2114</v>
+      </c>
+      <c r="D261">
+        <v>68</v>
+      </c>
+      <c r="E261" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262" s="2">
+        <v>46306.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>1846.522</v>
+      </c>
+      <c r="C262">
+        <v>2104</v>
+      </c>
+      <c r="D262">
+        <v>69</v>
+      </c>
+      <c r="E262" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263" s="2">
+        <v>46306.71875</v>
+      </c>
+      <c r="B263">
+        <v>1850.804</v>
+      </c>
+      <c r="C263">
+        <v>2103</v>
+      </c>
+      <c r="D263">
+        <v>70</v>
+      </c>
+      <c r="E263" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264" s="2">
+        <v>46306.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>1858.041</v>
+      </c>
+      <c r="C264">
+        <v>2076</v>
+      </c>
+      <c r="D264">
+        <v>71</v>
+      </c>
+      <c r="E264" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265" s="2">
+        <v>46306.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>1866.884</v>
+      </c>
+      <c r="C265">
+        <v>2069</v>
+      </c>
+      <c r="D265">
+        <v>72</v>
+      </c>
+      <c r="E265" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="A266" s="2">
+        <v>46306.75</v>
+      </c>
+      <c r="B266">
+        <v>1778.625</v>
+      </c>
+      <c r="C266">
+        <v>2047</v>
+      </c>
+      <c r="D266">
+        <v>73</v>
+      </c>
+      <c r="E266" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267" s="2">
+        <v>46306.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>1776.598</v>
+      </c>
+      <c r="C267">
+        <v>2050</v>
+      </c>
+      <c r="D267">
+        <v>74</v>
+      </c>
+      <c r="E267" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268" s="2">
+        <v>46306.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>1771.185</v>
+      </c>
+      <c r="C268">
+        <v>2080</v>
+      </c>
+      <c r="D268">
+        <v>75</v>
+      </c>
+      <c r="E268" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269" s="2">
+        <v>46306.78125</v>
+      </c>
+      <c r="B269">
+        <v>1764.383</v>
+      </c>
+      <c r="C269">
+        <v>2104</v>
+      </c>
+      <c r="D269">
+        <v>76</v>
+      </c>
+      <c r="E269" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270" s="2">
+        <v>46306.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>1748.166</v>
+      </c>
+      <c r="C270">
+        <v>2116</v>
+      </c>
+      <c r="D270">
+        <v>77</v>
+      </c>
+      <c r="E270" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271" s="2">
+        <v>46306.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>1725.905</v>
+      </c>
+      <c r="C271">
+        <v>2110</v>
+      </c>
+      <c r="D271">
+        <v>78</v>
+      </c>
+      <c r="E271" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272" s="2">
+        <v>46306.8125</v>
+      </c>
+      <c r="B272">
+        <v>1699.817</v>
+      </c>
+      <c r="C272">
+        <v>2051</v>
+      </c>
+      <c r="D272">
+        <v>79</v>
+      </c>
+      <c r="E272" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5">
+      <c r="A273" s="2">
+        <v>46306.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>1675.697</v>
+      </c>
+      <c r="C273">
+        <v>1984</v>
+      </c>
+      <c r="D273">
+        <v>80</v>
+      </c>
+      <c r="E273" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5">
+      <c r="A274" s="2">
+        <v>46306.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>1641.994</v>
+      </c>
+      <c r="C274">
+        <v>1950</v>
+      </c>
+      <c r="D274">
+        <v>81</v>
+      </c>
+      <c r="E274" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5">
+      <c r="A275" s="2">
+        <v>46306.84375</v>
+      </c>
+      <c r="B275">
+        <v>1611.67</v>
+      </c>
+      <c r="C275">
+        <v>1865</v>
+      </c>
+      <c r="D275">
+        <v>82</v>
+      </c>
+      <c r="E275" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5">
+      <c r="A276" s="2">
+        <v>46306.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>1580.407</v>
+      </c>
+      <c r="C276">
+        <v>1780</v>
+      </c>
+      <c r="D276">
+        <v>83</v>
+      </c>
+      <c r="E276" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5">
+      <c r="A277" s="2">
+        <v>46306.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>1547.495</v>
+      </c>
+      <c r="C277">
+        <v>1684</v>
+      </c>
+      <c r="D277">
+        <v>84</v>
+      </c>
+      <c r="E277" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5">
+      <c r="A278" s="2">
+        <v>46306.875</v>
+      </c>
+      <c r="B278">
+        <v>1505.131</v>
+      </c>
+      <c r="C278">
+        <v>1617</v>
+      </c>
+      <c r="D278">
+        <v>85</v>
+      </c>
+      <c r="E278" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5">
+      <c r="A279" s="2">
+        <v>46306.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>1462.512</v>
+      </c>
+      <c r="C279">
+        <v>1591</v>
+      </c>
+      <c r="D279">
+        <v>86</v>
+      </c>
+      <c r="E279" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5">
+      <c r="A280" s="2">
+        <v>46306.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>1419.672</v>
+      </c>
+      <c r="C280">
+        <v>1549</v>
+      </c>
+      <c r="D280">
+        <v>87</v>
+      </c>
+      <c r="E280" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5">
+      <c r="A281" s="2">
+        <v>46306.90625</v>
+      </c>
+      <c r="B281">
+        <v>1378.34</v>
+      </c>
+      <c r="C281">
+        <v>1510</v>
+      </c>
+      <c r="D281">
+        <v>88</v>
+      </c>
+      <c r="E281" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5">
+      <c r="A282" s="2">
+        <v>46306.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>1329.066</v>
+      </c>
+      <c r="C282">
+        <v>1477</v>
+      </c>
+      <c r="D282">
+        <v>89</v>
+      </c>
+      <c r="E282" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5">
+      <c r="A283" s="2">
+        <v>46306.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>1289.83</v>
+      </c>
+      <c r="C283">
+        <v>1431</v>
+      </c>
+      <c r="D283">
+        <v>90</v>
+      </c>
+      <c r="E283" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5">
+      <c r="A284" s="2">
+        <v>46306.9375</v>
+      </c>
+      <c r="B284">
+        <v>1251.489</v>
+      </c>
+      <c r="C284">
+        <v>1359</v>
+      </c>
+      <c r="D284">
+        <v>91</v>
+      </c>
+      <c r="E284" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5">
+      <c r="A285" s="2">
+        <v>46306.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>1211.828</v>
+      </c>
+      <c r="C285">
+        <v>1256</v>
+      </c>
+      <c r="D285">
+        <v>92</v>
+      </c>
+      <c r="E285" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5">
+      <c r="A286" s="2">
+        <v>46306.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>1177.825</v>
+      </c>
+      <c r="C286">
+        <v>1164</v>
+      </c>
+      <c r="D286">
+        <v>93</v>
+      </c>
+      <c r="E286" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5">
+      <c r="A287" s="2">
+        <v>46306.96875</v>
+      </c>
+      <c r="B287">
+        <v>1151.034</v>
+      </c>
+      <c r="C287">
+        <v>1068</v>
+      </c>
+      <c r="D287">
+        <v>94</v>
+      </c>
+      <c r="E287" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5">
+      <c r="A288" s="2">
+        <v>46306.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>1111.104</v>
+      </c>
+      <c r="C288">
+        <v>951</v>
+      </c>
+      <c r="D288">
+        <v>95</v>
+      </c>
+      <c r="E288" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5">
+      <c r="A289" s="2">
+        <v>46306.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>1055.66</v>
+      </c>
+      <c r="C289">
+        <v>843</v>
+      </c>
+      <c r="D289">
+        <v>96</v>
+      </c>
+      <c r="E289" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B290">
+        <v>935.28</v>
+      </c>
+      <c r="C290">
+        <v>758</v>
+      </c>
+      <c r="D290">
+        <v>1</v>
+      </c>
+      <c r="E290" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291" s="2">
+        <v>46307.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>897.212</v>
+      </c>
+      <c r="C291">
+        <v>726</v>
+      </c>
+      <c r="D291">
+        <v>2</v>
+      </c>
+      <c r="E291" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292" s="2">
+        <v>46307.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>860.513</v>
+      </c>
+      <c r="C292">
+        <v>726</v>
+      </c>
+      <c r="D292">
+        <v>3</v>
+      </c>
+      <c r="E292" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" s="2">
+        <v>46307.03125</v>
+      </c>
+      <c r="B293">
+        <v>808.576</v>
+      </c>
+      <c r="C293">
+        <v>728</v>
+      </c>
+      <c r="D293">
+        <v>4</v>
+      </c>
+      <c r="E293" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294" s="2">
+        <v>46307.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>723.9589999999999</v>
+      </c>
+      <c r="C294">
+        <v>712</v>
+      </c>
+      <c r="D294">
+        <v>5</v>
+      </c>
+      <c r="E294" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295" s="2">
+        <v>46307.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>694.572</v>
+      </c>
+      <c r="C295">
+        <v>737</v>
+      </c>
+      <c r="D295">
+        <v>6</v>
+      </c>
+      <c r="E295" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296" s="2">
+        <v>46307.0625</v>
+      </c>
+      <c r="B296">
+        <v>665.443</v>
+      </c>
+      <c r="C296">
+        <v>731</v>
+      </c>
+      <c r="D296">
+        <v>7</v>
+      </c>
+      <c r="E296" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297" s="2">
+        <v>46307.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>628.763</v>
+      </c>
+      <c r="C297">
+        <v>727</v>
+      </c>
+      <c r="D297">
+        <v>8</v>
+      </c>
+      <c r="E297" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="A298" s="2">
+        <v>46307.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>608.696</v>
+      </c>
+      <c r="C298">
+        <v>708</v>
+      </c>
+      <c r="D298">
+        <v>9</v>
+      </c>
+      <c r="E298" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="A299" s="2">
+        <v>46307.09375</v>
+      </c>
+      <c r="B299">
+        <v>596.585</v>
+      </c>
+      <c r="C299">
+        <v>712</v>
+      </c>
+      <c r="D299">
+        <v>10</v>
+      </c>
+      <c r="E299" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300" s="2">
+        <v>46307.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>582.4829999999999</v>
+      </c>
+      <c r="C300">
+        <v>727</v>
+      </c>
+      <c r="D300">
+        <v>11</v>
+      </c>
+      <c r="E300" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5">
+      <c r="A301" s="2">
+        <v>46307.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>574.008</v>
+      </c>
+      <c r="C301">
+        <v>728</v>
+      </c>
+      <c r="D301">
+        <v>12</v>
+      </c>
+      <c r="E301" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5">
+      <c r="A302" s="2">
+        <v>46307.125</v>
+      </c>
+      <c r="B302">
+        <v>586.0309999999999</v>
+      </c>
+      <c r="C302">
+        <v>768</v>
+      </c>
+      <c r="D302">
+        <v>13</v>
+      </c>
+      <c r="E302" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303" s="2">
+        <v>46307.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>583.832</v>
+      </c>
+      <c r="C303">
+        <v>883</v>
+      </c>
+      <c r="D303">
+        <v>14</v>
+      </c>
+      <c r="E303" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304" s="2">
+        <v>46307.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>589.158</v>
+      </c>
+      <c r="C304">
+        <v>1053</v>
+      </c>
+      <c r="D304">
+        <v>15</v>
+      </c>
+      <c r="E304" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305" s="2">
+        <v>46307.15625</v>
+      </c>
+      <c r="B305">
+        <v>595.721</v>
+      </c>
+      <c r="C305">
+        <v>1216</v>
+      </c>
+      <c r="D305">
+        <v>16</v>
+      </c>
+      <c r="E305" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306" s="2">
+        <v>46307.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>620.583</v>
+      </c>
+      <c r="C306">
+        <v>1241</v>
+      </c>
+      <c r="D306">
+        <v>17</v>
+      </c>
+      <c r="E306" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307" s="2">
+        <v>46307.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>636.164</v>
+      </c>
+      <c r="C307">
+        <v>1139</v>
+      </c>
+      <c r="D307">
+        <v>18</v>
+      </c>
+      <c r="E307" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308" s="2">
+        <v>46307.1875</v>
+      </c>
+      <c r="B308">
+        <v>657.821</v>
+      </c>
+      <c r="C308">
+        <v>1188</v>
+      </c>
+      <c r="D308">
+        <v>19</v>
+      </c>
+      <c r="E308" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309" s="2">
+        <v>46307.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>678.283</v>
+      </c>
+      <c r="C309">
+        <v>1191</v>
+      </c>
+      <c r="D309">
+        <v>20</v>
+      </c>
+      <c r="E309" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310" s="2">
+        <v>46307.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>746.412</v>
+      </c>
+      <c r="C310">
+        <v>1416</v>
+      </c>
+      <c r="D310">
+        <v>21</v>
+      </c>
+      <c r="E310" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" s="2">
+        <v>46307.21875</v>
+      </c>
+      <c r="B311">
+        <v>778.248</v>
+      </c>
+      <c r="C311">
+        <v>1507</v>
+      </c>
+      <c r="D311">
+        <v>22</v>
+      </c>
+      <c r="E311" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" s="2">
+        <v>46307.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>787.473</v>
+      </c>
+      <c r="C312">
+        <v>1462</v>
+      </c>
+      <c r="D312">
+        <v>23</v>
+      </c>
+      <c r="E312" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313" s="2">
+        <v>46307.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>817.22</v>
+      </c>
+      <c r="C313">
+        <v>1377</v>
+      </c>
+      <c r="D313">
+        <v>24</v>
+      </c>
+      <c r="E313" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" s="2">
+        <v>46307.25</v>
+      </c>
+      <c r="B314">
+        <v>789.324</v>
+      </c>
+      <c r="C314">
+        <v>1241</v>
+      </c>
+      <c r="D314">
+        <v>25</v>
+      </c>
+      <c r="E314" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" s="2">
+        <v>46307.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>809.117</v>
+      </c>
+      <c r="C315">
+        <v>1102</v>
+      </c>
+      <c r="D315">
+        <v>26</v>
+      </c>
+      <c r="E315" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" s="2">
+        <v>46307.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>817.35</v>
+      </c>
+      <c r="C316">
+        <v>1014</v>
+      </c>
+      <c r="D316">
+        <v>27</v>
+      </c>
+      <c r="E316" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317" s="2">
+        <v>46307.28125</v>
+      </c>
+      <c r="B317">
+        <v>831.064</v>
+      </c>
+      <c r="C317">
+        <v>888</v>
+      </c>
+      <c r="D317">
+        <v>28</v>
+      </c>
+      <c r="E317" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318" s="2">
+        <v>46307.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>915.611</v>
+      </c>
+      <c r="C318">
+        <v>775</v>
+      </c>
+      <c r="D318">
+        <v>29</v>
+      </c>
+      <c r="E318" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319" s="2">
+        <v>46307.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>913.2140000000001</v>
+      </c>
+      <c r="C319">
+        <v>662</v>
+      </c>
+      <c r="D319">
+        <v>30</v>
+      </c>
+      <c r="E319" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320" s="2">
+        <v>46307.3125</v>
+      </c>
+      <c r="B320">
+        <v>914.5</v>
+      </c>
+      <c r="C320">
+        <v>598</v>
+      </c>
+      <c r="D320">
+        <v>31</v>
+      </c>
+      <c r="E320" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5">
+      <c r="A321" s="2">
+        <v>46307.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>917.663</v>
+      </c>
+      <c r="C321">
+        <v>568</v>
+      </c>
+      <c r="D321">
+        <v>32</v>
+      </c>
+      <c r="E321" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5">
+      <c r="A322" s="2">
+        <v>46307.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>802.996</v>
+      </c>
+      <c r="C322">
+        <v>558</v>
+      </c>
+      <c r="D322">
+        <v>33</v>
+      </c>
+      <c r="E322" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5">
+      <c r="A323" s="2">
+        <v>46307.34375</v>
+      </c>
+      <c r="B323">
+        <v>809.417</v>
+      </c>
+      <c r="C323">
+        <v>560</v>
+      </c>
+      <c r="D323">
+        <v>34</v>
+      </c>
+      <c r="E323" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5">
+      <c r="A324" s="2">
+        <v>46307.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>816.022</v>
+      </c>
+      <c r="C324">
+        <v>567</v>
+      </c>
+      <c r="D324">
+        <v>35</v>
+      </c>
+      <c r="E324" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5">
+      <c r="A325" s="2">
+        <v>46307.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>822.0890000000001</v>
+      </c>
+      <c r="C325">
+        <v>580</v>
+      </c>
+      <c r="D325">
+        <v>36</v>
+      </c>
+      <c r="E325" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5">
+      <c r="A326" s="2">
+        <v>46307.375</v>
+      </c>
+      <c r="B326">
+        <v>795.671</v>
+      </c>
+      <c r="C326">
+        <v>602</v>
+      </c>
+      <c r="D326">
+        <v>37</v>
+      </c>
+      <c r="E326" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5">
+      <c r="A327" s="2">
+        <v>46307.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>800.687</v>
+      </c>
+      <c r="C327">
+        <v>639</v>
+      </c>
+      <c r="D327">
+        <v>38</v>
+      </c>
+      <c r="E327" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5">
+      <c r="A328" s="2">
+        <v>46307.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>807.314</v>
+      </c>
+      <c r="D328">
+        <v>39</v>
+      </c>
+      <c r="E328" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5">
+      <c r="A329" s="2">
+        <v>46307.40625</v>
+      </c>
+      <c r="B329">
+        <v>813.246</v>
+      </c>
+      <c r="D329">
+        <v>40</v>
+      </c>
+      <c r="E329" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5">
+      <c r="A330" s="2">
+        <v>46307.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>850.569</v>
+      </c>
+      <c r="D330">
+        <v>41</v>
+      </c>
+      <c r="E330" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5">
+      <c r="A331" s="2">
+        <v>46307.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>857.36</v>
+      </c>
+      <c r="D331">
+        <v>42</v>
+      </c>
+      <c r="E331" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5">
+      <c r="A332" s="2">
+        <v>46307.4375</v>
+      </c>
+      <c r="B332">
+        <v>864.919</v>
+      </c>
+      <c r="D332">
+        <v>43</v>
+      </c>
+      <c r="E332" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5">
+      <c r="A333" s="2">
+        <v>46307.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>872.048</v>
+      </c>
+      <c r="D333">
+        <v>44</v>
+      </c>
+      <c r="E333" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5">
+      <c r="A334" s="2">
+        <v>46307.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>894.274</v>
+      </c>
+      <c r="D334">
+        <v>45</v>
+      </c>
+      <c r="E334" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5">
+      <c r="A335" s="2">
+        <v>46307.46875</v>
+      </c>
+      <c r="B335">
+        <v>899.135</v>
+      </c>
+      <c r="D335">
+        <v>46</v>
+      </c>
+      <c r="E335" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5">
+      <c r="A336" s="2">
+        <v>46307.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>904.255</v>
+      </c>
+      <c r="D336">
+        <v>47</v>
+      </c>
+      <c r="E336" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5">
+      <c r="A337" s="2">
+        <v>46307.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>908.457</v>
+      </c>
+      <c r="D337">
+        <v>48</v>
+      </c>
+      <c r="E337" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5">
+      <c r="A338" s="2">
+        <v>46307.5</v>
+      </c>
+      <c r="B338">
+        <v>922.9299999999999</v>
+      </c>
+      <c r="D338">
+        <v>49</v>
+      </c>
+      <c r="E338" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5">
+      <c r="A339" s="2">
+        <v>46307.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>928.495</v>
+      </c>
+      <c r="D339">
+        <v>50</v>
+      </c>
+      <c r="E339" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5">
+      <c r="A340" s="2">
+        <v>46307.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>931.785</v>
+      </c>
+      <c r="D340">
+        <v>51</v>
+      </c>
+      <c r="E340" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5">
+      <c r="A341" s="2">
+        <v>46307.53125</v>
+      </c>
+      <c r="B341">
+        <v>935.991</v>
+      </c>
+      <c r="D341">
+        <v>52</v>
+      </c>
+      <c r="E341" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5">
+      <c r="A342" s="2">
+        <v>46307.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>957.833</v>
+      </c>
+      <c r="D342">
+        <v>53</v>
+      </c>
+      <c r="E342" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5">
+      <c r="A343" s="2">
+        <v>46307.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>967.715</v>
+      </c>
+      <c r="D343">
+        <v>54</v>
+      </c>
+      <c r="E343" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5">
+      <c r="A344" s="2">
+        <v>46307.5625</v>
+      </c>
+      <c r="B344">
+        <v>979.6180000000001</v>
+      </c>
+      <c r="D344">
+        <v>55</v>
+      </c>
+      <c r="E344" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5">
+      <c r="A345" s="2">
+        <v>46307.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>988.706</v>
+      </c>
+      <c r="D345">
+        <v>56</v>
+      </c>
+      <c r="E345" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5">
+      <c r="A346" s="2">
+        <v>46307.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>1026.044</v>
+      </c>
+      <c r="D346">
+        <v>57</v>
+      </c>
+      <c r="E346" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5">
+      <c r="A347" s="2">
+        <v>46307.59375</v>
+      </c>
+      <c r="B347">
+        <v>1044.331</v>
+      </c>
+      <c r="D347">
+        <v>58</v>
+      </c>
+      <c r="E347" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5">
+      <c r="A348" s="2">
+        <v>46307.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>1063.788</v>
+      </c>
+      <c r="D348">
+        <v>59</v>
+      </c>
+      <c r="E348" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5">
+      <c r="A349" s="2">
+        <v>46307.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>1084.793</v>
+      </c>
+      <c r="D349">
+        <v>60</v>
+      </c>
+      <c r="E349" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5">
+      <c r="A350" s="2">
+        <v>46307.625</v>
+      </c>
+      <c r="B350">
+        <v>1125.224</v>
+      </c>
+      <c r="D350">
+        <v>61</v>
+      </c>
+      <c r="E350" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5">
+      <c r="A351" s="2">
+        <v>46307.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>1148.403</v>
+      </c>
+      <c r="D351">
+        <v>62</v>
+      </c>
+      <c r="E351" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5">
+      <c r="A352" s="2">
+        <v>46307.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>1171.189</v>
+      </c>
+      <c r="D352">
+        <v>63</v>
+      </c>
+      <c r="E352" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5">
+      <c r="A353" s="2">
+        <v>46307.65625</v>
+      </c>
+      <c r="B353">
+        <v>1194.605</v>
+      </c>
+      <c r="D353">
+        <v>64</v>
+      </c>
+      <c r="E353" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5">
+      <c r="A354" s="2">
+        <v>46307.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>1234.616</v>
+      </c>
+      <c r="D354">
+        <v>65</v>
+      </c>
+      <c r="E354" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5">
+      <c r="A355" s="2">
+        <v>46307.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>1264.756</v>
+      </c>
+      <c r="D355">
+        <v>66</v>
+      </c>
+      <c r="E355" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5">
+      <c r="A356" s="2">
+        <v>46307.6875</v>
+      </c>
+      <c r="B356">
+        <v>1294.29</v>
+      </c>
+      <c r="D356">
+        <v>67</v>
+      </c>
+      <c r="E356" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5">
+      <c r="A357" s="2">
+        <v>46307.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>1324.912</v>
+      </c>
+      <c r="D357">
+        <v>68</v>
+      </c>
+      <c r="E357" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5">
+      <c r="A358" s="2">
+        <v>46307.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>1361.38</v>
+      </c>
+      <c r="D358">
+        <v>69</v>
+      </c>
+      <c r="E358" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5">
+      <c r="A359" s="2">
+        <v>46307.71875</v>
+      </c>
+      <c r="B359">
+        <v>1396.876</v>
+      </c>
+      <c r="D359">
+        <v>70</v>
+      </c>
+      <c r="E359" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5">
+      <c r="A360" s="2">
+        <v>46307.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>1431.895</v>
+      </c>
+      <c r="D360">
+        <v>71</v>
+      </c>
+      <c r="E360" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5">
+      <c r="A361" s="2">
+        <v>46307.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>1468.284</v>
+      </c>
+      <c r="D361">
+        <v>72</v>
+      </c>
+      <c r="E361" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5">
+      <c r="A362" s="2">
+        <v>46307.75</v>
+      </c>
+      <c r="B362">
+        <v>1515.371</v>
+      </c>
+      <c r="D362">
+        <v>73</v>
+      </c>
+      <c r="E362" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5">
+      <c r="A363" s="2">
+        <v>46307.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>1546.394</v>
+      </c>
+      <c r="D363">
+        <v>74</v>
+      </c>
+      <c r="E363" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5">
+      <c r="A364" s="2">
+        <v>46307.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>1578.46</v>
+      </c>
+      <c r="D364">
+        <v>75</v>
+      </c>
+      <c r="E364" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5">
+      <c r="A365" s="2">
+        <v>46307.78125</v>
+      </c>
+      <c r="B365">
+        <v>1609.067</v>
+      </c>
+      <c r="D365">
+        <v>76</v>
+      </c>
+      <c r="E365" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5">
+      <c r="A366" s="2">
+        <v>46307.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>1641.225</v>
+      </c>
+      <c r="D366">
+        <v>77</v>
+      </c>
+      <c r="E366" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5">
+      <c r="A367" s="2">
+        <v>46307.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>1669.41</v>
+      </c>
+      <c r="D367">
+        <v>78</v>
+      </c>
+      <c r="E367" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5">
+      <c r="A368" s="2">
+        <v>46307.8125</v>
+      </c>
+      <c r="B368">
+        <v>1698.167</v>
+      </c>
+      <c r="D368">
+        <v>79</v>
+      </c>
+      <c r="E368" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5">
+      <c r="A369" s="2">
+        <v>46307.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>1724.591</v>
+      </c>
+      <c r="D369">
+        <v>80</v>
+      </c>
+      <c r="E369" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5">
+      <c r="A370" s="2">
+        <v>46307.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>1754.13</v>
+      </c>
+      <c r="D370">
+        <v>81</v>
+      </c>
+      <c r="E370" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5">
+      <c r="A371" s="2">
+        <v>46307.84375</v>
+      </c>
+      <c r="B371">
+        <v>1770.683</v>
+      </c>
+      <c r="D371">
+        <v>82</v>
+      </c>
+      <c r="E371" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5">
+      <c r="A372" s="2">
+        <v>46307.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>1787.49</v>
+      </c>
+      <c r="D372">
+        <v>83</v>
+      </c>
+      <c r="E372" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5">
+      <c r="A373" s="2">
+        <v>46307.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>1799.805</v>
+      </c>
+      <c r="D373">
+        <v>84</v>
+      </c>
+      <c r="E373" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5">
+      <c r="A374" s="2">
+        <v>46307.875</v>
+      </c>
+      <c r="B374">
+        <v>1809.15</v>
+      </c>
+      <c r="D374">
+        <v>85</v>
+      </c>
+      <c r="E374" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5">
+      <c r="A375" s="2">
+        <v>46307.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>1819.12</v>
+      </c>
+      <c r="D375">
+        <v>86</v>
+      </c>
+      <c r="E375" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5">
+      <c r="A376" s="2">
+        <v>46307.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>1829.227</v>
+      </c>
+      <c r="D376">
+        <v>87</v>
+      </c>
+      <c r="E376" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5">
+      <c r="A377" s="2">
+        <v>46307.90625</v>
+      </c>
+      <c r="B377">
+        <v>1841.686</v>
+      </c>
+      <c r="D377">
+        <v>88</v>
+      </c>
+      <c r="E377" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5">
+      <c r="A378" s="2">
+        <v>46307.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>1849.762</v>
+      </c>
+      <c r="D378">
+        <v>89</v>
+      </c>
+      <c r="E378" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5">
+      <c r="A379" s="2">
+        <v>46307.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>1862.323</v>
+      </c>
+      <c r="D379">
+        <v>90</v>
+      </c>
+      <c r="E379" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5">
+      <c r="A380" s="2">
+        <v>46307.9375</v>
+      </c>
+      <c r="B380">
+        <v>1872.522</v>
+      </c>
+      <c r="D380">
+        <v>91</v>
+      </c>
+      <c r="E380" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5">
+      <c r="A381" s="2">
+        <v>46307.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>1884.267</v>
+      </c>
+      <c r="D381">
+        <v>92</v>
+      </c>
+      <c r="E381" t="s">
+        <v>384</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Wind_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Wind_Production_Historical.xlsx
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>12.10.20261</t>
-  </si>
-  <si>
-    <t>12.10.20262</t>
-  </si>
-  <si>
-    <t>12.10.20263</t>
-  </si>
-  <si>
-    <t>12.10.20264</t>
-  </si>
-  <si>
-    <t>12.10.20265</t>
-  </si>
-  <si>
-    <t>12.10.20266</t>
-  </si>
-  <si>
-    <t>12.10.20267</t>
-  </si>
-  <si>
-    <t>12.10.20268</t>
-  </si>
-  <si>
-    <t>12.10.20269</t>
-  </si>
-  <si>
-    <t>12.10.202610</t>
-  </si>
-  <si>
-    <t>12.10.202611</t>
-  </si>
-  <si>
-    <t>12.10.202612</t>
-  </si>
-  <si>
-    <t>12.10.202613</t>
-  </si>
-  <si>
-    <t>12.10.202614</t>
-  </si>
-  <si>
-    <t>12.10.202615</t>
-  </si>
-  <si>
-    <t>12.10.202616</t>
-  </si>
-  <si>
-    <t>12.10.202617</t>
-  </si>
-  <si>
-    <t>12.10.202618</t>
-  </si>
-  <si>
-    <t>12.10.202619</t>
-  </si>
-  <si>
-    <t>12.10.202620</t>
-  </si>
-  <si>
-    <t>12.10.202621</t>
-  </si>
-  <si>
-    <t>12.10.202622</t>
-  </si>
-  <si>
-    <t>12.10.202623</t>
-  </si>
-  <si>
-    <t>12.10.202624</t>
-  </si>
-  <si>
-    <t>12.10.202625</t>
-  </si>
-  <si>
-    <t>12.10.202626</t>
-  </si>
-  <si>
-    <t>12.10.202627</t>
-  </si>
-  <si>
-    <t>12.10.202628</t>
-  </si>
-  <si>
-    <t>12.10.202629</t>
-  </si>
-  <si>
-    <t>12.10.202630</t>
-  </si>
-  <si>
-    <t>12.10.202631</t>
-  </si>
-  <si>
-    <t>12.10.202632</t>
-  </si>
-  <si>
-    <t>12.10.202633</t>
-  </si>
-  <si>
-    <t>12.10.202634</t>
-  </si>
-  <si>
-    <t>12.10.202635</t>
-  </si>
-  <si>
-    <t>12.10.202636</t>
-  </si>
-  <si>
-    <t>12.10.202637</t>
-  </si>
-  <si>
-    <t>12.10.202638</t>
-  </si>
-  <si>
-    <t>12.10.202639</t>
-  </si>
-  <si>
-    <t>12.10.202640</t>
-  </si>
-  <si>
-    <t>12.10.202641</t>
-  </si>
-  <si>
-    <t>12.10.202642</t>
-  </si>
-  <si>
-    <t>12.10.202643</t>
-  </si>
-  <si>
-    <t>12.10.202644</t>
-  </si>
-  <si>
-    <t>12.10.202645</t>
-  </si>
-  <si>
-    <t>12.10.202646</t>
-  </si>
-  <si>
-    <t>12.10.202647</t>
-  </si>
-  <si>
-    <t>12.10.202648</t>
-  </si>
-  <si>
-    <t>12.10.202649</t>
-  </si>
-  <si>
-    <t>12.10.202650</t>
-  </si>
-  <si>
-    <t>12.10.202651</t>
-  </si>
-  <si>
-    <t>12.10.202652</t>
-  </si>
-  <si>
-    <t>12.10.202653</t>
-  </si>
-  <si>
-    <t>12.10.202654</t>
-  </si>
-  <si>
-    <t>12.10.202655</t>
-  </si>
-  <si>
-    <t>12.10.202656</t>
-  </si>
-  <si>
-    <t>12.10.202657</t>
-  </si>
-  <si>
-    <t>12.10.202658</t>
-  </si>
-  <si>
-    <t>12.10.202659</t>
-  </si>
-  <si>
-    <t>12.10.202660</t>
-  </si>
-  <si>
-    <t>12.10.202661</t>
-  </si>
-  <si>
-    <t>12.10.202662</t>
-  </si>
-  <si>
-    <t>12.10.202663</t>
-  </si>
-  <si>
-    <t>12.10.202664</t>
-  </si>
-  <si>
-    <t>12.10.202665</t>
-  </si>
-  <si>
-    <t>12.10.202666</t>
-  </si>
-  <si>
-    <t>12.10.202667</t>
-  </si>
-  <si>
-    <t>12.10.202668</t>
-  </si>
-  <si>
-    <t>12.10.202669</t>
-  </si>
-  <si>
-    <t>12.10.202670</t>
-  </si>
-  <si>
-    <t>12.10.202671</t>
-  </si>
-  <si>
-    <t>12.10.202672</t>
-  </si>
-  <si>
-    <t>12.10.202673</t>
-  </si>
-  <si>
-    <t>12.10.202674</t>
-  </si>
-  <si>
-    <t>12.10.202675</t>
-  </si>
-  <si>
-    <t>12.10.202676</t>
-  </si>
-  <si>
-    <t>12.10.202677</t>
-  </si>
-  <si>
-    <t>12.10.202678</t>
-  </si>
-  <si>
-    <t>12.10.202679</t>
-  </si>
-  <si>
-    <t>12.10.202680</t>
-  </si>
-  <si>
-    <t>12.10.202681</t>
-  </si>
-  <si>
-    <t>12.10.202682</t>
-  </si>
-  <si>
-    <t>12.10.202683</t>
-  </si>
-  <si>
-    <t>12.10.202684</t>
-  </si>
-  <si>
-    <t>12.10.202685</t>
-  </si>
-  <si>
-    <t>12.10.202686</t>
-  </si>
-  <si>
-    <t>12.10.202687</t>
-  </si>
-  <si>
-    <t>12.10.202688</t>
-  </si>
-  <si>
-    <t>12.10.202689</t>
-  </si>
-  <si>
-    <t>12.10.202690</t>
-  </si>
-  <si>
-    <t>12.10.202691</t>
-  </si>
-  <si>
-    <t>12.10.202692</t>
-  </si>
-  <si>
-    <t>12.10.202693</t>
-  </si>
-  <si>
-    <t>12.10.202694</t>
-  </si>
-  <si>
-    <t>12.10.202695</t>
-  </si>
-  <si>
-    <t>12.10.202696</t>
-  </si>
-  <si>
     <t>13.10.20261</t>
   </si>
   <si>
@@ -593,6 +305,294 @@
   </si>
   <si>
     <t>13.10.202692</t>
+  </si>
+  <si>
+    <t>13.10.202693</t>
+  </si>
+  <si>
+    <t>13.10.202694</t>
+  </si>
+  <si>
+    <t>13.10.202695</t>
+  </si>
+  <si>
+    <t>13.10.202696</t>
+  </si>
+  <si>
+    <t>14.10.20261</t>
+  </si>
+  <si>
+    <t>14.10.20262</t>
+  </si>
+  <si>
+    <t>14.10.20263</t>
+  </si>
+  <si>
+    <t>14.10.20264</t>
+  </si>
+  <si>
+    <t>14.10.20265</t>
+  </si>
+  <si>
+    <t>14.10.20266</t>
+  </si>
+  <si>
+    <t>14.10.20267</t>
+  </si>
+  <si>
+    <t>14.10.20268</t>
+  </si>
+  <si>
+    <t>14.10.20269</t>
+  </si>
+  <si>
+    <t>14.10.202610</t>
+  </si>
+  <si>
+    <t>14.10.202611</t>
+  </si>
+  <si>
+    <t>14.10.202612</t>
+  </si>
+  <si>
+    <t>14.10.202613</t>
+  </si>
+  <si>
+    <t>14.10.202614</t>
+  </si>
+  <si>
+    <t>14.10.202615</t>
+  </si>
+  <si>
+    <t>14.10.202616</t>
+  </si>
+  <si>
+    <t>14.10.202617</t>
+  </si>
+  <si>
+    <t>14.10.202618</t>
+  </si>
+  <si>
+    <t>14.10.202619</t>
+  </si>
+  <si>
+    <t>14.10.202620</t>
+  </si>
+  <si>
+    <t>14.10.202621</t>
+  </si>
+  <si>
+    <t>14.10.202622</t>
+  </si>
+  <si>
+    <t>14.10.202623</t>
+  </si>
+  <si>
+    <t>14.10.202624</t>
+  </si>
+  <si>
+    <t>14.10.202625</t>
+  </si>
+  <si>
+    <t>14.10.202626</t>
+  </si>
+  <si>
+    <t>14.10.202627</t>
+  </si>
+  <si>
+    <t>14.10.202628</t>
+  </si>
+  <si>
+    <t>14.10.202629</t>
+  </si>
+  <si>
+    <t>14.10.202630</t>
+  </si>
+  <si>
+    <t>14.10.202631</t>
+  </si>
+  <si>
+    <t>14.10.202632</t>
+  </si>
+  <si>
+    <t>14.10.202633</t>
+  </si>
+  <si>
+    <t>14.10.202634</t>
+  </si>
+  <si>
+    <t>14.10.202635</t>
+  </si>
+  <si>
+    <t>14.10.202636</t>
+  </si>
+  <si>
+    <t>14.10.202637</t>
+  </si>
+  <si>
+    <t>14.10.202638</t>
+  </si>
+  <si>
+    <t>14.10.202639</t>
+  </si>
+  <si>
+    <t>14.10.202640</t>
+  </si>
+  <si>
+    <t>14.10.202641</t>
+  </si>
+  <si>
+    <t>14.10.202642</t>
+  </si>
+  <si>
+    <t>14.10.202643</t>
+  </si>
+  <si>
+    <t>14.10.202644</t>
+  </si>
+  <si>
+    <t>14.10.202645</t>
+  </si>
+  <si>
+    <t>14.10.202646</t>
+  </si>
+  <si>
+    <t>14.10.202647</t>
+  </si>
+  <si>
+    <t>14.10.202648</t>
+  </si>
+  <si>
+    <t>14.10.202649</t>
+  </si>
+  <si>
+    <t>14.10.202650</t>
+  </si>
+  <si>
+    <t>14.10.202651</t>
+  </si>
+  <si>
+    <t>14.10.202652</t>
+  </si>
+  <si>
+    <t>14.10.202653</t>
+  </si>
+  <si>
+    <t>14.10.202654</t>
+  </si>
+  <si>
+    <t>14.10.202655</t>
+  </si>
+  <si>
+    <t>14.10.202656</t>
+  </si>
+  <si>
+    <t>14.10.202657</t>
+  </si>
+  <si>
+    <t>14.10.202658</t>
+  </si>
+  <si>
+    <t>14.10.202659</t>
+  </si>
+  <si>
+    <t>14.10.202660</t>
+  </si>
+  <si>
+    <t>14.10.202661</t>
+  </si>
+  <si>
+    <t>14.10.202662</t>
+  </si>
+  <si>
+    <t>14.10.202663</t>
+  </si>
+  <si>
+    <t>14.10.202664</t>
+  </si>
+  <si>
+    <t>14.10.202665</t>
+  </si>
+  <si>
+    <t>14.10.202666</t>
+  </si>
+  <si>
+    <t>14.10.202667</t>
+  </si>
+  <si>
+    <t>14.10.202668</t>
+  </si>
+  <si>
+    <t>14.10.202669</t>
+  </si>
+  <si>
+    <t>14.10.202670</t>
+  </si>
+  <si>
+    <t>14.10.202671</t>
+  </si>
+  <si>
+    <t>14.10.202672</t>
+  </si>
+  <si>
+    <t>14.10.202673</t>
+  </si>
+  <si>
+    <t>14.10.202674</t>
+  </si>
+  <si>
+    <t>14.10.202675</t>
+  </si>
+  <si>
+    <t>14.10.202676</t>
+  </si>
+  <si>
+    <t>14.10.202677</t>
+  </si>
+  <si>
+    <t>14.10.202678</t>
+  </si>
+  <si>
+    <t>14.10.202679</t>
+  </si>
+  <si>
+    <t>14.10.202680</t>
+  </si>
+  <si>
+    <t>14.10.202681</t>
+  </si>
+  <si>
+    <t>14.10.202682</t>
+  </si>
+  <si>
+    <t>14.10.202683</t>
+  </si>
+  <si>
+    <t>14.10.202684</t>
+  </si>
+  <si>
+    <t>14.10.202685</t>
+  </si>
+  <si>
+    <t>14.10.202686</t>
+  </si>
+  <si>
+    <t>14.10.202687</t>
+  </si>
+  <si>
+    <t>14.10.202688</t>
+  </si>
+  <si>
+    <t>14.10.202689</t>
+  </si>
+  <si>
+    <t>14.10.202690</t>
+  </si>
+  <si>
+    <t>14.10.202691</t>
+  </si>
+  <si>
+    <t>14.10.202692</t>
   </si>
 </sst>
 </file>
@@ -976,13 +976,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B2">
-        <v>935.28</v>
+        <v>1941.64</v>
       </c>
       <c r="C2">
-        <v>758</v>
+        <v>2259</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -993,13 +993,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46307.01041666666</v>
+        <v>46308.01041666666</v>
       </c>
       <c r="B3">
-        <v>897.212</v>
+        <v>1957.481</v>
       </c>
       <c r="C3">
-        <v>726</v>
+        <v>2236</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1010,13 +1010,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46307.02083333334</v>
+        <v>46308.02083333334</v>
       </c>
       <c r="B4">
-        <v>860.513</v>
+        <v>1973.214</v>
       </c>
       <c r="C4">
-        <v>726</v>
+        <v>2206</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1027,13 +1027,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46307.03125</v>
+        <v>46308.03125</v>
       </c>
       <c r="B5">
-        <v>808.576</v>
+        <v>1988.772</v>
       </c>
       <c r="C5">
-        <v>728</v>
+        <v>2171</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1044,13 +1044,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46307.04166666666</v>
+        <v>46308.04166666666</v>
       </c>
       <c r="B6">
-        <v>723.9589999999999</v>
+        <v>1980.982</v>
       </c>
       <c r="C6">
-        <v>712</v>
+        <v>2133</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1061,13 +1061,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46307.05208333334</v>
+        <v>46308.05208333334</v>
       </c>
       <c r="B7">
-        <v>694.572</v>
+        <v>2017.875</v>
       </c>
       <c r="C7">
-        <v>737</v>
+        <v>2153</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1078,13 +1078,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46307.0625</v>
+        <v>46308.0625</v>
       </c>
       <c r="B8">
-        <v>665.443</v>
+        <v>2041.072</v>
       </c>
       <c r="C8">
-        <v>731</v>
+        <v>2170</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1095,13 +1095,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46307.07291666666</v>
+        <v>46308.07291666666</v>
       </c>
       <c r="B9">
-        <v>628.763</v>
+        <v>2052.74</v>
       </c>
       <c r="C9">
-        <v>727</v>
+        <v>2161</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1112,13 +1112,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46307.08333333334</v>
+        <v>46308.08333333334</v>
       </c>
       <c r="B10">
-        <v>608.696</v>
+        <v>2060.445</v>
       </c>
       <c r="C10">
-        <v>708</v>
+        <v>2161</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1129,13 +1129,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46307.09375</v>
+        <v>46308.09375</v>
       </c>
       <c r="B11">
-        <v>596.585</v>
+        <v>2057.801</v>
       </c>
       <c r="C11">
-        <v>712</v>
+        <v>2173</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1146,13 +1146,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46307.10416666666</v>
+        <v>46308.10416666666</v>
       </c>
       <c r="B12">
-        <v>582.4829999999999</v>
+        <v>2058.189</v>
       </c>
       <c r="C12">
-        <v>727</v>
+        <v>2153</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1163,13 +1163,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46307.11458333334</v>
+        <v>46308.11458333334</v>
       </c>
       <c r="B13">
-        <v>574.008</v>
+        <v>2056.84</v>
       </c>
       <c r="C13">
-        <v>728</v>
+        <v>2112</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1180,13 +1180,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46307.125</v>
+        <v>46308.125</v>
       </c>
       <c r="B14">
-        <v>586.0309999999999</v>
+        <v>2037.552</v>
       </c>
       <c r="C14">
-        <v>768</v>
+        <v>2118</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1197,13 +1197,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46307.13541666666</v>
+        <v>46308.13541666666</v>
       </c>
       <c r="B15">
-        <v>583.832</v>
+        <v>2042.185</v>
       </c>
       <c r="C15">
-        <v>883</v>
+        <v>2095</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1214,13 +1214,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46307.14583333334</v>
+        <v>46308.14583333334</v>
       </c>
       <c r="B16">
-        <v>589.158</v>
+        <v>2048.055</v>
       </c>
       <c r="C16">
-        <v>1053</v>
+        <v>2110</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1231,13 +1231,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46307.15625</v>
+        <v>46308.15625</v>
       </c>
       <c r="B17">
-        <v>595.721</v>
+        <v>2051.478</v>
       </c>
       <c r="C17">
-        <v>1216</v>
+        <v>2145</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1248,13 +1248,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46307.16666666666</v>
+        <v>46308.16666666666</v>
       </c>
       <c r="B18">
-        <v>620.583</v>
+        <v>2055.868</v>
       </c>
       <c r="C18">
-        <v>1241</v>
+        <v>2141</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1265,13 +1265,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46307.17708333334</v>
+        <v>46308.17708333334</v>
       </c>
       <c r="B19">
-        <v>636.164</v>
+        <v>2054.967</v>
       </c>
       <c r="C19">
-        <v>1139</v>
+        <v>2150</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1282,13 +1282,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46307.1875</v>
+        <v>46308.1875</v>
       </c>
       <c r="B20">
-        <v>657.821</v>
+        <v>2051.248</v>
       </c>
       <c r="C20">
-        <v>1188</v>
+        <v>2126</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1299,13 +1299,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46307.19791666666</v>
+        <v>46308.19791666666</v>
       </c>
       <c r="B21">
-        <v>678.283</v>
+        <v>2053.857</v>
       </c>
       <c r="C21">
-        <v>1191</v>
+        <v>2139</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1316,13 +1316,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46307.20833333334</v>
+        <v>46308.20833333334</v>
       </c>
       <c r="B22">
-        <v>746.412</v>
+        <v>2104.469</v>
       </c>
       <c r="C22">
-        <v>1416</v>
+        <v>2201</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1333,13 +1333,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46307.21875</v>
+        <v>46308.21875</v>
       </c>
       <c r="B23">
-        <v>778.248</v>
+        <v>2111.796</v>
       </c>
       <c r="C23">
-        <v>1507</v>
+        <v>2305</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1350,13 +1350,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46307.22916666666</v>
+        <v>46308.22916666666</v>
       </c>
       <c r="B24">
-        <v>787.473</v>
+        <v>2118.405</v>
       </c>
       <c r="C24">
-        <v>1462</v>
+        <v>2397</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1367,13 +1367,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46307.23958333334</v>
+        <v>46308.23958333334</v>
       </c>
       <c r="B25">
-        <v>817.22</v>
+        <v>2124.492</v>
       </c>
       <c r="C25">
-        <v>1377</v>
+        <v>2433</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1384,13 +1384,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46307.25</v>
+        <v>46308.25</v>
       </c>
       <c r="B26">
-        <v>789.324</v>
+        <v>2113.498</v>
       </c>
       <c r="C26">
-        <v>1241</v>
+        <v>2466</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1401,13 +1401,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46307.26041666666</v>
+        <v>46308.26041666666</v>
       </c>
       <c r="B27">
-        <v>809.117</v>
+        <v>2128.737</v>
       </c>
       <c r="C27">
-        <v>1102</v>
+        <v>2442</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1418,13 +1418,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46307.27083333334</v>
+        <v>46308.27083333334</v>
       </c>
       <c r="B28">
-        <v>817.35</v>
+        <v>2132.841</v>
       </c>
       <c r="C28">
-        <v>1014</v>
+        <v>2426</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1435,13 +1435,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46307.28125</v>
+        <v>46308.28125</v>
       </c>
       <c r="B29">
-        <v>831.064</v>
+        <v>2145.936</v>
       </c>
       <c r="C29">
-        <v>888</v>
+        <v>2464</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1452,13 +1452,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46307.29166666666</v>
+        <v>46308.29166666666</v>
       </c>
       <c r="B30">
-        <v>915.611</v>
+        <v>2182.844</v>
       </c>
       <c r="C30">
-        <v>775</v>
+        <v>2522</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1469,13 +1469,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46307.30208333334</v>
+        <v>46308.30208333334</v>
       </c>
       <c r="B31">
-        <v>913.2140000000001</v>
+        <v>2224.695</v>
       </c>
       <c r="C31">
-        <v>662</v>
+        <v>2573</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1486,13 +1486,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46307.3125</v>
+        <v>46308.3125</v>
       </c>
       <c r="B32">
-        <v>914.5</v>
+        <v>2261.349</v>
       </c>
       <c r="C32">
-        <v>598</v>
+        <v>2597</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1503,13 +1503,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46307.32291666666</v>
+        <v>46308.32291666666</v>
       </c>
       <c r="B33">
-        <v>917.663</v>
+        <v>2266.463</v>
       </c>
       <c r="C33">
-        <v>568</v>
+        <v>2609</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1520,13 +1520,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46307.33333333334</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="B34">
-        <v>802.996</v>
+        <v>2271.582</v>
       </c>
       <c r="C34">
-        <v>558</v>
+        <v>2601</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1537,13 +1537,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46307.34375</v>
+        <v>46308.34375</v>
       </c>
       <c r="B35">
-        <v>809.417</v>
+        <v>2274.897</v>
       </c>
       <c r="C35">
-        <v>560</v>
+        <v>2627</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1554,13 +1554,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46307.35416666666</v>
+        <v>46308.35416666666</v>
       </c>
       <c r="B36">
-        <v>816.022</v>
+        <v>2260.406</v>
       </c>
       <c r="C36">
-        <v>567</v>
+        <v>2662</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1571,13 +1571,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46307.36458333334</v>
+        <v>46308.36458333334</v>
       </c>
       <c r="B37">
-        <v>822.0890000000001</v>
+        <v>2262.916</v>
       </c>
       <c r="C37">
-        <v>580</v>
+        <v>2656</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1588,13 +1588,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46307.375</v>
+        <v>46308.375</v>
       </c>
       <c r="B38">
-        <v>795.671</v>
+        <v>2238.129</v>
       </c>
       <c r="C38">
-        <v>602</v>
+        <v>2650</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1605,13 +1605,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46307.38541666666</v>
+        <v>46308.38541666666</v>
       </c>
       <c r="B39">
-        <v>800.687</v>
+        <v>2249.516</v>
       </c>
       <c r="C39">
-        <v>639</v>
+        <v>2648</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1622,13 +1622,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46307.39583333334</v>
+        <v>46308.39583333334</v>
       </c>
       <c r="B40">
-        <v>807.314</v>
+        <v>2257.31</v>
       </c>
       <c r="C40">
-        <v>661</v>
+        <v>2672</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1639,13 +1639,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46307.40625</v>
+        <v>46308.40625</v>
       </c>
       <c r="B41">
-        <v>813.246</v>
+        <v>2265.23</v>
       </c>
       <c r="C41">
-        <v>678</v>
+        <v>2667</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1656,13 +1656,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46307.41666666666</v>
+        <v>46308.41666666666</v>
       </c>
       <c r="B42">
-        <v>850.569</v>
+        <v>2247.099</v>
       </c>
       <c r="C42">
-        <v>703</v>
+        <v>2684</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1673,13 +1673,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46307.42708333334</v>
+        <v>46308.42708333334</v>
       </c>
       <c r="B43">
-        <v>857.36</v>
+        <v>2267.11</v>
       </c>
       <c r="C43">
-        <v>720</v>
+        <v>2679</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1690,13 +1690,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46307.4375</v>
+        <v>46308.4375</v>
       </c>
       <c r="B44">
-        <v>864.919</v>
+        <v>2286.18</v>
       </c>
       <c r="C44">
-        <v>733</v>
+        <v>2672</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1707,13 +1707,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46307.44791666666</v>
+        <v>46308.44791666666</v>
       </c>
       <c r="B45">
-        <v>872.048</v>
+        <v>2305.898</v>
       </c>
       <c r="C45">
-        <v>720</v>
+        <v>2651</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1724,13 +1724,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46307.45833333334</v>
+        <v>46308.45833333334</v>
       </c>
       <c r="B46">
-        <v>894.274</v>
+        <v>2329.751</v>
       </c>
       <c r="C46">
-        <v>748</v>
+        <v>2668</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1741,13 +1741,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46307.46875</v>
+        <v>46308.46875</v>
       </c>
       <c r="B47">
-        <v>899.135</v>
+        <v>2339.796</v>
       </c>
       <c r="C47">
-        <v>751</v>
+        <v>2687</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1758,13 +1758,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46307.47916666666</v>
+        <v>46308.47916666666</v>
       </c>
       <c r="B48">
-        <v>904.255</v>
+        <v>2351.296</v>
       </c>
       <c r="C48">
-        <v>785</v>
+        <v>2701</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1775,13 +1775,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46307.48958333334</v>
+        <v>46308.48958333334</v>
       </c>
       <c r="B49">
-        <v>908.457</v>
+        <v>2361.946</v>
       </c>
       <c r="C49">
-        <v>817</v>
+        <v>2704</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1792,13 +1792,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46307.5</v>
+        <v>46308.5</v>
       </c>
       <c r="B50">
-        <v>922.9299999999999</v>
+        <v>2333.141</v>
       </c>
       <c r="C50">
-        <v>864</v>
+        <v>2678</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1809,13 +1809,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46307.51041666666</v>
+        <v>46308.51041666666</v>
       </c>
       <c r="B51">
-        <v>928.495</v>
+        <v>2339.899</v>
       </c>
       <c r="C51">
-        <v>895</v>
+        <v>2667</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1826,13 +1826,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46307.52083333334</v>
+        <v>46308.52083333334</v>
       </c>
       <c r="B52">
-        <v>931.785</v>
+        <v>2346.417</v>
       </c>
       <c r="C52">
-        <v>941</v>
+        <v>2686</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1843,13 +1843,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46307.53125</v>
+        <v>46308.53125</v>
       </c>
       <c r="B53">
-        <v>935.991</v>
+        <v>2353.978</v>
       </c>
       <c r="C53">
-        <v>978</v>
+        <v>2699</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1860,13 +1860,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46307.54166666666</v>
+        <v>46308.54166666666</v>
       </c>
       <c r="B54">
-        <v>957.833</v>
+        <v>2347.053</v>
       </c>
       <c r="C54">
-        <v>1018</v>
+        <v>2788</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1877,13 +1877,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46307.55208333334</v>
+        <v>46308.55208333334</v>
       </c>
       <c r="B55">
-        <v>967.715</v>
+        <v>2353.852</v>
       </c>
       <c r="C55">
-        <v>1010</v>
+        <v>2779</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1894,13 +1894,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46307.5625</v>
+        <v>46308.5625</v>
       </c>
       <c r="B56">
-        <v>979.6180000000001</v>
+        <v>2357.706</v>
       </c>
       <c r="C56">
-        <v>1080</v>
+        <v>2739</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1911,13 +1911,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46307.57291666666</v>
+        <v>46308.57291666666</v>
       </c>
       <c r="B57">
-        <v>988.706</v>
+        <v>2361.414</v>
       </c>
       <c r="C57">
-        <v>1209</v>
+        <v>2730</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1928,13 +1928,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46307.58333333334</v>
+        <v>46308.58333333334</v>
       </c>
       <c r="B58">
-        <v>1026.044</v>
+        <v>2380.025</v>
       </c>
       <c r="C58">
-        <v>1314</v>
+        <v>2738</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1945,13 +1945,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46307.59375</v>
+        <v>46308.59375</v>
       </c>
       <c r="B59">
-        <v>1044.331</v>
+        <v>2382.058</v>
       </c>
       <c r="C59">
-        <v>1361</v>
+        <v>2730</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1962,13 +1962,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46307.60416666666</v>
+        <v>46308.60416666666</v>
       </c>
       <c r="B60">
-        <v>1063.788</v>
+        <v>2379.138</v>
       </c>
       <c r="C60">
-        <v>1385</v>
+        <v>2679</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1979,13 +1979,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46307.61458333334</v>
+        <v>46308.61458333334</v>
       </c>
       <c r="B61">
-        <v>1084.793</v>
+        <v>2381.592</v>
       </c>
       <c r="C61">
-        <v>1437</v>
+        <v>2616</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -1996,13 +1996,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46307.625</v>
+        <v>46308.625</v>
       </c>
       <c r="B62">
-        <v>1125.224</v>
+        <v>2346.183</v>
       </c>
       <c r="C62">
-        <v>1496</v>
+        <v>2649</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2013,13 +2013,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46307.63541666666</v>
+        <v>46308.63541666666</v>
       </c>
       <c r="B63">
-        <v>1148.403</v>
+        <v>2342.452</v>
       </c>
       <c r="C63">
-        <v>1547</v>
+        <v>2670</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2030,13 +2030,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46307.64583333334</v>
+        <v>46308.64583333334</v>
       </c>
       <c r="B64">
-        <v>1171.189</v>
+        <v>2333.291</v>
       </c>
       <c r="C64">
-        <v>1578</v>
+        <v>2627</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2047,13 +2047,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46307.65625</v>
+        <v>46308.65625</v>
       </c>
       <c r="B65">
-        <v>1194.605</v>
+        <v>2324.024</v>
       </c>
       <c r="C65">
-        <v>1602</v>
+        <v>2537</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2064,13 +2064,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46307.66666666666</v>
+        <v>46308.66666666666</v>
       </c>
       <c r="B66">
-        <v>1234.616</v>
+        <v>2304.594</v>
       </c>
       <c r="C66">
-        <v>1628</v>
+        <v>2532</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2081,13 +2081,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46307.67708333334</v>
+        <v>46308.67708333334</v>
       </c>
       <c r="B67">
-        <v>1264.756</v>
+        <v>2296.569</v>
       </c>
       <c r="C67">
-        <v>1620</v>
+        <v>2464</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2098,13 +2098,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46307.6875</v>
+        <v>46308.6875</v>
       </c>
       <c r="B68">
-        <v>1294.29</v>
+        <v>2288.237</v>
       </c>
       <c r="C68">
-        <v>1581</v>
+        <v>2403</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2115,13 +2115,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46307.69791666666</v>
+        <v>46308.69791666666</v>
       </c>
       <c r="B69">
-        <v>1324.912</v>
+        <v>2280.087</v>
       </c>
       <c r="C69">
-        <v>1528</v>
+        <v>2354</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2132,13 +2132,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46307.70833333334</v>
+        <v>46308.70833333334</v>
       </c>
       <c r="B70">
-        <v>1361.38</v>
+        <v>2265.647</v>
       </c>
       <c r="C70">
-        <v>1529</v>
+        <v>2346</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2149,13 +2149,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46307.71875</v>
+        <v>46308.71875</v>
       </c>
       <c r="B71">
-        <v>1396.876</v>
+        <v>2272.405</v>
       </c>
       <c r="C71">
-        <v>1526</v>
+        <v>2337</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2166,13 +2166,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46307.72916666666</v>
+        <v>46308.72916666666</v>
       </c>
       <c r="B72">
-        <v>1431.895</v>
+        <v>2280.394</v>
       </c>
       <c r="C72">
-        <v>1493</v>
+        <v>2336</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2183,13 +2183,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46307.73958333334</v>
+        <v>46308.73958333334</v>
       </c>
       <c r="B73">
-        <v>1468.284</v>
+        <v>2289.333</v>
       </c>
       <c r="C73">
-        <v>1521</v>
+        <v>2257</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2200,13 +2200,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46307.75</v>
+        <v>46308.75</v>
       </c>
       <c r="B74">
-        <v>1515.371</v>
+        <v>2293.876</v>
       </c>
       <c r="C74">
-        <v>1541</v>
+        <v>2214</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2217,13 +2217,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46307.76041666666</v>
+        <v>46308.76041666666</v>
       </c>
       <c r="B75">
-        <v>1546.394</v>
+        <v>2295.821</v>
       </c>
       <c r="C75">
-        <v>1561</v>
+        <v>2279</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2234,13 +2234,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46307.77083333334</v>
+        <v>46308.77083333334</v>
       </c>
       <c r="B76">
-        <v>1578.46</v>
+        <v>2303.508</v>
       </c>
       <c r="C76">
-        <v>1594</v>
+        <v>2310</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2251,13 +2251,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46307.78125</v>
+        <v>46308.78125</v>
       </c>
       <c r="B77">
-        <v>1609.067</v>
+        <v>2304.376</v>
       </c>
       <c r="C77">
-        <v>1640</v>
+        <v>2253</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2268,13 +2268,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46307.79166666666</v>
+        <v>46308.79166666666</v>
       </c>
       <c r="B78">
-        <v>1641.225</v>
+        <v>2306.063</v>
       </c>
       <c r="C78">
-        <v>1679</v>
+        <v>2220</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2285,13 +2285,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46307.80208333334</v>
+        <v>46308.80208333334</v>
       </c>
       <c r="B79">
-        <v>1669.41</v>
+        <v>2304.435</v>
       </c>
       <c r="C79">
-        <v>1648</v>
+        <v>2296</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2302,13 +2302,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46307.8125</v>
+        <v>46308.8125</v>
       </c>
       <c r="B80">
-        <v>1698.167</v>
+        <v>2303.44</v>
       </c>
       <c r="C80">
-        <v>1660</v>
+        <v>2327</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2319,13 +2319,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46307.82291666666</v>
+        <v>46308.82291666666</v>
       </c>
       <c r="B81">
-        <v>1724.591</v>
+        <v>2302.711</v>
       </c>
       <c r="C81">
-        <v>1708</v>
+        <v>2384</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2336,13 +2336,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46307.83333333334</v>
+        <v>46308.83333333334</v>
       </c>
       <c r="B82">
-        <v>1754.13</v>
+        <v>2305.963</v>
       </c>
       <c r="C82">
-        <v>1757</v>
+        <v>2446</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2353,13 +2353,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46307.84375</v>
+        <v>46308.84375</v>
       </c>
       <c r="B83">
-        <v>1770.683</v>
+        <v>2300.354</v>
       </c>
       <c r="C83">
-        <v>1811</v>
+        <v>2432</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2370,13 +2370,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46307.85416666666</v>
+        <v>46308.85416666666</v>
       </c>
       <c r="B84">
-        <v>1787.49</v>
+        <v>2296.98</v>
       </c>
       <c r="C84">
-        <v>1829</v>
+        <v>2434</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2387,13 +2387,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46307.86458333334</v>
+        <v>46308.86458333334</v>
       </c>
       <c r="B85">
-        <v>1799.805</v>
+        <v>2292.754</v>
       </c>
       <c r="C85">
-        <v>1893</v>
+        <v>2473</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2404,13 +2404,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46307.875</v>
+        <v>46308.875</v>
       </c>
       <c r="B86">
-        <v>1809.15</v>
+        <v>2317.27</v>
       </c>
       <c r="C86">
-        <v>1958</v>
+        <v>2510</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2421,13 +2421,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46307.88541666666</v>
+        <v>46308.88541666666</v>
       </c>
       <c r="B87">
-        <v>1819.12</v>
+        <v>2316.237</v>
       </c>
       <c r="C87">
-        <v>1993</v>
+        <v>2517</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2438,13 +2438,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46307.89583333334</v>
+        <v>46308.89583333334</v>
       </c>
       <c r="B88">
-        <v>1829.227</v>
+        <v>2313.366</v>
       </c>
       <c r="C88">
-        <v>2069</v>
+        <v>2534</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2455,13 +2455,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46307.90625</v>
+        <v>46308.90625</v>
       </c>
       <c r="B89">
-        <v>1841.686</v>
+        <v>2314.597</v>
       </c>
       <c r="C89">
-        <v>2099</v>
+        <v>2492</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2472,13 +2472,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46307.91666666666</v>
+        <v>46308.91666666666</v>
       </c>
       <c r="B90">
-        <v>1849.762</v>
+        <v>2329.79</v>
       </c>
       <c r="C90">
-        <v>2123</v>
+        <v>2446</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2489,13 +2489,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46307.92708333334</v>
+        <v>46308.92708333334</v>
       </c>
       <c r="B91">
-        <v>1862.323</v>
+        <v>2332.851</v>
       </c>
       <c r="C91">
-        <v>2090</v>
+        <v>2424</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2506,13 +2506,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46307.9375</v>
+        <v>46308.9375</v>
       </c>
       <c r="B92">
-        <v>1872.522</v>
+        <v>2335.233</v>
       </c>
       <c r="C92">
-        <v>2030</v>
+        <v>2353</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2523,13 +2523,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46307.94791666666</v>
+        <v>46308.94791666666</v>
       </c>
       <c r="B93">
-        <v>1884.267</v>
+        <v>2337.297</v>
       </c>
       <c r="C93">
-        <v>1987</v>
+        <v>2292</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2540,13 +2540,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46307.95833333334</v>
+        <v>46308.95833333334</v>
       </c>
       <c r="B94">
-        <v>1847.762</v>
+        <v>2444.507</v>
       </c>
       <c r="C94">
-        <v>2024</v>
+        <v>2232</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2557,13 +2557,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46307.96875</v>
+        <v>46308.96875</v>
       </c>
       <c r="B95">
-        <v>1863.222</v>
+        <v>2442.786</v>
       </c>
       <c r="C95">
-        <v>2046</v>
+        <v>2204</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2574,13 +2574,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46307.97916666666</v>
+        <v>46308.97916666666</v>
       </c>
       <c r="B96">
-        <v>1879.046</v>
+        <v>2442.317</v>
       </c>
       <c r="C96">
-        <v>2111</v>
+        <v>2229</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2591,13 +2591,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46307.98958333334</v>
+        <v>46308.98958333334</v>
       </c>
       <c r="B97">
-        <v>1883.352</v>
+        <v>2451.336</v>
       </c>
       <c r="C97">
-        <v>2198</v>
+        <v>2227</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2608,13 +2608,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B98">
-        <v>1941.64</v>
+        <v>2454.623</v>
       </c>
       <c r="C98">
-        <v>2259</v>
+        <v>2228</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2625,13 +2625,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46308.01041666666</v>
+        <v>46309.01041666666</v>
       </c>
       <c r="B99">
-        <v>1957.481</v>
+        <v>2454.535</v>
       </c>
       <c r="C99">
-        <v>2236</v>
+        <v>2256</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2642,13 +2642,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46308.02083333334</v>
+        <v>46309.02083333334</v>
       </c>
       <c r="B100">
-        <v>1973.214</v>
+        <v>2452.395</v>
       </c>
       <c r="C100">
-        <v>2206</v>
+        <v>2299</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2659,13 +2659,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46308.03125</v>
+        <v>46309.03125</v>
       </c>
       <c r="B101">
-        <v>1988.772</v>
+        <v>2453.732</v>
       </c>
       <c r="C101">
-        <v>2171</v>
+        <v>2333</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2676,13 +2676,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46308.04166666666</v>
+        <v>46309.04166666666</v>
       </c>
       <c r="B102">
-        <v>1980.982</v>
+        <v>2444.137</v>
       </c>
       <c r="C102">
-        <v>2133</v>
+        <v>2306</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2693,13 +2693,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46308.05208333334</v>
+        <v>46309.05208333334</v>
       </c>
       <c r="B103">
-        <v>2017.875</v>
+        <v>2443.466</v>
       </c>
       <c r="C103">
-        <v>2153</v>
+        <v>2239</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2710,13 +2710,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46308.0625</v>
+        <v>46309.0625</v>
       </c>
       <c r="B104">
-        <v>2041.072</v>
+        <v>2441.667</v>
       </c>
       <c r="C104">
-        <v>2170</v>
+        <v>2238</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2727,13 +2727,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46308.07291666666</v>
+        <v>46309.07291666666</v>
       </c>
       <c r="B105">
-        <v>2052.74</v>
+        <v>2438.431</v>
       </c>
       <c r="C105">
-        <v>2161</v>
+        <v>2281</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2744,13 +2744,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46308.08333333334</v>
+        <v>46309.08333333334</v>
       </c>
       <c r="B106">
-        <v>2060.445</v>
+        <v>2440.881</v>
       </c>
       <c r="C106">
-        <v>2161</v>
+        <v>2303</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2761,13 +2761,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46308.09375</v>
+        <v>46309.09375</v>
       </c>
       <c r="B107">
-        <v>2057.801</v>
+        <v>2433.954</v>
       </c>
       <c r="C107">
-        <v>2173</v>
+        <v>2331</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2778,13 +2778,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46308.10416666666</v>
+        <v>46309.10416666666</v>
       </c>
       <c r="B108">
-        <v>2058.189</v>
+        <v>2429.397</v>
       </c>
       <c r="C108">
-        <v>2153</v>
+        <v>2400</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2795,13 +2795,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46308.11458333334</v>
+        <v>46309.11458333334</v>
       </c>
       <c r="B109">
-        <v>2056.84</v>
+        <v>2420.925</v>
       </c>
       <c r="C109">
-        <v>2112</v>
+        <v>2440</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2812,13 +2812,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46308.125</v>
+        <v>46309.125</v>
       </c>
       <c r="B110">
-        <v>2037.552</v>
+        <v>2419.846</v>
       </c>
       <c r="C110">
-        <v>2118</v>
+        <v>2443</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2829,13 +2829,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46308.13541666666</v>
+        <v>46309.13541666666</v>
       </c>
       <c r="B111">
-        <v>2042.185</v>
+        <v>2417.313</v>
       </c>
       <c r="C111">
-        <v>2095</v>
+        <v>2434</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2846,13 +2846,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46308.14583333334</v>
+        <v>46309.14583333334</v>
       </c>
       <c r="B112">
-        <v>2048.055</v>
+        <v>2420.971</v>
       </c>
       <c r="C112">
-        <v>2110</v>
+        <v>2445</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2863,13 +2863,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46308.15625</v>
+        <v>46309.15625</v>
       </c>
       <c r="B113">
-        <v>2051.478</v>
+        <v>2409.355</v>
       </c>
       <c r="C113">
-        <v>2145</v>
+        <v>2433</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2880,13 +2880,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46308.16666666666</v>
+        <v>46309.16666666666</v>
       </c>
       <c r="B114">
-        <v>2055.868</v>
+        <v>2381.823</v>
       </c>
       <c r="C114">
-        <v>2141</v>
+        <v>2400</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2897,13 +2897,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46308.17708333334</v>
+        <v>46309.17708333334</v>
       </c>
       <c r="B115">
-        <v>2054.967</v>
+        <v>2384.713</v>
       </c>
       <c r="C115">
-        <v>2150</v>
+        <v>2375</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2914,13 +2914,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46308.1875</v>
+        <v>46309.1875</v>
       </c>
       <c r="B116">
-        <v>2051.248</v>
+        <v>2385.622</v>
       </c>
       <c r="C116">
-        <v>2126</v>
+        <v>2404</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2931,13 +2931,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46308.19791666666</v>
+        <v>46309.19791666666</v>
       </c>
       <c r="B117">
-        <v>2053.857</v>
+        <v>2388.234</v>
       </c>
       <c r="C117">
-        <v>2139</v>
+        <v>2456</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2948,13 +2948,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46308.20833333334</v>
+        <v>46309.20833333334</v>
       </c>
       <c r="B118">
-        <v>2104.469</v>
+        <v>2479.054</v>
       </c>
       <c r="C118">
-        <v>2201</v>
+        <v>2440</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2965,13 +2965,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46308.21875</v>
+        <v>46309.21875</v>
       </c>
       <c r="B119">
-        <v>2111.796</v>
+        <v>2482.633</v>
       </c>
       <c r="C119">
-        <v>2305</v>
+        <v>2420</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2982,13 +2982,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46308.22916666666</v>
+        <v>46309.22916666666</v>
       </c>
       <c r="B120">
-        <v>2118.405</v>
+        <v>2485.628</v>
       </c>
       <c r="C120">
-        <v>2397</v>
+        <v>2440</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -2999,13 +2999,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46308.23958333334</v>
+        <v>46309.23958333334</v>
       </c>
       <c r="B121">
-        <v>2124.492</v>
+        <v>2491.009</v>
       </c>
       <c r="C121">
-        <v>2433</v>
+        <v>2428</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3016,13 +3016,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46308.25</v>
+        <v>46309.25</v>
       </c>
       <c r="B122">
-        <v>2113.498</v>
+        <v>2432.847</v>
       </c>
       <c r="C122">
-        <v>2466</v>
+        <v>2377</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3033,13 +3033,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46308.26041666666</v>
+        <v>46309.26041666666</v>
       </c>
       <c r="B123">
-        <v>2128.737</v>
+        <v>2423.243</v>
       </c>
       <c r="C123">
-        <v>2442</v>
+        <v>2364</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3050,13 +3050,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46308.27083333334</v>
+        <v>46309.27083333334</v>
       </c>
       <c r="B124">
-        <v>2132.841</v>
+        <v>2410.11</v>
       </c>
       <c r="C124">
-        <v>2426</v>
+        <v>2355</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3067,13 +3067,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46308.28125</v>
+        <v>46309.28125</v>
       </c>
       <c r="B125">
-        <v>2145.936</v>
+        <v>2402.078</v>
       </c>
       <c r="C125">
-        <v>2464</v>
+        <v>2318</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3084,13 +3084,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46308.29166666666</v>
+        <v>46309.29166666666</v>
       </c>
       <c r="B126">
-        <v>2182.844</v>
+        <v>2375.157</v>
       </c>
       <c r="C126">
-        <v>2522</v>
+        <v>2271</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3101,13 +3101,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46308.30208333334</v>
+        <v>46309.30208333334</v>
       </c>
       <c r="B127">
-        <v>2224.695</v>
+        <v>2376.279</v>
       </c>
       <c r="C127">
-        <v>2573</v>
+        <v>2277</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3118,13 +3118,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46308.3125</v>
+        <v>46309.3125</v>
       </c>
       <c r="B128">
-        <v>2261.349</v>
+        <v>2366.567</v>
       </c>
       <c r="C128">
-        <v>2597</v>
+        <v>2353</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3135,13 +3135,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46308.32291666666</v>
+        <v>46309.32291666666</v>
       </c>
       <c r="B129">
-        <v>2266.463</v>
+        <v>2351.05</v>
       </c>
       <c r="C129">
-        <v>2609</v>
+        <v>2430</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3152,13 +3152,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46308.33333333334</v>
+        <v>46309.33333333334</v>
       </c>
       <c r="B130">
-        <v>2271.582</v>
+        <v>2287.961</v>
       </c>
       <c r="C130">
-        <v>2601</v>
+        <v>2481</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3169,13 +3169,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46308.34375</v>
+        <v>46309.34375</v>
       </c>
       <c r="B131">
-        <v>2274.897</v>
+        <v>2297.147</v>
       </c>
       <c r="C131">
-        <v>2627</v>
+        <v>2480</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3186,13 +3186,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46308.35416666666</v>
+        <v>46309.35416666666</v>
       </c>
       <c r="B132">
-        <v>2260.406</v>
+        <v>2302.8</v>
       </c>
       <c r="C132">
-        <v>2662</v>
+        <v>2481</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3203,13 +3203,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46308.36458333334</v>
+        <v>46309.36458333334</v>
       </c>
       <c r="B133">
-        <v>2262.916</v>
+        <v>2312.624</v>
       </c>
       <c r="C133">
-        <v>2656</v>
+        <v>2467</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3220,13 +3220,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46308.375</v>
+        <v>46309.375</v>
       </c>
       <c r="B134">
-        <v>2238.129</v>
+        <v>2330.181</v>
       </c>
       <c r="C134">
-        <v>2650</v>
+        <v>2424</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3237,13 +3237,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46308.38541666666</v>
+        <v>46309.38541666666</v>
       </c>
       <c r="B135">
-        <v>2249.516</v>
+        <v>2334.173</v>
       </c>
       <c r="C135">
-        <v>2648</v>
+        <v>2355</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3254,13 +3254,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46308.39583333334</v>
+        <v>46309.39583333334</v>
       </c>
       <c r="B136">
-        <v>2257.31</v>
+        <v>2340.315</v>
       </c>
       <c r="C136">
-        <v>2672</v>
+        <v>2318</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3271,13 +3271,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46308.40625</v>
+        <v>46309.40625</v>
       </c>
       <c r="B137">
-        <v>2265.23</v>
+        <v>2347.987</v>
       </c>
       <c r="C137">
-        <v>2667</v>
+        <v>2269</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3288,13 +3288,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46308.41666666666</v>
+        <v>46309.41666666666</v>
       </c>
       <c r="B138">
-        <v>2247.099</v>
+        <v>2355.544</v>
       </c>
       <c r="C138">
-        <v>2684</v>
+        <v>2210</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3305,13 +3305,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46308.42708333334</v>
+        <v>46309.42708333334</v>
       </c>
       <c r="B139">
-        <v>2267.11</v>
+        <v>2350.134</v>
       </c>
       <c r="C139">
-        <v>2679</v>
+        <v>2249</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3322,13 +3322,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46308.4375</v>
+        <v>46309.4375</v>
       </c>
       <c r="B140">
-        <v>2286.18</v>
+        <v>2344.889</v>
       </c>
       <c r="C140">
-        <v>2672</v>
+        <v>2233</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3339,13 +3339,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46308.44791666666</v>
+        <v>46309.44791666666</v>
       </c>
       <c r="B141">
-        <v>2305.898</v>
+        <v>2339.392</v>
       </c>
       <c r="C141">
-        <v>2651</v>
+        <v>2209</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3356,13 +3356,13 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46308.45833333334</v>
+        <v>46309.45833333334</v>
       </c>
       <c r="B142">
-        <v>2329.751</v>
+        <v>2301.593</v>
       </c>
       <c r="C142">
-        <v>2668</v>
+        <v>2203</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3373,13 +3373,13 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46308.46875</v>
+        <v>46309.46875</v>
       </c>
       <c r="B143">
-        <v>2339.796</v>
+        <v>2303.708</v>
       </c>
       <c r="C143">
-        <v>2687</v>
+        <v>2187</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3390,13 +3390,13 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46308.47916666666</v>
+        <v>46309.47916666666</v>
       </c>
       <c r="B144">
-        <v>2351.296</v>
+        <v>2304.703</v>
       </c>
       <c r="C144">
-        <v>2701</v>
+        <v>2224</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3407,13 +3407,13 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46308.48958333334</v>
+        <v>46309.48958333334</v>
       </c>
       <c r="B145">
-        <v>2361.946</v>
+        <v>2305.973</v>
       </c>
       <c r="C145">
-        <v>2704</v>
+        <v>2228</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3424,13 +3424,13 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="B146">
-        <v>2333.141</v>
+        <v>2308.768</v>
       </c>
       <c r="C146">
-        <v>2678</v>
+        <v>2281</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3441,13 +3441,13 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46308.51041666666</v>
+        <v>46309.51041666666</v>
       </c>
       <c r="B147">
-        <v>2339.899</v>
+        <v>2304.492</v>
       </c>
       <c r="C147">
-        <v>2667</v>
+        <v>2341</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3458,13 +3458,13 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46308.52083333334</v>
+        <v>46309.52083333334</v>
       </c>
       <c r="B148">
-        <v>2346.417</v>
+        <v>2297.336</v>
       </c>
       <c r="C148">
-        <v>2686</v>
+        <v>2386</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3475,13 +3475,13 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46308.53125</v>
+        <v>46309.53125</v>
       </c>
       <c r="B149">
-        <v>2353.978</v>
+        <v>2288.318</v>
       </c>
       <c r="C149">
-        <v>2699</v>
+        <v>2494</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3492,13 +3492,13 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46308.54166666666</v>
+        <v>46309.54166666666</v>
       </c>
       <c r="B150">
-        <v>2347.053</v>
+        <v>2317.614</v>
       </c>
       <c r="C150">
-        <v>2788</v>
+        <v>2534</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3509,13 +3509,13 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46308.55208333334</v>
+        <v>46309.55208333334</v>
       </c>
       <c r="B151">
-        <v>2353.852</v>
+        <v>2300.315</v>
       </c>
       <c r="C151">
-        <v>2779</v>
+        <v>2495</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3526,10 +3526,13 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46308.5625</v>
+        <v>46309.5625</v>
       </c>
       <c r="B152">
-        <v>2357.706</v>
+        <v>2280.91</v>
+      </c>
+      <c r="C152">
+        <v>2539</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3540,10 +3543,13 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46308.57291666666</v>
+        <v>46309.57291666666</v>
       </c>
       <c r="B153">
-        <v>2361.414</v>
+        <v>2263.522</v>
+      </c>
+      <c r="C153">
+        <v>2403</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3554,10 +3560,13 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46308.58333333334</v>
+        <v>46309.58333333334</v>
       </c>
       <c r="B154">
-        <v>2380.025</v>
+        <v>2230.336</v>
+      </c>
+      <c r="C154">
+        <v>2357</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3568,10 +3577,13 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46308.59375</v>
+        <v>46309.59375</v>
       </c>
       <c r="B155">
-        <v>2382.058</v>
+        <v>2205.166</v>
+      </c>
+      <c r="C155">
+        <v>2260</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3582,10 +3594,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46308.60416666666</v>
+        <v>46309.60416666666</v>
       </c>
       <c r="B156">
-        <v>2379.138</v>
+        <v>2178.262</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3596,10 +3608,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46308.61458333334</v>
+        <v>46309.61458333334</v>
       </c>
       <c r="B157">
-        <v>2381.592</v>
+        <v>2154.155</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3610,10 +3622,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46308.625</v>
+        <v>46309.625</v>
       </c>
       <c r="B158">
-        <v>2346.183</v>
+        <v>2138.321</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3624,10 +3636,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46308.63541666666</v>
+        <v>46309.63541666666</v>
       </c>
       <c r="B159">
-        <v>2342.452</v>
+        <v>2110.205</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3638,10 +3650,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46308.64583333334</v>
+        <v>46309.64583333334</v>
       </c>
       <c r="B160">
-        <v>2333.291</v>
+        <v>2080.831</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3652,10 +3664,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46308.65625</v>
+        <v>46309.65625</v>
       </c>
       <c r="B161">
-        <v>2324.024</v>
+        <v>2050.827</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3666,10 +3678,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46308.66666666666</v>
+        <v>46309.66666666666</v>
       </c>
       <c r="B162">
-        <v>2304.594</v>
+        <v>2018.127</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -3680,10 +3692,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46308.67708333334</v>
+        <v>46309.67708333334</v>
       </c>
       <c r="B163">
-        <v>2296.569</v>
+        <v>1967.294</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -3694,10 +3706,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46308.6875</v>
+        <v>46309.6875</v>
       </c>
       <c r="B164">
-        <v>2288.237</v>
+        <v>1919.104</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -3708,10 +3720,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46308.69791666666</v>
+        <v>46309.69791666666</v>
       </c>
       <c r="B165">
-        <v>2280.087</v>
+        <v>1873.846</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -3722,10 +3734,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46308.70833333334</v>
+        <v>46309.70833333334</v>
       </c>
       <c r="B166">
-        <v>2265.647</v>
+        <v>1807.618</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -3736,10 +3748,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46308.71875</v>
+        <v>46309.71875</v>
       </c>
       <c r="B167">
-        <v>2272.405</v>
+        <v>1762.15</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -3750,10 +3762,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46308.72916666666</v>
+        <v>46309.72916666666</v>
       </c>
       <c r="B168">
-        <v>2280.394</v>
+        <v>1716.06</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -3764,10 +3776,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46308.73958333334</v>
+        <v>46309.73958333334</v>
       </c>
       <c r="B169">
-        <v>2289.333</v>
+        <v>1674.125</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -3778,10 +3790,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46308.75</v>
+        <v>46309.75</v>
       </c>
       <c r="B170">
-        <v>2293.876</v>
+        <v>1676.529</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -3792,10 +3804,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46308.76041666666</v>
+        <v>46309.76041666666</v>
       </c>
       <c r="B171">
-        <v>2295.821</v>
+        <v>1657.854</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -3806,10 +3818,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46308.77083333334</v>
+        <v>46309.77083333334</v>
       </c>
       <c r="B172">
-        <v>2303.508</v>
+        <v>1636.225</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -3820,10 +3832,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46308.78125</v>
+        <v>46309.78125</v>
       </c>
       <c r="B173">
-        <v>2304.376</v>
+        <v>1616.017</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -3834,10 +3846,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46308.79166666666</v>
+        <v>46309.79166666666</v>
       </c>
       <c r="B174">
-        <v>2306.063</v>
+        <v>1598.004</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -3848,10 +3860,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46308.80208333334</v>
+        <v>46309.80208333334</v>
       </c>
       <c r="B175">
-        <v>2304.435</v>
+        <v>1596.037</v>
       </c>
       <c r="D175">
         <v>78</v>
@@ -3862,10 +3874,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46308.8125</v>
+        <v>46309.8125</v>
       </c>
       <c r="B176">
-        <v>2303.44</v>
+        <v>1593.61</v>
       </c>
       <c r="D176">
         <v>79</v>
@@ -3876,10 +3888,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46308.82291666666</v>
+        <v>46309.82291666666</v>
       </c>
       <c r="B177">
-        <v>2302.711</v>
+        <v>1591.66</v>
       </c>
       <c r="D177">
         <v>80</v>
@@ -3890,10 +3902,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46308.83333333334</v>
+        <v>46309.83333333334</v>
       </c>
       <c r="B178">
-        <v>2305.963</v>
+        <v>1589.105</v>
       </c>
       <c r="D178">
         <v>81</v>
@@ -3904,10 +3916,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46308.84375</v>
+        <v>46309.84375</v>
       </c>
       <c r="B179">
-        <v>2300.354</v>
+        <v>1582.822</v>
       </c>
       <c r="D179">
         <v>82</v>
@@ -3918,10 +3930,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46308.85416666666</v>
+        <v>46309.85416666666</v>
       </c>
       <c r="B180">
-        <v>2296.98</v>
+        <v>1574.842</v>
       </c>
       <c r="D180">
         <v>83</v>
@@ -3932,10 +3944,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46308.86458333334</v>
+        <v>46309.86458333334</v>
       </c>
       <c r="B181">
-        <v>2292.754</v>
+        <v>1566.252</v>
       </c>
       <c r="D181">
         <v>84</v>
@@ -3946,10 +3958,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46308.875</v>
+        <v>46309.875</v>
       </c>
       <c r="B182">
-        <v>2317.27</v>
+        <v>1559.561</v>
       </c>
       <c r="D182">
         <v>85</v>
@@ -3960,10 +3972,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46308.88541666666</v>
+        <v>46309.88541666666</v>
       </c>
       <c r="B183">
-        <v>2316.237</v>
+        <v>1557.678</v>
       </c>
       <c r="D183">
         <v>86</v>
@@ -3974,10 +3986,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46308.89583333334</v>
+        <v>46309.89583333334</v>
       </c>
       <c r="B184">
-        <v>2313.366</v>
+        <v>1554.838</v>
       </c>
       <c r="D184">
         <v>87</v>
@@ -3988,10 +4000,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46308.90625</v>
+        <v>46309.90625</v>
       </c>
       <c r="B185">
-        <v>2314.597</v>
+        <v>1552.265</v>
       </c>
       <c r="D185">
         <v>88</v>
@@ -4002,10 +4014,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46308.91666666666</v>
+        <v>46309.91666666666</v>
       </c>
       <c r="B186">
-        <v>2329.79</v>
+        <v>1547.213</v>
       </c>
       <c r="D186">
         <v>89</v>
@@ -4016,10 +4028,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46308.92708333334</v>
+        <v>46309.92708333334</v>
       </c>
       <c r="B187">
-        <v>2332.851</v>
+        <v>1543.284</v>
       </c>
       <c r="D187">
         <v>90</v>
@@ -4030,10 +4042,10 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46308.9375</v>
+        <v>46309.9375</v>
       </c>
       <c r="B188">
-        <v>2335.233</v>
+        <v>1547.448</v>
       </c>
       <c r="D188">
         <v>91</v>
@@ -4044,10 +4056,10 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46308.94791666666</v>
+        <v>46309.94791666666</v>
       </c>
       <c r="B189">
-        <v>2337.297</v>
+        <v>1552.923</v>
       </c>
       <c r="D189">
         <v>92</v>

--- a/data_fetching/Entsoe/Wind_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Wind_Production_Historical.xlsx
@@ -31,568 +31,568 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>13.10.20261</t>
-  </si>
-  <si>
-    <t>13.10.20262</t>
-  </si>
-  <si>
-    <t>13.10.20263</t>
-  </si>
-  <si>
-    <t>13.10.20264</t>
-  </si>
-  <si>
-    <t>13.10.20265</t>
-  </si>
-  <si>
-    <t>13.10.20266</t>
-  </si>
-  <si>
-    <t>13.10.20267</t>
-  </si>
-  <si>
-    <t>13.10.20268</t>
-  </si>
-  <si>
-    <t>13.10.20269</t>
-  </si>
-  <si>
-    <t>13.10.202610</t>
-  </si>
-  <si>
-    <t>13.10.202611</t>
-  </si>
-  <si>
-    <t>13.10.202612</t>
-  </si>
-  <si>
-    <t>13.10.202613</t>
-  </si>
-  <si>
-    <t>13.10.202614</t>
-  </si>
-  <si>
-    <t>13.10.202615</t>
-  </si>
-  <si>
-    <t>13.10.202616</t>
-  </si>
-  <si>
-    <t>13.10.202617</t>
-  </si>
-  <si>
-    <t>13.10.202618</t>
-  </si>
-  <si>
-    <t>13.10.202619</t>
-  </si>
-  <si>
-    <t>13.10.202620</t>
-  </si>
-  <si>
-    <t>13.10.202621</t>
-  </si>
-  <si>
-    <t>13.10.202622</t>
-  </si>
-  <si>
-    <t>13.10.202623</t>
-  </si>
-  <si>
-    <t>13.10.202624</t>
-  </si>
-  <si>
-    <t>13.10.202625</t>
-  </si>
-  <si>
-    <t>13.10.202626</t>
-  </si>
-  <si>
-    <t>13.10.202627</t>
-  </si>
-  <si>
-    <t>13.10.202628</t>
-  </si>
-  <si>
-    <t>13.10.202629</t>
-  </si>
-  <si>
-    <t>13.10.202630</t>
-  </si>
-  <si>
-    <t>13.10.202631</t>
-  </si>
-  <si>
-    <t>13.10.202632</t>
-  </si>
-  <si>
-    <t>13.10.202633</t>
-  </si>
-  <si>
-    <t>13.10.202634</t>
-  </si>
-  <si>
-    <t>13.10.202635</t>
-  </si>
-  <si>
-    <t>13.10.202636</t>
-  </si>
-  <si>
-    <t>13.10.202637</t>
-  </si>
-  <si>
-    <t>13.10.202638</t>
-  </si>
-  <si>
-    <t>13.10.202639</t>
-  </si>
-  <si>
-    <t>13.10.202640</t>
-  </si>
-  <si>
-    <t>13.10.202641</t>
-  </si>
-  <si>
-    <t>13.10.202642</t>
-  </si>
-  <si>
-    <t>13.10.202643</t>
-  </si>
-  <si>
-    <t>13.10.202644</t>
-  </si>
-  <si>
-    <t>13.10.202645</t>
-  </si>
-  <si>
-    <t>13.10.202646</t>
-  </si>
-  <si>
-    <t>13.10.202647</t>
-  </si>
-  <si>
-    <t>13.10.202648</t>
-  </si>
-  <si>
-    <t>13.10.202649</t>
-  </si>
-  <si>
-    <t>13.10.202650</t>
-  </si>
-  <si>
-    <t>13.10.202651</t>
-  </si>
-  <si>
-    <t>13.10.202652</t>
-  </si>
-  <si>
-    <t>13.10.202653</t>
-  </si>
-  <si>
-    <t>13.10.202654</t>
-  </si>
-  <si>
-    <t>13.10.202655</t>
-  </si>
-  <si>
-    <t>13.10.202656</t>
-  </si>
-  <si>
-    <t>13.10.202657</t>
-  </si>
-  <si>
-    <t>13.10.202658</t>
-  </si>
-  <si>
-    <t>13.10.202659</t>
-  </si>
-  <si>
-    <t>13.10.202660</t>
-  </si>
-  <si>
-    <t>13.10.202661</t>
-  </si>
-  <si>
-    <t>13.10.202662</t>
-  </si>
-  <si>
-    <t>13.10.202663</t>
-  </si>
-  <si>
-    <t>13.10.202664</t>
-  </si>
-  <si>
-    <t>13.10.202665</t>
-  </si>
-  <si>
-    <t>13.10.202666</t>
-  </si>
-  <si>
-    <t>13.10.202667</t>
-  </si>
-  <si>
-    <t>13.10.202668</t>
-  </si>
-  <si>
-    <t>13.10.202669</t>
-  </si>
-  <si>
-    <t>13.10.202670</t>
-  </si>
-  <si>
-    <t>13.10.202671</t>
-  </si>
-  <si>
-    <t>13.10.202672</t>
-  </si>
-  <si>
-    <t>13.10.202673</t>
-  </si>
-  <si>
-    <t>13.10.202674</t>
-  </si>
-  <si>
-    <t>13.10.202675</t>
-  </si>
-  <si>
-    <t>13.10.202676</t>
-  </si>
-  <si>
-    <t>13.10.202677</t>
-  </si>
-  <si>
-    <t>13.10.202678</t>
-  </si>
-  <si>
-    <t>13.10.202679</t>
-  </si>
-  <si>
-    <t>13.10.202680</t>
-  </si>
-  <si>
-    <t>13.10.202681</t>
-  </si>
-  <si>
-    <t>13.10.202682</t>
-  </si>
-  <si>
-    <t>13.10.202683</t>
-  </si>
-  <si>
-    <t>13.10.202684</t>
-  </si>
-  <si>
-    <t>13.10.202685</t>
-  </si>
-  <si>
-    <t>13.10.202686</t>
-  </si>
-  <si>
-    <t>13.10.202687</t>
-  </si>
-  <si>
-    <t>13.10.202688</t>
-  </si>
-  <si>
-    <t>13.10.202689</t>
-  </si>
-  <si>
-    <t>13.10.202690</t>
-  </si>
-  <si>
-    <t>13.10.202691</t>
-  </si>
-  <si>
-    <t>13.10.202692</t>
-  </si>
-  <si>
-    <t>13.10.202693</t>
-  </si>
-  <si>
-    <t>13.10.202694</t>
-  </si>
-  <si>
-    <t>13.10.202695</t>
-  </si>
-  <si>
-    <t>13.10.202696</t>
-  </si>
-  <si>
-    <t>14.10.20261</t>
-  </si>
-  <si>
-    <t>14.10.20262</t>
-  </si>
-  <si>
-    <t>14.10.20263</t>
-  </si>
-  <si>
-    <t>14.10.20264</t>
-  </si>
-  <si>
-    <t>14.10.20265</t>
-  </si>
-  <si>
-    <t>14.10.20266</t>
-  </si>
-  <si>
-    <t>14.10.20267</t>
-  </si>
-  <si>
-    <t>14.10.20268</t>
-  </si>
-  <si>
-    <t>14.10.20269</t>
-  </si>
-  <si>
-    <t>14.10.202610</t>
-  </si>
-  <si>
-    <t>14.10.202611</t>
-  </si>
-  <si>
-    <t>14.10.202612</t>
-  </si>
-  <si>
-    <t>14.10.202613</t>
-  </si>
-  <si>
-    <t>14.10.202614</t>
-  </si>
-  <si>
-    <t>14.10.202615</t>
-  </si>
-  <si>
-    <t>14.10.202616</t>
-  </si>
-  <si>
-    <t>14.10.202617</t>
-  </si>
-  <si>
-    <t>14.10.202618</t>
-  </si>
-  <si>
-    <t>14.10.202619</t>
-  </si>
-  <si>
-    <t>14.10.202620</t>
-  </si>
-  <si>
-    <t>14.10.202621</t>
-  </si>
-  <si>
-    <t>14.10.202622</t>
-  </si>
-  <si>
-    <t>14.10.202623</t>
-  </si>
-  <si>
-    <t>14.10.202624</t>
-  </si>
-  <si>
-    <t>14.10.202625</t>
-  </si>
-  <si>
-    <t>14.10.202626</t>
-  </si>
-  <si>
-    <t>14.10.202627</t>
-  </si>
-  <si>
-    <t>14.10.202628</t>
-  </si>
-  <si>
-    <t>14.10.202629</t>
-  </si>
-  <si>
-    <t>14.10.202630</t>
-  </si>
-  <si>
-    <t>14.10.202631</t>
-  </si>
-  <si>
-    <t>14.10.202632</t>
-  </si>
-  <si>
-    <t>14.10.202633</t>
-  </si>
-  <si>
-    <t>14.10.202634</t>
-  </si>
-  <si>
-    <t>14.10.202635</t>
-  </si>
-  <si>
-    <t>14.10.202636</t>
-  </si>
-  <si>
-    <t>14.10.202637</t>
-  </si>
-  <si>
-    <t>14.10.202638</t>
-  </si>
-  <si>
-    <t>14.10.202639</t>
-  </si>
-  <si>
-    <t>14.10.202640</t>
-  </si>
-  <si>
-    <t>14.10.202641</t>
-  </si>
-  <si>
-    <t>14.10.202642</t>
-  </si>
-  <si>
-    <t>14.10.202643</t>
-  </si>
-  <si>
-    <t>14.10.202644</t>
-  </si>
-  <si>
-    <t>14.10.202645</t>
-  </si>
-  <si>
-    <t>14.10.202646</t>
-  </si>
-  <si>
-    <t>14.10.202647</t>
-  </si>
-  <si>
-    <t>14.10.202648</t>
-  </si>
-  <si>
-    <t>14.10.202649</t>
-  </si>
-  <si>
-    <t>14.10.202650</t>
-  </si>
-  <si>
-    <t>14.10.202651</t>
-  </si>
-  <si>
-    <t>14.10.202652</t>
-  </si>
-  <si>
-    <t>14.10.202653</t>
-  </si>
-  <si>
-    <t>14.10.202654</t>
-  </si>
-  <si>
-    <t>14.10.202655</t>
-  </si>
-  <si>
-    <t>14.10.202656</t>
-  </si>
-  <si>
-    <t>14.10.202657</t>
-  </si>
-  <si>
-    <t>14.10.202658</t>
-  </si>
-  <si>
-    <t>14.10.202659</t>
-  </si>
-  <si>
-    <t>14.10.202660</t>
-  </si>
-  <si>
-    <t>14.10.202661</t>
-  </si>
-  <si>
-    <t>14.10.202662</t>
-  </si>
-  <si>
-    <t>14.10.202663</t>
-  </si>
-  <si>
-    <t>14.10.202664</t>
-  </si>
-  <si>
-    <t>14.10.202665</t>
-  </si>
-  <si>
-    <t>14.10.202666</t>
-  </si>
-  <si>
-    <t>14.10.202667</t>
-  </si>
-  <si>
-    <t>14.10.202668</t>
-  </si>
-  <si>
-    <t>14.10.202669</t>
-  </si>
-  <si>
-    <t>14.10.202670</t>
-  </si>
-  <si>
-    <t>14.10.202671</t>
-  </si>
-  <si>
-    <t>14.10.202672</t>
-  </si>
-  <si>
-    <t>14.10.202673</t>
-  </si>
-  <si>
-    <t>14.10.202674</t>
-  </si>
-  <si>
-    <t>14.10.202675</t>
-  </si>
-  <si>
-    <t>14.10.202676</t>
-  </si>
-  <si>
-    <t>14.10.202677</t>
-  </si>
-  <si>
-    <t>14.10.202678</t>
-  </si>
-  <si>
-    <t>14.10.202679</t>
-  </si>
-  <si>
-    <t>14.10.202680</t>
-  </si>
-  <si>
-    <t>14.10.202681</t>
-  </si>
-  <si>
-    <t>14.10.202682</t>
-  </si>
-  <si>
-    <t>14.10.202683</t>
-  </si>
-  <si>
-    <t>14.10.202684</t>
-  </si>
-  <si>
-    <t>14.10.202685</t>
-  </si>
-  <si>
-    <t>14.10.202686</t>
-  </si>
-  <si>
-    <t>14.10.202687</t>
-  </si>
-  <si>
-    <t>14.10.202688</t>
-  </si>
-  <si>
-    <t>14.10.202689</t>
-  </si>
-  <si>
-    <t>14.10.202690</t>
-  </si>
-  <si>
-    <t>14.10.202691</t>
-  </si>
-  <si>
-    <t>14.10.202692</t>
+    <t>15.10.20261</t>
+  </si>
+  <si>
+    <t>15.10.20262</t>
+  </si>
+  <si>
+    <t>15.10.20263</t>
+  </si>
+  <si>
+    <t>15.10.20264</t>
+  </si>
+  <si>
+    <t>15.10.20265</t>
+  </si>
+  <si>
+    <t>15.10.20266</t>
+  </si>
+  <si>
+    <t>15.10.20267</t>
+  </si>
+  <si>
+    <t>15.10.20268</t>
+  </si>
+  <si>
+    <t>15.10.20269</t>
+  </si>
+  <si>
+    <t>15.10.202610</t>
+  </si>
+  <si>
+    <t>15.10.202611</t>
+  </si>
+  <si>
+    <t>15.10.202612</t>
+  </si>
+  <si>
+    <t>15.10.202613</t>
+  </si>
+  <si>
+    <t>15.10.202614</t>
+  </si>
+  <si>
+    <t>15.10.202615</t>
+  </si>
+  <si>
+    <t>15.10.202616</t>
+  </si>
+  <si>
+    <t>15.10.202617</t>
+  </si>
+  <si>
+    <t>15.10.202618</t>
+  </si>
+  <si>
+    <t>15.10.202619</t>
+  </si>
+  <si>
+    <t>15.10.202620</t>
+  </si>
+  <si>
+    <t>15.10.202621</t>
+  </si>
+  <si>
+    <t>15.10.202622</t>
+  </si>
+  <si>
+    <t>15.10.202623</t>
+  </si>
+  <si>
+    <t>15.10.202624</t>
+  </si>
+  <si>
+    <t>15.10.202625</t>
+  </si>
+  <si>
+    <t>15.10.202626</t>
+  </si>
+  <si>
+    <t>15.10.202627</t>
+  </si>
+  <si>
+    <t>15.10.202628</t>
+  </si>
+  <si>
+    <t>15.10.202629</t>
+  </si>
+  <si>
+    <t>15.10.202630</t>
+  </si>
+  <si>
+    <t>15.10.202631</t>
+  </si>
+  <si>
+    <t>15.10.202632</t>
+  </si>
+  <si>
+    <t>15.10.202633</t>
+  </si>
+  <si>
+    <t>15.10.202634</t>
+  </si>
+  <si>
+    <t>15.10.202635</t>
+  </si>
+  <si>
+    <t>15.10.202636</t>
+  </si>
+  <si>
+    <t>15.10.202637</t>
+  </si>
+  <si>
+    <t>15.10.202638</t>
+  </si>
+  <si>
+    <t>15.10.202639</t>
+  </si>
+  <si>
+    <t>15.10.202640</t>
+  </si>
+  <si>
+    <t>15.10.202641</t>
+  </si>
+  <si>
+    <t>15.10.202642</t>
+  </si>
+  <si>
+    <t>15.10.202643</t>
+  </si>
+  <si>
+    <t>15.10.202644</t>
+  </si>
+  <si>
+    <t>15.10.202645</t>
+  </si>
+  <si>
+    <t>15.10.202646</t>
+  </si>
+  <si>
+    <t>15.10.202647</t>
+  </si>
+  <si>
+    <t>15.10.202648</t>
+  </si>
+  <si>
+    <t>15.10.202649</t>
+  </si>
+  <si>
+    <t>15.10.202650</t>
+  </si>
+  <si>
+    <t>15.10.202651</t>
+  </si>
+  <si>
+    <t>15.10.202652</t>
+  </si>
+  <si>
+    <t>15.10.202653</t>
+  </si>
+  <si>
+    <t>15.10.202654</t>
+  </si>
+  <si>
+    <t>15.10.202655</t>
+  </si>
+  <si>
+    <t>15.10.202656</t>
+  </si>
+  <si>
+    <t>15.10.202657</t>
+  </si>
+  <si>
+    <t>15.10.202658</t>
+  </si>
+  <si>
+    <t>15.10.202659</t>
+  </si>
+  <si>
+    <t>15.10.202660</t>
+  </si>
+  <si>
+    <t>15.10.202661</t>
+  </si>
+  <si>
+    <t>15.10.202662</t>
+  </si>
+  <si>
+    <t>15.10.202663</t>
+  </si>
+  <si>
+    <t>15.10.202664</t>
+  </si>
+  <si>
+    <t>15.10.202665</t>
+  </si>
+  <si>
+    <t>15.10.202666</t>
+  </si>
+  <si>
+    <t>15.10.202667</t>
+  </si>
+  <si>
+    <t>15.10.202668</t>
+  </si>
+  <si>
+    <t>15.10.202669</t>
+  </si>
+  <si>
+    <t>15.10.202670</t>
+  </si>
+  <si>
+    <t>15.10.202671</t>
+  </si>
+  <si>
+    <t>15.10.202672</t>
+  </si>
+  <si>
+    <t>15.10.202673</t>
+  </si>
+  <si>
+    <t>15.10.202674</t>
+  </si>
+  <si>
+    <t>15.10.202675</t>
+  </si>
+  <si>
+    <t>15.10.202676</t>
+  </si>
+  <si>
+    <t>15.10.202677</t>
+  </si>
+  <si>
+    <t>15.10.202678</t>
+  </si>
+  <si>
+    <t>15.10.202679</t>
+  </si>
+  <si>
+    <t>15.10.202680</t>
+  </si>
+  <si>
+    <t>15.10.202681</t>
+  </si>
+  <si>
+    <t>15.10.202682</t>
+  </si>
+  <si>
+    <t>15.10.202683</t>
+  </si>
+  <si>
+    <t>15.10.202684</t>
+  </si>
+  <si>
+    <t>15.10.202685</t>
+  </si>
+  <si>
+    <t>15.10.202686</t>
+  </si>
+  <si>
+    <t>15.10.202687</t>
+  </si>
+  <si>
+    <t>15.10.202688</t>
+  </si>
+  <si>
+    <t>15.10.202689</t>
+  </si>
+  <si>
+    <t>15.10.202690</t>
+  </si>
+  <si>
+    <t>15.10.202691</t>
+  </si>
+  <si>
+    <t>15.10.202692</t>
+  </si>
+  <si>
+    <t>15.10.202693</t>
+  </si>
+  <si>
+    <t>15.10.202694</t>
+  </si>
+  <si>
+    <t>15.10.202695</t>
+  </si>
+  <si>
+    <t>15.10.202696</t>
+  </si>
+  <si>
+    <t>16.10.20261</t>
+  </si>
+  <si>
+    <t>16.10.20262</t>
+  </si>
+  <si>
+    <t>16.10.20263</t>
+  </si>
+  <si>
+    <t>16.10.20264</t>
+  </si>
+  <si>
+    <t>16.10.20265</t>
+  </si>
+  <si>
+    <t>16.10.20266</t>
+  </si>
+  <si>
+    <t>16.10.20267</t>
+  </si>
+  <si>
+    <t>16.10.20268</t>
+  </si>
+  <si>
+    <t>16.10.20269</t>
+  </si>
+  <si>
+    <t>16.10.202610</t>
+  </si>
+  <si>
+    <t>16.10.202611</t>
+  </si>
+  <si>
+    <t>16.10.202612</t>
+  </si>
+  <si>
+    <t>16.10.202613</t>
+  </si>
+  <si>
+    <t>16.10.202614</t>
+  </si>
+  <si>
+    <t>16.10.202615</t>
+  </si>
+  <si>
+    <t>16.10.202616</t>
+  </si>
+  <si>
+    <t>16.10.202617</t>
+  </si>
+  <si>
+    <t>16.10.202618</t>
+  </si>
+  <si>
+    <t>16.10.202619</t>
+  </si>
+  <si>
+    <t>16.10.202620</t>
+  </si>
+  <si>
+    <t>16.10.202621</t>
+  </si>
+  <si>
+    <t>16.10.202622</t>
+  </si>
+  <si>
+    <t>16.10.202623</t>
+  </si>
+  <si>
+    <t>16.10.202624</t>
+  </si>
+  <si>
+    <t>16.10.202625</t>
+  </si>
+  <si>
+    <t>16.10.202626</t>
+  </si>
+  <si>
+    <t>16.10.202627</t>
+  </si>
+  <si>
+    <t>16.10.202628</t>
+  </si>
+  <si>
+    <t>16.10.202629</t>
+  </si>
+  <si>
+    <t>16.10.202630</t>
+  </si>
+  <si>
+    <t>16.10.202631</t>
+  </si>
+  <si>
+    <t>16.10.202632</t>
+  </si>
+  <si>
+    <t>16.10.202633</t>
+  </si>
+  <si>
+    <t>16.10.202634</t>
+  </si>
+  <si>
+    <t>16.10.202635</t>
+  </si>
+  <si>
+    <t>16.10.202636</t>
+  </si>
+  <si>
+    <t>16.10.202637</t>
+  </si>
+  <si>
+    <t>16.10.202638</t>
+  </si>
+  <si>
+    <t>16.10.202639</t>
+  </si>
+  <si>
+    <t>16.10.202640</t>
+  </si>
+  <si>
+    <t>16.10.202641</t>
+  </si>
+  <si>
+    <t>16.10.202642</t>
+  </si>
+  <si>
+    <t>16.10.202643</t>
+  </si>
+  <si>
+    <t>16.10.202644</t>
+  </si>
+  <si>
+    <t>16.10.202645</t>
+  </si>
+  <si>
+    <t>16.10.202646</t>
+  </si>
+  <si>
+    <t>16.10.202647</t>
+  </si>
+  <si>
+    <t>16.10.202648</t>
+  </si>
+  <si>
+    <t>16.10.202649</t>
+  </si>
+  <si>
+    <t>16.10.202650</t>
+  </si>
+  <si>
+    <t>16.10.202651</t>
+  </si>
+  <si>
+    <t>16.10.202652</t>
+  </si>
+  <si>
+    <t>16.10.202653</t>
+  </si>
+  <si>
+    <t>16.10.202654</t>
+  </si>
+  <si>
+    <t>16.10.202655</t>
+  </si>
+  <si>
+    <t>16.10.202656</t>
+  </si>
+  <si>
+    <t>16.10.202657</t>
+  </si>
+  <si>
+    <t>16.10.202658</t>
+  </si>
+  <si>
+    <t>16.10.202659</t>
+  </si>
+  <si>
+    <t>16.10.202660</t>
+  </si>
+  <si>
+    <t>16.10.202661</t>
+  </si>
+  <si>
+    <t>16.10.202662</t>
+  </si>
+  <si>
+    <t>16.10.202663</t>
+  </si>
+  <si>
+    <t>16.10.202664</t>
+  </si>
+  <si>
+    <t>16.10.202665</t>
+  </si>
+  <si>
+    <t>16.10.202666</t>
+  </si>
+  <si>
+    <t>16.10.202667</t>
+  </si>
+  <si>
+    <t>16.10.202668</t>
+  </si>
+  <si>
+    <t>16.10.202669</t>
+  </si>
+  <si>
+    <t>16.10.202670</t>
+  </si>
+  <si>
+    <t>16.10.202671</t>
+  </si>
+  <si>
+    <t>16.10.202672</t>
+  </si>
+  <si>
+    <t>16.10.202673</t>
+  </si>
+  <si>
+    <t>16.10.202674</t>
+  </si>
+  <si>
+    <t>16.10.202675</t>
+  </si>
+  <si>
+    <t>16.10.202676</t>
+  </si>
+  <si>
+    <t>16.10.202677</t>
+  </si>
+  <si>
+    <t>16.10.202678</t>
+  </si>
+  <si>
+    <t>16.10.202679</t>
+  </si>
+  <si>
+    <t>16.10.202680</t>
+  </si>
+  <si>
+    <t>16.10.202681</t>
+  </si>
+  <si>
+    <t>16.10.202682</t>
+  </si>
+  <si>
+    <t>16.10.202683</t>
+  </si>
+  <si>
+    <t>16.10.202684</t>
+  </si>
+  <si>
+    <t>16.10.202685</t>
+  </si>
+  <si>
+    <t>16.10.202686</t>
+  </si>
+  <si>
+    <t>16.10.202687</t>
+  </si>
+  <si>
+    <t>16.10.202688</t>
+  </si>
+  <si>
+    <t>16.10.202689</t>
+  </si>
+  <si>
+    <t>16.10.202690</t>
+  </si>
+  <si>
+    <t>16.10.202691</t>
+  </si>
+  <si>
+    <t>16.10.202692</t>
   </si>
 </sst>
 </file>
@@ -976,13 +976,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
       <c r="B2">
-        <v>1941.64</v>
+        <v>1831.749</v>
       </c>
       <c r="C2">
-        <v>2259</v>
+        <v>1735</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -993,13 +993,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46308.01041666666</v>
+        <v>46310.01041666666</v>
       </c>
       <c r="B3">
-        <v>1957.481</v>
+        <v>1837.179</v>
       </c>
       <c r="C3">
-        <v>2236</v>
+        <v>1703</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1010,13 +1010,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46308.02083333334</v>
+        <v>46310.02083333334</v>
       </c>
       <c r="B4">
-        <v>1973.214</v>
+        <v>1839.563</v>
       </c>
       <c r="C4">
-        <v>2206</v>
+        <v>1696</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1027,13 +1027,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46308.03125</v>
+        <v>46310.03125</v>
       </c>
       <c r="B5">
-        <v>1988.772</v>
+        <v>1842.049</v>
       </c>
       <c r="C5">
-        <v>2171</v>
+        <v>1698</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1044,13 +1044,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46308.04166666666</v>
+        <v>46310.04166666666</v>
       </c>
       <c r="B6">
-        <v>1980.982</v>
+        <v>1811.621</v>
       </c>
       <c r="C6">
-        <v>2133</v>
+        <v>1709</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1061,13 +1061,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46308.05208333334</v>
+        <v>46310.05208333334</v>
       </c>
       <c r="B7">
-        <v>2017.875</v>
+        <v>1804.002</v>
       </c>
       <c r="C7">
-        <v>2153</v>
+        <v>1734</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1078,13 +1078,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46308.0625</v>
+        <v>46310.0625</v>
       </c>
       <c r="B8">
-        <v>2041.072</v>
+        <v>1801.719</v>
       </c>
       <c r="C8">
-        <v>2170</v>
+        <v>1792</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1095,13 +1095,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46308.07291666666</v>
+        <v>46310.07291666666</v>
       </c>
       <c r="B9">
-        <v>2052.74</v>
+        <v>1795.08</v>
       </c>
       <c r="C9">
-        <v>2161</v>
+        <v>1843</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1112,13 +1112,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46308.08333333334</v>
+        <v>46310.08333333334</v>
       </c>
       <c r="B10">
-        <v>2060.445</v>
+        <v>1777.478</v>
       </c>
       <c r="C10">
-        <v>2161</v>
+        <v>1879</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1129,13 +1129,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46308.09375</v>
+        <v>46310.09375</v>
       </c>
       <c r="B11">
-        <v>2057.801</v>
+        <v>1764.128</v>
       </c>
       <c r="C11">
-        <v>2173</v>
+        <v>1827</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1146,13 +1146,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46308.10416666666</v>
+        <v>46310.10416666666</v>
       </c>
       <c r="B12">
-        <v>2058.189</v>
+        <v>1761</v>
       </c>
       <c r="C12">
-        <v>2153</v>
+        <v>1767</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1163,13 +1163,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46308.11458333334</v>
+        <v>46310.11458333334</v>
       </c>
       <c r="B13">
-        <v>2056.84</v>
+        <v>1749.048</v>
       </c>
       <c r="C13">
-        <v>2112</v>
+        <v>1784</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1180,13 +1180,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46308.125</v>
+        <v>46310.125</v>
       </c>
       <c r="B14">
-        <v>2037.552</v>
+        <v>1753.55</v>
       </c>
       <c r="C14">
-        <v>2118</v>
+        <v>1803</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1197,13 +1197,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46308.13541666666</v>
+        <v>46310.13541666666</v>
       </c>
       <c r="B15">
-        <v>2042.185</v>
+        <v>1736.304</v>
       </c>
       <c r="C15">
-        <v>2095</v>
+        <v>1842</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1214,13 +1214,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46308.14583333334</v>
+        <v>46310.14583333334</v>
       </c>
       <c r="B16">
-        <v>2048.055</v>
+        <v>1713.341</v>
       </c>
       <c r="C16">
-        <v>2110</v>
+        <v>1904</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1231,13 +1231,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46308.15625</v>
+        <v>46310.15625</v>
       </c>
       <c r="B17">
-        <v>2051.478</v>
+        <v>1694.465</v>
       </c>
       <c r="C17">
-        <v>2145</v>
+        <v>1968</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1248,13 +1248,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46308.16666666666</v>
+        <v>46310.16666666666</v>
       </c>
       <c r="B18">
-        <v>2055.868</v>
+        <v>1665.902</v>
       </c>
       <c r="C18">
-        <v>2141</v>
+        <v>1971</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1265,13 +1265,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46308.17708333334</v>
+        <v>46310.17708333334</v>
       </c>
       <c r="B19">
-        <v>2054.967</v>
+        <v>1643.951</v>
       </c>
       <c r="C19">
-        <v>2150</v>
+        <v>1883</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1282,13 +1282,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46308.1875</v>
+        <v>46310.1875</v>
       </c>
       <c r="B20">
-        <v>2051.248</v>
+        <v>1625.348</v>
       </c>
       <c r="C20">
-        <v>2126</v>
+        <v>1830</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1299,13 +1299,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46308.19791666666</v>
+        <v>46310.19791666666</v>
       </c>
       <c r="B21">
-        <v>2053.857</v>
+        <v>1617.244</v>
       </c>
       <c r="C21">
-        <v>2139</v>
+        <v>1726</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1316,13 +1316,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46308.20833333334</v>
+        <v>46310.20833333334</v>
       </c>
       <c r="B22">
-        <v>2104.469</v>
+        <v>1585.641</v>
       </c>
       <c r="C22">
-        <v>2201</v>
+        <v>1718</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1333,13 +1333,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46308.21875</v>
+        <v>46310.21875</v>
       </c>
       <c r="B23">
-        <v>2111.796</v>
+        <v>1564.972</v>
       </c>
       <c r="C23">
-        <v>2305</v>
+        <v>1686</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1350,13 +1350,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46308.22916666666</v>
+        <v>46310.22916666666</v>
       </c>
       <c r="B24">
-        <v>2118.405</v>
+        <v>1550.213</v>
       </c>
       <c r="C24">
-        <v>2397</v>
+        <v>1632</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1367,13 +1367,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46308.23958333334</v>
+        <v>46310.23958333334</v>
       </c>
       <c r="B25">
-        <v>2124.492</v>
+        <v>1531.329</v>
       </c>
       <c r="C25">
-        <v>2433</v>
+        <v>1613</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1384,13 +1384,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46308.25</v>
+        <v>46310.25</v>
       </c>
       <c r="B26">
-        <v>2113.498</v>
+        <v>1469.595</v>
       </c>
       <c r="C26">
-        <v>2466</v>
+        <v>1589</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1401,13 +1401,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46308.26041666666</v>
+        <v>46310.26041666666</v>
       </c>
       <c r="B27">
-        <v>2128.737</v>
+        <v>1455.824</v>
       </c>
       <c r="C27">
-        <v>2442</v>
+        <v>1486</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1418,13 +1418,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46308.27083333334</v>
+        <v>46310.27083333334</v>
       </c>
       <c r="B28">
-        <v>2132.841</v>
+        <v>1438.289</v>
       </c>
       <c r="C28">
-        <v>2426</v>
+        <v>1453</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1435,13 +1435,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46308.28125</v>
+        <v>46310.28125</v>
       </c>
       <c r="B29">
-        <v>2145.936</v>
+        <v>1427.149</v>
       </c>
       <c r="C29">
-        <v>2464</v>
+        <v>1423</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1452,13 +1452,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46308.29166666666</v>
+        <v>46310.29166666666</v>
       </c>
       <c r="B30">
-        <v>2182.844</v>
+        <v>1418.34</v>
       </c>
       <c r="C30">
-        <v>2522</v>
+        <v>1351</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1469,13 +1469,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46308.30208333334</v>
+        <v>46310.30208333334</v>
       </c>
       <c r="B31">
-        <v>2224.695</v>
+        <v>1405.981</v>
       </c>
       <c r="C31">
-        <v>2573</v>
+        <v>1294</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1486,13 +1486,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46308.3125</v>
+        <v>46310.3125</v>
       </c>
       <c r="B32">
-        <v>2261.349</v>
+        <v>1391.904</v>
       </c>
       <c r="C32">
-        <v>2597</v>
+        <v>1298</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1503,13 +1503,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46308.32291666666</v>
+        <v>46310.32291666666</v>
       </c>
       <c r="B33">
-        <v>2266.463</v>
+        <v>1385.515</v>
       </c>
       <c r="C33">
-        <v>2609</v>
+        <v>1245</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1520,13 +1520,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46308.33333333334</v>
+        <v>46310.33333333334</v>
       </c>
       <c r="B34">
-        <v>2271.582</v>
+        <v>1378.261</v>
       </c>
       <c r="C34">
-        <v>2601</v>
+        <v>1097</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1537,13 +1537,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46308.34375</v>
+        <v>46310.34375</v>
       </c>
       <c r="B35">
-        <v>2274.897</v>
+        <v>1350.894</v>
       </c>
       <c r="C35">
-        <v>2627</v>
+        <v>989</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1554,13 +1554,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46308.35416666666</v>
+        <v>46310.35416666666</v>
       </c>
       <c r="B36">
-        <v>2260.406</v>
+        <v>1322.854</v>
       </c>
       <c r="C36">
-        <v>2662</v>
+        <v>888</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1571,13 +1571,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46308.36458333334</v>
+        <v>46310.36458333334</v>
       </c>
       <c r="B37">
-        <v>2262.916</v>
+        <v>1283.976</v>
       </c>
       <c r="C37">
-        <v>2656</v>
+        <v>825</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1588,13 +1588,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46308.375</v>
+        <v>46310.375</v>
       </c>
       <c r="B38">
-        <v>2238.129</v>
+        <v>1250.559</v>
       </c>
       <c r="C38">
-        <v>2650</v>
+        <v>885</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1605,13 +1605,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46308.38541666666</v>
+        <v>46310.38541666666</v>
       </c>
       <c r="B39">
-        <v>2249.516</v>
+        <v>1278.322</v>
       </c>
       <c r="C39">
-        <v>2648</v>
+        <v>1033</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1622,13 +1622,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46308.39583333334</v>
+        <v>46310.39583333334</v>
       </c>
       <c r="B40">
-        <v>2257.31</v>
+        <v>1306.267</v>
       </c>
       <c r="C40">
-        <v>2672</v>
+        <v>1128</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1639,13 +1639,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46308.40625</v>
+        <v>46310.40625</v>
       </c>
       <c r="B41">
-        <v>2265.23</v>
+        <v>1333.993</v>
       </c>
       <c r="C41">
-        <v>2667</v>
+        <v>1193</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1656,13 +1656,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46308.41666666666</v>
+        <v>46310.41666666666</v>
       </c>
       <c r="B42">
-        <v>2247.099</v>
+        <v>1386.432</v>
       </c>
       <c r="C42">
-        <v>2684</v>
+        <v>1228</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1673,13 +1673,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46308.42708333334</v>
+        <v>46310.42708333334</v>
       </c>
       <c r="B43">
-        <v>2267.11</v>
+        <v>1436.951</v>
       </c>
       <c r="C43">
-        <v>2679</v>
+        <v>1285</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1690,13 +1690,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46308.4375</v>
+        <v>46310.4375</v>
       </c>
       <c r="B44">
-        <v>2286.18</v>
+        <v>1487.893</v>
       </c>
       <c r="C44">
-        <v>2672</v>
+        <v>1352</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1707,13 +1707,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46308.44791666666</v>
+        <v>46310.44791666666</v>
       </c>
       <c r="B45">
-        <v>2305.898</v>
+        <v>1545.831</v>
       </c>
       <c r="C45">
-        <v>2651</v>
+        <v>1463</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1724,13 +1724,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46308.45833333334</v>
+        <v>46310.45833333334</v>
       </c>
       <c r="B46">
-        <v>2329.751</v>
+        <v>1602.801</v>
       </c>
       <c r="C46">
-        <v>2668</v>
+        <v>1546</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1741,13 +1741,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46308.46875</v>
+        <v>46310.46875</v>
       </c>
       <c r="B47">
-        <v>2339.796</v>
+        <v>1646.772</v>
       </c>
       <c r="C47">
-        <v>2687</v>
+        <v>1700</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1758,13 +1758,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46308.47916666666</v>
+        <v>46310.47916666666</v>
       </c>
       <c r="B48">
-        <v>2351.296</v>
+        <v>1688.253</v>
       </c>
       <c r="C48">
-        <v>2701</v>
+        <v>1781</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1775,13 +1775,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46308.48958333334</v>
+        <v>46310.48958333334</v>
       </c>
       <c r="B49">
-        <v>2361.946</v>
+        <v>1723.599</v>
       </c>
       <c r="C49">
-        <v>2704</v>
+        <v>1864</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1792,13 +1792,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46308.5</v>
+        <v>46310.5</v>
       </c>
       <c r="B50">
-        <v>2333.141</v>
+        <v>1769.531</v>
       </c>
       <c r="C50">
-        <v>2678</v>
+        <v>2044</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1809,13 +1809,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46308.51041666666</v>
+        <v>46310.51041666666</v>
       </c>
       <c r="B51">
-        <v>2339.899</v>
+        <v>1803.827</v>
       </c>
       <c r="C51">
-        <v>2667</v>
+        <v>2050</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1826,13 +1826,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46308.52083333334</v>
+        <v>46310.52083333334</v>
       </c>
       <c r="B52">
-        <v>2346.417</v>
+        <v>1835.886</v>
       </c>
       <c r="C52">
-        <v>2686</v>
+        <v>1966</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1843,13 +1843,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46308.53125</v>
+        <v>46310.53125</v>
       </c>
       <c r="B53">
-        <v>2353.978</v>
+        <v>1868.236</v>
       </c>
       <c r="C53">
-        <v>2699</v>
+        <v>1816</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1860,13 +1860,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46308.54166666666</v>
+        <v>46310.54166666666</v>
       </c>
       <c r="B54">
-        <v>2347.053</v>
+        <v>1901.065</v>
       </c>
       <c r="C54">
-        <v>2788</v>
+        <v>1881</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1877,13 +1877,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46308.55208333334</v>
+        <v>46310.55208333334</v>
       </c>
       <c r="B55">
-        <v>2353.852</v>
+        <v>1911.647</v>
       </c>
       <c r="C55">
-        <v>2779</v>
+        <v>1906</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1894,13 +1894,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46308.5625</v>
+        <v>46310.5625</v>
       </c>
       <c r="B56">
-        <v>2357.706</v>
+        <v>1917.017</v>
       </c>
       <c r="C56">
-        <v>2739</v>
+        <v>1985</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1911,13 +1911,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46308.57291666666</v>
+        <v>46310.57291666666</v>
       </c>
       <c r="B57">
-        <v>2361.414</v>
+        <v>1921.364</v>
       </c>
       <c r="C57">
-        <v>2730</v>
+        <v>2024</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1928,13 +1928,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46308.58333333334</v>
+        <v>46310.58333333334</v>
       </c>
       <c r="B58">
-        <v>2380.025</v>
+        <v>1935.575</v>
       </c>
       <c r="C58">
-        <v>2738</v>
+        <v>2014</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1945,13 +1945,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46308.59375</v>
+        <v>46310.59375</v>
       </c>
       <c r="B59">
-        <v>2382.058</v>
+        <v>1901.823</v>
       </c>
       <c r="C59">
-        <v>2730</v>
+        <v>1960</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1962,13 +1962,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46308.60416666666</v>
+        <v>46310.60416666666</v>
       </c>
       <c r="B60">
-        <v>2379.138</v>
+        <v>1867.47</v>
       </c>
       <c r="C60">
-        <v>2679</v>
+        <v>2050</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1979,13 +1979,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46308.61458333334</v>
+        <v>46310.61458333334</v>
       </c>
       <c r="B61">
-        <v>2381.592</v>
+        <v>1831.503</v>
       </c>
       <c r="C61">
-        <v>2616</v>
+        <v>2207</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -1996,13 +1996,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46308.625</v>
+        <v>46310.625</v>
       </c>
       <c r="B62">
-        <v>2346.183</v>
+        <v>1780.797</v>
       </c>
       <c r="C62">
-        <v>2649</v>
+        <v>2207</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2013,13 +2013,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46308.63541666666</v>
+        <v>46310.63541666666</v>
       </c>
       <c r="B63">
-        <v>2342.452</v>
+        <v>1714.992</v>
       </c>
       <c r="C63">
-        <v>2670</v>
+        <v>2163</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2030,13 +2030,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46308.64583333334</v>
+        <v>46310.64583333334</v>
       </c>
       <c r="B64">
-        <v>2333.291</v>
+        <v>1651.315</v>
       </c>
       <c r="C64">
-        <v>2627</v>
+        <v>2110</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2047,13 +2047,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46308.65625</v>
+        <v>46310.65625</v>
       </c>
       <c r="B65">
-        <v>2324.024</v>
+        <v>1589.091</v>
       </c>
       <c r="C65">
-        <v>2537</v>
+        <v>2154</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2064,13 +2064,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46308.66666666666</v>
+        <v>46310.66666666666</v>
       </c>
       <c r="B66">
-        <v>2304.594</v>
+        <v>1399.738</v>
       </c>
       <c r="C66">
-        <v>2532</v>
+        <v>2103</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2081,13 +2081,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46308.67708333334</v>
+        <v>46310.67708333334</v>
       </c>
       <c r="B67">
-        <v>2296.569</v>
+        <v>1344.638</v>
       </c>
       <c r="C67">
-        <v>2464</v>
+        <v>1991</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2098,13 +2098,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46308.6875</v>
+        <v>46310.6875</v>
       </c>
       <c r="B68">
-        <v>2288.237</v>
+        <v>1293.719</v>
       </c>
       <c r="C68">
-        <v>2403</v>
+        <v>1923</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2115,13 +2115,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46308.69791666666</v>
+        <v>46310.69791666666</v>
       </c>
       <c r="B69">
-        <v>2280.087</v>
+        <v>1246.164</v>
       </c>
       <c r="C69">
-        <v>2354</v>
+        <v>1834</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2132,13 +2132,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46308.70833333334</v>
+        <v>46310.70833333334</v>
       </c>
       <c r="B70">
-        <v>2265.647</v>
+        <v>1199.716</v>
       </c>
       <c r="C70">
-        <v>2346</v>
+        <v>1738</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2149,13 +2149,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46308.71875</v>
+        <v>46310.71875</v>
       </c>
       <c r="B71">
-        <v>2272.405</v>
+        <v>1187.677</v>
       </c>
       <c r="C71">
-        <v>2337</v>
+        <v>1632</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2166,13 +2166,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46308.72916666666</v>
+        <v>46310.72916666666</v>
       </c>
       <c r="B72">
-        <v>2280.394</v>
+        <v>1176.972</v>
       </c>
       <c r="C72">
-        <v>2336</v>
+        <v>1542</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2183,13 +2183,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46308.73958333334</v>
+        <v>46310.73958333334</v>
       </c>
       <c r="B73">
-        <v>2289.333</v>
+        <v>1170.283</v>
       </c>
       <c r="C73">
-        <v>2257</v>
+        <v>1585</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2200,13 +2200,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46308.75</v>
+        <v>46310.75</v>
       </c>
       <c r="B74">
-        <v>2293.876</v>
+        <v>1161.014</v>
       </c>
       <c r="C74">
-        <v>2214</v>
+        <v>1551</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2217,13 +2217,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46308.76041666666</v>
+        <v>46310.76041666666</v>
       </c>
       <c r="B75">
-        <v>2295.821</v>
+        <v>1170.815</v>
       </c>
       <c r="C75">
-        <v>2279</v>
+        <v>1515</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2234,13 +2234,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46308.77083333334</v>
+        <v>46310.77083333334</v>
       </c>
       <c r="B76">
-        <v>2303.508</v>
+        <v>1178.692</v>
       </c>
       <c r="C76">
-        <v>2310</v>
+        <v>1547</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2251,13 +2251,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46308.78125</v>
+        <v>46310.78125</v>
       </c>
       <c r="B77">
-        <v>2304.376</v>
+        <v>1186.182</v>
       </c>
       <c r="C77">
-        <v>2253</v>
+        <v>1573</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2268,13 +2268,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46308.79166666666</v>
+        <v>46310.79166666666</v>
       </c>
       <c r="B78">
-        <v>2306.063</v>
+        <v>1205.343</v>
       </c>
       <c r="C78">
-        <v>2220</v>
+        <v>1559</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2285,13 +2285,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46308.80208333334</v>
+        <v>46310.80208333334</v>
       </c>
       <c r="B79">
-        <v>2304.435</v>
+        <v>1216.753</v>
       </c>
       <c r="C79">
-        <v>2296</v>
+        <v>1529</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2302,13 +2302,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46308.8125</v>
+        <v>46310.8125</v>
       </c>
       <c r="B80">
-        <v>2303.44</v>
+        <v>1228.486</v>
       </c>
       <c r="C80">
-        <v>2327</v>
+        <v>1533</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2319,13 +2319,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46308.82291666666</v>
+        <v>46310.82291666666</v>
       </c>
       <c r="B81">
-        <v>2302.711</v>
+        <v>1238.607</v>
       </c>
       <c r="C81">
-        <v>2384</v>
+        <v>1582</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2336,13 +2336,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46308.83333333334</v>
+        <v>46310.83333333334</v>
       </c>
       <c r="B82">
-        <v>2305.963</v>
+        <v>1265.043</v>
       </c>
       <c r="C82">
-        <v>2446</v>
+        <v>1708</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2353,13 +2353,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46308.84375</v>
+        <v>46310.84375</v>
       </c>
       <c r="B83">
-        <v>2300.354</v>
+        <v>1267.079</v>
       </c>
       <c r="C83">
-        <v>2432</v>
+        <v>1764</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2370,13 +2370,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46308.85416666666</v>
+        <v>46310.85416666666</v>
       </c>
       <c r="B84">
-        <v>2296.98</v>
+        <v>1270.069</v>
       </c>
       <c r="C84">
-        <v>2434</v>
+        <v>1759</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2387,13 +2387,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46308.86458333334</v>
+        <v>46310.86458333334</v>
       </c>
       <c r="B85">
-        <v>2292.754</v>
+        <v>1272.317</v>
       </c>
       <c r="C85">
-        <v>2473</v>
+        <v>1759</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2404,13 +2404,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46308.875</v>
+        <v>46310.875</v>
       </c>
       <c r="B86">
-        <v>2317.27</v>
+        <v>1274.889</v>
       </c>
       <c r="C86">
-        <v>2510</v>
+        <v>1740</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2421,13 +2421,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46308.88541666666</v>
+        <v>46310.88541666666</v>
       </c>
       <c r="B87">
-        <v>2316.237</v>
+        <v>1277.918</v>
       </c>
       <c r="C87">
-        <v>2517</v>
+        <v>1729</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2438,13 +2438,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46308.89583333334</v>
+        <v>46310.89583333334</v>
       </c>
       <c r="B88">
-        <v>2313.366</v>
+        <v>1280.61</v>
       </c>
       <c r="C88">
-        <v>2534</v>
+        <v>1747</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2455,13 +2455,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46308.90625</v>
+        <v>46310.90625</v>
       </c>
       <c r="B89">
-        <v>2314.597</v>
+        <v>1286.181</v>
       </c>
       <c r="C89">
-        <v>2492</v>
+        <v>1768</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2472,13 +2472,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46308.91666666666</v>
+        <v>46310.91666666666</v>
       </c>
       <c r="B90">
-        <v>2329.79</v>
+        <v>1267.147</v>
       </c>
       <c r="C90">
-        <v>2446</v>
+        <v>1805</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2489,13 +2489,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46308.92708333334</v>
+        <v>46310.92708333334</v>
       </c>
       <c r="B91">
-        <v>2332.851</v>
+        <v>1272.717</v>
       </c>
       <c r="C91">
-        <v>2424</v>
+        <v>1778</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2506,13 +2506,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46308.9375</v>
+        <v>46310.9375</v>
       </c>
       <c r="B92">
-        <v>2335.233</v>
+        <v>1283.241</v>
       </c>
       <c r="C92">
-        <v>2353</v>
+        <v>1783</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2523,13 +2523,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46308.94791666666</v>
+        <v>46310.94791666666</v>
       </c>
       <c r="B93">
-        <v>2337.297</v>
+        <v>1299.698</v>
       </c>
       <c r="C93">
-        <v>2292</v>
+        <v>1812</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2540,13 +2540,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46308.95833333334</v>
+        <v>46310.95833333334</v>
       </c>
       <c r="B94">
-        <v>2444.507</v>
+        <v>1477.868</v>
       </c>
       <c r="C94">
-        <v>2232</v>
+        <v>1819</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2557,13 +2557,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46308.96875</v>
+        <v>46310.96875</v>
       </c>
       <c r="B95">
-        <v>2442.786</v>
+        <v>1486.738</v>
       </c>
       <c r="C95">
-        <v>2204</v>
+        <v>1865</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2574,13 +2574,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46308.97916666666</v>
+        <v>46310.97916666666</v>
       </c>
       <c r="B96">
-        <v>2442.317</v>
+        <v>1505.366</v>
       </c>
       <c r="C96">
-        <v>2229</v>
+        <v>1924</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2591,13 +2591,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46308.98958333334</v>
+        <v>46310.98958333334</v>
       </c>
       <c r="B97">
-        <v>2451.336</v>
+        <v>1467.994</v>
       </c>
       <c r="C97">
-        <v>2227</v>
+        <v>1845</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2608,13 +2608,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="B98">
-        <v>2454.623</v>
+        <v>1580.982</v>
       </c>
       <c r="C98">
-        <v>2228</v>
+        <v>1722</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2625,13 +2625,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46309.01041666666</v>
+        <v>46311.01041666666</v>
       </c>
       <c r="B99">
-        <v>2454.535</v>
+        <v>1575.836</v>
       </c>
       <c r="C99">
-        <v>2256</v>
+        <v>1633</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2642,13 +2642,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46309.02083333334</v>
+        <v>46311.02083333334</v>
       </c>
       <c r="B100">
-        <v>2452.395</v>
+        <v>1582.94</v>
       </c>
       <c r="C100">
-        <v>2299</v>
+        <v>1563</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2659,13 +2659,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46309.03125</v>
+        <v>46311.03125</v>
       </c>
       <c r="B101">
-        <v>2453.732</v>
+        <v>1571.718</v>
       </c>
       <c r="C101">
-        <v>2333</v>
+        <v>1642</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2676,13 +2676,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46309.04166666666</v>
+        <v>46311.04166666666</v>
       </c>
       <c r="B102">
-        <v>2444.137</v>
+        <v>1534.452</v>
       </c>
       <c r="C102">
-        <v>2306</v>
+        <v>1670</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2693,13 +2693,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46309.05208333334</v>
+        <v>46311.05208333334</v>
       </c>
       <c r="B103">
-        <v>2443.466</v>
+        <v>1522.574</v>
       </c>
       <c r="C103">
-        <v>2239</v>
+        <v>1678</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2710,13 +2710,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46309.0625</v>
+        <v>46311.0625</v>
       </c>
       <c r="B104">
-        <v>2441.667</v>
+        <v>1515.981</v>
       </c>
       <c r="C104">
-        <v>2238</v>
+        <v>1718</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2727,13 +2727,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46309.07291666666</v>
+        <v>46311.07291666666</v>
       </c>
       <c r="B105">
-        <v>2438.431</v>
+        <v>1505.17</v>
       </c>
       <c r="C105">
-        <v>2281</v>
+        <v>1750</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2744,13 +2744,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46309.08333333334</v>
+        <v>46311.08333333334</v>
       </c>
       <c r="B106">
-        <v>2440.881</v>
+        <v>1469.421</v>
       </c>
       <c r="C106">
-        <v>2303</v>
+        <v>1721</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2761,13 +2761,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46309.09375</v>
+        <v>46311.09375</v>
       </c>
       <c r="B107">
-        <v>2433.954</v>
+        <v>1461.798</v>
       </c>
       <c r="C107">
-        <v>2331</v>
+        <v>1645</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2778,13 +2778,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46309.10416666666</v>
+        <v>46311.10416666666</v>
       </c>
       <c r="B108">
-        <v>2429.397</v>
+        <v>1448.094</v>
       </c>
       <c r="C108">
-        <v>2400</v>
+        <v>1604</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2795,13 +2795,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46309.11458333334</v>
+        <v>46311.11458333334</v>
       </c>
       <c r="B109">
-        <v>2420.925</v>
+        <v>1460.27</v>
       </c>
       <c r="C109">
-        <v>2440</v>
+        <v>1574</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2812,13 +2812,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46309.125</v>
+        <v>46311.125</v>
       </c>
       <c r="B110">
-        <v>2419.846</v>
+        <v>1444.246</v>
       </c>
       <c r="C110">
-        <v>2443</v>
+        <v>1518</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2829,13 +2829,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46309.13541666666</v>
+        <v>46311.13541666666</v>
       </c>
       <c r="B111">
-        <v>2417.313</v>
+        <v>1431.126</v>
       </c>
       <c r="C111">
-        <v>2434</v>
+        <v>1483</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2846,13 +2846,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46309.14583333334</v>
+        <v>46311.14583333334</v>
       </c>
       <c r="B112">
-        <v>2420.971</v>
+        <v>1424.831</v>
       </c>
       <c r="C112">
-        <v>2445</v>
+        <v>1504</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2863,13 +2863,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46309.15625</v>
+        <v>46311.15625</v>
       </c>
       <c r="B113">
-        <v>2409.355</v>
+        <v>1422.514</v>
       </c>
       <c r="C113">
-        <v>2433</v>
+        <v>1553</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2880,13 +2880,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46309.16666666666</v>
+        <v>46311.16666666666</v>
       </c>
       <c r="B114">
-        <v>2381.823</v>
+        <v>1424.231</v>
       </c>
       <c r="C114">
-        <v>2400</v>
+        <v>1551</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2897,13 +2897,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46309.17708333334</v>
+        <v>46311.17708333334</v>
       </c>
       <c r="B115">
-        <v>2384.713</v>
+        <v>1404.097</v>
       </c>
       <c r="C115">
-        <v>2375</v>
+        <v>1521</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2914,13 +2914,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46309.1875</v>
+        <v>46311.1875</v>
       </c>
       <c r="B116">
-        <v>2385.622</v>
+        <v>1394.278</v>
       </c>
       <c r="C116">
-        <v>2404</v>
+        <v>1496</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2931,13 +2931,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46309.19791666666</v>
+        <v>46311.19791666666</v>
       </c>
       <c r="B117">
-        <v>2388.234</v>
+        <v>1374.658</v>
       </c>
       <c r="C117">
-        <v>2456</v>
+        <v>1564</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2948,13 +2948,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46309.20833333334</v>
+        <v>46311.20833333334</v>
       </c>
       <c r="B118">
-        <v>2479.054</v>
+        <v>1366.209</v>
       </c>
       <c r="C118">
-        <v>2440</v>
+        <v>1596</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2965,13 +2965,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46309.21875</v>
+        <v>46311.21875</v>
       </c>
       <c r="B119">
-        <v>2482.633</v>
+        <v>1357.363</v>
       </c>
       <c r="C119">
-        <v>2420</v>
+        <v>1562</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2982,13 +2982,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46309.22916666666</v>
+        <v>46311.22916666666</v>
       </c>
       <c r="B120">
-        <v>2485.628</v>
+        <v>1350.17</v>
       </c>
       <c r="C120">
-        <v>2440</v>
+        <v>1606</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -2999,13 +2999,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46309.23958333334</v>
+        <v>46311.23958333334</v>
       </c>
       <c r="B121">
-        <v>2491.009</v>
+        <v>1342.49</v>
       </c>
       <c r="C121">
-        <v>2428</v>
+        <v>1643</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3016,13 +3016,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46309.25</v>
+        <v>46311.25</v>
       </c>
       <c r="B122">
-        <v>2432.847</v>
+        <v>1279.213</v>
       </c>
       <c r="C122">
-        <v>2377</v>
+        <v>1657</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3033,13 +3033,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46309.26041666666</v>
+        <v>46311.26041666666</v>
       </c>
       <c r="B123">
-        <v>2423.243</v>
+        <v>1265.283</v>
       </c>
       <c r="C123">
-        <v>2364</v>
+        <v>1684</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3050,13 +3050,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46309.27083333334</v>
+        <v>46311.27083333334</v>
       </c>
       <c r="B124">
-        <v>2410.11</v>
+        <v>1251.974</v>
       </c>
       <c r="C124">
-        <v>2355</v>
+        <v>1662</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3067,13 +3067,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46309.28125</v>
+        <v>46311.28125</v>
       </c>
       <c r="B125">
-        <v>2402.078</v>
+        <v>1245.114</v>
       </c>
       <c r="C125">
-        <v>2318</v>
+        <v>1663</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3084,13 +3084,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46309.29166666666</v>
+        <v>46311.29166666666</v>
       </c>
       <c r="B126">
-        <v>2375.157</v>
+        <v>1227.887</v>
       </c>
       <c r="C126">
-        <v>2271</v>
+        <v>1639</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3101,13 +3101,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46309.30208333334</v>
+        <v>46311.30208333334</v>
       </c>
       <c r="B127">
-        <v>2376.279</v>
+        <v>1213.85</v>
       </c>
       <c r="C127">
-        <v>2277</v>
+        <v>1616</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3118,13 +3118,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46309.3125</v>
+        <v>46311.3125</v>
       </c>
       <c r="B128">
-        <v>2366.567</v>
+        <v>1192.769</v>
       </c>
       <c r="C128">
-        <v>2353</v>
+        <v>1538</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3135,13 +3135,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46309.32291666666</v>
+        <v>46311.32291666666</v>
       </c>
       <c r="B129">
-        <v>2351.05</v>
+        <v>1177.878</v>
       </c>
       <c r="C129">
-        <v>2430</v>
+        <v>1486</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3152,13 +3152,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46309.33333333334</v>
+        <v>46311.33333333334</v>
       </c>
       <c r="B130">
-        <v>2287.961</v>
+        <v>1256.566</v>
       </c>
       <c r="C130">
-        <v>2481</v>
+        <v>1503</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3169,13 +3169,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46309.34375</v>
+        <v>46311.34375</v>
       </c>
       <c r="B131">
-        <v>2297.147</v>
+        <v>1267.498</v>
       </c>
       <c r="C131">
-        <v>2480</v>
+        <v>1515</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3186,13 +3186,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46309.35416666666</v>
+        <v>46311.35416666666</v>
       </c>
       <c r="B132">
-        <v>2302.8</v>
+        <v>1290.019</v>
       </c>
       <c r="C132">
-        <v>2481</v>
+        <v>1558</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3203,13 +3203,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46309.36458333334</v>
+        <v>46311.36458333334</v>
       </c>
       <c r="B133">
-        <v>2312.624</v>
+        <v>1283.328</v>
       </c>
       <c r="C133">
-        <v>2467</v>
+        <v>1702</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3220,13 +3220,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46309.375</v>
+        <v>46311.375</v>
       </c>
       <c r="B134">
-        <v>2330.181</v>
+        <v>1267.766</v>
       </c>
       <c r="C134">
-        <v>2424</v>
+        <v>1804</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3237,13 +3237,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46309.38541666666</v>
+        <v>46311.38541666666</v>
       </c>
       <c r="B135">
-        <v>2334.173</v>
+        <v>1280.532</v>
       </c>
       <c r="C135">
-        <v>2355</v>
+        <v>1825</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3254,13 +3254,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46309.39583333334</v>
+        <v>46311.39583333334</v>
       </c>
       <c r="B136">
-        <v>2340.315</v>
+        <v>1293.744</v>
       </c>
       <c r="C136">
-        <v>2318</v>
+        <v>1888</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3271,13 +3271,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46309.40625</v>
+        <v>46311.40625</v>
       </c>
       <c r="B137">
-        <v>2347.987</v>
+        <v>1308.65</v>
       </c>
       <c r="C137">
-        <v>2269</v>
+        <v>1931</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3288,13 +3288,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46309.41666666666</v>
+        <v>46311.41666666666</v>
       </c>
       <c r="B138">
-        <v>2355.544</v>
+        <v>1280.942</v>
       </c>
       <c r="C138">
-        <v>2210</v>
+        <v>1870</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3305,13 +3305,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46309.42708333334</v>
+        <v>46311.42708333334</v>
       </c>
       <c r="B139">
-        <v>2350.134</v>
+        <v>1293.842</v>
       </c>
       <c r="C139">
-        <v>2249</v>
+        <v>1885</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3322,13 +3322,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46309.4375</v>
+        <v>46311.4375</v>
       </c>
       <c r="B140">
-        <v>2344.889</v>
+        <v>1308.062</v>
       </c>
       <c r="C140">
-        <v>2233</v>
+        <v>1912</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3339,13 +3339,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46309.44791666666</v>
+        <v>46311.44791666666</v>
       </c>
       <c r="B141">
-        <v>2339.392</v>
+        <v>1318.602</v>
       </c>
       <c r="C141">
-        <v>2209</v>
+        <v>1912</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3356,13 +3356,13 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46309.45833333334</v>
+        <v>46311.45833333334</v>
       </c>
       <c r="B142">
-        <v>2301.593</v>
+        <v>1358.6</v>
       </c>
       <c r="C142">
-        <v>2203</v>
+        <v>1892</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3373,13 +3373,13 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46309.46875</v>
+        <v>46311.46875</v>
       </c>
       <c r="B143">
-        <v>2303.708</v>
+        <v>1366.415</v>
       </c>
       <c r="C143">
-        <v>2187</v>
+        <v>1908</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3390,13 +3390,13 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46309.47916666666</v>
+        <v>46311.47916666666</v>
       </c>
       <c r="B144">
-        <v>2304.703</v>
+        <v>1372.395</v>
       </c>
       <c r="C144">
-        <v>2224</v>
+        <v>1906</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3407,13 +3407,13 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46309.48958333334</v>
+        <v>46311.48958333334</v>
       </c>
       <c r="B145">
-        <v>2305.973</v>
+        <v>1376.25</v>
       </c>
       <c r="C145">
-        <v>2228</v>
+        <v>1874</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3424,13 +3424,13 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="B146">
-        <v>2308.768</v>
+        <v>1364.006</v>
       </c>
       <c r="C146">
-        <v>2281</v>
+        <v>1841</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3441,13 +3441,13 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46309.51041666666</v>
+        <v>46311.51041666666</v>
       </c>
       <c r="B147">
-        <v>2304.492</v>
+        <v>1358.348</v>
       </c>
       <c r="C147">
-        <v>2341</v>
+        <v>1743</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3458,13 +3458,13 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46309.52083333334</v>
+        <v>46311.52083333334</v>
       </c>
       <c r="B148">
-        <v>2297.336</v>
+        <v>1352.003</v>
       </c>
       <c r="C148">
-        <v>2386</v>
+        <v>1705</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3475,13 +3475,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46309.53125</v>
+        <v>46311.53125</v>
       </c>
       <c r="B149">
-        <v>2288.318</v>
-      </c>
-      <c r="C149">
-        <v>2494</v>
+        <v>1343.992</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3492,13 +3489,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46309.54166666666</v>
+        <v>46311.54166666666</v>
       </c>
       <c r="B150">
-        <v>2317.614</v>
-      </c>
-      <c r="C150">
-        <v>2534</v>
+        <v>1336.513</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3509,13 +3503,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46309.55208333334</v>
+        <v>46311.55208333334</v>
       </c>
       <c r="B151">
-        <v>2300.315</v>
-      </c>
-      <c r="C151">
-        <v>2495</v>
+        <v>1331.115</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3526,13 +3517,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46309.5625</v>
+        <v>46311.5625</v>
       </c>
       <c r="B152">
-        <v>2280.91</v>
-      </c>
-      <c r="C152">
-        <v>2539</v>
+        <v>1326.533</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3543,13 +3531,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46309.57291666666</v>
+        <v>46311.57291666666</v>
       </c>
       <c r="B153">
-        <v>2263.522</v>
-      </c>
-      <c r="C153">
-        <v>2403</v>
+        <v>1320.661</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3560,13 +3545,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46309.58333333334</v>
+        <v>46311.58333333334</v>
       </c>
       <c r="B154">
-        <v>2230.336</v>
-      </c>
-      <c r="C154">
-        <v>2357</v>
+        <v>1331.763</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3577,13 +3559,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46309.59375</v>
+        <v>46311.59375</v>
       </c>
       <c r="B155">
-        <v>2205.166</v>
-      </c>
-      <c r="C155">
-        <v>2260</v>
+        <v>1322.832</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3594,10 +3573,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46309.60416666666</v>
+        <v>46311.60416666666</v>
       </c>
       <c r="B156">
-        <v>2178.262</v>
+        <v>1308.915</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3608,10 +3587,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46309.61458333334</v>
+        <v>46311.61458333334</v>
       </c>
       <c r="B157">
-        <v>2154.155</v>
+        <v>1297.927</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3622,10 +3601,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46309.625</v>
+        <v>46311.625</v>
       </c>
       <c r="B158">
-        <v>2138.321</v>
+        <v>1267.886</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3636,10 +3615,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46309.63541666666</v>
+        <v>46311.63541666666</v>
       </c>
       <c r="B159">
-        <v>2110.205</v>
+        <v>1250.787</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3650,10 +3629,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46309.64583333334</v>
+        <v>46311.64583333334</v>
       </c>
       <c r="B160">
-        <v>2080.831</v>
+        <v>1231.544</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3664,10 +3643,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46309.65625</v>
+        <v>46311.65625</v>
       </c>
       <c r="B161">
-        <v>2050.827</v>
+        <v>1211.62</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3678,10 +3657,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46309.66666666666</v>
+        <v>46311.66666666666</v>
       </c>
       <c r="B162">
-        <v>2018.127</v>
+        <v>1057.421</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -3692,10 +3671,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46309.67708333334</v>
+        <v>46311.67708333334</v>
       </c>
       <c r="B163">
-        <v>1967.294</v>
+        <v>1027.365</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -3706,10 +3685,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46309.6875</v>
+        <v>46311.6875</v>
       </c>
       <c r="B164">
-        <v>1919.104</v>
+        <v>998.605</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -3720,10 +3699,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46309.69791666666</v>
+        <v>46311.69791666666</v>
       </c>
       <c r="B165">
-        <v>1873.846</v>
+        <v>968.1130000000001</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -3734,10 +3713,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46309.70833333334</v>
+        <v>46311.70833333334</v>
       </c>
       <c r="B166">
-        <v>1807.618</v>
+        <v>974.2430000000001</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -3748,10 +3727,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46309.71875</v>
+        <v>46311.71875</v>
       </c>
       <c r="B167">
-        <v>1762.15</v>
+        <v>966.776</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -3762,10 +3741,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46309.72916666666</v>
+        <v>46311.72916666666</v>
       </c>
       <c r="B168">
-        <v>1716.06</v>
+        <v>959.078</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -3776,10 +3755,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46309.73958333334</v>
+        <v>46311.73958333334</v>
       </c>
       <c r="B169">
-        <v>1674.125</v>
+        <v>953.099</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -3790,10 +3769,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46309.75</v>
+        <v>46311.75</v>
       </c>
       <c r="B170">
-        <v>1676.529</v>
+        <v>946.223</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -3804,10 +3783,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46309.76041666666</v>
+        <v>46311.76041666666</v>
       </c>
       <c r="B171">
-        <v>1657.854</v>
+        <v>939.279</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -3818,10 +3797,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46309.77083333334</v>
+        <v>46311.77083333334</v>
       </c>
       <c r="B172">
-        <v>1636.225</v>
+        <v>934.9160000000001</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -3832,10 +3811,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46309.78125</v>
+        <v>46311.78125</v>
       </c>
       <c r="B173">
-        <v>1616.017</v>
+        <v>930.221</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -3846,10 +3825,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46309.79166666666</v>
+        <v>46311.79166666666</v>
       </c>
       <c r="B174">
-        <v>1598.004</v>
+        <v>933.617</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -3860,10 +3839,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46309.80208333334</v>
+        <v>46311.80208333334</v>
       </c>
       <c r="B175">
-        <v>1596.037</v>
+        <v>931.436</v>
       </c>
       <c r="D175">
         <v>78</v>
@@ -3874,10 +3853,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46309.8125</v>
+        <v>46311.8125</v>
       </c>
       <c r="B176">
-        <v>1593.61</v>
+        <v>931.423</v>
       </c>
       <c r="D176">
         <v>79</v>
@@ -3888,10 +3867,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46309.82291666666</v>
+        <v>46311.82291666666</v>
       </c>
       <c r="B177">
-        <v>1591.66</v>
+        <v>929.6369999999999</v>
       </c>
       <c r="D177">
         <v>80</v>
@@ -3902,10 +3881,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46309.83333333334</v>
+        <v>46311.83333333334</v>
       </c>
       <c r="B178">
-        <v>1589.105</v>
+        <v>945.0549999999999</v>
       </c>
       <c r="D178">
         <v>81</v>
@@ -3916,10 +3895,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46309.84375</v>
+        <v>46311.84375</v>
       </c>
       <c r="B179">
-        <v>1582.822</v>
+        <v>943.747</v>
       </c>
       <c r="D179">
         <v>82</v>
@@ -3930,10 +3909,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46309.85416666666</v>
+        <v>46311.85416666666</v>
       </c>
       <c r="B180">
-        <v>1574.842</v>
+        <v>943.3339999999999</v>
       </c>
       <c r="D180">
         <v>83</v>
@@ -3944,10 +3923,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46309.86458333334</v>
+        <v>46311.86458333334</v>
       </c>
       <c r="B181">
-        <v>1566.252</v>
+        <v>941.231</v>
       </c>
       <c r="D181">
         <v>84</v>
@@ -3958,10 +3937,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46309.875</v>
+        <v>46311.875</v>
       </c>
       <c r="B182">
-        <v>1559.561</v>
+        <v>931.573</v>
       </c>
       <c r="D182">
         <v>85</v>
@@ -3972,10 +3951,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46309.88541666666</v>
+        <v>46311.88541666666</v>
       </c>
       <c r="B183">
-        <v>1557.678</v>
+        <v>933.4829999999999</v>
       </c>
       <c r="D183">
         <v>86</v>
@@ -3986,10 +3965,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46309.89583333334</v>
+        <v>46311.89583333334</v>
       </c>
       <c r="B184">
-        <v>1554.838</v>
+        <v>933.758</v>
       </c>
       <c r="D184">
         <v>87</v>
@@ -4000,10 +3979,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46309.90625</v>
+        <v>46311.90625</v>
       </c>
       <c r="B185">
-        <v>1552.265</v>
+        <v>934.4349999999999</v>
       </c>
       <c r="D185">
         <v>88</v>
@@ -4014,10 +3993,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46309.91666666666</v>
+        <v>46311.91666666666</v>
       </c>
       <c r="B186">
-        <v>1547.213</v>
+        <v>940.535</v>
       </c>
       <c r="D186">
         <v>89</v>
@@ -4028,10 +4007,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46309.92708333334</v>
+        <v>46311.92708333334</v>
       </c>
       <c r="B187">
-        <v>1543.284</v>
+        <v>944.9640000000001</v>
       </c>
       <c r="D187">
         <v>90</v>
@@ -4042,10 +4021,10 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46309.9375</v>
+        <v>46311.9375</v>
       </c>
       <c r="B188">
-        <v>1547.448</v>
+        <v>953.845</v>
       </c>
       <c r="D188">
         <v>91</v>
@@ -4056,10 +4035,10 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46309.94791666666</v>
+        <v>46311.94791666666</v>
       </c>
       <c r="B189">
-        <v>1552.923</v>
+        <v>965.016</v>
       </c>
       <c r="D189">
         <v>92</v>

--- a/data_fetching/Entsoe/Wind_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Wind_Production_Historical.xlsx
@@ -31,568 +31,568 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>15.10.20261</t>
-  </si>
-  <si>
-    <t>15.10.20262</t>
-  </si>
-  <si>
-    <t>15.10.20263</t>
-  </si>
-  <si>
-    <t>15.10.20264</t>
-  </si>
-  <si>
-    <t>15.10.20265</t>
-  </si>
-  <si>
-    <t>15.10.20266</t>
-  </si>
-  <si>
-    <t>15.10.20267</t>
-  </si>
-  <si>
-    <t>15.10.20268</t>
-  </si>
-  <si>
-    <t>15.10.20269</t>
-  </si>
-  <si>
-    <t>15.10.202610</t>
-  </si>
-  <si>
-    <t>15.10.202611</t>
-  </si>
-  <si>
-    <t>15.10.202612</t>
-  </si>
-  <si>
-    <t>15.10.202613</t>
-  </si>
-  <si>
-    <t>15.10.202614</t>
-  </si>
-  <si>
-    <t>15.10.202615</t>
-  </si>
-  <si>
-    <t>15.10.202616</t>
-  </si>
-  <si>
-    <t>15.10.202617</t>
-  </si>
-  <si>
-    <t>15.10.202618</t>
-  </si>
-  <si>
-    <t>15.10.202619</t>
-  </si>
-  <si>
-    <t>15.10.202620</t>
-  </si>
-  <si>
-    <t>15.10.202621</t>
-  </si>
-  <si>
-    <t>15.10.202622</t>
-  </si>
-  <si>
-    <t>15.10.202623</t>
-  </si>
-  <si>
-    <t>15.10.202624</t>
-  </si>
-  <si>
-    <t>15.10.202625</t>
-  </si>
-  <si>
-    <t>15.10.202626</t>
-  </si>
-  <si>
-    <t>15.10.202627</t>
-  </si>
-  <si>
-    <t>15.10.202628</t>
-  </si>
-  <si>
-    <t>15.10.202629</t>
-  </si>
-  <si>
-    <t>15.10.202630</t>
-  </si>
-  <si>
-    <t>15.10.202631</t>
-  </si>
-  <si>
-    <t>15.10.202632</t>
-  </si>
-  <si>
-    <t>15.10.202633</t>
-  </si>
-  <si>
-    <t>15.10.202634</t>
-  </si>
-  <si>
-    <t>15.10.202635</t>
-  </si>
-  <si>
-    <t>15.10.202636</t>
-  </si>
-  <si>
-    <t>15.10.202637</t>
-  </si>
-  <si>
-    <t>15.10.202638</t>
-  </si>
-  <si>
-    <t>15.10.202639</t>
-  </si>
-  <si>
-    <t>15.10.202640</t>
-  </si>
-  <si>
-    <t>15.10.202641</t>
-  </si>
-  <si>
-    <t>15.10.202642</t>
-  </si>
-  <si>
-    <t>15.10.202643</t>
-  </si>
-  <si>
-    <t>15.10.202644</t>
-  </si>
-  <si>
-    <t>15.10.202645</t>
-  </si>
-  <si>
-    <t>15.10.202646</t>
-  </si>
-  <si>
-    <t>15.10.202647</t>
-  </si>
-  <si>
-    <t>15.10.202648</t>
-  </si>
-  <si>
-    <t>15.10.202649</t>
-  </si>
-  <si>
-    <t>15.10.202650</t>
-  </si>
-  <si>
-    <t>15.10.202651</t>
-  </si>
-  <si>
-    <t>15.10.202652</t>
-  </si>
-  <si>
-    <t>15.10.202653</t>
-  </si>
-  <si>
-    <t>15.10.202654</t>
-  </si>
-  <si>
-    <t>15.10.202655</t>
-  </si>
-  <si>
-    <t>15.10.202656</t>
-  </si>
-  <si>
-    <t>15.10.202657</t>
-  </si>
-  <si>
-    <t>15.10.202658</t>
-  </si>
-  <si>
-    <t>15.10.202659</t>
-  </si>
-  <si>
-    <t>15.10.202660</t>
-  </si>
-  <si>
-    <t>15.10.202661</t>
-  </si>
-  <si>
-    <t>15.10.202662</t>
-  </si>
-  <si>
-    <t>15.10.202663</t>
-  </si>
-  <si>
-    <t>15.10.202664</t>
-  </si>
-  <si>
-    <t>15.10.202665</t>
-  </si>
-  <si>
-    <t>15.10.202666</t>
-  </si>
-  <si>
-    <t>15.10.202667</t>
-  </si>
-  <si>
-    <t>15.10.202668</t>
-  </si>
-  <si>
-    <t>15.10.202669</t>
-  </si>
-  <si>
-    <t>15.10.202670</t>
-  </si>
-  <si>
-    <t>15.10.202671</t>
-  </si>
-  <si>
-    <t>15.10.202672</t>
-  </si>
-  <si>
-    <t>15.10.202673</t>
-  </si>
-  <si>
-    <t>15.10.202674</t>
-  </si>
-  <si>
-    <t>15.10.202675</t>
-  </si>
-  <si>
-    <t>15.10.202676</t>
-  </si>
-  <si>
-    <t>15.10.202677</t>
-  </si>
-  <si>
-    <t>15.10.202678</t>
-  </si>
-  <si>
-    <t>15.10.202679</t>
-  </si>
-  <si>
-    <t>15.10.202680</t>
-  </si>
-  <si>
-    <t>15.10.202681</t>
-  </si>
-  <si>
-    <t>15.10.202682</t>
-  </si>
-  <si>
-    <t>15.10.202683</t>
-  </si>
-  <si>
-    <t>15.10.202684</t>
-  </si>
-  <si>
-    <t>15.10.202685</t>
-  </si>
-  <si>
-    <t>15.10.202686</t>
-  </si>
-  <si>
-    <t>15.10.202687</t>
-  </si>
-  <si>
-    <t>15.10.202688</t>
-  </si>
-  <si>
-    <t>15.10.202689</t>
-  </si>
-  <si>
-    <t>15.10.202690</t>
-  </si>
-  <si>
-    <t>15.10.202691</t>
-  </si>
-  <si>
-    <t>15.10.202692</t>
-  </si>
-  <si>
-    <t>15.10.202693</t>
-  </si>
-  <si>
-    <t>15.10.202694</t>
-  </si>
-  <si>
-    <t>15.10.202695</t>
-  </si>
-  <si>
-    <t>15.10.202696</t>
-  </si>
-  <si>
-    <t>16.10.20261</t>
-  </si>
-  <si>
-    <t>16.10.20262</t>
-  </si>
-  <si>
-    <t>16.10.20263</t>
-  </si>
-  <si>
-    <t>16.10.20264</t>
-  </si>
-  <si>
-    <t>16.10.20265</t>
-  </si>
-  <si>
-    <t>16.10.20266</t>
-  </si>
-  <si>
-    <t>16.10.20267</t>
-  </si>
-  <si>
-    <t>16.10.20268</t>
-  </si>
-  <si>
-    <t>16.10.20269</t>
-  </si>
-  <si>
-    <t>16.10.202610</t>
-  </si>
-  <si>
-    <t>16.10.202611</t>
-  </si>
-  <si>
-    <t>16.10.202612</t>
-  </si>
-  <si>
-    <t>16.10.202613</t>
-  </si>
-  <si>
-    <t>16.10.202614</t>
-  </si>
-  <si>
-    <t>16.10.202615</t>
-  </si>
-  <si>
-    <t>16.10.202616</t>
-  </si>
-  <si>
-    <t>16.10.202617</t>
-  </si>
-  <si>
-    <t>16.10.202618</t>
-  </si>
-  <si>
-    <t>16.10.202619</t>
-  </si>
-  <si>
-    <t>16.10.202620</t>
-  </si>
-  <si>
-    <t>16.10.202621</t>
-  </si>
-  <si>
-    <t>16.10.202622</t>
-  </si>
-  <si>
-    <t>16.10.202623</t>
-  </si>
-  <si>
-    <t>16.10.202624</t>
-  </si>
-  <si>
-    <t>16.10.202625</t>
-  </si>
-  <si>
-    <t>16.10.202626</t>
-  </si>
-  <si>
-    <t>16.10.202627</t>
-  </si>
-  <si>
-    <t>16.10.202628</t>
-  </si>
-  <si>
-    <t>16.10.202629</t>
-  </si>
-  <si>
-    <t>16.10.202630</t>
-  </si>
-  <si>
-    <t>16.10.202631</t>
-  </si>
-  <si>
-    <t>16.10.202632</t>
-  </si>
-  <si>
-    <t>16.10.202633</t>
-  </si>
-  <si>
-    <t>16.10.202634</t>
-  </si>
-  <si>
-    <t>16.10.202635</t>
-  </si>
-  <si>
-    <t>16.10.202636</t>
-  </si>
-  <si>
-    <t>16.10.202637</t>
-  </si>
-  <si>
-    <t>16.10.202638</t>
-  </si>
-  <si>
-    <t>16.10.202639</t>
-  </si>
-  <si>
-    <t>16.10.202640</t>
-  </si>
-  <si>
-    <t>16.10.202641</t>
-  </si>
-  <si>
-    <t>16.10.202642</t>
-  </si>
-  <si>
-    <t>16.10.202643</t>
-  </si>
-  <si>
-    <t>16.10.202644</t>
-  </si>
-  <si>
-    <t>16.10.202645</t>
-  </si>
-  <si>
-    <t>16.10.202646</t>
-  </si>
-  <si>
-    <t>16.10.202647</t>
-  </si>
-  <si>
-    <t>16.10.202648</t>
-  </si>
-  <si>
-    <t>16.10.202649</t>
-  </si>
-  <si>
-    <t>16.10.202650</t>
-  </si>
-  <si>
-    <t>16.10.202651</t>
-  </si>
-  <si>
-    <t>16.10.202652</t>
-  </si>
-  <si>
-    <t>16.10.202653</t>
-  </si>
-  <si>
-    <t>16.10.202654</t>
-  </si>
-  <si>
-    <t>16.10.202655</t>
-  </si>
-  <si>
-    <t>16.10.202656</t>
-  </si>
-  <si>
-    <t>16.10.202657</t>
-  </si>
-  <si>
-    <t>16.10.202658</t>
-  </si>
-  <si>
-    <t>16.10.202659</t>
-  </si>
-  <si>
-    <t>16.10.202660</t>
-  </si>
-  <si>
-    <t>16.10.202661</t>
-  </si>
-  <si>
-    <t>16.10.202662</t>
-  </si>
-  <si>
-    <t>16.10.202663</t>
-  </si>
-  <si>
-    <t>16.10.202664</t>
-  </si>
-  <si>
-    <t>16.10.202665</t>
-  </si>
-  <si>
-    <t>16.10.202666</t>
-  </si>
-  <si>
-    <t>16.10.202667</t>
-  </si>
-  <si>
-    <t>16.10.202668</t>
-  </si>
-  <si>
-    <t>16.10.202669</t>
-  </si>
-  <si>
-    <t>16.10.202670</t>
-  </si>
-  <si>
-    <t>16.10.202671</t>
-  </si>
-  <si>
-    <t>16.10.202672</t>
-  </si>
-  <si>
-    <t>16.10.202673</t>
-  </si>
-  <si>
-    <t>16.10.202674</t>
-  </si>
-  <si>
-    <t>16.10.202675</t>
-  </si>
-  <si>
-    <t>16.10.202676</t>
-  </si>
-  <si>
-    <t>16.10.202677</t>
-  </si>
-  <si>
-    <t>16.10.202678</t>
-  </si>
-  <si>
-    <t>16.10.202679</t>
-  </si>
-  <si>
-    <t>16.10.202680</t>
-  </si>
-  <si>
-    <t>16.10.202681</t>
-  </si>
-  <si>
-    <t>16.10.202682</t>
-  </si>
-  <si>
-    <t>16.10.202683</t>
-  </si>
-  <si>
-    <t>16.10.202684</t>
-  </si>
-  <si>
-    <t>16.10.202685</t>
-  </si>
-  <si>
-    <t>16.10.202686</t>
-  </si>
-  <si>
-    <t>16.10.202687</t>
-  </si>
-  <si>
-    <t>16.10.202688</t>
-  </si>
-  <si>
-    <t>16.10.202689</t>
-  </si>
-  <si>
-    <t>16.10.202690</t>
-  </si>
-  <si>
-    <t>16.10.202691</t>
-  </si>
-  <si>
-    <t>16.10.202692</t>
+    <t>20.10.20261</t>
+  </si>
+  <si>
+    <t>20.10.20262</t>
+  </si>
+  <si>
+    <t>20.10.20263</t>
+  </si>
+  <si>
+    <t>20.10.20264</t>
+  </si>
+  <si>
+    <t>20.10.20265</t>
+  </si>
+  <si>
+    <t>20.10.20266</t>
+  </si>
+  <si>
+    <t>20.10.20267</t>
+  </si>
+  <si>
+    <t>20.10.20268</t>
+  </si>
+  <si>
+    <t>20.10.20269</t>
+  </si>
+  <si>
+    <t>20.10.202610</t>
+  </si>
+  <si>
+    <t>20.10.202611</t>
+  </si>
+  <si>
+    <t>20.10.202612</t>
+  </si>
+  <si>
+    <t>20.10.202613</t>
+  </si>
+  <si>
+    <t>20.10.202614</t>
+  </si>
+  <si>
+    <t>20.10.202615</t>
+  </si>
+  <si>
+    <t>20.10.202616</t>
+  </si>
+  <si>
+    <t>20.10.202617</t>
+  </si>
+  <si>
+    <t>20.10.202618</t>
+  </si>
+  <si>
+    <t>20.10.202619</t>
+  </si>
+  <si>
+    <t>20.10.202620</t>
+  </si>
+  <si>
+    <t>20.10.202621</t>
+  </si>
+  <si>
+    <t>20.10.202622</t>
+  </si>
+  <si>
+    <t>20.10.202623</t>
+  </si>
+  <si>
+    <t>20.10.202624</t>
+  </si>
+  <si>
+    <t>20.10.202625</t>
+  </si>
+  <si>
+    <t>20.10.202626</t>
+  </si>
+  <si>
+    <t>20.10.202627</t>
+  </si>
+  <si>
+    <t>20.10.202628</t>
+  </si>
+  <si>
+    <t>20.10.202629</t>
+  </si>
+  <si>
+    <t>20.10.202630</t>
+  </si>
+  <si>
+    <t>20.10.202631</t>
+  </si>
+  <si>
+    <t>20.10.202632</t>
+  </si>
+  <si>
+    <t>20.10.202633</t>
+  </si>
+  <si>
+    <t>20.10.202634</t>
+  </si>
+  <si>
+    <t>20.10.202635</t>
+  </si>
+  <si>
+    <t>20.10.202636</t>
+  </si>
+  <si>
+    <t>20.10.202637</t>
+  </si>
+  <si>
+    <t>20.10.202638</t>
+  </si>
+  <si>
+    <t>20.10.202639</t>
+  </si>
+  <si>
+    <t>20.10.202640</t>
+  </si>
+  <si>
+    <t>20.10.202641</t>
+  </si>
+  <si>
+    <t>20.10.202642</t>
+  </si>
+  <si>
+    <t>20.10.202643</t>
+  </si>
+  <si>
+    <t>20.10.202644</t>
+  </si>
+  <si>
+    <t>20.10.202645</t>
+  </si>
+  <si>
+    <t>20.10.202646</t>
+  </si>
+  <si>
+    <t>20.10.202647</t>
+  </si>
+  <si>
+    <t>20.10.202648</t>
+  </si>
+  <si>
+    <t>20.10.202649</t>
+  </si>
+  <si>
+    <t>20.10.202650</t>
+  </si>
+  <si>
+    <t>20.10.202651</t>
+  </si>
+  <si>
+    <t>20.10.202652</t>
+  </si>
+  <si>
+    <t>20.10.202653</t>
+  </si>
+  <si>
+    <t>20.10.202654</t>
+  </si>
+  <si>
+    <t>20.10.202655</t>
+  </si>
+  <si>
+    <t>20.10.202656</t>
+  </si>
+  <si>
+    <t>20.10.202657</t>
+  </si>
+  <si>
+    <t>20.10.202658</t>
+  </si>
+  <si>
+    <t>20.10.202659</t>
+  </si>
+  <si>
+    <t>20.10.202660</t>
+  </si>
+  <si>
+    <t>20.10.202661</t>
+  </si>
+  <si>
+    <t>20.10.202662</t>
+  </si>
+  <si>
+    <t>20.10.202663</t>
+  </si>
+  <si>
+    <t>20.10.202664</t>
+  </si>
+  <si>
+    <t>20.10.202665</t>
+  </si>
+  <si>
+    <t>20.10.202666</t>
+  </si>
+  <si>
+    <t>20.10.202667</t>
+  </si>
+  <si>
+    <t>20.10.202668</t>
+  </si>
+  <si>
+    <t>20.10.202669</t>
+  </si>
+  <si>
+    <t>20.10.202670</t>
+  </si>
+  <si>
+    <t>20.10.202671</t>
+  </si>
+  <si>
+    <t>20.10.202672</t>
+  </si>
+  <si>
+    <t>20.10.202673</t>
+  </si>
+  <si>
+    <t>20.10.202674</t>
+  </si>
+  <si>
+    <t>20.10.202675</t>
+  </si>
+  <si>
+    <t>20.10.202676</t>
+  </si>
+  <si>
+    <t>20.10.202677</t>
+  </si>
+  <si>
+    <t>20.10.202678</t>
+  </si>
+  <si>
+    <t>20.10.202679</t>
+  </si>
+  <si>
+    <t>20.10.202680</t>
+  </si>
+  <si>
+    <t>20.10.202681</t>
+  </si>
+  <si>
+    <t>20.10.202682</t>
+  </si>
+  <si>
+    <t>20.10.202683</t>
+  </si>
+  <si>
+    <t>20.10.202684</t>
+  </si>
+  <si>
+    <t>20.10.202685</t>
+  </si>
+  <si>
+    <t>20.10.202686</t>
+  </si>
+  <si>
+    <t>20.10.202687</t>
+  </si>
+  <si>
+    <t>20.10.202688</t>
+  </si>
+  <si>
+    <t>20.10.202689</t>
+  </si>
+  <si>
+    <t>20.10.202690</t>
+  </si>
+  <si>
+    <t>20.10.202691</t>
+  </si>
+  <si>
+    <t>20.10.202692</t>
+  </si>
+  <si>
+    <t>20.10.202693</t>
+  </si>
+  <si>
+    <t>20.10.202694</t>
+  </si>
+  <si>
+    <t>20.10.202695</t>
+  </si>
+  <si>
+    <t>20.10.202696</t>
+  </si>
+  <si>
+    <t>21.10.20261</t>
+  </si>
+  <si>
+    <t>21.10.20262</t>
+  </si>
+  <si>
+    <t>21.10.20263</t>
+  </si>
+  <si>
+    <t>21.10.20264</t>
+  </si>
+  <si>
+    <t>21.10.20265</t>
+  </si>
+  <si>
+    <t>21.10.20266</t>
+  </si>
+  <si>
+    <t>21.10.20267</t>
+  </si>
+  <si>
+    <t>21.10.20268</t>
+  </si>
+  <si>
+    <t>21.10.20269</t>
+  </si>
+  <si>
+    <t>21.10.202610</t>
+  </si>
+  <si>
+    <t>21.10.202611</t>
+  </si>
+  <si>
+    <t>21.10.202612</t>
+  </si>
+  <si>
+    <t>21.10.202613</t>
+  </si>
+  <si>
+    <t>21.10.202614</t>
+  </si>
+  <si>
+    <t>21.10.202615</t>
+  </si>
+  <si>
+    <t>21.10.202616</t>
+  </si>
+  <si>
+    <t>21.10.202617</t>
+  </si>
+  <si>
+    <t>21.10.202618</t>
+  </si>
+  <si>
+    <t>21.10.202619</t>
+  </si>
+  <si>
+    <t>21.10.202620</t>
+  </si>
+  <si>
+    <t>21.10.202621</t>
+  </si>
+  <si>
+    <t>21.10.202622</t>
+  </si>
+  <si>
+    <t>21.10.202623</t>
+  </si>
+  <si>
+    <t>21.10.202624</t>
+  </si>
+  <si>
+    <t>21.10.202625</t>
+  </si>
+  <si>
+    <t>21.10.202626</t>
+  </si>
+  <si>
+    <t>21.10.202627</t>
+  </si>
+  <si>
+    <t>21.10.202628</t>
+  </si>
+  <si>
+    <t>21.10.202629</t>
+  </si>
+  <si>
+    <t>21.10.202630</t>
+  </si>
+  <si>
+    <t>21.10.202631</t>
+  </si>
+  <si>
+    <t>21.10.202632</t>
+  </si>
+  <si>
+    <t>21.10.202633</t>
+  </si>
+  <si>
+    <t>21.10.202634</t>
+  </si>
+  <si>
+    <t>21.10.202635</t>
+  </si>
+  <si>
+    <t>21.10.202636</t>
+  </si>
+  <si>
+    <t>21.10.202637</t>
+  </si>
+  <si>
+    <t>21.10.202638</t>
+  </si>
+  <si>
+    <t>21.10.202639</t>
+  </si>
+  <si>
+    <t>21.10.202640</t>
+  </si>
+  <si>
+    <t>21.10.202641</t>
+  </si>
+  <si>
+    <t>21.10.202642</t>
+  </si>
+  <si>
+    <t>21.10.202643</t>
+  </si>
+  <si>
+    <t>21.10.202644</t>
+  </si>
+  <si>
+    <t>21.10.202645</t>
+  </si>
+  <si>
+    <t>21.10.202646</t>
+  </si>
+  <si>
+    <t>21.10.202647</t>
+  </si>
+  <si>
+    <t>21.10.202648</t>
+  </si>
+  <si>
+    <t>21.10.202649</t>
+  </si>
+  <si>
+    <t>21.10.202650</t>
+  </si>
+  <si>
+    <t>21.10.202651</t>
+  </si>
+  <si>
+    <t>21.10.202652</t>
+  </si>
+  <si>
+    <t>21.10.202653</t>
+  </si>
+  <si>
+    <t>21.10.202654</t>
+  </si>
+  <si>
+    <t>21.10.202655</t>
+  </si>
+  <si>
+    <t>21.10.202656</t>
+  </si>
+  <si>
+    <t>21.10.202657</t>
+  </si>
+  <si>
+    <t>21.10.202658</t>
+  </si>
+  <si>
+    <t>21.10.202659</t>
+  </si>
+  <si>
+    <t>21.10.202660</t>
+  </si>
+  <si>
+    <t>21.10.202661</t>
+  </si>
+  <si>
+    <t>21.10.202662</t>
+  </si>
+  <si>
+    <t>21.10.202663</t>
+  </si>
+  <si>
+    <t>21.10.202664</t>
+  </si>
+  <si>
+    <t>21.10.202665</t>
+  </si>
+  <si>
+    <t>21.10.202666</t>
+  </si>
+  <si>
+    <t>21.10.202667</t>
+  </si>
+  <si>
+    <t>21.10.202668</t>
+  </si>
+  <si>
+    <t>21.10.202669</t>
+  </si>
+  <si>
+    <t>21.10.202670</t>
+  </si>
+  <si>
+    <t>21.10.202671</t>
+  </si>
+  <si>
+    <t>21.10.202672</t>
+  </si>
+  <si>
+    <t>21.10.202673</t>
+  </si>
+  <si>
+    <t>21.10.202674</t>
+  </si>
+  <si>
+    <t>21.10.202675</t>
+  </si>
+  <si>
+    <t>21.10.202676</t>
+  </si>
+  <si>
+    <t>21.10.202677</t>
+  </si>
+  <si>
+    <t>21.10.202678</t>
+  </si>
+  <si>
+    <t>21.10.202679</t>
+  </si>
+  <si>
+    <t>21.10.202680</t>
+  </si>
+  <si>
+    <t>21.10.202681</t>
+  </si>
+  <si>
+    <t>21.10.202682</t>
+  </si>
+  <si>
+    <t>21.10.202683</t>
+  </si>
+  <si>
+    <t>21.10.202684</t>
+  </si>
+  <si>
+    <t>21.10.202685</t>
+  </si>
+  <si>
+    <t>21.10.202686</t>
+  </si>
+  <si>
+    <t>21.10.202687</t>
+  </si>
+  <si>
+    <t>21.10.202688</t>
+  </si>
+  <si>
+    <t>21.10.202689</t>
+  </si>
+  <si>
+    <t>21.10.202690</t>
+  </si>
+  <si>
+    <t>21.10.202691</t>
+  </si>
+  <si>
+    <t>21.10.202692</t>
   </si>
 </sst>
 </file>
@@ -976,13 +976,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46310</v>
+        <v>46315</v>
       </c>
       <c r="B2">
-        <v>1831.749</v>
+        <v>1476.59</v>
       </c>
       <c r="C2">
-        <v>1735</v>
+        <v>1931</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -993,13 +993,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46310.01041666666</v>
+        <v>46315.01041666666</v>
       </c>
       <c r="B3">
-        <v>1837.179</v>
+        <v>1447.031</v>
       </c>
       <c r="C3">
-        <v>1703</v>
+        <v>1889</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1010,13 +1010,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46310.02083333334</v>
+        <v>46315.02083333334</v>
       </c>
       <c r="B4">
-        <v>1839.563</v>
+        <v>1393.5</v>
       </c>
       <c r="C4">
-        <v>1696</v>
+        <v>1800</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1027,13 +1027,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46310.03125</v>
+        <v>46315.03125</v>
       </c>
       <c r="B5">
-        <v>1842.049</v>
+        <v>1368.284</v>
       </c>
       <c r="C5">
-        <v>1698</v>
+        <v>1694</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1044,13 +1044,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46310.04166666666</v>
+        <v>46315.04166666666</v>
       </c>
       <c r="B6">
-        <v>1811.621</v>
+        <v>1317.92</v>
       </c>
       <c r="C6">
-        <v>1709</v>
+        <v>1559</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1061,13 +1061,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46310.05208333334</v>
+        <v>46315.05208333334</v>
       </c>
       <c r="B7">
-        <v>1804.002</v>
+        <v>1295.396</v>
       </c>
       <c r="C7">
-        <v>1734</v>
+        <v>1427</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1078,13 +1078,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46310.0625</v>
+        <v>46315.0625</v>
       </c>
       <c r="B8">
-        <v>1801.719</v>
+        <v>1275.516</v>
       </c>
       <c r="C8">
-        <v>1792</v>
+        <v>1377</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1095,13 +1095,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46310.07291666666</v>
+        <v>46315.07291666666</v>
       </c>
       <c r="B9">
-        <v>1795.08</v>
+        <v>1246.126</v>
       </c>
       <c r="C9">
-        <v>1843</v>
+        <v>1350</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1112,13 +1112,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46310.08333333334</v>
+        <v>46315.08333333334</v>
       </c>
       <c r="B10">
-        <v>1777.478</v>
+        <v>1108.346</v>
       </c>
       <c r="C10">
-        <v>1879</v>
+        <v>1338</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1129,13 +1129,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46310.09375</v>
+        <v>46315.09375</v>
       </c>
       <c r="B11">
-        <v>1764.128</v>
+        <v>1072.744</v>
       </c>
       <c r="C11">
-        <v>1827</v>
+        <v>1307</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1146,13 +1146,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46310.10416666666</v>
+        <v>46315.10416666666</v>
       </c>
       <c r="B12">
-        <v>1761</v>
+        <v>1037.705</v>
       </c>
       <c r="C12">
-        <v>1767</v>
+        <v>1232</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1163,13 +1163,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46310.11458333334</v>
+        <v>46315.11458333334</v>
       </c>
       <c r="B13">
-        <v>1749.048</v>
+        <v>1005.817</v>
       </c>
       <c r="C13">
-        <v>1784</v>
+        <v>1199</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1180,13 +1180,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46310.125</v>
+        <v>46315.125</v>
       </c>
       <c r="B14">
-        <v>1753.55</v>
+        <v>973.033</v>
       </c>
       <c r="C14">
-        <v>1803</v>
+        <v>1196</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1197,13 +1197,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46310.13541666666</v>
+        <v>46315.13541666666</v>
       </c>
       <c r="B15">
-        <v>1736.304</v>
+        <v>947.698</v>
       </c>
       <c r="C15">
-        <v>1842</v>
+        <v>1172</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1214,13 +1214,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46310.14583333334</v>
+        <v>46315.14583333334</v>
       </c>
       <c r="B16">
-        <v>1713.341</v>
+        <v>921.6</v>
       </c>
       <c r="C16">
-        <v>1904</v>
+        <v>1120</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1231,13 +1231,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46310.15625</v>
+        <v>46315.15625</v>
       </c>
       <c r="B17">
-        <v>1694.465</v>
+        <v>903.802</v>
       </c>
       <c r="C17">
-        <v>1968</v>
+        <v>1045</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1248,13 +1248,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46310.16666666666</v>
+        <v>46315.16666666666</v>
       </c>
       <c r="B18">
-        <v>1665.902</v>
+        <v>850.353</v>
       </c>
       <c r="C18">
-        <v>1971</v>
+        <v>958</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1265,13 +1265,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46310.17708333334</v>
+        <v>46315.17708333334</v>
       </c>
       <c r="B19">
-        <v>1643.951</v>
+        <v>833.466</v>
       </c>
       <c r="C19">
-        <v>1883</v>
+        <v>963</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1282,13 +1282,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46310.1875</v>
+        <v>46315.1875</v>
       </c>
       <c r="B20">
-        <v>1625.348</v>
+        <v>812.87</v>
       </c>
       <c r="C20">
-        <v>1830</v>
+        <v>990</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1299,13 +1299,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46310.19791666666</v>
+        <v>46315.19791666666</v>
       </c>
       <c r="B21">
-        <v>1617.244</v>
+        <v>793.735</v>
       </c>
       <c r="C21">
-        <v>1726</v>
+        <v>963</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1316,13 +1316,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46310.20833333334</v>
+        <v>46315.20833333334</v>
       </c>
       <c r="B22">
-        <v>1585.641</v>
+        <v>741.808</v>
       </c>
       <c r="C22">
-        <v>1718</v>
+        <v>921</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1333,13 +1333,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46310.21875</v>
+        <v>46315.21875</v>
       </c>
       <c r="B23">
-        <v>1564.972</v>
+        <v>711.943</v>
       </c>
       <c r="C23">
-        <v>1686</v>
+        <v>900</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1350,13 +1350,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46310.22916666666</v>
+        <v>46315.22916666666</v>
       </c>
       <c r="B24">
-        <v>1550.213</v>
+        <v>683.397</v>
       </c>
       <c r="C24">
-        <v>1632</v>
+        <v>879</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1367,13 +1367,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46310.23958333334</v>
+        <v>46315.23958333334</v>
       </c>
       <c r="B25">
-        <v>1531.329</v>
+        <v>655.04</v>
       </c>
       <c r="C25">
-        <v>1613</v>
+        <v>854</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1384,13 +1384,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46310.25</v>
+        <v>46315.25</v>
       </c>
       <c r="B26">
-        <v>1469.595</v>
+        <v>626.845</v>
       </c>
       <c r="C26">
-        <v>1589</v>
+        <v>825</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1401,13 +1401,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46310.26041666666</v>
+        <v>46315.26041666666</v>
       </c>
       <c r="B27">
-        <v>1455.824</v>
+        <v>609.077</v>
       </c>
       <c r="C27">
-        <v>1486</v>
+        <v>874</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1418,13 +1418,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46310.27083333334</v>
+        <v>46315.27083333334</v>
       </c>
       <c r="B28">
-        <v>1438.289</v>
+        <v>601.01</v>
       </c>
       <c r="C28">
-        <v>1453</v>
+        <v>850</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1435,13 +1435,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46310.28125</v>
+        <v>46315.28125</v>
       </c>
       <c r="B29">
-        <v>1427.149</v>
+        <v>548.648</v>
       </c>
       <c r="C29">
-        <v>1423</v>
+        <v>826</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1452,13 +1452,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46310.29166666666</v>
+        <v>46315.29166666666</v>
       </c>
       <c r="B30">
-        <v>1418.34</v>
+        <v>516.064</v>
       </c>
       <c r="C30">
-        <v>1351</v>
+        <v>841</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1469,13 +1469,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46310.30208333334</v>
+        <v>46315.30208333334</v>
       </c>
       <c r="B31">
-        <v>1405.981</v>
+        <v>499.512</v>
       </c>
       <c r="C31">
-        <v>1294</v>
+        <v>856</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1486,13 +1486,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46310.3125</v>
+        <v>46315.3125</v>
       </c>
       <c r="B32">
-        <v>1391.904</v>
+        <v>399.977</v>
       </c>
       <c r="C32">
-        <v>1298</v>
+        <v>788</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1503,13 +1503,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46310.32291666666</v>
+        <v>46315.32291666666</v>
       </c>
       <c r="B33">
-        <v>1385.515</v>
+        <v>376.008</v>
       </c>
       <c r="C33">
-        <v>1245</v>
+        <v>723</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1520,13 +1520,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46310.33333333334</v>
+        <v>46315.33333333334</v>
       </c>
       <c r="B34">
-        <v>1378.261</v>
+        <v>388.134</v>
       </c>
       <c r="C34">
-        <v>1097</v>
+        <v>638</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1537,13 +1537,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46310.34375</v>
+        <v>46315.34375</v>
       </c>
       <c r="B35">
-        <v>1350.894</v>
+        <v>364.64</v>
       </c>
       <c r="C35">
-        <v>989</v>
+        <v>574</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1554,13 +1554,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46310.35416666666</v>
+        <v>46315.35416666666</v>
       </c>
       <c r="B36">
-        <v>1322.854</v>
+        <v>332.301</v>
       </c>
       <c r="C36">
-        <v>888</v>
+        <v>475</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1571,13 +1571,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46310.36458333334</v>
+        <v>46315.36458333334</v>
       </c>
       <c r="B37">
-        <v>1283.976</v>
+        <v>308.466</v>
       </c>
       <c r="C37">
-        <v>825</v>
+        <v>420</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1588,13 +1588,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46310.375</v>
+        <v>46315.375</v>
       </c>
       <c r="B38">
-        <v>1250.559</v>
+        <v>284.964</v>
       </c>
       <c r="C38">
-        <v>885</v>
+        <v>365</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1605,13 +1605,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46310.38541666666</v>
+        <v>46315.38541666666</v>
       </c>
       <c r="B39">
-        <v>1278.322</v>
+        <v>276.459</v>
       </c>
       <c r="C39">
-        <v>1033</v>
+        <v>320</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1622,13 +1622,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46310.39583333334</v>
+        <v>46315.39583333334</v>
       </c>
       <c r="B40">
-        <v>1306.267</v>
+        <v>270.556</v>
       </c>
       <c r="C40">
-        <v>1128</v>
+        <v>305</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1639,13 +1639,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46310.40625</v>
+        <v>46315.40625</v>
       </c>
       <c r="B41">
-        <v>1333.993</v>
+        <v>247.341</v>
       </c>
       <c r="C41">
-        <v>1193</v>
+        <v>300</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1656,13 +1656,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46310.41666666666</v>
+        <v>46315.41666666666</v>
       </c>
       <c r="B42">
-        <v>1386.432</v>
+        <v>218.013</v>
       </c>
       <c r="C42">
-        <v>1228</v>
+        <v>262</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1673,13 +1673,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46310.42708333334</v>
+        <v>46315.42708333334</v>
       </c>
       <c r="B43">
-        <v>1436.951</v>
+        <v>211.872</v>
       </c>
       <c r="C43">
-        <v>1285</v>
+        <v>227</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1690,13 +1690,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46310.4375</v>
+        <v>46315.4375</v>
       </c>
       <c r="B44">
-        <v>1487.893</v>
+        <v>192.759</v>
       </c>
       <c r="C44">
-        <v>1352</v>
+        <v>173</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1707,13 +1707,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46310.44791666666</v>
+        <v>46315.44791666666</v>
       </c>
       <c r="B45">
-        <v>1545.831</v>
+        <v>185.724</v>
       </c>
       <c r="C45">
-        <v>1463</v>
+        <v>113</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1724,13 +1724,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46310.45833333334</v>
+        <v>46315.45833333334</v>
       </c>
       <c r="B46">
-        <v>1602.801</v>
+        <v>202.413</v>
       </c>
       <c r="C46">
-        <v>1546</v>
+        <v>70</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1741,13 +1741,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46310.46875</v>
+        <v>46315.46875</v>
       </c>
       <c r="B47">
-        <v>1646.772</v>
+        <v>200.558</v>
       </c>
       <c r="C47">
-        <v>1700</v>
+        <v>53</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1758,13 +1758,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46310.47916666666</v>
+        <v>46315.47916666666</v>
       </c>
       <c r="B48">
-        <v>1688.253</v>
+        <v>187.226</v>
       </c>
       <c r="C48">
-        <v>1781</v>
+        <v>36</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1775,13 +1775,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46310.48958333334</v>
+        <v>46315.48958333334</v>
       </c>
       <c r="B49">
-        <v>1723.599</v>
+        <v>185.565</v>
       </c>
       <c r="C49">
-        <v>1864</v>
+        <v>24</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1792,13 +1792,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46310.5</v>
+        <v>46315.5</v>
       </c>
       <c r="B50">
-        <v>1769.531</v>
+        <v>180.573</v>
       </c>
       <c r="C50">
-        <v>2044</v>
+        <v>12</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1809,13 +1809,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46310.51041666666</v>
+        <v>46315.51041666666</v>
       </c>
       <c r="B51">
-        <v>1803.827</v>
+        <v>180.167</v>
       </c>
       <c r="C51">
-        <v>2050</v>
+        <v>6</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1826,13 +1826,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46310.52083333334</v>
+        <v>46315.52083333334</v>
       </c>
       <c r="B52">
-        <v>1835.886</v>
+        <v>180.033</v>
       </c>
       <c r="C52">
-        <v>1966</v>
+        <v>8</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1843,13 +1843,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46310.53125</v>
+        <v>46315.53125</v>
       </c>
       <c r="B53">
-        <v>1868.236</v>
+        <v>179.913</v>
       </c>
       <c r="C53">
-        <v>1816</v>
+        <v>12</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1860,13 +1860,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46310.54166666666</v>
+        <v>46315.54166666666</v>
       </c>
       <c r="B54">
-        <v>1901.065</v>
+        <v>163.295</v>
       </c>
       <c r="C54">
-        <v>1881</v>
+        <v>19</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1877,13 +1877,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46310.55208333334</v>
+        <v>46315.55208333334</v>
       </c>
       <c r="B55">
-        <v>1911.647</v>
+        <v>165.084</v>
       </c>
       <c r="C55">
-        <v>1906</v>
+        <v>21</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1894,13 +1894,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46310.5625</v>
+        <v>46315.5625</v>
       </c>
       <c r="B56">
-        <v>1917.017</v>
+        <v>166.77</v>
       </c>
       <c r="C56">
-        <v>1985</v>
+        <v>20</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1911,13 +1911,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46310.57291666666</v>
+        <v>46315.57291666666</v>
       </c>
       <c r="B57">
-        <v>1921.364</v>
+        <v>169.065</v>
       </c>
       <c r="C57">
-        <v>2024</v>
+        <v>12</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1928,13 +1928,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46310.58333333334</v>
+        <v>46315.58333333334</v>
       </c>
       <c r="B58">
-        <v>1935.575</v>
+        <v>166.323</v>
       </c>
       <c r="C58">
-        <v>2014</v>
+        <v>10</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1945,13 +1945,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46310.59375</v>
+        <v>46315.59375</v>
       </c>
       <c r="B59">
-        <v>1901.823</v>
+        <v>174.214</v>
       </c>
       <c r="C59">
-        <v>1960</v>
+        <v>10</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1962,13 +1962,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46310.60416666666</v>
+        <v>46315.60416666666</v>
       </c>
       <c r="B60">
-        <v>1867.47</v>
+        <v>184.867</v>
       </c>
       <c r="C60">
-        <v>2050</v>
+        <v>18</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1979,13 +1979,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46310.61458333334</v>
+        <v>46315.61458333334</v>
       </c>
       <c r="B61">
-        <v>1831.503</v>
+        <v>193.991</v>
       </c>
       <c r="C61">
-        <v>2207</v>
+        <v>29</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -1996,13 +1996,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46310.625</v>
+        <v>46315.625</v>
       </c>
       <c r="B62">
-        <v>1780.797</v>
+        <v>231.734</v>
       </c>
       <c r="C62">
-        <v>2207</v>
+        <v>53</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2013,13 +2013,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46310.63541666666</v>
+        <v>46315.63541666666</v>
       </c>
       <c r="B63">
-        <v>1714.992</v>
+        <v>246.606</v>
       </c>
       <c r="C63">
-        <v>2163</v>
+        <v>82</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2030,13 +2030,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46310.64583333334</v>
+        <v>46315.64583333334</v>
       </c>
       <c r="B64">
-        <v>1651.315</v>
+        <v>263.107</v>
       </c>
       <c r="C64">
-        <v>2110</v>
+        <v>97</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2047,13 +2047,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46310.65625</v>
+        <v>46315.65625</v>
       </c>
       <c r="B65">
-        <v>1589.091</v>
+        <v>279.324</v>
       </c>
       <c r="C65">
-        <v>2154</v>
+        <v>131</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2064,13 +2064,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46310.66666666666</v>
+        <v>46315.66666666666</v>
       </c>
       <c r="B66">
-        <v>1399.738</v>
+        <v>299.605</v>
       </c>
       <c r="C66">
-        <v>2103</v>
+        <v>147</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2081,13 +2081,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46310.67708333334</v>
+        <v>46315.67708333334</v>
       </c>
       <c r="B67">
-        <v>1344.638</v>
+        <v>327.844</v>
       </c>
       <c r="C67">
-        <v>1991</v>
+        <v>175</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2098,13 +2098,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46310.6875</v>
+        <v>46315.6875</v>
       </c>
       <c r="B68">
-        <v>1293.719</v>
+        <v>354.761</v>
       </c>
       <c r="C68">
-        <v>1923</v>
+        <v>224</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2115,13 +2115,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46310.69791666666</v>
+        <v>46315.69791666666</v>
       </c>
       <c r="B69">
-        <v>1246.164</v>
+        <v>383.831</v>
       </c>
       <c r="C69">
-        <v>1834</v>
+        <v>270</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2132,13 +2132,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46310.70833333334</v>
+        <v>46315.70833333334</v>
       </c>
       <c r="B70">
-        <v>1199.716</v>
+        <v>435.831</v>
       </c>
       <c r="C70">
-        <v>1738</v>
+        <v>333</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2149,13 +2149,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46310.71875</v>
+        <v>46315.71875</v>
       </c>
       <c r="B71">
-        <v>1187.677</v>
+        <v>474.599</v>
       </c>
       <c r="C71">
-        <v>1632</v>
+        <v>393</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2166,13 +2166,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46310.72916666666</v>
+        <v>46315.72916666666</v>
       </c>
       <c r="B72">
-        <v>1176.972</v>
+        <v>517.693</v>
       </c>
       <c r="C72">
-        <v>1542</v>
+        <v>439</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2183,13 +2183,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46310.73958333334</v>
+        <v>46315.73958333334</v>
       </c>
       <c r="B73">
-        <v>1170.283</v>
+        <v>562.136</v>
       </c>
       <c r="C73">
-        <v>1585</v>
+        <v>475</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2200,13 +2200,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46310.75</v>
+        <v>46315.75</v>
       </c>
       <c r="B74">
-        <v>1161.014</v>
+        <v>572.966</v>
       </c>
       <c r="C74">
-        <v>1551</v>
+        <v>499</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2217,13 +2217,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46310.76041666666</v>
+        <v>46315.76041666666</v>
       </c>
       <c r="B75">
-        <v>1170.815</v>
+        <v>598.147</v>
       </c>
       <c r="C75">
-        <v>1515</v>
+        <v>506</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2234,13 +2234,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46310.77083333334</v>
+        <v>46315.77083333334</v>
       </c>
       <c r="B76">
-        <v>1178.692</v>
+        <v>618.771</v>
       </c>
       <c r="C76">
-        <v>1547</v>
+        <v>522</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2251,13 +2251,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46310.78125</v>
+        <v>46315.78125</v>
       </c>
       <c r="B77">
-        <v>1186.182</v>
+        <v>640.8</v>
       </c>
       <c r="C77">
-        <v>1573</v>
+        <v>529</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2268,13 +2268,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46310.79166666666</v>
+        <v>46315.79166666666</v>
       </c>
       <c r="B78">
-        <v>1205.343</v>
+        <v>663.0410000000001</v>
       </c>
       <c r="C78">
-        <v>1559</v>
+        <v>550</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2285,13 +2285,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46310.80208333334</v>
+        <v>46315.80208333334</v>
       </c>
       <c r="B79">
-        <v>1216.753</v>
+        <v>679.505</v>
       </c>
       <c r="C79">
-        <v>1529</v>
+        <v>598</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2302,13 +2302,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46310.8125</v>
+        <v>46315.8125</v>
       </c>
       <c r="B80">
-        <v>1228.486</v>
+        <v>693.466</v>
       </c>
       <c r="C80">
-        <v>1533</v>
+        <v>617</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2319,13 +2319,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46310.82291666666</v>
+        <v>46315.82291666666</v>
       </c>
       <c r="B81">
-        <v>1238.607</v>
+        <v>708.593</v>
       </c>
       <c r="C81">
-        <v>1582</v>
+        <v>642</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2336,13 +2336,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46310.83333333334</v>
+        <v>46315.83333333334</v>
       </c>
       <c r="B82">
-        <v>1265.043</v>
+        <v>723.2430000000001</v>
       </c>
       <c r="C82">
-        <v>1708</v>
+        <v>632</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2353,13 +2353,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46310.84375</v>
+        <v>46315.84375</v>
       </c>
       <c r="B83">
-        <v>1267.079</v>
+        <v>725.21</v>
       </c>
       <c r="C83">
-        <v>1764</v>
+        <v>629</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2370,13 +2370,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46310.85416666666</v>
+        <v>46315.85416666666</v>
       </c>
       <c r="B84">
-        <v>1270.069</v>
+        <v>730.266</v>
       </c>
       <c r="C84">
-        <v>1759</v>
+        <v>627</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2387,13 +2387,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46310.86458333334</v>
+        <v>46315.86458333334</v>
       </c>
       <c r="B85">
-        <v>1272.317</v>
+        <v>735.178</v>
       </c>
       <c r="C85">
-        <v>1759</v>
+        <v>605</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2404,13 +2404,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46310.875</v>
+        <v>46315.875</v>
       </c>
       <c r="B86">
-        <v>1274.889</v>
+        <v>738.188</v>
       </c>
       <c r="C86">
-        <v>1740</v>
+        <v>610</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2421,13 +2421,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46310.88541666666</v>
+        <v>46315.88541666666</v>
       </c>
       <c r="B87">
-        <v>1277.918</v>
+        <v>738.347</v>
       </c>
       <c r="C87">
-        <v>1729</v>
+        <v>613</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2438,13 +2438,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46310.89583333334</v>
+        <v>46315.89583333334</v>
       </c>
       <c r="B88">
-        <v>1280.61</v>
+        <v>737.174</v>
       </c>
       <c r="C88">
-        <v>1747</v>
+        <v>600</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2455,13 +2455,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46310.90625</v>
+        <v>46315.90625</v>
       </c>
       <c r="B89">
-        <v>1286.181</v>
+        <v>736.455</v>
       </c>
       <c r="C89">
-        <v>1768</v>
+        <v>588</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2472,13 +2472,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46310.91666666666</v>
+        <v>46315.91666666666</v>
       </c>
       <c r="B90">
-        <v>1267.147</v>
+        <v>729.514</v>
       </c>
       <c r="C90">
-        <v>1805</v>
+        <v>583</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2489,13 +2489,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46310.92708333334</v>
+        <v>46315.92708333334</v>
       </c>
       <c r="B91">
-        <v>1272.717</v>
+        <v>725.297</v>
       </c>
       <c r="C91">
-        <v>1778</v>
+        <v>579</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2506,13 +2506,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46310.9375</v>
+        <v>46315.9375</v>
       </c>
       <c r="B92">
-        <v>1283.241</v>
+        <v>721.716</v>
       </c>
       <c r="C92">
-        <v>1783</v>
+        <v>569</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2523,13 +2523,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46310.94791666666</v>
+        <v>46315.94791666666</v>
       </c>
       <c r="B93">
-        <v>1299.698</v>
+        <v>719.05</v>
       </c>
       <c r="C93">
-        <v>1812</v>
+        <v>552</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2540,13 +2540,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46310.95833333334</v>
+        <v>46315.95833333334</v>
       </c>
       <c r="B94">
-        <v>1477.868</v>
+        <v>662.495</v>
       </c>
       <c r="C94">
-        <v>1819</v>
+        <v>542</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2557,13 +2557,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46310.96875</v>
+        <v>46315.96875</v>
       </c>
       <c r="B95">
-        <v>1486.738</v>
+        <v>655.026</v>
       </c>
       <c r="C95">
-        <v>1865</v>
+        <v>526</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2574,13 +2574,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46310.97916666666</v>
+        <v>46315.97916666666</v>
       </c>
       <c r="B96">
-        <v>1505.366</v>
+        <v>637.314</v>
       </c>
       <c r="C96">
-        <v>1924</v>
+        <v>515</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2591,13 +2591,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46310.98958333334</v>
+        <v>46315.98958333334</v>
       </c>
       <c r="B97">
-        <v>1467.994</v>
+        <v>629.715</v>
       </c>
       <c r="C97">
-        <v>1845</v>
+        <v>534</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2608,13 +2608,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46311</v>
+        <v>46316</v>
       </c>
       <c r="B98">
-        <v>1580.982</v>
+        <v>575.335</v>
       </c>
       <c r="C98">
-        <v>1722</v>
+        <v>551</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2625,13 +2625,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46311.01041666666</v>
+        <v>46316.01041666666</v>
       </c>
       <c r="B99">
-        <v>1575.836</v>
+        <v>566.782</v>
       </c>
       <c r="C99">
-        <v>1633</v>
+        <v>554</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2642,13 +2642,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46311.02083333334</v>
+        <v>46316.02083333334</v>
       </c>
       <c r="B100">
-        <v>1582.94</v>
+        <v>558.311</v>
       </c>
       <c r="C100">
-        <v>1563</v>
+        <v>542</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2659,13 +2659,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46311.03125</v>
+        <v>46316.03125</v>
       </c>
       <c r="B101">
-        <v>1571.718</v>
+        <v>549.244</v>
       </c>
       <c r="C101">
-        <v>1642</v>
+        <v>533</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2676,13 +2676,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46311.04166666666</v>
+        <v>46316.04166666666</v>
       </c>
       <c r="B102">
-        <v>1534.452</v>
+        <v>553.963</v>
       </c>
       <c r="C102">
-        <v>1670</v>
+        <v>546</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2693,13 +2693,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46311.05208333334</v>
+        <v>46316.05208333334</v>
       </c>
       <c r="B103">
-        <v>1522.574</v>
+        <v>555.462</v>
       </c>
       <c r="C103">
-        <v>1678</v>
+        <v>574</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2710,13 +2710,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46311.0625</v>
+        <v>46316.0625</v>
       </c>
       <c r="B104">
-        <v>1515.981</v>
+        <v>549.395</v>
       </c>
       <c r="C104">
-        <v>1718</v>
+        <v>594</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2727,13 +2727,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46311.07291666666</v>
+        <v>46316.07291666666</v>
       </c>
       <c r="B105">
-        <v>1505.17</v>
+        <v>539.942</v>
       </c>
       <c r="C105">
-        <v>1750</v>
+        <v>574</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2744,13 +2744,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46311.08333333334</v>
+        <v>46316.08333333334</v>
       </c>
       <c r="B106">
-        <v>1469.421</v>
+        <v>515.899</v>
       </c>
       <c r="C106">
-        <v>1721</v>
+        <v>537</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2761,13 +2761,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46311.09375</v>
+        <v>46316.09375</v>
       </c>
       <c r="B107">
-        <v>1461.798</v>
+        <v>516.421</v>
       </c>
       <c r="C107">
-        <v>1645</v>
+        <v>523</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2778,13 +2778,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46311.10416666666</v>
+        <v>46316.10416666666</v>
       </c>
       <c r="B108">
-        <v>1448.094</v>
+        <v>521.8099999999999</v>
       </c>
       <c r="C108">
-        <v>1604</v>
+        <v>505</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2795,13 +2795,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46311.11458333334</v>
+        <v>46316.11458333334</v>
       </c>
       <c r="B109">
-        <v>1460.27</v>
+        <v>521.904</v>
       </c>
       <c r="C109">
-        <v>1574</v>
+        <v>490</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2812,13 +2812,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46311.125</v>
+        <v>46316.125</v>
       </c>
       <c r="B110">
-        <v>1444.246</v>
+        <v>541.598</v>
       </c>
       <c r="C110">
-        <v>1518</v>
+        <v>493</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2829,13 +2829,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46311.13541666666</v>
+        <v>46316.13541666666</v>
       </c>
       <c r="B111">
-        <v>1431.126</v>
+        <v>545.636</v>
       </c>
       <c r="C111">
-        <v>1483</v>
+        <v>485</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2846,13 +2846,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46311.14583333334</v>
+        <v>46316.14583333334</v>
       </c>
       <c r="B112">
-        <v>1424.831</v>
+        <v>550.8869999999999</v>
       </c>
       <c r="C112">
-        <v>1504</v>
+        <v>476</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2863,13 +2863,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46311.15625</v>
+        <v>46316.15625</v>
       </c>
       <c r="B113">
-        <v>1422.514</v>
+        <v>559.639</v>
       </c>
       <c r="C113">
-        <v>1553</v>
+        <v>482</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2880,13 +2880,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46311.16666666666</v>
+        <v>46316.16666666666</v>
       </c>
       <c r="B114">
-        <v>1424.231</v>
+        <v>578.811</v>
       </c>
       <c r="C114">
-        <v>1551</v>
+        <v>509</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2897,13 +2897,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46311.17708333334</v>
+        <v>46316.17708333334</v>
       </c>
       <c r="B115">
-        <v>1404.097</v>
+        <v>585.715</v>
       </c>
       <c r="C115">
-        <v>1521</v>
+        <v>583</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2914,13 +2914,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46311.1875</v>
+        <v>46316.1875</v>
       </c>
       <c r="B116">
-        <v>1394.278</v>
+        <v>593.921</v>
       </c>
       <c r="C116">
-        <v>1496</v>
+        <v>646</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2931,13 +2931,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46311.19791666666</v>
+        <v>46316.19791666666</v>
       </c>
       <c r="B117">
-        <v>1374.658</v>
+        <v>603.081</v>
       </c>
       <c r="C117">
-        <v>1564</v>
+        <v>682</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2948,13 +2948,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46311.20833333334</v>
+        <v>46316.20833333334</v>
       </c>
       <c r="B118">
-        <v>1366.209</v>
+        <v>605.341</v>
       </c>
       <c r="C118">
-        <v>1596</v>
+        <v>698</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2965,13 +2965,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46311.21875</v>
+        <v>46316.21875</v>
       </c>
       <c r="B119">
-        <v>1357.363</v>
+        <v>611.621</v>
       </c>
       <c r="C119">
-        <v>1562</v>
+        <v>662</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2982,13 +2982,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46311.22916666666</v>
+        <v>46316.22916666666</v>
       </c>
       <c r="B120">
-        <v>1350.17</v>
+        <v>614.4349999999999</v>
       </c>
       <c r="C120">
-        <v>1606</v>
+        <v>707</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -2999,13 +2999,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46311.23958333334</v>
+        <v>46316.23958333334</v>
       </c>
       <c r="B121">
-        <v>1342.49</v>
+        <v>623.889</v>
       </c>
       <c r="C121">
-        <v>1643</v>
+        <v>762</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3016,13 +3016,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46311.25</v>
+        <v>46316.25</v>
       </c>
       <c r="B122">
-        <v>1279.213</v>
+        <v>611.425</v>
       </c>
       <c r="C122">
-        <v>1657</v>
+        <v>804</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3033,13 +3033,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46311.26041666666</v>
+        <v>46316.26041666666</v>
       </c>
       <c r="B123">
-        <v>1265.283</v>
+        <v>618.261</v>
       </c>
       <c r="C123">
-        <v>1684</v>
+        <v>812</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3050,13 +3050,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46311.27083333334</v>
+        <v>46316.27083333334</v>
       </c>
       <c r="B124">
-        <v>1251.974</v>
+        <v>630.205</v>
       </c>
       <c r="C124">
-        <v>1662</v>
+        <v>814</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3067,13 +3067,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46311.28125</v>
+        <v>46316.28125</v>
       </c>
       <c r="B125">
-        <v>1245.114</v>
+        <v>631.958</v>
       </c>
       <c r="C125">
-        <v>1663</v>
+        <v>839</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3084,13 +3084,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46311.29166666666</v>
+        <v>46316.29166666666</v>
       </c>
       <c r="B126">
-        <v>1227.887</v>
+        <v>609.3630000000001</v>
       </c>
       <c r="C126">
-        <v>1639</v>
+        <v>851</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3101,13 +3101,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46311.30208333334</v>
+        <v>46316.30208333334</v>
       </c>
       <c r="B127">
-        <v>1213.85</v>
+        <v>612.254</v>
       </c>
       <c r="C127">
-        <v>1616</v>
+        <v>847</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3118,13 +3118,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46311.3125</v>
+        <v>46316.3125</v>
       </c>
       <c r="B128">
-        <v>1192.769</v>
+        <v>625.27</v>
       </c>
       <c r="C128">
-        <v>1538</v>
+        <v>864</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3135,13 +3135,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46311.32291666666</v>
+        <v>46316.32291666666</v>
       </c>
       <c r="B129">
-        <v>1177.878</v>
+        <v>626.982</v>
       </c>
       <c r="C129">
-        <v>1486</v>
+        <v>834</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3152,13 +3152,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46311.33333333334</v>
+        <v>46316.33333333334</v>
       </c>
       <c r="B130">
-        <v>1256.566</v>
+        <v>699.966</v>
       </c>
       <c r="C130">
-        <v>1503</v>
+        <v>798</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3169,13 +3169,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46311.34375</v>
+        <v>46316.34375</v>
       </c>
       <c r="B131">
-        <v>1267.498</v>
+        <v>700.119</v>
       </c>
       <c r="C131">
-        <v>1515</v>
+        <v>763</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3186,13 +3186,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46311.35416666666</v>
+        <v>46316.35416666666</v>
       </c>
       <c r="B132">
-        <v>1290.019</v>
+        <v>701.492</v>
       </c>
       <c r="C132">
-        <v>1558</v>
+        <v>705</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3203,13 +3203,10 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46311.36458333334</v>
+        <v>46316.36458333334</v>
       </c>
       <c r="B133">
-        <v>1283.328</v>
-      </c>
-      <c r="C133">
-        <v>1702</v>
+        <v>697.279</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3220,13 +3217,10 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46311.375</v>
+        <v>46316.375</v>
       </c>
       <c r="B134">
-        <v>1267.766</v>
-      </c>
-      <c r="C134">
-        <v>1804</v>
+        <v>667.239</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3237,13 +3231,10 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46311.38541666666</v>
+        <v>46316.38541666666</v>
       </c>
       <c r="B135">
-        <v>1280.532</v>
-      </c>
-      <c r="C135">
-        <v>1825</v>
+        <v>684.149</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3254,13 +3245,10 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46311.39583333334</v>
+        <v>46316.39583333334</v>
       </c>
       <c r="B136">
-        <v>1293.744</v>
-      </c>
-      <c r="C136">
-        <v>1888</v>
+        <v>698.453</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3271,13 +3259,10 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46311.40625</v>
+        <v>46316.40625</v>
       </c>
       <c r="B137">
-        <v>1308.65</v>
-      </c>
-      <c r="C137">
-        <v>1931</v>
+        <v>713.4450000000001</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3288,13 +3273,10 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46311.41666666666</v>
+        <v>46316.41666666666</v>
       </c>
       <c r="B138">
-        <v>1280.942</v>
-      </c>
-      <c r="C138">
-        <v>1870</v>
+        <v>705.95</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3305,13 +3287,10 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46311.42708333334</v>
+        <v>46316.42708333334</v>
       </c>
       <c r="B139">
-        <v>1293.842</v>
-      </c>
-      <c r="C139">
-        <v>1885</v>
+        <v>721.025</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3322,13 +3301,10 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46311.4375</v>
+        <v>46316.4375</v>
       </c>
       <c r="B140">
-        <v>1308.062</v>
-      </c>
-      <c r="C140">
-        <v>1912</v>
+        <v>736.481</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3339,13 +3315,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46311.44791666666</v>
+        <v>46316.44791666666</v>
       </c>
       <c r="B141">
-        <v>1318.602</v>
-      </c>
-      <c r="C141">
-        <v>1912</v>
+        <v>748.211</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3356,13 +3329,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46311.45833333334</v>
+        <v>46316.45833333334</v>
       </c>
       <c r="B142">
-        <v>1358.6</v>
-      </c>
-      <c r="C142">
-        <v>1892</v>
+        <v>800.8</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3373,13 +3343,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46311.46875</v>
+        <v>46316.46875</v>
       </c>
       <c r="B143">
-        <v>1366.415</v>
-      </c>
-      <c r="C143">
-        <v>1908</v>
+        <v>814.471</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3390,13 +3357,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46311.47916666666</v>
+        <v>46316.47916666666</v>
       </c>
       <c r="B144">
-        <v>1372.395</v>
-      </c>
-      <c r="C144">
-        <v>1906</v>
+        <v>841.831</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3407,13 +3371,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46311.48958333334</v>
+        <v>46316.48958333334</v>
       </c>
       <c r="B145">
-        <v>1376.25</v>
-      </c>
-      <c r="C145">
-        <v>1874</v>
+        <v>854.605</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3424,13 +3385,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46311.5</v>
+        <v>46316.5</v>
       </c>
       <c r="B146">
-        <v>1364.006</v>
-      </c>
-      <c r="C146">
-        <v>1841</v>
+        <v>881.051</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3441,13 +3399,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46311.51041666666</v>
+        <v>46316.51041666666</v>
       </c>
       <c r="B147">
-        <v>1358.348</v>
-      </c>
-      <c r="C147">
-        <v>1743</v>
+        <v>895.157</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3458,13 +3413,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46311.52083333334</v>
+        <v>46316.52083333334</v>
       </c>
       <c r="B148">
-        <v>1352.003</v>
-      </c>
-      <c r="C148">
-        <v>1705</v>
+        <v>909.141</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3475,10 +3427,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46311.53125</v>
+        <v>46316.53125</v>
       </c>
       <c r="B149">
-        <v>1343.992</v>
+        <v>923.009</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3489,10 +3441,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46311.54166666666</v>
+        <v>46316.54166666666</v>
       </c>
       <c r="B150">
-        <v>1336.513</v>
+        <v>942.269</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3503,10 +3455,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46311.55208333334</v>
+        <v>46316.55208333334</v>
       </c>
       <c r="B151">
-        <v>1331.115</v>
+        <v>957.739</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3517,10 +3469,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46311.5625</v>
+        <v>46316.5625</v>
       </c>
       <c r="B152">
-        <v>1326.533</v>
+        <v>973.726</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3531,10 +3483,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46311.57291666666</v>
+        <v>46316.57291666666</v>
       </c>
       <c r="B153">
-        <v>1320.661</v>
+        <v>990.8869999999999</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3545,10 +3497,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46311.58333333334</v>
+        <v>46316.58333333334</v>
       </c>
       <c r="B154">
-        <v>1331.763</v>
+        <v>1044.467</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3559,10 +3511,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46311.59375</v>
+        <v>46316.59375</v>
       </c>
       <c r="B155">
-        <v>1322.832</v>
+        <v>1072.247</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3573,10 +3525,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46311.60416666666</v>
+        <v>46316.60416666666</v>
       </c>
       <c r="B156">
-        <v>1308.915</v>
+        <v>1098.085</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3587,10 +3539,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46311.61458333334</v>
+        <v>46316.61458333334</v>
       </c>
       <c r="B157">
-        <v>1297.927</v>
+        <v>1123.953</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3601,10 +3553,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46311.625</v>
+        <v>46316.625</v>
       </c>
       <c r="B158">
-        <v>1267.886</v>
+        <v>1108.464</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3615,10 +3567,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46311.63541666666</v>
+        <v>46316.63541666666</v>
       </c>
       <c r="B159">
-        <v>1250.787</v>
+        <v>1137.986</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3629,10 +3581,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46311.64583333334</v>
+        <v>46316.64583333334</v>
       </c>
       <c r="B160">
-        <v>1231.544</v>
+        <v>1168.455</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3643,10 +3595,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46311.65625</v>
+        <v>46316.65625</v>
       </c>
       <c r="B161">
-        <v>1211.62</v>
+        <v>1194.973</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3657,10 +3609,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46311.66666666666</v>
+        <v>46316.66666666666</v>
       </c>
       <c r="B162">
-        <v>1057.421</v>
+        <v>1212.557</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -3671,10 +3623,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46311.67708333334</v>
+        <v>46316.67708333334</v>
       </c>
       <c r="B163">
-        <v>1027.365</v>
+        <v>1252.87</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -3685,10 +3637,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46311.6875</v>
+        <v>46316.6875</v>
       </c>
       <c r="B164">
-        <v>998.605</v>
+        <v>1289.963</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -3699,10 +3651,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46311.69791666666</v>
+        <v>46316.69791666666</v>
       </c>
       <c r="B165">
-        <v>968.1130000000001</v>
+        <v>1320.553</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -3713,10 +3665,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46311.70833333334</v>
+        <v>46316.70833333334</v>
       </c>
       <c r="B166">
-        <v>974.2430000000001</v>
+        <v>1369.452</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -3727,10 +3679,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46311.71875</v>
+        <v>46316.71875</v>
       </c>
       <c r="B167">
-        <v>966.776</v>
+        <v>1404.117</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -3741,10 +3693,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46311.72916666666</v>
+        <v>46316.72916666666</v>
       </c>
       <c r="B168">
-        <v>959.078</v>
+        <v>1443.435</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -3755,10 +3707,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46311.73958333334</v>
+        <v>46316.73958333334</v>
       </c>
       <c r="B169">
-        <v>953.099</v>
+        <v>1480.117</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -3769,10 +3721,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46311.75</v>
+        <v>46316.75</v>
       </c>
       <c r="B170">
-        <v>946.223</v>
+        <v>1574.901</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -3783,10 +3735,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46311.76041666666</v>
+        <v>46316.76041666666</v>
       </c>
       <c r="B171">
-        <v>939.279</v>
+        <v>1590.373</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -3797,10 +3749,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46311.77083333334</v>
+        <v>46316.77083333334</v>
       </c>
       <c r="B172">
-        <v>934.9160000000001</v>
+        <v>1606.308</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -3811,10 +3763,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46311.78125</v>
+        <v>46316.78125</v>
       </c>
       <c r="B173">
-        <v>930.221</v>
+        <v>1621.973</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -3825,10 +3777,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46311.79166666666</v>
+        <v>46316.79166666666</v>
       </c>
       <c r="B174">
-        <v>933.617</v>
+        <v>1667.364</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -3839,10 +3791,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46311.80208333334</v>
+        <v>46316.80208333334</v>
       </c>
       <c r="B175">
-        <v>931.436</v>
+        <v>1677.171</v>
       </c>
       <c r="D175">
         <v>78</v>
@@ -3853,10 +3805,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46311.8125</v>
+        <v>46316.8125</v>
       </c>
       <c r="B176">
-        <v>931.423</v>
+        <v>1683.382</v>
       </c>
       <c r="D176">
         <v>79</v>
@@ -3867,10 +3819,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46311.82291666666</v>
+        <v>46316.82291666666</v>
       </c>
       <c r="B177">
-        <v>929.6369999999999</v>
+        <v>1688.427</v>
       </c>
       <c r="D177">
         <v>80</v>
@@ -3881,10 +3833,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46311.83333333334</v>
+        <v>46316.83333333334</v>
       </c>
       <c r="B178">
-        <v>945.0549999999999</v>
+        <v>1688.314</v>
       </c>
       <c r="D178">
         <v>81</v>
@@ -3895,10 +3847,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46311.84375</v>
+        <v>46316.84375</v>
       </c>
       <c r="B179">
-        <v>943.747</v>
+        <v>1692.062</v>
       </c>
       <c r="D179">
         <v>82</v>
@@ -3909,10 +3861,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46311.85416666666</v>
+        <v>46316.85416666666</v>
       </c>
       <c r="B180">
-        <v>943.3339999999999</v>
+        <v>1691.531</v>
       </c>
       <c r="D180">
         <v>83</v>
@@ -3923,10 +3875,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46311.86458333334</v>
+        <v>46316.86458333334</v>
       </c>
       <c r="B181">
-        <v>941.231</v>
+        <v>1689.731</v>
       </c>
       <c r="D181">
         <v>84</v>
@@ -3937,10 +3889,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46311.875</v>
+        <v>46316.875</v>
       </c>
       <c r="B182">
-        <v>931.573</v>
+        <v>1688.268</v>
       </c>
       <c r="D182">
         <v>85</v>
@@ -3951,10 +3903,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46311.88541666666</v>
+        <v>46316.88541666666</v>
       </c>
       <c r="B183">
-        <v>933.4829999999999</v>
+        <v>1689.631</v>
       </c>
       <c r="D183">
         <v>86</v>
@@ -3965,10 +3917,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46311.89583333334</v>
+        <v>46316.89583333334</v>
       </c>
       <c r="B184">
-        <v>933.758</v>
+        <v>1692.048</v>
       </c>
       <c r="D184">
         <v>87</v>
@@ -3979,10 +3931,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46311.90625</v>
+        <v>46316.90625</v>
       </c>
       <c r="B185">
-        <v>934.4349999999999</v>
+        <v>1692.881</v>
       </c>
       <c r="D185">
         <v>88</v>
@@ -3993,10 +3945,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46311.91666666666</v>
+        <v>46316.91666666666</v>
       </c>
       <c r="B186">
-        <v>940.535</v>
+        <v>1666.074</v>
       </c>
       <c r="D186">
         <v>89</v>
@@ -4007,10 +3959,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46311.92708333334</v>
+        <v>46316.92708333334</v>
       </c>
       <c r="B187">
-        <v>944.9640000000001</v>
+        <v>1664.411</v>
       </c>
       <c r="D187">
         <v>90</v>
@@ -4021,10 +3973,10 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46311.9375</v>
+        <v>46316.9375</v>
       </c>
       <c r="B188">
-        <v>953.845</v>
+        <v>1667.802</v>
       </c>
       <c r="D188">
         <v>91</v>
@@ -4035,10 +3987,10 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46311.94791666666</v>
+        <v>46316.94791666666</v>
       </c>
       <c r="B189">
-        <v>965.016</v>
+        <v>1674.037</v>
       </c>
       <c r="D189">
         <v>92</v>

--- a/data_fetching/Entsoe/Wind_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Wind_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,568 +31,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>20.10.20261</t>
-  </si>
-  <si>
-    <t>20.10.20262</t>
-  </si>
-  <si>
-    <t>20.10.20263</t>
-  </si>
-  <si>
-    <t>20.10.20264</t>
-  </si>
-  <si>
-    <t>20.10.20265</t>
-  </si>
-  <si>
-    <t>20.10.20266</t>
-  </si>
-  <si>
-    <t>20.10.20267</t>
-  </si>
-  <si>
-    <t>20.10.20268</t>
-  </si>
-  <si>
-    <t>20.10.20269</t>
-  </si>
-  <si>
-    <t>20.10.202610</t>
-  </si>
-  <si>
-    <t>20.10.202611</t>
-  </si>
-  <si>
-    <t>20.10.202612</t>
-  </si>
-  <si>
-    <t>20.10.202613</t>
-  </si>
-  <si>
-    <t>20.10.202614</t>
-  </si>
-  <si>
-    <t>20.10.202615</t>
-  </si>
-  <si>
-    <t>20.10.202616</t>
-  </si>
-  <si>
-    <t>20.10.202617</t>
-  </si>
-  <si>
-    <t>20.10.202618</t>
-  </si>
-  <si>
-    <t>20.10.202619</t>
-  </si>
-  <si>
-    <t>20.10.202620</t>
-  </si>
-  <si>
-    <t>20.10.202621</t>
-  </si>
-  <si>
-    <t>20.10.202622</t>
-  </si>
-  <si>
-    <t>20.10.202623</t>
-  </si>
-  <si>
-    <t>20.10.202624</t>
-  </si>
-  <si>
-    <t>20.10.202625</t>
-  </si>
-  <si>
-    <t>20.10.202626</t>
-  </si>
-  <si>
-    <t>20.10.202627</t>
-  </si>
-  <si>
-    <t>20.10.202628</t>
-  </si>
-  <si>
-    <t>20.10.202629</t>
-  </si>
-  <si>
-    <t>20.10.202630</t>
-  </si>
-  <si>
-    <t>20.10.202631</t>
-  </si>
-  <si>
-    <t>20.10.202632</t>
-  </si>
-  <si>
-    <t>20.10.202633</t>
-  </si>
-  <si>
-    <t>20.10.202634</t>
-  </si>
-  <si>
-    <t>20.10.202635</t>
-  </si>
-  <si>
-    <t>20.10.202636</t>
-  </si>
-  <si>
-    <t>20.10.202637</t>
-  </si>
-  <si>
-    <t>20.10.202638</t>
-  </si>
-  <si>
-    <t>20.10.202639</t>
-  </si>
-  <si>
-    <t>20.10.202640</t>
-  </si>
-  <si>
-    <t>20.10.202641</t>
-  </si>
-  <si>
-    <t>20.10.202642</t>
-  </si>
-  <si>
-    <t>20.10.202643</t>
-  </si>
-  <si>
-    <t>20.10.202644</t>
-  </si>
-  <si>
-    <t>20.10.202645</t>
-  </si>
-  <si>
-    <t>20.10.202646</t>
-  </si>
-  <si>
-    <t>20.10.202647</t>
-  </si>
-  <si>
-    <t>20.10.202648</t>
-  </si>
-  <si>
-    <t>20.10.202649</t>
-  </si>
-  <si>
-    <t>20.10.202650</t>
-  </si>
-  <si>
-    <t>20.10.202651</t>
-  </si>
-  <si>
-    <t>20.10.202652</t>
-  </si>
-  <si>
-    <t>20.10.202653</t>
-  </si>
-  <si>
-    <t>20.10.202654</t>
-  </si>
-  <si>
-    <t>20.10.202655</t>
-  </si>
-  <si>
-    <t>20.10.202656</t>
-  </si>
-  <si>
-    <t>20.10.202657</t>
-  </si>
-  <si>
-    <t>20.10.202658</t>
-  </si>
-  <si>
-    <t>20.10.202659</t>
-  </si>
-  <si>
-    <t>20.10.202660</t>
-  </si>
-  <si>
-    <t>20.10.202661</t>
-  </si>
-  <si>
-    <t>20.10.202662</t>
-  </si>
-  <si>
-    <t>20.10.202663</t>
-  </si>
-  <si>
-    <t>20.10.202664</t>
-  </si>
-  <si>
-    <t>20.10.202665</t>
-  </si>
-  <si>
-    <t>20.10.202666</t>
-  </si>
-  <si>
-    <t>20.10.202667</t>
-  </si>
-  <si>
-    <t>20.10.202668</t>
-  </si>
-  <si>
-    <t>20.10.202669</t>
-  </si>
-  <si>
-    <t>20.10.202670</t>
-  </si>
-  <si>
-    <t>20.10.202671</t>
-  </si>
-  <si>
-    <t>20.10.202672</t>
-  </si>
-  <si>
-    <t>20.10.202673</t>
-  </si>
-  <si>
-    <t>20.10.202674</t>
-  </si>
-  <si>
-    <t>20.10.202675</t>
-  </si>
-  <si>
-    <t>20.10.202676</t>
-  </si>
-  <si>
-    <t>20.10.202677</t>
-  </si>
-  <si>
-    <t>20.10.202678</t>
-  </si>
-  <si>
-    <t>20.10.202679</t>
-  </si>
-  <si>
-    <t>20.10.202680</t>
-  </si>
-  <si>
-    <t>20.10.202681</t>
-  </si>
-  <si>
-    <t>20.10.202682</t>
-  </si>
-  <si>
-    <t>20.10.202683</t>
-  </si>
-  <si>
-    <t>20.10.202684</t>
-  </si>
-  <si>
-    <t>20.10.202685</t>
-  </si>
-  <si>
-    <t>20.10.202686</t>
-  </si>
-  <si>
-    <t>20.10.202687</t>
-  </si>
-  <si>
-    <t>20.10.202688</t>
-  </si>
-  <si>
-    <t>20.10.202689</t>
-  </si>
-  <si>
-    <t>20.10.202690</t>
-  </si>
-  <si>
-    <t>20.10.202691</t>
-  </si>
-  <si>
-    <t>20.10.202692</t>
-  </si>
-  <si>
-    <t>20.10.202693</t>
-  </si>
-  <si>
-    <t>20.10.202694</t>
-  </si>
-  <si>
-    <t>20.10.202695</t>
-  </si>
-  <si>
-    <t>20.10.202696</t>
-  </si>
-  <si>
-    <t>21.10.20261</t>
-  </si>
-  <si>
-    <t>21.10.20262</t>
-  </si>
-  <si>
-    <t>21.10.20263</t>
-  </si>
-  <si>
-    <t>21.10.20264</t>
-  </si>
-  <si>
-    <t>21.10.20265</t>
-  </si>
-  <si>
-    <t>21.10.20266</t>
-  </si>
-  <si>
-    <t>21.10.20267</t>
-  </si>
-  <si>
-    <t>21.10.20268</t>
-  </si>
-  <si>
-    <t>21.10.20269</t>
-  </si>
-  <si>
-    <t>21.10.202610</t>
-  </si>
-  <si>
-    <t>21.10.202611</t>
-  </si>
-  <si>
-    <t>21.10.202612</t>
-  </si>
-  <si>
-    <t>21.10.202613</t>
-  </si>
-  <si>
-    <t>21.10.202614</t>
-  </si>
-  <si>
-    <t>21.10.202615</t>
-  </si>
-  <si>
-    <t>21.10.202616</t>
-  </si>
-  <si>
-    <t>21.10.202617</t>
-  </si>
-  <si>
-    <t>21.10.202618</t>
-  </si>
-  <si>
-    <t>21.10.202619</t>
-  </si>
-  <si>
-    <t>21.10.202620</t>
-  </si>
-  <si>
-    <t>21.10.202621</t>
-  </si>
-  <si>
-    <t>21.10.202622</t>
-  </si>
-  <si>
-    <t>21.10.202623</t>
-  </si>
-  <si>
-    <t>21.10.202624</t>
-  </si>
-  <si>
-    <t>21.10.202625</t>
-  </si>
-  <si>
-    <t>21.10.202626</t>
-  </si>
-  <si>
-    <t>21.10.202627</t>
-  </si>
-  <si>
-    <t>21.10.202628</t>
-  </si>
-  <si>
-    <t>21.10.202629</t>
-  </si>
-  <si>
-    <t>21.10.202630</t>
-  </si>
-  <si>
-    <t>21.10.202631</t>
-  </si>
-  <si>
-    <t>21.10.202632</t>
-  </si>
-  <si>
-    <t>21.10.202633</t>
-  </si>
-  <si>
-    <t>21.10.202634</t>
-  </si>
-  <si>
-    <t>21.10.202635</t>
-  </si>
-  <si>
-    <t>21.10.202636</t>
-  </si>
-  <si>
-    <t>21.10.202637</t>
-  </si>
-  <si>
-    <t>21.10.202638</t>
-  </si>
-  <si>
-    <t>21.10.202639</t>
-  </si>
-  <si>
-    <t>21.10.202640</t>
-  </si>
-  <si>
-    <t>21.10.202641</t>
-  </si>
-  <si>
-    <t>21.10.202642</t>
-  </si>
-  <si>
-    <t>21.10.202643</t>
-  </si>
-  <si>
-    <t>21.10.202644</t>
-  </si>
-  <si>
-    <t>21.10.202645</t>
-  </si>
-  <si>
-    <t>21.10.202646</t>
-  </si>
-  <si>
-    <t>21.10.202647</t>
-  </si>
-  <si>
-    <t>21.10.202648</t>
-  </si>
-  <si>
-    <t>21.10.202649</t>
-  </si>
-  <si>
-    <t>21.10.202650</t>
-  </si>
-  <si>
-    <t>21.10.202651</t>
-  </si>
-  <si>
-    <t>21.10.202652</t>
-  </si>
-  <si>
-    <t>21.10.202653</t>
-  </si>
-  <si>
-    <t>21.10.202654</t>
-  </si>
-  <si>
-    <t>21.10.202655</t>
-  </si>
-  <si>
-    <t>21.10.202656</t>
-  </si>
-  <si>
-    <t>21.10.202657</t>
-  </si>
-  <si>
-    <t>21.10.202658</t>
-  </si>
-  <si>
-    <t>21.10.202659</t>
-  </si>
-  <si>
-    <t>21.10.202660</t>
-  </si>
-  <si>
-    <t>21.10.202661</t>
-  </si>
-  <si>
-    <t>21.10.202662</t>
-  </si>
-  <si>
-    <t>21.10.202663</t>
-  </si>
-  <si>
-    <t>21.10.202664</t>
-  </si>
-  <si>
-    <t>21.10.202665</t>
-  </si>
-  <si>
-    <t>21.10.202666</t>
-  </si>
-  <si>
-    <t>21.10.202667</t>
-  </si>
-  <si>
-    <t>21.10.202668</t>
-  </si>
-  <si>
-    <t>21.10.202669</t>
-  </si>
-  <si>
-    <t>21.10.202670</t>
-  </si>
-  <si>
-    <t>21.10.202671</t>
-  </si>
-  <si>
-    <t>21.10.202672</t>
-  </si>
-  <si>
-    <t>21.10.202673</t>
-  </si>
-  <si>
-    <t>21.10.202674</t>
-  </si>
-  <si>
-    <t>21.10.202675</t>
-  </si>
-  <si>
-    <t>21.10.202676</t>
-  </si>
-  <si>
-    <t>21.10.202677</t>
-  </si>
-  <si>
-    <t>21.10.202678</t>
-  </si>
-  <si>
-    <t>21.10.202679</t>
-  </si>
-  <si>
-    <t>21.10.202680</t>
-  </si>
-  <si>
-    <t>21.10.202681</t>
-  </si>
-  <si>
-    <t>21.10.202682</t>
-  </si>
-  <si>
-    <t>21.10.202683</t>
-  </si>
-  <si>
-    <t>21.10.202684</t>
-  </si>
-  <si>
-    <t>21.10.202685</t>
-  </si>
-  <si>
-    <t>21.10.202686</t>
-  </si>
-  <si>
-    <t>21.10.202687</t>
-  </si>
-  <si>
-    <t>21.10.202688</t>
-  </si>
-  <si>
-    <t>21.10.202689</t>
-  </si>
-  <si>
-    <t>21.10.202690</t>
-  </si>
-  <si>
-    <t>21.10.202691</t>
-  </si>
-  <si>
-    <t>21.10.202692</t>
+    <t>24.10.20261</t>
+  </si>
+  <si>
+    <t>24.10.20262</t>
+  </si>
+  <si>
+    <t>24.10.20263</t>
+  </si>
+  <si>
+    <t>24.10.20264</t>
+  </si>
+  <si>
+    <t>24.10.20265</t>
+  </si>
+  <si>
+    <t>24.10.20266</t>
+  </si>
+  <si>
+    <t>24.10.20267</t>
+  </si>
+  <si>
+    <t>24.10.20268</t>
+  </si>
+  <si>
+    <t>24.10.20269</t>
+  </si>
+  <si>
+    <t>24.10.202610</t>
+  </si>
+  <si>
+    <t>24.10.202611</t>
+  </si>
+  <si>
+    <t>24.10.202612</t>
+  </si>
+  <si>
+    <t>24.10.202613</t>
+  </si>
+  <si>
+    <t>24.10.202614</t>
+  </si>
+  <si>
+    <t>24.10.202615</t>
+  </si>
+  <si>
+    <t>24.10.202616</t>
+  </si>
+  <si>
+    <t>24.10.202617</t>
+  </si>
+  <si>
+    <t>24.10.202618</t>
+  </si>
+  <si>
+    <t>24.10.202619</t>
+  </si>
+  <si>
+    <t>24.10.202620</t>
+  </si>
+  <si>
+    <t>24.10.202621</t>
+  </si>
+  <si>
+    <t>24.10.202622</t>
+  </si>
+  <si>
+    <t>24.10.202623</t>
+  </si>
+  <si>
+    <t>24.10.202624</t>
+  </si>
+  <si>
+    <t>24.10.202625</t>
+  </si>
+  <si>
+    <t>24.10.202626</t>
+  </si>
+  <si>
+    <t>24.10.202627</t>
+  </si>
+  <si>
+    <t>24.10.202628</t>
+  </si>
+  <si>
+    <t>24.10.202629</t>
+  </si>
+  <si>
+    <t>24.10.202630</t>
+  </si>
+  <si>
+    <t>24.10.202631</t>
+  </si>
+  <si>
+    <t>24.10.202632</t>
+  </si>
+  <si>
+    <t>24.10.202633</t>
+  </si>
+  <si>
+    <t>24.10.202634</t>
+  </si>
+  <si>
+    <t>24.10.202635</t>
+  </si>
+  <si>
+    <t>24.10.202636</t>
+  </si>
+  <si>
+    <t>24.10.202637</t>
+  </si>
+  <si>
+    <t>24.10.202638</t>
+  </si>
+  <si>
+    <t>24.10.202639</t>
+  </si>
+  <si>
+    <t>24.10.202640</t>
+  </si>
+  <si>
+    <t>24.10.202641</t>
+  </si>
+  <si>
+    <t>24.10.202642</t>
+  </si>
+  <si>
+    <t>24.10.202643</t>
+  </si>
+  <si>
+    <t>24.10.202644</t>
+  </si>
+  <si>
+    <t>24.10.202645</t>
+  </si>
+  <si>
+    <t>24.10.202646</t>
+  </si>
+  <si>
+    <t>24.10.202647</t>
+  </si>
+  <si>
+    <t>24.10.202648</t>
+  </si>
+  <si>
+    <t>24.10.202649</t>
+  </si>
+  <si>
+    <t>24.10.202650</t>
+  </si>
+  <si>
+    <t>24.10.202651</t>
+  </si>
+  <si>
+    <t>24.10.202652</t>
+  </si>
+  <si>
+    <t>24.10.202653</t>
+  </si>
+  <si>
+    <t>24.10.202654</t>
+  </si>
+  <si>
+    <t>24.10.202655</t>
+  </si>
+  <si>
+    <t>24.10.202656</t>
+  </si>
+  <si>
+    <t>24.10.202657</t>
+  </si>
+  <si>
+    <t>24.10.202658</t>
+  </si>
+  <si>
+    <t>24.10.202659</t>
+  </si>
+  <si>
+    <t>24.10.202660</t>
+  </si>
+  <si>
+    <t>24.10.202661</t>
+  </si>
+  <si>
+    <t>24.10.202662</t>
+  </si>
+  <si>
+    <t>24.10.202663</t>
+  </si>
+  <si>
+    <t>24.10.202664</t>
+  </si>
+  <si>
+    <t>24.10.202665</t>
+  </si>
+  <si>
+    <t>24.10.202666</t>
+  </si>
+  <si>
+    <t>24.10.202667</t>
+  </si>
+  <si>
+    <t>24.10.202668</t>
+  </si>
+  <si>
+    <t>24.10.202669</t>
+  </si>
+  <si>
+    <t>24.10.202670</t>
+  </si>
+  <si>
+    <t>24.10.202671</t>
+  </si>
+  <si>
+    <t>24.10.202672</t>
+  </si>
+  <si>
+    <t>24.10.202673</t>
+  </si>
+  <si>
+    <t>24.10.202674</t>
+  </si>
+  <si>
+    <t>24.10.202675</t>
+  </si>
+  <si>
+    <t>24.10.202676</t>
+  </si>
+  <si>
+    <t>24.10.202677</t>
+  </si>
+  <si>
+    <t>24.10.202678</t>
+  </si>
+  <si>
+    <t>24.10.202679</t>
+  </si>
+  <si>
+    <t>24.10.202680</t>
+  </si>
+  <si>
+    <t>24.10.202681</t>
+  </si>
+  <si>
+    <t>24.10.202682</t>
+  </si>
+  <si>
+    <t>24.10.202683</t>
+  </si>
+  <si>
+    <t>24.10.202684</t>
+  </si>
+  <si>
+    <t>24.10.202685</t>
+  </si>
+  <si>
+    <t>24.10.202686</t>
+  </si>
+  <si>
+    <t>24.10.202687</t>
+  </si>
+  <si>
+    <t>24.10.202688</t>
+  </si>
+  <si>
+    <t>24.10.202689</t>
+  </si>
+  <si>
+    <t>24.10.202690</t>
+  </si>
+  <si>
+    <t>24.10.202691</t>
+  </si>
+  <si>
+    <t>24.10.202692</t>
+  </si>
+  <si>
+    <t>24.10.202693</t>
+  </si>
+  <si>
+    <t>24.10.202694</t>
+  </si>
+  <si>
+    <t>24.10.202695</t>
+  </si>
+  <si>
+    <t>24.10.202696</t>
+  </si>
+  <si>
+    <t>25.10.20261</t>
+  </si>
+  <si>
+    <t>25.10.20262</t>
+  </si>
+  <si>
+    <t>25.10.20263</t>
+  </si>
+  <si>
+    <t>25.10.20264</t>
+  </si>
+  <si>
+    <t>25.10.20265</t>
+  </si>
+  <si>
+    <t>25.10.20266</t>
+  </si>
+  <si>
+    <t>25.10.20267</t>
+  </si>
+  <si>
+    <t>25.10.20268</t>
+  </si>
+  <si>
+    <t>25.10.20269</t>
+  </si>
+  <si>
+    <t>25.10.202610</t>
+  </si>
+  <si>
+    <t>25.10.202611</t>
+  </si>
+  <si>
+    <t>25.10.202612</t>
+  </si>
+  <si>
+    <t>25.10.202613</t>
+  </si>
+  <si>
+    <t>25.10.202614</t>
+  </si>
+  <si>
+    <t>25.10.202615</t>
+  </si>
+  <si>
+    <t>25.10.202616</t>
+  </si>
+  <si>
+    <t>25.10.202617</t>
+  </si>
+  <si>
+    <t>25.10.202618</t>
+  </si>
+  <si>
+    <t>25.10.202619</t>
+  </si>
+  <si>
+    <t>25.10.202620</t>
+  </si>
+  <si>
+    <t>25.10.202621</t>
+  </si>
+  <si>
+    <t>25.10.202622</t>
+  </si>
+  <si>
+    <t>25.10.202623</t>
+  </si>
+  <si>
+    <t>25.10.202624</t>
+  </si>
+  <si>
+    <t>25.10.202625</t>
+  </si>
+  <si>
+    <t>25.10.202626</t>
+  </si>
+  <si>
+    <t>25.10.202627</t>
+  </si>
+  <si>
+    <t>25.10.202628</t>
+  </si>
+  <si>
+    <t>25.10.202629</t>
+  </si>
+  <si>
+    <t>25.10.202630</t>
+  </si>
+  <si>
+    <t>25.10.202631</t>
+  </si>
+  <si>
+    <t>25.10.202632</t>
+  </si>
+  <si>
+    <t>25.10.202633</t>
+  </si>
+  <si>
+    <t>25.10.202634</t>
+  </si>
+  <si>
+    <t>25.10.202635</t>
+  </si>
+  <si>
+    <t>25.10.202636</t>
+  </si>
+  <si>
+    <t>25.10.202637</t>
+  </si>
+  <si>
+    <t>25.10.202638</t>
+  </si>
+  <si>
+    <t>25.10.202639</t>
+  </si>
+  <si>
+    <t>25.10.202640</t>
+  </si>
+  <si>
+    <t>25.10.202641</t>
+  </si>
+  <si>
+    <t>25.10.202642</t>
+  </si>
+  <si>
+    <t>25.10.202643</t>
+  </si>
+  <si>
+    <t>25.10.202644</t>
+  </si>
+  <si>
+    <t>25.10.202645</t>
+  </si>
+  <si>
+    <t>25.10.202646</t>
+  </si>
+  <si>
+    <t>25.10.202647</t>
+  </si>
+  <si>
+    <t>25.10.202648</t>
+  </si>
+  <si>
+    <t>25.10.202649</t>
+  </si>
+  <si>
+    <t>25.10.202650</t>
+  </si>
+  <si>
+    <t>25.10.202651</t>
+  </si>
+  <si>
+    <t>25.10.202652</t>
+  </si>
+  <si>
+    <t>25.10.202653</t>
+  </si>
+  <si>
+    <t>25.10.202654</t>
+  </si>
+  <si>
+    <t>25.10.202655</t>
+  </si>
+  <si>
+    <t>25.10.202656</t>
+  </si>
+  <si>
+    <t>25.10.202657</t>
+  </si>
+  <si>
+    <t>25.10.202658</t>
+  </si>
+  <si>
+    <t>25.10.202659</t>
+  </si>
+  <si>
+    <t>25.10.202660</t>
+  </si>
+  <si>
+    <t>25.10.202661</t>
+  </si>
+  <si>
+    <t>25.10.202662</t>
+  </si>
+  <si>
+    <t>25.10.202663</t>
+  </si>
+  <si>
+    <t>25.10.202664</t>
+  </si>
+  <si>
+    <t>25.10.202665</t>
+  </si>
+  <si>
+    <t>25.10.202666</t>
+  </si>
+  <si>
+    <t>25.10.202667</t>
+  </si>
+  <si>
+    <t>25.10.202668</t>
+  </si>
+  <si>
+    <t>25.10.202669</t>
+  </si>
+  <si>
+    <t>25.10.202670</t>
+  </si>
+  <si>
+    <t>25.10.202671</t>
+  </si>
+  <si>
+    <t>25.10.202672</t>
+  </si>
+  <si>
+    <t>25.10.202673</t>
+  </si>
+  <si>
+    <t>25.10.202674</t>
+  </si>
+  <si>
+    <t>25.10.202675</t>
+  </si>
+  <si>
+    <t>25.10.202676</t>
+  </si>
+  <si>
+    <t>25.10.202677</t>
+  </si>
+  <si>
+    <t>25.10.202678</t>
+  </si>
+  <si>
+    <t>25.10.202679</t>
+  </si>
+  <si>
+    <t>25.10.202680</t>
+  </si>
+  <si>
+    <t>25.10.202681</t>
+  </si>
+  <si>
+    <t>25.10.202682</t>
+  </si>
+  <si>
+    <t>25.10.202683</t>
+  </si>
+  <si>
+    <t>25.10.202684</t>
+  </si>
+  <si>
+    <t>25.10.202685</t>
+  </si>
+  <si>
+    <t>25.10.202686</t>
+  </si>
+  <si>
+    <t>25.10.202687</t>
+  </si>
+  <si>
+    <t>25.10.202688</t>
+  </si>
+  <si>
+    <t>25.10.202689</t>
+  </si>
+  <si>
+    <t>25.10.202690</t>
+  </si>
+  <si>
+    <t>25.10.202691</t>
+  </si>
+  <si>
+    <t>25.10.202692</t>
+  </si>
+  <si>
+    <t>25.10.202693</t>
+  </si>
+  <si>
+    <t>25.10.202694</t>
+  </si>
+  <si>
+    <t>25.10.202695</t>
+  </si>
+  <si>
+    <t>25.10.202696</t>
   </si>
 </sst>
 </file>
@@ -954,7 +966,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E189"/>
+  <dimension ref="A1:E193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -976,13 +988,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46315</v>
+        <v>46319</v>
       </c>
       <c r="B2">
-        <v>1476.59</v>
+        <v>1320.016</v>
       </c>
       <c r="C2">
-        <v>1931</v>
+        <v>1419</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -993,13 +1005,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46315.01041666666</v>
+        <v>46319.01041666666</v>
       </c>
       <c r="B3">
-        <v>1447.031</v>
+        <v>1297.24</v>
       </c>
       <c r="C3">
-        <v>1889</v>
+        <v>1455</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1010,13 +1022,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46315.02083333334</v>
+        <v>46319.02083333334</v>
       </c>
       <c r="B4">
-        <v>1393.5</v>
+        <v>1284.371</v>
       </c>
       <c r="C4">
-        <v>1800</v>
+        <v>1537</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1027,13 +1039,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46315.03125</v>
+        <v>46319.03125</v>
       </c>
       <c r="B5">
-        <v>1368.284</v>
+        <v>1272.122</v>
       </c>
       <c r="C5">
-        <v>1694</v>
+        <v>1561</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1044,13 +1056,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46315.04166666666</v>
+        <v>46319.04166666666</v>
       </c>
       <c r="B6">
-        <v>1317.92</v>
+        <v>1227.251</v>
       </c>
       <c r="C6">
-        <v>1559</v>
+        <v>1550</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1061,13 +1073,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46315.05208333334</v>
+        <v>46319.05208333334</v>
       </c>
       <c r="B7">
-        <v>1295.396</v>
+        <v>1239.521</v>
       </c>
       <c r="C7">
-        <v>1427</v>
+        <v>1548</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1078,13 +1090,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46315.0625</v>
+        <v>46319.0625</v>
       </c>
       <c r="B8">
-        <v>1275.516</v>
+        <v>1217.679</v>
       </c>
       <c r="C8">
-        <v>1377</v>
+        <v>1531</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1095,13 +1107,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46315.07291666666</v>
+        <v>46319.07291666666</v>
       </c>
       <c r="B9">
-        <v>1246.126</v>
+        <v>1206.936</v>
       </c>
       <c r="C9">
-        <v>1350</v>
+        <v>1499</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1112,13 +1124,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46315.08333333334</v>
+        <v>46319.08333333334</v>
       </c>
       <c r="B10">
-        <v>1108.346</v>
+        <v>1152.741</v>
       </c>
       <c r="C10">
-        <v>1338</v>
+        <v>1477</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1129,13 +1141,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46315.09375</v>
+        <v>46319.09375</v>
       </c>
       <c r="B11">
-        <v>1072.744</v>
+        <v>1144.999</v>
       </c>
       <c r="C11">
-        <v>1307</v>
+        <v>1444</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1146,13 +1158,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46315.10416666666</v>
+        <v>46319.10416666666</v>
       </c>
       <c r="B12">
-        <v>1037.705</v>
+        <v>1105.818</v>
       </c>
       <c r="C12">
-        <v>1232</v>
+        <v>1364</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1163,13 +1175,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46315.11458333334</v>
+        <v>46319.11458333334</v>
       </c>
       <c r="B13">
-        <v>1005.817</v>
+        <v>1086.723</v>
       </c>
       <c r="C13">
-        <v>1199</v>
+        <v>1320</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1180,13 +1192,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46315.125</v>
+        <v>46319.125</v>
       </c>
       <c r="B14">
-        <v>973.033</v>
+        <v>1034.849</v>
       </c>
       <c r="C14">
-        <v>1196</v>
+        <v>1258</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1197,13 +1209,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46315.13541666666</v>
+        <v>46319.13541666666</v>
       </c>
       <c r="B15">
-        <v>947.698</v>
+        <v>1024.423</v>
       </c>
       <c r="C15">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1214,13 +1226,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46315.14583333334</v>
+        <v>46319.14583333334</v>
       </c>
       <c r="B16">
-        <v>921.6</v>
+        <v>987.283</v>
       </c>
       <c r="C16">
-        <v>1120</v>
+        <v>1159</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1231,13 +1243,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46315.15625</v>
+        <v>46319.15625</v>
       </c>
       <c r="B17">
-        <v>903.802</v>
+        <v>961.051</v>
       </c>
       <c r="C17">
-        <v>1045</v>
+        <v>1177</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1248,13 +1260,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46315.16666666666</v>
+        <v>46319.16666666666</v>
       </c>
       <c r="B18">
-        <v>850.353</v>
+        <v>885.7089999999999</v>
       </c>
       <c r="C18">
-        <v>958</v>
+        <v>1167</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1265,13 +1277,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46315.17708333334</v>
+        <v>46319.17708333334</v>
       </c>
       <c r="B19">
-        <v>833.466</v>
+        <v>893.317</v>
       </c>
       <c r="C19">
-        <v>963</v>
+        <v>1144</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1282,13 +1294,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46315.1875</v>
+        <v>46319.1875</v>
       </c>
       <c r="B20">
-        <v>812.87</v>
+        <v>851.828</v>
       </c>
       <c r="C20">
-        <v>990</v>
+        <v>1135</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1299,13 +1311,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46315.19791666666</v>
+        <v>46319.19791666666</v>
       </c>
       <c r="B21">
-        <v>793.735</v>
+        <v>834.559</v>
       </c>
       <c r="C21">
-        <v>963</v>
+        <v>1089</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1316,13 +1328,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46315.20833333334</v>
+        <v>46319.20833333334</v>
       </c>
       <c r="B22">
-        <v>741.808</v>
+        <v>809.72</v>
       </c>
       <c r="C22">
-        <v>921</v>
+        <v>1042</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1333,13 +1345,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46315.21875</v>
+        <v>46319.21875</v>
       </c>
       <c r="B23">
-        <v>711.943</v>
+        <v>808.532</v>
       </c>
       <c r="C23">
-        <v>900</v>
+        <v>1036</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1350,13 +1362,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46315.22916666666</v>
+        <v>46319.22916666666</v>
       </c>
       <c r="B24">
-        <v>683.397</v>
+        <v>787.979</v>
       </c>
       <c r="C24">
-        <v>879</v>
+        <v>967</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1367,13 +1379,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46315.23958333334</v>
+        <v>46319.23958333334</v>
       </c>
       <c r="B25">
-        <v>655.04</v>
+        <v>760.946</v>
       </c>
       <c r="C25">
-        <v>854</v>
+        <v>909</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1384,13 +1396,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46315.25</v>
+        <v>46319.25</v>
       </c>
       <c r="B26">
-        <v>626.845</v>
+        <v>691.739</v>
       </c>
       <c r="C26">
-        <v>825</v>
+        <v>911</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1401,13 +1413,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46315.26041666666</v>
+        <v>46319.26041666666</v>
       </c>
       <c r="B27">
-        <v>609.077</v>
+        <v>669.329</v>
       </c>
       <c r="C27">
-        <v>874</v>
+        <v>907</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1418,13 +1430,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46315.27083333334</v>
+        <v>46319.27083333334</v>
       </c>
       <c r="B28">
-        <v>601.01</v>
+        <v>650.431</v>
       </c>
       <c r="C28">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1435,13 +1447,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46315.28125</v>
+        <v>46319.28125</v>
       </c>
       <c r="B29">
-        <v>548.648</v>
+        <v>620.36</v>
       </c>
       <c r="C29">
-        <v>826</v>
+        <v>806</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1452,13 +1464,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46315.29166666666</v>
+        <v>46319.29166666666</v>
       </c>
       <c r="B30">
-        <v>516.064</v>
+        <v>554.422</v>
       </c>
       <c r="C30">
-        <v>841</v>
+        <v>764</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1469,13 +1481,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46315.30208333334</v>
+        <v>46319.30208333334</v>
       </c>
       <c r="B31">
-        <v>499.512</v>
+        <v>520.846</v>
       </c>
       <c r="C31">
-        <v>856</v>
+        <v>707</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1486,13 +1498,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46315.3125</v>
+        <v>46319.3125</v>
       </c>
       <c r="B32">
-        <v>399.977</v>
+        <v>507.229</v>
       </c>
       <c r="C32">
-        <v>788</v>
+        <v>694</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1503,13 +1515,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46315.32291666666</v>
+        <v>46319.32291666666</v>
       </c>
       <c r="B33">
-        <v>376.008</v>
+        <v>493.373</v>
       </c>
       <c r="C33">
-        <v>723</v>
+        <v>654</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1520,13 +1532,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46315.33333333334</v>
+        <v>46319.33333333334</v>
       </c>
       <c r="B34">
-        <v>388.134</v>
+        <v>401.471</v>
       </c>
       <c r="C34">
-        <v>638</v>
+        <v>611</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1537,13 +1549,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46315.34375</v>
+        <v>46319.34375</v>
       </c>
       <c r="B35">
-        <v>364.64</v>
+        <v>385.049</v>
       </c>
       <c r="C35">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1554,13 +1566,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46315.35416666666</v>
+        <v>46319.35416666666</v>
       </c>
       <c r="B36">
-        <v>332.301</v>
+        <v>373.935</v>
       </c>
       <c r="C36">
-        <v>475</v>
+        <v>521</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1571,13 +1583,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46315.36458333334</v>
+        <v>46319.36458333334</v>
       </c>
       <c r="B37">
-        <v>308.466</v>
+        <v>353.743</v>
       </c>
       <c r="C37">
-        <v>420</v>
+        <v>470</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1588,13 +1600,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46315.375</v>
+        <v>46319.375</v>
       </c>
       <c r="B38">
-        <v>284.964</v>
+        <v>324.253</v>
       </c>
       <c r="C38">
-        <v>365</v>
+        <v>439</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1605,13 +1617,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46315.38541666666</v>
+        <v>46319.38541666666</v>
       </c>
       <c r="B39">
-        <v>276.459</v>
+        <v>316.264</v>
       </c>
       <c r="C39">
-        <v>320</v>
+        <v>424</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1622,13 +1634,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46315.39583333334</v>
+        <v>46319.39583333334</v>
       </c>
       <c r="B40">
-        <v>270.556</v>
+        <v>295.651</v>
       </c>
       <c r="C40">
-        <v>305</v>
+        <v>392</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1639,13 +1651,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46315.40625</v>
+        <v>46319.40625</v>
       </c>
       <c r="B41">
-        <v>247.341</v>
+        <v>284.985</v>
       </c>
       <c r="C41">
-        <v>300</v>
+        <v>366</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1656,13 +1668,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46315.41666666666</v>
+        <v>46319.41666666666</v>
       </c>
       <c r="B42">
-        <v>218.013</v>
+        <v>262.124</v>
       </c>
       <c r="C42">
-        <v>262</v>
+        <v>350</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1673,13 +1685,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46315.42708333334</v>
+        <v>46319.42708333334</v>
       </c>
       <c r="B43">
-        <v>211.872</v>
+        <v>255.71</v>
       </c>
       <c r="C43">
-        <v>227</v>
+        <v>342</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1690,13 +1702,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46315.4375</v>
+        <v>46319.4375</v>
       </c>
       <c r="B44">
-        <v>192.759</v>
+        <v>250.324</v>
       </c>
       <c r="C44">
-        <v>173</v>
+        <v>325</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1707,13 +1719,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46315.44791666666</v>
+        <v>46319.44791666666</v>
       </c>
       <c r="B45">
-        <v>185.724</v>
+        <v>244.956</v>
       </c>
       <c r="C45">
-        <v>113</v>
+        <v>320</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1724,13 +1736,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46315.45833333334</v>
+        <v>46319.45833333334</v>
       </c>
       <c r="B46">
-        <v>202.413</v>
+        <v>226.512</v>
       </c>
       <c r="C46">
-        <v>70</v>
+        <v>301</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1741,13 +1753,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46315.46875</v>
+        <v>46319.46875</v>
       </c>
       <c r="B47">
-        <v>200.558</v>
+        <v>223.63</v>
       </c>
       <c r="C47">
-        <v>53</v>
+        <v>272</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1758,13 +1770,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46315.47916666666</v>
+        <v>46319.47916666666</v>
       </c>
       <c r="B48">
-        <v>187.226</v>
+        <v>219.878</v>
       </c>
       <c r="C48">
-        <v>36</v>
+        <v>231</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1775,13 +1787,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46315.48958333334</v>
+        <v>46319.48958333334</v>
       </c>
       <c r="B49">
-        <v>185.565</v>
+        <v>216.647</v>
       </c>
       <c r="C49">
-        <v>24</v>
+        <v>225</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1792,13 +1804,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46315.5</v>
+        <v>46319.5</v>
       </c>
       <c r="B50">
-        <v>180.573</v>
+        <v>204.756</v>
       </c>
       <c r="C50">
-        <v>12</v>
+        <v>205</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1809,13 +1821,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46315.51041666666</v>
+        <v>46319.51041666666</v>
       </c>
       <c r="B51">
-        <v>180.167</v>
+        <v>201.389</v>
       </c>
       <c r="C51">
-        <v>6</v>
+        <v>177</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1826,13 +1838,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46315.52083333334</v>
+        <v>46319.52083333334</v>
       </c>
       <c r="B52">
-        <v>180.033</v>
+        <v>194.75</v>
       </c>
       <c r="C52">
-        <v>8</v>
+        <v>155</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1843,13 +1855,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46315.53125</v>
+        <v>46319.53125</v>
       </c>
       <c r="B53">
-        <v>179.913</v>
+        <v>191.799</v>
       </c>
       <c r="C53">
-        <v>12</v>
+        <v>156</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1860,13 +1872,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46315.54166666666</v>
+        <v>46319.54166666666</v>
       </c>
       <c r="B54">
-        <v>163.295</v>
+        <v>183.975</v>
       </c>
       <c r="C54">
-        <v>19</v>
+        <v>161</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1877,13 +1889,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46315.55208333334</v>
+        <v>46319.55208333334</v>
       </c>
       <c r="B55">
-        <v>165.084</v>
+        <v>179.099</v>
       </c>
       <c r="C55">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1894,13 +1906,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46315.5625</v>
+        <v>46319.5625</v>
       </c>
       <c r="B56">
-        <v>166.77</v>
+        <v>174.25</v>
       </c>
       <c r="C56">
-        <v>20</v>
+        <v>135</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1911,13 +1923,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46315.57291666666</v>
+        <v>46319.57291666666</v>
       </c>
       <c r="B57">
-        <v>169.065</v>
+        <v>169.431</v>
       </c>
       <c r="C57">
-        <v>12</v>
+        <v>157</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1928,13 +1940,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46315.58333333334</v>
+        <v>46319.58333333334</v>
       </c>
       <c r="B58">
-        <v>166.323</v>
+        <v>156.629</v>
       </c>
       <c r="C58">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1945,13 +1957,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46315.59375</v>
+        <v>46319.59375</v>
       </c>
       <c r="B59">
-        <v>174.214</v>
+        <v>151.312</v>
       </c>
       <c r="C59">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1962,13 +1974,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46315.60416666666</v>
+        <v>46319.60416666666</v>
       </c>
       <c r="B60">
-        <v>184.867</v>
+        <v>145.852</v>
       </c>
       <c r="C60">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1979,13 +1991,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46315.61458333334</v>
+        <v>46319.61458333334</v>
       </c>
       <c r="B61">
-        <v>193.991</v>
+        <v>140.299</v>
       </c>
       <c r="C61">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -1996,13 +2008,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46315.625</v>
+        <v>46319.625</v>
       </c>
       <c r="B62">
-        <v>231.734</v>
+        <v>141.527</v>
       </c>
       <c r="C62">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2013,13 +2025,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46315.63541666666</v>
+        <v>46319.63541666666</v>
       </c>
       <c r="B63">
-        <v>246.606</v>
+        <v>136.439</v>
       </c>
       <c r="C63">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2030,13 +2042,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46315.64583333334</v>
+        <v>46319.64583333334</v>
       </c>
       <c r="B64">
-        <v>263.107</v>
+        <v>130.399</v>
       </c>
       <c r="C64">
-        <v>97</v>
+        <v>12</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2047,13 +2059,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46315.65625</v>
+        <v>46319.65625</v>
       </c>
       <c r="B65">
-        <v>279.324</v>
+        <v>124.805</v>
       </c>
       <c r="C65">
-        <v>131</v>
+        <v>6</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2064,13 +2076,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46315.66666666666</v>
+        <v>46319.66666666666</v>
       </c>
       <c r="B66">
-        <v>299.605</v>
+        <v>126.277</v>
       </c>
       <c r="C66">
-        <v>147</v>
+        <v>2</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2081,13 +2093,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46315.67708333334</v>
+        <v>46319.67708333334</v>
       </c>
       <c r="B67">
-        <v>327.844</v>
+        <v>121.903</v>
       </c>
       <c r="C67">
-        <v>175</v>
+        <v>2</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2098,13 +2110,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46315.6875</v>
+        <v>46319.6875</v>
       </c>
       <c r="B68">
-        <v>354.761</v>
+        <v>118.348</v>
       </c>
       <c r="C68">
-        <v>224</v>
+        <v>3</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2115,13 +2127,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46315.69791666666</v>
+        <v>46319.69791666666</v>
       </c>
       <c r="B69">
-        <v>383.831</v>
+        <v>115.046</v>
       </c>
       <c r="C69">
-        <v>270</v>
+        <v>4</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2132,13 +2144,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46315.70833333334</v>
+        <v>46319.70833333334</v>
       </c>
       <c r="B70">
-        <v>435.831</v>
+        <v>108.333</v>
       </c>
       <c r="C70">
-        <v>333</v>
+        <v>6</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2149,13 +2161,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46315.71875</v>
+        <v>46319.71875</v>
       </c>
       <c r="B71">
-        <v>474.599</v>
+        <v>110.084</v>
       </c>
       <c r="C71">
-        <v>393</v>
+        <v>6</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2166,13 +2178,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46315.72916666666</v>
+        <v>46319.72916666666</v>
       </c>
       <c r="B72">
-        <v>517.693</v>
+        <v>112.386</v>
       </c>
       <c r="C72">
-        <v>439</v>
+        <v>10</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2183,13 +2195,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46315.73958333334</v>
+        <v>46319.73958333334</v>
       </c>
       <c r="B73">
-        <v>562.136</v>
+        <v>115.03</v>
       </c>
       <c r="C73">
-        <v>475</v>
+        <v>14</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2200,13 +2212,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46315.75</v>
+        <v>46319.75</v>
       </c>
       <c r="B74">
-        <v>572.966</v>
+        <v>132.37</v>
       </c>
       <c r="C74">
-        <v>499</v>
+        <v>19</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2217,13 +2229,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46315.76041666666</v>
+        <v>46319.76041666666</v>
       </c>
       <c r="B75">
-        <v>598.147</v>
+        <v>136.868</v>
       </c>
       <c r="C75">
-        <v>506</v>
+        <v>18</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2234,13 +2246,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46315.77083333334</v>
+        <v>46319.77083333334</v>
       </c>
       <c r="B76">
-        <v>618.771</v>
+        <v>141.926</v>
       </c>
       <c r="C76">
-        <v>522</v>
+        <v>18</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2251,13 +2263,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46315.78125</v>
+        <v>46319.78125</v>
       </c>
       <c r="B77">
-        <v>640.8</v>
+        <v>146.202</v>
       </c>
       <c r="C77">
-        <v>529</v>
+        <v>17</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2268,13 +2280,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46315.79166666666</v>
+        <v>46319.79166666666</v>
       </c>
       <c r="B78">
-        <v>663.0410000000001</v>
+        <v>152.032</v>
       </c>
       <c r="C78">
-        <v>550</v>
+        <v>19</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2285,13 +2297,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46315.80208333334</v>
+        <v>46319.80208333334</v>
       </c>
       <c r="B79">
-        <v>679.505</v>
+        <v>156.338</v>
       </c>
       <c r="C79">
-        <v>598</v>
+        <v>22</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2302,13 +2314,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46315.8125</v>
+        <v>46319.8125</v>
       </c>
       <c r="B80">
-        <v>693.466</v>
+        <v>160.56</v>
       </c>
       <c r="C80">
-        <v>617</v>
+        <v>25</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2319,13 +2331,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46315.82291666666</v>
+        <v>46319.82291666666</v>
       </c>
       <c r="B81">
-        <v>708.593</v>
+        <v>164.964</v>
       </c>
       <c r="C81">
-        <v>642</v>
+        <v>24</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2336,13 +2348,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46315.83333333334</v>
+        <v>46319.83333333334</v>
       </c>
       <c r="B82">
-        <v>723.2430000000001</v>
+        <v>169.814</v>
       </c>
       <c r="C82">
-        <v>632</v>
+        <v>23</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2353,13 +2365,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46315.84375</v>
+        <v>46319.84375</v>
       </c>
       <c r="B83">
-        <v>725.21</v>
+        <v>173.613</v>
       </c>
       <c r="C83">
-        <v>629</v>
+        <v>30</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2370,13 +2382,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46315.85416666666</v>
+        <v>46319.85416666666</v>
       </c>
       <c r="B84">
-        <v>730.266</v>
+        <v>181.247</v>
       </c>
       <c r="C84">
-        <v>627</v>
+        <v>31</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2387,13 +2399,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46315.86458333334</v>
+        <v>46319.86458333334</v>
       </c>
       <c r="B85">
-        <v>735.178</v>
+        <v>181.829</v>
       </c>
       <c r="C85">
-        <v>605</v>
+        <v>35</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2404,13 +2416,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46315.875</v>
+        <v>46319.875</v>
       </c>
       <c r="B86">
-        <v>738.188</v>
+        <v>158.228</v>
       </c>
       <c r="C86">
-        <v>610</v>
+        <v>48</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2421,13 +2433,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46315.88541666666</v>
+        <v>46319.88541666666</v>
       </c>
       <c r="B87">
-        <v>738.347</v>
+        <v>160.722</v>
       </c>
       <c r="C87">
-        <v>613</v>
+        <v>58</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2438,13 +2450,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46315.89583333334</v>
+        <v>46319.89583333334</v>
       </c>
       <c r="B88">
-        <v>737.174</v>
+        <v>162.586</v>
       </c>
       <c r="C88">
-        <v>600</v>
+        <v>69</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2455,13 +2467,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46315.90625</v>
+        <v>46319.90625</v>
       </c>
       <c r="B89">
-        <v>736.455</v>
+        <v>164.002</v>
       </c>
       <c r="C89">
-        <v>588</v>
+        <v>74</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2472,13 +2484,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46315.91666666666</v>
+        <v>46319.91666666666</v>
       </c>
       <c r="B90">
-        <v>729.514</v>
+        <v>190.672</v>
       </c>
       <c r="C90">
-        <v>583</v>
+        <v>80</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2489,13 +2501,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46315.92708333334</v>
+        <v>46319.92708333334</v>
       </c>
       <c r="B91">
-        <v>725.297</v>
+        <v>189.992</v>
       </c>
       <c r="C91">
-        <v>579</v>
+        <v>88</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2506,13 +2518,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46315.9375</v>
+        <v>46319.9375</v>
       </c>
       <c r="B92">
-        <v>721.716</v>
+        <v>189.726</v>
       </c>
       <c r="C92">
-        <v>569</v>
+        <v>91</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2523,13 +2535,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46315.94791666666</v>
+        <v>46319.94791666666</v>
       </c>
       <c r="B93">
-        <v>719.05</v>
+        <v>189.014</v>
       </c>
       <c r="C93">
-        <v>552</v>
+        <v>95</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2540,13 +2552,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46315.95833333334</v>
+        <v>46319.95833333334</v>
       </c>
       <c r="B94">
-        <v>662.495</v>
+        <v>183.253</v>
       </c>
       <c r="C94">
-        <v>542</v>
+        <v>87</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2557,13 +2569,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46315.96875</v>
+        <v>46319.96875</v>
       </c>
       <c r="B95">
-        <v>655.026</v>
+        <v>179.461</v>
       </c>
       <c r="C95">
-        <v>526</v>
+        <v>90</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2574,13 +2586,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46315.97916666666</v>
+        <v>46319.97916666666</v>
       </c>
       <c r="B96">
-        <v>637.314</v>
+        <v>176.219</v>
       </c>
       <c r="C96">
-        <v>515</v>
+        <v>93</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2591,13 +2603,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46315.98958333334</v>
+        <v>46319.98958333334</v>
       </c>
       <c r="B97">
-        <v>629.715</v>
+        <v>174.005</v>
       </c>
       <c r="C97">
-        <v>534</v>
+        <v>83</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2608,13 +2620,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46316</v>
+        <v>46320</v>
       </c>
       <c r="B98">
-        <v>575.335</v>
+        <v>169.093</v>
       </c>
       <c r="C98">
-        <v>551</v>
+        <v>73</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2625,13 +2637,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46316.01041666666</v>
+        <v>46320.01041666666</v>
       </c>
       <c r="B99">
-        <v>566.782</v>
+        <v>149.652</v>
       </c>
       <c r="C99">
-        <v>554</v>
+        <v>66</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2642,13 +2654,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46316.02083333334</v>
+        <v>46320.02083333334</v>
       </c>
       <c r="B100">
-        <v>558.311</v>
+        <v>145.865</v>
       </c>
       <c r="C100">
-        <v>542</v>
+        <v>70</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2659,13 +2671,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46316.03125</v>
+        <v>46320.03125</v>
       </c>
       <c r="B101">
-        <v>549.244</v>
+        <v>141.217</v>
       </c>
       <c r="C101">
-        <v>533</v>
+        <v>71</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2676,13 +2688,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46316.04166666666</v>
+        <v>46320.04166666666</v>
       </c>
       <c r="B102">
-        <v>553.963</v>
+        <v>136.787</v>
       </c>
       <c r="C102">
-        <v>546</v>
+        <v>72</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2693,13 +2705,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46316.05208333334</v>
+        <v>46320.05208333334</v>
       </c>
       <c r="B103">
-        <v>555.462</v>
+        <v>132.449</v>
       </c>
       <c r="C103">
-        <v>574</v>
+        <v>73</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2710,13 +2722,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46316.0625</v>
+        <v>46320.0625</v>
       </c>
       <c r="B104">
-        <v>549.395</v>
+        <v>127.688</v>
       </c>
       <c r="C104">
-        <v>594</v>
+        <v>75</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2727,13 +2739,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46316.07291666666</v>
+        <v>46320.07291666666</v>
       </c>
       <c r="B105">
-        <v>539.942</v>
+        <v>123.345</v>
       </c>
       <c r="C105">
-        <v>574</v>
+        <v>65</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2744,13 +2756,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46316.08333333334</v>
+        <v>46320.08333333334</v>
       </c>
       <c r="B106">
-        <v>515.899</v>
+        <v>119.398</v>
       </c>
       <c r="C106">
-        <v>537</v>
+        <v>71</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2761,13 +2773,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46316.09375</v>
+        <v>46320.09375</v>
       </c>
       <c r="B107">
-        <v>516.421</v>
+        <v>115.603</v>
       </c>
       <c r="C107">
-        <v>523</v>
+        <v>71</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2778,13 +2790,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46316.10416666666</v>
+        <v>46320.10416666666</v>
       </c>
       <c r="B108">
-        <v>521.8099999999999</v>
+        <v>111.982</v>
       </c>
       <c r="C108">
-        <v>505</v>
+        <v>71</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2795,13 +2807,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46316.11458333334</v>
+        <v>46320.11458333334</v>
       </c>
       <c r="B109">
-        <v>521.904</v>
+        <v>108.435</v>
       </c>
       <c r="C109">
-        <v>490</v>
+        <v>71</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2812,13 +2824,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46316.125</v>
+        <v>46320.08333333334</v>
       </c>
       <c r="B110">
-        <v>541.598</v>
+        <v>105.717</v>
       </c>
       <c r="C110">
-        <v>493</v>
+        <v>71</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2829,13 +2841,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46316.13541666666</v>
+        <v>46320.09375</v>
       </c>
       <c r="B111">
-        <v>545.636</v>
+        <v>103.527</v>
       </c>
       <c r="C111">
-        <v>485</v>
+        <v>71</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2846,13 +2858,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46316.14583333334</v>
+        <v>46320.10416666666</v>
       </c>
       <c r="B112">
-        <v>550.8869999999999</v>
+        <v>101.014</v>
       </c>
       <c r="C112">
-        <v>476</v>
+        <v>71</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2863,13 +2875,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46316.15625</v>
+        <v>46320.11458333334</v>
       </c>
       <c r="B113">
-        <v>559.639</v>
+        <v>98.586</v>
       </c>
       <c r="C113">
-        <v>482</v>
+        <v>71</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2880,13 +2892,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46316.16666666666</v>
+        <v>46320.125</v>
       </c>
       <c r="B114">
-        <v>578.811</v>
+        <v>96.89400000000001</v>
       </c>
       <c r="C114">
-        <v>509</v>
+        <v>71</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2897,13 +2909,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46316.17708333334</v>
+        <v>46320.13541666666</v>
       </c>
       <c r="B115">
-        <v>585.715</v>
+        <v>94.911</v>
       </c>
       <c r="C115">
-        <v>583</v>
+        <v>27</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2914,13 +2926,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46316.1875</v>
+        <v>46320.14583333334</v>
       </c>
       <c r="B116">
-        <v>593.921</v>
+        <v>93.05500000000001</v>
       </c>
       <c r="C116">
-        <v>646</v>
+        <v>27</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2931,13 +2943,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46316.19791666666</v>
+        <v>46320.15625</v>
       </c>
       <c r="B117">
-        <v>603.081</v>
+        <v>91.589</v>
       </c>
       <c r="C117">
-        <v>682</v>
+        <v>25</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2948,13 +2960,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46316.20833333334</v>
+        <v>46320.16666666666</v>
       </c>
       <c r="B118">
-        <v>605.341</v>
+        <v>92.322</v>
       </c>
       <c r="C118">
-        <v>698</v>
+        <v>27</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2965,13 +2977,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46316.21875</v>
+        <v>46320.17708333334</v>
       </c>
       <c r="B119">
-        <v>611.621</v>
+        <v>91.13200000000001</v>
       </c>
       <c r="C119">
-        <v>662</v>
+        <v>23</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2982,13 +2994,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46316.22916666666</v>
+        <v>46320.1875</v>
       </c>
       <c r="B120">
-        <v>614.4349999999999</v>
+        <v>90.001</v>
       </c>
       <c r="C120">
-        <v>707</v>
+        <v>14</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -2999,13 +3011,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46316.23958333334</v>
+        <v>46320.19791666666</v>
       </c>
       <c r="B121">
-        <v>623.889</v>
+        <v>103.114</v>
       </c>
       <c r="C121">
-        <v>762</v>
+        <v>12</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3016,13 +3028,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46316.25</v>
+        <v>46320.20833333334</v>
       </c>
       <c r="B122">
-        <v>611.425</v>
+        <v>103.703</v>
       </c>
       <c r="C122">
-        <v>804</v>
+        <v>8</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3033,13 +3045,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46316.26041666666</v>
+        <v>46320.21875</v>
       </c>
       <c r="B123">
-        <v>618.261</v>
+        <v>85.43300000000001</v>
       </c>
       <c r="C123">
-        <v>812</v>
+        <v>5</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3050,13 +3062,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46316.27083333334</v>
+        <v>46320.22916666666</v>
       </c>
       <c r="B124">
-        <v>630.205</v>
+        <v>84.491</v>
       </c>
       <c r="C124">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3067,13 +3079,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46316.28125</v>
+        <v>46320.23958333334</v>
       </c>
       <c r="B125">
-        <v>631.958</v>
+        <v>84.071</v>
       </c>
       <c r="C125">
-        <v>839</v>
+        <v>0</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3084,13 +3096,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46316.29166666666</v>
+        <v>46320.25</v>
       </c>
       <c r="B126">
-        <v>609.3630000000001</v>
+        <v>88.056</v>
       </c>
       <c r="C126">
-        <v>851</v>
+        <v>0</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3101,13 +3113,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46316.30208333334</v>
+        <v>46320.26041666666</v>
       </c>
       <c r="B127">
-        <v>612.254</v>
+        <v>88.148</v>
       </c>
       <c r="C127">
-        <v>847</v>
+        <v>12</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3118,13 +3130,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46316.3125</v>
+        <v>46320.27083333334</v>
       </c>
       <c r="B128">
-        <v>625.27</v>
+        <v>90.55</v>
       </c>
       <c r="C128">
-        <v>864</v>
+        <v>20</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3135,13 +3147,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46316.32291666666</v>
+        <v>46320.28125</v>
       </c>
       <c r="B129">
-        <v>626.982</v>
+        <v>92.47</v>
       </c>
       <c r="C129">
-        <v>834</v>
+        <v>26</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3152,13 +3164,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46316.33333333334</v>
+        <v>46320.29166666666</v>
       </c>
       <c r="B130">
-        <v>699.966</v>
+        <v>94.08199999999999</v>
       </c>
       <c r="C130">
-        <v>798</v>
+        <v>17</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3169,13 +3181,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46316.34375</v>
+        <v>46320.30208333334</v>
       </c>
       <c r="B131">
-        <v>700.119</v>
+        <v>94.273</v>
       </c>
       <c r="C131">
-        <v>763</v>
+        <v>11</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3186,13 +3198,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46316.35416666666</v>
+        <v>46320.3125</v>
       </c>
       <c r="B132">
-        <v>701.492</v>
+        <v>94.673</v>
       </c>
       <c r="C132">
-        <v>705</v>
+        <v>18</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3203,10 +3215,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46316.36458333334</v>
+        <v>46320.32291666666</v>
       </c>
       <c r="B133">
-        <v>697.279</v>
+        <v>94.95699999999999</v>
+      </c>
+      <c r="C133">
+        <v>26</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3217,10 +3232,10 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46316.375</v>
+        <v>46320.33333333334</v>
       </c>
       <c r="B134">
-        <v>667.239</v>
+        <v>96.02500000000001</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3231,10 +3246,10 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46316.38541666666</v>
+        <v>46320.34375</v>
       </c>
       <c r="B135">
-        <v>684.149</v>
+        <v>97.774</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3245,10 +3260,10 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46316.39583333334</v>
+        <v>46320.35416666666</v>
       </c>
       <c r="B136">
-        <v>698.453</v>
+        <v>98.64</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3259,10 +3274,10 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46316.40625</v>
+        <v>46320.36458333334</v>
       </c>
       <c r="B137">
-        <v>713.4450000000001</v>
+        <v>99.28100000000001</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3273,10 +3288,10 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46316.41666666666</v>
+        <v>46320.375</v>
       </c>
       <c r="B138">
-        <v>705.95</v>
+        <v>101.16</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3287,10 +3302,10 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46316.42708333334</v>
+        <v>46320.38541666666</v>
       </c>
       <c r="B139">
-        <v>721.025</v>
+        <v>108.173</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3301,10 +3316,10 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46316.4375</v>
+        <v>46320.39583333334</v>
       </c>
       <c r="B140">
-        <v>736.481</v>
+        <v>111.458</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3315,10 +3330,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46316.44791666666</v>
+        <v>46320.40625</v>
       </c>
       <c r="B141">
-        <v>748.211</v>
+        <v>115.179</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3329,10 +3344,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46316.45833333334</v>
+        <v>46320.41666666666</v>
       </c>
       <c r="B142">
-        <v>800.8</v>
+        <v>119.995</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3343,10 +3358,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46316.46875</v>
+        <v>46320.42708333334</v>
       </c>
       <c r="B143">
-        <v>814.471</v>
+        <v>124.17</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3357,10 +3372,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46316.47916666666</v>
+        <v>46320.4375</v>
       </c>
       <c r="B144">
-        <v>841.831</v>
+        <v>127.471</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3371,10 +3386,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46316.48958333334</v>
+        <v>46320.44791666666</v>
       </c>
       <c r="B145">
-        <v>854.605</v>
+        <v>130.574</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3385,10 +3400,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46316.5</v>
+        <v>46320.45833333334</v>
       </c>
       <c r="B146">
-        <v>881.051</v>
+        <v>133.123</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3399,10 +3414,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46316.51041666666</v>
+        <v>46320.46875</v>
       </c>
       <c r="B147">
-        <v>895.157</v>
+        <v>135.721</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3413,10 +3428,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46316.52083333334</v>
+        <v>46320.47916666666</v>
       </c>
       <c r="B148">
-        <v>909.141</v>
+        <v>137.915</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3427,10 +3442,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46316.53125</v>
+        <v>46320.48958333334</v>
       </c>
       <c r="B149">
-        <v>923.009</v>
+        <v>140.452</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3441,10 +3456,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46316.54166666666</v>
+        <v>46320.5</v>
       </c>
       <c r="B150">
-        <v>942.269</v>
+        <v>143.141</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3455,10 +3470,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46316.55208333334</v>
+        <v>46320.51041666666</v>
       </c>
       <c r="B151">
-        <v>957.739</v>
+        <v>146.106</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3469,10 +3484,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46316.5625</v>
+        <v>46320.52083333334</v>
       </c>
       <c r="B152">
-        <v>973.726</v>
+        <v>148.758</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3483,10 +3498,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46316.57291666666</v>
+        <v>46320.53125</v>
       </c>
       <c r="B153">
-        <v>990.8869999999999</v>
+        <v>151.472</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3497,10 +3512,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46316.58333333334</v>
+        <v>46320.54166666666</v>
       </c>
       <c r="B154">
-        <v>1044.467</v>
+        <v>152.468</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3511,10 +3526,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46316.59375</v>
+        <v>46320.55208333334</v>
       </c>
       <c r="B155">
-        <v>1072.247</v>
+        <v>154.53</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3525,10 +3540,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46316.60416666666</v>
+        <v>46320.5625</v>
       </c>
       <c r="B156">
-        <v>1098.085</v>
+        <v>156.772</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3539,10 +3554,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46316.61458333334</v>
+        <v>46320.57291666666</v>
       </c>
       <c r="B157">
-        <v>1123.953</v>
+        <v>159.02</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3553,10 +3568,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46316.625</v>
+        <v>46320.58333333334</v>
       </c>
       <c r="B158">
-        <v>1108.464</v>
+        <v>163.131</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3567,10 +3582,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46316.63541666666</v>
+        <v>46320.59375</v>
       </c>
       <c r="B159">
-        <v>1137.986</v>
+        <v>165.161</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3581,10 +3596,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46316.64583333334</v>
+        <v>46320.60416666666</v>
       </c>
       <c r="B160">
-        <v>1168.455</v>
+        <v>167.569</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3595,10 +3610,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46316.65625</v>
+        <v>46320.61458333334</v>
       </c>
       <c r="B161">
-        <v>1194.973</v>
+        <v>173.015</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3609,10 +3624,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46316.66666666666</v>
+        <v>46320.625</v>
       </c>
       <c r="B162">
-        <v>1212.557</v>
+        <v>180.234</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -3623,10 +3638,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46316.67708333334</v>
+        <v>46320.63541666666</v>
       </c>
       <c r="B163">
-        <v>1252.87</v>
+        <v>190.504</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -3637,10 +3652,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46316.6875</v>
+        <v>46320.64583333334</v>
       </c>
       <c r="B164">
-        <v>1289.963</v>
+        <v>200.692</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -3651,10 +3666,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46316.69791666666</v>
+        <v>46320.65625</v>
       </c>
       <c r="B165">
-        <v>1320.553</v>
+        <v>210.96</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -3665,10 +3680,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46316.70833333334</v>
+        <v>46320.66666666666</v>
       </c>
       <c r="B166">
-        <v>1369.452</v>
+        <v>225.598</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -3679,10 +3694,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46316.71875</v>
+        <v>46320.67708333334</v>
       </c>
       <c r="B167">
-        <v>1404.117</v>
+        <v>239.99</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -3693,10 +3708,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46316.72916666666</v>
+        <v>46320.6875</v>
       </c>
       <c r="B168">
-        <v>1443.435</v>
+        <v>254.72</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -3707,10 +3722,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46316.73958333334</v>
+        <v>46320.69791666666</v>
       </c>
       <c r="B169">
-        <v>1480.117</v>
+        <v>269.035</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -3721,10 +3736,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46316.75</v>
+        <v>46320.70833333334</v>
       </c>
       <c r="B170">
-        <v>1574.901</v>
+        <v>288.274</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -3735,10 +3750,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46316.76041666666</v>
+        <v>46320.71875</v>
       </c>
       <c r="B171">
-        <v>1590.373</v>
+        <v>302.36</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -3749,10 +3764,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46316.77083333334</v>
+        <v>46320.72916666666</v>
       </c>
       <c r="B172">
-        <v>1606.308</v>
+        <v>316.69</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -3763,10 +3778,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46316.78125</v>
+        <v>46320.73958333334</v>
       </c>
       <c r="B173">
-        <v>1621.973</v>
+        <v>331.476</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -3777,10 +3792,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46316.79166666666</v>
+        <v>46320.75</v>
       </c>
       <c r="B174">
-        <v>1667.364</v>
+        <v>346.991</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -3791,10 +3806,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46316.80208333334</v>
+        <v>46320.76041666666</v>
       </c>
       <c r="B175">
-        <v>1677.171</v>
+        <v>359.803</v>
       </c>
       <c r="D175">
         <v>78</v>
@@ -3805,10 +3820,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46316.8125</v>
+        <v>46320.77083333334</v>
       </c>
       <c r="B176">
-        <v>1683.382</v>
+        <v>372.271</v>
       </c>
       <c r="D176">
         <v>79</v>
@@ -3819,10 +3834,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46316.82291666666</v>
+        <v>46320.78125</v>
       </c>
       <c r="B177">
-        <v>1688.427</v>
+        <v>384.821</v>
       </c>
       <c r="D177">
         <v>80</v>
@@ -3833,10 +3848,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46316.83333333334</v>
+        <v>46320.79166666666</v>
       </c>
       <c r="B178">
-        <v>1688.314</v>
+        <v>398.206</v>
       </c>
       <c r="D178">
         <v>81</v>
@@ -3847,10 +3862,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46316.84375</v>
+        <v>46320.80208333334</v>
       </c>
       <c r="B179">
-        <v>1692.062</v>
+        <v>408.986</v>
       </c>
       <c r="D179">
         <v>82</v>
@@ -3861,10 +3876,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46316.85416666666</v>
+        <v>46320.8125</v>
       </c>
       <c r="B180">
-        <v>1691.531</v>
+        <v>420.397</v>
       </c>
       <c r="D180">
         <v>83</v>
@@ -3875,10 +3890,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46316.86458333334</v>
+        <v>46320.82291666666</v>
       </c>
       <c r="B181">
-        <v>1689.731</v>
+        <v>430.428</v>
       </c>
       <c r="D181">
         <v>84</v>
@@ -3889,10 +3904,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46316.875</v>
+        <v>46320.83333333334</v>
       </c>
       <c r="B182">
-        <v>1688.268</v>
+        <v>439.448</v>
       </c>
       <c r="D182">
         <v>85</v>
@@ -3903,10 +3918,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46316.88541666666</v>
+        <v>46320.84375</v>
       </c>
       <c r="B183">
-        <v>1689.631</v>
+        <v>442.483</v>
       </c>
       <c r="D183">
         <v>86</v>
@@ -3917,10 +3932,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46316.89583333334</v>
+        <v>46320.85416666666</v>
       </c>
       <c r="B184">
-        <v>1692.048</v>
+        <v>444.649</v>
       </c>
       <c r="D184">
         <v>87</v>
@@ -3931,10 +3946,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46316.90625</v>
+        <v>46320.86458333334</v>
       </c>
       <c r="B185">
-        <v>1692.881</v>
+        <v>447.371</v>
       </c>
       <c r="D185">
         <v>88</v>
@@ -3945,10 +3960,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46316.91666666666</v>
+        <v>46320.875</v>
       </c>
       <c r="B186">
-        <v>1666.074</v>
+        <v>445.992</v>
       </c>
       <c r="D186">
         <v>89</v>
@@ -3959,10 +3974,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46316.92708333334</v>
+        <v>46320.88541666666</v>
       </c>
       <c r="B187">
-        <v>1664.411</v>
+        <v>444.703</v>
       </c>
       <c r="D187">
         <v>90</v>
@@ -3973,10 +3988,10 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46316.9375</v>
+        <v>46320.89583333334</v>
       </c>
       <c r="B188">
-        <v>1667.802</v>
+        <v>440.457</v>
       </c>
       <c r="D188">
         <v>91</v>
@@ -3987,16 +4002,72 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46316.94791666666</v>
+        <v>46320.90625</v>
       </c>
       <c r="B189">
-        <v>1674.037</v>
+        <v>439.466</v>
       </c>
       <c r="D189">
         <v>92</v>
       </c>
       <c r="E189" t="s">
         <v>192</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190" s="2">
+        <v>46320.91666666666</v>
+      </c>
+      <c r="B190">
+        <v>431.57</v>
+      </c>
+      <c r="D190">
+        <v>93</v>
+      </c>
+      <c r="E190" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191" s="2">
+        <v>46320.92708333334</v>
+      </c>
+      <c r="B191">
+        <v>424.995</v>
+      </c>
+      <c r="D191">
+        <v>94</v>
+      </c>
+      <c r="E191" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192" s="2">
+        <v>46320.9375</v>
+      </c>
+      <c r="B192">
+        <v>421.639</v>
+      </c>
+      <c r="D192">
+        <v>95</v>
+      </c>
+      <c r="E192" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193" s="2">
+        <v>46320.94791666666</v>
+      </c>
+      <c r="B193">
+        <v>420.161</v>
+      </c>
+      <c r="D193">
+        <v>96</v>
+      </c>
+      <c r="E193" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
